--- a/Result/analyze_2.xlsx
+++ b/Result/analyze_2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L174"/>
+  <dimension ref="A1:J174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,57 +436,47 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
+          <t>2026-10-02</t>
         </is>
       </c>
     </row>
@@ -496,36 +486,32 @@
           <t>光電業右上上市</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="n">
+        <v>65690.527527</v>
+      </c>
       <c r="C2" t="n">
-        <v>69168.480648</v>
+        <v>78279.22962899999</v>
       </c>
       <c r="D2" t="n">
-        <v>51339.237087</v>
+        <v>115422.481566</v>
       </c>
       <c r="E2" t="n">
-        <v>76992.72938800001</v>
+        <v>75436.525366</v>
       </c>
       <c r="F2" t="n">
-        <v>98232.588972</v>
+        <v>46586.686312</v>
       </c>
       <c r="G2" t="n">
-        <v>53479.659015</v>
+        <v>51847.523042</v>
       </c>
       <c r="H2" t="n">
-        <v>65558.47786</v>
+        <v>86070.802371</v>
       </c>
       <c r="I2" t="n">
-        <v>60868.608004</v>
+        <v>106432.610774</v>
       </c>
       <c r="J2" t="n">
-        <v>75009.490121</v>
-      </c>
-      <c r="K2" t="n">
-        <v>47917.761202</v>
-      </c>
-      <c r="L2" t="n">
-        <v>43739.746014</v>
+        <v>74175.14004899999</v>
       </c>
     </row>
     <row r="3">
@@ -534,36 +520,32 @@
           <t>光電業右上上櫃</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="n">
+        <v>7.587945</v>
+      </c>
       <c r="C3" t="n">
-        <v>4.014865</v>
+        <v>7.202591</v>
       </c>
       <c r="D3" t="n">
-        <v>7.717198</v>
+        <v>4.93632</v>
       </c>
       <c r="E3" t="n">
-        <v>10.306841</v>
+        <v>1.988611</v>
       </c>
       <c r="F3" t="n">
-        <v>8.042102999999999</v>
+        <v>4.200368</v>
       </c>
       <c r="G3" t="n">
-        <v>8.449287</v>
+        <v>6.813472</v>
       </c>
       <c r="H3" t="n">
-        <v>9.494458</v>
+        <v>6.721156</v>
       </c>
       <c r="I3" t="n">
-        <v>11.088317</v>
+        <v>6.072605</v>
       </c>
       <c r="J3" t="n">
-        <v>9.393929999999999</v>
-      </c>
-      <c r="K3" t="n">
-        <v>4.823701</v>
-      </c>
-      <c r="L3" t="n">
-        <v>2.50486</v>
+        <v>12.53609</v>
       </c>
     </row>
     <row r="4">
@@ -572,36 +554,32 @@
           <t>光電業右下上市</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="n">
+        <v>1218.572409</v>
+      </c>
       <c r="C4" t="n">
-        <v>504.591504</v>
+        <v>1113.648427</v>
       </c>
       <c r="D4" t="n">
-        <v>868.082949</v>
+        <v>2192.450429</v>
       </c>
       <c r="E4" t="n">
-        <v>979.19547175</v>
+        <v>1103.326977</v>
       </c>
       <c r="F4" t="n">
-        <v>796.455411</v>
+        <v>1742.305728</v>
       </c>
       <c r="G4" t="n">
-        <v>463.744138</v>
+        <v>898.356579</v>
       </c>
       <c r="H4" t="n">
-        <v>407.279628</v>
+        <v>1542.59659</v>
       </c>
       <c r="I4" t="n">
-        <v>513.93569</v>
+        <v>627.005644</v>
       </c>
       <c r="J4" t="n">
-        <v>910.819295</v>
-      </c>
-      <c r="K4" t="n">
-        <v>483.783495</v>
-      </c>
-      <c r="L4" t="n">
-        <v>371.409726</v>
+        <v>809.753993</v>
       </c>
     </row>
     <row r="5">
@@ -611,37 +589,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1.65914</v>
       </c>
       <c r="C5" t="n">
-        <v>0.057714</v>
+        <v>1.232648</v>
       </c>
       <c r="D5" t="n">
-        <v>0.093448</v>
+        <v>1.026978</v>
       </c>
       <c r="E5" t="n">
-        <v>0.099763</v>
+        <v>1.008579</v>
       </c>
       <c r="F5" t="n">
-        <v>0.106089</v>
+        <v>0.944307</v>
       </c>
       <c r="G5" t="n">
-        <v>0.073877</v>
+        <v>1.39092525</v>
       </c>
       <c r="H5" t="n">
-        <v>0.06838</v>
+        <v>0.866345</v>
       </c>
       <c r="I5" t="n">
-        <v>0.099899</v>
+        <v>0.9060865</v>
       </c>
       <c r="J5" t="n">
-        <v>0.166633</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1.442518</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.169018</v>
+        <v>0.9748790000000001</v>
       </c>
     </row>
     <row r="6">
@@ -650,36 +622,32 @@
           <t>光電業平上市</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="n">
+        <v>2260.003599</v>
+      </c>
       <c r="C6" t="n">
-        <v>1160.478917</v>
+        <v>1925.604833</v>
       </c>
       <c r="D6" t="n">
-        <v>400.176465</v>
+        <v>3533.057299</v>
       </c>
       <c r="E6" t="n">
-        <v>424.527091</v>
+        <v>1768.985805</v>
       </c>
       <c r="F6" t="n">
-        <v>1193.047793</v>
+        <v>1177.860188</v>
       </c>
       <c r="G6" t="n">
-        <v>518.102108</v>
+        <v>656.082342</v>
       </c>
       <c r="H6" t="n">
-        <v>595.3650270000001</v>
+        <v>1194.916813</v>
       </c>
       <c r="I6" t="n">
-        <v>1741.646117</v>
+        <v>1063.781628</v>
       </c>
       <c r="J6" t="n">
-        <v>2213.390461</v>
-      </c>
-      <c r="K6" t="n">
-        <v>869.2434510000001</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1114.83443</v>
+        <v>1114.478124</v>
       </c>
     </row>
     <row r="7">
@@ -688,36 +656,32 @@
           <t>光電業平上櫃</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="B7" t="n">
+        <v>0.43081</v>
+      </c>
       <c r="C7" t="n">
-        <v>6.033637</v>
+        <v>0.285278</v>
       </c>
       <c r="D7" t="n">
-        <v>2.226799</v>
+        <v>0.684599</v>
       </c>
       <c r="E7" t="n">
-        <v>1.765912</v>
+        <v>0.510082</v>
       </c>
       <c r="F7" t="n">
-        <v>1.753688</v>
+        <v>0.936181</v>
       </c>
       <c r="G7" t="n">
-        <v>1.010952</v>
+        <v>0.22408</v>
       </c>
       <c r="H7" t="n">
-        <v>1.193793</v>
+        <v>0.507507</v>
       </c>
       <c r="I7" t="n">
-        <v>0.883117</v>
+        <v>0.161472</v>
       </c>
       <c r="J7" t="n">
-        <v>1.482621</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.049452</v>
-      </c>
-      <c r="L7" t="n">
-        <v>3.213919</v>
+        <v>0.230956</v>
       </c>
     </row>
     <row r="8">
@@ -726,36 +690,32 @@
           <t>其他右上上市</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" t="n">
+        <v>1055.206274</v>
+      </c>
       <c r="C8" t="n">
-        <v>10455.685047</v>
+        <v>820.930312</v>
       </c>
       <c r="D8" t="n">
-        <v>3434.856333</v>
+        <v>708.754765</v>
       </c>
       <c r="E8" t="n">
-        <v>2887.410651</v>
+        <v>695.467022</v>
       </c>
       <c r="F8" t="n">
-        <v>2528.599976</v>
+        <v>804.3266159999999</v>
       </c>
       <c r="G8" t="n">
-        <v>2491.855395</v>
+        <v>945.081587</v>
       </c>
       <c r="H8" t="n">
-        <v>2227.326645</v>
+        <v>1026.433541</v>
       </c>
       <c r="I8" t="n">
-        <v>3155.464235</v>
+        <v>1319.534296</v>
       </c>
       <c r="J8" t="n">
-        <v>4151.812266</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2784.693071</v>
-      </c>
-      <c r="L8" t="n">
-        <v>3098.974922</v>
+        <v>1653.5761</v>
       </c>
     </row>
     <row r="9">
@@ -764,36 +724,32 @@
           <t>其他右上上櫃</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="n">
+        <v>3.467932</v>
+      </c>
       <c r="C9" t="n">
-        <v>1.228061</v>
+        <v>2.240566666666667</v>
       </c>
       <c r="D9" t="n">
-        <v>1.126605</v>
+        <v>1.733862</v>
       </c>
       <c r="E9" t="n">
-        <v>1.537084</v>
+        <v>4.251473</v>
       </c>
       <c r="F9" t="n">
-        <v>1.266028</v>
+        <v>1.366303</v>
       </c>
       <c r="G9" t="n">
-        <v>1.197983</v>
+        <v>1.71218</v>
       </c>
       <c r="H9" t="n">
-        <v>1.08820875</v>
+        <v>1.99472</v>
       </c>
       <c r="I9" t="n">
-        <v>0.788064</v>
+        <v>1.926111</v>
       </c>
       <c r="J9" t="n">
-        <v>3.101578</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1.477490666666667</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.799196</v>
+        <v>1.867746</v>
       </c>
     </row>
     <row r="10">
@@ -802,36 +758,32 @@
           <t>其他右下上市</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="n">
+        <v>241.472439</v>
+      </c>
       <c r="C10" t="n">
-        <v>1550.588148</v>
+        <v>209.442973</v>
       </c>
       <c r="D10" t="n">
-        <v>1365.063561</v>
+        <v>1887.073794</v>
       </c>
       <c r="E10" t="n">
-        <v>1230.212064</v>
+        <v>1367.403104</v>
       </c>
       <c r="F10" t="n">
-        <v>967.773148</v>
+        <v>821.838253</v>
       </c>
       <c r="G10" t="n">
-        <v>718.16815</v>
+        <v>957.630659</v>
       </c>
       <c r="H10" t="n">
-        <v>634.794416</v>
+        <v>1092.657216</v>
       </c>
       <c r="I10" t="n">
-        <v>976.093147</v>
+        <v>1151.470527</v>
       </c>
       <c r="J10" t="n">
-        <v>773.893277</v>
-      </c>
-      <c r="K10" t="n">
-        <v>712.3047769999999</v>
-      </c>
-      <c r="L10" t="n">
-        <v>933.558506</v>
+        <v>1061.894658</v>
       </c>
     </row>
     <row r="11">
@@ -840,36 +792,32 @@
           <t>其他右下上櫃</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="n">
+        <v>3.741591</v>
+      </c>
       <c r="C11" t="n">
-        <v>0.530554</v>
+        <v>4.223545</v>
       </c>
       <c r="D11" t="n">
-        <v>2.214575</v>
+        <v>0.7884640000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>2.569927</v>
+        <v>0.36906525</v>
       </c>
       <c r="F11" t="n">
-        <v>0.924262</v>
+        <v>0.2415985</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6534285</v>
+        <v>0.308221</v>
       </c>
       <c r="H11" t="n">
-        <v>0.456652</v>
+        <v>0.341959</v>
       </c>
       <c r="I11" t="n">
-        <v>0.659567</v>
+        <v>2.512299</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8596780000000001</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.502216</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.280239</v>
+        <v>0.9608650833333334</v>
       </c>
     </row>
     <row r="12">
@@ -878,36 +826,32 @@
           <t>其他平上市</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="n">
+        <v>1355.467353</v>
+      </c>
       <c r="C12" t="n">
-        <v>984.982545</v>
+        <v>1098.174253</v>
       </c>
       <c r="D12" t="n">
-        <v>37.87701</v>
+        <v>368.675684</v>
       </c>
       <c r="E12" t="n">
-        <v>651.699239</v>
+        <v>281.544287</v>
       </c>
       <c r="F12" t="n">
-        <v>691.7281829999999</v>
+        <v>142.31445</v>
       </c>
       <c r="G12" t="n">
-        <v>528.451283</v>
+        <v>164.8614</v>
       </c>
       <c r="H12" t="n">
-        <v>663.853909</v>
+        <v>148.657663</v>
       </c>
       <c r="I12" t="n">
-        <v>216.742554</v>
+        <v>246.467539</v>
       </c>
       <c r="J12" t="n">
-        <v>117.663621</v>
-      </c>
-      <c r="K12" t="n">
-        <v>196.932976</v>
-      </c>
-      <c r="L12" t="n">
-        <v>157.673957</v>
+        <v>179.031457</v>
       </c>
     </row>
     <row r="13">
@@ -916,36 +860,32 @@
           <t>其他平上櫃</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
+      <c r="B13" t="n">
+        <v>0.16779</v>
+      </c>
       <c r="C13" t="n">
-        <v>0.014069</v>
+        <v>0.108556</v>
       </c>
       <c r="D13" t="n">
-        <v>0.025796</v>
+        <v>0.045488</v>
       </c>
       <c r="E13" t="n">
-        <v>0.158404</v>
+        <v>0.053156</v>
       </c>
       <c r="F13" t="n">
-        <v>0.198724</v>
+        <v>0.07677200000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0435</v>
+        <v>0.073134</v>
       </c>
       <c r="H13" t="n">
-        <v>0.116057</v>
+        <v>0.10516</v>
       </c>
       <c r="I13" t="n">
-        <v>0.235033</v>
+        <v>0.0696565</v>
       </c>
       <c r="J13" t="n">
-        <v>0.202822</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.22255025</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.1309816666666667</v>
+        <v>0.085149</v>
       </c>
     </row>
     <row r="14">
@@ -954,36 +894,32 @@
           <t>其他電子業右上上市</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
+      <c r="B14" t="n">
+        <v>51547.946181</v>
+      </c>
       <c r="C14" t="n">
-        <v>59625.935369</v>
+        <v>35334.124465</v>
       </c>
       <c r="D14" t="n">
-        <v>43652.759162</v>
+        <v>43866.035113</v>
       </c>
       <c r="E14" t="n">
-        <v>34155.24931</v>
+        <v>39906.027565</v>
       </c>
       <c r="F14" t="n">
-        <v>43577.081949</v>
+        <v>36079.271484</v>
       </c>
       <c r="G14" t="n">
-        <v>39774.577222</v>
+        <v>35352.869423</v>
       </c>
       <c r="H14" t="n">
-        <v>28423.700467</v>
+        <v>43844.505121</v>
       </c>
       <c r="I14" t="n">
-        <v>30467.527962</v>
+        <v>33855.922663</v>
       </c>
       <c r="J14" t="n">
-        <v>34146.377443</v>
-      </c>
-      <c r="K14" t="n">
-        <v>31910.469771</v>
-      </c>
-      <c r="L14" t="n">
-        <v>33477.207812</v>
+        <v>39818.732</v>
       </c>
     </row>
     <row r="15">
@@ -992,36 +928,32 @@
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
+      <c r="B15" t="n">
+        <v>14.315344</v>
+      </c>
       <c r="C15" t="n">
-        <v>12.303118</v>
+        <v>7.751108</v>
       </c>
       <c r="D15" t="n">
-        <v>14.822481</v>
+        <v>11.431169</v>
       </c>
       <c r="E15" t="n">
-        <v>10.833339</v>
+        <v>9.114428</v>
       </c>
       <c r="F15" t="n">
-        <v>10.952274</v>
+        <v>13.437214</v>
       </c>
       <c r="G15" t="n">
-        <v>6.808917</v>
+        <v>8.991203000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>5.220246</v>
+        <v>10.506049</v>
       </c>
       <c r="I15" t="n">
-        <v>8.117222</v>
+        <v>6.719846</v>
       </c>
       <c r="J15" t="n">
-        <v>7.509871</v>
-      </c>
-      <c r="K15" t="n">
-        <v>4.997421</v>
-      </c>
-      <c r="L15" t="n">
-        <v>4.452962</v>
+        <v>7.302763</v>
       </c>
     </row>
     <row r="16">
@@ -1031,37 +963,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>234.284746</v>
       </c>
       <c r="C16" t="n">
-        <v>406.570727</v>
+        <v>156.381504</v>
       </c>
       <c r="D16" t="n">
-        <v>253.339272</v>
+        <v>206.00848</v>
       </c>
       <c r="E16" t="n">
-        <v>3227.616167</v>
+        <v>156.812233</v>
       </c>
       <c r="F16" t="n">
-        <v>1779.706425</v>
+        <v>122.867876</v>
       </c>
       <c r="G16" t="n">
-        <v>1462.475906</v>
+        <v>175.389483</v>
       </c>
       <c r="H16" t="n">
-        <v>1028.621264</v>
+        <v>168.399942</v>
       </c>
       <c r="I16" t="n">
-        <v>1264.64228</v>
+        <v>163.335916</v>
       </c>
       <c r="J16" t="n">
-        <v>1753.087911</v>
-      </c>
-      <c r="K16" t="n">
-        <v>855.163878</v>
-      </c>
-      <c r="L16" t="n">
-        <v>866.556647</v>
+        <v>192.89349</v>
       </c>
     </row>
     <row r="17">
@@ -1071,37 +997,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>0.491751</v>
       </c>
       <c r="C17" t="n">
-        <v>0.019862</v>
+        <v>0.184766</v>
       </c>
       <c r="D17" t="n">
-        <v>0.036515</v>
+        <v>0.2174656666666667</v>
       </c>
       <c r="E17" t="n">
-        <v>0.071225</v>
+        <v>0.184608</v>
       </c>
       <c r="F17" t="n">
-        <v>0.089419</v>
+        <v>0.238945</v>
       </c>
       <c r="G17" t="n">
-        <v>0.07406699999999999</v>
+        <v>0.102638</v>
       </c>
       <c r="H17" t="n">
-        <v>0.034059</v>
+        <v>0.075781</v>
       </c>
       <c r="I17" t="n">
-        <v>0.070603</v>
+        <v>0.087064</v>
       </c>
       <c r="J17" t="n">
-        <v>0.105059</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.028571</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.035706</v>
+        <v>0.114932</v>
       </c>
     </row>
     <row r="18">
@@ -1110,36 +1030,32 @@
           <t>其他電子業平上市</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
+      <c r="B18" t="n">
+        <v>2074.881403</v>
+      </c>
       <c r="C18" t="n">
-        <v>1625.929747</v>
+        <v>2251.592724</v>
       </c>
       <c r="D18" t="n">
-        <v>1466.729563</v>
+        <v>2269.923561</v>
       </c>
       <c r="E18" t="n">
-        <v>654.634944</v>
+        <v>1069.607557</v>
       </c>
       <c r="F18" t="n">
-        <v>700.525491</v>
+        <v>733.0549140000001</v>
       </c>
       <c r="G18" t="n">
-        <v>571.452897</v>
+        <v>1399.054171</v>
       </c>
       <c r="H18" t="n">
-        <v>1069.367627</v>
+        <v>662.797492</v>
       </c>
       <c r="I18" t="n">
-        <v>1679.51224</v>
+        <v>756.907611</v>
       </c>
       <c r="J18" t="n">
-        <v>2272.76142</v>
-      </c>
-      <c r="K18" t="n">
-        <v>958.421424</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1099.228037</v>
+        <v>1625.270931</v>
       </c>
     </row>
     <row r="19">
@@ -1148,36 +1064,32 @@
           <t>其他電子業平上櫃</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
+      <c r="B19" t="n">
+        <v>1.982743</v>
+      </c>
       <c r="C19" t="n">
-        <v>0.009253000000000001</v>
+        <v>2.216785</v>
       </c>
       <c r="D19" t="n">
-        <v>0.025883</v>
+        <v>3.218028</v>
       </c>
       <c r="E19" t="n">
-        <v>0.020441</v>
+        <v>2.334074</v>
       </c>
       <c r="F19" t="n">
-        <v>0.142561</v>
+        <v>1.500443</v>
       </c>
       <c r="G19" t="n">
-        <v>3.479031</v>
+        <v>1.856242</v>
       </c>
       <c r="H19" t="n">
-        <v>1.487429</v>
+        <v>3.652731</v>
       </c>
       <c r="I19" t="n">
-        <v>1.228883</v>
+        <v>3.487986</v>
       </c>
       <c r="J19" t="n">
-        <v>2.433707</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1.090637</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1.523459</v>
+        <v>3.057712</v>
       </c>
     </row>
     <row r="20">
@@ -1186,36 +1098,32 @@
           <t>化學工業右上上市</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
+      <c r="B20" t="n">
+        <v>6032.167382</v>
+      </c>
       <c r="C20" t="n">
-        <v>5299.27521</v>
+        <v>4010.314605</v>
       </c>
       <c r="D20" t="n">
-        <v>12380.099104</v>
+        <v>5364.965027</v>
       </c>
       <c r="E20" t="n">
-        <v>22175.765727</v>
+        <v>8292.582050000001</v>
       </c>
       <c r="F20" t="n">
-        <v>11365.246151</v>
+        <v>9882.511367999999</v>
       </c>
       <c r="G20" t="n">
-        <v>4890.397271</v>
+        <v>6355.062814</v>
       </c>
       <c r="H20" t="n">
-        <v>4392.357889</v>
+        <v>8542.054827</v>
       </c>
       <c r="I20" t="n">
-        <v>4447.503083</v>
+        <v>5022.470767</v>
       </c>
       <c r="J20" t="n">
-        <v>5397.389361</v>
-      </c>
-      <c r="K20" t="n">
-        <v>3747.004098</v>
-      </c>
-      <c r="L20" t="n">
-        <v>2845.161608</v>
+        <v>10431.09168</v>
       </c>
     </row>
     <row r="21">
@@ -1224,36 +1132,32 @@
           <t>化學工業右上上櫃</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="n">
+        <v>0.079762</v>
+      </c>
       <c r="C21" t="n">
-        <v>0.918505</v>
+        <v>0.157836</v>
       </c>
       <c r="D21" t="n">
-        <v>1.229618</v>
+        <v>0.104806</v>
       </c>
       <c r="E21" t="n">
-        <v>1.417567</v>
+        <v>0.08237700000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>1.332957</v>
+        <v>0.129619</v>
       </c>
       <c r="G21" t="n">
-        <v>1.08941</v>
+        <v>0.08554200000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>0.42016</v>
+        <v>0.243057</v>
       </c>
       <c r="I21" t="n">
-        <v>0.359502</v>
+        <v>0.089675</v>
       </c>
       <c r="J21" t="n">
-        <v>0.413922</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.387048</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.472831</v>
+        <v>0.294889</v>
       </c>
     </row>
     <row r="22">
@@ -1262,36 +1166,32 @@
           <t>化學工業右下上市</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="n">
+        <v>207.753629</v>
+      </c>
       <c r="C22" t="n">
-        <v>60.802233</v>
+        <v>168.434019</v>
       </c>
       <c r="D22" t="n">
-        <v>143.23714</v>
+        <v>231.748497</v>
       </c>
       <c r="E22" t="n">
-        <v>90.160196</v>
+        <v>142.264442</v>
       </c>
       <c r="F22" t="n">
-        <v>62.894257</v>
+        <v>386.917159</v>
       </c>
       <c r="G22" t="n">
-        <v>79.55046900000001</v>
+        <v>174.154573</v>
       </c>
       <c r="H22" t="n">
-        <v>533.417289</v>
+        <v>137.624827</v>
       </c>
       <c r="I22" t="n">
-        <v>481.980651</v>
+        <v>104.854825</v>
       </c>
       <c r="J22" t="n">
-        <v>565.84085</v>
-      </c>
-      <c r="K22" t="n">
-        <v>321.590632</v>
-      </c>
-      <c r="L22" t="n">
-        <v>549.481547</v>
+        <v>196.898298</v>
       </c>
     </row>
     <row r="23">
@@ -1301,33 +1201,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>0.309473</v>
       </c>
       <c r="C23" t="n">
-        <v>0.00019</v>
+        <v>0.326445</v>
       </c>
       <c r="D23" t="n">
-        <v>0.000243</v>
-      </c>
-      <c r="E23" t="inlineStr"/>
+        <v>0.251038</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.425178</v>
+      </c>
       <c r="F23" t="n">
-        <v>0.000271</v>
+        <v>0.302992</v>
       </c>
       <c r="G23" t="n">
-        <v>0.000355</v>
+        <v>0.75597</v>
       </c>
       <c r="H23" t="n">
-        <v>0.000108</v>
-      </c>
-      <c r="I23" t="inlineStr"/>
+        <v>0.639278</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.2668</v>
+      </c>
       <c r="J23" t="n">
-        <v>3.3e-05</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0.00011</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0.000192</v>
+        <v>0.024437</v>
       </c>
     </row>
     <row r="24">
@@ -1336,36 +1234,32 @@
           <t>化學工業平上市</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="n">
+        <v>785.238852</v>
+      </c>
       <c r="C24" t="n">
-        <v>1023.732297</v>
+        <v>649.440349</v>
       </c>
       <c r="D24" t="n">
-        <v>1348.306685</v>
+        <v>1410.923435</v>
       </c>
       <c r="E24" t="n">
-        <v>861.940455</v>
+        <v>996.066389</v>
       </c>
       <c r="F24" t="n">
-        <v>650.580474</v>
+        <v>749.073516</v>
       </c>
       <c r="G24" t="n">
-        <v>680.759114</v>
+        <v>1063.384379</v>
       </c>
       <c r="H24" t="n">
-        <v>195.77703</v>
+        <v>1014.584463</v>
       </c>
       <c r="I24" t="n">
-        <v>110.224892</v>
+        <v>1574.244514</v>
       </c>
       <c r="J24" t="n">
-        <v>160.517001</v>
-      </c>
-      <c r="K24" t="n">
-        <v>128.366238</v>
-      </c>
-      <c r="L24" t="n">
-        <v>82.18592200000001</v>
+        <v>723.970323</v>
       </c>
     </row>
     <row r="25">
@@ -1374,36 +1268,32 @@
           <t>化學工業平上櫃</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
+      <c r="B25" t="n">
+        <v>0.052941</v>
+      </c>
       <c r="C25" t="n">
-        <v>0.000261</v>
+        <v>0.087949</v>
       </c>
       <c r="D25" t="n">
-        <v>0.000548</v>
+        <v>0.053762</v>
       </c>
       <c r="E25" t="n">
-        <v>0.000297</v>
+        <v>0.049746</v>
       </c>
       <c r="F25" t="n">
-        <v>0.000546</v>
+        <v>0.178292</v>
       </c>
       <c r="G25" t="n">
-        <v>0.000185</v>
+        <v>0.693905</v>
       </c>
       <c r="H25" t="n">
-        <v>9.1e-05</v>
+        <v>1.141352</v>
       </c>
       <c r="I25" t="n">
-        <v>0.000381</v>
+        <v>0.89294</v>
       </c>
       <c r="J25" t="n">
-        <v>0.088753</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0.046228</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0.0364</v>
+        <v>2.197642</v>
       </c>
     </row>
     <row r="26">
@@ -1412,36 +1302,32 @@
           <t>半導體業右上上市</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="n">
+        <v>418807.723536</v>
+      </c>
       <c r="C26" t="n">
-        <v>359997.189167</v>
+        <v>298551.554095</v>
       </c>
       <c r="D26" t="n">
-        <v>316518.144949</v>
+        <v>380269.750197</v>
       </c>
       <c r="E26" t="n">
-        <v>308334.2698</v>
+        <v>301340.906928</v>
       </c>
       <c r="F26" t="n">
-        <v>350446.438793</v>
+        <v>270822.403683</v>
       </c>
       <c r="G26" t="n">
-        <v>267674.445039</v>
+        <v>285493.879323</v>
       </c>
       <c r="H26" t="n">
-        <v>302704.207451</v>
+        <v>307574.643404</v>
       </c>
       <c r="I26" t="n">
-        <v>322031.804462</v>
+        <v>229451.108898</v>
       </c>
       <c r="J26" t="n">
-        <v>336524.499184</v>
-      </c>
-      <c r="K26" t="n">
-        <v>329032.181467</v>
-      </c>
-      <c r="L26" t="n">
-        <v>321480.84003</v>
+        <v>238507.170435</v>
       </c>
     </row>
     <row r="27">
@@ -1450,36 +1336,32 @@
           <t>半導體業右上上櫃</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
+      <c r="B27" t="n">
+        <v>128.575994</v>
+      </c>
       <c r="C27" t="n">
-        <v>118.671037</v>
+        <v>88.41125700000001</v>
       </c>
       <c r="D27" t="n">
-        <v>121.196987</v>
+        <v>155.644348</v>
       </c>
       <c r="E27" t="n">
-        <v>170.248849</v>
+        <v>154.61431</v>
       </c>
       <c r="F27" t="n">
-        <v>141.729285</v>
+        <v>90.226675</v>
       </c>
       <c r="G27" t="n">
-        <v>105.873119</v>
+        <v>79.75349</v>
       </c>
       <c r="H27" t="n">
-        <v>122.985507</v>
+        <v>123.720141</v>
       </c>
       <c r="I27" t="n">
-        <v>101.084237</v>
+        <v>128.156429</v>
       </c>
       <c r="J27" t="n">
-        <v>176.989199</v>
-      </c>
-      <c r="K27" t="n">
-        <v>126.842458</v>
-      </c>
-      <c r="L27" t="n">
-        <v>120.153324</v>
+        <v>116.521098</v>
       </c>
     </row>
     <row r="28">
@@ -1489,37 +1371,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>2197.74669</v>
       </c>
       <c r="C28" t="n">
-        <v>438.809247</v>
+        <v>814.063477</v>
       </c>
       <c r="D28" t="n">
-        <v>333.693449</v>
+        <v>3777.169563</v>
       </c>
       <c r="E28" t="n">
-        <v>950.827211</v>
+        <v>982.275547</v>
       </c>
       <c r="F28" t="n">
-        <v>805.604816</v>
+        <v>1190.705722</v>
       </c>
       <c r="G28" t="n">
-        <v>560.237463</v>
+        <v>1215.495016</v>
       </c>
       <c r="H28" t="n">
-        <v>633.046905</v>
+        <v>1089.004733</v>
       </c>
       <c r="I28" t="n">
-        <v>686.277766</v>
+        <v>957.057733</v>
       </c>
       <c r="J28" t="n">
-        <v>1735.457036</v>
-      </c>
-      <c r="K28" t="n">
-        <v>967.416278</v>
-      </c>
-      <c r="L28" t="n">
-        <v>1435.896374</v>
+        <v>621.03682</v>
       </c>
     </row>
     <row r="29">
@@ -1529,37 +1405,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>1.431211</v>
       </c>
       <c r="C29" t="n">
-        <v>0.197963</v>
+        <v>1.084483</v>
       </c>
       <c r="D29" t="n">
-        <v>0.241776</v>
+        <v>1.655492</v>
       </c>
       <c r="E29" t="n">
-        <v>0.08459999999999999</v>
+        <v>1.559106</v>
       </c>
       <c r="F29" t="n">
-        <v>0.7051685</v>
+        <v>0.8938</v>
       </c>
       <c r="G29" t="n">
-        <v>0.7437589999999999</v>
+        <v>3.88121825</v>
       </c>
       <c r="H29" t="n">
-        <v>0.59846</v>
+        <v>2.94116</v>
       </c>
       <c r="I29" t="n">
-        <v>1.55997</v>
+        <v>3.985883</v>
       </c>
       <c r="J29" t="n">
-        <v>1.594863</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0.901992</v>
-      </c>
-      <c r="L29" t="n">
-        <v>1.048053</v>
+        <v>4.884573</v>
       </c>
     </row>
     <row r="30">
@@ -1568,36 +1438,32 @@
           <t>半導體業平上市</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="n">
+        <v>48691.187002</v>
+      </c>
       <c r="C30" t="n">
-        <v>3527.901112</v>
+        <v>24145.954311</v>
       </c>
       <c r="D30" t="n">
-        <v>3937.161967</v>
+        <v>30973.84923</v>
       </c>
       <c r="E30" t="n">
-        <v>2505.491967</v>
+        <v>28779.054187</v>
       </c>
       <c r="F30" t="n">
-        <v>2471.756775</v>
+        <v>18447.333554</v>
       </c>
       <c r="G30" t="n">
-        <v>1800.370921</v>
+        <v>16209.80837</v>
       </c>
       <c r="H30" t="n">
-        <v>1366.335267</v>
+        <v>18913.857904</v>
       </c>
       <c r="I30" t="n">
-        <v>2678.616284</v>
+        <v>12874.398476</v>
       </c>
       <c r="J30" t="n">
-        <v>15529.111555</v>
-      </c>
-      <c r="K30" t="n">
-        <v>11868.786529</v>
-      </c>
-      <c r="L30" t="n">
-        <v>1193.602504</v>
+        <v>16711.163602</v>
       </c>
     </row>
     <row r="31">
@@ -1606,36 +1472,32 @@
           <t>半導體業平上櫃</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
+      <c r="B31" t="n">
+        <v>12.222525</v>
+      </c>
       <c r="C31" t="n">
-        <v>1.750297</v>
+        <v>12.01162</v>
       </c>
       <c r="D31" t="n">
-        <v>1.095022</v>
+        <v>8.919328999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>2.764585</v>
+        <v>7.408792</v>
       </c>
       <c r="F31" t="n">
-        <v>2.934657</v>
+        <v>9.363797</v>
       </c>
       <c r="G31" t="n">
-        <v>2.90803</v>
+        <v>8.949622</v>
       </c>
       <c r="H31" t="n">
-        <v>4.562035</v>
+        <v>16.412917</v>
       </c>
       <c r="I31" t="n">
-        <v>4.065158</v>
+        <v>14.89894</v>
       </c>
       <c r="J31" t="n">
-        <v>6.938099</v>
-      </c>
-      <c r="K31" t="n">
-        <v>3.633953</v>
-      </c>
-      <c r="L31" t="n">
-        <v>2.435817</v>
+        <v>10.004281</v>
       </c>
     </row>
     <row r="32">
@@ -1644,36 +1506,32 @@
           <t>塑膠工業右上上市</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="n">
+        <v>24775.24986</v>
+      </c>
       <c r="C32" t="n">
-        <v>23079.477803</v>
+        <v>14556.142562</v>
       </c>
       <c r="D32" t="n">
-        <v>31707.111188</v>
+        <v>20403.743481</v>
       </c>
       <c r="E32" t="n">
-        <v>24897.205775</v>
+        <v>15904.156976</v>
       </c>
       <c r="F32" t="n">
-        <v>15234.45657</v>
+        <v>18414.422521</v>
       </c>
       <c r="G32" t="n">
-        <v>30855.574013</v>
+        <v>23993.723144</v>
       </c>
       <c r="H32" t="n">
-        <v>31202.061175</v>
+        <v>38398.115906</v>
       </c>
       <c r="I32" t="n">
-        <v>28235.302984</v>
+        <v>17613.517817</v>
       </c>
       <c r="J32" t="n">
-        <v>47302.0593</v>
-      </c>
-      <c r="K32" t="n">
-        <v>54383.704651</v>
-      </c>
-      <c r="L32" t="n">
-        <v>47435.697731</v>
+        <v>17741.971142</v>
       </c>
     </row>
     <row r="33">
@@ -1682,36 +1540,32 @@
           <t>塑膠工業右下上市</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
+      <c r="B33" t="n">
+        <v>86.327966</v>
+      </c>
       <c r="C33" t="n">
-        <v>24.500432</v>
+        <v>38.665136</v>
       </c>
       <c r="D33" t="n">
-        <v>18.906877</v>
+        <v>43.737029</v>
       </c>
       <c r="E33" t="n">
-        <v>17.303578</v>
+        <v>26.41518</v>
       </c>
       <c r="F33" t="n">
-        <v>10.807483</v>
+        <v>21.393921</v>
       </c>
       <c r="G33" t="n">
-        <v>59.38141</v>
+        <v>39.355459</v>
       </c>
       <c r="H33" t="n">
-        <v>42.797866</v>
+        <v>34.904345</v>
       </c>
       <c r="I33" t="n">
-        <v>46.846058</v>
+        <v>28.912333</v>
       </c>
       <c r="J33" t="n">
-        <v>22.017468</v>
-      </c>
-      <c r="K33" t="n">
-        <v>56.290278</v>
-      </c>
-      <c r="L33" t="n">
-        <v>19.543416</v>
+        <v>15.643569</v>
       </c>
     </row>
     <row r="34">
@@ -1720,36 +1574,32 @@
           <t>塑膠工業右下上櫃</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="n">
+        <v>0.029903</v>
+      </c>
       <c r="C34" t="n">
-        <v>0.017583</v>
+        <v>0.020185</v>
       </c>
       <c r="D34" t="n">
-        <v>0.102871</v>
+        <v>0.02357733333333333</v>
       </c>
       <c r="E34" t="n">
-        <v>0.037021</v>
+        <v>0.0225495</v>
       </c>
       <c r="F34" t="n">
-        <v>0.024807</v>
+        <v>0.043256</v>
       </c>
       <c r="G34" t="n">
-        <v>0.014311</v>
+        <v>0.028786</v>
       </c>
       <c r="H34" t="n">
-        <v>0.016211</v>
+        <v>0.0244545</v>
       </c>
       <c r="I34" t="n">
-        <v>0.023688</v>
+        <v>0.029761</v>
       </c>
       <c r="J34" t="n">
-        <v>0.033461</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0.016074</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0.01980925</v>
+        <v>0.016262</v>
       </c>
     </row>
     <row r="35">
@@ -1758,34 +1608,32 @@
           <t>塑膠工業平上市</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
+      <c r="B35" t="n">
+        <v>80.799667</v>
+      </c>
       <c r="C35" t="n">
-        <v>0.703873</v>
+        <v>45.4635</v>
       </c>
       <c r="D35" t="n">
-        <v>8.436616000000001</v>
+        <v>51.638723</v>
       </c>
       <c r="E35" t="n">
-        <v>94.34626</v>
+        <v>78.35193200000001</v>
       </c>
       <c r="F35" t="n">
-        <v>50.149553</v>
+        <v>86.148461</v>
       </c>
       <c r="G35" t="n">
-        <v>3.850197</v>
-      </c>
-      <c r="H35" t="inlineStr"/>
+        <v>105.869253</v>
+      </c>
+      <c r="H35" t="n">
+        <v>159.785773</v>
+      </c>
       <c r="I35" t="n">
-        <v>28.752186</v>
+        <v>84.431816</v>
       </c>
       <c r="J35" t="n">
-        <v>123.154859</v>
-      </c>
-      <c r="K35" t="n">
-        <v>40.073198</v>
-      </c>
-      <c r="L35" t="n">
-        <v>18.757633</v>
+        <v>244.212676</v>
       </c>
     </row>
     <row r="36">
@@ -1794,938 +1642,816 @@
           <t>塑膠工業平上櫃</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="n">
-        <v>0.000946</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0.000751</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.0005820000000000001</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.000635</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.000593</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0.0005999999999999999</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0.000754</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0.000121</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0.000361</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0.000266</v>
-      </c>
+      <c r="B36" t="n">
+        <v>0.00022125</v>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>居家生活右上上市</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
+          <t>居家生活右上上櫃</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0.000165</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.000522</v>
+      </c>
       <c r="D37" t="n">
-        <v>15.123212</v>
+        <v>0.0013</v>
       </c>
       <c r="E37" t="n">
-        <v>13.043192</v>
+        <v>0.004544</v>
       </c>
       <c r="F37" t="n">
-        <v>7.719037</v>
-      </c>
-      <c r="G37" t="inlineStr"/>
+        <v>0.002171</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.000613</v>
+      </c>
       <c r="H37" t="n">
-        <v>4.936764</v>
+        <v>0.000906</v>
       </c>
       <c r="I37" t="n">
-        <v>46.877795</v>
+        <v>0.000283</v>
       </c>
       <c r="J37" t="n">
-        <v>23.295779</v>
-      </c>
-      <c r="K37" t="n">
-        <v>11.497832</v>
-      </c>
-      <c r="L37" t="n">
-        <v>7.797026</v>
+        <v>0.001482</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>居家生活右上上櫃</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
+          <t>居家生活右下上市</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>44.767089</v>
+      </c>
       <c r="C38" t="n">
-        <v>0.543303</v>
+        <v>29.50069</v>
       </c>
       <c r="D38" t="n">
-        <v>0.645215</v>
+        <v>37.008341</v>
       </c>
       <c r="E38" t="n">
-        <v>0.705775</v>
+        <v>22.73136</v>
       </c>
       <c r="F38" t="n">
-        <v>0.495393</v>
+        <v>20.023105</v>
       </c>
       <c r="G38" t="n">
-        <v>0.390816</v>
+        <v>29.842921</v>
       </c>
       <c r="H38" t="n">
-        <v>0.236235</v>
+        <v>27.947611</v>
       </c>
       <c r="I38" t="n">
-        <v>0.826088</v>
+        <v>20.812951</v>
       </c>
       <c r="J38" t="n">
-        <v>0.427494</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0.464047</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0.697994</v>
+        <v>28.538201</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>居家生活右下上市</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
+          <t>居家生活右下上櫃</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0.443066</v>
+      </c>
       <c r="C39" t="n">
-        <v>39.676442</v>
+        <v>0.376446</v>
       </c>
       <c r="D39" t="n">
-        <v>286.670469</v>
+        <v>0.541181</v>
       </c>
       <c r="E39" t="n">
-        <v>240.246426</v>
+        <v>0.367615</v>
       </c>
       <c r="F39" t="n">
-        <v>322.978526</v>
+        <v>0.55962575</v>
       </c>
       <c r="G39" t="n">
-        <v>140.107833</v>
+        <v>0.3257003333333333</v>
       </c>
       <c r="H39" t="n">
-        <v>105.594571</v>
+        <v>0.3575955</v>
       </c>
       <c r="I39" t="n">
-        <v>324.284747</v>
+        <v>0.2460553333333333</v>
       </c>
       <c r="J39" t="n">
-        <v>252.929736</v>
-      </c>
-      <c r="K39" t="n">
-        <v>205.999254</v>
-      </c>
-      <c r="L39" t="n">
-        <v>229.876631</v>
+        <v>0.312833</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>居家生活右下上櫃</t>
+          <t>居家生活平上市</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>406.235329</v>
       </c>
       <c r="C40" t="n">
-        <v>0.02126025</v>
+        <v>285.665435</v>
       </c>
       <c r="D40" t="n">
-        <v>0.018787</v>
+        <v>144.489178</v>
       </c>
       <c r="E40" t="n">
-        <v>0.028962</v>
+        <v>87.577246</v>
       </c>
       <c r="F40" t="n">
-        <v>0.038182</v>
+        <v>64.49407600000001</v>
       </c>
       <c r="G40" t="n">
-        <v>0.03852425</v>
+        <v>195.838725</v>
       </c>
       <c r="H40" t="n">
-        <v>0.02133925</v>
+        <v>129.132417</v>
       </c>
       <c r="I40" t="n">
-        <v>0.02811258333333333</v>
+        <v>68.960701</v>
       </c>
       <c r="J40" t="n">
-        <v>0.04733666666666667</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0.02269575</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0.01845233333333333</v>
+        <v>57.20569</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>居家生活平上市</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
+          <t>居家生活平上櫃</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0.002518</v>
+      </c>
       <c r="C41" t="n">
-        <v>797.102847</v>
+        <v>0.007408</v>
       </c>
       <c r="D41" t="n">
-        <v>75.12583100000001</v>
+        <v>0.002442</v>
       </c>
       <c r="E41" t="n">
-        <v>41.392319</v>
-      </c>
-      <c r="F41" t="inlineStr"/>
+        <v>0.001043</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.00075</v>
+      </c>
       <c r="G41" t="n">
-        <v>4.162421</v>
-      </c>
-      <c r="H41" t="inlineStr"/>
+        <v>0.001274</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.000901</v>
+      </c>
       <c r="I41" t="n">
-        <v>24.162953</v>
-      </c>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
+        <v>0.004289</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.003008</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>居家生活平上櫃</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
+          <t>建材營造右上上市</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>2018.405348</v>
+      </c>
       <c r="C42" t="n">
-        <v>0.003019</v>
+        <v>1098.044722</v>
       </c>
       <c r="D42" t="n">
-        <v>0.007782</v>
+        <v>1311.540773</v>
       </c>
       <c r="E42" t="n">
-        <v>0.002758</v>
+        <v>144.487166</v>
       </c>
       <c r="F42" t="n">
-        <v>0.008389000000000001</v>
+        <v>149.45803</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0009990000000000001</v>
+        <v>124.981634</v>
       </c>
       <c r="H42" t="n">
-        <v>0.003602</v>
+        <v>201.107528</v>
       </c>
       <c r="I42" t="n">
-        <v>0.012965</v>
+        <v>147.807027</v>
       </c>
       <c r="J42" t="n">
-        <v>0.00804</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0.001947</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0.002272</v>
+        <v>164.04647</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>建材營造右上上市</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
+          <t>建材營造右上上櫃</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>0.016124</v>
+      </c>
       <c r="C43" t="n">
-        <v>556.981037</v>
+        <v>0.007722</v>
       </c>
       <c r="D43" t="n">
-        <v>787.47568</v>
+        <v>0.008525</v>
       </c>
       <c r="E43" t="n">
-        <v>1051.593988</v>
+        <v>0.008455000000000001</v>
       </c>
       <c r="F43" t="n">
-        <v>681.711295</v>
+        <v>0.007346</v>
       </c>
       <c r="G43" t="n">
-        <v>660.405064</v>
+        <v>0.012669</v>
       </c>
       <c r="H43" t="n">
-        <v>450.402745</v>
+        <v>0.015847</v>
       </c>
       <c r="I43" t="n">
-        <v>853.774814</v>
+        <v>0.020326</v>
       </c>
       <c r="J43" t="n">
-        <v>533.637306</v>
-      </c>
-      <c r="K43" t="n">
-        <v>625.648042</v>
-      </c>
-      <c r="L43" t="n">
-        <v>724.074308</v>
+        <v>0.01373125</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>建材營造右上上櫃</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
+          <t>建材營造右下上市</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1854.204051</v>
+      </c>
       <c r="C44" t="n">
-        <v>0.037054</v>
+        <v>707.2115659999999</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0427</v>
+        <v>457.357728</v>
       </c>
       <c r="E44" t="n">
-        <v>0.053261</v>
+        <v>597.730444</v>
       </c>
       <c r="F44" t="n">
-        <v>0.145483</v>
+        <v>428.069404</v>
       </c>
       <c r="G44" t="n">
-        <v>0.055718</v>
+        <v>1042.3501</v>
       </c>
       <c r="H44" t="n">
-        <v>0.030384</v>
+        <v>1117.33762</v>
       </c>
       <c r="I44" t="n">
-        <v>0.139311</v>
+        <v>829.348561</v>
       </c>
       <c r="J44" t="n">
-        <v>0.00121</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0.007013</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0.003254</v>
+        <v>930.680146</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>建材營造右下上市</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
+          <t>建材營造右下上櫃</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>0.215736</v>
+      </c>
       <c r="C45" t="n">
-        <v>812.085232</v>
+        <v>0.09563000000000001</v>
       </c>
       <c r="D45" t="n">
-        <v>912.92776</v>
+        <v>0.108894</v>
       </c>
       <c r="E45" t="n">
-        <v>718.566729</v>
+        <v>0.076583</v>
       </c>
       <c r="F45" t="n">
-        <v>789.0201949999999</v>
+        <v>0.06238</v>
       </c>
       <c r="G45" t="n">
-        <v>627.176105</v>
+        <v>0.054294</v>
       </c>
       <c r="H45" t="n">
-        <v>507.965039</v>
+        <v>0.050976</v>
       </c>
       <c r="I45" t="n">
-        <v>812.313853</v>
+        <v>0.03979466666666667</v>
       </c>
       <c r="J45" t="n">
-        <v>916.775796</v>
-      </c>
-      <c r="K45" t="n">
-        <v>567.275864</v>
-      </c>
-      <c r="L45" t="n">
-        <v>703.447122</v>
+        <v>0.044147</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>建材營造右下上櫃</t>
+          <t>建材營造平上市</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>123.388588</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0824135</v>
+        <v>95.518418</v>
       </c>
       <c r="D46" t="n">
-        <v>0.09442399999999999</v>
+        <v>105.337666</v>
       </c>
       <c r="E46" t="n">
-        <v>0.085261</v>
+        <v>2054.58486</v>
       </c>
       <c r="F46" t="n">
-        <v>0.09354766666666667</v>
+        <v>581.465077</v>
       </c>
       <c r="G46" t="n">
-        <v>0.0669985</v>
+        <v>36.673821</v>
       </c>
       <c r="H46" t="n">
-        <v>0.1327125</v>
+        <v>53.262782</v>
       </c>
       <c r="I46" t="n">
-        <v>0.077672</v>
+        <v>166.435499</v>
       </c>
       <c r="J46" t="n">
-        <v>0.097196</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0.094249</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0.06675499999999999</v>
+        <v>76.116998</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>建材營造平上市</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
+          <t>建材營造平上櫃</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>0.165724</v>
+      </c>
       <c r="C47" t="n">
-        <v>192.082101</v>
+        <v>0.047342</v>
       </c>
       <c r="D47" t="n">
-        <v>386.301429</v>
+        <v>0.036039</v>
       </c>
       <c r="E47" t="n">
-        <v>381.909806</v>
+        <v>0.032516</v>
       </c>
       <c r="F47" t="n">
-        <v>330.741041</v>
+        <v>0.022415</v>
       </c>
       <c r="G47" t="n">
-        <v>193.707976</v>
+        <v>0.010698</v>
       </c>
       <c r="H47" t="n">
-        <v>191.395744</v>
+        <v>0.013407</v>
       </c>
       <c r="I47" t="n">
-        <v>256.681433</v>
+        <v>0.026788</v>
       </c>
       <c r="J47" t="n">
-        <v>796.7467820000001</v>
-      </c>
-      <c r="K47" t="n">
-        <v>496.612799</v>
-      </c>
-      <c r="L47" t="n">
-        <v>633.272863</v>
+        <v>0.023503</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>建材營造平上櫃</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
+          <t>數位雲端右上上市</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>292.09829</v>
+      </c>
       <c r="C48" t="n">
-        <v>0.013641</v>
+        <v>184.730686</v>
       </c>
       <c r="D48" t="n">
-        <v>0.012683</v>
+        <v>524.292661</v>
       </c>
       <c r="E48" t="n">
-        <v>0.013031</v>
+        <v>232.139303</v>
       </c>
       <c r="F48" t="n">
-        <v>0.011914</v>
+        <v>212.845719</v>
       </c>
       <c r="G48" t="n">
-        <v>0.005428</v>
+        <v>131.591225</v>
       </c>
       <c r="H48" t="n">
-        <v>0.005947</v>
+        <v>273.926956</v>
       </c>
       <c r="I48" t="n">
-        <v>0.007475</v>
+        <v>79.373986</v>
       </c>
       <c r="J48" t="n">
-        <v>0.046493</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0.01834</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0.03556</v>
+        <v>81.745813</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>數位雲端右上上市</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
+          <t>數位雲端右上上櫃</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>0.5358540000000001</v>
+      </c>
       <c r="C49" t="n">
-        <v>740.247091</v>
+        <v>0.338427</v>
       </c>
       <c r="D49" t="n">
-        <v>543.788042</v>
+        <v>0.324899</v>
       </c>
       <c r="E49" t="n">
-        <v>435.630536</v>
+        <v>0.506584</v>
       </c>
       <c r="F49" t="n">
-        <v>363.425125</v>
+        <v>0.218607</v>
       </c>
       <c r="G49" t="n">
-        <v>178.709252</v>
+        <v>0.179389</v>
       </c>
       <c r="H49" t="n">
-        <v>152.165969</v>
+        <v>0.296095</v>
       </c>
       <c r="I49" t="n">
-        <v>281.455257</v>
+        <v>0.1936893333333334</v>
       </c>
       <c r="J49" t="n">
-        <v>295.871914</v>
-      </c>
-      <c r="K49" t="n">
-        <v>236.069871</v>
-      </c>
-      <c r="L49" t="n">
-        <v>167.574029</v>
+        <v>0.121387</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>數位雲端右上上櫃</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
+          <t>數位雲端右下上市</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>29.283771</v>
+      </c>
       <c r="C50" t="n">
-        <v>0.226788</v>
+        <v>22.149554</v>
       </c>
       <c r="D50" t="n">
-        <v>0.227342</v>
+        <v>25.923961</v>
       </c>
       <c r="E50" t="n">
-        <v>0.107819</v>
+        <v>25.247635</v>
       </c>
       <c r="F50" t="n">
-        <v>0.080166</v>
+        <v>22.50859</v>
       </c>
       <c r="G50" t="n">
-        <v>0.133454</v>
+        <v>28.703929</v>
       </c>
       <c r="H50" t="n">
-        <v>0.119742</v>
+        <v>24.480949</v>
       </c>
       <c r="I50" t="n">
-        <v>0.5762930000000001</v>
+        <v>28.726985</v>
       </c>
       <c r="J50" t="n">
-        <v>0.54243</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0.428566</v>
-      </c>
-      <c r="L50" t="n">
-        <v>0.499948</v>
+        <v>38.646655</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>數位雲端右下上市</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr"/>
+          <t>數位雲端右下上櫃</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0.399932</v>
+      </c>
       <c r="C51" t="n">
-        <v>103.787139</v>
+        <v>0.287752</v>
       </c>
       <c r="D51" t="n">
-        <v>75.91532100000001</v>
+        <v>0.205242</v>
       </c>
       <c r="E51" t="n">
-        <v>111.37864</v>
+        <v>0.179853</v>
       </c>
       <c r="F51" t="n">
-        <v>107.789504</v>
+        <v>0.09177299999999999</v>
       </c>
       <c r="G51" t="n">
-        <v>139.047915</v>
+        <v>0.11663</v>
       </c>
       <c r="H51" t="n">
-        <v>96.584531</v>
+        <v>0.115867</v>
       </c>
       <c r="I51" t="n">
-        <v>144.391418</v>
+        <v>0.173237</v>
       </c>
       <c r="J51" t="n">
-        <v>160.869259</v>
-      </c>
-      <c r="K51" t="n">
-        <v>56.822454</v>
-      </c>
-      <c r="L51" t="n">
-        <v>77.25176</v>
+        <v>0.181664</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>數位雲端右下上櫃</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
+          <t>數位雲端平上市</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>175.29473</v>
+      </c>
       <c r="C52" t="n">
-        <v>0.227132</v>
+        <v>117.378274</v>
       </c>
       <c r="D52" t="n">
-        <v>0.357154</v>
+        <v>189.304916</v>
       </c>
       <c r="E52" t="n">
-        <v>0.889545</v>
+        <v>142.973795</v>
       </c>
       <c r="F52" t="n">
-        <v>1.032101</v>
+        <v>117.038726</v>
       </c>
       <c r="G52" t="n">
-        <v>1.317067</v>
+        <v>117.851939</v>
       </c>
       <c r="H52" t="n">
-        <v>0.90057</v>
+        <v>132.340216</v>
       </c>
       <c r="I52" t="n">
-        <v>0.576919</v>
+        <v>83.747483</v>
       </c>
       <c r="J52" t="n">
-        <v>0.6365420000000001</v>
-      </c>
-      <c r="K52" t="n">
-        <v>1.23999</v>
-      </c>
-      <c r="L52" t="n">
-        <v>0.061174</v>
+        <v>60.660386</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>數位雲端平上市</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr"/>
+          <t>數位雲端平上櫃</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>0.000124</v>
+      </c>
       <c r="C53" t="n">
-        <v>8.904928</v>
+        <v>0.00059625</v>
       </c>
       <c r="D53" t="n">
-        <v>27.006314</v>
+        <v>0.001018333333333333</v>
       </c>
       <c r="E53" t="n">
-        <v>100.694087</v>
+        <v>0.000483</v>
       </c>
       <c r="F53" t="n">
-        <v>60.188821</v>
+        <v>0.118701</v>
       </c>
       <c r="G53" t="n">
-        <v>44.694074</v>
+        <v>0.152504</v>
       </c>
       <c r="H53" t="n">
-        <v>44.986519</v>
+        <v>0.093373</v>
       </c>
       <c r="I53" t="n">
-        <v>44.055808</v>
+        <v>0.074028</v>
       </c>
       <c r="J53" t="n">
-        <v>34.41067</v>
-      </c>
-      <c r="K53" t="n">
-        <v>22.332572</v>
-      </c>
-      <c r="L53" t="n">
-        <v>35.290643</v>
+        <v>0.036497</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>數位雲端平上櫃</t>
+          <t>文化創意業右上上櫃</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
-      <c r="C54" t="n">
-        <v>0.096055</v>
-      </c>
-      <c r="D54" t="n">
-        <v>0.097095</v>
-      </c>
-      <c r="E54" t="n">
-        <v>0.115679</v>
-      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="n">
-        <v>0.101775</v>
+        <v>4.373877</v>
       </c>
       <c r="G54" t="n">
-        <v>0.047791</v>
+        <v>2.718566</v>
       </c>
       <c r="H54" t="n">
-        <v>0.046147</v>
+        <v>1.632479</v>
       </c>
       <c r="I54" t="n">
-        <v>0.043985</v>
+        <v>4.801571</v>
       </c>
       <c r="J54" t="n">
-        <v>0.051021</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0.027052</v>
-      </c>
-      <c r="L54" t="n">
-        <v>1.658592</v>
+        <v>2.438659</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>文化創意業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr"/>
+          <t>文化創意業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>0.060443</v>
+      </c>
       <c r="C55" t="n">
-        <v>1.712564</v>
+        <v>0.87181725</v>
       </c>
       <c r="D55" t="n">
-        <v>1.015231</v>
+        <v>0.057446</v>
       </c>
       <c r="E55" t="n">
-        <v>1.186455</v>
+        <v>0.0641065</v>
       </c>
       <c r="F55" t="n">
-        <v>0.051062</v>
+        <v>0.0408735</v>
       </c>
       <c r="G55" t="n">
-        <v>0.136713</v>
+        <v>0.06168375</v>
       </c>
       <c r="H55" t="n">
-        <v>0.037393</v>
+        <v>0.073361</v>
       </c>
       <c r="I55" t="n">
-        <v>0.063236</v>
+        <v>0.049902</v>
       </c>
       <c r="J55" t="n">
-        <v>0.024218</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0.02475</v>
-      </c>
-      <c r="L55" t="n">
-        <v>0.001716</v>
+        <v>0.05330483333333334</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>文化創意業右下上櫃</t>
+          <t>文化創意業平上櫃</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0</v>
+        <v>3.036963666666666</v>
       </c>
       <c r="C56" t="n">
-        <v>0.09888</v>
+        <v>0.016009</v>
       </c>
       <c r="D56" t="n">
-        <v>0.132187</v>
+        <v>0.853862</v>
       </c>
       <c r="E56" t="n">
-        <v>0.113503</v>
+        <v>0.596025</v>
       </c>
       <c r="F56" t="n">
-        <v>0.184662</v>
+        <v>0.008586999999999999</v>
       </c>
       <c r="G56" t="n">
-        <v>1.639029</v>
+        <v>0.003479</v>
       </c>
       <c r="H56" t="n">
-        <v>0.927786</v>
+        <v>0.001894</v>
       </c>
       <c r="I56" t="n">
-        <v>1.206728333333333</v>
+        <v>0.011794</v>
       </c>
       <c r="J56" t="n">
-        <v>1.5078565</v>
-      </c>
-      <c r="K56" t="n">
-        <v>1.39690625</v>
-      </c>
-      <c r="L56" t="n">
-        <v>0.954035</v>
+        <v>0.004545</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>文化創意業平上櫃</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr"/>
+          <t>橡膠工業右上上市</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>159.304336</v>
+      </c>
       <c r="C57" t="n">
-        <v>0.052978</v>
+        <v>64.999539</v>
       </c>
       <c r="D57" t="n">
-        <v>0.030543</v>
+        <v>74.300687</v>
       </c>
       <c r="E57" t="n">
-        <v>0.06344</v>
+        <v>380.284936</v>
       </c>
       <c r="F57" t="n">
-        <v>1.72866</v>
+        <v>59.31454</v>
       </c>
       <c r="G57" t="n">
-        <v>0.009294999999999999</v>
+        <v>91.80184300000001</v>
       </c>
       <c r="H57" t="n">
-        <v>0.006829</v>
+        <v>91.7514</v>
       </c>
       <c r="I57" t="n">
-        <v>0.000114</v>
+        <v>64.15203700000001</v>
       </c>
       <c r="J57" t="n">
-        <v>0.024058</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0.014317</v>
-      </c>
-      <c r="L57" t="n">
-        <v>0.036539</v>
+        <v>159.079605</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>橡膠工業右上上市</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr"/>
+          <t>橡膠工業右下上市</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>448.313426</v>
+      </c>
       <c r="C58" t="n">
-        <v>99.35086</v>
+        <v>355.156177</v>
       </c>
       <c r="D58" t="n">
-        <v>596.483056</v>
+        <v>234.544684</v>
       </c>
       <c r="E58" t="n">
-        <v>945.305809</v>
+        <v>147.169752</v>
       </c>
       <c r="F58" t="n">
-        <v>298.520803</v>
+        <v>116.233975</v>
       </c>
       <c r="G58" t="n">
-        <v>192.173078</v>
+        <v>165.105133</v>
       </c>
       <c r="H58" t="n">
-        <v>198.868352</v>
+        <v>65.736844</v>
       </c>
       <c r="I58" t="n">
-        <v>100.398442</v>
+        <v>172.168685</v>
       </c>
       <c r="J58" t="n">
-        <v>443.216733</v>
-      </c>
-      <c r="K58" t="n">
-        <v>322.141715</v>
-      </c>
-      <c r="L58" t="n">
-        <v>535.076115</v>
+        <v>235.463628</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>橡膠工業右下上市</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr"/>
+          <t>橡膠工業平上市</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>3.999998</v>
+      </c>
       <c r="C59" t="n">
-        <v>931.801027</v>
+        <v>0.567801</v>
       </c>
       <c r="D59" t="n">
-        <v>1093.195274</v>
-      </c>
-      <c r="E59" t="n">
-        <v>611.886482</v>
-      </c>
+        <v>0.448149</v>
+      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="n">
-        <v>572.360334</v>
+        <v>110.326311</v>
       </c>
       <c r="G59" t="n">
-        <v>285.899301</v>
+        <v>67.582936</v>
       </c>
       <c r="H59" t="n">
-        <v>327.982043</v>
+        <v>210.676112</v>
       </c>
       <c r="I59" t="n">
-        <v>463.181324</v>
+        <v>34.688359</v>
       </c>
       <c r="J59" t="n">
-        <v>728.391242</v>
-      </c>
-      <c r="K59" t="n">
-        <v>346.968929</v>
-      </c>
-      <c r="L59" t="n">
-        <v>148.611364</v>
+        <v>20.422541</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>橡膠工業平上市</t>
+          <t>水泥工業右上上市</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
-      <c r="C60" t="n">
-        <v>1.384229</v>
-      </c>
-      <c r="D60" t="n">
-        <v>136.378039</v>
-      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="n">
-        <v>5.175845</v>
+        <v>3742.980955</v>
       </c>
       <c r="F60" t="n">
-        <v>81.287525</v>
+        <v>995.089243</v>
       </c>
       <c r="G60" t="n">
-        <v>38.718311</v>
+        <v>796.559063</v>
       </c>
       <c r="H60" t="n">
-        <v>4.28475</v>
+        <v>2967.114292</v>
       </c>
       <c r="I60" t="n">
-        <v>7.223429</v>
-      </c>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="n">
-        <v>1.953672</v>
-      </c>
-      <c r="L60" t="n">
-        <v>719.78311</v>
+        <v>1412.587301</v>
+      </c>
+      <c r="J60" t="n">
+        <v>641.982484</v>
       </c>
     </row>
     <row r="61">
@@ -2734,36 +2460,32 @@
           <t>水泥工業右下上市</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr"/>
+      <c r="B61" t="n">
+        <v>45.964614</v>
+      </c>
       <c r="C61" t="n">
-        <v>1541.827726</v>
+        <v>23.146596</v>
       </c>
       <c r="D61" t="n">
-        <v>59.772179</v>
+        <v>23.131303</v>
       </c>
       <c r="E61" t="n">
-        <v>37.050423</v>
+        <v>27.97068</v>
       </c>
       <c r="F61" t="n">
-        <v>1270.286425</v>
+        <v>23.890866</v>
       </c>
       <c r="G61" t="n">
-        <v>876.134365</v>
+        <v>36.108083</v>
       </c>
       <c r="H61" t="n">
-        <v>1389.362274</v>
+        <v>25.533089</v>
       </c>
       <c r="I61" t="n">
-        <v>1363.536415</v>
+        <v>24.011971</v>
       </c>
       <c r="J61" t="n">
-        <v>1476.362156</v>
-      </c>
-      <c r="K61" t="n">
-        <v>1627.78388</v>
-      </c>
-      <c r="L61" t="n">
-        <v>1274.909131</v>
+        <v>17.212754</v>
       </c>
     </row>
     <row r="62">
@@ -2772,22 +2494,28 @@
           <t>水泥工業平上市</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr"/>
-      <c r="C62" t="inlineStr"/>
+      <c r="B62" t="n">
+        <v>899.392789</v>
+      </c>
+      <c r="C62" t="n">
+        <v>472.762869</v>
+      </c>
       <c r="D62" t="n">
-        <v>1317.994459</v>
-      </c>
-      <c r="E62" t="n">
-        <v>803.107363</v>
-      </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
+        <v>949.079145</v>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="n">
+        <v>265.593417</v>
+      </c>
+      <c r="G62" t="n">
+        <v>339.290351</v>
+      </c>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="n">
-        <v>665.654465</v>
+      <c r="I62" t="n">
+        <v>420.783956</v>
+      </c>
+      <c r="J62" t="n">
+        <v>174.267952</v>
       </c>
     </row>
     <row r="63">
@@ -2796,36 +2524,32 @@
           <t>汽車工業右上上市</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr"/>
+      <c r="B63" t="n">
+        <v>1120.352731</v>
+      </c>
       <c r="C63" t="n">
-        <v>2234.074494</v>
+        <v>904.787535</v>
       </c>
       <c r="D63" t="n">
-        <v>3002.616451</v>
+        <v>806.547029</v>
       </c>
       <c r="E63" t="n">
-        <v>3167.789583</v>
+        <v>1669.721101</v>
       </c>
       <c r="F63" t="n">
-        <v>3389.993579</v>
+        <v>1001.153987</v>
       </c>
       <c r="G63" t="n">
-        <v>2129.90816</v>
+        <v>1376.904598</v>
       </c>
       <c r="H63" t="n">
-        <v>1653.501954</v>
+        <v>2530.817868</v>
       </c>
       <c r="I63" t="n">
-        <v>1558.184947</v>
+        <v>894.608758</v>
       </c>
       <c r="J63" t="n">
-        <v>1718.57399</v>
-      </c>
-      <c r="K63" t="n">
-        <v>1168.759092</v>
-      </c>
-      <c r="L63" t="n">
-        <v>845.878695</v>
+        <v>1258.292474</v>
       </c>
     </row>
     <row r="64">
@@ -2834,36 +2558,32 @@
           <t>汽車工業右下上市</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr"/>
+      <c r="B64" t="n">
+        <v>442.698247</v>
+      </c>
       <c r="C64" t="n">
-        <v>1360.652256</v>
+        <v>344.796209</v>
       </c>
       <c r="D64" t="n">
-        <v>1345.028885</v>
+        <v>420.177898</v>
       </c>
       <c r="E64" t="n">
-        <v>983.42304</v>
+        <v>295.1171815</v>
       </c>
       <c r="F64" t="n">
-        <v>979.785094</v>
+        <v>270.273582</v>
       </c>
       <c r="G64" t="n">
-        <v>703.677709</v>
+        <v>464.299762</v>
       </c>
       <c r="H64" t="n">
-        <v>1425.753004</v>
+        <v>412.71605</v>
       </c>
       <c r="I64" t="n">
-        <v>557.40995</v>
+        <v>323.712412</v>
       </c>
       <c r="J64" t="n">
-        <v>972.591669</v>
-      </c>
-      <c r="K64" t="n">
-        <v>693.067183</v>
-      </c>
-      <c r="L64" t="n">
-        <v>830.107078</v>
+        <v>377.708464</v>
       </c>
     </row>
     <row r="65">
@@ -2872,36 +2592,32 @@
           <t>汽車工業平上市</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr"/>
+      <c r="B65" t="n">
+        <v>594.089462</v>
+      </c>
       <c r="C65" t="n">
-        <v>158.359791</v>
+        <v>279.300722</v>
       </c>
       <c r="D65" t="n">
-        <v>106.202138</v>
+        <v>269.349393</v>
       </c>
       <c r="E65" t="n">
-        <v>75.424081</v>
+        <v>199.842169</v>
       </c>
       <c r="F65" t="n">
-        <v>9.029563</v>
+        <v>208.878708</v>
       </c>
       <c r="G65" t="n">
-        <v>83.938838</v>
+        <v>198.14848</v>
       </c>
       <c r="H65" t="n">
-        <v>3.576226</v>
+        <v>284.679117</v>
       </c>
       <c r="I65" t="n">
-        <v>809.465858</v>
+        <v>244.890534</v>
       </c>
       <c r="J65" t="n">
-        <v>255.134162</v>
-      </c>
-      <c r="K65" t="n">
-        <v>242.980112</v>
-      </c>
-      <c r="L65" t="n">
-        <v>218.800755</v>
+        <v>391.432299</v>
       </c>
     </row>
     <row r="66">
@@ -2910,36 +2626,32 @@
           <t>油電燃氣業右上上市</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr"/>
+      <c r="B66" t="n">
+        <v>2254.681543</v>
+      </c>
       <c r="C66" t="n">
-        <v>1799.292436</v>
+        <v>1540.168944</v>
       </c>
       <c r="D66" t="n">
-        <v>2909.563459</v>
+        <v>1563.610846</v>
       </c>
       <c r="E66" t="n">
-        <v>2135.843911</v>
+        <v>1120.951175</v>
       </c>
       <c r="F66" t="n">
-        <v>1528.74467</v>
+        <v>1016.909933</v>
       </c>
       <c r="G66" t="n">
-        <v>1297.807236</v>
+        <v>3827.737724</v>
       </c>
       <c r="H66" t="n">
-        <v>1505.378649</v>
+        <v>3768.070051</v>
       </c>
       <c r="I66" t="n">
-        <v>3264.897724</v>
+        <v>2657.525003</v>
       </c>
       <c r="J66" t="n">
-        <v>4022.761264</v>
-      </c>
-      <c r="K66" t="n">
-        <v>4533.403722</v>
-      </c>
-      <c r="L66" t="n">
-        <v>8129.727426</v>
+        <v>3632.530573</v>
       </c>
     </row>
     <row r="67">
@@ -2948,36 +2660,32 @@
           <t>油電燃氣業右下上市</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr"/>
+      <c r="B67" t="n">
+        <v>5.858001</v>
+      </c>
       <c r="C67" t="n">
-        <v>10.306033</v>
+        <v>6.526438</v>
       </c>
       <c r="D67" t="n">
-        <v>25.886225</v>
+        <v>4.976994</v>
       </c>
       <c r="E67" t="n">
-        <v>5.912424</v>
+        <v>4.671305</v>
       </c>
       <c r="F67" t="n">
-        <v>9.898058000000001</v>
+        <v>4.464252</v>
       </c>
       <c r="G67" t="n">
-        <v>9.374789</v>
+        <v>6.8068</v>
       </c>
       <c r="H67" t="n">
-        <v>159.791585</v>
+        <v>5.852749</v>
       </c>
       <c r="I67" t="n">
-        <v>17.600701</v>
+        <v>3.578119</v>
       </c>
       <c r="J67" t="n">
-        <v>30.236257</v>
-      </c>
-      <c r="K67" t="n">
-        <v>25.789061</v>
-      </c>
-      <c r="L67" t="n">
-        <v>11.717196</v>
+        <v>6.830817</v>
       </c>
     </row>
     <row r="68">
@@ -2986,36 +2694,32 @@
           <t>油電燃氣業右下上櫃</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr"/>
+      <c r="B68" t="n">
+        <v>0.004761</v>
+      </c>
       <c r="C68" t="n">
-        <v>0.018012</v>
+        <v>0.006872</v>
       </c>
       <c r="D68" t="n">
-        <v>0.022445</v>
+        <v>0.004074</v>
       </c>
       <c r="E68" t="n">
-        <v>0.020267</v>
+        <v>0.00622</v>
       </c>
       <c r="F68" t="n">
-        <v>0.016908</v>
+        <v>0.003165</v>
       </c>
       <c r="G68" t="n">
-        <v>0.0123705</v>
+        <v>0.003294</v>
       </c>
       <c r="H68" t="n">
-        <v>0.014226</v>
+        <v>0.002846</v>
       </c>
       <c r="I68" t="n">
-        <v>0.025375</v>
+        <v>0.00394</v>
       </c>
       <c r="J68" t="n">
-        <v>0.012999</v>
-      </c>
-      <c r="K68" t="n">
-        <v>0.008338999999999999</v>
-      </c>
-      <c r="L68" t="n">
-        <v>0.007523</v>
+        <v>0.0022</v>
       </c>
     </row>
     <row r="69">
@@ -3024,867 +2728,815 @@
           <t>油電燃氣業平上市</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr"/>
-      <c r="C69" t="inlineStr"/>
+      <c r="B69" t="n">
+        <v>1.878674</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0.705493</v>
+      </c>
       <c r="D69" t="n">
-        <v>1.006582</v>
+        <v>1.06129</v>
       </c>
       <c r="E69" t="n">
-        <v>17.607205</v>
-      </c>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
+        <v>88.001926</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.416998</v>
+      </c>
+      <c r="G69" t="n">
+        <v>75.293695</v>
+      </c>
+      <c r="H69" t="n">
+        <v>1.0206</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.687299</v>
+      </c>
       <c r="J69" t="n">
-        <v>1.267576</v>
-      </c>
-      <c r="K69" t="n">
-        <v>0.910846</v>
-      </c>
-      <c r="L69" t="n">
-        <v>1.57221</v>
+        <v>0.993817</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷右上上市</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr"/>
+          <t>油電燃氣業平上櫃</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>0.001304</v>
+      </c>
       <c r="C70" t="n">
-        <v>3479.153573</v>
+        <v>0.005765</v>
       </c>
       <c r="D70" t="n">
-        <v>3311.033853</v>
+        <v>0.00202</v>
       </c>
       <c r="E70" t="n">
-        <v>2980.642301</v>
+        <v>0.004737</v>
       </c>
       <c r="F70" t="n">
-        <v>4364.429569</v>
+        <v>0.012791</v>
       </c>
       <c r="G70" t="n">
-        <v>3118.731007</v>
+        <v>0.003837</v>
       </c>
       <c r="H70" t="n">
-        <v>2252.227198</v>
+        <v>0.010741</v>
       </c>
       <c r="I70" t="n">
-        <v>4265.880282</v>
+        <v>0.000701</v>
       </c>
       <c r="J70" t="n">
-        <v>4527.341471</v>
-      </c>
-      <c r="K70" t="n">
-        <v>4303.272966</v>
-      </c>
-      <c r="L70" t="n">
-        <v>2723.042265</v>
+        <v>0.000886</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷右下上市</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr"/>
+          <t>玻璃陶瓷右上上市</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>128.349649</v>
+      </c>
       <c r="C71" t="n">
-        <v>8.63514</v>
+        <v>97.21011799999999</v>
       </c>
       <c r="D71" t="n">
-        <v>16.564416</v>
+        <v>180.249203</v>
       </c>
       <c r="E71" t="n">
-        <v>9.548494</v>
+        <v>308.760818</v>
       </c>
       <c r="F71" t="n">
-        <v>5.792786</v>
+        <v>336.767867</v>
       </c>
       <c r="G71" t="n">
-        <v>5.121537</v>
+        <v>1394.507219</v>
       </c>
       <c r="H71" t="n">
-        <v>2.651794</v>
+        <v>980.572891</v>
       </c>
       <c r="I71" t="n">
-        <v>3.525597</v>
+        <v>297.549161</v>
       </c>
       <c r="J71" t="n">
-        <v>7.20599</v>
-      </c>
-      <c r="K71" t="n">
-        <v>4.877046</v>
-      </c>
-      <c r="L71" t="n">
-        <v>3.698902</v>
+        <v>572.510755</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷平上市</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr"/>
-      <c r="C72" t="inlineStr"/>
+          <t>玻璃陶瓷右下上市</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>0.744646</v>
+      </c>
+      <c r="C72" t="n">
+        <v>0.751342</v>
+      </c>
       <c r="D72" t="n">
-        <v>2.1582</v>
-      </c>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
+        <v>1.292641</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.469083</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.521244</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.500364</v>
+      </c>
+      <c r="H72" t="n">
+        <v>1.209878</v>
+      </c>
+      <c r="I72" t="n">
+        <v>2.726514</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.8914299999999999</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右上上市</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr"/>
+          <t>玻璃陶瓷平上市</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>1960.267031</v>
+      </c>
       <c r="C73" t="n">
-        <v>4331.456468</v>
+        <v>1169.464009</v>
       </c>
       <c r="D73" t="n">
-        <v>6912.279719</v>
+        <v>1593.900291</v>
       </c>
       <c r="E73" t="n">
-        <v>5114.3019</v>
+        <v>931.223287</v>
       </c>
       <c r="F73" t="n">
-        <v>7363.108659</v>
+        <v>464.349189</v>
       </c>
       <c r="G73" t="n">
-        <v>8282.368633</v>
+        <v>460.082038</v>
       </c>
       <c r="H73" t="n">
-        <v>9959.902998</v>
+        <v>1411.506215</v>
       </c>
       <c r="I73" t="n">
-        <v>5521.524694</v>
+        <v>913.096038</v>
       </c>
       <c r="J73" t="n">
-        <v>5932.384345</v>
-      </c>
-      <c r="K73" t="n">
-        <v>4161.045841</v>
-      </c>
-      <c r="L73" t="n">
-        <v>7338.613155</v>
+        <v>716.628303</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr"/>
+          <t>生技醫療業右上上市</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>16849.850547</v>
+      </c>
       <c r="C74" t="n">
-        <v>0.216173</v>
+        <v>4475.343683</v>
       </c>
       <c r="D74" t="n">
-        <v>0.77923</v>
+        <v>6022.66941</v>
       </c>
       <c r="E74" t="n">
-        <v>1.097394</v>
+        <v>5969.716865</v>
       </c>
       <c r="F74" t="n">
-        <v>1.684603</v>
+        <v>4097.608961</v>
       </c>
       <c r="G74" t="n">
-        <v>1.745513</v>
+        <v>3885.775727</v>
       </c>
       <c r="H74" t="n">
-        <v>0.962255</v>
+        <v>4196.073425</v>
       </c>
       <c r="I74" t="n">
-        <v>0.80627</v>
+        <v>6374.150305</v>
       </c>
       <c r="J74" t="n">
-        <v>0.616945</v>
-      </c>
-      <c r="K74" t="n">
-        <v>0.595113</v>
-      </c>
-      <c r="L74" t="n">
-        <v>0.457392</v>
+        <v>2873.532273</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右下上市</t>
+          <t>生技醫療業右上上櫃</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0</v>
+        <v>2.223199</v>
       </c>
       <c r="C75" t="n">
-        <v>1475.08488</v>
+        <v>1.394526</v>
       </c>
       <c r="D75" t="n">
-        <v>3348.684711</v>
+        <v>1.27838</v>
       </c>
       <c r="E75" t="n">
-        <v>2130.995753</v>
+        <v>0.974698</v>
       </c>
       <c r="F75" t="n">
-        <v>3221.093527</v>
+        <v>0.796296</v>
       </c>
       <c r="G75" t="n">
-        <v>3945.157078</v>
+        <v>0.814196</v>
       </c>
       <c r="H75" t="n">
-        <v>2071.456177</v>
+        <v>1.607912</v>
       </c>
       <c r="I75" t="n">
-        <v>2248.248916</v>
+        <v>1.910936</v>
       </c>
       <c r="J75" t="n">
-        <v>2284.663582</v>
-      </c>
-      <c r="K75" t="n">
-        <v>2379.374993</v>
-      </c>
-      <c r="L75" t="n">
-        <v>2402.850805</v>
+        <v>1.355821</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右下上櫃</t>
+          <t>生技醫療業右下上市</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0</v>
+        <v>1489.704493</v>
       </c>
       <c r="C76" t="n">
-        <v>0.74843</v>
+        <v>1380.833839</v>
       </c>
       <c r="D76" t="n">
-        <v>1.667664</v>
+        <v>1420.340333</v>
       </c>
       <c r="E76" t="n">
-        <v>0.88356975</v>
+        <v>790.299203</v>
       </c>
       <c r="F76" t="n">
-        <v>0.970935</v>
+        <v>882.589772</v>
       </c>
       <c r="G76" t="n">
-        <v>1.102805</v>
+        <v>831.72542</v>
       </c>
       <c r="H76" t="n">
-        <v>0.655508</v>
+        <v>998.401114</v>
       </c>
       <c r="I76" t="n">
-        <v>0.68007775</v>
+        <v>576.713749</v>
       </c>
       <c r="J76" t="n">
-        <v>0.85655975</v>
-      </c>
-      <c r="K76" t="n">
-        <v>0.3904693333333334</v>
-      </c>
-      <c r="L76" t="n">
-        <v>0.3912165</v>
+        <v>1361.174952</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業平上市</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr"/>
+          <t>生技醫療業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>0.614899</v>
+      </c>
       <c r="C77" t="n">
-        <v>190.869093</v>
+        <v>0.317249</v>
       </c>
       <c r="D77" t="n">
-        <v>168.683872</v>
+        <v>0.40359625</v>
       </c>
       <c r="E77" t="n">
-        <v>611.56023</v>
+        <v>0.345726</v>
       </c>
       <c r="F77" t="n">
-        <v>1996.057699</v>
+        <v>0.3164330833333333</v>
       </c>
       <c r="G77" t="n">
-        <v>952.644348</v>
+        <v>0.3441363333333333</v>
       </c>
       <c r="H77" t="n">
-        <v>746.9721970000001</v>
+        <v>0.3782826666666667</v>
       </c>
       <c r="I77" t="n">
-        <v>93.67379699999999</v>
+        <v>0.3214551666666667</v>
       </c>
       <c r="J77" t="n">
-        <v>257.931183</v>
-      </c>
-      <c r="K77" t="n">
-        <v>97.350154</v>
-      </c>
-      <c r="L77" t="n">
-        <v>1129.203392</v>
+        <v>0.3472475</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業平上櫃</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr"/>
+          <t>生技醫療業平上市</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>1204.498288</v>
+      </c>
       <c r="C78" t="n">
-        <v>0.410267</v>
+        <v>1114.28476</v>
       </c>
       <c r="D78" t="n">
-        <v>0.761396</v>
+        <v>52.616483</v>
       </c>
       <c r="E78" t="n">
-        <v>1.724247</v>
+        <v>466.542454</v>
       </c>
       <c r="F78" t="n">
-        <v>0.731829</v>
+        <v>85.77894999999999</v>
       </c>
       <c r="G78" t="n">
-        <v>0.6091839999999999</v>
+        <v>103.755408</v>
       </c>
       <c r="H78" t="n">
-        <v>0.471479</v>
+        <v>138.845666</v>
       </c>
       <c r="I78" t="n">
-        <v>0.588156</v>
+        <v>387.875188</v>
       </c>
       <c r="J78" t="n">
-        <v>0.394233</v>
-      </c>
-      <c r="K78" t="n">
-        <v>0.465057</v>
-      </c>
-      <c r="L78" t="n">
-        <v>0.564678</v>
+        <v>129.548609</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右上上市</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr"/>
+          <t>生技醫療業平上櫃</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>0.09131</v>
+      </c>
       <c r="C79" t="n">
-        <v>2081.488032</v>
+        <v>0.105263</v>
       </c>
       <c r="D79" t="n">
-        <v>4040.848687</v>
+        <v>0.164759</v>
       </c>
       <c r="E79" t="n">
-        <v>5947.292629</v>
+        <v>0.165728</v>
       </c>
       <c r="F79" t="n">
-        <v>7373.941224</v>
+        <v>0.1738</v>
       </c>
       <c r="G79" t="n">
-        <v>3609.281076</v>
+        <v>0.06646000000000001</v>
       </c>
       <c r="H79" t="n">
-        <v>2379.393795</v>
+        <v>0.181862</v>
       </c>
       <c r="I79" t="n">
-        <v>1238.302682</v>
+        <v>0.126775</v>
       </c>
       <c r="J79" t="n">
-        <v>1335.538883</v>
-      </c>
-      <c r="K79" t="n">
-        <v>1123.258023</v>
-      </c>
-      <c r="L79" t="n">
-        <v>1058.12963</v>
+        <v>0.097179</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右上上櫃</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr"/>
+          <t>紡織纖維右上上市</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>732.466211</v>
+      </c>
       <c r="C80" t="n">
-        <v>0.001332</v>
+        <v>187.341735</v>
       </c>
       <c r="D80" t="n">
-        <v>0.003188</v>
+        <v>243.927543</v>
       </c>
       <c r="E80" t="n">
-        <v>0.003318</v>
+        <v>156.612433</v>
       </c>
       <c r="F80" t="n">
-        <v>0.003451</v>
+        <v>292.472929</v>
       </c>
       <c r="G80" t="n">
-        <v>0.002415</v>
+        <v>185.653581</v>
       </c>
       <c r="H80" t="n">
-        <v>0.001719</v>
+        <v>680.52637</v>
       </c>
       <c r="I80" t="n">
-        <v>0.00509</v>
+        <v>253.387223</v>
       </c>
       <c r="J80" t="n">
-        <v>0.00259</v>
-      </c>
-      <c r="K80" t="n">
-        <v>0.001986</v>
-      </c>
-      <c r="L80" t="n">
-        <v>0.00308</v>
+        <v>522.9243310000001</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右下上市</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr"/>
+          <t>紡織纖維右上上櫃</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>0.0009493333333333333</v>
+      </c>
       <c r="C81" t="n">
-        <v>727.87618</v>
+        <v>0.002949</v>
       </c>
       <c r="D81" t="n">
-        <v>1080.959869</v>
+        <v>0.004252</v>
       </c>
       <c r="E81" t="n">
-        <v>1102.917999</v>
+        <v>0.002614</v>
       </c>
       <c r="F81" t="n">
-        <v>2339.591473</v>
+        <v>0.003562</v>
       </c>
       <c r="G81" t="n">
-        <v>1563.208646</v>
+        <v>0.002342</v>
       </c>
       <c r="H81" t="n">
-        <v>1737.038516</v>
+        <v>0.003026</v>
       </c>
       <c r="I81" t="n">
-        <v>2521.94624</v>
+        <v>0.000842</v>
       </c>
       <c r="J81" t="n">
-        <v>2094.826107</v>
-      </c>
-      <c r="K81" t="n">
-        <v>1782.033739</v>
-      </c>
-      <c r="L81" t="n">
-        <v>952.102422</v>
+        <v>0.001892</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右下上櫃</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr"/>
+          <t>紡織纖維右下上市</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>752.129802</v>
+      </c>
       <c r="C82" t="n">
-        <v>0.008377000000000001</v>
+        <v>538.748886</v>
       </c>
       <c r="D82" t="n">
-        <v>0.011077</v>
+        <v>1029.650505</v>
       </c>
       <c r="E82" t="n">
-        <v>0.012388</v>
+        <v>529.1533889999999</v>
       </c>
       <c r="F82" t="n">
-        <v>0.004055</v>
+        <v>559.467184</v>
       </c>
       <c r="G82" t="n">
-        <v>0.00465</v>
+        <v>497.35158</v>
       </c>
       <c r="H82" t="n">
-        <v>0.012185</v>
+        <v>690.9260829999999</v>
       </c>
       <c r="I82" t="n">
-        <v>0.018001</v>
+        <v>429.938206</v>
       </c>
       <c r="J82" t="n">
-        <v>0.016048</v>
-      </c>
-      <c r="K82" t="n">
-        <v>0.007402</v>
-      </c>
-      <c r="L82" t="n">
-        <v>0.005703</v>
+        <v>409.600498</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維平上市</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr"/>
+          <t>紡織纖維右下上櫃</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>0.0055</v>
+      </c>
       <c r="C83" t="n">
-        <v>331.665676</v>
+        <v>0.005398</v>
       </c>
       <c r="D83" t="n">
-        <v>861.274229</v>
+        <v>0.009835</v>
       </c>
       <c r="E83" t="n">
-        <v>393.903896</v>
+        <v>0.003755</v>
       </c>
       <c r="F83" t="n">
-        <v>624.320844</v>
+        <v>0.003866</v>
       </c>
       <c r="G83" t="n">
-        <v>791.4819220000001</v>
+        <v>0.002449</v>
       </c>
       <c r="H83" t="n">
-        <v>56.597864</v>
+        <v>0.005551</v>
       </c>
       <c r="I83" t="n">
-        <v>30.226962</v>
+        <v>0.003023</v>
       </c>
       <c r="J83" t="n">
-        <v>33.243685</v>
-      </c>
-      <c r="K83" t="n">
-        <v>51.314166</v>
-      </c>
-      <c r="L83" t="n">
-        <v>643.991274</v>
+        <v>0.002772</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維平上櫃</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr"/>
+          <t>紡織纖維平上市</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>46.233444</v>
+      </c>
       <c r="C84" t="n">
-        <v>0.00139</v>
+        <v>197.458483</v>
       </c>
       <c r="D84" t="n">
-        <v>0.008061</v>
+        <v>181.637446</v>
       </c>
       <c r="E84" t="n">
-        <v>0.005062</v>
+        <v>195.153821</v>
       </c>
       <c r="F84" t="n">
-        <v>0.006218</v>
+        <v>89.492357</v>
       </c>
       <c r="G84" t="n">
-        <v>0.005282</v>
-      </c>
-      <c r="H84" t="inlineStr"/>
+        <v>225.18276</v>
+      </c>
+      <c r="H84" t="n">
+        <v>15.404155</v>
+      </c>
       <c r="I84" t="n">
-        <v>0.000337</v>
+        <v>464.799887</v>
       </c>
       <c r="J84" t="n">
-        <v>0.000376</v>
-      </c>
-      <c r="K84" t="n">
-        <v>0.000149</v>
-      </c>
-      <c r="L84" t="n">
-        <v>0.000116</v>
+        <v>41.503846</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右上上市</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr"/>
+          <t>紡織纖維平上櫃</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>0.009106</v>
+      </c>
       <c r="C85" t="n">
-        <v>1123.540797</v>
+        <v>0.002764</v>
       </c>
       <c r="D85" t="n">
-        <v>1067.240207</v>
+        <v>0.002626</v>
       </c>
       <c r="E85" t="n">
-        <v>1264.303834</v>
+        <v>0.003386</v>
       </c>
       <c r="F85" t="n">
-        <v>1413.309729</v>
+        <v>0.001247</v>
       </c>
       <c r="G85" t="n">
-        <v>3671.565789</v>
+        <v>0.002145</v>
       </c>
       <c r="H85" t="n">
-        <v>3320.730909</v>
+        <v>0.003993</v>
       </c>
       <c r="I85" t="n">
-        <v>2250.84936</v>
+        <v>0.001704</v>
       </c>
       <c r="J85" t="n">
-        <v>2955.262345</v>
-      </c>
-      <c r="K85" t="n">
-        <v>2018.559697</v>
-      </c>
-      <c r="L85" t="n">
-        <v>2495.187563</v>
+        <v>0.001875</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右上上櫃</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr"/>
+          <t>綠能環保右上上市</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>4961.954771</v>
+      </c>
       <c r="C86" t="n">
-        <v>0.148657</v>
+        <v>1355.177009</v>
       </c>
       <c r="D86" t="n">
-        <v>0.1728</v>
+        <v>1169.933032</v>
       </c>
       <c r="E86" t="n">
-        <v>0.328383</v>
+        <v>1083.445147</v>
       </c>
       <c r="F86" t="n">
-        <v>0.264843</v>
+        <v>987.254875</v>
       </c>
       <c r="G86" t="n">
-        <v>0.130741</v>
+        <v>1065.228574</v>
       </c>
       <c r="H86" t="n">
-        <v>0.303413</v>
+        <v>1461.418548</v>
       </c>
       <c r="I86" t="n">
-        <v>0.346477</v>
+        <v>1090.069752</v>
       </c>
       <c r="J86" t="n">
-        <v>0.33183</v>
-      </c>
-      <c r="K86" t="n">
-        <v>0.99458</v>
-      </c>
-      <c r="L86" t="n">
-        <v>1.124607</v>
+        <v>1296.447198</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右下上市</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr"/>
+          <t>綠能環保右上上櫃</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>0.075873</v>
+      </c>
       <c r="C87" t="n">
-        <v>626.868787</v>
+        <v>0.123075</v>
       </c>
       <c r="D87" t="n">
-        <v>2226.803993</v>
+        <v>0.056319</v>
       </c>
       <c r="E87" t="n">
-        <v>1029.922883</v>
+        <v>0.08539099999999999</v>
       </c>
       <c r="F87" t="n">
-        <v>915.7144070000001</v>
+        <v>0.08933199999999999</v>
       </c>
       <c r="G87" t="n">
-        <v>664.683191</v>
+        <v>0.031627</v>
       </c>
       <c r="H87" t="n">
-        <v>435.230158</v>
+        <v>0.034733</v>
       </c>
       <c r="I87" t="n">
-        <v>644.077276</v>
+        <v>0.06268700000000001</v>
       </c>
       <c r="J87" t="n">
-        <v>859.683461</v>
-      </c>
-      <c r="K87" t="n">
-        <v>387.117663</v>
-      </c>
-      <c r="L87" t="n">
-        <v>282.29799</v>
+        <v>0.668552</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右下上櫃</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr"/>
+          <t>綠能環保右下上市</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>948.345542</v>
+      </c>
       <c r="C88" t="n">
-        <v>0.012602</v>
+        <v>528.034793</v>
       </c>
       <c r="D88" t="n">
-        <v>0.102444</v>
+        <v>621.8295010000001</v>
       </c>
       <c r="E88" t="n">
-        <v>0.06436699999999999</v>
+        <v>539.273703</v>
       </c>
       <c r="F88" t="n">
-        <v>0.103024</v>
+        <v>278.616048</v>
       </c>
       <c r="G88" t="n">
-        <v>0.0502</v>
+        <v>274.468824</v>
       </c>
       <c r="H88" t="n">
-        <v>0.017408</v>
+        <v>246.334542</v>
       </c>
       <c r="I88" t="n">
-        <v>0.07094</v>
+        <v>273.107014</v>
       </c>
       <c r="J88" t="n">
-        <v>0.07088999999999999</v>
-      </c>
-      <c r="K88" t="n">
-        <v>0.028894</v>
-      </c>
-      <c r="L88" t="n">
-        <v>0.034939</v>
+        <v>308.175048</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>綠能環保平上市</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr"/>
+          <t>綠能環保右下上櫃</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>0.04692425</v>
+      </c>
       <c r="C89" t="n">
-        <v>51.646856</v>
+        <v>0.040527</v>
       </c>
       <c r="D89" t="n">
-        <v>94.489932</v>
+        <v>0.223725</v>
       </c>
       <c r="E89" t="n">
-        <v>22.8336</v>
+        <v>0.2862343333333333</v>
       </c>
       <c r="F89" t="n">
-        <v>146.01117</v>
+        <v>0.114534</v>
       </c>
       <c r="G89" t="n">
-        <v>225.507906</v>
+        <v>0.06042566666666667</v>
       </c>
       <c r="H89" t="n">
-        <v>82.356973</v>
+        <v>0.040755</v>
       </c>
       <c r="I89" t="n">
-        <v>154.875297</v>
+        <v>0.03678</v>
       </c>
       <c r="J89" t="n">
-        <v>60.20533</v>
-      </c>
-      <c r="K89" t="n">
-        <v>27.060787</v>
-      </c>
-      <c r="L89" t="n">
-        <v>39.103909</v>
+        <v>0.041197</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>綠能環保平上櫃</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr"/>
+          <t>綠能環保平上市</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>43.441831</v>
+      </c>
       <c r="C90" t="n">
-        <v>0.0924</v>
+        <v>14.02138</v>
       </c>
       <c r="D90" t="n">
-        <v>0.017271</v>
+        <v>87.93873600000001</v>
       </c>
       <c r="E90" t="n">
-        <v>0.031136</v>
+        <v>13.809897</v>
       </c>
       <c r="F90" t="n">
-        <v>0.006781</v>
+        <v>456.031398</v>
       </c>
       <c r="G90" t="n">
-        <v>0.018228</v>
+        <v>544.36019</v>
       </c>
       <c r="H90" t="n">
-        <v>0.014449</v>
+        <v>411.932598</v>
       </c>
       <c r="I90" t="n">
-        <v>0.029006</v>
+        <v>545.813419</v>
       </c>
       <c r="J90" t="n">
-        <v>0.016505</v>
-      </c>
-      <c r="K90" t="n">
-        <v>0.006947</v>
-      </c>
-      <c r="L90" t="n">
-        <v>0.000345</v>
+        <v>390.621942</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>航運業右上上市</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr"/>
+          <t>綠能環保平上櫃</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>0.271423</v>
+      </c>
       <c r="C91" t="n">
-        <v>7450.73606</v>
+        <v>0.355539</v>
       </c>
       <c r="D91" t="n">
-        <v>9382.611312000001</v>
+        <v>0.013315</v>
       </c>
       <c r="E91" t="n">
-        <v>15933.90096</v>
+        <v>0.001381</v>
       </c>
       <c r="F91" t="n">
-        <v>9765.371423000001</v>
+        <v>0.000392</v>
       </c>
       <c r="G91" t="n">
-        <v>11608.204189</v>
+        <v>0.179047</v>
       </c>
       <c r="H91" t="n">
-        <v>12044.728934</v>
+        <v>0.177882</v>
       </c>
       <c r="I91" t="n">
-        <v>13825.103709</v>
+        <v>0.215974</v>
       </c>
       <c r="J91" t="n">
-        <v>21369.238958</v>
-      </c>
-      <c r="K91" t="n">
-        <v>12333.181332</v>
-      </c>
-      <c r="L91" t="n">
-        <v>6912.22509</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>航運業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr"/>
-      <c r="C92" t="inlineStr"/>
+          <t>航運業右上上市</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>11853.026073</v>
+      </c>
+      <c r="C92" t="n">
+        <v>6250.921795</v>
+      </c>
       <c r="D92" t="n">
-        <v>0.000489</v>
-      </c>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
+        <v>5391.171935</v>
+      </c>
+      <c r="E92" t="n">
+        <v>6706.51643</v>
+      </c>
+      <c r="F92" t="n">
+        <v>4550.993342</v>
+      </c>
+      <c r="G92" t="n">
+        <v>6235.148024</v>
+      </c>
+      <c r="H92" t="n">
+        <v>5045.109869</v>
+      </c>
+      <c r="I92" t="n">
+        <v>4288.824517</v>
+      </c>
+      <c r="J92" t="n">
+        <v>4613.845504</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
@@ -3893,37 +3545,31 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0</v>
+        <v>784.947189</v>
       </c>
       <c r="C93" t="n">
-        <v>2621.276264</v>
+        <v>240.273186</v>
       </c>
       <c r="D93" t="n">
-        <v>2845.56978</v>
+        <v>321.987568</v>
       </c>
       <c r="E93" t="n">
-        <v>1408.903913</v>
+        <v>323.013159</v>
       </c>
       <c r="F93" t="n">
-        <v>6667.482546</v>
+        <v>223.085712</v>
       </c>
       <c r="G93" t="n">
-        <v>1696.958916</v>
+        <v>319.29705</v>
       </c>
       <c r="H93" t="n">
-        <v>981.860132</v>
+        <v>272.893445</v>
       </c>
       <c r="I93" t="n">
-        <v>2747.592237</v>
+        <v>227.609198</v>
       </c>
       <c r="J93" t="n">
-        <v>3045.094229</v>
-      </c>
-      <c r="K93" t="n">
-        <v>1428.924639</v>
-      </c>
-      <c r="L93" t="n">
-        <v>842.0437480000001</v>
+        <v>252.512685</v>
       </c>
     </row>
     <row r="94">
@@ -3933,37 +3579,31 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0</v>
+        <v>0.0307545</v>
       </c>
       <c r="C94" t="n">
-        <v>0.027208</v>
+        <v>0.023707</v>
       </c>
       <c r="D94" t="n">
-        <v>0.049209</v>
+        <v>0.017652</v>
       </c>
       <c r="E94" t="n">
-        <v>0.035102</v>
+        <v>0.0187445</v>
       </c>
       <c r="F94" t="n">
-        <v>0.032845</v>
+        <v>0.015171</v>
       </c>
       <c r="G94" t="n">
-        <v>0.017689</v>
+        <v>0.027518</v>
       </c>
       <c r="H94" t="n">
-        <v>0.01737</v>
+        <v>0.031577</v>
       </c>
       <c r="I94" t="n">
-        <v>0.019508</v>
+        <v>0.018536</v>
       </c>
       <c r="J94" t="n">
-        <v>0.040315</v>
-      </c>
-      <c r="K94" t="n">
-        <v>0.0244865</v>
-      </c>
-      <c r="L94" t="n">
-        <v>0.027712</v>
+        <v>0.021268</v>
       </c>
     </row>
     <row r="95">
@@ -3972,36 +3612,32 @@
           <t>航運業平上市</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr"/>
+      <c r="B95" t="n">
+        <v>885.59461</v>
+      </c>
       <c r="C95" t="n">
-        <v>1020.823342</v>
+        <v>449.23892</v>
       </c>
       <c r="D95" t="n">
-        <v>7366.80687</v>
+        <v>637.521775</v>
       </c>
       <c r="E95" t="n">
-        <v>3247.917137</v>
+        <v>901.599531</v>
       </c>
       <c r="F95" t="n">
-        <v>241.076198</v>
+        <v>692.5978699999999</v>
       </c>
       <c r="G95" t="n">
-        <v>3420.627225</v>
+        <v>291.581164</v>
       </c>
       <c r="H95" t="n">
-        <v>1985.345934</v>
+        <v>526.1090380000001</v>
       </c>
       <c r="I95" t="n">
-        <v>2753.295012</v>
+        <v>397.091163</v>
       </c>
       <c r="J95" t="n">
-        <v>3041.268128</v>
-      </c>
-      <c r="K95" t="n">
-        <v>4004.428537</v>
-      </c>
-      <c r="L95" t="n">
-        <v>2522.275096</v>
+        <v>293.732243</v>
       </c>
     </row>
     <row r="96">
@@ -4010,37 +3646,23 @@
           <t>航運業平上櫃</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr"/>
+      <c r="B96" t="n">
+        <v>0.015036</v>
+      </c>
       <c r="C96" t="n">
-        <v>0.000676</v>
+        <v>0.007715</v>
       </c>
       <c r="D96" t="n">
-        <v>0.02213</v>
+        <v>0.003387</v>
       </c>
       <c r="E96" t="n">
-        <v>0.036225</v>
-      </c>
-      <c r="F96" t="n">
-        <v>0.036514</v>
-      </c>
-      <c r="G96" t="n">
-        <v>0.016543</v>
-      </c>
-      <c r="H96" t="n">
-        <v>0.007261</v>
-      </c>
-      <c r="I96" t="n">
-        <v>0.009464999999999999</v>
-      </c>
-      <c r="J96" t="n">
-        <v>0.012759</v>
-      </c>
-      <c r="K96" t="n">
-        <v>0.008349000000000001</v>
-      </c>
-      <c r="L96" t="n">
-        <v>0.00719</v>
-      </c>
+        <v>0.003643</v>
+      </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
@@ -4048,36 +3670,32 @@
           <t>觀光事業右上上市</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr"/>
+      <c r="B97" t="n">
+        <v>27.444641</v>
+      </c>
       <c r="C97" t="n">
-        <v>80.796819</v>
+        <v>19.597812</v>
       </c>
       <c r="D97" t="n">
-        <v>162.64116</v>
+        <v>17.981812</v>
       </c>
       <c r="E97" t="n">
-        <v>185.206541</v>
+        <v>12.021829</v>
       </c>
       <c r="F97" t="n">
-        <v>154.420246</v>
+        <v>135.017384</v>
       </c>
       <c r="G97" t="n">
-        <v>128.368286</v>
+        <v>139.47937</v>
       </c>
       <c r="H97" t="n">
-        <v>147.642624</v>
+        <v>81.415419</v>
       </c>
       <c r="I97" t="n">
-        <v>164.591011</v>
+        <v>52.444073</v>
       </c>
       <c r="J97" t="n">
-        <v>8.167926</v>
-      </c>
-      <c r="K97" t="n">
-        <v>301.087083</v>
-      </c>
-      <c r="L97" t="n">
-        <v>4.112135</v>
+        <v>95.54313500000001</v>
       </c>
     </row>
     <row r="98">
@@ -4086,36 +3704,32 @@
           <t>觀光事業右上上櫃</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr"/>
+      <c r="B98" t="n">
+        <v>0.010605</v>
+      </c>
       <c r="C98" t="n">
-        <v>0.024377</v>
+        <v>0.009384</v>
       </c>
       <c r="D98" t="n">
-        <v>0.016875</v>
+        <v>0.002788</v>
       </c>
       <c r="E98" t="n">
-        <v>0.02559</v>
+        <v>0.005511</v>
       </c>
       <c r="F98" t="n">
-        <v>0.021918</v>
+        <v>0.005694</v>
       </c>
       <c r="G98" t="n">
-        <v>0.00839</v>
+        <v>0.009537</v>
       </c>
       <c r="H98" t="n">
-        <v>0.02421741666666667</v>
+        <v>0.028504</v>
       </c>
       <c r="I98" t="n">
-        <v>0.019662</v>
+        <v>0.0221175</v>
       </c>
       <c r="J98" t="n">
-        <v>0.002502</v>
-      </c>
-      <c r="K98" t="n">
-        <v>0.025627</v>
-      </c>
-      <c r="L98" t="n">
-        <v>0.016796</v>
+        <v>0.00347</v>
       </c>
     </row>
     <row r="99">
@@ -4125,37 +3739,31 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0</v>
+        <v>100.201892</v>
       </c>
       <c r="C99" t="n">
-        <v>226.291946</v>
+        <v>57.639539</v>
       </c>
       <c r="D99" t="n">
-        <v>317.127586</v>
+        <v>70.396855</v>
       </c>
       <c r="E99" t="n">
-        <v>226.967204</v>
+        <v>73.746514</v>
       </c>
       <c r="F99" t="n">
-        <v>242.471973</v>
+        <v>57.692754</v>
       </c>
       <c r="G99" t="n">
-        <v>206.639845</v>
+        <v>82.187201</v>
       </c>
       <c r="H99" t="n">
-        <v>236.056368</v>
+        <v>75.432047</v>
       </c>
       <c r="I99" t="n">
-        <v>200.753375</v>
+        <v>40.885461</v>
       </c>
       <c r="J99" t="n">
-        <v>271.63988</v>
-      </c>
-      <c r="K99" t="n">
-        <v>124.983924</v>
-      </c>
-      <c r="L99" t="n">
-        <v>489.449081</v>
+        <v>48.094337</v>
       </c>
     </row>
     <row r="100">
@@ -4164,36 +3772,32 @@
           <t>觀光事業右下上櫃</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr"/>
+      <c r="B100" t="n">
+        <v>0.040576</v>
+      </c>
       <c r="C100" t="n">
-        <v>0.052286</v>
+        <v>0.034939</v>
       </c>
       <c r="D100" t="n">
-        <v>0.070019</v>
+        <v>0.035491</v>
       </c>
       <c r="E100" t="n">
-        <v>0.067685</v>
+        <v>0.0379</v>
       </c>
       <c r="F100" t="n">
-        <v>0.067493</v>
+        <v>0.031228</v>
       </c>
       <c r="G100" t="n">
-        <v>0.037576</v>
+        <v>0.02585375</v>
       </c>
       <c r="H100" t="n">
-        <v>0.045288</v>
+        <v>0.025105</v>
       </c>
       <c r="I100" t="n">
-        <v>0.070677</v>
+        <v>0.021688</v>
       </c>
       <c r="J100" t="n">
-        <v>0.090269</v>
-      </c>
-      <c r="K100" t="n">
-        <v>0.061664</v>
-      </c>
-      <c r="L100" t="n">
-        <v>0.078516</v>
+        <v>0.02571725</v>
       </c>
     </row>
     <row r="101">
@@ -4202,33 +3806,29 @@
           <t>觀光事業平上市</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr"/>
+      <c r="B101" t="n">
+        <v>52.412322</v>
+      </c>
       <c r="C101" t="n">
-        <v>7.166836</v>
+        <v>26.443981</v>
       </c>
       <c r="D101" t="n">
-        <v>3.031453</v>
+        <v>63.217595</v>
       </c>
       <c r="E101" t="n">
-        <v>11.793554</v>
+        <v>42.480294</v>
       </c>
       <c r="F101" t="n">
-        <v>9.814275</v>
+        <v>0.38104</v>
       </c>
       <c r="G101" t="n">
-        <v>14.544585</v>
+        <v>0.7070109999999999</v>
       </c>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="n">
-        <v>0.69748</v>
-      </c>
-      <c r="J101" t="n">
-        <v>246.116607</v>
-      </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="n">
-        <v>3.108569</v>
-      </c>
+        <v>70.926901</v>
+      </c>
+      <c r="J101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
@@ -4236,36 +3836,32 @@
           <t>觀光事業平上櫃</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr"/>
+      <c r="B102" t="n">
+        <v>0.004231</v>
+      </c>
       <c r="C102" t="n">
-        <v>0.006582</v>
+        <v>0.005689</v>
       </c>
       <c r="D102" t="n">
-        <v>0.002347</v>
+        <v>0.002429</v>
       </c>
       <c r="E102" t="n">
-        <v>0.004194</v>
+        <v>0.002757</v>
       </c>
       <c r="F102" t="n">
-        <v>0.000874</v>
+        <v>0.001546</v>
       </c>
       <c r="G102" t="n">
-        <v>0.001478</v>
+        <v>0.000648</v>
       </c>
       <c r="H102" t="n">
-        <v>0.001685</v>
+        <v>0.002487</v>
       </c>
       <c r="I102" t="n">
-        <v>0.00272</v>
+        <v>0.000375</v>
       </c>
       <c r="J102" t="n">
-        <v>0.016803</v>
-      </c>
-      <c r="K102" t="n">
-        <v>0.001504</v>
-      </c>
-      <c r="L102" t="n">
-        <v>0.002719</v>
+        <v>0.00052</v>
       </c>
     </row>
     <row r="103">
@@ -4274,36 +3870,32 @@
           <t>貿易百貨右上上市</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr"/>
+      <c r="B103" t="n">
+        <v>213.17421</v>
+      </c>
       <c r="C103" t="n">
-        <v>35.740115</v>
+        <v>118.613415</v>
       </c>
       <c r="D103" t="n">
-        <v>60.167468</v>
+        <v>134.583649</v>
       </c>
       <c r="E103" t="n">
-        <v>25.110235</v>
+        <v>173.191176</v>
       </c>
       <c r="F103" t="n">
-        <v>40.914587</v>
+        <v>124.12725</v>
       </c>
       <c r="G103" t="n">
-        <v>39.256066</v>
+        <v>123.87734</v>
       </c>
       <c r="H103" t="n">
-        <v>37.543773</v>
+        <v>101.572075</v>
       </c>
       <c r="I103" t="n">
-        <v>43.673527</v>
+        <v>97.257312</v>
       </c>
       <c r="J103" t="n">
-        <v>59.610908</v>
-      </c>
-      <c r="K103" t="n">
-        <v>49.021186</v>
-      </c>
-      <c r="L103" t="n">
-        <v>1321.365387</v>
+        <v>116.831751</v>
       </c>
     </row>
     <row r="104">
@@ -4313,37 +3905,31 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0</v>
+        <v>662.673498</v>
       </c>
       <c r="C104" t="n">
-        <v>987.154116</v>
+        <v>283.905508</v>
       </c>
       <c r="D104" t="n">
-        <v>1001.905185</v>
+        <v>228.051738</v>
       </c>
       <c r="E104" t="n">
-        <v>52.83609125</v>
+        <v>545.00246</v>
       </c>
       <c r="F104" t="n">
-        <v>23.496761</v>
+        <v>502.007682</v>
       </c>
       <c r="G104" t="n">
-        <v>49.422937</v>
+        <v>353.8224913333333</v>
       </c>
       <c r="H104" t="n">
-        <v>288.193351</v>
+        <v>405.806172</v>
       </c>
       <c r="I104" t="n">
-        <v>140.276804</v>
+        <v>516.970554</v>
       </c>
       <c r="J104" t="n">
-        <v>84.784221</v>
-      </c>
-      <c r="K104" t="n">
-        <v>32.422903</v>
-      </c>
-      <c r="L104" t="n">
-        <v>49.587701</v>
+        <v>676.738581</v>
       </c>
     </row>
     <row r="105">
@@ -4352,36 +3938,32 @@
           <t>貿易百貨平上市</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr"/>
+      <c r="B105" t="n">
+        <v>1.055977</v>
+      </c>
       <c r="C105" t="n">
-        <v>111.409478</v>
+        <v>31.438809</v>
       </c>
       <c r="D105" t="n">
-        <v>118.40061</v>
+        <v>1.363332</v>
       </c>
       <c r="E105" t="n">
-        <v>1170.764112</v>
+        <v>9.015001</v>
       </c>
       <c r="F105" t="n">
-        <v>961.1492929999999</v>
+        <v>0.238075</v>
       </c>
       <c r="G105" t="n">
-        <v>651.197846</v>
+        <v>1.958319</v>
       </c>
       <c r="H105" t="n">
-        <v>868.342433</v>
+        <v>3.482226</v>
       </c>
       <c r="I105" t="n">
-        <v>753.365221</v>
+        <v>1.073951</v>
       </c>
       <c r="J105" t="n">
-        <v>882.65675</v>
-      </c>
-      <c r="K105" t="n">
-        <v>1428.816704</v>
-      </c>
-      <c r="L105" t="n">
-        <v>386.999991</v>
+        <v>2.602827</v>
       </c>
     </row>
     <row r="106">
@@ -4390,36 +3972,32 @@
           <t>資訊服務業右上上市</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr"/>
+      <c r="B106" t="n">
+        <v>2420.209919</v>
+      </c>
       <c r="C106" t="n">
-        <v>276.609217</v>
+        <v>2324.315633</v>
       </c>
       <c r="D106" t="n">
-        <v>201.449156</v>
+        <v>999.44839</v>
       </c>
       <c r="E106" t="n">
-        <v>354.056332</v>
+        <v>816.0570310000001</v>
       </c>
       <c r="F106" t="n">
-        <v>300.141046</v>
+        <v>921.361164</v>
       </c>
       <c r="G106" t="n">
-        <v>143.044808</v>
+        <v>525.655053</v>
       </c>
       <c r="H106" t="n">
-        <v>784.290875</v>
+        <v>637.545508</v>
       </c>
       <c r="I106" t="n">
-        <v>331.108162</v>
+        <v>335.86408</v>
       </c>
       <c r="J106" t="n">
-        <v>250.765921</v>
-      </c>
-      <c r="K106" t="n">
-        <v>155.027177</v>
-      </c>
-      <c r="L106" t="n">
-        <v>183.967625</v>
+        <v>309.39226</v>
       </c>
     </row>
     <row r="107">
@@ -4428,36 +4006,32 @@
           <t>資訊服務業右上上櫃</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr"/>
+      <c r="B107" t="n">
+        <v>0.735469</v>
+      </c>
       <c r="C107" t="n">
-        <v>0.797808</v>
+        <v>0.968853</v>
       </c>
       <c r="D107" t="n">
-        <v>0.689758</v>
+        <v>0.28803</v>
       </c>
       <c r="E107" t="n">
-        <v>0.522277</v>
+        <v>0.180248</v>
       </c>
       <c r="F107" t="n">
-        <v>0.441195</v>
+        <v>0.624803</v>
       </c>
       <c r="G107" t="n">
-        <v>0.234436</v>
+        <v>0.272337</v>
       </c>
       <c r="H107" t="n">
-        <v>0.250564</v>
+        <v>0.270188</v>
       </c>
       <c r="I107" t="n">
-        <v>0.297532</v>
+        <v>0.531964</v>
       </c>
       <c r="J107" t="n">
-        <v>0.253392</v>
-      </c>
-      <c r="K107" t="n">
-        <v>0.146024</v>
-      </c>
-      <c r="L107" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.654319</v>
       </c>
     </row>
     <row r="108">
@@ -4466,36 +4040,32 @@
           <t>資訊服務業右下上市</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr"/>
+      <c r="B108" t="n">
+        <v>15.956034</v>
+      </c>
       <c r="C108" t="n">
-        <v>421.747591</v>
+        <v>7.692126</v>
       </c>
       <c r="D108" t="n">
-        <v>383.561188</v>
+        <v>5.549619</v>
       </c>
       <c r="E108" t="n">
-        <v>289.770115</v>
+        <v>4.066226</v>
       </c>
       <c r="F108" t="n">
-        <v>263.713062</v>
+        <v>6.540235</v>
       </c>
       <c r="G108" t="n">
-        <v>153.229089</v>
+        <v>16.557683</v>
       </c>
       <c r="H108" t="n">
-        <v>157.846677</v>
+        <v>8.925591000000001</v>
       </c>
       <c r="I108" t="n">
-        <v>163.648316</v>
+        <v>4.865924</v>
       </c>
       <c r="J108" t="n">
-        <v>246.953155</v>
-      </c>
-      <c r="K108" t="n">
-        <v>117.381949</v>
-      </c>
-      <c r="L108" t="n">
-        <v>168.120568</v>
+        <v>13.219645</v>
       </c>
     </row>
     <row r="109">
@@ -4505,37 +4075,31 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0</v>
+        <v>0.131389</v>
       </c>
       <c r="C109" t="n">
-        <v>0.104145</v>
+        <v>0.180008</v>
       </c>
       <c r="D109" t="n">
-        <v>0.186839</v>
+        <v>0.16141</v>
       </c>
       <c r="E109" t="n">
-        <v>0.08981699999999999</v>
+        <v>0.11476</v>
       </c>
       <c r="F109" t="n">
-        <v>0.143509</v>
+        <v>0.06328499999999999</v>
       </c>
       <c r="G109" t="n">
-        <v>0.07843650000000001</v>
+        <v>0.0534</v>
       </c>
       <c r="H109" t="n">
-        <v>0.08780300000000001</v>
+        <v>0.09637</v>
       </c>
       <c r="I109" t="n">
-        <v>0.08233024999999999</v>
+        <v>0.060962</v>
       </c>
       <c r="J109" t="n">
-        <v>0.108816</v>
-      </c>
-      <c r="K109" t="n">
-        <v>0.05478</v>
-      </c>
-      <c r="L109" t="n">
-        <v>0.05159075</v>
+        <v>0.066687</v>
       </c>
     </row>
     <row r="110">
@@ -4544,36 +4108,32 @@
           <t>資訊服務業平上市</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr"/>
+      <c r="B110" t="n">
+        <v>35.293026</v>
+      </c>
       <c r="C110" t="n">
-        <v>45.562417</v>
+        <v>55.909266</v>
       </c>
       <c r="D110" t="n">
-        <v>456.857907</v>
+        <v>32.594114</v>
       </c>
       <c r="E110" t="n">
-        <v>331.755663</v>
+        <v>39.491765</v>
       </c>
       <c r="F110" t="n">
-        <v>200.173124</v>
+        <v>48.614308</v>
       </c>
       <c r="G110" t="n">
-        <v>193.526187</v>
+        <v>23.721963</v>
       </c>
       <c r="H110" t="n">
-        <v>51.991214</v>
+        <v>32.069459</v>
       </c>
       <c r="I110" t="n">
-        <v>137.366546</v>
+        <v>18.425521</v>
       </c>
       <c r="J110" t="n">
-        <v>150.849742</v>
-      </c>
-      <c r="K110" t="n">
-        <v>146.703642</v>
-      </c>
-      <c r="L110" t="n">
-        <v>35.405321</v>
+        <v>18.234497</v>
       </c>
     </row>
     <row r="111">
@@ -4582,108 +4142,100 @@
           <t>資訊服務業平上櫃</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr"/>
+      <c r="B111" t="n">
+        <v>0.086302</v>
+      </c>
       <c r="C111" t="n">
-        <v>0.016298</v>
+        <v>0.011431</v>
       </c>
       <c r="D111" t="n">
-        <v>0.007055</v>
+        <v>0.077565</v>
       </c>
       <c r="E111" t="n">
-        <v>0.000728</v>
+        <v>0.029834</v>
       </c>
       <c r="F111" t="n">
-        <v>0.024579</v>
+        <v>0.183793</v>
       </c>
       <c r="G111" t="n">
-        <v>0.009665999999999999</v>
+        <v>0.171734</v>
       </c>
       <c r="H111" t="n">
-        <v>0.020622</v>
+        <v>0.128434</v>
       </c>
       <c r="I111" t="n">
-        <v>0.05304</v>
+        <v>0.07986699999999999</v>
       </c>
       <c r="J111" t="n">
-        <v>0.239913</v>
-      </c>
-      <c r="K111" t="n">
-        <v>0.09747500000000001</v>
-      </c>
-      <c r="L111" t="n">
-        <v>0.09071</v>
+        <v>0.114254</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>農業科技業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr"/>
+          <t>農業科技業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>0.006962</v>
+      </c>
       <c r="C112" t="n">
-        <v>0.003966</v>
+        <v>0.035455</v>
       </c>
       <c r="D112" t="n">
-        <v>0.003958</v>
+        <v>0.010882</v>
       </c>
       <c r="E112" t="n">
-        <v>0.002881</v>
+        <v>0.003346</v>
       </c>
       <c r="F112" t="n">
-        <v>0.003538</v>
+        <v>0.00109</v>
       </c>
       <c r="G112" t="n">
-        <v>0.004218</v>
+        <v>0.000695</v>
       </c>
       <c r="H112" t="n">
-        <v>0.002593</v>
+        <v>0.000838</v>
       </c>
       <c r="I112" t="n">
-        <v>0.006297</v>
+        <v>0.00054</v>
       </c>
       <c r="J112" t="n">
-        <v>0.007611</v>
-      </c>
-      <c r="K112" t="n">
-        <v>0.00602</v>
-      </c>
-      <c r="L112" t="n">
-        <v>0.003502</v>
+        <v>0.00107</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>農業科技業平上櫃</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr"/>
-      <c r="C113" t="inlineStr"/>
-      <c r="D113" t="inlineStr"/>
+          <t>農業科技業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>0.001664</v>
+      </c>
+      <c r="C113" t="n">
+        <v>0.001512</v>
+      </c>
+      <c r="D113" t="n">
+        <v>0.00152</v>
+      </c>
       <c r="E113" t="n">
-        <v>0.001283</v>
+        <v>0.00236</v>
       </c>
       <c r="F113" t="n">
-        <v>0.002363</v>
+        <v>0.004261</v>
       </c>
       <c r="G113" t="n">
-        <v>0.002141</v>
+        <v>0.002522</v>
       </c>
       <c r="H113" t="n">
-        <v>0.000828</v>
+        <v>0.002449</v>
       </c>
       <c r="I113" t="n">
-        <v>0.001911</v>
+        <v>0.00161</v>
       </c>
       <c r="J113" t="n">
-        <v>0.001109</v>
-      </c>
-      <c r="K113" t="n">
-        <v>0.002937</v>
-      </c>
-      <c r="L113" t="n">
-        <v>0.001782</v>
+        <v>0.001331</v>
       </c>
     </row>
     <row r="114">
@@ -4692,36 +4244,32 @@
           <t>通信網路業右上上市</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr"/>
+      <c r="B114" t="n">
+        <v>21660.982126</v>
+      </c>
       <c r="C114" t="n">
-        <v>24396.393849</v>
+        <v>14444.86348</v>
       </c>
       <c r="D114" t="n">
-        <v>22265.755006</v>
+        <v>16622.501014</v>
       </c>
       <c r="E114" t="n">
-        <v>21463.998464</v>
+        <v>6095.028413</v>
       </c>
       <c r="F114" t="n">
-        <v>28529.769749</v>
+        <v>6082.970456</v>
       </c>
       <c r="G114" t="n">
-        <v>25738.725857</v>
+        <v>6103.551493</v>
       </c>
       <c r="H114" t="n">
-        <v>20699.865955</v>
+        <v>6746.818307</v>
       </c>
       <c r="I114" t="n">
-        <v>17996.693025</v>
+        <v>5664.386803</v>
       </c>
       <c r="J114" t="n">
-        <v>16413.522656</v>
-      </c>
-      <c r="K114" t="n">
-        <v>13241.861587</v>
-      </c>
-      <c r="L114" t="n">
-        <v>12256.531162</v>
+        <v>8245.252662000001</v>
       </c>
     </row>
     <row r="115">
@@ -4730,36 +4278,32 @@
           <t>通信網路業右上上櫃</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr"/>
+      <c r="B115" t="n">
+        <v>24.05772</v>
+      </c>
       <c r="C115" t="n">
-        <v>11.937863</v>
+        <v>21.767781</v>
       </c>
       <c r="D115" t="n">
-        <v>17.776965</v>
+        <v>16.6943</v>
       </c>
       <c r="E115" t="n">
-        <v>16.251135</v>
+        <v>22.811269</v>
       </c>
       <c r="F115" t="n">
-        <v>19.568195</v>
+        <v>13.621921</v>
       </c>
       <c r="G115" t="n">
-        <v>20.205684</v>
+        <v>7.615602</v>
       </c>
       <c r="H115" t="n">
-        <v>13.019272</v>
+        <v>7.114229</v>
       </c>
       <c r="I115" t="n">
-        <v>9.941355</v>
+        <v>8.893762000000001</v>
       </c>
       <c r="J115" t="n">
-        <v>12.280394</v>
-      </c>
-      <c r="K115" t="n">
-        <v>9.59742325</v>
-      </c>
-      <c r="L115" t="n">
-        <v>12.005331</v>
+        <v>18.312942</v>
       </c>
     </row>
     <row r="116">
@@ -4769,37 +4313,31 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0</v>
+        <v>1418.101958</v>
       </c>
       <c r="C116" t="n">
-        <v>576.080509</v>
+        <v>3734.229225</v>
       </c>
       <c r="D116" t="n">
-        <v>506.069473</v>
+        <v>2800.97613</v>
       </c>
       <c r="E116" t="n">
-        <v>539.9540500000001</v>
+        <v>3905.975775</v>
       </c>
       <c r="F116" t="n">
-        <v>1412.030184</v>
+        <v>2277.09085</v>
       </c>
       <c r="G116" t="n">
-        <v>552.198306</v>
+        <v>1946.021499</v>
       </c>
       <c r="H116" t="n">
-        <v>6169.383253</v>
+        <v>2796.897423</v>
       </c>
       <c r="I116" t="n">
-        <v>678.454021</v>
+        <v>2244.085252</v>
       </c>
       <c r="J116" t="n">
-        <v>1122.003202</v>
-      </c>
-      <c r="K116" t="n">
-        <v>222.878699</v>
-      </c>
-      <c r="L116" t="n">
-        <v>523.809766</v>
+        <v>592.812061</v>
       </c>
     </row>
     <row r="117">
@@ -4809,37 +4347,31 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0</v>
+        <v>0.210037</v>
       </c>
       <c r="C117" t="n">
-        <v>0.302955</v>
+        <v>0.104276</v>
       </c>
       <c r="D117" t="n">
-        <v>0.807125</v>
+        <v>0.108687</v>
       </c>
       <c r="E117" t="n">
-        <v>0.263935</v>
+        <v>0.177069</v>
       </c>
       <c r="F117" t="n">
-        <v>0.5282559999999999</v>
+        <v>0.092809</v>
       </c>
       <c r="G117" t="n">
-        <v>0.422158</v>
+        <v>0.139641</v>
       </c>
       <c r="H117" t="n">
-        <v>0.224005</v>
+        <v>0.121491</v>
       </c>
       <c r="I117" t="n">
-        <v>0.238276</v>
+        <v>0.078808</v>
       </c>
       <c r="J117" t="n">
-        <v>0.308286</v>
-      </c>
-      <c r="K117" t="n">
-        <v>0.201302</v>
-      </c>
-      <c r="L117" t="n">
-        <v>0.185088</v>
+        <v>0.084409</v>
       </c>
     </row>
     <row r="118">
@@ -4848,36 +4380,32 @@
           <t>通信網路業平上市</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr"/>
+      <c r="B118" t="n">
+        <v>15530.982164</v>
+      </c>
       <c r="C118" t="n">
-        <v>985.048151</v>
+        <v>7051.592614</v>
       </c>
       <c r="D118" t="n">
-        <v>979.326366</v>
+        <v>8748.802201</v>
       </c>
       <c r="E118" t="n">
-        <v>946.7745179999999</v>
+        <v>8856.093255</v>
       </c>
       <c r="F118" t="n">
-        <v>1547.919673</v>
+        <v>5162.65965</v>
       </c>
       <c r="G118" t="n">
-        <v>4107.239022</v>
+        <v>8297.360316</v>
       </c>
       <c r="H118" t="n">
-        <v>8924.446980999999</v>
+        <v>13957.577554</v>
       </c>
       <c r="I118" t="n">
-        <v>9305.031605</v>
+        <v>12339.661725</v>
       </c>
       <c r="J118" t="n">
-        <v>10735.420884</v>
-      </c>
-      <c r="K118" t="n">
-        <v>7130.957642</v>
-      </c>
-      <c r="L118" t="n">
-        <v>4194.554171</v>
+        <v>17667.338244</v>
       </c>
     </row>
     <row r="119">
@@ -4886,36 +4414,32 @@
           <t>通信網路業平上櫃</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr"/>
+      <c r="B119" t="n">
+        <v>2.541905</v>
+      </c>
       <c r="C119" t="n">
-        <v>1.203125</v>
+        <v>3.456953</v>
       </c>
       <c r="D119" t="n">
-        <v>0.040709</v>
+        <v>6.538407</v>
       </c>
       <c r="E119" t="n">
-        <v>0.986932</v>
+        <v>3.420577</v>
       </c>
       <c r="F119" t="n">
-        <v>0.192797</v>
+        <v>2.191077</v>
       </c>
       <c r="G119" t="n">
-        <v>0.037374</v>
+        <v>2.291996</v>
       </c>
       <c r="H119" t="n">
-        <v>0.391977</v>
+        <v>2.261277</v>
       </c>
       <c r="I119" t="n">
-        <v>0.162314</v>
+        <v>3.489899</v>
       </c>
       <c r="J119" t="n">
-        <v>0.491176</v>
-      </c>
-      <c r="K119" t="n">
-        <v>0.333492</v>
-      </c>
-      <c r="L119" t="n">
-        <v>0.279023</v>
+        <v>8.566473999999999</v>
       </c>
     </row>
     <row r="120">
@@ -4924,36 +4448,32 @@
           <t>造紙工業右上上市</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr"/>
+      <c r="B120" t="n">
+        <v>49.845177</v>
+      </c>
       <c r="C120" t="n">
-        <v>244.741608</v>
+        <v>37.698224</v>
       </c>
       <c r="D120" t="n">
-        <v>438.06777</v>
+        <v>64.522261</v>
       </c>
       <c r="E120" t="n">
-        <v>540.516555</v>
+        <v>41.474092</v>
       </c>
       <c r="F120" t="n">
-        <v>345.928655</v>
+        <v>57.019267</v>
       </c>
       <c r="G120" t="n">
-        <v>327.972094</v>
+        <v>95.750647</v>
       </c>
       <c r="H120" t="n">
-        <v>414.202617</v>
+        <v>70.719487</v>
       </c>
       <c r="I120" t="n">
-        <v>234.220947</v>
+        <v>92.464285</v>
       </c>
       <c r="J120" t="n">
-        <v>197.532714</v>
-      </c>
-      <c r="K120" t="n">
-        <v>234.567811</v>
-      </c>
-      <c r="L120" t="n">
-        <v>161.467695</v>
+        <v>63.28767</v>
       </c>
     </row>
     <row r="121">
@@ -4963,37 +4483,31 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0</v>
+        <v>12.247197</v>
       </c>
       <c r="C121" t="n">
-        <v>9.691417</v>
+        <v>5.766187</v>
       </c>
       <c r="D121" t="n">
-        <v>14.658787</v>
+        <v>8.746762</v>
       </c>
       <c r="E121" t="n">
-        <v>40.205349</v>
+        <v>8.611516999999999</v>
       </c>
       <c r="F121" t="n">
-        <v>8.886793000000001</v>
+        <v>4.116534</v>
       </c>
       <c r="G121" t="n">
-        <v>5.71856</v>
+        <v>8.170572</v>
       </c>
       <c r="H121" t="n">
-        <v>3.090718</v>
+        <v>6.624743</v>
       </c>
       <c r="I121" t="n">
-        <v>23.082663</v>
+        <v>6.312246</v>
       </c>
       <c r="J121" t="n">
-        <v>17.725534</v>
-      </c>
-      <c r="K121" t="n">
-        <v>12.178288</v>
-      </c>
-      <c r="L121" t="n">
-        <v>11.547305</v>
+        <v>7.259808</v>
       </c>
     </row>
     <row r="122">
@@ -5002,19 +4516,33 @@
           <t>造紙工業平上市</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr"/>
+      <c r="B122" t="n">
+        <v>41.826683</v>
+      </c>
       <c r="C122" t="n">
-        <v>38.44307</v>
-      </c>
-      <c r="D122" t="inlineStr"/>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
+        <v>27.811811</v>
+      </c>
+      <c r="D122" t="n">
+        <v>39.868425</v>
+      </c>
+      <c r="E122" t="n">
+        <v>31.600935</v>
+      </c>
+      <c r="F122" t="n">
+        <v>23.263533</v>
+      </c>
+      <c r="G122" t="n">
+        <v>54.222929</v>
+      </c>
+      <c r="H122" t="n">
+        <v>27.470921</v>
+      </c>
+      <c r="I122" t="n">
+        <v>54.140034</v>
+      </c>
+      <c r="J122" t="n">
+        <v>31.758988</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
@@ -5022,36 +4550,32 @@
           <t>運動休閒右上上市</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr"/>
+      <c r="B123" t="n">
+        <v>636.16023</v>
+      </c>
       <c r="C123" t="n">
-        <v>11.432884</v>
+        <v>147.854351</v>
       </c>
       <c r="D123" t="n">
-        <v>9.463635999999999</v>
+        <v>161.276417</v>
       </c>
       <c r="E123" t="n">
-        <v>37.346417</v>
+        <v>156.233187</v>
       </c>
       <c r="F123" t="n">
-        <v>58.283933</v>
+        <v>127.930135</v>
       </c>
       <c r="G123" t="n">
-        <v>34.017867</v>
+        <v>222.315562</v>
       </c>
       <c r="H123" t="n">
-        <v>61.014476</v>
+        <v>159.66203</v>
       </c>
       <c r="I123" t="n">
-        <v>65.310605</v>
+        <v>173.07071</v>
       </c>
       <c r="J123" t="n">
-        <v>184.67257</v>
-      </c>
-      <c r="K123" t="n">
-        <v>75.172668</v>
-      </c>
-      <c r="L123" t="n">
-        <v>214.175393</v>
+        <v>149.450741</v>
       </c>
     </row>
     <row r="124">
@@ -5060,36 +4584,32 @@
           <t>運動休閒右上上櫃</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr"/>
+      <c r="B124" t="n">
+        <v>0.002807</v>
+      </c>
       <c r="C124" t="n">
-        <v>0.000592</v>
+        <v>0.004426</v>
       </c>
       <c r="D124" t="n">
-        <v>0.000138</v>
+        <v>0.008544</v>
       </c>
       <c r="E124" t="n">
-        <v>0.00048</v>
+        <v>0.007512</v>
       </c>
       <c r="F124" t="n">
-        <v>0.000826</v>
+        <v>0.008066</v>
       </c>
       <c r="G124" t="n">
-        <v>0.000373</v>
+        <v>0.00397</v>
       </c>
       <c r="H124" t="n">
-        <v>0.000936</v>
+        <v>0.003778</v>
       </c>
       <c r="I124" t="n">
-        <v>0.000977</v>
+        <v>0.006495</v>
       </c>
       <c r="J124" t="n">
-        <v>0.0009810000000000001</v>
-      </c>
-      <c r="K124" t="n">
-        <v>0.000227</v>
-      </c>
-      <c r="L124" t="n">
-        <v>0.00078</v>
+        <v>0.002192</v>
       </c>
     </row>
     <row r="125">
@@ -5098,36 +4618,32 @@
           <t>運動休閒右下上市</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr"/>
+      <c r="B125" t="n">
+        <v>986.052947</v>
+      </c>
       <c r="C125" t="n">
-        <v>2250.16424</v>
+        <v>604.61089</v>
       </c>
       <c r="D125" t="n">
-        <v>1582.013713</v>
+        <v>516.815906</v>
       </c>
       <c r="E125" t="n">
-        <v>1354.719184</v>
+        <v>631.525347</v>
       </c>
       <c r="F125" t="n">
-        <v>1129.692147</v>
+        <v>537.375755</v>
       </c>
       <c r="G125" t="n">
-        <v>887.735439</v>
+        <v>513.733269</v>
       </c>
       <c r="H125" t="n">
-        <v>1009.340196</v>
+        <v>544.3139159999999</v>
       </c>
       <c r="I125" t="n">
-        <v>1297.250418</v>
+        <v>523.45054</v>
       </c>
       <c r="J125" t="n">
-        <v>1552.718867</v>
-      </c>
-      <c r="K125" t="n">
-        <v>1136.456368</v>
-      </c>
-      <c r="L125" t="n">
-        <v>1412.220533</v>
+        <v>549.850026</v>
       </c>
     </row>
     <row r="126">
@@ -5136,36 +4652,32 @@
           <t>運動休閒右下上櫃</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr"/>
+      <c r="B126" t="n">
+        <v>0.013357</v>
+      </c>
       <c r="C126" t="n">
-        <v>0.027852</v>
+        <v>0.008547000000000001</v>
       </c>
       <c r="D126" t="n">
-        <v>0.039266</v>
+        <v>0.012284</v>
       </c>
       <c r="E126" t="n">
-        <v>0.022232</v>
+        <v>0.005907</v>
       </c>
       <c r="F126" t="n">
-        <v>0.01449</v>
+        <v>0.005639</v>
       </c>
       <c r="G126" t="n">
-        <v>0.012179</v>
+        <v>0.004976</v>
       </c>
       <c r="H126" t="n">
-        <v>0.006005</v>
+        <v>0.003873</v>
       </c>
       <c r="I126" t="n">
-        <v>0.015023</v>
+        <v>0.00535</v>
       </c>
       <c r="J126" t="n">
-        <v>0.012758</v>
-      </c>
-      <c r="K126" t="n">
-        <v>0.008768</v>
-      </c>
-      <c r="L126" t="n">
-        <v>0.026619</v>
+        <v>0.005399</v>
       </c>
     </row>
     <row r="127">
@@ -5174,36 +4686,32 @@
           <t>運動休閒平上市</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr"/>
+      <c r="B127" t="n">
+        <v>16.909733</v>
+      </c>
       <c r="C127" t="n">
-        <v>17.971369</v>
+        <v>7.26905</v>
       </c>
       <c r="D127" t="n">
-        <v>177.802271</v>
+        <v>11.696813</v>
       </c>
       <c r="E127" t="n">
-        <v>91.858739</v>
+        <v>8.888235</v>
       </c>
       <c r="F127" t="n">
-        <v>67.318535</v>
+        <v>47.479196</v>
       </c>
       <c r="G127" t="n">
-        <v>31.469313</v>
+        <v>88.51274100000001</v>
       </c>
       <c r="H127" t="n">
-        <v>42.686136</v>
+        <v>83.666366</v>
       </c>
       <c r="I127" t="n">
-        <v>92.294726</v>
+        <v>59.722284</v>
       </c>
       <c r="J127" t="n">
-        <v>159.236737</v>
-      </c>
-      <c r="K127" t="n">
-        <v>165.009049</v>
-      </c>
-      <c r="L127" t="n">
-        <v>1507.995744</v>
+        <v>42.191244</v>
       </c>
     </row>
     <row r="128">
@@ -5212,36 +4720,32 @@
           <t>運動休閒平上櫃</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr"/>
+      <c r="B128" t="n">
+        <v>0.000374</v>
+      </c>
       <c r="C128" t="n">
-        <v>0.001099</v>
+        <v>0.000341</v>
       </c>
       <c r="D128" t="n">
-        <v>0.003798</v>
+        <v>0.000204</v>
       </c>
       <c r="E128" t="n">
-        <v>0.001296</v>
+        <v>0.000623</v>
       </c>
       <c r="F128" t="n">
-        <v>0.001692</v>
+        <v>0.001134</v>
       </c>
       <c r="G128" t="n">
-        <v>0.003422</v>
+        <v>0.000725</v>
       </c>
       <c r="H128" t="n">
-        <v>0.00464</v>
+        <v>0.000571</v>
       </c>
       <c r="I128" t="n">
-        <v>0.000641</v>
+        <v>0.00091</v>
       </c>
       <c r="J128" t="n">
-        <v>0.001392</v>
-      </c>
-      <c r="K128" t="n">
-        <v>0.003114</v>
-      </c>
-      <c r="L128" t="n">
-        <v>0.000469</v>
+        <v>0.000621</v>
       </c>
     </row>
     <row r="129">
@@ -5250,36 +4754,32 @@
           <t>金融保險右上上市</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr"/>
+      <c r="B129" t="n">
+        <v>45554.511467</v>
+      </c>
       <c r="C129" t="n">
-        <v>35604.525715</v>
+        <v>17584.706175</v>
       </c>
       <c r="D129" t="n">
-        <v>24370.360953</v>
+        <v>16987.289529</v>
       </c>
       <c r="E129" t="n">
-        <v>19092.932693</v>
+        <v>17478.522511</v>
       </c>
       <c r="F129" t="n">
-        <v>31175.250103</v>
+        <v>10882.35721</v>
       </c>
       <c r="G129" t="n">
-        <v>26364.098343</v>
+        <v>19643.829874</v>
       </c>
       <c r="H129" t="n">
-        <v>23460.16658</v>
+        <v>17163.268297</v>
       </c>
       <c r="I129" t="n">
-        <v>27123.558485</v>
+        <v>24618.524731</v>
       </c>
       <c r="J129" t="n">
-        <v>28214.155163</v>
-      </c>
-      <c r="K129" t="n">
-        <v>26342.668337</v>
-      </c>
-      <c r="L129" t="n">
-        <v>22971.691178</v>
+        <v>16298.205375</v>
       </c>
     </row>
     <row r="130">
@@ -5289,31 +4789,31 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0</v>
+        <v>489.87573</v>
       </c>
       <c r="C130" t="n">
-        <v>224.624201</v>
+        <v>274.286538</v>
       </c>
       <c r="D130" t="n">
-        <v>385.7182</v>
+        <v>189.086642</v>
       </c>
       <c r="E130" t="n">
-        <v>227.294605</v>
+        <v>205.909852</v>
       </c>
       <c r="F130" t="n">
-        <v>7.739491</v>
-      </c>
-      <c r="G130" t="inlineStr"/>
-      <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr"/>
+        <v>244.900842</v>
+      </c>
+      <c r="G130" t="n">
+        <v>387.63469</v>
+      </c>
+      <c r="H130" t="n">
+        <v>265.348802</v>
+      </c>
+      <c r="I130" t="n">
+        <v>233.42015</v>
+      </c>
       <c r="J130" t="n">
-        <v>323.343626</v>
-      </c>
-      <c r="K130" t="n">
-        <v>300.850594</v>
-      </c>
-      <c r="L130" t="n">
-        <v>298.677792</v>
+        <v>116.899227</v>
       </c>
     </row>
     <row r="131">
@@ -5322,36 +4822,32 @@
           <t>金融保險平上市</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr"/>
+      <c r="B131" t="n">
+        <v>321.424823</v>
+      </c>
       <c r="C131" t="n">
-        <v>349.245259</v>
+        <v>362.141174</v>
       </c>
       <c r="D131" t="n">
-        <v>291.492292</v>
+        <v>354.572106</v>
       </c>
       <c r="E131" t="n">
-        <v>338.247094</v>
+        <v>228.885439</v>
       </c>
       <c r="F131" t="n">
-        <v>787.896931</v>
+        <v>209.691372</v>
       </c>
       <c r="G131" t="n">
-        <v>468.758084</v>
+        <v>280.204653</v>
       </c>
       <c r="H131" t="n">
-        <v>575.591515</v>
+        <v>256.305102</v>
       </c>
       <c r="I131" t="n">
-        <v>272.222659</v>
+        <v>351.325567</v>
       </c>
       <c r="J131" t="n">
-        <v>61.56495</v>
-      </c>
-      <c r="K131" t="n">
-        <v>37.065761</v>
-      </c>
-      <c r="L131" t="n">
-        <v>27.089764</v>
+        <v>464.231308</v>
       </c>
     </row>
     <row r="132">
@@ -5360,36 +4856,32 @@
           <t>金融業右上上櫃</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr"/>
+      <c r="B132" t="n">
+        <v>0.287552</v>
+      </c>
       <c r="C132" t="n">
-        <v>0.489011</v>
+        <v>0.50264</v>
       </c>
       <c r="D132" t="n">
-        <v>0.719213</v>
+        <v>0.511979</v>
       </c>
       <c r="E132" t="n">
-        <v>0.580044</v>
+        <v>0.300829</v>
       </c>
       <c r="F132" t="n">
-        <v>0.897415</v>
+        <v>0.200969</v>
       </c>
       <c r="G132" t="n">
-        <v>0.885456</v>
+        <v>0.161656</v>
       </c>
       <c r="H132" t="n">
-        <v>0.488973</v>
+        <v>0.400318</v>
       </c>
       <c r="I132" t="n">
-        <v>0.580902</v>
+        <v>0.34688</v>
       </c>
       <c r="J132" t="n">
-        <v>0.735648</v>
-      </c>
-      <c r="K132" t="n">
-        <v>0.34192</v>
-      </c>
-      <c r="L132" t="n">
-        <v>0.327026</v>
+        <v>0.207437</v>
       </c>
     </row>
     <row r="133">
@@ -5398,36 +4890,32 @@
           <t>金融業右下上櫃</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr"/>
+      <c r="B133" t="n">
+        <v>0.036779</v>
+      </c>
       <c r="C133" t="n">
-        <v>0.003124</v>
+        <v>0.053885</v>
       </c>
       <c r="D133" t="n">
-        <v>0.00462</v>
+        <v>0.02408566666666667</v>
       </c>
       <c r="E133" t="n">
-        <v>0.004811</v>
+        <v>0.043228</v>
       </c>
       <c r="F133" t="n">
-        <v>0.000935</v>
+        <v>0.102314</v>
       </c>
       <c r="G133" t="n">
-        <v>0.000422</v>
+        <v>0.038874</v>
       </c>
       <c r="H133" t="n">
-        <v>0.001901</v>
+        <v>0.064808</v>
       </c>
       <c r="I133" t="n">
-        <v>0.001443</v>
+        <v>0.08569</v>
       </c>
       <c r="J133" t="n">
-        <v>8.4e-05</v>
-      </c>
-      <c r="K133" t="n">
-        <v>0.000867</v>
-      </c>
-      <c r="L133" t="n">
-        <v>8.500000000000001e-05</v>
+        <v>0.030934</v>
       </c>
     </row>
     <row r="134">
@@ -5436,22 +4924,32 @@
           <t>金融業平上櫃</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr"/>
-      <c r="C134" t="inlineStr"/>
-      <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr"/>
-      <c r="H134" t="inlineStr"/>
-      <c r="I134" t="inlineStr"/>
+      <c r="B134" t="n">
+        <v>0.000309</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.001322</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.000562</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.000744</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.000225</v>
+      </c>
+      <c r="G134" t="n">
+        <v>6.2e-05</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.00025</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.000124</v>
+      </c>
       <c r="J134" t="n">
-        <v>0.00083</v>
-      </c>
-      <c r="K134" t="n">
-        <v>0.002732</v>
-      </c>
-      <c r="L134" t="n">
-        <v>5.3e-05</v>
+        <v>0.000248</v>
       </c>
     </row>
     <row r="135">
@@ -5460,36 +4958,32 @@
           <t>鋼鐵工業右上上市</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr"/>
+      <c r="B135" t="n">
+        <v>1464.341412</v>
+      </c>
       <c r="C135" t="n">
-        <v>900.186824</v>
+        <v>724.043505</v>
       </c>
       <c r="D135" t="n">
-        <v>1028.940782</v>
+        <v>1244.936603</v>
       </c>
       <c r="E135" t="n">
-        <v>1141.791483</v>
+        <v>1702.258596</v>
       </c>
       <c r="F135" t="n">
-        <v>1036.059944</v>
+        <v>1668.035173</v>
       </c>
       <c r="G135" t="n">
-        <v>800.904872</v>
+        <v>2123.299819</v>
       </c>
       <c r="H135" t="n">
-        <v>981.490377</v>
+        <v>2472.356878</v>
       </c>
       <c r="I135" t="n">
-        <v>1361.097368</v>
+        <v>4794.875688</v>
       </c>
       <c r="J135" t="n">
-        <v>1164.362055</v>
-      </c>
-      <c r="K135" t="n">
-        <v>1494.221787</v>
-      </c>
-      <c r="L135" t="n">
-        <v>958.9764259999999</v>
+        <v>1359.890176</v>
       </c>
     </row>
     <row r="136">
@@ -5498,36 +4992,32 @@
           <t>鋼鐵工業右上上櫃</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr"/>
+      <c r="B136" t="n">
+        <v>0.006179</v>
+      </c>
       <c r="C136" t="n">
-        <v>0.066813</v>
+        <v>0.009807</v>
       </c>
       <c r="D136" t="n">
-        <v>0.035432</v>
+        <v>0.017194</v>
       </c>
       <c r="E136" t="n">
-        <v>0.034326</v>
+        <v>0.012871</v>
       </c>
       <c r="F136" t="n">
-        <v>0.044487</v>
+        <v>0.006391</v>
       </c>
       <c r="G136" t="n">
-        <v>0.026188</v>
+        <v>0.044205</v>
       </c>
       <c r="H136" t="n">
-        <v>0.030109</v>
+        <v>0.05524</v>
       </c>
       <c r="I136" t="n">
-        <v>0.046642</v>
+        <v>0.032969</v>
       </c>
       <c r="J136" t="n">
-        <v>0.105133</v>
-      </c>
-      <c r="K136" t="n">
-        <v>0.057144</v>
-      </c>
-      <c r="L136" t="n">
-        <v>0.027587</v>
+        <v>0.090244</v>
       </c>
     </row>
     <row r="137">
@@ -5537,37 +5027,31 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0</v>
+        <v>885.374656</v>
       </c>
       <c r="C137" t="n">
-        <v>839.530156</v>
+        <v>763.805825</v>
       </c>
       <c r="D137" t="n">
-        <v>1282.706388</v>
+        <v>845.004486</v>
       </c>
       <c r="E137" t="n">
-        <v>522.327838</v>
+        <v>788.213784</v>
       </c>
       <c r="F137" t="n">
-        <v>1075.729194</v>
+        <v>690.654503</v>
       </c>
       <c r="G137" t="n">
-        <v>705.116832</v>
+        <v>1034.546462</v>
       </c>
       <c r="H137" t="n">
-        <v>733.171453</v>
+        <v>233.418087</v>
       </c>
       <c r="I137" t="n">
-        <v>1068.05894</v>
+        <v>217.573193</v>
       </c>
       <c r="J137" t="n">
-        <v>1167.372206</v>
-      </c>
-      <c r="K137" t="n">
-        <v>927.150883</v>
-      </c>
-      <c r="L137" t="n">
-        <v>755.346754</v>
+        <v>147.093842</v>
       </c>
     </row>
     <row r="138">
@@ -5576,36 +5060,32 @@
           <t>鋼鐵工業右下上櫃</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr"/>
+      <c r="B138" t="n">
+        <v>0.2316725</v>
+      </c>
       <c r="C138" t="n">
-        <v>0.0924075</v>
+        <v>0.036438</v>
       </c>
       <c r="D138" t="n">
-        <v>0.225894</v>
+        <v>0.043378</v>
       </c>
       <c r="E138" t="n">
-        <v>0.013236</v>
+        <v>0.028808</v>
       </c>
       <c r="F138" t="n">
-        <v>0.178667</v>
+        <v>0.0357425</v>
       </c>
       <c r="G138" t="n">
-        <v>0.08053399999999999</v>
+        <v>0.066598</v>
       </c>
       <c r="H138" t="n">
-        <v>0.054322</v>
+        <v>0.01580233333333333</v>
       </c>
       <c r="I138" t="n">
-        <v>0.006185</v>
+        <v>0.07816099999999999</v>
       </c>
       <c r="J138" t="n">
-        <v>0.01079866666666667</v>
-      </c>
-      <c r="K138" t="n">
-        <v>0.005729</v>
-      </c>
-      <c r="L138" t="n">
-        <v>0.006108</v>
+        <v>0.008527</v>
       </c>
     </row>
     <row r="139">
@@ -5614,36 +5094,32 @@
           <t>鋼鐵工業平上市</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr"/>
+      <c r="B139" t="n">
+        <v>34.929924</v>
+      </c>
       <c r="C139" t="n">
-        <v>194.595836</v>
+        <v>29.547407</v>
       </c>
       <c r="D139" t="n">
-        <v>254.608617</v>
+        <v>35.389744</v>
       </c>
       <c r="E139" t="n">
-        <v>679.86886</v>
+        <v>25.446863</v>
       </c>
       <c r="F139" t="n">
-        <v>163.572914</v>
+        <v>51.27883</v>
       </c>
       <c r="G139" t="n">
-        <v>134.669791</v>
+        <v>69.504525</v>
       </c>
       <c r="H139" t="n">
-        <v>85.29900499999999</v>
+        <v>1959.791285</v>
       </c>
       <c r="I139" t="n">
-        <v>159.157532</v>
+        <v>880.248299</v>
       </c>
       <c r="J139" t="n">
-        <v>155.669223</v>
-      </c>
-      <c r="K139" t="n">
-        <v>196.082275</v>
-      </c>
-      <c r="L139" t="n">
-        <v>181.526651</v>
+        <v>474.633615</v>
       </c>
     </row>
     <row r="140">
@@ -5652,36 +5128,32 @@
           <t>鋼鐵工業平上櫃</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr"/>
+      <c r="B140" t="n">
+        <v>0.00062</v>
+      </c>
       <c r="C140" t="n">
-        <v>0.002361</v>
+        <v>0.023936</v>
       </c>
       <c r="D140" t="n">
-        <v>0.006019</v>
+        <v>0.009734</v>
       </c>
       <c r="E140" t="n">
-        <v>0.197579</v>
+        <v>0.004176</v>
       </c>
       <c r="F140" t="n">
-        <v>0.0032455</v>
+        <v>0.007728</v>
       </c>
       <c r="G140" t="n">
-        <v>0.007846666666666667</v>
+        <v>0.022195</v>
       </c>
       <c r="H140" t="n">
-        <v>0.010002</v>
+        <v>0.22675</v>
       </c>
       <c r="I140" t="n">
-        <v>0.258272</v>
+        <v>0.017764</v>
       </c>
       <c r="J140" t="n">
-        <v>0.217707</v>
-      </c>
-      <c r="K140" t="n">
-        <v>0.11237</v>
-      </c>
-      <c r="L140" t="n">
-        <v>0.114476</v>
+        <v>0.049575</v>
       </c>
     </row>
     <row r="141">
@@ -5690,36 +5162,32 @@
           <t>電器電纜右上上市</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr"/>
+      <c r="B141" t="n">
+        <v>1175.370349</v>
+      </c>
       <c r="C141" t="n">
-        <v>900.67542</v>
+        <v>548.098926</v>
       </c>
       <c r="D141" t="n">
-        <v>1629.47852</v>
+        <v>783.843303</v>
       </c>
       <c r="E141" t="n">
-        <v>3106.962566</v>
+        <v>459.979709</v>
       </c>
       <c r="F141" t="n">
-        <v>2946.530733</v>
+        <v>243.385274</v>
       </c>
       <c r="G141" t="n">
-        <v>1485.098974</v>
+        <v>221.164725</v>
       </c>
       <c r="H141" t="n">
-        <v>553.607796</v>
+        <v>2022.93564</v>
       </c>
       <c r="I141" t="n">
-        <v>1048.504517</v>
+        <v>1815.128022</v>
       </c>
       <c r="J141" t="n">
-        <v>912.395733</v>
-      </c>
-      <c r="K141" t="n">
-        <v>854.698136</v>
-      </c>
-      <c r="L141" t="n">
-        <v>366.066339</v>
+        <v>1400.305424</v>
       </c>
     </row>
     <row r="142">
@@ -5728,36 +5196,32 @@
           <t>電器電纜右上上櫃</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr"/>
+      <c r="B142" t="n">
+        <v>0.103899</v>
+      </c>
       <c r="C142" t="n">
-        <v>0.036283</v>
+        <v>0.108179</v>
       </c>
       <c r="D142" t="n">
-        <v>0.056806</v>
+        <v>0.111628</v>
       </c>
       <c r="E142" t="n">
-        <v>0.059368</v>
+        <v>0.09124</v>
       </c>
       <c r="F142" t="n">
-        <v>0.053787</v>
+        <v>0.091242</v>
       </c>
       <c r="G142" t="n">
-        <v>0.448434</v>
+        <v>0.112558</v>
       </c>
       <c r="H142" t="n">
-        <v>0.333231</v>
+        <v>0.294298</v>
       </c>
       <c r="I142" t="n">
-        <v>0.324776</v>
+        <v>0.204111</v>
       </c>
       <c r="J142" t="n">
-        <v>0.281098</v>
-      </c>
-      <c r="K142" t="n">
-        <v>0.233522</v>
-      </c>
-      <c r="L142" t="n">
-        <v>0.25268</v>
+        <v>0.346172</v>
       </c>
     </row>
     <row r="143">
@@ -5766,36 +5230,32 @@
           <t>電器電纜右下上市</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr"/>
+      <c r="B143" t="n">
+        <v>153.170499</v>
+      </c>
       <c r="C143" t="n">
-        <v>208.560316</v>
+        <v>88.494788</v>
       </c>
       <c r="D143" t="n">
-        <v>150.597245</v>
+        <v>65.49185300000001</v>
       </c>
       <c r="E143" t="n">
-        <v>171.381806</v>
+        <v>41.538122</v>
       </c>
       <c r="F143" t="n">
-        <v>159.6027</v>
+        <v>39.275066</v>
       </c>
       <c r="G143" t="n">
-        <v>118.00876</v>
+        <v>40.346396</v>
       </c>
       <c r="H143" t="n">
-        <v>184.29146</v>
+        <v>55.382448</v>
       </c>
       <c r="I143" t="n">
-        <v>196.146271</v>
+        <v>41.834918</v>
       </c>
       <c r="J143" t="n">
-        <v>199.544088</v>
-      </c>
-      <c r="K143" t="n">
-        <v>116.242132</v>
-      </c>
-      <c r="L143" t="n">
-        <v>75.363747</v>
+        <v>50.073944</v>
       </c>
     </row>
     <row r="144">
@@ -5804,36 +5264,32 @@
           <t>電器電纜平上市</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr"/>
+      <c r="B144" t="n">
+        <v>205.904956</v>
+      </c>
       <c r="C144" t="n">
-        <v>250.217647</v>
+        <v>112.573224</v>
       </c>
       <c r="D144" t="n">
-        <v>86.694931</v>
+        <v>197.780769</v>
       </c>
       <c r="E144" t="n">
-        <v>3.008508</v>
+        <v>170.127462</v>
       </c>
       <c r="F144" t="n">
-        <v>420.772427</v>
+        <v>116.254235</v>
       </c>
       <c r="G144" t="n">
-        <v>110.845805</v>
+        <v>420.560636</v>
       </c>
       <c r="H144" t="n">
-        <v>433.435724</v>
+        <v>44.797637</v>
       </c>
       <c r="I144" t="n">
-        <v>175.391726</v>
+        <v>21.090587</v>
       </c>
       <c r="J144" t="n">
-        <v>425.023977</v>
-      </c>
-      <c r="K144" t="n">
-        <v>264.400775</v>
-      </c>
-      <c r="L144" t="n">
-        <v>267.85399</v>
+        <v>11.466549</v>
       </c>
     </row>
     <row r="145">
@@ -5842,36 +5298,32 @@
           <t>電子通路業右上上市</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr"/>
+      <c r="B145" t="n">
+        <v>3008.739938</v>
+      </c>
       <c r="C145" t="n">
-        <v>9237.44808</v>
+        <v>2462.842603</v>
       </c>
       <c r="D145" t="n">
-        <v>10789.499919</v>
+        <v>3533.092438</v>
       </c>
       <c r="E145" t="n">
-        <v>8050.719739</v>
+        <v>7357.524566</v>
       </c>
       <c r="F145" t="n">
-        <v>9729.760442000001</v>
+        <v>3162.15291</v>
       </c>
       <c r="G145" t="n">
-        <v>7536.29481</v>
+        <v>3504.588651</v>
       </c>
       <c r="H145" t="n">
-        <v>5364.940585</v>
+        <v>4790.204438</v>
       </c>
       <c r="I145" t="n">
-        <v>10694.717168</v>
+        <v>2482.396615</v>
       </c>
       <c r="J145" t="n">
-        <v>10560.4945</v>
-      </c>
-      <c r="K145" t="n">
-        <v>10888.926075</v>
-      </c>
-      <c r="L145" t="n">
-        <v>10906.365135</v>
+        <v>2196.270989</v>
       </c>
     </row>
     <row r="146">
@@ -5880,36 +5332,32 @@
           <t>電子通路業右上上櫃</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr"/>
+      <c r="B146" t="n">
+        <v>0.358937</v>
+      </c>
       <c r="C146" t="n">
-        <v>0.568505</v>
+        <v>0.152499</v>
       </c>
       <c r="D146" t="n">
-        <v>0.587448</v>
+        <v>0.291336</v>
       </c>
       <c r="E146" t="n">
-        <v>1.090006</v>
+        <v>0.107882</v>
       </c>
       <c r="F146" t="n">
-        <v>0.963468</v>
+        <v>0.127115</v>
       </c>
       <c r="G146" t="n">
-        <v>2.617598</v>
+        <v>0.114703</v>
       </c>
       <c r="H146" t="n">
-        <v>5.173714</v>
+        <v>0.131196</v>
       </c>
       <c r="I146" t="n">
-        <v>3.25745</v>
+        <v>0.332757</v>
       </c>
       <c r="J146" t="n">
-        <v>2.529851</v>
-      </c>
-      <c r="K146" t="n">
-        <v>3.600575</v>
-      </c>
-      <c r="L146" t="n">
-        <v>0.735941</v>
+        <v>0.374888</v>
       </c>
     </row>
     <row r="147">
@@ -5918,36 +5366,32 @@
           <t>電子通路業右下上市</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr"/>
+      <c r="B147" t="n">
+        <v>38.368699</v>
+      </c>
       <c r="C147" t="n">
-        <v>16.747297</v>
+        <v>10.916063</v>
       </c>
       <c r="D147" t="n">
-        <v>29.325931</v>
+        <v>10.344134</v>
       </c>
       <c r="E147" t="n">
-        <v>25.002504</v>
+        <v>5.689849</v>
       </c>
       <c r="F147" t="n">
-        <v>20.9475</v>
+        <v>6.727905</v>
       </c>
       <c r="G147" t="n">
-        <v>10.200378</v>
+        <v>18.247482</v>
       </c>
       <c r="H147" t="n">
-        <v>15.802789</v>
+        <v>12.283079</v>
       </c>
       <c r="I147" t="n">
-        <v>27.030393</v>
+        <v>13.321644</v>
       </c>
       <c r="J147" t="n">
-        <v>81.07152000000001</v>
-      </c>
-      <c r="K147" t="n">
-        <v>30.716469</v>
-      </c>
-      <c r="L147" t="n">
-        <v>32.246402</v>
+        <v>11.089148</v>
       </c>
     </row>
     <row r="148">
@@ -5957,37 +5401,31 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0</v>
+        <v>0.035434</v>
       </c>
       <c r="C148" t="n">
-        <v>0.006517</v>
+        <v>0.032335</v>
       </c>
       <c r="D148" t="n">
-        <v>0.010672</v>
+        <v>0.033982</v>
       </c>
       <c r="E148" t="n">
-        <v>0.004925</v>
+        <v>0.173565</v>
       </c>
       <c r="F148" t="n">
-        <v>0.015332</v>
+        <v>0.06376800000000001</v>
       </c>
       <c r="G148" t="n">
-        <v>0.008348</v>
+        <v>0.0418</v>
       </c>
       <c r="H148" t="n">
-        <v>0.007461</v>
+        <v>0.04535</v>
       </c>
       <c r="I148" t="n">
-        <v>0.010562</v>
+        <v>0.081911</v>
       </c>
       <c r="J148" t="n">
-        <v>0.065166</v>
-      </c>
-      <c r="K148" t="n">
-        <v>0.024462</v>
-      </c>
-      <c r="L148" t="n">
-        <v>0.019098</v>
+        <v>0.022376</v>
       </c>
     </row>
     <row r="149">
@@ -5996,36 +5434,32 @@
           <t>電子通路業平上市</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr"/>
+      <c r="B149" t="n">
+        <v>3295.513809</v>
+      </c>
       <c r="C149" t="n">
-        <v>61.680668</v>
+        <v>1867.739468</v>
       </c>
       <c r="D149" t="n">
-        <v>52.070762</v>
+        <v>2400.502435</v>
       </c>
       <c r="E149" t="n">
-        <v>47.896318</v>
+        <v>1537.856671</v>
       </c>
       <c r="F149" t="n">
-        <v>79.152973</v>
+        <v>2036.568067</v>
       </c>
       <c r="G149" t="n">
-        <v>41.385477</v>
+        <v>1544.029191</v>
       </c>
       <c r="H149" t="n">
-        <v>44.82201</v>
+        <v>2244.493983</v>
       </c>
       <c r="I149" t="n">
-        <v>34.751708</v>
+        <v>2879.512206</v>
       </c>
       <c r="J149" t="n">
-        <v>180.692574</v>
-      </c>
-      <c r="K149" t="n">
-        <v>6.888177</v>
-      </c>
-      <c r="L149" t="n">
-        <v>4.054274</v>
+        <v>2031.06244</v>
       </c>
     </row>
     <row r="150">
@@ -6034,34 +5468,32 @@
           <t>電子通路業平上櫃</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr"/>
-      <c r="C150" t="inlineStr"/>
+      <c r="B150" t="n">
+        <v>0.238213</v>
+      </c>
+      <c r="C150" t="n">
+        <v>0.288456</v>
+      </c>
       <c r="D150" t="n">
-        <v>0.00186</v>
+        <v>0.481713</v>
       </c>
       <c r="E150" t="n">
-        <v>0.009204</v>
+        <v>0.334162</v>
       </c>
       <c r="F150" t="n">
-        <v>0.005109</v>
+        <v>0.277588</v>
       </c>
       <c r="G150" t="n">
-        <v>0.00511</v>
+        <v>0.466732</v>
       </c>
       <c r="H150" t="n">
-        <v>0.007946999999999999</v>
+        <v>0.359879</v>
       </c>
       <c r="I150" t="n">
-        <v>0.035014</v>
+        <v>0.272872</v>
       </c>
       <c r="J150" t="n">
-        <v>0.022731</v>
-      </c>
-      <c r="K150" t="n">
-        <v>0.028077</v>
-      </c>
-      <c r="L150" t="n">
-        <v>0.022233</v>
+        <v>0.205556</v>
       </c>
     </row>
     <row r="151">
@@ -6070,36 +5502,32 @@
           <t>電子零組件業右上上市</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr"/>
+      <c r="B151" t="n">
+        <v>134799.474724</v>
+      </c>
       <c r="C151" t="n">
-        <v>212239.923382</v>
+        <v>159816.755702</v>
       </c>
       <c r="D151" t="n">
-        <v>260644.770609</v>
+        <v>165334.465168</v>
       </c>
       <c r="E151" t="n">
-        <v>252881.350332</v>
+        <v>203195.758365</v>
       </c>
       <c r="F151" t="n">
-        <v>288280.137475</v>
+        <v>192273.274984</v>
       </c>
       <c r="G151" t="n">
-        <v>272216.951119</v>
+        <v>169228.907964</v>
       </c>
       <c r="H151" t="n">
-        <v>249523.234844</v>
+        <v>175378.057132</v>
       </c>
       <c r="I151" t="n">
-        <v>281496.611912</v>
+        <v>230089.556546</v>
       </c>
       <c r="J151" t="n">
-        <v>274577.631584</v>
-      </c>
-      <c r="K151" t="n">
-        <v>240379.925722</v>
-      </c>
-      <c r="L151" t="n">
-        <v>190996.039914</v>
+        <v>296047.038899</v>
       </c>
     </row>
     <row r="152">
@@ -6108,36 +5536,32 @@
           <t>電子零組件業右上上櫃</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr"/>
+      <c r="B152" t="n">
+        <v>43.010299</v>
+      </c>
       <c r="C152" t="n">
-        <v>56.518314</v>
+        <v>42.700541</v>
       </c>
       <c r="D152" t="n">
-        <v>66.367521</v>
+        <v>43.028877</v>
       </c>
       <c r="E152" t="n">
-        <v>53.284507</v>
+        <v>26.789032</v>
       </c>
       <c r="F152" t="n">
-        <v>48.241051</v>
+        <v>42.105221</v>
       </c>
       <c r="G152" t="n">
-        <v>36.284562</v>
+        <v>38.990583</v>
       </c>
       <c r="H152" t="n">
-        <v>31.809219</v>
+        <v>38.012147</v>
       </c>
       <c r="I152" t="n">
-        <v>29.809244</v>
+        <v>66.00247400000001</v>
       </c>
       <c r="J152" t="n">
-        <v>33.764138</v>
-      </c>
-      <c r="K152" t="n">
-        <v>23.432639</v>
-      </c>
-      <c r="L152" t="n">
-        <v>31.436099</v>
+        <v>76.51372600000001</v>
       </c>
     </row>
     <row r="153">
@@ -6147,37 +5571,31 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0</v>
+        <v>4079.414857</v>
       </c>
       <c r="C153" t="n">
-        <v>1514.297729</v>
+        <v>2976.363321</v>
       </c>
       <c r="D153" t="n">
-        <v>1426.535756</v>
+        <v>4168.602855</v>
       </c>
       <c r="E153" t="n">
-        <v>2704.842008</v>
+        <v>7165.028589</v>
       </c>
       <c r="F153" t="n">
-        <v>2048.036309</v>
+        <v>3340.325803</v>
       </c>
       <c r="G153" t="n">
-        <v>1342.595385</v>
+        <v>5280.673074</v>
       </c>
       <c r="H153" t="n">
-        <v>1240.2426</v>
+        <v>2364.317114</v>
       </c>
       <c r="I153" t="n">
-        <v>1218.164008</v>
+        <v>2046.42661</v>
       </c>
       <c r="J153" t="n">
-        <v>3032.27055</v>
-      </c>
-      <c r="K153" t="n">
-        <v>1709.610922</v>
-      </c>
-      <c r="L153" t="n">
-        <v>1774.183622</v>
+        <v>2344.140071</v>
       </c>
     </row>
     <row r="154">
@@ -6187,37 +5605,31 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0</v>
+        <v>1.163785</v>
       </c>
       <c r="C154" t="n">
-        <v>0.282105</v>
+        <v>0.868373</v>
       </c>
       <c r="D154" t="n">
-        <v>0.216645</v>
+        <v>1.349424</v>
       </c>
       <c r="E154" t="n">
-        <v>0.327658</v>
+        <v>0.878818</v>
       </c>
       <c r="F154" t="n">
-        <v>0.536124</v>
+        <v>0.906027</v>
       </c>
       <c r="G154" t="n">
-        <v>0.581533</v>
+        <v>0.585062</v>
       </c>
       <c r="H154" t="n">
-        <v>0.354968</v>
+        <v>1.265771</v>
       </c>
       <c r="I154" t="n">
-        <v>0.66725625</v>
+        <v>1.083809</v>
       </c>
       <c r="J154" t="n">
-        <v>0.594823</v>
-      </c>
-      <c r="K154" t="n">
-        <v>0.271261</v>
-      </c>
-      <c r="L154" t="n">
-        <v>0.285248</v>
+        <v>0.763621</v>
       </c>
     </row>
     <row r="155">
@@ -6226,36 +5638,32 @@
           <t>電子零組件業平上市</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr"/>
+      <c r="B155" t="n">
+        <v>51202.763845</v>
+      </c>
       <c r="C155" t="n">
-        <v>1170.493586</v>
+        <v>30402.918995</v>
       </c>
       <c r="D155" t="n">
-        <v>5181.276807</v>
+        <v>41379.869619</v>
       </c>
       <c r="E155" t="n">
-        <v>1379.712515</v>
+        <v>2613.190429</v>
       </c>
       <c r="F155" t="n">
-        <v>5193.63549</v>
+        <v>3730.19601</v>
       </c>
       <c r="G155" t="n">
-        <v>6460.095241</v>
+        <v>24378.716212</v>
       </c>
       <c r="H155" t="n">
-        <v>4326.091821</v>
+        <v>19899.378642</v>
       </c>
       <c r="I155" t="n">
-        <v>2637.501858</v>
+        <v>9628.734207</v>
       </c>
       <c r="J155" t="n">
-        <v>3284.802021</v>
-      </c>
-      <c r="K155" t="n">
-        <v>2017.403891</v>
-      </c>
-      <c r="L155" t="n">
-        <v>1896.789729</v>
+        <v>8858.221991</v>
       </c>
     </row>
     <row r="156">
@@ -6264,36 +5672,32 @@
           <t>電子零組件業平上櫃</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr"/>
+      <c r="B156" t="n">
+        <v>3.798308</v>
+      </c>
       <c r="C156" t="n">
-        <v>0.07321900000000001</v>
+        <v>2.451794</v>
       </c>
       <c r="D156" t="n">
-        <v>0.407361</v>
+        <v>3.729705</v>
       </c>
       <c r="E156" t="n">
-        <v>0.62092</v>
+        <v>1.601472</v>
       </c>
       <c r="F156" t="n">
-        <v>0.580129</v>
+        <v>1.503673</v>
       </c>
       <c r="G156" t="n">
-        <v>0.280409</v>
+        <v>3.26944</v>
       </c>
       <c r="H156" t="n">
-        <v>0.218052</v>
+        <v>4.11166</v>
       </c>
       <c r="I156" t="n">
-        <v>1.148515</v>
+        <v>3.518995</v>
       </c>
       <c r="J156" t="n">
-        <v>1.307391</v>
-      </c>
-      <c r="K156" t="n">
-        <v>0.491261</v>
-      </c>
-      <c r="L156" t="n">
-        <v>0.462389</v>
+        <v>3.443462</v>
       </c>
     </row>
     <row r="157">
@@ -6302,36 +5706,32 @@
           <t>電機機械右上上市</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr"/>
+      <c r="B157" t="n">
+        <v>16702.322234</v>
+      </c>
       <c r="C157" t="n">
-        <v>13321.278082</v>
+        <v>12518.33041</v>
       </c>
       <c r="D157" t="n">
-        <v>14004.530873</v>
+        <v>20018.210526</v>
       </c>
       <c r="E157" t="n">
-        <v>18090.810561</v>
+        <v>19665.379644</v>
       </c>
       <c r="F157" t="n">
-        <v>12284.476715</v>
+        <v>16041.960584</v>
       </c>
       <c r="G157" t="n">
-        <v>11314.209497</v>
+        <v>16397.971383</v>
       </c>
       <c r="H157" t="n">
-        <v>9066.040854000001</v>
+        <v>15648.185563</v>
       </c>
       <c r="I157" t="n">
-        <v>10134.515194</v>
+        <v>20759.210972</v>
       </c>
       <c r="J157" t="n">
-        <v>14781.455424</v>
-      </c>
-      <c r="K157" t="n">
-        <v>12620.408788</v>
-      </c>
-      <c r="L157" t="n">
-        <v>10544.10687</v>
+        <v>19153.740726</v>
       </c>
     </row>
     <row r="158">
@@ -6340,36 +5740,32 @@
           <t>電機機械右上上櫃</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr"/>
+      <c r="B158" t="n">
+        <v>0.488623</v>
+      </c>
       <c r="C158" t="n">
-        <v>1.74163</v>
+        <v>0.322147</v>
       </c>
       <c r="D158" t="n">
-        <v>3.269753</v>
+        <v>0.406659</v>
       </c>
       <c r="E158" t="n">
-        <v>3.14509</v>
+        <v>0.255269</v>
       </c>
       <c r="F158" t="n">
-        <v>2.301886</v>
+        <v>0.281269</v>
       </c>
       <c r="G158" t="n">
-        <v>1.467358</v>
+        <v>1.930055</v>
       </c>
       <c r="H158" t="n">
-        <v>2.107852</v>
+        <v>1.779102</v>
       </c>
       <c r="I158" t="n">
-        <v>5.427414</v>
+        <v>3.481795</v>
       </c>
       <c r="J158" t="n">
-        <v>1.253359</v>
-      </c>
-      <c r="K158" t="n">
-        <v>1.139573</v>
-      </c>
-      <c r="L158" t="n">
-        <v>0.931666</v>
+        <v>2.240837</v>
       </c>
     </row>
     <row r="159">
@@ -6378,36 +5774,32 @@
           <t>電機機械右下上市</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr"/>
+      <c r="B159" t="n">
+        <v>2519.834647</v>
+      </c>
       <c r="C159" t="n">
-        <v>611.489534</v>
+        <v>884.234767</v>
       </c>
       <c r="D159" t="n">
-        <v>680.48504</v>
+        <v>960.535046</v>
       </c>
       <c r="E159" t="n">
-        <v>473.558533</v>
+        <v>1205.127393</v>
       </c>
       <c r="F159" t="n">
-        <v>584.027189</v>
+        <v>1278.56809225</v>
       </c>
       <c r="G159" t="n">
-        <v>343.269193</v>
+        <v>1352.800315</v>
       </c>
       <c r="H159" t="n">
-        <v>543.075396</v>
+        <v>1402.402289</v>
       </c>
       <c r="I159" t="n">
-        <v>646.117702</v>
+        <v>905.25175</v>
       </c>
       <c r="J159" t="n">
-        <v>1717.028051</v>
-      </c>
-      <c r="K159" t="n">
-        <v>352.824763</v>
-      </c>
-      <c r="L159" t="n">
-        <v>331.923278</v>
+        <v>1280.301169</v>
       </c>
     </row>
     <row r="160">
@@ -6417,37 +5809,31 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>0</v>
+        <v>0.2448195</v>
       </c>
       <c r="C160" t="n">
-        <v>0.170811</v>
+        <v>0.092209</v>
       </c>
       <c r="D160" t="n">
-        <v>0.220903</v>
+        <v>0.100141</v>
       </c>
       <c r="E160" t="n">
-        <v>0.16924</v>
+        <v>0.1047293333333333</v>
       </c>
       <c r="F160" t="n">
-        <v>0.207404</v>
+        <v>0.070176</v>
       </c>
       <c r="G160" t="n">
-        <v>0.15540275</v>
+        <v>0.085379</v>
       </c>
       <c r="H160" t="n">
-        <v>0.169802</v>
+        <v>0.128986</v>
       </c>
       <c r="I160" t="n">
-        <v>0.209134</v>
+        <v>0.09494175000000001</v>
       </c>
       <c r="J160" t="n">
-        <v>0.235345</v>
-      </c>
-      <c r="K160" t="n">
-        <v>0.130042</v>
-      </c>
-      <c r="L160" t="n">
-        <v>0.093056</v>
+        <v>0.145845</v>
       </c>
     </row>
     <row r="161">
@@ -6456,36 +5842,32 @@
           <t>電機機械平上市</t>
         </is>
       </c>
-      <c r="B161" t="inlineStr"/>
+      <c r="B161" t="n">
+        <v>2647.954011</v>
+      </c>
       <c r="C161" t="n">
-        <v>1707.75413</v>
+        <v>2332.54009</v>
       </c>
       <c r="D161" t="n">
-        <v>1955.966043</v>
+        <v>2449.834377</v>
       </c>
       <c r="E161" t="n">
-        <v>5092.939709</v>
+        <v>1136.442185</v>
       </c>
       <c r="F161" t="n">
-        <v>3150.795765</v>
+        <v>1901.489896</v>
       </c>
       <c r="G161" t="n">
-        <v>2491.977635</v>
+        <v>1746.753474</v>
       </c>
       <c r="H161" t="n">
-        <v>2144.443487</v>
+        <v>2660.71323</v>
       </c>
       <c r="I161" t="n">
-        <v>1723.208382</v>
+        <v>2417.710967</v>
       </c>
       <c r="J161" t="n">
-        <v>4955.894492</v>
-      </c>
-      <c r="K161" t="n">
-        <v>3359.359191</v>
-      </c>
-      <c r="L161" t="n">
-        <v>2471.751405</v>
+        <v>2536.58318</v>
       </c>
     </row>
     <row r="162">
@@ -6494,36 +5876,32 @@
           <t>電機機械平上櫃</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr"/>
+      <c r="B162" t="n">
+        <v>0.83971</v>
+      </c>
       <c r="C162" t="n">
-        <v>0.257052</v>
+        <v>0.744787</v>
       </c>
       <c r="D162" t="n">
-        <v>0.238004</v>
+        <v>0.979351</v>
       </c>
       <c r="E162" t="n">
-        <v>0.134215</v>
+        <v>0.675076</v>
       </c>
       <c r="F162" t="n">
-        <v>0.190753</v>
+        <v>0.768943</v>
       </c>
       <c r="G162" t="n">
-        <v>0.083256</v>
+        <v>0.155259</v>
       </c>
       <c r="H162" t="n">
-        <v>0.08768275</v>
+        <v>0.127739</v>
       </c>
       <c r="I162" t="n">
-        <v>0.1640553333333333</v>
+        <v>0.081984</v>
       </c>
       <c r="J162" t="n">
-        <v>0.157744</v>
-      </c>
-      <c r="K162" t="n">
-        <v>0.048963</v>
-      </c>
-      <c r="L162" t="n">
-        <v>0.073341</v>
+        <v>0.084762</v>
       </c>
     </row>
     <row r="163">
@@ -6532,36 +5910,32 @@
           <t>電腦及週邊設備業右上上市</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr"/>
+      <c r="B163" t="n">
+        <v>57189.849332</v>
+      </c>
       <c r="C163" t="n">
-        <v>63492.129342</v>
+        <v>33751.357946</v>
       </c>
       <c r="D163" t="n">
-        <v>53335.324846</v>
+        <v>43549.262809</v>
       </c>
       <c r="E163" t="n">
-        <v>58880.779072</v>
+        <v>31308.359244</v>
       </c>
       <c r="F163" t="n">
-        <v>63478.90797</v>
+        <v>31417.612394</v>
       </c>
       <c r="G163" t="n">
-        <v>59226.460614</v>
+        <v>44384.685133</v>
       </c>
       <c r="H163" t="n">
-        <v>65272.565677</v>
+        <v>38506.827754</v>
       </c>
       <c r="I163" t="n">
-        <v>63031.611578</v>
+        <v>42820.410934</v>
       </c>
       <c r="J163" t="n">
-        <v>55826.439154</v>
-      </c>
-      <c r="K163" t="n">
-        <v>42900.627578</v>
-      </c>
-      <c r="L163" t="n">
-        <v>46915.846703</v>
+        <v>39218.248622</v>
       </c>
     </row>
     <row r="164">
@@ -6570,36 +5944,32 @@
           <t>電腦及週邊設備業右上上櫃</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr"/>
+      <c r="B164" t="n">
+        <v>2.548452</v>
+      </c>
       <c r="C164" t="n">
-        <v>10.068981</v>
+        <v>6.445669</v>
       </c>
       <c r="D164" t="n">
-        <v>10.509797</v>
+        <v>6.813135</v>
       </c>
       <c r="E164" t="n">
-        <v>14.172706</v>
+        <v>3.458445</v>
       </c>
       <c r="F164" t="n">
-        <v>19.291862</v>
+        <v>3.286976</v>
       </c>
       <c r="G164" t="n">
-        <v>15.12789</v>
+        <v>5.63341</v>
       </c>
       <c r="H164" t="n">
-        <v>25.661031</v>
+        <v>7.647517</v>
       </c>
       <c r="I164" t="n">
-        <v>16.269784</v>
+        <v>4.386462</v>
       </c>
       <c r="J164" t="n">
-        <v>12.876549</v>
-      </c>
-      <c r="K164" t="n">
-        <v>9.253819999999999</v>
-      </c>
-      <c r="L164" t="n">
-        <v>8.036675000000001</v>
+        <v>3.744373</v>
       </c>
     </row>
     <row r="165">
@@ -6608,36 +5978,32 @@
           <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
-      <c r="B165" t="inlineStr"/>
+      <c r="B165" t="n">
+        <v>12295.172011</v>
+      </c>
       <c r="C165" t="n">
-        <v>1597.651389</v>
+        <v>8786.508749000001</v>
       </c>
       <c r="D165" t="n">
-        <v>1813.384412</v>
+        <v>15058.478097</v>
       </c>
       <c r="E165" t="n">
-        <v>1729.179547</v>
+        <v>8090.653738</v>
       </c>
       <c r="F165" t="n">
-        <v>1158.559299</v>
+        <v>8372.407546</v>
       </c>
       <c r="G165" t="n">
-        <v>784.6489</v>
+        <v>5011.133429</v>
       </c>
       <c r="H165" t="n">
-        <v>2001.439825</v>
+        <v>9046.637635999999</v>
       </c>
       <c r="I165" t="n">
-        <v>769.700337</v>
+        <v>6167.77495</v>
       </c>
       <c r="J165" t="n">
-        <v>946.853157</v>
-      </c>
-      <c r="K165" t="n">
-        <v>758.905752</v>
-      </c>
-      <c r="L165" t="n">
-        <v>968.824812</v>
+        <v>7418.865709</v>
       </c>
     </row>
     <row r="166">
@@ -6646,36 +6012,32 @@
           <t>電腦及週邊設備業右下上櫃</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr"/>
+      <c r="B166" t="n">
+        <v>0.141577</v>
+      </c>
       <c r="C166" t="n">
-        <v>0.46632</v>
+        <v>0.127289</v>
       </c>
       <c r="D166" t="n">
-        <v>0.423427</v>
+        <v>0.168679</v>
       </c>
       <c r="E166" t="n">
-        <v>0.421287</v>
+        <v>0.1089475</v>
       </c>
       <c r="F166" t="n">
-        <v>0.470641</v>
+        <v>0.087995</v>
       </c>
       <c r="G166" t="n">
-        <v>0.303985</v>
+        <v>0.151576</v>
       </c>
       <c r="H166" t="n">
-        <v>0.442342</v>
+        <v>0.163469</v>
       </c>
       <c r="I166" t="n">
-        <v>0.389074</v>
+        <v>0.09155199999999999</v>
       </c>
       <c r="J166" t="n">
-        <v>0.507887</v>
-      </c>
-      <c r="K166" t="n">
-        <v>0.223246</v>
-      </c>
-      <c r="L166" t="n">
-        <v>0.243398</v>
+        <v>0.15035425</v>
       </c>
     </row>
     <row r="167">
@@ -6684,36 +6046,32 @@
           <t>電腦及週邊設備業平上市</t>
         </is>
       </c>
-      <c r="B167" t="inlineStr"/>
+      <c r="B167" t="n">
+        <v>1160.820659</v>
+      </c>
       <c r="C167" t="n">
-        <v>268.546737</v>
+        <v>722.401066</v>
       </c>
       <c r="D167" t="n">
-        <v>240.647019</v>
+        <v>429.318786</v>
       </c>
       <c r="E167" t="n">
-        <v>332.327043</v>
+        <v>328.729665</v>
       </c>
       <c r="F167" t="n">
-        <v>756.057362</v>
+        <v>642.189541</v>
       </c>
       <c r="G167" t="n">
-        <v>371.585356</v>
+        <v>458.611679</v>
       </c>
       <c r="H167" t="n">
-        <v>203.031313</v>
+        <v>610.820832</v>
       </c>
       <c r="I167" t="n">
-        <v>1421.381164</v>
+        <v>904.703303</v>
       </c>
       <c r="J167" t="n">
-        <v>2624.697161</v>
-      </c>
-      <c r="K167" t="n">
-        <v>2175.023082</v>
-      </c>
-      <c r="L167" t="n">
-        <v>1278.674557</v>
+        <v>423.71279</v>
       </c>
     </row>
     <row r="168">
@@ -6722,36 +6080,32 @@
           <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
-      <c r="B168" t="inlineStr"/>
+      <c r="B168" t="n">
+        <v>3.247679</v>
+      </c>
       <c r="C168" t="n">
-        <v>0.385124</v>
+        <v>2.020245</v>
       </c>
       <c r="D168" t="n">
-        <v>0.013802</v>
+        <v>1.749221</v>
       </c>
       <c r="E168" t="n">
-        <v>0.256068</v>
+        <v>3.07077</v>
       </c>
       <c r="F168" t="n">
-        <v>0.234718</v>
+        <v>1.472591</v>
       </c>
       <c r="G168" t="n">
-        <v>0.446175</v>
+        <v>1.429916</v>
       </c>
       <c r="H168" t="n">
-        <v>0.06744600000000001</v>
+        <v>1.54623</v>
       </c>
       <c r="I168" t="n">
-        <v>0.06780799999999999</v>
+        <v>0.896875</v>
       </c>
       <c r="J168" t="n">
-        <v>0.050011</v>
-      </c>
-      <c r="K168" t="n">
-        <v>0.036287</v>
-      </c>
-      <c r="L168" t="n">
-        <v>0.021291</v>
+        <v>1.494557</v>
       </c>
     </row>
     <row r="169">
@@ -6760,36 +6114,32 @@
           <t>食品工業右上上市</t>
         </is>
       </c>
-      <c r="B169" t="inlineStr"/>
+      <c r="B169" t="n">
+        <v>15.076274</v>
+      </c>
       <c r="C169" t="n">
-        <v>469.126039</v>
+        <v>6.825473</v>
       </c>
       <c r="D169" t="n">
-        <v>375.624628</v>
+        <v>10.989736</v>
       </c>
       <c r="E169" t="n">
-        <v>273.06633</v>
+        <v>586.277846</v>
       </c>
       <c r="F169" t="n">
-        <v>1771.792354</v>
+        <v>7.264615</v>
       </c>
       <c r="G169" t="n">
-        <v>1756.260636</v>
+        <v>8.02271</v>
       </c>
       <c r="H169" t="n">
-        <v>1654.563608</v>
+        <v>11.865974</v>
       </c>
       <c r="I169" t="n">
-        <v>1818.287772</v>
+        <v>16.580074</v>
       </c>
       <c r="J169" t="n">
-        <v>1643.778448</v>
-      </c>
-      <c r="K169" t="n">
-        <v>2051.00961</v>
-      </c>
-      <c r="L169" t="n">
-        <v>2151.208133</v>
+        <v>7.674888</v>
       </c>
     </row>
     <row r="170">
@@ -6798,36 +6148,32 @@
           <t>食品工業右上上櫃</t>
         </is>
       </c>
-      <c r="B170" t="inlineStr"/>
+      <c r="B170" t="n">
+        <v>0.002855</v>
+      </c>
       <c r="C170" t="n">
-        <v>0.003339</v>
+        <v>0.002955</v>
       </c>
       <c r="D170" t="n">
-        <v>0.011337</v>
+        <v>0.004336</v>
       </c>
       <c r="E170" t="n">
-        <v>0.008984000000000001</v>
+        <v>0.002534</v>
       </c>
       <c r="F170" t="n">
-        <v>0.005588</v>
+        <v>0.001886</v>
       </c>
       <c r="G170" t="n">
-        <v>0.0041</v>
+        <v>0.003556</v>
       </c>
       <c r="H170" t="n">
-        <v>0.003348</v>
+        <v>0.004412</v>
       </c>
       <c r="I170" t="n">
-        <v>0.003849</v>
+        <v>0.005225</v>
       </c>
       <c r="J170" t="n">
-        <v>0.005952</v>
-      </c>
-      <c r="K170" t="n">
-        <v>0.002668</v>
-      </c>
-      <c r="L170" t="n">
-        <v>0.004825</v>
+        <v>0.005884</v>
       </c>
     </row>
     <row r="171">
@@ -6836,36 +6182,32 @@
           <t>食品工業右下上市</t>
         </is>
       </c>
-      <c r="B171" t="inlineStr"/>
+      <c r="B171" t="n">
+        <v>652.643063</v>
+      </c>
       <c r="C171" t="n">
-        <v>1477.885633</v>
+        <v>278.579927</v>
       </c>
       <c r="D171" t="n">
-        <v>672.012913</v>
+        <v>412.232246</v>
       </c>
       <c r="E171" t="n">
-        <v>606.756761</v>
+        <v>284.234782</v>
       </c>
       <c r="F171" t="n">
-        <v>556.059529</v>
+        <v>286.797627</v>
       </c>
       <c r="G171" t="n">
-        <v>394.99157</v>
+        <v>318.886002</v>
       </c>
       <c r="H171" t="n">
-        <v>440.144214</v>
+        <v>261.472583</v>
       </c>
       <c r="I171" t="n">
-        <v>515.359555</v>
+        <v>264.272879</v>
       </c>
       <c r="J171" t="n">
-        <v>458.714676</v>
-      </c>
-      <c r="K171" t="n">
-        <v>249.687836</v>
-      </c>
-      <c r="L171" t="n">
-        <v>477.015005</v>
+        <v>1672.273661</v>
       </c>
     </row>
     <row r="172">
@@ -6874,36 +6216,32 @@
           <t>食品工業右下上櫃</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr"/>
+      <c r="B172" t="n">
+        <v>0.009090000000000001</v>
+      </c>
       <c r="C172" t="n">
-        <v>0.01254933333333333</v>
+        <v>0.007544</v>
       </c>
       <c r="D172" t="n">
-        <v>0.039715</v>
+        <v>0.014792</v>
       </c>
       <c r="E172" t="n">
-        <v>0.030591</v>
+        <v>0.01134</v>
       </c>
       <c r="F172" t="n">
-        <v>0.021794</v>
+        <v>0.010856</v>
       </c>
       <c r="G172" t="n">
-        <v>0.028857</v>
+        <v>0.005911</v>
       </c>
       <c r="H172" t="n">
-        <v>0.022423</v>
+        <v>0.010054</v>
       </c>
       <c r="I172" t="n">
-        <v>0.052808</v>
+        <v>0.006973</v>
       </c>
       <c r="J172" t="n">
-        <v>0.042615</v>
-      </c>
-      <c r="K172" t="n">
-        <v>0.035191</v>
-      </c>
-      <c r="L172" t="n">
-        <v>0.026652</v>
+        <v>0.010705</v>
       </c>
     </row>
     <row r="173">
@@ -6912,36 +6250,32 @@
           <t>食品工業平上市</t>
         </is>
       </c>
-      <c r="B173" t="inlineStr"/>
+      <c r="B173" t="n">
+        <v>1389.010951</v>
+      </c>
       <c r="C173" t="n">
-        <v>3.831788</v>
+        <v>349.625369</v>
       </c>
       <c r="D173" t="n">
-        <v>1239.255507</v>
+        <v>500.595241</v>
       </c>
       <c r="E173" t="n">
-        <v>1989.418686</v>
+        <v>17.710497</v>
       </c>
       <c r="F173" t="n">
-        <v>48.063088</v>
+        <v>373.919301</v>
       </c>
       <c r="G173" t="n">
-        <v>234.910596</v>
+        <v>490.134677</v>
       </c>
       <c r="H173" t="n">
-        <v>5.828933</v>
+        <v>526.461753</v>
       </c>
       <c r="I173" t="n">
-        <v>165.375512</v>
+        <v>441.182343</v>
       </c>
       <c r="J173" t="n">
-        <v>6.777092</v>
-      </c>
-      <c r="K173" t="n">
-        <v>37.806877</v>
-      </c>
-      <c r="L173" t="n">
-        <v>35.700802</v>
+        <v>5.599845</v>
       </c>
     </row>
     <row r="174">
@@ -6950,29 +6284,33 @@
           <t>食品工業平上櫃</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr"/>
+      <c r="B174" t="n">
+        <v>0.002604</v>
+      </c>
       <c r="C174" t="n">
-        <v>0.039357</v>
+        <v>0.000697</v>
       </c>
       <c r="D174" t="n">
-        <v>0.003659</v>
+        <v>0.000831</v>
       </c>
       <c r="E174" t="n">
-        <v>0.002276</v>
+        <v>0.002383</v>
       </c>
       <c r="F174" t="n">
-        <v>0.004203</v>
+        <v>0.004609</v>
       </c>
       <c r="G174" t="n">
-        <v>0.003217</v>
+        <v>0.003325</v>
       </c>
       <c r="H174" t="n">
-        <v>0.001827</v>
-      </c>
-      <c r="I174" t="inlineStr"/>
-      <c r="J174" t="inlineStr"/>
-      <c r="K174" t="inlineStr"/>
-      <c r="L174" t="inlineStr"/>
+        <v>0.0007</v>
+      </c>
+      <c r="I174" t="n">
+        <v>0.001953</v>
+      </c>
+      <c r="J174" t="n">
+        <v>0.001035</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Result/analyze_2.xlsx
+++ b/Result/analyze_2.xlsx
@@ -963,31 +963,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>234.284746</v>
+        <v>230.51159</v>
       </c>
       <c r="C16" t="n">
-        <v>156.381504</v>
+        <v>154.974416</v>
       </c>
       <c r="D16" t="n">
-        <v>206.00848</v>
+        <v>204.045792</v>
       </c>
       <c r="E16" t="n">
-        <v>156.812233</v>
+        <v>156.255981</v>
       </c>
       <c r="F16" t="n">
-        <v>122.867876</v>
+        <v>122.188769</v>
       </c>
       <c r="G16" t="n">
-        <v>175.389483</v>
+        <v>173.258883</v>
       </c>
       <c r="H16" t="n">
-        <v>168.399942</v>
+        <v>167.846943</v>
       </c>
       <c r="I16" t="n">
-        <v>163.335916</v>
+        <v>162.343206</v>
       </c>
       <c r="J16" t="n">
-        <v>192.89349</v>
+        <v>190.95954</v>
       </c>
     </row>
     <row r="17">
@@ -1358,10 +1358,10 @@
         <v>123.720141</v>
       </c>
       <c r="I27" t="n">
-        <v>128.156429</v>
+        <v>128.044739</v>
       </c>
       <c r="J27" t="n">
-        <v>116.521098</v>
+        <v>116.435808</v>
       </c>
     </row>
     <row r="28">
@@ -1473,25 +1473,25 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>12.222525</v>
+        <v>12.194661</v>
       </c>
       <c r="C31" t="n">
-        <v>12.01162</v>
+        <v>11.973196</v>
       </c>
       <c r="D31" t="n">
-        <v>8.919328999999999</v>
+        <v>8.887313000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>7.408792</v>
+        <v>7.38079</v>
       </c>
       <c r="F31" t="n">
-        <v>9.363797</v>
+        <v>9.350882</v>
       </c>
       <c r="G31" t="n">
-        <v>8.949622</v>
+        <v>8.927008000000001</v>
       </c>
       <c r="H31" t="n">
-        <v>16.412917</v>
+        <v>16.387354</v>
       </c>
       <c r="I31" t="n">
         <v>14.89894</v>
@@ -4619,31 +4619,31 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>986.052947</v>
+        <v>905.133794</v>
       </c>
       <c r="C125" t="n">
-        <v>604.61089</v>
+        <v>491.960239</v>
       </c>
       <c r="D125" t="n">
-        <v>516.815906</v>
+        <v>431.198429</v>
       </c>
       <c r="E125" t="n">
-        <v>631.525347</v>
+        <v>574.917972</v>
       </c>
       <c r="F125" t="n">
-        <v>537.375755</v>
+        <v>437.072996</v>
       </c>
       <c r="G125" t="n">
-        <v>513.733269</v>
+        <v>441.590088</v>
       </c>
       <c r="H125" t="n">
-        <v>544.3139159999999</v>
+        <v>449.552373</v>
       </c>
       <c r="I125" t="n">
-        <v>523.45054</v>
+        <v>413.635324</v>
       </c>
       <c r="J125" t="n">
-        <v>549.850026</v>
+        <v>473.00502</v>
       </c>
     </row>
     <row r="126">
@@ -5506,28 +5506,28 @@
         <v>134799.474724</v>
       </c>
       <c r="C151" t="n">
-        <v>159816.755702</v>
+        <v>159551.687657</v>
       </c>
       <c r="D151" t="n">
         <v>165334.465168</v>
       </c>
       <c r="E151" t="n">
-        <v>203195.758365</v>
+        <v>202291.836966</v>
       </c>
       <c r="F151" t="n">
-        <v>192273.274984</v>
+        <v>189680.575138</v>
       </c>
       <c r="G151" t="n">
-        <v>169228.907964</v>
+        <v>168771.19836</v>
       </c>
       <c r="H151" t="n">
-        <v>175378.057132</v>
+        <v>175055.014039</v>
       </c>
       <c r="I151" t="n">
-        <v>230089.556546</v>
+        <v>229808.256647</v>
       </c>
       <c r="J151" t="n">
-        <v>296047.038899</v>
+        <v>295285.351175</v>
       </c>
     </row>
     <row r="152">
@@ -5537,31 +5537,31 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>43.010299</v>
+        <v>41.041835</v>
       </c>
       <c r="C152" t="n">
-        <v>42.700541</v>
+        <v>39.551208</v>
       </c>
       <c r="D152" t="n">
-        <v>43.028877</v>
+        <v>41.06388</v>
       </c>
       <c r="E152" t="n">
-        <v>26.789032</v>
+        <v>25.823852</v>
       </c>
       <c r="F152" t="n">
-        <v>42.105221</v>
+        <v>37.603645</v>
       </c>
       <c r="G152" t="n">
-        <v>38.990583</v>
+        <v>29.674985</v>
       </c>
       <c r="H152" t="n">
-        <v>38.012147</v>
+        <v>28.779912</v>
       </c>
       <c r="I152" t="n">
-        <v>66.00247400000001</v>
+        <v>49.045555</v>
       </c>
       <c r="J152" t="n">
-        <v>76.51372600000001</v>
+        <v>64.95413499999999</v>
       </c>
     </row>
     <row r="153">
@@ -5605,31 +5605,31 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>1.163785</v>
+        <v>1.15189</v>
       </c>
       <c r="C154" t="n">
-        <v>0.868373</v>
+        <v>0.8619560000000001</v>
       </c>
       <c r="D154" t="n">
-        <v>1.349424</v>
+        <v>1.339275</v>
       </c>
       <c r="E154" t="n">
-        <v>0.878818</v>
+        <v>0.87322</v>
       </c>
       <c r="F154" t="n">
-        <v>0.906027</v>
+        <v>0.901962</v>
       </c>
       <c r="G154" t="n">
-        <v>0.585062</v>
+        <v>0.574451</v>
       </c>
       <c r="H154" t="n">
-        <v>1.265771</v>
+        <v>1.249787</v>
       </c>
       <c r="I154" t="n">
-        <v>1.083809</v>
+        <v>1.073411</v>
       </c>
       <c r="J154" t="n">
-        <v>0.763621</v>
+        <v>0.757948</v>
       </c>
     </row>
     <row r="155">
@@ -5639,13 +5639,13 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>51202.763845</v>
+        <v>51156.753787</v>
       </c>
       <c r="C155" t="n">
         <v>30402.918995</v>
       </c>
       <c r="D155" t="n">
-        <v>41379.869619</v>
+        <v>40934.241108</v>
       </c>
       <c r="E155" t="n">
         <v>2613.190429</v>
@@ -5911,31 +5911,31 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>57189.849332</v>
+        <v>56799.699296</v>
       </c>
       <c r="C163" t="n">
-        <v>33751.357946</v>
+        <v>33251.31356</v>
       </c>
       <c r="D163" t="n">
-        <v>43549.262809</v>
+        <v>43335.107824</v>
       </c>
       <c r="E163" t="n">
-        <v>31308.359244</v>
+        <v>31110.029175</v>
       </c>
       <c r="F163" t="n">
-        <v>31417.612394</v>
+        <v>31285.393991</v>
       </c>
       <c r="G163" t="n">
-        <v>44384.685133</v>
+        <v>43834.111024</v>
       </c>
       <c r="H163" t="n">
-        <v>38506.827754</v>
+        <v>38144.865106</v>
       </c>
       <c r="I163" t="n">
-        <v>42820.410934</v>
+        <v>42702.884281</v>
       </c>
       <c r="J163" t="n">
-        <v>39218.248622</v>
+        <v>38943.878033</v>
       </c>
     </row>
     <row r="164">

--- a/Result/analyze_2.xlsx
+++ b/Result/analyze_2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J174"/>
+  <dimension ref="A1:K173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,7 +436,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -477,6 +477,11 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -486,32 +491,33 @@
           <t>光電業右上上市</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>65690.527527</v>
-      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>78279.22962899999</v>
+        <v>79928.792447</v>
       </c>
       <c r="D2" t="n">
-        <v>115422.481566</v>
+        <v>118574.925682</v>
       </c>
       <c r="E2" t="n">
-        <v>75436.525366</v>
+        <v>77016.14013699999</v>
       </c>
       <c r="F2" t="n">
-        <v>46586.686312</v>
+        <v>47630.618118</v>
       </c>
       <c r="G2" t="n">
-        <v>51847.523042</v>
+        <v>52329.13654</v>
       </c>
       <c r="H2" t="n">
-        <v>86070.802371</v>
+        <v>87049.123955</v>
       </c>
       <c r="I2" t="n">
-        <v>106432.610774</v>
+        <v>107133.497541</v>
       </c>
       <c r="J2" t="n">
-        <v>74175.14004899999</v>
+        <v>74782.54464199999</v>
+      </c>
+      <c r="K2" t="n">
+        <v>107205.401757</v>
       </c>
     </row>
     <row r="3">
@@ -520,32 +526,33 @@
           <t>光電業右上上櫃</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>7.587945</v>
-      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>7.202591</v>
+        <v>6.987814</v>
       </c>
       <c r="D3" t="n">
-        <v>4.93632</v>
+        <v>5.099475</v>
       </c>
       <c r="E3" t="n">
-        <v>1.988611</v>
+        <v>2.190618</v>
       </c>
       <c r="F3" t="n">
-        <v>4.200368</v>
+        <v>4.812548</v>
       </c>
       <c r="G3" t="n">
-        <v>6.813472</v>
+        <v>6.86136</v>
       </c>
       <c r="H3" t="n">
-        <v>6.721156</v>
+        <v>6.966875</v>
       </c>
       <c r="I3" t="n">
-        <v>6.072605</v>
+        <v>5.827265</v>
       </c>
       <c r="J3" t="n">
-        <v>12.53609</v>
+        <v>12.342156</v>
+      </c>
+      <c r="K3" t="n">
+        <v>10.210951</v>
       </c>
     </row>
     <row r="4">
@@ -554,32 +561,33 @@
           <t>光電業右下上市</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>1218.572409</v>
-      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>1113.648427</v>
+        <v>719.230276</v>
       </c>
       <c r="D4" t="n">
-        <v>2192.450429</v>
+        <v>777.189132</v>
       </c>
       <c r="E4" t="n">
-        <v>1103.326977</v>
+        <v>806.877796</v>
       </c>
       <c r="F4" t="n">
-        <v>1742.305728</v>
+        <v>1126.467387</v>
       </c>
       <c r="G4" t="n">
-        <v>898.356579</v>
+        <v>493.512412</v>
       </c>
       <c r="H4" t="n">
-        <v>1542.59659</v>
+        <v>1005.678589</v>
       </c>
       <c r="I4" t="n">
-        <v>627.005644</v>
+        <v>680.281414</v>
       </c>
       <c r="J4" t="n">
-        <v>809.753993</v>
+        <v>252.940066</v>
+      </c>
+      <c r="K4" t="n">
+        <v>522.107802</v>
       </c>
     </row>
     <row r="5">
@@ -589,31 +597,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.65914</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>1.232648</v>
+        <v>0.889545</v>
       </c>
       <c r="D5" t="n">
-        <v>1.026978</v>
+        <v>0.9406870000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>1.008579</v>
+        <v>0.91806</v>
       </c>
       <c r="F5" t="n">
-        <v>0.944307</v>
+        <v>0.875647</v>
       </c>
       <c r="G5" t="n">
-        <v>1.39092525</v>
+        <v>1.343617</v>
       </c>
       <c r="H5" t="n">
-        <v>0.866345</v>
+        <v>0.840773</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9060865</v>
+        <v>0.7844285</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9748790000000001</v>
+        <v>0.880501</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.19168</v>
       </c>
     </row>
     <row r="6">
@@ -622,32 +633,33 @@
           <t>光電業平上市</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>2260.003599</v>
-      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>1925.604833</v>
+        <v>670.460166</v>
       </c>
       <c r="D6" t="n">
-        <v>3533.057299</v>
+        <v>1795.87448</v>
       </c>
       <c r="E6" t="n">
-        <v>1768.985805</v>
+        <v>485.820215</v>
       </c>
       <c r="F6" t="n">
-        <v>1177.860188</v>
+        <v>749.766723</v>
       </c>
       <c r="G6" t="n">
-        <v>656.082342</v>
+        <v>579.313011</v>
       </c>
       <c r="H6" t="n">
-        <v>1194.916813</v>
+        <v>753.51323</v>
       </c>
       <c r="I6" t="n">
-        <v>1063.781628</v>
+        <v>309.619091</v>
       </c>
       <c r="J6" t="n">
-        <v>1114.478124</v>
+        <v>1063.887458</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1306.479152</v>
       </c>
     </row>
     <row r="7">
@@ -656,32 +668,33 @@
           <t>光電業平上櫃</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>0.43081</v>
-      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>0.285278</v>
+        <v>0.623261</v>
       </c>
       <c r="D7" t="n">
-        <v>0.684599</v>
+        <v>0.345019</v>
       </c>
       <c r="E7" t="n">
-        <v>0.510082</v>
+        <v>0.202875</v>
       </c>
       <c r="F7" t="n">
-        <v>0.936181</v>
+        <v>0.194899</v>
       </c>
       <c r="G7" t="n">
-        <v>0.22408</v>
+        <v>0.08137</v>
       </c>
       <c r="H7" t="n">
-        <v>0.507507</v>
+        <v>0.167453</v>
       </c>
       <c r="I7" t="n">
-        <v>0.161472</v>
+        <v>0.169812</v>
       </c>
       <c r="J7" t="n">
-        <v>0.230956</v>
+        <v>0.20574</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.461706</v>
       </c>
     </row>
     <row r="8">
@@ -690,32 +703,33 @@
           <t>其他右上上市</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>1055.206274</v>
-      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>820.930312</v>
+        <v>633.41831</v>
       </c>
       <c r="D8" t="n">
-        <v>708.754765</v>
+        <v>545.652845</v>
       </c>
       <c r="E8" t="n">
-        <v>695.467022</v>
+        <v>718.182277</v>
       </c>
       <c r="F8" t="n">
-        <v>804.3266159999999</v>
+        <v>808.951334</v>
       </c>
       <c r="G8" t="n">
-        <v>945.081587</v>
+        <v>653.1447899999999</v>
       </c>
       <c r="H8" t="n">
-        <v>1026.433541</v>
+        <v>806.822822</v>
       </c>
       <c r="I8" t="n">
-        <v>1319.534296</v>
+        <v>1166.586888</v>
       </c>
       <c r="J8" t="n">
-        <v>1653.5761</v>
+        <v>1535.231402</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1831.969767</v>
       </c>
     </row>
     <row r="9">
@@ -724,32 +738,33 @@
           <t>其他右上上櫃</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>3.467932</v>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>2.240566666666667</v>
+        <v>2.200489666666666</v>
       </c>
       <c r="D9" t="n">
-        <v>1.733862</v>
+        <v>1.709308</v>
       </c>
       <c r="E9" t="n">
-        <v>4.251473</v>
+        <v>4.243406</v>
       </c>
       <c r="F9" t="n">
-        <v>1.366303</v>
+        <v>1.365579</v>
       </c>
       <c r="G9" t="n">
-        <v>1.71218</v>
+        <v>1.710009</v>
       </c>
       <c r="H9" t="n">
-        <v>1.99472</v>
+        <v>1.993449</v>
       </c>
       <c r="I9" t="n">
-        <v>1.926111</v>
+        <v>1.906945</v>
       </c>
       <c r="J9" t="n">
-        <v>1.867746</v>
+        <v>1.842676</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.807055</v>
       </c>
     </row>
     <row r="10">
@@ -758,32 +773,33 @@
           <t>其他右下上市</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>241.472439</v>
-      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>209.442973</v>
+        <v>282.471823</v>
       </c>
       <c r="D10" t="n">
-        <v>1887.073794</v>
+        <v>2057.031488</v>
       </c>
       <c r="E10" t="n">
-        <v>1367.403104</v>
+        <v>1537.147381</v>
       </c>
       <c r="F10" t="n">
-        <v>821.838253</v>
+        <v>840.695142</v>
       </c>
       <c r="G10" t="n">
-        <v>957.630659</v>
+        <v>956.589307</v>
       </c>
       <c r="H10" t="n">
-        <v>1092.657216</v>
+        <v>1092.69051</v>
       </c>
       <c r="I10" t="n">
-        <v>1151.470527</v>
+        <v>1279.983284</v>
       </c>
       <c r="J10" t="n">
-        <v>1061.894658</v>
+        <v>1091.299464</v>
+      </c>
+      <c r="K10" t="n">
+        <v>916.9355430000001</v>
       </c>
     </row>
     <row r="11">
@@ -793,31 +809,34 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.741591</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>4.223545</v>
+        <v>4.280272</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7884640000000001</v>
+        <v>0.800986</v>
       </c>
       <c r="E11" t="n">
-        <v>0.36906525</v>
+        <v>0.38835725</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2415985</v>
+        <v>0.2769725</v>
       </c>
       <c r="G11" t="n">
-        <v>0.308221</v>
+        <v>0.318779</v>
       </c>
       <c r="H11" t="n">
-        <v>0.341959</v>
+        <v>0.413046</v>
       </c>
       <c r="I11" t="n">
-        <v>2.512299</v>
+        <v>2.517685</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9608650833333334</v>
+        <v>1.032013083333333</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.066645</v>
       </c>
     </row>
     <row r="12">
@@ -826,32 +845,33 @@
           <t>其他平上市</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>1355.467353</v>
-      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>1098.174253</v>
+        <v>1212.657405</v>
       </c>
       <c r="D12" t="n">
-        <v>368.675684</v>
+        <v>361.81991</v>
       </c>
       <c r="E12" t="n">
-        <v>281.544287</v>
+        <v>89.084755</v>
       </c>
       <c r="F12" t="n">
-        <v>142.31445</v>
+        <v>118.832843</v>
       </c>
       <c r="G12" t="n">
-        <v>164.8614</v>
+        <v>457.839549</v>
       </c>
       <c r="H12" t="n">
-        <v>148.657663</v>
+        <v>368.235088</v>
       </c>
       <c r="I12" t="n">
-        <v>246.467539</v>
+        <v>270.90219</v>
       </c>
       <c r="J12" t="n">
-        <v>179.031457</v>
+        <v>267.971349</v>
+      </c>
+      <c r="K12" t="n">
+        <v>598.822589</v>
       </c>
     </row>
     <row r="13">
@@ -860,32 +880,33 @@
           <t>其他平上櫃</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>0.16779</v>
-      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>0.108556</v>
+        <v>0.055679</v>
       </c>
       <c r="D13" t="n">
-        <v>0.045488</v>
+        <v>0.038459</v>
       </c>
       <c r="E13" t="n">
-        <v>0.053156</v>
+        <v>0.028894</v>
       </c>
       <c r="F13" t="n">
-        <v>0.07677200000000001</v>
+        <v>0.028113</v>
       </c>
       <c r="G13" t="n">
-        <v>0.073134</v>
+        <v>0.053851</v>
       </c>
       <c r="H13" t="n">
-        <v>0.10516</v>
+        <v>0.027037</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0696565</v>
+        <v>0.0627825</v>
       </c>
       <c r="J13" t="n">
-        <v>0.085149</v>
+        <v>0.011982</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.105841</v>
       </c>
     </row>
     <row r="14">
@@ -894,32 +915,33 @@
           <t>其他電子業右上上市</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>51547.946181</v>
-      </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>35334.124465</v>
+        <v>37059.210861</v>
       </c>
       <c r="D14" t="n">
-        <v>43866.035113</v>
+        <v>45538.942915</v>
       </c>
       <c r="E14" t="n">
-        <v>39906.027565</v>
+        <v>40603.861329</v>
       </c>
       <c r="F14" t="n">
-        <v>36079.271484</v>
+        <v>36308.402063</v>
       </c>
       <c r="G14" t="n">
-        <v>35352.869423</v>
+        <v>35956.648033</v>
       </c>
       <c r="H14" t="n">
-        <v>43844.505121</v>
+        <v>43873.810083</v>
       </c>
       <c r="I14" t="n">
-        <v>33855.922663</v>
+        <v>34212.143456</v>
       </c>
       <c r="J14" t="n">
-        <v>39818.732</v>
+        <v>41155.164782</v>
+      </c>
+      <c r="K14" t="n">
+        <v>58812.202222</v>
       </c>
     </row>
     <row r="15">
@@ -928,32 +950,33 @@
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>14.315344</v>
-      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
-        <v>7.751108</v>
+        <v>9.364144</v>
       </c>
       <c r="D15" t="n">
-        <v>11.431169</v>
+        <v>13.96111966666667</v>
       </c>
       <c r="E15" t="n">
-        <v>9.114428</v>
+        <v>10.770535</v>
       </c>
       <c r="F15" t="n">
-        <v>13.437214</v>
+        <v>14.468626</v>
       </c>
       <c r="G15" t="n">
-        <v>8.991203000000001</v>
+        <v>10.602243</v>
       </c>
       <c r="H15" t="n">
-        <v>10.506049</v>
+        <v>13.766269</v>
       </c>
       <c r="I15" t="n">
-        <v>6.719846</v>
+        <v>9.905314000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>7.302763</v>
+        <v>10.250491</v>
+      </c>
+      <c r="K15" t="n">
+        <v>13.550757</v>
       </c>
     </row>
     <row r="16">
@@ -962,32 +985,33 @@
           <t>其他電子業右下上市</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>230.51159</v>
-      </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>154.974416</v>
+        <v>359.326326</v>
       </c>
       <c r="D16" t="n">
-        <v>204.045792</v>
+        <v>399.891125</v>
       </c>
       <c r="E16" t="n">
-        <v>156.255981</v>
+        <v>418.121535</v>
       </c>
       <c r="F16" t="n">
-        <v>122.188769</v>
+        <v>387.959514</v>
       </c>
       <c r="G16" t="n">
-        <v>173.258883</v>
+        <v>388.689652</v>
       </c>
       <c r="H16" t="n">
-        <v>167.846943</v>
+        <v>437.686363</v>
       </c>
       <c r="I16" t="n">
-        <v>162.343206</v>
+        <v>342.637731</v>
       </c>
       <c r="J16" t="n">
-        <v>190.95954</v>
+        <v>368.704943</v>
+      </c>
+      <c r="K16" t="n">
+        <v>772.19219</v>
       </c>
     </row>
     <row r="17">
@@ -997,31 +1021,34 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.491751</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.184766</v>
+        <v>0.093711</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2174656666666667</v>
+        <v>0.066887</v>
       </c>
       <c r="E17" t="n">
-        <v>0.184608</v>
+        <v>0.084369</v>
       </c>
       <c r="F17" t="n">
-        <v>0.238945</v>
+        <v>0.158487</v>
       </c>
       <c r="G17" t="n">
-        <v>0.102638</v>
+        <v>0.042562</v>
       </c>
       <c r="H17" t="n">
-        <v>0.075781</v>
+        <v>0.034033</v>
       </c>
       <c r="I17" t="n">
-        <v>0.087064</v>
+        <v>0.043911</v>
       </c>
       <c r="J17" t="n">
-        <v>0.114932</v>
+        <v>0.058318</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.086136</v>
       </c>
     </row>
     <row r="18">
@@ -1030,32 +1057,33 @@
           <t>其他電子業平上市</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>2074.881403</v>
-      </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>2251.592724</v>
+        <v>322.154418</v>
       </c>
       <c r="D18" t="n">
-        <v>2269.923561</v>
+        <v>401.170426</v>
       </c>
       <c r="E18" t="n">
-        <v>1069.607557</v>
+        <v>109.908239</v>
       </c>
       <c r="F18" t="n">
-        <v>733.0549140000001</v>
+        <v>238.15359</v>
       </c>
       <c r="G18" t="n">
-        <v>1399.054171</v>
+        <v>579.844792</v>
       </c>
       <c r="H18" t="n">
-        <v>662.797492</v>
+        <v>363.65311</v>
       </c>
       <c r="I18" t="n">
-        <v>756.907611</v>
+        <v>220.392293</v>
       </c>
       <c r="J18" t="n">
-        <v>1625.270931</v>
+        <v>111.092746</v>
+      </c>
+      <c r="K18" t="n">
+        <v>157.503139</v>
       </c>
     </row>
     <row r="19">
@@ -1064,32 +1092,33 @@
           <t>其他電子業平上櫃</t>
         </is>
       </c>
-      <c r="B19" t="n">
-        <v>1.982743</v>
-      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>2.216785</v>
+        <v>0.669154</v>
       </c>
       <c r="D19" t="n">
-        <v>3.218028</v>
+        <v>0.820887</v>
       </c>
       <c r="E19" t="n">
-        <v>2.334074</v>
+        <v>0.761592</v>
       </c>
       <c r="F19" t="n">
-        <v>1.500443</v>
+        <v>0.539728</v>
       </c>
       <c r="G19" t="n">
-        <v>1.856242</v>
+        <v>0.296326</v>
       </c>
       <c r="H19" t="n">
-        <v>3.652731</v>
+        <v>0.422162</v>
       </c>
       <c r="I19" t="n">
-        <v>3.487986</v>
+        <v>0.336347</v>
       </c>
       <c r="J19" t="n">
-        <v>3.057712</v>
+        <v>0.14361</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.27148</v>
       </c>
     </row>
     <row r="20">
@@ -1098,32 +1127,33 @@
           <t>化學工業右上上市</t>
         </is>
       </c>
-      <c r="B20" t="n">
-        <v>6032.167382</v>
-      </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>4010.314605</v>
+        <v>3736.050449</v>
       </c>
       <c r="D20" t="n">
-        <v>5364.965027</v>
+        <v>5535.172004</v>
       </c>
       <c r="E20" t="n">
-        <v>8292.582050000001</v>
+        <v>8562.394875</v>
       </c>
       <c r="F20" t="n">
-        <v>9882.511367999999</v>
+        <v>10231.82806</v>
       </c>
       <c r="G20" t="n">
-        <v>6355.062814</v>
+        <v>7037.580581</v>
       </c>
       <c r="H20" t="n">
-        <v>8542.054827</v>
+        <v>8922.589506</v>
       </c>
       <c r="I20" t="n">
-        <v>5022.470767</v>
+        <v>5951.538249</v>
       </c>
       <c r="J20" t="n">
-        <v>10431.09168</v>
+        <v>10798.870931</v>
+      </c>
+      <c r="K20" t="n">
+        <v>11033.84295</v>
       </c>
     </row>
     <row r="21">
@@ -1132,32 +1162,33 @@
           <t>化學工業右上上櫃</t>
         </is>
       </c>
-      <c r="B21" t="n">
-        <v>0.079762</v>
-      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
-        <v>0.157836</v>
+        <v>0.207952</v>
       </c>
       <c r="D21" t="n">
-        <v>0.104806</v>
+        <v>0.136287</v>
       </c>
       <c r="E21" t="n">
-        <v>0.08237700000000001</v>
+        <v>0.108029</v>
       </c>
       <c r="F21" t="n">
-        <v>0.129619</v>
+        <v>0.253387</v>
       </c>
       <c r="G21" t="n">
-        <v>0.08554200000000001</v>
+        <v>0.776633</v>
       </c>
       <c r="H21" t="n">
-        <v>0.243057</v>
+        <v>1.370963</v>
       </c>
       <c r="I21" t="n">
-        <v>0.089675</v>
+        <v>0.982088</v>
       </c>
       <c r="J21" t="n">
-        <v>0.294889</v>
+        <v>0.809154</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.733225</v>
       </c>
     </row>
     <row r="22">
@@ -1166,32 +1197,33 @@
           <t>化學工業右下上市</t>
         </is>
       </c>
-      <c r="B22" t="n">
-        <v>207.753629</v>
-      </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>168.434019</v>
+        <v>167.232837</v>
       </c>
       <c r="D22" t="n">
-        <v>231.748497</v>
+        <v>229.714255</v>
       </c>
       <c r="E22" t="n">
-        <v>142.264442</v>
+        <v>140.860996</v>
       </c>
       <c r="F22" t="n">
-        <v>386.917159</v>
+        <v>236.819083</v>
       </c>
       <c r="G22" t="n">
-        <v>174.154573</v>
+        <v>148.261332</v>
       </c>
       <c r="H22" t="n">
-        <v>137.624827</v>
+        <v>101.718433</v>
       </c>
       <c r="I22" t="n">
-        <v>104.854825</v>
+        <v>85.72914299999999</v>
       </c>
       <c r="J22" t="n">
-        <v>196.898298</v>
+        <v>84.990664</v>
+      </c>
+      <c r="K22" t="n">
+        <v>183.488406</v>
       </c>
     </row>
     <row r="23">
@@ -1200,32 +1232,33 @@
           <t>化學工業右下上櫃</t>
         </is>
       </c>
-      <c r="B23" t="n">
-        <v>0.309473</v>
-      </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
-        <v>0.326445</v>
+        <v>0.15126</v>
       </c>
       <c r="D23" t="n">
-        <v>0.251038</v>
+        <v>0.13601</v>
       </c>
       <c r="E23" t="n">
-        <v>0.425178</v>
+        <v>0.08731899999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>0.302992</v>
+        <v>0.102565</v>
       </c>
       <c r="G23" t="n">
-        <v>0.75597</v>
+        <v>0.009887999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>0.639278</v>
+        <v>0.009261</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2668</v>
+        <v>0.008884</v>
       </c>
       <c r="J23" t="n">
-        <v>0.024437</v>
+        <v>0.025501</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.025438</v>
       </c>
     </row>
     <row r="24">
@@ -1234,32 +1267,33 @@
           <t>化學工業平上市</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>785.238852</v>
-      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
-        <v>649.440349</v>
+        <v>923.704505</v>
       </c>
       <c r="D24" t="n">
-        <v>1410.923435</v>
+        <v>1240.716458</v>
       </c>
       <c r="E24" t="n">
-        <v>996.066389</v>
+        <v>726.253564</v>
       </c>
       <c r="F24" t="n">
-        <v>749.073516</v>
+        <v>549.482212</v>
       </c>
       <c r="G24" t="n">
-        <v>1063.384379</v>
+        <v>405.298512</v>
       </c>
       <c r="H24" t="n">
-        <v>1014.584463</v>
+        <v>665.230258</v>
       </c>
       <c r="I24" t="n">
-        <v>1574.244514</v>
+        <v>663.405157</v>
       </c>
       <c r="J24" t="n">
-        <v>723.970323</v>
+        <v>466.581595</v>
+      </c>
+      <c r="K24" t="n">
+        <v>400.513666</v>
       </c>
     </row>
     <row r="25">
@@ -1268,32 +1302,33 @@
           <t>化學工業平上櫃</t>
         </is>
       </c>
-      <c r="B25" t="n">
-        <v>0.052941</v>
-      </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
-        <v>0.087949</v>
+        <v>0.213018</v>
       </c>
       <c r="D25" t="n">
-        <v>0.053762</v>
+        <v>0.137309</v>
       </c>
       <c r="E25" t="n">
-        <v>0.049746</v>
+        <v>0.361953</v>
       </c>
       <c r="F25" t="n">
-        <v>0.178292</v>
+        <v>0.254951</v>
       </c>
       <c r="G25" t="n">
-        <v>0.693905</v>
+        <v>0.748896</v>
       </c>
       <c r="H25" t="n">
-        <v>1.141352</v>
+        <v>0.643463</v>
       </c>
       <c r="I25" t="n">
-        <v>0.89294</v>
+        <v>0.258443</v>
       </c>
       <c r="J25" t="n">
-        <v>2.197642</v>
+        <v>1.682313</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.771212</v>
       </c>
     </row>
     <row r="26">
@@ -1302,32 +1337,33 @@
           <t>半導體業右上上市</t>
         </is>
       </c>
-      <c r="B26" t="n">
-        <v>418807.723536</v>
-      </c>
+      <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>298551.554095</v>
+        <v>314316.912468</v>
       </c>
       <c r="D26" t="n">
-        <v>380269.750197</v>
+        <v>395429.300042</v>
       </c>
       <c r="E26" t="n">
-        <v>301340.906928</v>
+        <v>317275.928486</v>
       </c>
       <c r="F26" t="n">
-        <v>270822.403683</v>
+        <v>280606.246302</v>
       </c>
       <c r="G26" t="n">
-        <v>285493.879323</v>
+        <v>290934.556133</v>
       </c>
       <c r="H26" t="n">
-        <v>307574.643404</v>
+        <v>315316.585395</v>
       </c>
       <c r="I26" t="n">
-        <v>229451.108898</v>
+        <v>234444.436922</v>
       </c>
       <c r="J26" t="n">
-        <v>238507.170435</v>
+        <v>259890.34109</v>
+      </c>
+      <c r="K26" t="n">
+        <v>373373.997905</v>
       </c>
     </row>
     <row r="27">
@@ -1336,32 +1372,33 @@
           <t>半導體業右上上櫃</t>
         </is>
       </c>
-      <c r="B27" t="n">
-        <v>128.575994</v>
-      </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
-        <v>88.41125700000001</v>
+        <v>96.131592</v>
       </c>
       <c r="D27" t="n">
-        <v>155.644348</v>
+        <v>154.880758</v>
       </c>
       <c r="E27" t="n">
-        <v>154.61431</v>
+        <v>156.149125</v>
       </c>
       <c r="F27" t="n">
-        <v>90.226675</v>
+        <v>95.266611</v>
       </c>
       <c r="G27" t="n">
-        <v>79.75349</v>
+        <v>83.360472</v>
       </c>
       <c r="H27" t="n">
-        <v>123.720141</v>
+        <v>135.079701</v>
       </c>
       <c r="I27" t="n">
-        <v>128.044739</v>
+        <v>140.272935</v>
       </c>
       <c r="J27" t="n">
-        <v>116.435808</v>
+        <v>123.430892</v>
+      </c>
+      <c r="K27" t="n">
+        <v>149.827761</v>
       </c>
     </row>
     <row r="28">
@@ -1370,32 +1407,33 @@
           <t>半導體業右下上市</t>
         </is>
       </c>
-      <c r="B28" t="n">
-        <v>2197.74669</v>
-      </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
-        <v>814.063477</v>
+        <v>746.338177</v>
       </c>
       <c r="D28" t="n">
-        <v>3777.169563</v>
+        <v>996.282696</v>
       </c>
       <c r="E28" t="n">
-        <v>982.275547</v>
+        <v>956.627656</v>
       </c>
       <c r="F28" t="n">
-        <v>1190.705722</v>
+        <v>832.405709</v>
       </c>
       <c r="G28" t="n">
-        <v>1215.495016</v>
+        <v>991.0951669999999</v>
       </c>
       <c r="H28" t="n">
-        <v>1089.004733</v>
+        <v>1104.460706</v>
       </c>
       <c r="I28" t="n">
-        <v>957.057733</v>
+        <v>1153.921524</v>
       </c>
       <c r="J28" t="n">
-        <v>621.03682</v>
+        <v>705.477575</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1021.386874</v>
       </c>
     </row>
     <row r="29">
@@ -1405,31 +1443,34 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.431211</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>1.084483</v>
+        <v>1.030227</v>
       </c>
       <c r="D29" t="n">
-        <v>1.655492</v>
+        <v>1.869736</v>
       </c>
       <c r="E29" t="n">
-        <v>1.559106</v>
+        <v>1.269868</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8938</v>
+        <v>0.871218</v>
       </c>
       <c r="G29" t="n">
-        <v>3.88121825</v>
+        <v>3.00092325</v>
       </c>
       <c r="H29" t="n">
-        <v>2.94116</v>
+        <v>1.752935</v>
       </c>
       <c r="I29" t="n">
-        <v>3.985883</v>
+        <v>3.038022</v>
       </c>
       <c r="J29" t="n">
-        <v>4.884573</v>
+        <v>2.423676</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.372169</v>
       </c>
     </row>
     <row r="30">
@@ -1438,32 +1479,33 @@
           <t>半導體業平上市</t>
         </is>
       </c>
-      <c r="B30" t="n">
-        <v>48691.187002</v>
-      </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>24145.954311</v>
+        <v>7627.062397</v>
       </c>
       <c r="D30" t="n">
-        <v>30973.84923</v>
+        <v>15829.831633</v>
       </c>
       <c r="E30" t="n">
-        <v>28779.054187</v>
+        <v>12092.675741</v>
       </c>
       <c r="F30" t="n">
-        <v>18447.333554</v>
+        <v>8574.452869999999</v>
       </c>
       <c r="G30" t="n">
-        <v>16209.80837</v>
+        <v>10705.973014</v>
       </c>
       <c r="H30" t="n">
-        <v>18913.857904</v>
+        <v>10741.106846</v>
       </c>
       <c r="I30" t="n">
-        <v>12874.398476</v>
+        <v>7129.630298</v>
       </c>
       <c r="J30" t="n">
-        <v>16711.163602</v>
+        <v>3639.240211</v>
+      </c>
+      <c r="K30" t="n">
+        <v>5598.691249</v>
       </c>
     </row>
     <row r="31">
@@ -1472,32 +1514,33 @@
           <t>半導體業平上櫃</t>
         </is>
       </c>
-      <c r="B31" t="n">
-        <v>12.194661</v>
-      </c>
+      <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
-        <v>11.973196</v>
+        <v>1.052763</v>
       </c>
       <c r="D31" t="n">
-        <v>8.887313000000001</v>
+        <v>1.562743</v>
       </c>
       <c r="E31" t="n">
-        <v>7.38079</v>
+        <v>0.867654</v>
       </c>
       <c r="F31" t="n">
-        <v>9.350882</v>
+        <v>0.350632</v>
       </c>
       <c r="G31" t="n">
-        <v>8.927008000000001</v>
+        <v>1.030853</v>
       </c>
       <c r="H31" t="n">
-        <v>16.387354</v>
+        <v>1.564575</v>
       </c>
       <c r="I31" t="n">
-        <v>14.89894</v>
+        <v>1.136972</v>
       </c>
       <c r="J31" t="n">
-        <v>10.004281</v>
+        <v>2.592812</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1.514762</v>
       </c>
     </row>
     <row r="32">
@@ -1506,32 +1549,33 @@
           <t>塑膠工業右上上市</t>
         </is>
       </c>
-      <c r="B32" t="n">
-        <v>24775.24986</v>
-      </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>14556.142562</v>
+        <v>14563.367158</v>
       </c>
       <c r="D32" t="n">
-        <v>20403.743481</v>
+        <v>20411.893102</v>
       </c>
       <c r="E32" t="n">
-        <v>15904.156976</v>
+        <v>15919.198001</v>
       </c>
       <c r="F32" t="n">
-        <v>18414.422521</v>
+        <v>18456.769403</v>
       </c>
       <c r="G32" t="n">
-        <v>23993.723144</v>
+        <v>24003.311254</v>
       </c>
       <c r="H32" t="n">
-        <v>38398.115906</v>
+        <v>38446.327975</v>
       </c>
       <c r="I32" t="n">
-        <v>17613.517817</v>
+        <v>17643.26033</v>
       </c>
       <c r="J32" t="n">
-        <v>17741.971142</v>
+        <v>17880.73366</v>
+      </c>
+      <c r="K32" t="n">
+        <v>29591.396337</v>
       </c>
     </row>
     <row r="33">
@@ -1540,32 +1584,33 @@
           <t>塑膠工業右下上市</t>
         </is>
       </c>
-      <c r="B33" t="n">
-        <v>86.327966</v>
-      </c>
+      <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
-        <v>38.665136</v>
+        <v>16.553126</v>
       </c>
       <c r="D33" t="n">
-        <v>43.737029</v>
+        <v>17.292945</v>
       </c>
       <c r="E33" t="n">
-        <v>26.41518</v>
+        <v>20.141526</v>
       </c>
       <c r="F33" t="n">
-        <v>21.393921</v>
+        <v>14.711618</v>
       </c>
       <c r="G33" t="n">
-        <v>39.355459</v>
+        <v>29.039463</v>
       </c>
       <c r="H33" t="n">
-        <v>34.904345</v>
+        <v>37.351237</v>
       </c>
       <c r="I33" t="n">
-        <v>28.912333</v>
+        <v>22.338546</v>
       </c>
       <c r="J33" t="n">
-        <v>15.643569</v>
+        <v>17.20861</v>
+      </c>
+      <c r="K33" t="n">
+        <v>43.752679</v>
       </c>
     </row>
     <row r="34">
@@ -1574,32 +1619,33 @@
           <t>塑膠工業右下上櫃</t>
         </is>
       </c>
-      <c r="B34" t="n">
-        <v>0.029903</v>
-      </c>
+      <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
-        <v>0.020185</v>
+        <v>0.016873</v>
       </c>
       <c r="D34" t="n">
-        <v>0.02357733333333333</v>
+        <v>0.02010833333333333</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0225495</v>
+        <v>0.0145135</v>
       </c>
       <c r="F34" t="n">
-        <v>0.043256</v>
+        <v>0.041813</v>
       </c>
       <c r="G34" t="n">
-        <v>0.028786</v>
+        <v>0.028097</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0244545</v>
+        <v>0.0236345</v>
       </c>
       <c r="I34" t="n">
-        <v>0.029761</v>
+        <v>0.029495</v>
       </c>
       <c r="J34" t="n">
-        <v>0.016262</v>
+        <v>0.015748</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.0384175</v>
       </c>
     </row>
     <row r="35">
@@ -1608,32 +1654,33 @@
           <t>塑膠工業平上市</t>
         </is>
       </c>
-      <c r="B35" t="n">
-        <v>80.799667</v>
-      </c>
+      <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
-        <v>45.4635</v>
+        <v>60.350914</v>
       </c>
       <c r="D35" t="n">
-        <v>51.638723</v>
+        <v>69.93318600000001</v>
       </c>
       <c r="E35" t="n">
-        <v>78.35193200000001</v>
+        <v>69.58456099999999</v>
       </c>
       <c r="F35" t="n">
-        <v>86.148461</v>
+        <v>50.483882</v>
       </c>
       <c r="G35" t="n">
-        <v>105.869253</v>
+        <v>106.597139</v>
       </c>
       <c r="H35" t="n">
-        <v>159.785773</v>
+        <v>109.126812</v>
       </c>
       <c r="I35" t="n">
-        <v>84.431816</v>
+        <v>61.26309</v>
       </c>
       <c r="J35" t="n">
-        <v>244.212676</v>
+        <v>103.885117</v>
+      </c>
+      <c r="K35" t="n">
+        <v>48.532115</v>
       </c>
     </row>
     <row r="36">
@@ -1642,17 +1689,34 @@
           <t>塑膠工業平上櫃</t>
         </is>
       </c>
-      <c r="B36" t="n">
-        <v>0.00022125</v>
-      </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="n">
+        <v>0.003312</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.003469</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.008036</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.001443</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.0006890000000000001</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.00082</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.000266</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.000514</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.000893</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -1660,26 +1724,22 @@
           <t>居家生活右上上櫃</t>
         </is>
       </c>
-      <c r="B37" t="n">
-        <v>0.000165</v>
-      </c>
-      <c r="C37" t="n">
-        <v>0.000522</v>
-      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="n">
-        <v>0.0013</v>
+        <v>0.001312</v>
       </c>
       <c r="E37" t="n">
-        <v>0.004544</v>
+        <v>0.005049</v>
       </c>
       <c r="F37" t="n">
-        <v>0.002171</v>
+        <v>0.002355</v>
       </c>
       <c r="G37" t="n">
         <v>0.000613</v>
       </c>
       <c r="H37" t="n">
-        <v>0.000906</v>
+        <v>0.001147</v>
       </c>
       <c r="I37" t="n">
         <v>0.000283</v>
@@ -1687,6 +1747,9 @@
       <c r="J37" t="n">
         <v>0.001482</v>
       </c>
+      <c r="K37" t="n">
+        <v>0.00025</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -1694,32 +1757,33 @@
           <t>居家生活右下上市</t>
         </is>
       </c>
-      <c r="B38" t="n">
-        <v>44.767089</v>
-      </c>
+      <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>29.50069</v>
+        <v>315.166125</v>
       </c>
       <c r="D38" t="n">
         <v>37.008341</v>
       </c>
       <c r="E38" t="n">
-        <v>22.73136</v>
+        <v>110.308606</v>
       </c>
       <c r="F38" t="n">
-        <v>20.023105</v>
+        <v>84.51718099999999</v>
       </c>
       <c r="G38" t="n">
-        <v>29.842921</v>
+        <v>225.681646</v>
       </c>
       <c r="H38" t="n">
-        <v>27.947611</v>
+        <v>157.080028</v>
       </c>
       <c r="I38" t="n">
-        <v>20.812951</v>
+        <v>89.773652</v>
       </c>
       <c r="J38" t="n">
-        <v>28.538201</v>
+        <v>85.743891</v>
+      </c>
+      <c r="K38" t="n">
+        <v>94.456698</v>
       </c>
     </row>
     <row r="39">
@@ -1728,32 +1792,33 @@
           <t>居家生活右下上櫃</t>
         </is>
       </c>
-      <c r="B39" t="n">
-        <v>0.443066</v>
-      </c>
+      <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
-        <v>0.376446</v>
+        <v>0.37386</v>
       </c>
       <c r="D39" t="n">
-        <v>0.541181</v>
+        <v>0.538758</v>
       </c>
       <c r="E39" t="n">
-        <v>0.367615</v>
+        <v>0.366794</v>
       </c>
       <c r="F39" t="n">
-        <v>0.55962575</v>
+        <v>0.55957575</v>
       </c>
       <c r="G39" t="n">
-        <v>0.3257003333333333</v>
+        <v>0.3252453333333333</v>
       </c>
       <c r="H39" t="n">
-        <v>0.3575955</v>
+        <v>0.3573575</v>
       </c>
       <c r="I39" t="n">
-        <v>0.2460553333333333</v>
+        <v>0.245567</v>
       </c>
       <c r="J39" t="n">
-        <v>0.312833</v>
+        <v>0.307899</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.226301</v>
       </c>
     </row>
     <row r="40">
@@ -1762,33 +1827,18 @@
           <t>居家生活平上市</t>
         </is>
       </c>
-      <c r="B40" t="n">
-        <v>406.235329</v>
-      </c>
-      <c r="C40" t="n">
-        <v>285.665435</v>
-      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="n">
         <v>144.489178</v>
       </c>
-      <c r="E40" t="n">
-        <v>87.577246</v>
-      </c>
-      <c r="F40" t="n">
-        <v>64.49407600000001</v>
-      </c>
-      <c r="G40" t="n">
-        <v>195.838725</v>
-      </c>
-      <c r="H40" t="n">
-        <v>129.132417</v>
-      </c>
-      <c r="I40" t="n">
-        <v>68.960701</v>
-      </c>
-      <c r="J40" t="n">
-        <v>57.20569</v>
-      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
@@ -1796,32 +1846,33 @@
           <t>居家生活平上櫃</t>
         </is>
       </c>
-      <c r="B41" t="n">
-        <v>0.002518</v>
-      </c>
+      <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
-        <v>0.007408</v>
+        <v>0.010516</v>
       </c>
       <c r="D41" t="n">
-        <v>0.002442</v>
+        <v>0.004853</v>
       </c>
       <c r="E41" t="n">
-        <v>0.001043</v>
+        <v>0.001359</v>
       </c>
       <c r="F41" t="n">
-        <v>0.00075</v>
+        <v>0.000616</v>
       </c>
       <c r="G41" t="n">
-        <v>0.001274</v>
+        <v>0.001729</v>
       </c>
       <c r="H41" t="n">
-        <v>0.000901</v>
+        <v>0.000898</v>
       </c>
       <c r="I41" t="n">
-        <v>0.004289</v>
+        <v>0.004777333333333333</v>
       </c>
       <c r="J41" t="n">
-        <v>0.003008</v>
+        <v>0.007941999999999999</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.001168</v>
       </c>
     </row>
     <row r="42">
@@ -1830,32 +1881,33 @@
           <t>建材營造右上上市</t>
         </is>
       </c>
-      <c r="B42" t="n">
-        <v>2018.405348</v>
-      </c>
+      <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>1098.044722</v>
+        <v>1006.339109</v>
       </c>
       <c r="D42" t="n">
-        <v>1311.540773</v>
+        <v>1205.666688</v>
       </c>
       <c r="E42" t="n">
-        <v>144.487166</v>
+        <v>102.798544</v>
       </c>
       <c r="F42" t="n">
-        <v>149.45803</v>
+        <v>111.02575</v>
       </c>
       <c r="G42" t="n">
-        <v>124.981634</v>
+        <v>76.98213</v>
       </c>
       <c r="H42" t="n">
-        <v>201.107528</v>
+        <v>130.417564</v>
       </c>
       <c r="I42" t="n">
-        <v>147.807027</v>
+        <v>87.222176</v>
       </c>
       <c r="J42" t="n">
-        <v>164.04647</v>
+        <v>110.783978</v>
+      </c>
+      <c r="K42" t="n">
+        <v>152.611407</v>
       </c>
     </row>
     <row r="43">
@@ -1864,32 +1916,33 @@
           <t>建材營造右上上櫃</t>
         </is>
       </c>
-      <c r="B43" t="n">
-        <v>0.016124</v>
-      </c>
+      <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
-        <v>0.007722</v>
+        <v>0.008662</v>
       </c>
       <c r="D43" t="n">
-        <v>0.008525</v>
+        <v>0.019533</v>
       </c>
       <c r="E43" t="n">
-        <v>0.008455000000000001</v>
+        <v>0.015812</v>
       </c>
       <c r="F43" t="n">
-        <v>0.007346</v>
+        <v>0.015308</v>
       </c>
       <c r="G43" t="n">
-        <v>0.012669</v>
+        <v>0.012671</v>
       </c>
       <c r="H43" t="n">
-        <v>0.015847</v>
+        <v>0.016945</v>
       </c>
       <c r="I43" t="n">
-        <v>0.020326</v>
+        <v>0.022928</v>
       </c>
       <c r="J43" t="n">
-        <v>0.01373125</v>
+        <v>0.014092</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.005928</v>
       </c>
     </row>
     <row r="44">
@@ -1898,32 +1951,33 @@
           <t>建材營造右下上市</t>
         </is>
       </c>
-      <c r="B44" t="n">
-        <v>1854.204051</v>
-      </c>
+      <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>707.2115659999999</v>
+        <v>761.269444</v>
       </c>
       <c r="D44" t="n">
-        <v>457.357728</v>
+        <v>514.0784200000001</v>
       </c>
       <c r="E44" t="n">
-        <v>597.730444</v>
+        <v>2484.126006</v>
       </c>
       <c r="F44" t="n">
-        <v>428.069404</v>
+        <v>930.419503</v>
       </c>
       <c r="G44" t="n">
-        <v>1042.3501</v>
+        <v>1047.499389</v>
       </c>
       <c r="H44" t="n">
-        <v>1117.33762</v>
+        <v>1121.877582</v>
       </c>
       <c r="I44" t="n">
-        <v>829.348561</v>
+        <v>832.779625</v>
       </c>
       <c r="J44" t="n">
-        <v>930.680146</v>
+        <v>939.653986</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1444.134285</v>
       </c>
     </row>
     <row r="45">
@@ -1933,31 +1987,34 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.215736</v>
+        <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>0.09563000000000001</v>
+        <v>0.119496</v>
       </c>
       <c r="D45" t="n">
-        <v>0.108894</v>
+        <v>0.127281</v>
       </c>
       <c r="E45" t="n">
-        <v>0.076583</v>
+        <v>0.094918</v>
       </c>
       <c r="F45" t="n">
-        <v>0.06238</v>
+        <v>0.060662</v>
       </c>
       <c r="G45" t="n">
-        <v>0.054294</v>
+        <v>0.048336</v>
       </c>
       <c r="H45" t="n">
-        <v>0.050976</v>
+        <v>0.053015</v>
       </c>
       <c r="I45" t="n">
-        <v>0.03979466666666667</v>
+        <v>0.03701266666666667</v>
       </c>
       <c r="J45" t="n">
-        <v>0.044147</v>
+        <v>0.060752</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.06973600000000001</v>
       </c>
     </row>
     <row r="46">
@@ -1966,32 +2023,33 @@
           <t>建材營造平上市</t>
         </is>
       </c>
-      <c r="B46" t="n">
-        <v>123.388588</v>
-      </c>
+      <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>95.518418</v>
+        <v>133.166153</v>
       </c>
       <c r="D46" t="n">
-        <v>105.337666</v>
+        <v>154.491059</v>
       </c>
       <c r="E46" t="n">
-        <v>2054.58486</v>
+        <v>209.87792</v>
       </c>
       <c r="F46" t="n">
-        <v>581.465077</v>
+        <v>117.547258</v>
       </c>
       <c r="G46" t="n">
-        <v>36.673821</v>
+        <v>79.524036</v>
       </c>
       <c r="H46" t="n">
-        <v>53.262782</v>
+        <v>119.412784</v>
       </c>
       <c r="I46" t="n">
-        <v>166.435499</v>
+        <v>223.589286</v>
       </c>
       <c r="J46" t="n">
-        <v>76.116998</v>
+        <v>125.055751</v>
+      </c>
+      <c r="K46" t="n">
+        <v>148.370581</v>
       </c>
     </row>
     <row r="47">
@@ -2000,32 +2058,33 @@
           <t>建材營造平上櫃</t>
         </is>
       </c>
-      <c r="B47" t="n">
-        <v>0.165724</v>
-      </c>
+      <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
-        <v>0.047342</v>
+        <v>0.006034</v>
       </c>
       <c r="D47" t="n">
-        <v>0.036039</v>
+        <v>0.002899</v>
       </c>
       <c r="E47" t="n">
-        <v>0.032516</v>
+        <v>0.003659</v>
       </c>
       <c r="F47" t="n">
-        <v>0.022415</v>
+        <v>0.001731</v>
       </c>
       <c r="G47" t="n">
-        <v>0.010698</v>
+        <v>0.004705</v>
       </c>
       <c r="H47" t="n">
-        <v>0.013407</v>
+        <v>0.004307</v>
       </c>
       <c r="I47" t="n">
-        <v>0.026788</v>
+        <v>0.014848</v>
       </c>
       <c r="J47" t="n">
-        <v>0.023503</v>
+        <v>0.00322425</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0.019664</v>
       </c>
     </row>
     <row r="48">
@@ -2034,32 +2093,33 @@
           <t>數位雲端右上上市</t>
         </is>
       </c>
-      <c r="B48" t="n">
-        <v>292.09829</v>
-      </c>
+      <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
-        <v>184.730686</v>
+        <v>49.21963</v>
       </c>
       <c r="D48" t="n">
-        <v>524.292661</v>
+        <v>502.753895</v>
       </c>
       <c r="E48" t="n">
-        <v>232.139303</v>
+        <v>229.721265</v>
       </c>
       <c r="F48" t="n">
-        <v>212.845719</v>
+        <v>201.553671</v>
       </c>
       <c r="G48" t="n">
-        <v>131.591225</v>
+        <v>123.789134</v>
       </c>
       <c r="H48" t="n">
-        <v>273.926956</v>
+        <v>88.29381600000001</v>
       </c>
       <c r="I48" t="n">
-        <v>79.373986</v>
+        <v>61.638603</v>
       </c>
       <c r="J48" t="n">
-        <v>81.745813</v>
+        <v>71.518085</v>
+      </c>
+      <c r="K48" t="n">
+        <v>62.462198</v>
       </c>
     </row>
     <row r="49">
@@ -2068,32 +2128,33 @@
           <t>數位雲端右上上櫃</t>
         </is>
       </c>
-      <c r="B49" t="n">
-        <v>0.5358540000000001</v>
-      </c>
+      <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
-        <v>0.338427</v>
+        <v>0.338035</v>
       </c>
       <c r="D49" t="n">
-        <v>0.324899</v>
+        <v>0.324127</v>
       </c>
       <c r="E49" t="n">
-        <v>0.506584</v>
+        <v>0.506271</v>
       </c>
       <c r="F49" t="n">
-        <v>0.218607</v>
+        <v>0.223265</v>
       </c>
       <c r="G49" t="n">
-        <v>0.179389</v>
+        <v>0.166084</v>
       </c>
       <c r="H49" t="n">
-        <v>0.296095</v>
+        <v>0.244618</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1936893333333334</v>
+        <v>0.1803</v>
       </c>
       <c r="J49" t="n">
-        <v>0.121387</v>
+        <v>0.115223</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0.19295</v>
       </c>
     </row>
     <row r="50">
@@ -2102,32 +2163,33 @@
           <t>數位雲端右下上市</t>
         </is>
       </c>
-      <c r="B50" t="n">
-        <v>29.283771</v>
-      </c>
+      <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
-        <v>22.149554</v>
+        <v>133.666363</v>
       </c>
       <c r="D50" t="n">
-        <v>25.923961</v>
+        <v>111.166761</v>
       </c>
       <c r="E50" t="n">
-        <v>25.247635</v>
+        <v>53.080761</v>
       </c>
       <c r="F50" t="n">
-        <v>22.50859</v>
+        <v>82.262708</v>
       </c>
       <c r="G50" t="n">
-        <v>28.703929</v>
+        <v>65.905101</v>
       </c>
       <c r="H50" t="n">
-        <v>24.480949</v>
+        <v>58.653519</v>
       </c>
       <c r="I50" t="n">
-        <v>28.726985</v>
+        <v>58.105474</v>
       </c>
       <c r="J50" t="n">
-        <v>38.646655</v>
+        <v>50.751367</v>
+      </c>
+      <c r="K50" t="n">
+        <v>106.150777</v>
       </c>
     </row>
     <row r="51">
@@ -2137,31 +2199,34 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.399932</v>
+        <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>0.287752</v>
+        <v>0.28790625</v>
       </c>
       <c r="D51" t="n">
-        <v>0.205242</v>
+        <v>0.2053863333333333</v>
       </c>
       <c r="E51" t="n">
-        <v>0.179853</v>
+        <v>0.179874</v>
       </c>
       <c r="F51" t="n">
-        <v>0.09177299999999999</v>
+        <v>0.205574</v>
       </c>
       <c r="G51" t="n">
-        <v>0.11663</v>
+        <v>0.267687</v>
       </c>
       <c r="H51" t="n">
-        <v>0.115867</v>
+        <v>0.205313</v>
       </c>
       <c r="I51" t="n">
-        <v>0.173237</v>
+        <v>0.232625</v>
       </c>
       <c r="J51" t="n">
-        <v>0.181664</v>
+        <v>0.210537</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0.25565475</v>
       </c>
     </row>
     <row r="52">
@@ -2170,32 +2235,33 @@
           <t>數位雲端平上市</t>
         </is>
       </c>
-      <c r="B52" t="n">
-        <v>175.29473</v>
-      </c>
+      <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>117.378274</v>
+        <v>141.372521</v>
       </c>
       <c r="D52" t="n">
-        <v>189.304916</v>
+        <v>125.600882</v>
       </c>
       <c r="E52" t="n">
-        <v>142.973795</v>
+        <v>117.558707</v>
       </c>
       <c r="F52" t="n">
-        <v>117.038726</v>
+        <v>68.576656</v>
       </c>
       <c r="G52" t="n">
-        <v>117.851939</v>
+        <v>88.45285800000001</v>
       </c>
       <c r="H52" t="n">
-        <v>132.340216</v>
+        <v>283.800786</v>
       </c>
       <c r="I52" t="n">
-        <v>83.747483</v>
+        <v>72.104377</v>
       </c>
       <c r="J52" t="n">
-        <v>60.660386</v>
+        <v>58.783402</v>
+      </c>
+      <c r="K52" t="n">
+        <v>133.565777</v>
       </c>
     </row>
     <row r="53">
@@ -2204,32 +2270,25 @@
           <t>數位雲端平上櫃</t>
         </is>
       </c>
-      <c r="B53" t="n">
-        <v>0.000124</v>
-      </c>
-      <c r="C53" t="n">
-        <v>0.00059625</v>
-      </c>
-      <c r="D53" t="n">
-        <v>0.001018333333333333</v>
-      </c>
-      <c r="E53" t="n">
-        <v>0.000483</v>
-      </c>
-      <c r="F53" t="n">
-        <v>0.118701</v>
-      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
-        <v>0.152504</v>
+        <v>0.013305</v>
       </c>
       <c r="H53" t="n">
-        <v>0.093373</v>
+        <v>0.053744</v>
       </c>
       <c r="I53" t="n">
-        <v>0.074028</v>
+        <v>0.01615433333333333</v>
       </c>
       <c r="J53" t="n">
-        <v>0.036497</v>
+        <v>0.007483</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0.005895</v>
       </c>
     </row>
     <row r="54">
@@ -2242,12 +2301,8 @@
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
-      <c r="F54" t="n">
-        <v>4.373877</v>
-      </c>
-      <c r="G54" t="n">
-        <v>2.718566</v>
-      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
         <v>1.632479</v>
       </c>
@@ -2257,6 +2312,9 @@
       <c r="J54" t="n">
         <v>2.438659</v>
       </c>
+      <c r="K54" t="n">
+        <v>1.087361</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
@@ -2265,31 +2323,34 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.060443</v>
+        <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>0.87181725</v>
+        <v>0.8757652500000001</v>
       </c>
       <c r="D55" t="n">
-        <v>0.057446</v>
+        <v>0.897614</v>
       </c>
       <c r="E55" t="n">
-        <v>0.0641065</v>
+        <v>0.6511585</v>
       </c>
       <c r="F55" t="n">
-        <v>0.0408735</v>
+        <v>0.0456975</v>
       </c>
       <c r="G55" t="n">
-        <v>0.06168375</v>
+        <v>0.06317775</v>
       </c>
       <c r="H55" t="n">
-        <v>0.073361</v>
+        <v>0.06902700000000001</v>
       </c>
       <c r="I55" t="n">
-        <v>0.049902</v>
+        <v>0.052756</v>
       </c>
       <c r="J55" t="n">
-        <v>0.05330483333333334</v>
+        <v>0.05194683333333334</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0.068241</v>
       </c>
     </row>
     <row r="56">
@@ -2298,32 +2359,33 @@
           <t>文化創意業平上櫃</t>
         </is>
       </c>
-      <c r="B56" t="n">
-        <v>3.036963666666666</v>
-      </c>
+      <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>0.016009</v>
+        <v>0.010959</v>
       </c>
       <c r="D56" t="n">
-        <v>0.853862</v>
+        <v>0.011212</v>
       </c>
       <c r="E56" t="n">
-        <v>0.596025</v>
+        <v>0.00653</v>
       </c>
       <c r="F56" t="n">
-        <v>0.008586999999999999</v>
+        <v>4.376937</v>
       </c>
       <c r="G56" t="n">
-        <v>0.003479</v>
+        <v>2.718797</v>
       </c>
       <c r="H56" t="n">
-        <v>0.001894</v>
+        <v>0.001631</v>
       </c>
       <c r="I56" t="n">
-        <v>0.011794</v>
+        <v>0.007647</v>
       </c>
       <c r="J56" t="n">
-        <v>0.004545</v>
+        <v>0.003466</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0.000139</v>
       </c>
     </row>
     <row r="57">
@@ -2332,32 +2394,33 @@
           <t>橡膠工業右上上市</t>
         </is>
       </c>
-      <c r="B57" t="n">
-        <v>159.304336</v>
-      </c>
+      <c r="B57" t="inlineStr"/>
       <c r="C57" t="n">
-        <v>64.999539</v>
+        <v>62.371494</v>
       </c>
       <c r="D57" t="n">
-        <v>74.300687</v>
+        <v>72.667136</v>
       </c>
       <c r="E57" t="n">
-        <v>380.284936</v>
+        <v>134.681077</v>
       </c>
       <c r="F57" t="n">
-        <v>59.31454</v>
+        <v>53.153067</v>
       </c>
       <c r="G57" t="n">
-        <v>91.80184300000001</v>
+        <v>89.79392199999999</v>
       </c>
       <c r="H57" t="n">
-        <v>91.7514</v>
+        <v>90.27554600000001</v>
       </c>
       <c r="I57" t="n">
-        <v>64.15203700000001</v>
+        <v>63.309303</v>
       </c>
       <c r="J57" t="n">
-        <v>159.079605</v>
+        <v>156.840719</v>
+      </c>
+      <c r="K57" t="n">
+        <v>128.352831</v>
       </c>
     </row>
     <row r="58">
@@ -2367,16 +2430,16 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>448.313426</v>
+        <v>0</v>
       </c>
       <c r="C58" t="n">
-        <v>355.156177</v>
+        <v>342.115921</v>
       </c>
       <c r="D58" t="n">
-        <v>234.544684</v>
+        <v>199.233712</v>
       </c>
       <c r="E58" t="n">
-        <v>147.169752</v>
+        <v>150.43609</v>
       </c>
       <c r="F58" t="n">
         <v>116.233975</v>
@@ -2385,7 +2448,7 @@
         <v>165.105133</v>
       </c>
       <c r="H58" t="n">
-        <v>65.736844</v>
+        <v>219.105697</v>
       </c>
       <c r="I58" t="n">
         <v>172.168685</v>
@@ -2393,6 +2456,9 @@
       <c r="J58" t="n">
         <v>235.463628</v>
       </c>
+      <c r="K58" t="n">
+        <v>359.573597</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
@@ -2400,30 +2466,33 @@
           <t>橡膠工業平上市</t>
         </is>
       </c>
-      <c r="B59" t="n">
-        <v>3.999998</v>
-      </c>
+      <c r="B59" t="inlineStr"/>
       <c r="C59" t="n">
-        <v>0.567801</v>
+        <v>2.628045</v>
       </c>
       <c r="D59" t="n">
-        <v>0.448149</v>
-      </c>
-      <c r="E59" t="inlineStr"/>
+        <v>1.633551</v>
+      </c>
+      <c r="E59" t="n">
+        <v>4.689042</v>
+      </c>
       <c r="F59" t="n">
-        <v>110.326311</v>
+        <v>6.161473</v>
       </c>
       <c r="G59" t="n">
-        <v>67.582936</v>
+        <v>2.007921</v>
       </c>
       <c r="H59" t="n">
-        <v>210.676112</v>
+        <v>1.475854</v>
       </c>
       <c r="I59" t="n">
-        <v>34.688359</v>
+        <v>0.842734</v>
       </c>
       <c r="J59" t="n">
-        <v>20.422541</v>
+        <v>2.238886</v>
+      </c>
+      <c r="K59" t="n">
+        <v>2.490222</v>
       </c>
     </row>
     <row r="60">
@@ -2436,7 +2505,7 @@
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="n">
-        <v>3742.980955</v>
+        <v>3336.742112</v>
       </c>
       <c r="F60" t="n">
         <v>995.089243</v>
@@ -2445,7 +2514,7 @@
         <v>796.559063</v>
       </c>
       <c r="H60" t="n">
-        <v>2967.114292</v>
+        <v>2745.271403</v>
       </c>
       <c r="I60" t="n">
         <v>1412.587301</v>
@@ -2453,6 +2522,7 @@
       <c r="J60" t="n">
         <v>641.982484</v>
       </c>
+      <c r="K60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
@@ -2460,32 +2530,33 @@
           <t>水泥工業右下上市</t>
         </is>
       </c>
-      <c r="B61" t="n">
-        <v>45.964614</v>
-      </c>
+      <c r="B61" t="inlineStr"/>
       <c r="C61" t="n">
-        <v>23.146596</v>
+        <v>195.322445</v>
       </c>
       <c r="D61" t="n">
-        <v>23.131303</v>
+        <v>249.15688</v>
       </c>
       <c r="E61" t="n">
         <v>27.97068</v>
       </c>
       <c r="F61" t="n">
-        <v>23.890866</v>
+        <v>289.484283</v>
       </c>
       <c r="G61" t="n">
-        <v>36.108083</v>
+        <v>375.398434</v>
       </c>
       <c r="H61" t="n">
-        <v>25.533089</v>
+        <v>247.375978</v>
       </c>
       <c r="I61" t="n">
-        <v>24.011971</v>
+        <v>444.795927</v>
       </c>
       <c r="J61" t="n">
-        <v>17.212754</v>
+        <v>191.480706</v>
+      </c>
+      <c r="K61" t="n">
+        <v>201.274146</v>
       </c>
     </row>
     <row r="62">
@@ -2494,28 +2565,23 @@
           <t>水泥工業平上市</t>
         </is>
       </c>
-      <c r="B62" t="n">
-        <v>899.392789</v>
-      </c>
+      <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>472.762869</v>
+        <v>300.58702</v>
       </c>
       <c r="D62" t="n">
-        <v>949.079145</v>
-      </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="n">
-        <v>265.593417</v>
-      </c>
-      <c r="G62" t="n">
-        <v>339.290351</v>
-      </c>
+        <v>723.053568</v>
+      </c>
+      <c r="E62" t="n">
+        <v>406.238843</v>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" t="n">
-        <v>420.783956</v>
-      </c>
-      <c r="J62" t="n">
-        <v>174.267952</v>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="n">
+        <v>900.0369920000001</v>
       </c>
     </row>
     <row r="63">
@@ -2524,32 +2590,33 @@
           <t>汽車工業右上上市</t>
         </is>
       </c>
-      <c r="B63" t="n">
-        <v>1120.352731</v>
-      </c>
+      <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
-        <v>904.787535</v>
+        <v>811.908445</v>
       </c>
       <c r="D63" t="n">
-        <v>806.547029</v>
+        <v>736.432685</v>
       </c>
       <c r="E63" t="n">
-        <v>1669.721101</v>
+        <v>1376.488449</v>
       </c>
       <c r="F63" t="n">
-        <v>1001.153987</v>
+        <v>739.149461</v>
       </c>
       <c r="G63" t="n">
-        <v>1376.904598</v>
+        <v>1116.671849</v>
       </c>
       <c r="H63" t="n">
-        <v>2530.817868</v>
+        <v>2266.668821</v>
       </c>
       <c r="I63" t="n">
-        <v>894.608758</v>
+        <v>703.694757</v>
       </c>
       <c r="J63" t="n">
-        <v>1258.292474</v>
+        <v>1006.860223</v>
+      </c>
+      <c r="K63" t="n">
+        <v>1741.231331</v>
       </c>
     </row>
     <row r="64">
@@ -2559,31 +2626,34 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>442.698247</v>
+        <v>0</v>
       </c>
       <c r="C64" t="n">
-        <v>344.796209</v>
+        <v>427.38797</v>
       </c>
       <c r="D64" t="n">
-        <v>420.177898</v>
+        <v>486.394346</v>
       </c>
       <c r="E64" t="n">
-        <v>295.1171815</v>
+        <v>442.6297595</v>
       </c>
       <c r="F64" t="n">
-        <v>270.273582</v>
+        <v>418.980136</v>
       </c>
       <c r="G64" t="n">
-        <v>464.299762</v>
+        <v>481.024679</v>
       </c>
       <c r="H64" t="n">
-        <v>412.71605</v>
+        <v>639.632731</v>
       </c>
       <c r="I64" t="n">
-        <v>323.712412</v>
+        <v>482.415312</v>
       </c>
       <c r="J64" t="n">
-        <v>377.708464</v>
+        <v>672.995857</v>
+      </c>
+      <c r="K64" t="n">
+        <v>647.508377</v>
       </c>
     </row>
     <row r="65">
@@ -2592,32 +2662,33 @@
           <t>汽車工業平上市</t>
         </is>
       </c>
-      <c r="B65" t="n">
-        <v>594.089462</v>
-      </c>
+      <c r="B65" t="inlineStr"/>
       <c r="C65" t="n">
-        <v>279.300722</v>
+        <v>56.104699</v>
       </c>
       <c r="D65" t="n">
-        <v>269.349393</v>
+        <v>41.807062</v>
       </c>
       <c r="E65" t="n">
-        <v>199.842169</v>
+        <v>12.430991</v>
       </c>
       <c r="F65" t="n">
-        <v>208.878708</v>
+        <v>20.413591</v>
       </c>
       <c r="G65" t="n">
-        <v>198.14848</v>
+        <v>46.925254</v>
       </c>
       <c r="H65" t="n">
-        <v>284.679117</v>
+        <v>77.7034</v>
       </c>
       <c r="I65" t="n">
-        <v>244.890534</v>
+        <v>54.51133</v>
       </c>
       <c r="J65" t="n">
-        <v>391.432299</v>
+        <v>46.653295</v>
+      </c>
+      <c r="K65" t="n">
+        <v>79.294453</v>
       </c>
     </row>
     <row r="66">
@@ -2626,32 +2697,33 @@
           <t>油電燃氣業右上上市</t>
         </is>
       </c>
-      <c r="B66" t="n">
-        <v>2254.681543</v>
-      </c>
+      <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
-        <v>1540.168944</v>
+        <v>1540.444376</v>
       </c>
       <c r="D66" t="n">
-        <v>1563.610846</v>
+        <v>1564.428917</v>
       </c>
       <c r="E66" t="n">
-        <v>1120.951175</v>
+        <v>1207.454396</v>
       </c>
       <c r="F66" t="n">
         <v>1016.909933</v>
       </c>
       <c r="G66" t="n">
-        <v>3827.737724</v>
+        <v>3902.406555</v>
       </c>
       <c r="H66" t="n">
-        <v>3768.070051</v>
+        <v>3768.592343</v>
       </c>
       <c r="I66" t="n">
-        <v>2657.525003</v>
+        <v>2658.038261</v>
       </c>
       <c r="J66" t="n">
-        <v>3632.530573</v>
+        <v>3633.52439</v>
+      </c>
+      <c r="K66" t="n">
+        <v>2116.46865</v>
       </c>
     </row>
     <row r="67">
@@ -2660,14 +2732,12 @@
           <t>油電燃氣業右下上市</t>
         </is>
       </c>
-      <c r="B67" t="n">
-        <v>5.858001</v>
-      </c>
+      <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
-        <v>6.526438</v>
+        <v>6.854077</v>
       </c>
       <c r="D67" t="n">
-        <v>4.976994</v>
+        <v>5.220213</v>
       </c>
       <c r="E67" t="n">
         <v>4.671305</v>
@@ -2687,6 +2757,9 @@
       <c r="J67" t="n">
         <v>6.830817</v>
       </c>
+      <c r="K67" t="n">
+        <v>6.653482</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
@@ -2694,32 +2767,33 @@
           <t>油電燃氣業右下上櫃</t>
         </is>
       </c>
-      <c r="B68" t="n">
-        <v>0.004761</v>
-      </c>
+      <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>0.006872</v>
+        <v>0.012637</v>
       </c>
       <c r="D68" t="n">
-        <v>0.004074</v>
+        <v>0.006094</v>
       </c>
       <c r="E68" t="n">
-        <v>0.00622</v>
+        <v>0.010957</v>
       </c>
       <c r="F68" t="n">
-        <v>0.003165</v>
+        <v>0.015956</v>
       </c>
       <c r="G68" t="n">
-        <v>0.003294</v>
+        <v>0.007131</v>
       </c>
       <c r="H68" t="n">
-        <v>0.002846</v>
+        <v>0.013587</v>
       </c>
       <c r="I68" t="n">
-        <v>0.00394</v>
+        <v>0.004641</v>
       </c>
       <c r="J68" t="n">
-        <v>0.0022</v>
+        <v>0.003086</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0.007185</v>
       </c>
     </row>
     <row r="69">
@@ -2728,1514 +2802,1543 @@
           <t>油電燃氣業平上市</t>
         </is>
       </c>
-      <c r="B69" t="n">
-        <v>1.878674</v>
-      </c>
+      <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
-        <v>0.705493</v>
-      </c>
-      <c r="D69" t="n">
-        <v>1.06129</v>
-      </c>
+        <v>0.102422</v>
+      </c>
+      <c r="D69" t="inlineStr"/>
       <c r="E69" t="n">
-        <v>88.001926</v>
+        <v>1.498705</v>
       </c>
       <c r="F69" t="n">
         <v>0.416998</v>
       </c>
       <c r="G69" t="n">
-        <v>75.293695</v>
+        <v>0.624864</v>
       </c>
       <c r="H69" t="n">
-        <v>1.0206</v>
+        <v>0.498308</v>
       </c>
       <c r="I69" t="n">
-        <v>0.687299</v>
-      </c>
-      <c r="J69" t="n">
-        <v>0.993817</v>
-      </c>
+        <v>0.174041</v>
+      </c>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業平上櫃</t>
-        </is>
-      </c>
-      <c r="B70" t="n">
-        <v>0.001304</v>
-      </c>
+          <t>玻璃陶瓷右上上市</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
-        <v>0.005765</v>
+        <v>1201.340143</v>
       </c>
       <c r="D70" t="n">
-        <v>0.00202</v>
+        <v>1622.333522</v>
       </c>
       <c r="E70" t="n">
-        <v>0.004737</v>
+        <v>960.244794</v>
       </c>
       <c r="F70" t="n">
-        <v>0.012791</v>
+        <v>484.323571</v>
       </c>
       <c r="G70" t="n">
-        <v>0.003837</v>
+        <v>485.054299</v>
       </c>
       <c r="H70" t="n">
-        <v>0.010741</v>
+        <v>1474.814442</v>
       </c>
       <c r="I70" t="n">
-        <v>0.000701</v>
+        <v>944.915521</v>
       </c>
       <c r="J70" t="n">
-        <v>0.000886</v>
+        <v>745.171033</v>
+      </c>
+      <c r="K70" t="n">
+        <v>1425.148387</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷右上上市</t>
+          <t>玻璃陶瓷右下上市</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>128.349649</v>
+        <v>0</v>
       </c>
       <c r="C71" t="n">
-        <v>97.21011799999999</v>
+        <v>0.751342</v>
       </c>
       <c r="D71" t="n">
-        <v>180.249203</v>
+        <v>1.292641</v>
       </c>
       <c r="E71" t="n">
-        <v>308.760818</v>
+        <v>0.469083</v>
       </c>
       <c r="F71" t="n">
-        <v>336.767867</v>
+        <v>0.521244</v>
       </c>
       <c r="G71" t="n">
-        <v>1394.507219</v>
+        <v>0.500364</v>
       </c>
       <c r="H71" t="n">
-        <v>980.572891</v>
+        <v>1.209878</v>
       </c>
       <c r="I71" t="n">
-        <v>297.549161</v>
+        <v>2.726514</v>
       </c>
       <c r="J71" t="n">
-        <v>572.510755</v>
+        <v>0.8914299999999999</v>
+      </c>
+      <c r="K71" t="n">
+        <v>1.117833</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷右下上市</t>
-        </is>
-      </c>
-      <c r="B72" t="n">
-        <v>0.744646</v>
-      </c>
-      <c r="C72" t="n">
-        <v>0.751342</v>
-      </c>
-      <c r="D72" t="n">
-        <v>1.292641</v>
-      </c>
-      <c r="E72" t="n">
-        <v>0.469083</v>
-      </c>
+          <t>玻璃陶瓷平上市</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="n">
-        <v>0.521244</v>
+        <v>0.744384</v>
       </c>
       <c r="G72" t="n">
-        <v>0.500364</v>
+        <v>1.920693</v>
       </c>
       <c r="H72" t="n">
-        <v>1.209878</v>
+        <v>1.202745</v>
       </c>
       <c r="I72" t="n">
-        <v>2.726514</v>
+        <v>0.680389</v>
       </c>
       <c r="J72" t="n">
-        <v>0.8914299999999999</v>
+        <v>0.440229</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0.617168</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷平上市</t>
-        </is>
-      </c>
-      <c r="B73" t="n">
-        <v>1960.267031</v>
-      </c>
+          <t>生技醫療業右上上市</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
       <c r="C73" t="n">
-        <v>1169.464009</v>
+        <v>5530.108833</v>
       </c>
       <c r="D73" t="n">
-        <v>1593.900291</v>
+        <v>5999.20372</v>
       </c>
       <c r="E73" t="n">
-        <v>931.223287</v>
+        <v>5951.907732</v>
       </c>
       <c r="F73" t="n">
-        <v>464.349189</v>
+        <v>3086.100039</v>
       </c>
       <c r="G73" t="n">
-        <v>460.082038</v>
+        <v>3550.154512</v>
       </c>
       <c r="H73" t="n">
-        <v>1411.506215</v>
+        <v>4177.965948</v>
       </c>
       <c r="I73" t="n">
-        <v>913.096038</v>
+        <v>6361.363512</v>
       </c>
       <c r="J73" t="n">
-        <v>716.628303</v>
+        <v>2845.412558</v>
+      </c>
+      <c r="K73" t="n">
+        <v>3329.460827</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右上上市</t>
-        </is>
-      </c>
-      <c r="B74" t="n">
-        <v>16849.850547</v>
-      </c>
+          <t>生技醫療業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
       <c r="C74" t="n">
-        <v>4475.343683</v>
+        <v>1.269344</v>
       </c>
       <c r="D74" t="n">
-        <v>6022.66941</v>
+        <v>1.218987</v>
       </c>
       <c r="E74" t="n">
-        <v>5969.716865</v>
+        <v>0.8600989999999999</v>
       </c>
       <c r="F74" t="n">
-        <v>4097.608961</v>
+        <v>0.669752</v>
       </c>
       <c r="G74" t="n">
-        <v>3885.775727</v>
+        <v>0.773203</v>
       </c>
       <c r="H74" t="n">
-        <v>4196.073425</v>
+        <v>1.585432</v>
       </c>
       <c r="I74" t="n">
-        <v>6374.150305</v>
+        <v>1.823919</v>
       </c>
       <c r="J74" t="n">
-        <v>2873.532273</v>
+        <v>1.303966</v>
+      </c>
+      <c r="K74" t="n">
+        <v>1.141856</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右上上櫃</t>
+          <t>生技醫療業右下上市</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>2.223199</v>
+        <v>0</v>
       </c>
       <c r="C75" t="n">
-        <v>1.394526</v>
+        <v>1394.507632</v>
       </c>
       <c r="D75" t="n">
-        <v>1.27838</v>
+        <v>1439.696257</v>
       </c>
       <c r="E75" t="n">
-        <v>0.974698</v>
+        <v>1221.898304</v>
       </c>
       <c r="F75" t="n">
-        <v>0.796296</v>
+        <v>932.288263</v>
       </c>
       <c r="G75" t="n">
-        <v>0.814196</v>
+        <v>871.923425</v>
       </c>
       <c r="H75" t="n">
-        <v>1.607912</v>
+        <v>1063.75342</v>
       </c>
       <c r="I75" t="n">
-        <v>1.910936</v>
+        <v>929.41603</v>
       </c>
       <c r="J75" t="n">
-        <v>1.355821</v>
+        <v>1420.761809</v>
+      </c>
+      <c r="K75" t="n">
+        <v>967.64696</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右下上市</t>
-        </is>
-      </c>
-      <c r="B76" t="n">
-        <v>1489.704493</v>
-      </c>
+          <t>生技醫療業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
-        <v>1380.833839</v>
+        <v>0.289821</v>
       </c>
       <c r="D76" t="n">
-        <v>1420.340333</v>
+        <v>0.36148825</v>
       </c>
       <c r="E76" t="n">
-        <v>790.299203</v>
+        <v>0.306347</v>
       </c>
       <c r="F76" t="n">
-        <v>882.589772</v>
+        <v>0.3893810833333333</v>
       </c>
       <c r="G76" t="n">
-        <v>831.72542</v>
+        <v>0.3151093333333333</v>
       </c>
       <c r="H76" t="n">
-        <v>998.401114</v>
+        <v>0.4294376666666667</v>
       </c>
       <c r="I76" t="n">
-        <v>576.713749</v>
+        <v>0.4170741666666667</v>
       </c>
       <c r="J76" t="n">
-        <v>1361.174952</v>
+        <v>0.3776865</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0.7297864166666667</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B77" t="n">
-        <v>0.614899</v>
-      </c>
+          <t>生技醫療業平上市</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
       <c r="C77" t="n">
-        <v>0.317249</v>
+        <v>37.474575</v>
       </c>
       <c r="D77" t="n">
-        <v>0.40359625</v>
+        <v>42.889883</v>
       </c>
       <c r="E77" t="n">
-        <v>0.345726</v>
+        <v>46.709506</v>
       </c>
       <c r="F77" t="n">
-        <v>0.3164330833333333</v>
+        <v>1042.089824</v>
       </c>
       <c r="G77" t="n">
-        <v>0.3441363333333333</v>
+        <v>385.855107</v>
       </c>
       <c r="H77" t="n">
-        <v>0.3782826666666667</v>
+        <v>80.16861400000001</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3214551666666667</v>
+        <v>40.646904</v>
       </c>
       <c r="J77" t="n">
-        <v>0.3472475</v>
+        <v>87.079731</v>
+      </c>
+      <c r="K77" t="n">
+        <v>80.315482</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業平上市</t>
-        </is>
-      </c>
-      <c r="B78" t="n">
-        <v>1204.498288</v>
-      </c>
+          <t>生技醫療業平上櫃</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
       <c r="C78" t="n">
-        <v>1114.28476</v>
+        <v>0.228616</v>
       </c>
       <c r="D78" t="n">
-        <v>52.616483</v>
+        <v>0.217362</v>
       </c>
       <c r="E78" t="n">
-        <v>466.542454</v>
+        <v>0.275593</v>
       </c>
       <c r="F78" t="n">
-        <v>85.77894999999999</v>
+        <v>0.190755</v>
       </c>
       <c r="G78" t="n">
-        <v>103.755408</v>
+        <v>0.104061</v>
       </c>
       <c r="H78" t="n">
-        <v>138.845666</v>
+        <v>0.121558</v>
       </c>
       <c r="I78" t="n">
-        <v>387.875188</v>
+        <v>0.08987299999999999</v>
       </c>
       <c r="J78" t="n">
-        <v>129.548609</v>
+        <v>0.09468699999999999</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0.090987</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業平上櫃</t>
-        </is>
-      </c>
-      <c r="B79" t="n">
-        <v>0.09131</v>
-      </c>
+          <t>紡織纖維右上上市</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
       <c r="C79" t="n">
-        <v>0.105263</v>
+        <v>191.889821</v>
       </c>
       <c r="D79" t="n">
-        <v>0.164759</v>
+        <v>254.467923</v>
       </c>
       <c r="E79" t="n">
-        <v>0.165728</v>
+        <v>167.925014</v>
       </c>
       <c r="F79" t="n">
-        <v>0.1738</v>
+        <v>144.37402</v>
       </c>
       <c r="G79" t="n">
-        <v>0.06646000000000001</v>
+        <v>192.102061</v>
       </c>
       <c r="H79" t="n">
-        <v>0.181862</v>
+        <v>486.835413</v>
       </c>
       <c r="I79" t="n">
-        <v>0.126775</v>
+        <v>255.407393</v>
       </c>
       <c r="J79" t="n">
-        <v>0.097179</v>
+        <v>389.4149</v>
+      </c>
+      <c r="K79" t="n">
+        <v>699.954172</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右上上市</t>
-        </is>
-      </c>
-      <c r="B80" t="n">
-        <v>732.466211</v>
-      </c>
+          <t>紡織纖維右上上櫃</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
       <c r="C80" t="n">
-        <v>187.341735</v>
+        <v>0.002949</v>
       </c>
       <c r="D80" t="n">
-        <v>243.927543</v>
+        <v>0.004252</v>
       </c>
       <c r="E80" t="n">
-        <v>156.612433</v>
+        <v>0.002614</v>
       </c>
       <c r="F80" t="n">
-        <v>292.472929</v>
+        <v>0.003562</v>
       </c>
       <c r="G80" t="n">
-        <v>185.653581</v>
+        <v>0.002342</v>
       </c>
       <c r="H80" t="n">
-        <v>680.52637</v>
+        <v>0.003026</v>
       </c>
       <c r="I80" t="n">
-        <v>253.387223</v>
+        <v>0.000842</v>
       </c>
       <c r="J80" t="n">
-        <v>522.9243310000001</v>
+        <v>0.001892</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0.001417</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右上上櫃</t>
-        </is>
-      </c>
-      <c r="B81" t="n">
-        <v>0.0009493333333333333</v>
-      </c>
+          <t>紡織纖維右下上市</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
-        <v>0.002949</v>
+        <v>538.748886</v>
       </c>
       <c r="D81" t="n">
-        <v>0.004252</v>
+        <v>1029.650505</v>
       </c>
       <c r="E81" t="n">
-        <v>0.002614</v>
+        <v>528.422161</v>
       </c>
       <c r="F81" t="n">
-        <v>0.003562</v>
+        <v>563.181368</v>
       </c>
       <c r="G81" t="n">
-        <v>0.002342</v>
+        <v>498.794683</v>
       </c>
       <c r="H81" t="n">
-        <v>0.003026</v>
+        <v>691.878292</v>
       </c>
       <c r="I81" t="n">
-        <v>0.000842</v>
+        <v>430.52915</v>
       </c>
       <c r="J81" t="n">
-        <v>0.001892</v>
+        <v>409.086257</v>
+      </c>
+      <c r="K81" t="n">
+        <v>926.442956</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右下上市</t>
-        </is>
-      </c>
-      <c r="B82" t="n">
-        <v>752.129802</v>
-      </c>
+          <t>紡織纖維右下上櫃</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
       <c r="C82" t="n">
-        <v>538.748886</v>
+        <v>0.005398</v>
       </c>
       <c r="D82" t="n">
-        <v>1029.650505</v>
+        <v>0.0078</v>
       </c>
       <c r="E82" t="n">
-        <v>529.1533889999999</v>
+        <v>0.003755</v>
       </c>
       <c r="F82" t="n">
-        <v>559.467184</v>
+        <v>0.003316</v>
       </c>
       <c r="G82" t="n">
-        <v>497.35158</v>
+        <v>0.001696</v>
       </c>
       <c r="H82" t="n">
-        <v>690.9260829999999</v>
+        <v>0.005551</v>
       </c>
       <c r="I82" t="n">
-        <v>429.938206</v>
+        <v>0.001959</v>
       </c>
       <c r="J82" t="n">
-        <v>409.600498</v>
+        <v>0.002287</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0.004319</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右下上櫃</t>
-        </is>
-      </c>
-      <c r="B83" t="n">
-        <v>0.0055</v>
-      </c>
+          <t>紡織纖維平上市</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
-        <v>0.005398</v>
+        <v>192.910397</v>
       </c>
       <c r="D83" t="n">
-        <v>0.009835</v>
+        <v>171.097066</v>
       </c>
       <c r="E83" t="n">
-        <v>0.003755</v>
+        <v>184.572468</v>
       </c>
       <c r="F83" t="n">
-        <v>0.003866</v>
+        <v>233.877082</v>
       </c>
       <c r="G83" t="n">
-        <v>0.002449</v>
+        <v>217.291177</v>
       </c>
       <c r="H83" t="n">
-        <v>0.005551</v>
+        <v>208.142903</v>
       </c>
       <c r="I83" t="n">
-        <v>0.003023</v>
+        <v>462.188773</v>
       </c>
       <c r="J83" t="n">
-        <v>0.002772</v>
+        <v>175.527518</v>
+      </c>
+      <c r="K83" t="n">
+        <v>242.359446</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維平上市</t>
-        </is>
-      </c>
-      <c r="B84" t="n">
-        <v>46.233444</v>
-      </c>
+          <t>紡織纖維平上櫃</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
       <c r="C84" t="n">
-        <v>197.458483</v>
+        <v>0.002764</v>
       </c>
       <c r="D84" t="n">
-        <v>181.637446</v>
+        <v>0.004661</v>
       </c>
       <c r="E84" t="n">
-        <v>195.153821</v>
+        <v>0.003386</v>
       </c>
       <c r="F84" t="n">
-        <v>89.492357</v>
+        <v>0.001797</v>
       </c>
       <c r="G84" t="n">
-        <v>225.18276</v>
+        <v>0.002898</v>
       </c>
       <c r="H84" t="n">
-        <v>15.404155</v>
+        <v>0.003993</v>
       </c>
       <c r="I84" t="n">
-        <v>464.799887</v>
+        <v>0.002768</v>
       </c>
       <c r="J84" t="n">
-        <v>41.503846</v>
+        <v>0.00236</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0.004905</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維平上櫃</t>
-        </is>
-      </c>
-      <c r="B85" t="n">
-        <v>0.009106</v>
-      </c>
+          <t>綠能環保右上上市</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
-        <v>0.002764</v>
+        <v>1362.620758</v>
       </c>
       <c r="D85" t="n">
-        <v>0.002626</v>
+        <v>1242.464558</v>
       </c>
       <c r="E85" t="n">
-        <v>0.003386</v>
+        <v>1080.528652</v>
       </c>
       <c r="F85" t="n">
-        <v>0.001247</v>
+        <v>1417.01767</v>
       </c>
       <c r="G85" t="n">
-        <v>0.002145</v>
+        <v>1587.058712</v>
       </c>
       <c r="H85" t="n">
-        <v>0.003993</v>
+        <v>1847.634114</v>
       </c>
       <c r="I85" t="n">
-        <v>0.001704</v>
+        <v>1606.405262</v>
       </c>
       <c r="J85" t="n">
-        <v>0.001875</v>
+        <v>1655.750715</v>
+      </c>
+      <c r="K85" t="n">
+        <v>2934.521909</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右上上市</t>
-        </is>
-      </c>
-      <c r="B86" t="n">
-        <v>4961.954771</v>
-      </c>
+          <t>綠能環保右上上櫃</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
       <c r="C86" t="n">
-        <v>1355.177009</v>
+        <v>0.490202</v>
       </c>
       <c r="D86" t="n">
-        <v>1169.933032</v>
+        <v>0.06761399999999999</v>
       </c>
       <c r="E86" t="n">
-        <v>1083.445147</v>
+        <v>0.08539099999999999</v>
       </c>
       <c r="F86" t="n">
-        <v>987.254875</v>
+        <v>0.08933199999999999</v>
       </c>
       <c r="G86" t="n">
-        <v>1065.228574</v>
+        <v>0.210435</v>
       </c>
       <c r="H86" t="n">
-        <v>1461.418548</v>
+        <v>0.210932</v>
       </c>
       <c r="I86" t="n">
-        <v>1090.069752</v>
+        <v>0.278157</v>
       </c>
       <c r="J86" t="n">
-        <v>1296.447198</v>
+        <v>0.668552</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0.483589</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右上上櫃</t>
-        </is>
-      </c>
-      <c r="B87" t="n">
-        <v>0.075873</v>
-      </c>
+          <t>綠能環保右下上市</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
-        <v>0.123075</v>
+        <v>340.975202</v>
       </c>
       <c r="D87" t="n">
-        <v>0.056319</v>
+        <v>377.61428</v>
       </c>
       <c r="E87" t="n">
-        <v>0.08539099999999999</v>
+        <v>308.43768</v>
       </c>
       <c r="F87" t="n">
-        <v>0.08933199999999999</v>
+        <v>287.683514</v>
       </c>
       <c r="G87" t="n">
-        <v>0.031627</v>
+        <v>274.468824</v>
       </c>
       <c r="H87" t="n">
-        <v>0.034733</v>
+        <v>248.735441</v>
       </c>
       <c r="I87" t="n">
-        <v>0.06268700000000001</v>
+        <v>280.548546</v>
       </c>
       <c r="J87" t="n">
-        <v>0.668552</v>
+        <v>316.477195</v>
+      </c>
+      <c r="K87" t="n">
+        <v>515.226859</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右下上市</t>
-        </is>
-      </c>
-      <c r="B88" t="n">
-        <v>948.345542</v>
-      </c>
+          <t>綠能環保右下上櫃</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
-        <v>528.034793</v>
+        <v>0.028041</v>
       </c>
       <c r="D88" t="n">
-        <v>621.8295010000001</v>
+        <v>0.035772</v>
       </c>
       <c r="E88" t="n">
-        <v>539.273703</v>
+        <v>0.02672833333333334</v>
       </c>
       <c r="F88" t="n">
-        <v>278.616048</v>
+        <v>0.016288</v>
       </c>
       <c r="G88" t="n">
-        <v>274.468824</v>
+        <v>0.03483266666666667</v>
       </c>
       <c r="H88" t="n">
-        <v>246.334542</v>
+        <v>0.024313</v>
       </c>
       <c r="I88" t="n">
-        <v>273.107014</v>
+        <v>0.017407</v>
       </c>
       <c r="J88" t="n">
-        <v>308.175048</v>
+        <v>0.023258</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0.049814</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右下上櫃</t>
-        </is>
-      </c>
-      <c r="B89" t="n">
-        <v>0.04692425</v>
-      </c>
+          <t>綠能環保平上市</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>0.040527</v>
+        <v>193.637222</v>
       </c>
       <c r="D89" t="n">
-        <v>0.223725</v>
+        <v>259.622431</v>
       </c>
       <c r="E89" t="n">
-        <v>0.2862343333333333</v>
+        <v>247.562415</v>
       </c>
       <c r="F89" t="n">
-        <v>0.114534</v>
+        <v>17.201137</v>
       </c>
       <c r="G89" t="n">
-        <v>0.06042566666666667</v>
+        <v>22.530052</v>
       </c>
       <c r="H89" t="n">
-        <v>0.040755</v>
+        <v>23.316133</v>
       </c>
       <c r="I89" t="n">
-        <v>0.03678</v>
+        <v>22.036377</v>
       </c>
       <c r="J89" t="n">
-        <v>0.041197</v>
+        <v>23.016278</v>
+      </c>
+      <c r="K89" t="n">
+        <v>37.641095</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>綠能環保平上市</t>
-        </is>
-      </c>
-      <c r="B90" t="n">
-        <v>43.441831</v>
-      </c>
+          <t>綠能環保平上櫃</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
-        <v>14.02138</v>
+        <v>0.000898</v>
       </c>
       <c r="D90" t="n">
-        <v>87.93873600000001</v>
+        <v>0.189973</v>
       </c>
       <c r="E90" t="n">
-        <v>13.809897</v>
+        <v>0.260887</v>
       </c>
       <c r="F90" t="n">
-        <v>456.031398</v>
+        <v>0.098638</v>
       </c>
       <c r="G90" t="n">
-        <v>544.36019</v>
+        <v>0.025832</v>
       </c>
       <c r="H90" t="n">
-        <v>411.932598</v>
+        <v>0.018125</v>
       </c>
       <c r="I90" t="n">
-        <v>545.813419</v>
+        <v>0.019877</v>
       </c>
       <c r="J90" t="n">
-        <v>390.621942</v>
+        <v>0.018939</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0.064306</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>綠能環保平上櫃</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>0.271423</v>
-      </c>
+          <t>航運業右上上市</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>0.355539</v>
+        <v>6458.851736</v>
       </c>
       <c r="D91" t="n">
-        <v>0.013315</v>
+        <v>4536.012146</v>
       </c>
       <c r="E91" t="n">
-        <v>0.001381</v>
+        <v>5141.094921</v>
       </c>
       <c r="F91" t="n">
-        <v>0.000392</v>
+        <v>3937.638722</v>
       </c>
       <c r="G91" t="n">
-        <v>0.179047</v>
+        <v>4902.34093</v>
       </c>
       <c r="H91" t="n">
-        <v>0.177882</v>
+        <v>4162.974965</v>
       </c>
       <c r="I91" t="n">
-        <v>0.215974</v>
+        <v>3628.725363</v>
       </c>
       <c r="J91" t="n">
-        <v>0.001</v>
+        <v>4015.794107</v>
+      </c>
+      <c r="K91" t="n">
+        <v>4930.886461</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>航運業右上上市</t>
-        </is>
-      </c>
-      <c r="B92" t="n">
-        <v>11853.026073</v>
-      </c>
+          <t>航運業右下上市</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
-        <v>6250.921795</v>
+        <v>186.139995</v>
       </c>
       <c r="D92" t="n">
-        <v>5391.171935</v>
+        <v>264.35394</v>
       </c>
       <c r="E92" t="n">
-        <v>6706.51643</v>
+        <v>201.193499</v>
       </c>
       <c r="F92" t="n">
-        <v>4550.993342</v>
+        <v>172.265618</v>
       </c>
       <c r="G92" t="n">
-        <v>6235.148024</v>
+        <v>246.817529</v>
       </c>
       <c r="H92" t="n">
-        <v>5045.109869</v>
+        <v>207.837683</v>
       </c>
       <c r="I92" t="n">
-        <v>4288.824517</v>
+        <v>149.091351</v>
       </c>
       <c r="J92" t="n">
-        <v>4613.845504</v>
+        <v>190.484063</v>
+      </c>
+      <c r="K92" t="n">
+        <v>276.736665</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>航運業右下上市</t>
-        </is>
-      </c>
-      <c r="B93" t="n">
-        <v>784.947189</v>
-      </c>
+          <t>航運業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>240.273186</v>
+        <v>0.023707</v>
       </c>
       <c r="D93" t="n">
-        <v>321.987568</v>
+        <v>0.017652</v>
       </c>
       <c r="E93" t="n">
-        <v>323.013159</v>
+        <v>0.0187445</v>
       </c>
       <c r="F93" t="n">
-        <v>223.085712</v>
+        <v>0.012347</v>
       </c>
       <c r="G93" t="n">
-        <v>319.29705</v>
+        <v>0.018943</v>
       </c>
       <c r="H93" t="n">
-        <v>272.893445</v>
+        <v>0.021786</v>
       </c>
       <c r="I93" t="n">
-        <v>227.609198</v>
+        <v>0.018536</v>
       </c>
       <c r="J93" t="n">
-        <v>252.512685</v>
+        <v>0.021268</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0.0430535</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>航運業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B94" t="n">
-        <v>0.0307545</v>
-      </c>
+          <t>航運業平上市</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>0.023707</v>
+        <v>295.44217</v>
       </c>
       <c r="D94" t="n">
-        <v>0.017652</v>
+        <v>1550.315192</v>
       </c>
       <c r="E94" t="n">
-        <v>0.0187445</v>
+        <v>2588.8407</v>
       </c>
       <c r="F94" t="n">
-        <v>0.015171</v>
+        <v>1356.772584</v>
       </c>
       <c r="G94" t="n">
-        <v>0.027518</v>
+        <v>1696.867779</v>
       </c>
       <c r="H94" t="n">
-        <v>0.031577</v>
+        <v>1473.299704</v>
       </c>
       <c r="I94" t="n">
-        <v>0.018536</v>
+        <v>1135.708164</v>
       </c>
       <c r="J94" t="n">
-        <v>0.021268</v>
+        <v>953.812262</v>
+      </c>
+      <c r="K94" t="n">
+        <v>1262.589742</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>航運業平上市</t>
-        </is>
-      </c>
-      <c r="B95" t="n">
-        <v>885.59461</v>
-      </c>
+          <t>航運業平上櫃</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>449.23892</v>
+        <v>0.007715</v>
       </c>
       <c r="D95" t="n">
-        <v>637.521775</v>
+        <v>0.003387</v>
       </c>
       <c r="E95" t="n">
-        <v>901.599531</v>
+        <v>0.003643</v>
       </c>
       <c r="F95" t="n">
-        <v>692.5978699999999</v>
+        <v>0.002824</v>
       </c>
       <c r="G95" t="n">
-        <v>291.581164</v>
+        <v>0.008574999999999999</v>
       </c>
       <c r="H95" t="n">
-        <v>526.1090380000001</v>
-      </c>
-      <c r="I95" t="n">
-        <v>397.091163</v>
-      </c>
-      <c r="J95" t="n">
-        <v>293.732243</v>
-      </c>
+        <v>0.009790999999999999</v>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>航運業平上櫃</t>
-        </is>
-      </c>
-      <c r="B96" t="n">
-        <v>0.015036</v>
-      </c>
+          <t>觀光事業右上上市</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>0.007715</v>
+        <v>18.052509</v>
       </c>
       <c r="D96" t="n">
-        <v>0.003387</v>
+        <v>14.958555</v>
       </c>
       <c r="E96" t="n">
-        <v>0.003643</v>
-      </c>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
+        <v>11.00032</v>
+      </c>
+      <c r="F96" t="n">
+        <v>8.780357</v>
+      </c>
+      <c r="G96" t="n">
+        <v>105.657624</v>
+      </c>
+      <c r="H96" t="n">
+        <v>79.71870199999999</v>
+      </c>
+      <c r="I96" t="n">
+        <v>49.868836</v>
+      </c>
+      <c r="J96" t="n">
+        <v>57.785976</v>
+      </c>
+      <c r="K96" t="n">
+        <v>42.157955</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右上上市</t>
-        </is>
-      </c>
-      <c r="B97" t="n">
-        <v>27.444641</v>
-      </c>
+          <t>觀光事業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>19.597812</v>
+        <v>0.010267</v>
       </c>
       <c r="D97" t="n">
-        <v>17.981812</v>
+        <v>0.002791</v>
       </c>
       <c r="E97" t="n">
-        <v>12.021829</v>
+        <v>0.005545</v>
       </c>
       <c r="F97" t="n">
-        <v>135.017384</v>
+        <v>0.005721</v>
       </c>
       <c r="G97" t="n">
-        <v>139.47937</v>
+        <v>0.009771999999999999</v>
       </c>
       <c r="H97" t="n">
-        <v>81.415419</v>
+        <v>0.028757</v>
       </c>
       <c r="I97" t="n">
-        <v>52.444073</v>
+        <v>0.0221915</v>
       </c>
       <c r="J97" t="n">
-        <v>95.54313500000001</v>
+        <v>0.003814</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0.002144</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右上上櫃</t>
+          <t>觀光事業右下上市</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.010605</v>
+        <v>0</v>
       </c>
       <c r="C98" t="n">
-        <v>0.009384</v>
+        <v>57.379966</v>
       </c>
       <c r="D98" t="n">
-        <v>0.002788</v>
+        <v>94.060181</v>
       </c>
       <c r="E98" t="n">
-        <v>0.005511</v>
+        <v>72.018058</v>
       </c>
       <c r="F98" t="n">
-        <v>0.005694</v>
+        <v>56.471815</v>
       </c>
       <c r="G98" t="n">
-        <v>0.009537</v>
+        <v>81.909038</v>
       </c>
       <c r="H98" t="n">
-        <v>0.028504</v>
+        <v>74.94547900000001</v>
       </c>
       <c r="I98" t="n">
-        <v>0.0221175</v>
+        <v>40.343542</v>
       </c>
       <c r="J98" t="n">
-        <v>0.00347</v>
+        <v>47.711996</v>
+      </c>
+      <c r="K98" t="n">
+        <v>75.638076</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右下上市</t>
-        </is>
-      </c>
-      <c r="B99" t="n">
-        <v>100.201892</v>
-      </c>
+          <t>觀光事業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
-        <v>57.639539</v>
+        <v>0.039119</v>
       </c>
       <c r="D99" t="n">
-        <v>70.396855</v>
+        <v>0.036983</v>
       </c>
       <c r="E99" t="n">
-        <v>73.746514</v>
+        <v>0.03807</v>
       </c>
       <c r="F99" t="n">
-        <v>57.692754</v>
+        <v>0.031206</v>
       </c>
       <c r="G99" t="n">
-        <v>82.187201</v>
+        <v>0.025503</v>
       </c>
       <c r="H99" t="n">
-        <v>75.432047</v>
+        <v>0.026615</v>
       </c>
       <c r="I99" t="n">
-        <v>40.885461</v>
+        <v>0.021823</v>
       </c>
       <c r="J99" t="n">
-        <v>48.094337</v>
+        <v>0.02542625</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0.036685</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B100" t="n">
-        <v>0.040576</v>
-      </c>
+          <t>觀光事業平上市</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
       <c r="C100" t="n">
-        <v>0.034939</v>
+        <v>27.989284</v>
       </c>
       <c r="D100" t="n">
-        <v>0.035491</v>
+        <v>41.997589</v>
       </c>
       <c r="E100" t="n">
-        <v>0.0379</v>
+        <v>43.501803</v>
       </c>
       <c r="F100" t="n">
-        <v>0.031228</v>
+        <v>126.618067</v>
       </c>
       <c r="G100" t="n">
-        <v>0.02585375</v>
+        <v>34.528757</v>
       </c>
       <c r="H100" t="n">
-        <v>0.025105</v>
+        <v>1.696717</v>
       </c>
       <c r="I100" t="n">
-        <v>0.021688</v>
+        <v>73.502138</v>
       </c>
       <c r="J100" t="n">
-        <v>0.02571725</v>
+        <v>37.757159</v>
+      </c>
+      <c r="K100" t="n">
+        <v>36.973401</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>觀光事業平上市</t>
-        </is>
-      </c>
-      <c r="B101" t="n">
-        <v>52.412322</v>
-      </c>
+          <t>觀光事業平上櫃</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
       <c r="C101" t="n">
-        <v>26.443981</v>
+        <v>3.7e-05</v>
       </c>
       <c r="D101" t="n">
-        <v>63.217595</v>
+        <v>5e-05</v>
       </c>
       <c r="E101" t="n">
-        <v>42.480294</v>
+        <v>0.001799</v>
       </c>
       <c r="F101" t="n">
-        <v>0.38104</v>
+        <v>0.000703</v>
       </c>
       <c r="G101" t="n">
-        <v>0.7070109999999999</v>
-      </c>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="n">
-        <v>70.926901</v>
-      </c>
-      <c r="J101" t="inlineStr"/>
+        <v>0.00026275</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0.000408</v>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="n">
+        <v>0.000231</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0.000167</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>觀光事業平上櫃</t>
-        </is>
-      </c>
-      <c r="B102" t="n">
-        <v>0.004231</v>
-      </c>
+          <t>貿易百貨右上上市</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
       <c r="C102" t="n">
-        <v>0.005689</v>
+        <v>118.607371</v>
       </c>
       <c r="D102" t="n">
-        <v>0.002429</v>
+        <v>129.736089</v>
       </c>
       <c r="E102" t="n">
-        <v>0.002757</v>
+        <v>172.011245</v>
       </c>
       <c r="F102" t="n">
-        <v>0.001546</v>
+        <v>123.089602</v>
       </c>
       <c r="G102" t="n">
-        <v>0.000648</v>
+        <v>123.734111</v>
       </c>
       <c r="H102" t="n">
-        <v>0.002487</v>
+        <v>101.188944</v>
       </c>
       <c r="I102" t="n">
-        <v>0.000375</v>
+        <v>96.374189</v>
       </c>
       <c r="J102" t="n">
-        <v>0.00052</v>
+        <v>114.310155</v>
+      </c>
+      <c r="K102" t="n">
+        <v>117.16523</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨右上上市</t>
-        </is>
-      </c>
-      <c r="B103" t="n">
-        <v>213.17421</v>
-      </c>
+          <t>貿易百貨右下上市</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr"/>
       <c r="C103" t="n">
-        <v>118.613415</v>
+        <v>283.905508</v>
       </c>
       <c r="D103" t="n">
-        <v>134.583649</v>
+        <v>219.459544</v>
       </c>
       <c r="E103" t="n">
-        <v>173.191176</v>
+        <v>530.455793</v>
       </c>
       <c r="F103" t="n">
-        <v>124.12725</v>
+        <v>482.217237</v>
       </c>
       <c r="G103" t="n">
-        <v>123.87734</v>
+        <v>354.9255993333333</v>
       </c>
       <c r="H103" t="n">
-        <v>101.572075</v>
+        <v>368.929928</v>
       </c>
       <c r="I103" t="n">
-        <v>97.257312</v>
+        <v>516.631265</v>
       </c>
       <c r="J103" t="n">
-        <v>116.831751</v>
+        <v>677.631095</v>
+      </c>
+      <c r="K103" t="n">
+        <v>293.270035</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨右下上市</t>
-        </is>
-      </c>
-      <c r="B104" t="n">
-        <v>662.673498</v>
-      </c>
+          <t>貿易百貨平上市</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr"/>
       <c r="C104" t="n">
-        <v>283.905508</v>
+        <v>31.444853</v>
       </c>
       <c r="D104" t="n">
-        <v>228.051738</v>
+        <v>14.803086</v>
       </c>
       <c r="E104" t="n">
-        <v>545.00246</v>
+        <v>24.741599</v>
       </c>
       <c r="F104" t="n">
-        <v>502.007682</v>
+        <v>21.066168</v>
       </c>
       <c r="G104" t="n">
-        <v>353.8224913333333</v>
+        <v>0.99844</v>
       </c>
       <c r="H104" t="n">
-        <v>405.806172</v>
+        <v>40.741601</v>
       </c>
       <c r="I104" t="n">
-        <v>516.970554</v>
+        <v>2.296363</v>
       </c>
       <c r="J104" t="n">
-        <v>676.738581</v>
+        <v>4.231909</v>
+      </c>
+      <c r="K104" t="n">
+        <v>3.785008</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨平上市</t>
-        </is>
-      </c>
-      <c r="B105" t="n">
-        <v>1.055977</v>
-      </c>
+          <t>資訊服務業右上上市</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
       <c r="C105" t="n">
-        <v>31.438809</v>
+        <v>796.716895</v>
       </c>
       <c r="D105" t="n">
-        <v>1.363332</v>
+        <v>719.680639</v>
       </c>
       <c r="E105" t="n">
-        <v>9.015001</v>
+        <v>684.8656130000001</v>
       </c>
       <c r="F105" t="n">
-        <v>0.238075</v>
+        <v>733.865583</v>
       </c>
       <c r="G105" t="n">
-        <v>1.958319</v>
+        <v>418.030885</v>
       </c>
       <c r="H105" t="n">
-        <v>3.482226</v>
+        <v>547.916906</v>
       </c>
       <c r="I105" t="n">
-        <v>1.073951</v>
+        <v>262.218864</v>
       </c>
       <c r="J105" t="n">
-        <v>2.602827</v>
+        <v>217.2931</v>
+      </c>
+      <c r="K105" t="n">
+        <v>345.014255</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右上上市</t>
-        </is>
-      </c>
-      <c r="B106" t="n">
-        <v>2420.209919</v>
-      </c>
+          <t>資訊服務業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr"/>
       <c r="C106" t="n">
-        <v>2324.315633</v>
+        <v>0.157991</v>
       </c>
       <c r="D106" t="n">
-        <v>999.44839</v>
+        <v>0.153279</v>
       </c>
       <c r="E106" t="n">
-        <v>816.0570310000001</v>
+        <v>0.06589</v>
       </c>
       <c r="F106" t="n">
-        <v>921.361164</v>
+        <v>0.316551</v>
       </c>
       <c r="G106" t="n">
-        <v>525.655053</v>
+        <v>0.151087</v>
       </c>
       <c r="H106" t="n">
-        <v>637.545508</v>
+        <v>0.145614</v>
       </c>
       <c r="I106" t="n">
-        <v>335.86408</v>
+        <v>0.440767</v>
       </c>
       <c r="J106" t="n">
-        <v>309.39226</v>
+        <v>0.579151</v>
+      </c>
+      <c r="K106" t="n">
+        <v>0.405653</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B107" t="n">
-        <v>0.735469</v>
-      </c>
+          <t>資訊服務業右下上市</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
       <c r="C107" t="n">
-        <v>0.968853</v>
+        <v>49.539169</v>
       </c>
       <c r="D107" t="n">
-        <v>0.28803</v>
+        <v>38.143733</v>
       </c>
       <c r="E107" t="n">
-        <v>0.180248</v>
+        <v>31.30314</v>
       </c>
       <c r="F107" t="n">
-        <v>0.624803</v>
+        <v>32.514739</v>
       </c>
       <c r="G107" t="n">
-        <v>0.272337</v>
+        <v>30.620833</v>
       </c>
       <c r="H107" t="n">
-        <v>0.270188</v>
+        <v>33.041287</v>
       </c>
       <c r="I107" t="n">
-        <v>0.531964</v>
+        <v>23.291445</v>
       </c>
       <c r="J107" t="n">
-        <v>0.654319</v>
+        <v>26.608812</v>
+      </c>
+      <c r="K107" t="n">
+        <v>204.47693</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右下上市</t>
+          <t>資訊服務業右下上櫃</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>15.956034</v>
+        <v>0</v>
       </c>
       <c r="C108" t="n">
-        <v>7.692126</v>
+        <v>0.254495</v>
       </c>
       <c r="D108" t="n">
-        <v>5.549619</v>
+        <v>0.181211</v>
       </c>
       <c r="E108" t="n">
-        <v>4.066226</v>
+        <v>0.07320699999999999</v>
       </c>
       <c r="F108" t="n">
-        <v>6.540235</v>
+        <v>0.038081</v>
       </c>
       <c r="G108" t="n">
-        <v>16.557683</v>
+        <v>0.035812</v>
       </c>
       <c r="H108" t="n">
-        <v>8.925591000000001</v>
+        <v>0.108406</v>
       </c>
       <c r="I108" t="n">
-        <v>4.865924</v>
+        <v>0.096425</v>
       </c>
       <c r="J108" t="n">
-        <v>13.219645</v>
+        <v>0.056801</v>
+      </c>
+      <c r="K108" t="n">
+        <v>0.102778</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B109" t="n">
-        <v>0.131389</v>
-      </c>
+          <t>資訊服務業平上市</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr"/>
       <c r="C109" t="n">
-        <v>0.180008</v>
+        <v>1541.660961</v>
       </c>
       <c r="D109" t="n">
-        <v>0.16141</v>
+        <v>279.767751</v>
       </c>
       <c r="E109" t="n">
-        <v>0.11476</v>
+        <v>143.446269</v>
       </c>
       <c r="F109" t="n">
-        <v>0.06328499999999999</v>
+        <v>210.135385</v>
       </c>
       <c r="G109" t="n">
-        <v>0.0534</v>
+        <v>117.282981</v>
       </c>
       <c r="H109" t="n">
-        <v>0.09637</v>
+        <v>97.582365</v>
       </c>
       <c r="I109" t="n">
-        <v>0.060962</v>
+        <v>73.645216</v>
       </c>
       <c r="J109" t="n">
-        <v>0.066687</v>
+        <v>96.94449</v>
+      </c>
+      <c r="K109" t="n">
+        <v>193.477013</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業平上市</t>
-        </is>
-      </c>
-      <c r="B110" t="n">
-        <v>35.293026</v>
-      </c>
+          <t>資訊服務業平上櫃</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr"/>
       <c r="C110" t="n">
-        <v>55.909266</v>
+        <v>0.698663</v>
       </c>
       <c r="D110" t="n">
-        <v>32.594114</v>
+        <v>0.173308</v>
       </c>
       <c r="E110" t="n">
-        <v>39.491765</v>
+        <v>0.177853</v>
       </c>
       <c r="F110" t="n">
-        <v>48.614308</v>
+        <v>0.496781</v>
       </c>
       <c r="G110" t="n">
-        <v>23.721963</v>
+        <v>0.302936</v>
       </c>
       <c r="H110" t="n">
-        <v>32.069459</v>
+        <v>0.231086</v>
       </c>
       <c r="I110" t="n">
-        <v>18.425521</v>
+        <v>0.130729</v>
       </c>
       <c r="J110" t="n">
-        <v>18.234497</v>
+        <v>0.194487</v>
+      </c>
+      <c r="K110" t="n">
+        <v>0.291962</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業平上櫃</t>
-        </is>
-      </c>
-      <c r="B111" t="n">
-        <v>0.086302</v>
-      </c>
+          <t>農業科技業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr"/>
       <c r="C111" t="n">
-        <v>0.011431</v>
+        <v>0.035455</v>
       </c>
       <c r="D111" t="n">
-        <v>0.077565</v>
+        <v>0.010882</v>
       </c>
       <c r="E111" t="n">
-        <v>0.029834</v>
+        <v>0.003346</v>
       </c>
       <c r="F111" t="n">
-        <v>0.183793</v>
+        <v>0.00109</v>
       </c>
       <c r="G111" t="n">
-        <v>0.171734</v>
+        <v>0.000695</v>
       </c>
       <c r="H111" t="n">
-        <v>0.128434</v>
+        <v>0.000838</v>
       </c>
       <c r="I111" t="n">
-        <v>0.07986699999999999</v>
+        <v>0.00054</v>
       </c>
       <c r="J111" t="n">
-        <v>0.114254</v>
-      </c>
+        <v>0.00107</v>
+      </c>
+      <c r="K111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>農業科技業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B112" t="n">
-        <v>0.006962</v>
-      </c>
+          <t>農業科技業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr"/>
       <c r="C112" t="n">
-        <v>0.035455</v>
+        <v>0.001512</v>
       </c>
       <c r="D112" t="n">
-        <v>0.010882</v>
+        <v>0.00152</v>
       </c>
       <c r="E112" t="n">
-        <v>0.003346</v>
+        <v>0.00236</v>
       </c>
       <c r="F112" t="n">
-        <v>0.00109</v>
+        <v>0.004261</v>
       </c>
       <c r="G112" t="n">
-        <v>0.000695</v>
+        <v>0.002522</v>
       </c>
       <c r="H112" t="n">
-        <v>0.000838</v>
+        <v>0.002449</v>
       </c>
       <c r="I112" t="n">
-        <v>0.00054</v>
+        <v>0.00161</v>
       </c>
       <c r="J112" t="n">
-        <v>0.00107</v>
+        <v>0.001331</v>
+      </c>
+      <c r="K112" t="n">
+        <v>0.007381</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>農業科技業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B113" t="n">
-        <v>0.001664</v>
-      </c>
-      <c r="C113" t="n">
-        <v>0.001512</v>
-      </c>
-      <c r="D113" t="n">
-        <v>0.00152</v>
-      </c>
-      <c r="E113" t="n">
-        <v>0.00236</v>
-      </c>
-      <c r="F113" t="n">
-        <v>0.004261</v>
-      </c>
-      <c r="G113" t="n">
-        <v>0.002522</v>
-      </c>
-      <c r="H113" t="n">
-        <v>0.002449</v>
-      </c>
-      <c r="I113" t="n">
-        <v>0.00161</v>
-      </c>
-      <c r="J113" t="n">
-        <v>0.001331</v>
+          <t>農業科技業平上櫃</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr"/>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="n">
+        <v>0.00094</v>
       </c>
     </row>
     <row r="114">
@@ -4244,32 +4347,33 @@
           <t>通信網路業右上上市</t>
         </is>
       </c>
-      <c r="B114" t="n">
-        <v>21660.982126</v>
-      </c>
+      <c r="B114" t="inlineStr"/>
       <c r="C114" t="n">
-        <v>14444.86348</v>
+        <v>24264.042483</v>
       </c>
       <c r="D114" t="n">
-        <v>16622.501014</v>
+        <v>27098.836424</v>
       </c>
       <c r="E114" t="n">
-        <v>6095.028413</v>
+        <v>17046.602242</v>
       </c>
       <c r="F114" t="n">
-        <v>6082.970456</v>
+        <v>12598.586921</v>
       </c>
       <c r="G114" t="n">
-        <v>6103.551493</v>
+        <v>15290.862009</v>
       </c>
       <c r="H114" t="n">
-        <v>6746.818307</v>
+        <v>21928.342371</v>
       </c>
       <c r="I114" t="n">
-        <v>5664.386803</v>
+        <v>16945.150652</v>
       </c>
       <c r="J114" t="n">
-        <v>8245.252662000001</v>
+        <v>25518.394772</v>
+      </c>
+      <c r="K114" t="n">
+        <v>31299.192109</v>
       </c>
     </row>
     <row r="115">
@@ -4278,32 +4382,33 @@
           <t>通信網路業右上上櫃</t>
         </is>
       </c>
-      <c r="B115" t="n">
-        <v>24.05772</v>
-      </c>
+      <c r="B115" t="inlineStr"/>
       <c r="C115" t="n">
-        <v>21.767781</v>
+        <v>24.320434</v>
       </c>
       <c r="D115" t="n">
-        <v>16.6943</v>
+        <v>22.476129</v>
       </c>
       <c r="E115" t="n">
-        <v>22.811269</v>
+        <v>26.213372</v>
       </c>
       <c r="F115" t="n">
-        <v>13.621921</v>
+        <v>15.436857</v>
       </c>
       <c r="G115" t="n">
-        <v>7.615602</v>
+        <v>9.591949</v>
       </c>
       <c r="H115" t="n">
-        <v>7.114229</v>
+        <v>9.349261</v>
       </c>
       <c r="I115" t="n">
-        <v>8.893762000000001</v>
+        <v>11.691037</v>
       </c>
       <c r="J115" t="n">
-        <v>18.312942</v>
+        <v>26.466939</v>
+      </c>
+      <c r="K115" t="n">
+        <v>36.447042</v>
       </c>
     </row>
     <row r="116">
@@ -4312,32 +4417,33 @@
           <t>通信網路業右下上市</t>
         </is>
       </c>
-      <c r="B116" t="n">
-        <v>1418.101958</v>
-      </c>
+      <c r="B116" t="inlineStr"/>
       <c r="C116" t="n">
-        <v>3734.229225</v>
+        <v>831.251491</v>
       </c>
       <c r="D116" t="n">
-        <v>2800.97613</v>
+        <v>967.636108</v>
       </c>
       <c r="E116" t="n">
-        <v>3905.975775</v>
+        <v>1572.925061</v>
       </c>
       <c r="F116" t="n">
-        <v>2277.09085</v>
+        <v>834.745993</v>
       </c>
       <c r="G116" t="n">
-        <v>1946.021499</v>
+        <v>496.605319</v>
       </c>
       <c r="H116" t="n">
-        <v>2796.897423</v>
+        <v>627.669129</v>
       </c>
       <c r="I116" t="n">
-        <v>2244.085252</v>
+        <v>511.843469</v>
       </c>
       <c r="J116" t="n">
-        <v>592.812061</v>
+        <v>427.332467</v>
+      </c>
+      <c r="K116" t="n">
+        <v>823.802486</v>
       </c>
     </row>
     <row r="117">
@@ -4347,31 +4453,34 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.210037</v>
+        <v>0</v>
       </c>
       <c r="C117" t="n">
-        <v>0.104276</v>
+        <v>0.112218</v>
       </c>
       <c r="D117" t="n">
-        <v>0.108687</v>
+        <v>0.112675</v>
       </c>
       <c r="E117" t="n">
-        <v>0.177069</v>
+        <v>0.177407</v>
       </c>
       <c r="F117" t="n">
-        <v>0.092809</v>
+        <v>0.095875</v>
       </c>
       <c r="G117" t="n">
-        <v>0.139641</v>
+        <v>0.14341</v>
       </c>
       <c r="H117" t="n">
-        <v>0.121491</v>
+        <v>0.116765</v>
       </c>
       <c r="I117" t="n">
-        <v>0.078808</v>
+        <v>0.109925</v>
       </c>
       <c r="J117" t="n">
-        <v>0.084409</v>
+        <v>0.117526</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.131012</v>
       </c>
     </row>
     <row r="118">
@@ -4380,32 +4489,33 @@
           <t>通信網路業平上市</t>
         </is>
       </c>
-      <c r="B118" t="n">
-        <v>15530.982164</v>
-      </c>
+      <c r="B118" t="inlineStr"/>
       <c r="C118" t="n">
-        <v>7051.592614</v>
+        <v>135.391345</v>
       </c>
       <c r="D118" t="n">
-        <v>8748.802201</v>
+        <v>105.806813</v>
       </c>
       <c r="E118" t="n">
-        <v>8856.093255</v>
+        <v>237.57014</v>
       </c>
       <c r="F118" t="n">
-        <v>5162.65965</v>
+        <v>89.388042</v>
       </c>
       <c r="G118" t="n">
-        <v>8297.360316</v>
+        <v>559.4659799999999</v>
       </c>
       <c r="H118" t="n">
-        <v>13957.577554</v>
+        <v>945.281784</v>
       </c>
       <c r="I118" t="n">
-        <v>12339.661725</v>
+        <v>2791.139659</v>
       </c>
       <c r="J118" t="n">
-        <v>17667.338244</v>
+        <v>559.675728</v>
+      </c>
+      <c r="K118" t="n">
+        <v>305.608661</v>
       </c>
     </row>
     <row r="119">
@@ -4414,32 +4524,33 @@
           <t>通信網路業平上櫃</t>
         </is>
       </c>
-      <c r="B119" t="n">
-        <v>2.541905</v>
-      </c>
+      <c r="B119" t="inlineStr"/>
       <c r="C119" t="n">
-        <v>3.456953</v>
+        <v>0.8952059999999999</v>
       </c>
       <c r="D119" t="n">
-        <v>6.538407</v>
+        <v>0.751752</v>
       </c>
       <c r="E119" t="n">
-        <v>3.420577</v>
+        <v>0.017126</v>
       </c>
       <c r="F119" t="n">
-        <v>2.191077</v>
+        <v>0.372699</v>
       </c>
       <c r="G119" t="n">
-        <v>2.291996</v>
+        <v>0.310555</v>
       </c>
       <c r="H119" t="n">
-        <v>2.261277</v>
+        <v>0.029576</v>
       </c>
       <c r="I119" t="n">
-        <v>3.489899</v>
+        <v>0.660886</v>
       </c>
       <c r="J119" t="n">
-        <v>8.566473999999999</v>
+        <v>0.378057</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.788558</v>
       </c>
     </row>
     <row r="120">
@@ -4448,20 +4559,18 @@
           <t>造紙工業右上上市</t>
         </is>
       </c>
-      <c r="B120" t="n">
-        <v>49.845177</v>
-      </c>
+      <c r="B120" t="inlineStr"/>
       <c r="C120" t="n">
-        <v>37.698224</v>
+        <v>51.079864</v>
       </c>
       <c r="D120" t="n">
-        <v>64.522261</v>
+        <v>77.23409100000001</v>
       </c>
       <c r="E120" t="n">
-        <v>41.474092</v>
+        <v>55.228139</v>
       </c>
       <c r="F120" t="n">
-        <v>57.019267</v>
+        <v>67.6173</v>
       </c>
       <c r="G120" t="n">
         <v>95.750647</v>
@@ -4473,7 +4582,10 @@
         <v>92.464285</v>
       </c>
       <c r="J120" t="n">
-        <v>63.28767</v>
+        <v>79.71619</v>
+      </c>
+      <c r="K120" t="n">
+        <v>58.167627</v>
       </c>
     </row>
     <row r="121">
@@ -4482,9 +4594,7 @@
           <t>造紙工業右下上市</t>
         </is>
       </c>
-      <c r="B121" t="n">
-        <v>12.247197</v>
-      </c>
+      <c r="B121" t="inlineStr"/>
       <c r="C121" t="n">
         <v>5.766187</v>
       </c>
@@ -4509,6 +4619,9 @@
       <c r="J121" t="n">
         <v>7.259808</v>
       </c>
+      <c r="K121" t="n">
+        <v>13.316509</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
@@ -4516,20 +4629,18 @@
           <t>造紙工業平上市</t>
         </is>
       </c>
-      <c r="B122" t="n">
-        <v>41.826683</v>
-      </c>
+      <c r="B122" t="inlineStr"/>
       <c r="C122" t="n">
-        <v>27.811811</v>
+        <v>14.430171</v>
       </c>
       <c r="D122" t="n">
-        <v>39.868425</v>
+        <v>27.156595</v>
       </c>
       <c r="E122" t="n">
-        <v>31.600935</v>
+        <v>17.846888</v>
       </c>
       <c r="F122" t="n">
-        <v>23.263533</v>
+        <v>12.6655</v>
       </c>
       <c r="G122" t="n">
         <v>54.222929</v>
@@ -4541,7 +4652,10 @@
         <v>54.140034</v>
       </c>
       <c r="J122" t="n">
-        <v>31.758988</v>
+        <v>15.330468</v>
+      </c>
+      <c r="K122" t="n">
+        <v>46.895959</v>
       </c>
     </row>
     <row r="123">
@@ -4550,32 +4664,33 @@
           <t>運動休閒右上上市</t>
         </is>
       </c>
-      <c r="B123" t="n">
-        <v>636.16023</v>
-      </c>
+      <c r="B123" t="inlineStr"/>
       <c r="C123" t="n">
-        <v>147.854351</v>
+        <v>3.173968</v>
       </c>
       <c r="D123" t="n">
-        <v>161.276417</v>
+        <v>6.829026</v>
       </c>
       <c r="E123" t="n">
-        <v>156.233187</v>
+        <v>14.189534</v>
       </c>
       <c r="F123" t="n">
-        <v>127.930135</v>
+        <v>8.780303999999999</v>
       </c>
       <c r="G123" t="n">
-        <v>222.315562</v>
+        <v>8.784293999999999</v>
       </c>
       <c r="H123" t="n">
-        <v>159.66203</v>
+        <v>4.563235</v>
       </c>
       <c r="I123" t="n">
-        <v>173.07071</v>
+        <v>19.402717</v>
       </c>
       <c r="J123" t="n">
-        <v>149.450741</v>
+        <v>10.267939</v>
+      </c>
+      <c r="K123" t="n">
+        <v>4.269063</v>
       </c>
     </row>
     <row r="124">
@@ -4584,32 +4699,33 @@
           <t>運動休閒右上上櫃</t>
         </is>
       </c>
-      <c r="B124" t="n">
-        <v>0.002807</v>
-      </c>
+      <c r="B124" t="inlineStr"/>
       <c r="C124" t="n">
-        <v>0.004426</v>
+        <v>0.003218</v>
       </c>
       <c r="D124" t="n">
-        <v>0.008544</v>
+        <v>0.007213</v>
       </c>
       <c r="E124" t="n">
-        <v>0.007512</v>
+        <v>0.006858</v>
       </c>
       <c r="F124" t="n">
-        <v>0.008066</v>
+        <v>0.008021</v>
       </c>
       <c r="G124" t="n">
-        <v>0.00397</v>
+        <v>0.003447</v>
       </c>
       <c r="H124" t="n">
-        <v>0.003778</v>
+        <v>0.003155</v>
       </c>
       <c r="I124" t="n">
-        <v>0.006495</v>
+        <v>0.006757</v>
       </c>
       <c r="J124" t="n">
-        <v>0.002192</v>
+        <v>0.002266</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.000998</v>
       </c>
     </row>
     <row r="125">
@@ -4618,32 +4734,33 @@
           <t>運動休閒右下上市</t>
         </is>
       </c>
-      <c r="B125" t="n">
-        <v>905.133794</v>
-      </c>
+      <c r="B125" t="inlineStr"/>
       <c r="C125" t="n">
-        <v>491.960239</v>
+        <v>534.171991</v>
       </c>
       <c r="D125" t="n">
-        <v>431.198429</v>
+        <v>465.256605</v>
       </c>
       <c r="E125" t="n">
-        <v>574.917972</v>
+        <v>612.98116</v>
       </c>
       <c r="F125" t="n">
-        <v>437.072996</v>
+        <v>505.281862</v>
       </c>
       <c r="G125" t="n">
-        <v>441.590088</v>
+        <v>528.3968640000001</v>
       </c>
       <c r="H125" t="n">
-        <v>449.552373</v>
+        <v>526.544919</v>
       </c>
       <c r="I125" t="n">
-        <v>413.635324</v>
+        <v>466.358989</v>
       </c>
       <c r="J125" t="n">
-        <v>473.00502</v>
+        <v>513.529666</v>
+      </c>
+      <c r="K125" t="n">
+        <v>849.426072</v>
       </c>
     </row>
     <row r="126">
@@ -4652,32 +4769,33 @@
           <t>運動休閒右下上櫃</t>
         </is>
       </c>
-      <c r="B126" t="n">
-        <v>0.013357</v>
-      </c>
+      <c r="B126" t="inlineStr"/>
       <c r="C126" t="n">
-        <v>0.008547000000000001</v>
+        <v>0.008888</v>
       </c>
       <c r="D126" t="n">
-        <v>0.012284</v>
+        <v>0.012488</v>
       </c>
       <c r="E126" t="n">
-        <v>0.005907</v>
+        <v>0.00653</v>
       </c>
       <c r="F126" t="n">
-        <v>0.005639</v>
+        <v>0.005962</v>
       </c>
       <c r="G126" t="n">
-        <v>0.004976</v>
+        <v>0.005354</v>
       </c>
       <c r="H126" t="n">
-        <v>0.003873</v>
+        <v>0.004094</v>
       </c>
       <c r="I126" t="n">
-        <v>0.00535</v>
+        <v>0.005517</v>
       </c>
       <c r="J126" t="n">
-        <v>0.005399</v>
+        <v>0.005495</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.011286</v>
       </c>
     </row>
     <row r="127">
@@ -4686,32 +4804,33 @@
           <t>運動休閒平上市</t>
         </is>
       </c>
-      <c r="B127" t="n">
-        <v>16.909733</v>
-      </c>
+      <c r="B127" t="inlineStr"/>
       <c r="C127" t="n">
-        <v>7.26905</v>
+        <v>109.737681</v>
       </c>
       <c r="D127" t="n">
-        <v>11.696813</v>
+        <v>132.086028</v>
       </c>
       <c r="E127" t="n">
-        <v>8.888235</v>
+        <v>112.8687</v>
       </c>
       <c r="F127" t="n">
-        <v>47.479196</v>
+        <v>98.42016099999999</v>
       </c>
       <c r="G127" t="n">
-        <v>88.51274100000001</v>
+        <v>215.237233</v>
       </c>
       <c r="H127" t="n">
-        <v>83.666366</v>
+        <v>161.772615</v>
       </c>
       <c r="I127" t="n">
-        <v>59.722284</v>
+        <v>160.666612</v>
       </c>
       <c r="J127" t="n">
-        <v>42.191244</v>
+        <v>140.8494</v>
+      </c>
+      <c r="K127" t="n">
+        <v>161.143466</v>
       </c>
     </row>
     <row r="128">
@@ -4720,32 +4839,33 @@
           <t>運動休閒平上櫃</t>
         </is>
       </c>
-      <c r="B128" t="n">
-        <v>0.000374</v>
-      </c>
+      <c r="B128" t="inlineStr"/>
       <c r="C128" t="n">
-        <v>0.000341</v>
+        <v>0.001208</v>
       </c>
       <c r="D128" t="n">
-        <v>0.000204</v>
+        <v>0.001331</v>
       </c>
       <c r="E128" t="n">
-        <v>0.000623</v>
+        <v>0.000654</v>
       </c>
       <c r="F128" t="n">
-        <v>0.001134</v>
+        <v>0.000856</v>
       </c>
       <c r="G128" t="n">
-        <v>0.000725</v>
+        <v>0.00087</v>
       </c>
       <c r="H128" t="n">
-        <v>0.000571</v>
+        <v>0.000973</v>
       </c>
       <c r="I128" t="n">
-        <v>0.00091</v>
+        <v>0.000481</v>
       </c>
       <c r="J128" t="n">
-        <v>0.000621</v>
+        <v>0.000451</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.00085</v>
       </c>
     </row>
     <row r="129">
@@ -4754,32 +4874,33 @@
           <t>金融保險右上上市</t>
         </is>
       </c>
-      <c r="B129" t="n">
-        <v>45554.511467</v>
-      </c>
+      <c r="B129" t="inlineStr"/>
       <c r="C129" t="n">
-        <v>17584.706175</v>
+        <v>17943.773972</v>
       </c>
       <c r="D129" t="n">
-        <v>16987.289529</v>
+        <v>17340.268633</v>
       </c>
       <c r="E129" t="n">
-        <v>17478.522511</v>
+        <v>17688.882236</v>
       </c>
       <c r="F129" t="n">
-        <v>10882.35721</v>
+        <v>11082.751805</v>
       </c>
       <c r="G129" t="n">
-        <v>19643.829874</v>
+        <v>19921.687985</v>
       </c>
       <c r="H129" t="n">
-        <v>17163.268297</v>
+        <v>17409.609172</v>
       </c>
       <c r="I129" t="n">
-        <v>24618.524731</v>
+        <v>24968.988046</v>
       </c>
       <c r="J129" t="n">
-        <v>16298.205375</v>
+        <v>16528.964768</v>
+      </c>
+      <c r="K129" t="n">
+        <v>14024.486224</v>
       </c>
     </row>
     <row r="130">
@@ -4789,7 +4910,7 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>489.87573</v>
+        <v>0</v>
       </c>
       <c r="C130" t="n">
         <v>274.286538</v>
@@ -4804,16 +4925,19 @@
         <v>244.900842</v>
       </c>
       <c r="G130" t="n">
-        <v>387.63469</v>
+        <v>365.107306</v>
       </c>
       <c r="H130" t="n">
         <v>265.348802</v>
       </c>
       <c r="I130" t="n">
-        <v>233.42015</v>
+        <v>210.851143</v>
       </c>
       <c r="J130" t="n">
-        <v>116.899227</v>
+        <v>100.665858</v>
+      </c>
+      <c r="K130" t="n">
+        <v>581.610311</v>
       </c>
     </row>
     <row r="131">
@@ -4822,32 +4946,29 @@
           <t>金融保險平上市</t>
         </is>
       </c>
-      <c r="B131" t="n">
-        <v>321.424823</v>
-      </c>
-      <c r="C131" t="n">
-        <v>362.141174</v>
-      </c>
-      <c r="D131" t="n">
-        <v>354.572106</v>
-      </c>
+      <c r="B131" t="inlineStr"/>
+      <c r="C131" t="inlineStr"/>
+      <c r="D131" t="inlineStr"/>
       <c r="E131" t="n">
-        <v>228.885439</v>
+        <v>16.324356</v>
       </c>
       <c r="F131" t="n">
-        <v>209.691372</v>
+        <v>6.437949</v>
       </c>
       <c r="G131" t="n">
-        <v>280.204653</v>
+        <v>22.527384</v>
       </c>
       <c r="H131" t="n">
-        <v>256.305102</v>
+        <v>7.187692</v>
       </c>
       <c r="I131" t="n">
-        <v>351.325567</v>
+        <v>22.569007</v>
       </c>
       <c r="J131" t="n">
-        <v>464.231308</v>
+        <v>245.982012</v>
+      </c>
+      <c r="K131" t="n">
+        <v>192.893999</v>
       </c>
     </row>
     <row r="132">
@@ -4856,32 +4977,33 @@
           <t>金融業右上上櫃</t>
         </is>
       </c>
-      <c r="B132" t="n">
-        <v>0.287552</v>
-      </c>
+      <c r="B132" t="inlineStr"/>
       <c r="C132" t="n">
-        <v>0.50264</v>
+        <v>0.503962</v>
       </c>
       <c r="D132" t="n">
-        <v>0.511979</v>
+        <v>0.512541</v>
       </c>
       <c r="E132" t="n">
-        <v>0.300829</v>
+        <v>0.301573</v>
       </c>
       <c r="F132" t="n">
-        <v>0.200969</v>
+        <v>0.201194</v>
       </c>
       <c r="G132" t="n">
-        <v>0.161656</v>
+        <v>0.161718</v>
       </c>
       <c r="H132" t="n">
-        <v>0.400318</v>
+        <v>0.400568</v>
       </c>
       <c r="I132" t="n">
-        <v>0.34688</v>
+        <v>0.347004</v>
       </c>
       <c r="J132" t="n">
-        <v>0.207437</v>
+        <v>0.207685</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.328599</v>
       </c>
     </row>
     <row r="133">
@@ -4890,9 +5012,7 @@
           <t>金融業右下上櫃</t>
         </is>
       </c>
-      <c r="B133" t="n">
-        <v>0.036779</v>
-      </c>
+      <c r="B133" t="inlineStr"/>
       <c r="C133" t="n">
         <v>0.053885</v>
       </c>
@@ -4917,1400 +5037,1389 @@
       <c r="J133" t="n">
         <v>0.030934</v>
       </c>
+      <c r="K133" t="n">
+        <v>0.062779</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>金融業平上櫃</t>
-        </is>
-      </c>
-      <c r="B134" t="n">
-        <v>0.000309</v>
-      </c>
+          <t>鋼鐵工業右上上市</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr"/>
       <c r="C134" t="n">
-        <v>0.001322</v>
+        <v>539.900084</v>
       </c>
       <c r="D134" t="n">
-        <v>0.000562</v>
+        <v>1123.675553</v>
       </c>
       <c r="E134" t="n">
-        <v>0.000744</v>
+        <v>1454.599133</v>
       </c>
       <c r="F134" t="n">
-        <v>0.000225</v>
+        <v>1512.060135</v>
       </c>
       <c r="G134" t="n">
-        <v>6.2e-05</v>
+        <v>1695.675298</v>
       </c>
       <c r="H134" t="n">
-        <v>0.00025</v>
+        <v>2390.322117</v>
       </c>
       <c r="I134" t="n">
-        <v>0.000124</v>
+        <v>4730.164716</v>
       </c>
       <c r="J134" t="n">
-        <v>0.000248</v>
+        <v>1295.19524</v>
+      </c>
+      <c r="K134" t="n">
+        <v>1318.849101</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上上市</t>
-        </is>
-      </c>
-      <c r="B135" t="n">
-        <v>1464.341412</v>
-      </c>
+          <t>鋼鐵工業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr"/>
       <c r="C135" t="n">
-        <v>724.043505</v>
+        <v>0.009807</v>
       </c>
       <c r="D135" t="n">
-        <v>1244.936603</v>
+        <v>0.017194</v>
       </c>
       <c r="E135" t="n">
-        <v>1702.258596</v>
+        <v>0.016825</v>
       </c>
       <c r="F135" t="n">
-        <v>1668.035173</v>
+        <v>0.013359</v>
       </c>
       <c r="G135" t="n">
-        <v>2123.299819</v>
+        <v>0.06475</v>
       </c>
       <c r="H135" t="n">
-        <v>2472.356878</v>
+        <v>0.072867</v>
       </c>
       <c r="I135" t="n">
-        <v>4794.875688</v>
+        <v>0.049926</v>
       </c>
       <c r="J135" t="n">
-        <v>1359.890176</v>
+        <v>0.097998</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.06363175</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上上櫃</t>
+          <t>鋼鐵工業右下上市</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.006179</v>
+        <v>0</v>
       </c>
       <c r="C136" t="n">
-        <v>0.009807</v>
+        <v>693.307398</v>
       </c>
       <c r="D136" t="n">
-        <v>0.017194</v>
+        <v>730.516352</v>
       </c>
       <c r="E136" t="n">
-        <v>0.012871</v>
+        <v>628.6383509999999</v>
       </c>
       <c r="F136" t="n">
-        <v>0.006391</v>
+        <v>580.553522</v>
       </c>
       <c r="G136" t="n">
-        <v>0.044205</v>
+        <v>893.3883949999999</v>
       </c>
       <c r="H136" t="n">
-        <v>0.05524</v>
+        <v>130.607766</v>
       </c>
       <c r="I136" t="n">
-        <v>0.032969</v>
+        <v>871.420516</v>
       </c>
       <c r="J136" t="n">
-        <v>0.090244</v>
+        <v>96.25299099999999</v>
+      </c>
+      <c r="K136" t="n">
+        <v>672.790444</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右下上市</t>
+          <t>鋼鐵工業右下上櫃</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>885.374656</v>
+        <v>0</v>
       </c>
       <c r="C137" t="n">
-        <v>763.805825</v>
+        <v>0.034314</v>
       </c>
       <c r="D137" t="n">
-        <v>845.004486</v>
+        <v>0.035174</v>
       </c>
       <c r="E137" t="n">
-        <v>788.213784</v>
+        <v>0.024203</v>
       </c>
       <c r="F137" t="n">
-        <v>690.654503</v>
+        <v>0.0274235</v>
       </c>
       <c r="G137" t="n">
-        <v>1034.546462</v>
+        <v>0.062666</v>
       </c>
       <c r="H137" t="n">
-        <v>233.418087</v>
+        <v>0.2150343333333334</v>
       </c>
       <c r="I137" t="n">
-        <v>217.573193</v>
+        <v>0.071273</v>
       </c>
       <c r="J137" t="n">
-        <v>147.093842</v>
+        <v>0.048009</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.085073</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B138" t="n">
-        <v>0.2316725</v>
-      </c>
+          <t>鋼鐵工業平上市</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr"/>
       <c r="C138" t="n">
-        <v>0.036438</v>
+        <v>90.580046</v>
       </c>
       <c r="D138" t="n">
-        <v>0.043378</v>
+        <v>124.504458</v>
       </c>
       <c r="E138" t="n">
-        <v>0.028808</v>
+        <v>175.143425</v>
       </c>
       <c r="F138" t="n">
-        <v>0.0357425</v>
+        <v>124.788869</v>
       </c>
       <c r="G138" t="n">
-        <v>0.066598</v>
+        <v>310.398103</v>
       </c>
       <c r="H138" t="n">
-        <v>0.01580233333333333</v>
+        <v>1871.130716</v>
       </c>
       <c r="I138" t="n">
-        <v>0.07816099999999999</v>
+        <v>126.17484</v>
       </c>
       <c r="J138" t="n">
-        <v>0.008527</v>
+        <v>464.115664</v>
+      </c>
+      <c r="K138" t="n">
+        <v>191.129801</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業平上市</t>
-        </is>
-      </c>
-      <c r="B139" t="n">
-        <v>34.929924</v>
-      </c>
+          <t>鋼鐵工業平上櫃</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr"/>
       <c r="C139" t="n">
-        <v>29.547407</v>
+        <v>0.024233</v>
       </c>
       <c r="D139" t="n">
-        <v>35.389744</v>
+        <v>0.009988</v>
       </c>
       <c r="E139" t="n">
-        <v>25.446863</v>
+        <v>0.000393</v>
       </c>
       <c r="F139" t="n">
-        <v>51.27883</v>
+        <v>1.7e-05</v>
       </c>
       <c r="G139" t="n">
-        <v>69.504525</v>
+        <v>7.499999999999999e-05</v>
       </c>
       <c r="H139" t="n">
-        <v>1959.791285</v>
-      </c>
-      <c r="I139" t="n">
-        <v>880.248299</v>
-      </c>
-      <c r="J139" t="n">
-        <v>474.633615</v>
-      </c>
+        <v>0.003635</v>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業平上櫃</t>
-        </is>
-      </c>
-      <c r="B140" t="n">
-        <v>0.00062</v>
-      </c>
+          <t>電器電纜右上上市</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
       <c r="C140" t="n">
-        <v>0.023936</v>
+        <v>548.098926</v>
       </c>
       <c r="D140" t="n">
-        <v>0.009734</v>
+        <v>824.3166649999999</v>
       </c>
       <c r="E140" t="n">
-        <v>0.004176</v>
+        <v>527.970243</v>
       </c>
       <c r="F140" t="n">
-        <v>0.007728</v>
+        <v>281.900372</v>
       </c>
       <c r="G140" t="n">
-        <v>0.022195</v>
+        <v>431.899672</v>
       </c>
       <c r="H140" t="n">
-        <v>0.22675</v>
+        <v>1832.071461</v>
       </c>
       <c r="I140" t="n">
-        <v>0.017764</v>
+        <v>1627.572588</v>
       </c>
       <c r="J140" t="n">
-        <v>0.049575</v>
+        <v>1287.999043</v>
+      </c>
+      <c r="K140" t="n">
+        <v>1121.620276</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右上上市</t>
-        </is>
-      </c>
-      <c r="B141" t="n">
-        <v>1175.370349</v>
-      </c>
+          <t>電器電纜右上上櫃</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr"/>
       <c r="C141" t="n">
-        <v>548.098926</v>
+        <v>0.108179</v>
       </c>
       <c r="D141" t="n">
-        <v>783.843303</v>
+        <v>0.111628</v>
       </c>
       <c r="E141" t="n">
-        <v>459.979709</v>
+        <v>0.09124</v>
       </c>
       <c r="F141" t="n">
-        <v>243.385274</v>
+        <v>0.091242</v>
       </c>
       <c r="G141" t="n">
-        <v>221.164725</v>
+        <v>0.112558</v>
       </c>
       <c r="H141" t="n">
-        <v>2022.93564</v>
+        <v>0.294298</v>
       </c>
       <c r="I141" t="n">
-        <v>1815.128022</v>
+        <v>0.204111</v>
       </c>
       <c r="J141" t="n">
-        <v>1400.305424</v>
+        <v>0.346172</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.360224</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右上上櫃</t>
+          <t>電器電纜右下上市</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.103899</v>
+        <v>0</v>
       </c>
       <c r="C142" t="n">
-        <v>0.108179</v>
+        <v>91.36336300000001</v>
       </c>
       <c r="D142" t="n">
-        <v>0.111628</v>
+        <v>68.343518</v>
       </c>
       <c r="E142" t="n">
-        <v>0.09124</v>
+        <v>43.787224</v>
       </c>
       <c r="F142" t="n">
-        <v>0.091242</v>
+        <v>39.275066</v>
       </c>
       <c r="G142" t="n">
-        <v>0.112558</v>
+        <v>40.346396</v>
       </c>
       <c r="H142" t="n">
-        <v>0.294298</v>
+        <v>55.382448</v>
       </c>
       <c r="I142" t="n">
-        <v>0.204111</v>
+        <v>41.834918</v>
       </c>
       <c r="J142" t="n">
-        <v>0.346172</v>
+        <v>50.073944</v>
+      </c>
+      <c r="K142" t="n">
+        <v>62.3224</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右下上市</t>
-        </is>
-      </c>
-      <c r="B143" t="n">
-        <v>153.170499</v>
-      </c>
+          <t>電器電纜平上市</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
       <c r="C143" t="n">
-        <v>88.494788</v>
+        <v>102.379057</v>
       </c>
       <c r="D143" t="n">
-        <v>65.49185300000001</v>
+        <v>144.381005</v>
       </c>
       <c r="E143" t="n">
-        <v>41.538122</v>
+        <v>90.858828</v>
       </c>
       <c r="F143" t="n">
-        <v>39.275066</v>
+        <v>65.189415</v>
       </c>
       <c r="G143" t="n">
-        <v>40.346396</v>
+        <v>190.952255</v>
       </c>
       <c r="H143" t="n">
-        <v>55.382448</v>
+        <v>190.864179</v>
       </c>
       <c r="I143" t="n">
-        <v>41.834918</v>
+        <v>187.555434</v>
       </c>
       <c r="J143" t="n">
-        <v>50.073944</v>
+        <v>112.306381</v>
+      </c>
+      <c r="K143" t="n">
+        <v>134.839047</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>電器電纜平上市</t>
-        </is>
-      </c>
-      <c r="B144" t="n">
-        <v>205.904956</v>
-      </c>
+          <t>電子通路業右上上市</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr"/>
       <c r="C144" t="n">
-        <v>112.573224</v>
+        <v>4267.165228</v>
       </c>
       <c r="D144" t="n">
-        <v>197.780769</v>
+        <v>5878.449564</v>
       </c>
       <c r="E144" t="n">
-        <v>170.127462</v>
+        <v>8812.877887000001</v>
       </c>
       <c r="F144" t="n">
-        <v>116.254235</v>
+        <v>5102.029062</v>
       </c>
       <c r="G144" t="n">
-        <v>420.560636</v>
+        <v>4956.241487</v>
       </c>
       <c r="H144" t="n">
-        <v>44.797637</v>
+        <v>6977.782428</v>
       </c>
       <c r="I144" t="n">
-        <v>21.090587</v>
+        <v>5324.52747</v>
       </c>
       <c r="J144" t="n">
-        <v>11.466549</v>
+        <v>4295.648634</v>
+      </c>
+      <c r="K144" t="n">
+        <v>4441.152525</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右上上市</t>
-        </is>
-      </c>
-      <c r="B145" t="n">
-        <v>3008.739938</v>
-      </c>
+          <t>電子通路業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
       <c r="C145" t="n">
-        <v>2462.842603</v>
+        <v>0.20052</v>
       </c>
       <c r="D145" t="n">
-        <v>3533.092438</v>
+        <v>0.372864</v>
       </c>
       <c r="E145" t="n">
-        <v>7357.524566</v>
+        <v>0.16613</v>
       </c>
       <c r="F145" t="n">
-        <v>3162.15291</v>
+        <v>0.175534</v>
       </c>
       <c r="G145" t="n">
-        <v>3504.588651</v>
+        <v>0.5631930000000001</v>
       </c>
       <c r="H145" t="n">
-        <v>4790.204438</v>
+        <v>0.470245</v>
       </c>
       <c r="I145" t="n">
-        <v>2482.396615</v>
+        <v>0.335974</v>
       </c>
       <c r="J145" t="n">
-        <v>2196.270989</v>
+        <v>0.56393</v>
+      </c>
+      <c r="K145" t="n">
+        <v>0.809244</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B146" t="n">
-        <v>0.358937</v>
-      </c>
+          <t>電子通路業右下上市</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
       <c r="C146" t="n">
-        <v>0.152499</v>
+        <v>28.032008</v>
       </c>
       <c r="D146" t="n">
-        <v>0.291336</v>
+        <v>25.137513</v>
       </c>
       <c r="E146" t="n">
-        <v>0.107882</v>
+        <v>5.689849</v>
       </c>
       <c r="F146" t="n">
-        <v>0.127115</v>
+        <v>27.712111</v>
       </c>
       <c r="G146" t="n">
-        <v>0.114703</v>
+        <v>18.247482</v>
       </c>
       <c r="H146" t="n">
-        <v>0.131196</v>
+        <v>12.283079</v>
       </c>
       <c r="I146" t="n">
-        <v>0.332757</v>
+        <v>13.321644</v>
       </c>
       <c r="J146" t="n">
-        <v>0.374888</v>
+        <v>11.089148</v>
+      </c>
+      <c r="K146" t="n">
+        <v>13.469439</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右下上市</t>
+          <t>電子通路業右下上櫃</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>38.368699</v>
+        <v>0</v>
       </c>
       <c r="C147" t="n">
-        <v>10.916063</v>
+        <v>0.032335</v>
       </c>
       <c r="D147" t="n">
-        <v>10.344134</v>
+        <v>0.033982</v>
       </c>
       <c r="E147" t="n">
-        <v>5.689849</v>
+        <v>0.173565</v>
       </c>
       <c r="F147" t="n">
-        <v>6.727905</v>
+        <v>0.06376800000000001</v>
       </c>
       <c r="G147" t="n">
-        <v>18.247482</v>
+        <v>0.0418</v>
       </c>
       <c r="H147" t="n">
-        <v>12.283079</v>
+        <v>0.04535</v>
       </c>
       <c r="I147" t="n">
-        <v>13.321644</v>
+        <v>0.081911</v>
       </c>
       <c r="J147" t="n">
-        <v>11.089148</v>
+        <v>0.022376</v>
+      </c>
+      <c r="K147" t="n">
+        <v>0.01177</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B148" t="n">
-        <v>0.035434</v>
-      </c>
+          <t>電子通路業平上市</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
       <c r="C148" t="n">
-        <v>0.032335</v>
+        <v>46.300898</v>
       </c>
       <c r="D148" t="n">
-        <v>0.033982</v>
+        <v>40.35193</v>
       </c>
       <c r="E148" t="n">
-        <v>0.173565</v>
+        <v>82.50335</v>
       </c>
       <c r="F148" t="n">
-        <v>0.06376800000000001</v>
+        <v>75.70770899999999</v>
       </c>
       <c r="G148" t="n">
-        <v>0.0418</v>
+        <v>92.376355</v>
       </c>
       <c r="H148" t="n">
-        <v>0.04535</v>
+        <v>56.915993</v>
       </c>
       <c r="I148" t="n">
-        <v>0.081911</v>
+        <v>37.381351</v>
       </c>
       <c r="J148" t="n">
-        <v>0.022376</v>
+        <v>54.291443</v>
+      </c>
+      <c r="K148" t="n">
+        <v>65.30397000000001</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>電子通路業平上市</t>
-        </is>
-      </c>
-      <c r="B149" t="n">
-        <v>3295.513809</v>
-      </c>
+          <t>電子通路業平上櫃</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
       <c r="C149" t="n">
-        <v>1867.739468</v>
+        <v>0.226128</v>
       </c>
       <c r="D149" t="n">
-        <v>2400.502435</v>
+        <v>0.372122</v>
       </c>
       <c r="E149" t="n">
-        <v>1537.856671</v>
+        <v>0.266881</v>
       </c>
       <c r="F149" t="n">
-        <v>2036.568067</v>
+        <v>0.223138</v>
       </c>
       <c r="G149" t="n">
-        <v>1544.029191</v>
+        <v>0.000586</v>
       </c>
       <c r="H149" t="n">
-        <v>2244.493983</v>
+        <v>0.001673</v>
       </c>
       <c r="I149" t="n">
-        <v>2879.512206</v>
-      </c>
-      <c r="J149" t="n">
-        <v>2031.06244</v>
-      </c>
+        <v>0.263543</v>
+      </c>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>電子通路業平上櫃</t>
-        </is>
-      </c>
-      <c r="B150" t="n">
-        <v>0.238213</v>
-      </c>
+          <t>電子零組件業右上上市</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
       <c r="C150" t="n">
-        <v>0.288456</v>
+        <v>189211.270418</v>
       </c>
       <c r="D150" t="n">
-        <v>0.481713</v>
+        <v>204156.092618</v>
       </c>
       <c r="E150" t="n">
-        <v>0.334162</v>
+        <v>203798.645385</v>
       </c>
       <c r="F150" t="n">
-        <v>0.277588</v>
+        <v>192674.347327</v>
       </c>
       <c r="G150" t="n">
-        <v>0.466732</v>
+        <v>192587.977924</v>
       </c>
       <c r="H150" t="n">
-        <v>0.359879</v>
+        <v>189802.722785</v>
       </c>
       <c r="I150" t="n">
-        <v>0.272872</v>
+        <v>238921.442908</v>
       </c>
       <c r="J150" t="n">
-        <v>0.205556</v>
+        <v>303665.836696</v>
+      </c>
+      <c r="K150" t="n">
+        <v>337220.178575</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右上上市</t>
-        </is>
-      </c>
-      <c r="B151" t="n">
-        <v>134799.474724</v>
-      </c>
+          <t>電子零組件業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
       <c r="C151" t="n">
-        <v>159551.687657</v>
+        <v>40.781232</v>
       </c>
       <c r="D151" t="n">
-        <v>165334.465168</v>
+        <v>44.057549</v>
       </c>
       <c r="E151" t="n">
-        <v>202291.836966</v>
+        <v>26.401065</v>
       </c>
       <c r="F151" t="n">
-        <v>189680.575138</v>
+        <v>37.422991</v>
       </c>
       <c r="G151" t="n">
-        <v>168771.19836</v>
+        <v>25.173246</v>
       </c>
       <c r="H151" t="n">
-        <v>175055.014039</v>
+        <v>28.553205</v>
       </c>
       <c r="I151" t="n">
-        <v>229808.256647</v>
+        <v>43.43267</v>
       </c>
       <c r="J151" t="n">
-        <v>295285.351175</v>
+        <v>57.674496</v>
+      </c>
+      <c r="K151" t="n">
+        <v>54.274901</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右上上櫃</t>
+          <t>電子零組件業右下上市</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>41.041835</v>
+        <v>0</v>
       </c>
       <c r="C152" t="n">
-        <v>39.551208</v>
+        <v>900.024335</v>
       </c>
       <c r="D152" t="n">
-        <v>41.06388</v>
+        <v>1389.904697</v>
       </c>
       <c r="E152" t="n">
-        <v>25.823852</v>
+        <v>929.4195989999999</v>
       </c>
       <c r="F152" t="n">
-        <v>37.603645</v>
+        <v>729.336978</v>
       </c>
       <c r="G152" t="n">
-        <v>29.674985</v>
+        <v>949.087115</v>
       </c>
       <c r="H152" t="n">
-        <v>28.779912</v>
+        <v>1106.993769</v>
       </c>
       <c r="I152" t="n">
-        <v>49.045555</v>
+        <v>929.206581</v>
       </c>
       <c r="J152" t="n">
-        <v>64.95413499999999</v>
+        <v>823.3309410000001</v>
+      </c>
+      <c r="K152" t="n">
+        <v>1348.323574</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右下上市</t>
+          <t>電子零組件業右下上櫃</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>4079.414857</v>
+        <v>0</v>
       </c>
       <c r="C153" t="n">
-        <v>2976.363321</v>
+        <v>0.536405</v>
       </c>
       <c r="D153" t="n">
-        <v>4168.602855</v>
+        <v>0.644922</v>
       </c>
       <c r="E153" t="n">
-        <v>7165.028589</v>
+        <v>0.564061</v>
       </c>
       <c r="F153" t="n">
-        <v>3340.325803</v>
+        <v>0.605889</v>
       </c>
       <c r="G153" t="n">
-        <v>5280.673074</v>
+        <v>0.32839</v>
       </c>
       <c r="H153" t="n">
-        <v>2364.317114</v>
+        <v>0.904235</v>
       </c>
       <c r="I153" t="n">
-        <v>2046.42661</v>
+        <v>0.619853</v>
       </c>
       <c r="J153" t="n">
-        <v>2344.140071</v>
+        <v>0.56917</v>
+      </c>
+      <c r="K153" t="n">
+        <v>1.030055</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B154" t="n">
-        <v>1.15189</v>
-      </c>
+          <t>電子零組件業平上市</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr"/>
       <c r="C154" t="n">
-        <v>0.8619560000000001</v>
+        <v>2792.735522</v>
       </c>
       <c r="D154" t="n">
-        <v>1.339275</v>
+        <v>4865.581261</v>
       </c>
       <c r="E154" t="n">
-        <v>0.87322</v>
+        <v>7314.585275</v>
       </c>
       <c r="F154" t="n">
-        <v>0.901962</v>
+        <v>3323.928044</v>
       </c>
       <c r="G154" t="n">
-        <v>0.574451</v>
+        <v>4869.715431</v>
       </c>
       <c r="H154" t="n">
-        <v>1.249787</v>
+        <v>6364.882629</v>
       </c>
       <c r="I154" t="n">
-        <v>1.073411</v>
+        <v>1607.896464</v>
       </c>
       <c r="J154" t="n">
-        <v>0.757948</v>
+        <v>1967.018327</v>
+      </c>
+      <c r="K154" t="n">
+        <v>3271.617284</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業平上市</t>
-        </is>
-      </c>
-      <c r="B155" t="n">
-        <v>51156.753787</v>
-      </c>
+          <t>電子零組件業平上櫃</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr"/>
       <c r="C155" t="n">
-        <v>30402.918995</v>
+        <v>0.342766</v>
       </c>
       <c r="D155" t="n">
-        <v>40934.241108</v>
+        <v>0.27792</v>
       </c>
       <c r="E155" t="n">
-        <v>2613.190429</v>
+        <v>0.266301</v>
       </c>
       <c r="F155" t="n">
-        <v>3730.19601</v>
+        <v>0.322656</v>
       </c>
       <c r="G155" t="n">
-        <v>24378.716212</v>
+        <v>1.00409</v>
       </c>
       <c r="H155" t="n">
-        <v>19899.378642</v>
+        <v>0.317373</v>
       </c>
       <c r="I155" t="n">
-        <v>9628.734207</v>
+        <v>0.421761</v>
       </c>
       <c r="J155" t="n">
-        <v>8858.221991</v>
+        <v>0.366252</v>
+      </c>
+      <c r="K155" t="n">
+        <v>0.498292</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業平上櫃</t>
-        </is>
-      </c>
-      <c r="B156" t="n">
-        <v>3.798308</v>
-      </c>
+          <t>電機機械右上上市</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr"/>
       <c r="C156" t="n">
-        <v>2.451794</v>
+        <v>13952.53928</v>
       </c>
       <c r="D156" t="n">
-        <v>3.729705</v>
+        <v>21941.412373</v>
       </c>
       <c r="E156" t="n">
-        <v>1.601472</v>
+        <v>20653.023269</v>
       </c>
       <c r="F156" t="n">
-        <v>1.503673</v>
+        <v>17783.28272</v>
       </c>
       <c r="G156" t="n">
-        <v>3.26944</v>
+        <v>17698.696071</v>
       </c>
       <c r="H156" t="n">
-        <v>4.11166</v>
+        <v>17107.566288</v>
       </c>
       <c r="I156" t="n">
-        <v>3.518995</v>
+        <v>21736.79682</v>
       </c>
       <c r="J156" t="n">
-        <v>3.443462</v>
+        <v>20870.148901</v>
+      </c>
+      <c r="K156" t="n">
+        <v>9721.052197000001</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>電機機械右上上市</t>
-        </is>
-      </c>
-      <c r="B157" t="n">
-        <v>16702.322234</v>
-      </c>
+          <t>電機機械右上上櫃</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr"/>
       <c r="C157" t="n">
-        <v>12518.33041</v>
+        <v>0.9784</v>
       </c>
       <c r="D157" t="n">
-        <v>20018.210526</v>
+        <v>1.234403</v>
       </c>
       <c r="E157" t="n">
-        <v>19665.379644</v>
+        <v>0.736514</v>
       </c>
       <c r="F157" t="n">
-        <v>16041.960584</v>
+        <v>0.901869</v>
       </c>
       <c r="G157" t="n">
-        <v>16397.971383</v>
+        <v>2.045405</v>
       </c>
       <c r="H157" t="n">
-        <v>15648.185563</v>
+        <v>1.835066</v>
       </c>
       <c r="I157" t="n">
-        <v>20759.210972</v>
+        <v>3.495789</v>
       </c>
       <c r="J157" t="n">
-        <v>19153.740726</v>
+        <v>2.265916</v>
+      </c>
+      <c r="K157" t="n">
+        <v>1.696695</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>電機機械右上上櫃</t>
-        </is>
-      </c>
-      <c r="B158" t="n">
-        <v>0.488623</v>
-      </c>
+          <t>電機機械右下上市</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr"/>
       <c r="C158" t="n">
-        <v>0.322147</v>
+        <v>859.034638</v>
       </c>
       <c r="D158" t="n">
-        <v>0.406659</v>
+        <v>522.534125</v>
       </c>
       <c r="E158" t="n">
-        <v>0.255269</v>
+        <v>560.189292</v>
       </c>
       <c r="F158" t="n">
-        <v>0.281269</v>
+        <v>497.79934625</v>
       </c>
       <c r="G158" t="n">
-        <v>1.930055</v>
+        <v>484.273872</v>
       </c>
       <c r="H158" t="n">
-        <v>1.779102</v>
+        <v>1003.984237</v>
       </c>
       <c r="I158" t="n">
-        <v>3.481795</v>
+        <v>1204.163042</v>
       </c>
       <c r="J158" t="n">
-        <v>2.240837</v>
+        <v>803.446879</v>
+      </c>
+      <c r="K158" t="n">
+        <v>871.467301</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>電機機械右下上市</t>
+          <t>電機機械右下上櫃</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>2519.834647</v>
+        <v>0</v>
       </c>
       <c r="C159" t="n">
-        <v>884.234767</v>
+        <v>0.07742599999999999</v>
       </c>
       <c r="D159" t="n">
-        <v>960.535046</v>
+        <v>0.080253</v>
       </c>
       <c r="E159" t="n">
-        <v>1205.127393</v>
+        <v>0.07188633333333333</v>
       </c>
       <c r="F159" t="n">
-        <v>1278.56809225</v>
+        <v>0.065122</v>
       </c>
       <c r="G159" t="n">
-        <v>1352.800315</v>
+        <v>0.079804</v>
       </c>
       <c r="H159" t="n">
-        <v>1402.402289</v>
+        <v>0.105622</v>
       </c>
       <c r="I159" t="n">
-        <v>905.25175</v>
+        <v>0.08888875</v>
       </c>
       <c r="J159" t="n">
-        <v>1280.301169</v>
+        <v>0.08030900000000001</v>
+      </c>
+      <c r="K159" t="n">
+        <v>0.14932475</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>電機機械右下上櫃</t>
-        </is>
-      </c>
-      <c r="B160" t="n">
-        <v>0.2448195</v>
-      </c>
+          <t>電機機械平上市</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr"/>
       <c r="C160" t="n">
-        <v>0.092209</v>
+        <v>923.531349</v>
       </c>
       <c r="D160" t="n">
-        <v>0.100141</v>
+        <v>964.633451</v>
       </c>
       <c r="E160" t="n">
-        <v>0.1047293333333333</v>
+        <v>793.736661</v>
       </c>
       <c r="F160" t="n">
-        <v>0.070176</v>
+        <v>940.936506</v>
       </c>
       <c r="G160" t="n">
-        <v>0.085379</v>
+        <v>1314.555229</v>
       </c>
       <c r="H160" t="n">
-        <v>0.128986</v>
+        <v>1599.750557</v>
       </c>
       <c r="I160" t="n">
-        <v>0.09494175000000001</v>
+        <v>1141.213827</v>
       </c>
       <c r="J160" t="n">
-        <v>0.145845</v>
+        <v>1297.029295</v>
+      </c>
+      <c r="K160" t="n">
+        <v>1389.228828</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>電機機械平上市</t>
-        </is>
-      </c>
-      <c r="B161" t="n">
-        <v>2647.954011</v>
-      </c>
+          <t>電機機械平上櫃</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr"/>
       <c r="C161" t="n">
-        <v>2332.54009</v>
+        <v>0.091183</v>
       </c>
       <c r="D161" t="n">
-        <v>2449.834377</v>
+        <v>0.152994</v>
       </c>
       <c r="E161" t="n">
-        <v>1136.442185</v>
+        <v>0.196578</v>
       </c>
       <c r="F161" t="n">
-        <v>1901.489896</v>
+        <v>0.138342</v>
       </c>
       <c r="G161" t="n">
-        <v>1746.753474</v>
+        <v>0.033899</v>
       </c>
       <c r="H161" t="n">
-        <v>2660.71323</v>
+        <v>0.080669</v>
       </c>
       <c r="I161" t="n">
-        <v>2417.710967</v>
+        <v>0.06519899999999999</v>
       </c>
       <c r="J161" t="n">
-        <v>2536.58318</v>
+        <v>0.099492</v>
+      </c>
+      <c r="K161" t="n">
+        <v>0.047676</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>電機機械平上櫃</t>
-        </is>
-      </c>
-      <c r="B162" t="n">
-        <v>0.83971</v>
-      </c>
+          <t>電腦及週邊設備業右上上市</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr"/>
       <c r="C162" t="n">
-        <v>0.744787</v>
+        <v>33027.484691</v>
       </c>
       <c r="D162" t="n">
-        <v>0.979351</v>
+        <v>42588.00656</v>
       </c>
       <c r="E162" t="n">
-        <v>0.675076</v>
+        <v>30947.277086</v>
       </c>
       <c r="F162" t="n">
-        <v>0.768943</v>
+        <v>31226.702936</v>
       </c>
       <c r="G162" t="n">
-        <v>0.155259</v>
+        <v>43544.851477</v>
       </c>
       <c r="H162" t="n">
-        <v>0.127739</v>
+        <v>38030.459823</v>
       </c>
       <c r="I162" t="n">
-        <v>0.081984</v>
+        <v>43116.131312</v>
       </c>
       <c r="J162" t="n">
-        <v>0.084762</v>
+        <v>38475.016145</v>
+      </c>
+      <c r="K162" t="n">
+        <v>57387.377591</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上上市</t>
-        </is>
-      </c>
-      <c r="B163" t="n">
-        <v>56799.699296</v>
-      </c>
+          <t>電腦及週邊設備業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr"/>
       <c r="C163" t="n">
-        <v>33251.31356</v>
+        <v>7.514641</v>
       </c>
       <c r="D163" t="n">
-        <v>43335.107824</v>
+        <v>6.604121</v>
       </c>
       <c r="E163" t="n">
-        <v>31110.029175</v>
+        <v>4.522535</v>
       </c>
       <c r="F163" t="n">
-        <v>31285.393991</v>
+        <v>3.231759</v>
       </c>
       <c r="G163" t="n">
-        <v>43834.111024</v>
+        <v>5.96795</v>
       </c>
       <c r="H163" t="n">
-        <v>38144.865106</v>
+        <v>8.116228</v>
       </c>
       <c r="I163" t="n">
-        <v>42702.884281</v>
+        <v>3.257771</v>
       </c>
       <c r="J163" t="n">
-        <v>38943.878033</v>
+        <v>4.518528</v>
+      </c>
+      <c r="K163" t="n">
+        <v>5.078686</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B164" t="n">
-        <v>2.548452</v>
-      </c>
+          <t>電腦及週邊設備業右下上市</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr"/>
       <c r="C164" t="n">
-        <v>6.445669</v>
+        <v>7475.184712</v>
       </c>
       <c r="D164" t="n">
-        <v>6.813135</v>
+        <v>13609.225923</v>
       </c>
       <c r="E164" t="n">
-        <v>3.458445</v>
+        <v>6486.051783</v>
       </c>
       <c r="F164" t="n">
-        <v>3.286976</v>
+        <v>7857.032012</v>
       </c>
       <c r="G164" t="n">
-        <v>5.63341</v>
+        <v>3699.843837</v>
       </c>
       <c r="H164" t="n">
-        <v>7.647517</v>
+        <v>4448.901824</v>
       </c>
       <c r="I164" t="n">
-        <v>4.386462</v>
+        <v>3383.67531</v>
       </c>
       <c r="J164" t="n">
-        <v>3.744373</v>
+        <v>5495.817378</v>
+      </c>
+      <c r="K164" t="n">
+        <v>6999.368153</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上市</t>
+          <t>電腦及週邊設備業右下上櫃</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>12295.172011</v>
+        <v>0</v>
       </c>
       <c r="C165" t="n">
-        <v>8786.508749000001</v>
+        <v>0.117566</v>
       </c>
       <c r="D165" t="n">
-        <v>15058.478097</v>
+        <v>0.151613</v>
       </c>
       <c r="E165" t="n">
-        <v>8090.653738</v>
+        <v>0.1123185</v>
       </c>
       <c r="F165" t="n">
-        <v>8372.407546</v>
+        <v>0.078399</v>
       </c>
       <c r="G165" t="n">
-        <v>5011.133429</v>
+        <v>0.139536</v>
       </c>
       <c r="H165" t="n">
-        <v>9046.637635999999</v>
+        <v>0.133896</v>
       </c>
       <c r="I165" t="n">
-        <v>6167.77495</v>
+        <v>0.0814</v>
       </c>
       <c r="J165" t="n">
-        <v>7418.865709</v>
+        <v>0.14195925</v>
+      </c>
+      <c r="K165" t="n">
+        <v>0.287144</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B166" t="n">
-        <v>0.141577</v>
-      </c>
+          <t>電腦及週邊設備業平上市</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr"/>
       <c r="C166" t="n">
-        <v>0.127289</v>
+        <v>2257.553972</v>
       </c>
       <c r="D166" t="n">
-        <v>0.168679</v>
+        <v>2625.672224</v>
       </c>
       <c r="E166" t="n">
-        <v>0.1089475</v>
+        <v>2096.083709</v>
       </c>
       <c r="F166" t="n">
-        <v>0.087995</v>
+        <v>1216.25613</v>
       </c>
       <c r="G166" t="n">
-        <v>0.151576</v>
+        <v>2059.160818</v>
       </c>
       <c r="H166" t="n">
-        <v>0.163469</v>
+        <v>5322.961927</v>
       </c>
       <c r="I166" t="n">
-        <v>0.09155199999999999</v>
+        <v>3275.555912</v>
       </c>
       <c r="J166" t="n">
-        <v>0.15035425</v>
+        <v>2815.623009</v>
+      </c>
+      <c r="K166" t="n">
+        <v>6032.780847</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上市</t>
-        </is>
-      </c>
-      <c r="B167" t="n">
-        <v>1160.820659</v>
-      </c>
+          <t>電腦及週邊設備業平上櫃</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr"/>
       <c r="C167" t="n">
-        <v>722.401066</v>
+        <v>0.208538</v>
       </c>
       <c r="D167" t="n">
-        <v>429.318786</v>
+        <v>0.456795</v>
       </c>
       <c r="E167" t="n">
-        <v>328.729665</v>
+        <v>0.239754</v>
       </c>
       <c r="F167" t="n">
-        <v>642.189541</v>
+        <v>0.102567</v>
       </c>
       <c r="G167" t="n">
-        <v>458.611679</v>
+        <v>0.160217</v>
       </c>
       <c r="H167" t="n">
-        <v>610.820832</v>
+        <v>0.216791</v>
       </c>
       <c r="I167" t="n">
-        <v>904.703303</v>
+        <v>0.146328</v>
       </c>
       <c r="J167" t="n">
-        <v>423.71279</v>
+        <v>0.150315</v>
+      </c>
+      <c r="K167" t="n">
+        <v>0.28927</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上櫃</t>
-        </is>
-      </c>
-      <c r="B168" t="n">
-        <v>3.247679</v>
-      </c>
+          <t>食品工業右上上市</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr"/>
       <c r="C168" t="n">
-        <v>2.020245</v>
+        <v>12.361364</v>
       </c>
       <c r="D168" t="n">
-        <v>1.749221</v>
+        <v>24.985346</v>
       </c>
       <c r="E168" t="n">
-        <v>3.07077</v>
+        <v>19.176035</v>
       </c>
       <c r="F168" t="n">
-        <v>1.472591</v>
+        <v>18.254504</v>
       </c>
       <c r="G168" t="n">
-        <v>1.429916</v>
+        <v>15.030035</v>
       </c>
       <c r="H168" t="n">
-        <v>1.54623</v>
+        <v>22.714533</v>
       </c>
       <c r="I168" t="n">
-        <v>0.896875</v>
+        <v>18.953213</v>
       </c>
       <c r="J168" t="n">
-        <v>1.494557</v>
+        <v>13.274733</v>
+      </c>
+      <c r="K168" t="n">
+        <v>16.692089</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>食品工業右上上市</t>
-        </is>
-      </c>
-      <c r="B169" t="n">
-        <v>15.076274</v>
-      </c>
+          <t>食品工業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr"/>
       <c r="C169" t="n">
-        <v>6.825473</v>
+        <v>0.003652</v>
       </c>
       <c r="D169" t="n">
-        <v>10.989736</v>
+        <v>0.005167</v>
       </c>
       <c r="E169" t="n">
-        <v>586.277846</v>
+        <v>0.002534</v>
       </c>
       <c r="F169" t="n">
-        <v>7.264615</v>
+        <v>0.004008</v>
       </c>
       <c r="G169" t="n">
-        <v>8.02271</v>
+        <v>0.005365</v>
       </c>
       <c r="H169" t="n">
-        <v>11.865974</v>
+        <v>0.005112</v>
       </c>
       <c r="I169" t="n">
-        <v>16.580074</v>
+        <v>0.007178</v>
       </c>
       <c r="J169" t="n">
-        <v>7.674888</v>
+        <v>0.006919</v>
+      </c>
+      <c r="K169" t="n">
+        <v>0.008226000000000001</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>食品工業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B170" t="n">
-        <v>0.002855</v>
-      </c>
+          <t>食品工業右下上市</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr"/>
       <c r="C170" t="n">
-        <v>0.002955</v>
+        <v>622.669405</v>
       </c>
       <c r="D170" t="n">
-        <v>0.004336</v>
+        <v>898.831877</v>
       </c>
       <c r="E170" t="n">
-        <v>0.002534</v>
+        <v>293.333234</v>
       </c>
       <c r="F170" t="n">
-        <v>0.001886</v>
+        <v>649.727039</v>
       </c>
       <c r="G170" t="n">
-        <v>0.003556</v>
+        <v>802.013354</v>
       </c>
       <c r="H170" t="n">
-        <v>0.004412</v>
+        <v>777.085777</v>
       </c>
       <c r="I170" t="n">
-        <v>0.005225</v>
+        <v>703.082083</v>
       </c>
       <c r="J170" t="n">
-        <v>0.005884</v>
+        <v>1688.815661</v>
+      </c>
+      <c r="K170" t="n">
+        <v>1095.910492</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t>食品工業右下上市</t>
+          <t>食品工業右下上櫃</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>652.643063</v>
+        <v>0</v>
       </c>
       <c r="C171" t="n">
-        <v>278.579927</v>
+        <v>0.006211</v>
       </c>
       <c r="D171" t="n">
-        <v>412.232246</v>
+        <v>0.013842</v>
       </c>
       <c r="E171" t="n">
-        <v>284.234782</v>
+        <v>0.010018</v>
       </c>
       <c r="F171" t="n">
-        <v>286.797627</v>
+        <v>0.005706</v>
       </c>
       <c r="G171" t="n">
-        <v>318.886002</v>
+        <v>0.004506</v>
       </c>
       <c r="H171" t="n">
-        <v>261.472583</v>
+        <v>0.008725999999999999</v>
       </c>
       <c r="I171" t="n">
-        <v>264.272879</v>
+        <v>0.006001</v>
       </c>
       <c r="J171" t="n">
-        <v>1672.273661</v>
+        <v>0.007215</v>
+      </c>
+      <c r="K171" t="n">
+        <v>0.013382</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t>食品工業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B172" t="n">
-        <v>0.009090000000000001</v>
-      </c>
-      <c r="C172" t="n">
-        <v>0.007544</v>
-      </c>
-      <c r="D172" t="n">
-        <v>0.014792</v>
-      </c>
+          <t>食品工業平上市</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr"/>
+      <c r="C172" t="inlineStr"/>
+      <c r="D172" t="inlineStr"/>
       <c r="E172" t="n">
-        <v>0.01134</v>
-      </c>
-      <c r="F172" t="n">
-        <v>0.010856</v>
-      </c>
-      <c r="G172" t="n">
-        <v>0.005911</v>
-      </c>
-      <c r="H172" t="n">
-        <v>0.010054</v>
-      </c>
-      <c r="I172" t="n">
-        <v>0.006973</v>
-      </c>
-      <c r="J172" t="n">
-        <v>0.010705</v>
-      </c>
+        <v>575.713856</v>
+      </c>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
         <is>
-          <t>食品工業平上市</t>
-        </is>
-      </c>
-      <c r="B173" t="n">
-        <v>1389.010951</v>
-      </c>
-      <c r="C173" t="n">
-        <v>349.625369</v>
-      </c>
-      <c r="D173" t="n">
-        <v>500.595241</v>
-      </c>
+          <t>食品工業平上櫃</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr"/>
+      <c r="C173" t="inlineStr"/>
+      <c r="D173" t="inlineStr"/>
       <c r="E173" t="n">
-        <v>17.710497</v>
+        <v>0.002383</v>
       </c>
       <c r="F173" t="n">
-        <v>373.919301</v>
+        <v>0.002487</v>
       </c>
       <c r="G173" t="n">
-        <v>490.134677</v>
-      </c>
-      <c r="H173" t="n">
-        <v>526.461753</v>
-      </c>
-      <c r="I173" t="n">
-        <v>441.182343</v>
-      </c>
-      <c r="J173" t="n">
-        <v>5.599845</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="1" t="inlineStr">
-        <is>
-          <t>食品工業平上櫃</t>
-        </is>
-      </c>
-      <c r="B174" t="n">
-        <v>0.002604</v>
-      </c>
-      <c r="C174" t="n">
-        <v>0.000697</v>
-      </c>
-      <c r="D174" t="n">
-        <v>0.000831</v>
-      </c>
-      <c r="E174" t="n">
-        <v>0.002383</v>
-      </c>
-      <c r="F174" t="n">
-        <v>0.004609</v>
-      </c>
-      <c r="G174" t="n">
-        <v>0.003325</v>
-      </c>
-      <c r="H174" t="n">
-        <v>0.0007</v>
-      </c>
-      <c r="I174" t="n">
-        <v>0.001953</v>
-      </c>
-      <c r="J174" t="n">
-        <v>0.001035</v>
-      </c>
+        <v>0.001516</v>
+      </c>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Result/analyze_2.xlsx
+++ b/Result/analyze_2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K173"/>
+  <dimension ref="A1:J173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,52 +436,47 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -491,33 +486,32 @@
           <t>光電業右上上市</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="n">
+        <v>115422.481566</v>
+      </c>
       <c r="C2" t="n">
-        <v>79928.792447</v>
+        <v>75436.525366</v>
       </c>
       <c r="D2" t="n">
-        <v>118574.925682</v>
+        <v>46586.686312</v>
       </c>
       <c r="E2" t="n">
-        <v>77016.14013699999</v>
+        <v>51636.891594</v>
       </c>
       <c r="F2" t="n">
-        <v>47630.618118</v>
+        <v>86070.802371</v>
       </c>
       <c r="G2" t="n">
-        <v>52329.13654</v>
+        <v>106432.610774</v>
       </c>
       <c r="H2" t="n">
-        <v>87049.123955</v>
+        <v>74175.14004899999</v>
       </c>
       <c r="I2" t="n">
-        <v>107133.497541</v>
+        <v>106634.769564</v>
       </c>
       <c r="J2" t="n">
-        <v>74782.54464199999</v>
-      </c>
-      <c r="K2" t="n">
-        <v>107205.401757</v>
+        <v>72074.281301</v>
       </c>
     </row>
     <row r="3">
@@ -526,33 +520,32 @@
           <t>光電業右上上櫃</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="n">
+        <v>4.93632</v>
+      </c>
       <c r="C3" t="n">
-        <v>6.987814</v>
+        <v>1.988611</v>
       </c>
       <c r="D3" t="n">
-        <v>5.099475</v>
+        <v>4.200368</v>
       </c>
       <c r="E3" t="n">
-        <v>2.190618</v>
+        <v>6.813472</v>
       </c>
       <c r="F3" t="n">
-        <v>4.812548</v>
+        <v>6.721156</v>
       </c>
       <c r="G3" t="n">
-        <v>6.86136</v>
+        <v>6.072605</v>
       </c>
       <c r="H3" t="n">
-        <v>6.966875</v>
+        <v>12.53609</v>
       </c>
       <c r="I3" t="n">
-        <v>5.827265</v>
+        <v>11.669936</v>
       </c>
       <c r="J3" t="n">
-        <v>12.342156</v>
-      </c>
-      <c r="K3" t="n">
-        <v>10.210951</v>
+        <v>12.236182</v>
       </c>
     </row>
     <row r="4">
@@ -561,33 +554,32 @@
           <t>光電業右下上市</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="n">
+        <v>2192.450429</v>
+      </c>
       <c r="C4" t="n">
-        <v>719.230276</v>
+        <v>1103.326977</v>
       </c>
       <c r="D4" t="n">
-        <v>777.189132</v>
+        <v>1742.583713</v>
       </c>
       <c r="E4" t="n">
-        <v>806.877796</v>
+        <v>898.356579</v>
       </c>
       <c r="F4" t="n">
-        <v>1126.467387</v>
+        <v>1542.59659</v>
       </c>
       <c r="G4" t="n">
-        <v>493.512412</v>
+        <v>627.005644</v>
       </c>
       <c r="H4" t="n">
-        <v>1005.678589</v>
+        <v>809.753993</v>
       </c>
       <c r="I4" t="n">
-        <v>680.281414</v>
+        <v>874.586958</v>
       </c>
       <c r="J4" t="n">
-        <v>252.940066</v>
-      </c>
-      <c r="K4" t="n">
-        <v>522.107802</v>
+        <v>1018.523287</v>
       </c>
     </row>
     <row r="5">
@@ -597,34 +589,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1.026978</v>
       </c>
       <c r="C5" t="n">
-        <v>0.889545</v>
+        <v>1.008579</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9406870000000001</v>
+        <v>0.944307</v>
       </c>
       <c r="E5" t="n">
-        <v>0.91806</v>
+        <v>1.31829225</v>
       </c>
       <c r="F5" t="n">
-        <v>0.875647</v>
+        <v>0.866345</v>
       </c>
       <c r="G5" t="n">
-        <v>1.343617</v>
+        <v>0.9060865</v>
       </c>
       <c r="H5" t="n">
-        <v>0.840773</v>
+        <v>0.9748790000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7844285</v>
+        <v>1.483324</v>
       </c>
       <c r="J5" t="n">
-        <v>0.880501</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1.19168</v>
+        <v>1.933499</v>
       </c>
     </row>
     <row r="6">
@@ -633,33 +622,32 @@
           <t>光電業平上市</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="n">
+        <v>3533.057299</v>
+      </c>
       <c r="C6" t="n">
-        <v>670.460166</v>
+        <v>1768.985805</v>
       </c>
       <c r="D6" t="n">
-        <v>1795.87448</v>
+        <v>1177.582203</v>
       </c>
       <c r="E6" t="n">
-        <v>485.820215</v>
+        <v>866.71379</v>
       </c>
       <c r="F6" t="n">
-        <v>749.766723</v>
+        <v>1194.916813</v>
       </c>
       <c r="G6" t="n">
-        <v>579.313011</v>
+        <v>1063.781628</v>
       </c>
       <c r="H6" t="n">
-        <v>753.51323</v>
+        <v>1114.478124</v>
       </c>
       <c r="I6" t="n">
-        <v>309.619091</v>
+        <v>1524.632189</v>
       </c>
       <c r="J6" t="n">
-        <v>1063.887458</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1306.479152</v>
+        <v>1117.499227</v>
       </c>
     </row>
     <row r="7">
@@ -668,33 +656,32 @@
           <t>光電業平上櫃</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="B7" t="n">
+        <v>0.684599</v>
+      </c>
       <c r="C7" t="n">
-        <v>0.623261</v>
+        <v>0.510082</v>
       </c>
       <c r="D7" t="n">
-        <v>0.345019</v>
+        <v>0.936181</v>
       </c>
       <c r="E7" t="n">
-        <v>0.202875</v>
+        <v>0.296713</v>
       </c>
       <c r="F7" t="n">
-        <v>0.194899</v>
+        <v>0.507507</v>
       </c>
       <c r="G7" t="n">
-        <v>0.08137</v>
+        <v>0.161472</v>
       </c>
       <c r="H7" t="n">
-        <v>0.167453</v>
+        <v>0.230956</v>
       </c>
       <c r="I7" t="n">
-        <v>0.169812</v>
+        <v>0.216312</v>
       </c>
       <c r="J7" t="n">
-        <v>0.20574</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.461706</v>
+        <v>0.178666</v>
       </c>
     </row>
     <row r="8">
@@ -703,33 +690,32 @@
           <t>其他右上上市</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" t="n">
+        <v>708.754765</v>
+      </c>
       <c r="C8" t="n">
-        <v>633.41831</v>
+        <v>695.467022</v>
       </c>
       <c r="D8" t="n">
-        <v>545.652845</v>
+        <v>804.3266159999999</v>
       </c>
       <c r="E8" t="n">
-        <v>718.182277</v>
+        <v>945.081587</v>
       </c>
       <c r="F8" t="n">
-        <v>808.951334</v>
+        <v>1026.433541</v>
       </c>
       <c r="G8" t="n">
-        <v>653.1447899999999</v>
+        <v>1319.534296</v>
       </c>
       <c r="H8" t="n">
-        <v>806.822822</v>
+        <v>1653.5761</v>
       </c>
       <c r="I8" t="n">
-        <v>1166.586888</v>
+        <v>2214.886948</v>
       </c>
       <c r="J8" t="n">
-        <v>1535.231402</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1831.969767</v>
+        <v>1182.599023</v>
       </c>
     </row>
     <row r="9">
@@ -738,33 +724,32 @@
           <t>其他右上上櫃</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="n">
+        <v>1.733862</v>
+      </c>
       <c r="C9" t="n">
-        <v>2.200489666666666</v>
+        <v>4.251473</v>
       </c>
       <c r="D9" t="n">
-        <v>1.709308</v>
+        <v>1.366303</v>
       </c>
       <c r="E9" t="n">
-        <v>4.243406</v>
+        <v>1.71218</v>
       </c>
       <c r="F9" t="n">
-        <v>1.365579</v>
+        <v>1.99472</v>
       </c>
       <c r="G9" t="n">
-        <v>1.710009</v>
+        <v>1.926111</v>
       </c>
       <c r="H9" t="n">
-        <v>1.993449</v>
+        <v>1.867746</v>
       </c>
       <c r="I9" t="n">
-        <v>1.906945</v>
+        <v>1.821556</v>
       </c>
       <c r="J9" t="n">
-        <v>1.842676</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1.807055</v>
+        <v>1.777786</v>
       </c>
     </row>
     <row r="10">
@@ -773,33 +758,32 @@
           <t>其他右下上市</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="n">
+        <v>1887.073794</v>
+      </c>
       <c r="C10" t="n">
-        <v>282.471823</v>
+        <v>1367.403104</v>
       </c>
       <c r="D10" t="n">
-        <v>2057.031488</v>
+        <v>821.838253</v>
       </c>
       <c r="E10" t="n">
-        <v>1537.147381</v>
+        <v>957.630659</v>
       </c>
       <c r="F10" t="n">
-        <v>840.695142</v>
+        <v>1092.657216</v>
       </c>
       <c r="G10" t="n">
-        <v>956.589307</v>
+        <v>1151.470527</v>
       </c>
       <c r="H10" t="n">
-        <v>1092.69051</v>
+        <v>1061.894658</v>
       </c>
       <c r="I10" t="n">
-        <v>1279.983284</v>
+        <v>986.5640090000001</v>
       </c>
       <c r="J10" t="n">
-        <v>1091.299464</v>
-      </c>
-      <c r="K10" t="n">
-        <v>916.9355430000001</v>
+        <v>1214.916591</v>
       </c>
     </row>
     <row r="11">
@@ -809,34 +793,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>0.7884640000000001</v>
       </c>
       <c r="C11" t="n">
-        <v>4.280272</v>
+        <v>0.36906525</v>
       </c>
       <c r="D11" t="n">
-        <v>0.800986</v>
+        <v>0.2415985</v>
       </c>
       <c r="E11" t="n">
-        <v>0.38835725</v>
+        <v>0.308221</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2769725</v>
+        <v>0.341959</v>
       </c>
       <c r="G11" t="n">
-        <v>0.318779</v>
+        <v>2.512299</v>
       </c>
       <c r="H11" t="n">
-        <v>0.413046</v>
+        <v>0.9609550833333333</v>
       </c>
       <c r="I11" t="n">
-        <v>2.517685</v>
+        <v>1.05431</v>
       </c>
       <c r="J11" t="n">
-        <v>1.032013083333333</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1.066645</v>
+        <v>0.6217311666666666</v>
       </c>
     </row>
     <row r="12">
@@ -845,33 +826,32 @@
           <t>其他平上市</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="n">
+        <v>368.675684</v>
+      </c>
       <c r="C12" t="n">
-        <v>1212.657405</v>
+        <v>281.544287</v>
       </c>
       <c r="D12" t="n">
-        <v>361.81991</v>
+        <v>142.31445</v>
       </c>
       <c r="E12" t="n">
-        <v>89.084755</v>
+        <v>164.8614</v>
       </c>
       <c r="F12" t="n">
-        <v>118.832843</v>
+        <v>148.657663</v>
       </c>
       <c r="G12" t="n">
-        <v>457.839549</v>
+        <v>246.467539</v>
       </c>
       <c r="H12" t="n">
-        <v>368.235088</v>
+        <v>179.031457</v>
       </c>
       <c r="I12" t="n">
-        <v>270.90219</v>
+        <v>146.276942</v>
       </c>
       <c r="J12" t="n">
-        <v>267.971349</v>
-      </c>
-      <c r="K12" t="n">
-        <v>598.822589</v>
+        <v>53.90317</v>
       </c>
     </row>
     <row r="13">
@@ -880,33 +860,32 @@
           <t>其他平上櫃</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
+      <c r="B13" t="n">
+        <v>0.045488</v>
+      </c>
       <c r="C13" t="n">
-        <v>0.055679</v>
+        <v>0.053156</v>
       </c>
       <c r="D13" t="n">
-        <v>0.038459</v>
+        <v>0.07677200000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>0.028894</v>
+        <v>0.073134</v>
       </c>
       <c r="F13" t="n">
-        <v>0.028113</v>
+        <v>0.10516</v>
       </c>
       <c r="G13" t="n">
-        <v>0.053851</v>
+        <v>0.0696565</v>
       </c>
       <c r="H13" t="n">
-        <v>0.027037</v>
+        <v>0.085149</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0627825</v>
+        <v>0.121839</v>
       </c>
       <c r="J13" t="n">
-        <v>0.011982</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.105841</v>
+        <v>0.077456</v>
       </c>
     </row>
     <row r="14">
@@ -915,33 +894,32 @@
           <t>其他電子業右上上市</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
+      <c r="B14" t="n">
+        <v>43866.035113</v>
+      </c>
       <c r="C14" t="n">
-        <v>37059.210861</v>
+        <v>39906.027565</v>
       </c>
       <c r="D14" t="n">
-        <v>45538.942915</v>
+        <v>36079.271484</v>
       </c>
       <c r="E14" t="n">
-        <v>40603.861329</v>
+        <v>35352.869423</v>
       </c>
       <c r="F14" t="n">
-        <v>36308.402063</v>
+        <v>43844.505121</v>
       </c>
       <c r="G14" t="n">
-        <v>35956.648033</v>
+        <v>33855.922663</v>
       </c>
       <c r="H14" t="n">
-        <v>43873.810083</v>
+        <v>39818.732</v>
       </c>
       <c r="I14" t="n">
-        <v>34212.143456</v>
+        <v>58636.091601</v>
       </c>
       <c r="J14" t="n">
-        <v>41155.164782</v>
-      </c>
-      <c r="K14" t="n">
-        <v>58812.202222</v>
+        <v>61933.541822</v>
       </c>
     </row>
     <row r="15">
@@ -950,33 +928,32 @@
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
+      <c r="B15" t="n">
+        <v>11.431169</v>
+      </c>
       <c r="C15" t="n">
-        <v>9.364144</v>
+        <v>9.114428</v>
       </c>
       <c r="D15" t="n">
-        <v>13.96111966666667</v>
+        <v>13.437214</v>
       </c>
       <c r="E15" t="n">
-        <v>10.770535</v>
+        <v>8.991203000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>14.468626</v>
+        <v>10.506049</v>
       </c>
       <c r="G15" t="n">
-        <v>10.602243</v>
+        <v>6.719846</v>
       </c>
       <c r="H15" t="n">
-        <v>13.766269</v>
+        <v>7.302763</v>
       </c>
       <c r="I15" t="n">
-        <v>9.905314000000001</v>
+        <v>9.339683000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>10.250491</v>
-      </c>
-      <c r="K15" t="n">
-        <v>13.550757</v>
+        <v>8.56776</v>
       </c>
     </row>
     <row r="16">
@@ -985,33 +962,32 @@
           <t>其他電子業右下上市</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
+      <c r="B16" t="n">
+        <v>204.045792</v>
+      </c>
       <c r="C16" t="n">
-        <v>359.326326</v>
+        <v>156.255981</v>
       </c>
       <c r="D16" t="n">
-        <v>399.891125</v>
+        <v>122.188769</v>
       </c>
       <c r="E16" t="n">
-        <v>418.121535</v>
+        <v>173.258883</v>
       </c>
       <c r="F16" t="n">
-        <v>387.959514</v>
+        <v>167.846943</v>
       </c>
       <c r="G16" t="n">
-        <v>388.689652</v>
+        <v>162.343206</v>
       </c>
       <c r="H16" t="n">
-        <v>437.686363</v>
+        <v>190.95954</v>
       </c>
       <c r="I16" t="n">
-        <v>342.637731</v>
+        <v>302.511449</v>
       </c>
       <c r="J16" t="n">
-        <v>368.704943</v>
-      </c>
-      <c r="K16" t="n">
-        <v>772.19219</v>
+        <v>368.526172</v>
       </c>
     </row>
     <row r="17">
@@ -1021,34 +997,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>0.2174656666666667</v>
       </c>
       <c r="C17" t="n">
-        <v>0.093711</v>
+        <v>0.184608</v>
       </c>
       <c r="D17" t="n">
-        <v>0.066887</v>
+        <v>0.238945</v>
       </c>
       <c r="E17" t="n">
-        <v>0.084369</v>
+        <v>0.102638</v>
       </c>
       <c r="F17" t="n">
-        <v>0.158487</v>
+        <v>0.075781</v>
       </c>
       <c r="G17" t="n">
-        <v>0.042562</v>
+        <v>0.087064</v>
       </c>
       <c r="H17" t="n">
-        <v>0.034033</v>
+        <v>0.114932</v>
       </c>
       <c r="I17" t="n">
-        <v>0.043911</v>
+        <v>0.107558</v>
       </c>
       <c r="J17" t="n">
-        <v>0.058318</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.086136</v>
+        <v>0.082695</v>
       </c>
     </row>
     <row r="18">
@@ -1057,33 +1030,32 @@
           <t>其他電子業平上市</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
+      <c r="B18" t="n">
+        <v>2269.923561</v>
+      </c>
       <c r="C18" t="n">
-        <v>322.154418</v>
+        <v>1069.607557</v>
       </c>
       <c r="D18" t="n">
-        <v>401.170426</v>
+        <v>733.0549140000001</v>
       </c>
       <c r="E18" t="n">
-        <v>109.908239</v>
+        <v>1399.054171</v>
       </c>
       <c r="F18" t="n">
-        <v>238.15359</v>
+        <v>662.797492</v>
       </c>
       <c r="G18" t="n">
-        <v>579.844792</v>
+        <v>756.907611</v>
       </c>
       <c r="H18" t="n">
-        <v>363.65311</v>
+        <v>1625.270931</v>
       </c>
       <c r="I18" t="n">
-        <v>220.392293</v>
+        <v>803.294501</v>
       </c>
       <c r="J18" t="n">
-        <v>111.092746</v>
-      </c>
-      <c r="K18" t="n">
-        <v>157.503139</v>
+        <v>1393.298319</v>
       </c>
     </row>
     <row r="19">
@@ -1092,33 +1064,32 @@
           <t>其他電子業平上櫃</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
+      <c r="B19" t="n">
+        <v>3.218028</v>
+      </c>
       <c r="C19" t="n">
-        <v>0.669154</v>
+        <v>2.334074</v>
       </c>
       <c r="D19" t="n">
-        <v>0.820887</v>
+        <v>1.500443</v>
       </c>
       <c r="E19" t="n">
-        <v>0.761592</v>
+        <v>1.856242</v>
       </c>
       <c r="F19" t="n">
-        <v>0.539728</v>
+        <v>3.652731</v>
       </c>
       <c r="G19" t="n">
-        <v>0.296326</v>
+        <v>3.487986</v>
       </c>
       <c r="H19" t="n">
-        <v>0.422162</v>
+        <v>3.057712</v>
       </c>
       <c r="I19" t="n">
-        <v>0.336347</v>
+        <v>4.558452</v>
       </c>
       <c r="J19" t="n">
-        <v>0.14361</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.27148</v>
+        <v>5.827706</v>
       </c>
     </row>
     <row r="20">
@@ -1127,33 +1098,32 @@
           <t>化學工業右上上市</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
+      <c r="B20" t="n">
+        <v>5043.756829</v>
+      </c>
       <c r="C20" t="n">
-        <v>3736.050449</v>
+        <v>8292.582050000001</v>
       </c>
       <c r="D20" t="n">
-        <v>5535.172004</v>
+        <v>9882.511367999999</v>
       </c>
       <c r="E20" t="n">
-        <v>8562.394875</v>
+        <v>6355.062814</v>
       </c>
       <c r="F20" t="n">
-        <v>10231.82806</v>
+        <v>8542.054827</v>
       </c>
       <c r="G20" t="n">
-        <v>7037.580581</v>
+        <v>5022.470767</v>
       </c>
       <c r="H20" t="n">
-        <v>8922.589506</v>
+        <v>10431.09168</v>
       </c>
       <c r="I20" t="n">
-        <v>5951.538249</v>
+        <v>10362.427802</v>
       </c>
       <c r="J20" t="n">
-        <v>10798.870931</v>
-      </c>
-      <c r="K20" t="n">
-        <v>11033.84295</v>
+        <v>12846.881223</v>
       </c>
     </row>
     <row r="21">
@@ -1162,33 +1132,32 @@
           <t>化學工業右上上櫃</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="n">
+        <v>0.104806</v>
+      </c>
       <c r="C21" t="n">
-        <v>0.207952</v>
+        <v>0.08237700000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>0.136287</v>
+        <v>0.129619</v>
       </c>
       <c r="E21" t="n">
-        <v>0.108029</v>
+        <v>0.08554200000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>0.253387</v>
+        <v>0.243057</v>
       </c>
       <c r="G21" t="n">
-        <v>0.776633</v>
+        <v>0.089675</v>
       </c>
       <c r="H21" t="n">
-        <v>1.370963</v>
+        <v>0.294889</v>
       </c>
       <c r="I21" t="n">
-        <v>0.982088</v>
+        <v>0.334746</v>
       </c>
       <c r="J21" t="n">
-        <v>0.809154</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.733225</v>
+        <v>0.574137</v>
       </c>
     </row>
     <row r="22">
@@ -1197,33 +1166,32 @@
           <t>化學工業右下上市</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="n">
+        <v>231.748497</v>
+      </c>
       <c r="C22" t="n">
-        <v>167.232837</v>
+        <v>142.264442</v>
       </c>
       <c r="D22" t="n">
-        <v>229.714255</v>
+        <v>386.917159</v>
       </c>
       <c r="E22" t="n">
-        <v>140.860996</v>
+        <v>174.154573</v>
       </c>
       <c r="F22" t="n">
-        <v>236.819083</v>
+        <v>137.624827</v>
       </c>
       <c r="G22" t="n">
-        <v>148.261332</v>
+        <v>104.854825</v>
       </c>
       <c r="H22" t="n">
-        <v>101.718433</v>
+        <v>196.898298</v>
       </c>
       <c r="I22" t="n">
-        <v>85.72914299999999</v>
+        <v>217.971558</v>
       </c>
       <c r="J22" t="n">
-        <v>84.990664</v>
-      </c>
-      <c r="K22" t="n">
-        <v>183.488406</v>
+        <v>105.367152</v>
       </c>
     </row>
     <row r="23">
@@ -1232,33 +1200,32 @@
           <t>化學工業右下上櫃</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
+      <c r="B23" t="n">
+        <v>0.251038</v>
+      </c>
       <c r="C23" t="n">
-        <v>0.15126</v>
+        <v>0.425178</v>
       </c>
       <c r="D23" t="n">
-        <v>0.13601</v>
+        <v>0.302992</v>
       </c>
       <c r="E23" t="n">
-        <v>0.08731899999999999</v>
+        <v>0.75597</v>
       </c>
       <c r="F23" t="n">
-        <v>0.102565</v>
+        <v>0.639278</v>
       </c>
       <c r="G23" t="n">
-        <v>0.009887999999999999</v>
+        <v>0.2668</v>
       </c>
       <c r="H23" t="n">
-        <v>0.009261</v>
+        <v>0.024437</v>
       </c>
       <c r="I23" t="n">
-        <v>0.008884</v>
+        <v>0.024472</v>
       </c>
       <c r="J23" t="n">
-        <v>0.025501</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0.025438</v>
+        <v>0.236392</v>
       </c>
     </row>
     <row r="24">
@@ -1267,33 +1234,32 @@
           <t>化學工業平上市</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="n">
+        <v>1732.131633</v>
+      </c>
       <c r="C24" t="n">
-        <v>923.704505</v>
+        <v>996.066389</v>
       </c>
       <c r="D24" t="n">
-        <v>1240.716458</v>
+        <v>749.073516</v>
       </c>
       <c r="E24" t="n">
-        <v>726.253564</v>
+        <v>1063.384379</v>
       </c>
       <c r="F24" t="n">
-        <v>549.482212</v>
+        <v>1014.584463</v>
       </c>
       <c r="G24" t="n">
-        <v>405.298512</v>
+        <v>1574.244514</v>
       </c>
       <c r="H24" t="n">
-        <v>665.230258</v>
+        <v>723.970323</v>
       </c>
       <c r="I24" t="n">
-        <v>663.405157</v>
+        <v>1038.512025</v>
       </c>
       <c r="J24" t="n">
-        <v>466.581595</v>
-      </c>
-      <c r="K24" t="n">
-        <v>400.513666</v>
+        <v>762.959099</v>
       </c>
     </row>
     <row r="25">
@@ -1302,33 +1268,32 @@
           <t>化學工業平上櫃</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
+      <c r="B25" t="n">
+        <v>0.053762</v>
+      </c>
       <c r="C25" t="n">
-        <v>0.213018</v>
+        <v>0.049746</v>
       </c>
       <c r="D25" t="n">
-        <v>0.137309</v>
+        <v>0.178292</v>
       </c>
       <c r="E25" t="n">
-        <v>0.361953</v>
+        <v>0.693905</v>
       </c>
       <c r="F25" t="n">
-        <v>0.254951</v>
+        <v>1.141352</v>
       </c>
       <c r="G25" t="n">
-        <v>0.748896</v>
+        <v>0.89294</v>
       </c>
       <c r="H25" t="n">
-        <v>0.643463</v>
+        <v>2.197642</v>
       </c>
       <c r="I25" t="n">
-        <v>0.258443</v>
+        <v>1.170657</v>
       </c>
       <c r="J25" t="n">
-        <v>1.682313</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0.771212</v>
+        <v>0.382493</v>
       </c>
     </row>
     <row r="26">
@@ -1337,33 +1302,32 @@
           <t>半導體業右上上市</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="n">
+        <v>380269.750197</v>
+      </c>
       <c r="C26" t="n">
-        <v>314316.912468</v>
+        <v>301340.906928</v>
       </c>
       <c r="D26" t="n">
-        <v>395429.300042</v>
+        <v>270822.403683</v>
       </c>
       <c r="E26" t="n">
-        <v>317275.928486</v>
+        <v>285493.879323</v>
       </c>
       <c r="F26" t="n">
-        <v>280606.246302</v>
+        <v>307574.643404</v>
       </c>
       <c r="G26" t="n">
-        <v>290934.556133</v>
+        <v>229451.108898</v>
       </c>
       <c r="H26" t="n">
-        <v>315316.585395</v>
+        <v>247862.218384</v>
       </c>
       <c r="I26" t="n">
-        <v>234444.436922</v>
+        <v>366999.998588</v>
       </c>
       <c r="J26" t="n">
-        <v>259890.34109</v>
-      </c>
-      <c r="K26" t="n">
-        <v>373373.997905</v>
+        <v>309715.52784</v>
       </c>
     </row>
     <row r="27">
@@ -1372,33 +1336,32 @@
           <t>半導體業右上上櫃</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
+      <c r="B27" t="n">
+        <v>155.644348</v>
+      </c>
       <c r="C27" t="n">
-        <v>96.131592</v>
+        <v>154.61431</v>
       </c>
       <c r="D27" t="n">
-        <v>154.880758</v>
+        <v>90.226675</v>
       </c>
       <c r="E27" t="n">
-        <v>156.149125</v>
+        <v>79.75349</v>
       </c>
       <c r="F27" t="n">
-        <v>95.266611</v>
+        <v>123.720141</v>
       </c>
       <c r="G27" t="n">
-        <v>83.360472</v>
+        <v>128.044739</v>
       </c>
       <c r="H27" t="n">
-        <v>135.079701</v>
+        <v>116.418771</v>
       </c>
       <c r="I27" t="n">
-        <v>140.272935</v>
+        <v>141.135673</v>
       </c>
       <c r="J27" t="n">
-        <v>123.430892</v>
-      </c>
-      <c r="K27" t="n">
-        <v>149.827761</v>
+        <v>110.221825</v>
       </c>
     </row>
     <row r="28">
@@ -1407,33 +1370,32 @@
           <t>半導體業右下上市</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="n">
+        <v>3777.169563</v>
+      </c>
       <c r="C28" t="n">
-        <v>746.338177</v>
+        <v>982.275547</v>
       </c>
       <c r="D28" t="n">
-        <v>996.282696</v>
+        <v>1190.705722</v>
       </c>
       <c r="E28" t="n">
-        <v>956.627656</v>
+        <v>1215.495016</v>
       </c>
       <c r="F28" t="n">
-        <v>832.405709</v>
+        <v>1089.004733</v>
       </c>
       <c r="G28" t="n">
-        <v>991.0951669999999</v>
+        <v>957.057733</v>
       </c>
       <c r="H28" t="n">
-        <v>1104.460706</v>
+        <v>621.03682</v>
       </c>
       <c r="I28" t="n">
-        <v>1153.921524</v>
+        <v>1274.322432</v>
       </c>
       <c r="J28" t="n">
-        <v>705.477575</v>
-      </c>
-      <c r="K28" t="n">
-        <v>1021.386874</v>
+        <v>1297.387778</v>
       </c>
     </row>
     <row r="29">
@@ -1443,34 +1405,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>1.655054</v>
       </c>
       <c r="C29" t="n">
-        <v>1.030227</v>
+        <v>1.558873</v>
       </c>
       <c r="D29" t="n">
-        <v>1.869736</v>
+        <v>0.8938</v>
       </c>
       <c r="E29" t="n">
-        <v>1.269868</v>
+        <v>1.46473325</v>
       </c>
       <c r="F29" t="n">
-        <v>0.871218</v>
+        <v>2.935031</v>
       </c>
       <c r="G29" t="n">
-        <v>3.00092325</v>
+        <v>3.985883</v>
       </c>
       <c r="H29" t="n">
-        <v>1.752935</v>
+        <v>4.857131</v>
       </c>
       <c r="I29" t="n">
-        <v>3.038022</v>
+        <v>3.515911</v>
       </c>
       <c r="J29" t="n">
-        <v>2.423676</v>
-      </c>
-      <c r="K29" t="n">
-        <v>2.372169</v>
+        <v>2.824977</v>
       </c>
     </row>
     <row r="30">
@@ -1479,33 +1438,32 @@
           <t>半導體業平上市</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="n">
+        <v>30973.84923</v>
+      </c>
       <c r="C30" t="n">
-        <v>7627.062397</v>
+        <v>28779.054187</v>
       </c>
       <c r="D30" t="n">
-        <v>15829.831633</v>
+        <v>18447.333554</v>
       </c>
       <c r="E30" t="n">
-        <v>12092.675741</v>
+        <v>16209.80837</v>
       </c>
       <c r="F30" t="n">
-        <v>8574.452869999999</v>
+        <v>18913.857904</v>
       </c>
       <c r="G30" t="n">
-        <v>10705.973014</v>
+        <v>12874.398476</v>
       </c>
       <c r="H30" t="n">
-        <v>10741.106846</v>
+        <v>16711.163602</v>
       </c>
       <c r="I30" t="n">
-        <v>7129.630298</v>
+        <v>12336.164244</v>
       </c>
       <c r="J30" t="n">
-        <v>3639.240211</v>
-      </c>
-      <c r="K30" t="n">
-        <v>5598.691249</v>
+        <v>11623.162005</v>
       </c>
     </row>
     <row r="31">
@@ -1514,33 +1472,32 @@
           <t>半導體業平上櫃</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
+      <c r="B31" t="n">
+        <v>8.887751</v>
+      </c>
       <c r="C31" t="n">
-        <v>1.052763</v>
+        <v>7.381023</v>
       </c>
       <c r="D31" t="n">
-        <v>1.562743</v>
+        <v>9.350882</v>
       </c>
       <c r="E31" t="n">
-        <v>0.867654</v>
+        <v>11.343493</v>
       </c>
       <c r="F31" t="n">
-        <v>0.350632</v>
+        <v>16.393483</v>
       </c>
       <c r="G31" t="n">
-        <v>1.030853</v>
+        <v>14.89894</v>
       </c>
       <c r="H31" t="n">
-        <v>1.564575</v>
+        <v>10.04876</v>
       </c>
       <c r="I31" t="n">
-        <v>1.136972</v>
+        <v>11.599118</v>
       </c>
       <c r="J31" t="n">
-        <v>2.592812</v>
-      </c>
-      <c r="K31" t="n">
-        <v>1.514762</v>
+        <v>10.643007</v>
       </c>
     </row>
     <row r="32">
@@ -1549,33 +1506,32 @@
           <t>塑膠工業右上上市</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="n">
+        <v>20403.743481</v>
+      </c>
       <c r="C32" t="n">
-        <v>14563.367158</v>
+        <v>15904.156976</v>
       </c>
       <c r="D32" t="n">
-        <v>20411.893102</v>
+        <v>18414.422521</v>
       </c>
       <c r="E32" t="n">
-        <v>15919.198001</v>
+        <v>23993.723144</v>
       </c>
       <c r="F32" t="n">
-        <v>18456.769403</v>
+        <v>38398.115906</v>
       </c>
       <c r="G32" t="n">
-        <v>24003.311254</v>
+        <v>17613.517817</v>
       </c>
       <c r="H32" t="n">
-        <v>38446.327975</v>
+        <v>17741.971142</v>
       </c>
       <c r="I32" t="n">
-        <v>17643.26033</v>
+        <v>29521.399492</v>
       </c>
       <c r="J32" t="n">
-        <v>17880.73366</v>
-      </c>
-      <c r="K32" t="n">
-        <v>29591.396337</v>
+        <v>37282.689887</v>
       </c>
     </row>
     <row r="33">
@@ -1584,33 +1540,32 @@
           <t>塑膠工業右下上市</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
+      <c r="B33" t="n">
+        <v>43.737029</v>
+      </c>
       <c r="C33" t="n">
-        <v>16.553126</v>
+        <v>26.41518</v>
       </c>
       <c r="D33" t="n">
-        <v>17.292945</v>
+        <v>21.393921</v>
       </c>
       <c r="E33" t="n">
-        <v>20.141526</v>
+        <v>39.355459</v>
       </c>
       <c r="F33" t="n">
-        <v>14.711618</v>
+        <v>34.904345</v>
       </c>
       <c r="G33" t="n">
-        <v>29.039463</v>
+        <v>28.912333</v>
       </c>
       <c r="H33" t="n">
-        <v>37.351237</v>
+        <v>15.643569</v>
       </c>
       <c r="I33" t="n">
-        <v>22.338546</v>
+        <v>41.277259</v>
       </c>
       <c r="J33" t="n">
-        <v>17.20861</v>
-      </c>
-      <c r="K33" t="n">
-        <v>43.752679</v>
+        <v>56.90155</v>
       </c>
     </row>
     <row r="34">
@@ -1619,33 +1574,32 @@
           <t>塑膠工業右下上櫃</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="n">
+        <v>0.02357733333333333</v>
+      </c>
       <c r="C34" t="n">
-        <v>0.016873</v>
+        <v>0.0225495</v>
       </c>
       <c r="D34" t="n">
-        <v>0.02010833333333333</v>
+        <v>0.043256</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0145135</v>
+        <v>0.028786</v>
       </c>
       <c r="F34" t="n">
-        <v>0.041813</v>
+        <v>0.0244545</v>
       </c>
       <c r="G34" t="n">
-        <v>0.028097</v>
+        <v>0.029761</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0236345</v>
+        <v>0.016262</v>
       </c>
       <c r="I34" t="n">
-        <v>0.029495</v>
+        <v>0.0393105</v>
       </c>
       <c r="J34" t="n">
-        <v>0.015748</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0.0384175</v>
+        <v>0.03161</v>
       </c>
     </row>
     <row r="35">
@@ -1654,1176 +1608,1173 @@
           <t>塑膠工業平上市</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
+      <c r="B35" t="n">
+        <v>51.638723</v>
+      </c>
       <c r="C35" t="n">
-        <v>60.350914</v>
+        <v>78.35193200000001</v>
       </c>
       <c r="D35" t="n">
-        <v>69.93318600000001</v>
+        <v>86.148461</v>
       </c>
       <c r="E35" t="n">
-        <v>69.58456099999999</v>
+        <v>105.869253</v>
       </c>
       <c r="F35" t="n">
-        <v>50.483882</v>
+        <v>159.785773</v>
       </c>
       <c r="G35" t="n">
-        <v>106.597139</v>
+        <v>84.431816</v>
       </c>
       <c r="H35" t="n">
-        <v>109.126812</v>
+        <v>244.212676</v>
       </c>
       <c r="I35" t="n">
-        <v>61.26309</v>
+        <v>121.00438</v>
       </c>
       <c r="J35" t="n">
-        <v>103.885117</v>
-      </c>
-      <c r="K35" t="n">
-        <v>48.532115</v>
+        <v>87.37659499999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>塑膠工業平上櫃</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
+          <t>居家生活右上上櫃</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0.0013</v>
+      </c>
       <c r="C36" t="n">
-        <v>0.003312</v>
+        <v>0.004544</v>
       </c>
       <c r="D36" t="n">
-        <v>0.003469</v>
+        <v>0.002171</v>
       </c>
       <c r="E36" t="n">
-        <v>0.008036</v>
+        <v>0.001119</v>
       </c>
       <c r="F36" t="n">
-        <v>0.001443</v>
+        <v>0.000906</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0006890000000000001</v>
+        <v>0.000283</v>
       </c>
       <c r="H36" t="n">
-        <v>0.00082</v>
+        <v>0.001482</v>
       </c>
       <c r="I36" t="n">
-        <v>0.000266</v>
+        <v>0.00025</v>
       </c>
       <c r="J36" t="n">
-        <v>0.000514</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0.000893</v>
+        <v>0.00049</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>居家生活右上上櫃</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
+          <t>居家生活右下上市</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>37.008341</v>
+      </c>
+      <c r="C37" t="n">
+        <v>22.73136</v>
+      </c>
       <c r="D37" t="n">
-        <v>0.001312</v>
+        <v>20.023105</v>
       </c>
       <c r="E37" t="n">
-        <v>0.005049</v>
+        <v>29.842921</v>
       </c>
       <c r="F37" t="n">
-        <v>0.002355</v>
+        <v>27.947611</v>
       </c>
       <c r="G37" t="n">
-        <v>0.000613</v>
+        <v>20.812951</v>
       </c>
       <c r="H37" t="n">
-        <v>0.001147</v>
+        <v>28.538201</v>
       </c>
       <c r="I37" t="n">
-        <v>0.000283</v>
+        <v>52.805219</v>
       </c>
       <c r="J37" t="n">
-        <v>0.001482</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0.00025</v>
+        <v>33.439189</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>居家生活右下上市</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
+          <t>居家生活右下上櫃</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0.540394</v>
+      </c>
       <c r="C38" t="n">
-        <v>315.166125</v>
+        <v>0.367615</v>
       </c>
       <c r="D38" t="n">
-        <v>37.008341</v>
+        <v>0.55962575</v>
       </c>
       <c r="E38" t="n">
-        <v>110.308606</v>
+        <v>0.3257003333333333</v>
       </c>
       <c r="F38" t="n">
-        <v>84.51718099999999</v>
+        <v>0.3575955</v>
       </c>
       <c r="G38" t="n">
-        <v>225.681646</v>
+        <v>0.2460553333333333</v>
       </c>
       <c r="H38" t="n">
-        <v>157.080028</v>
+        <v>0.312833</v>
       </c>
       <c r="I38" t="n">
-        <v>89.773652</v>
+        <v>0.226244</v>
       </c>
       <c r="J38" t="n">
-        <v>85.743891</v>
-      </c>
-      <c r="K38" t="n">
-        <v>94.456698</v>
+        <v>0.217029</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>居家生活右下上櫃</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
+          <t>居家生活平上市</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>144.489178</v>
+      </c>
       <c r="C39" t="n">
-        <v>0.37386</v>
+        <v>87.577246</v>
       </c>
       <c r="D39" t="n">
-        <v>0.538758</v>
+        <v>64.49407600000001</v>
       </c>
       <c r="E39" t="n">
-        <v>0.366794</v>
+        <v>195.838725</v>
       </c>
       <c r="F39" t="n">
-        <v>0.55957575</v>
+        <v>129.132417</v>
       </c>
       <c r="G39" t="n">
-        <v>0.3252453333333333</v>
+        <v>68.960701</v>
       </c>
       <c r="H39" t="n">
-        <v>0.3573575</v>
+        <v>57.20569</v>
       </c>
       <c r="I39" t="n">
-        <v>0.245567</v>
+        <v>41.651479</v>
       </c>
       <c r="J39" t="n">
-        <v>0.307899</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0.226301</v>
+        <v>68.788026</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>居家生活平上市</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
+          <t>居家生活平上櫃</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0.003229</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.001043</v>
+      </c>
       <c r="D40" t="n">
-        <v>144.489178</v>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
+        <v>0.00075</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.000768</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.000901</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.004289</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.003008</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.001225</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.001313</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>居家生活平上櫃</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
+          <t>建材營造右上上市</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1311.540773</v>
+      </c>
       <c r="C41" t="n">
-        <v>0.010516</v>
+        <v>142.096299</v>
       </c>
       <c r="D41" t="n">
-        <v>0.004853</v>
+        <v>149.45803</v>
       </c>
       <c r="E41" t="n">
-        <v>0.001359</v>
+        <v>124.981634</v>
       </c>
       <c r="F41" t="n">
-        <v>0.000616</v>
+        <v>201.107528</v>
       </c>
       <c r="G41" t="n">
-        <v>0.001729</v>
+        <v>147.807027</v>
       </c>
       <c r="H41" t="n">
-        <v>0.000898</v>
+        <v>164.04647</v>
       </c>
       <c r="I41" t="n">
-        <v>0.004777333333333333</v>
+        <v>186.246527</v>
       </c>
       <c r="J41" t="n">
-        <v>0.007941999999999999</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0.001168</v>
+        <v>142.771721</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>建材營造右上上市</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
+          <t>建材營造右上上櫃</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>0.008525</v>
+      </c>
       <c r="C42" t="n">
-        <v>1006.339109</v>
+        <v>0.008455000000000001</v>
       </c>
       <c r="D42" t="n">
-        <v>1205.666688</v>
+        <v>0.007346</v>
       </c>
       <c r="E42" t="n">
-        <v>102.798544</v>
+        <v>0.012669</v>
       </c>
       <c r="F42" t="n">
-        <v>111.02575</v>
+        <v>0.015847</v>
       </c>
       <c r="G42" t="n">
-        <v>76.98213</v>
+        <v>0.020326</v>
       </c>
       <c r="H42" t="n">
-        <v>130.417564</v>
+        <v>0.01373125</v>
       </c>
       <c r="I42" t="n">
-        <v>87.222176</v>
+        <v>0.007236</v>
       </c>
       <c r="J42" t="n">
-        <v>110.783978</v>
-      </c>
-      <c r="K42" t="n">
-        <v>152.611407</v>
+        <v>0.006054</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>建材營造右上上櫃</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
+          <t>建材營造右下上市</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>457.357728</v>
+      </c>
       <c r="C43" t="n">
-        <v>0.008662</v>
+        <v>597.730444</v>
       </c>
       <c r="D43" t="n">
-        <v>0.019533</v>
+        <v>428.069404</v>
       </c>
       <c r="E43" t="n">
-        <v>0.015812</v>
+        <v>1042.3501</v>
       </c>
       <c r="F43" t="n">
-        <v>0.015308</v>
+        <v>1117.33762</v>
       </c>
       <c r="G43" t="n">
-        <v>0.012671</v>
+        <v>829.348561</v>
       </c>
       <c r="H43" t="n">
-        <v>0.016945</v>
+        <v>935.330247</v>
       </c>
       <c r="I43" t="n">
-        <v>0.022928</v>
+        <v>1437.091697</v>
       </c>
       <c r="J43" t="n">
-        <v>0.014092</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0.005928</v>
+        <v>904.735288</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>建材營造右下上市</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
+          <t>建材營造右下上櫃</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>0.108894</v>
+      </c>
       <c r="C44" t="n">
-        <v>761.269444</v>
+        <v>0.076583</v>
       </c>
       <c r="D44" t="n">
-        <v>514.0784200000001</v>
+        <v>0.06238</v>
       </c>
       <c r="E44" t="n">
-        <v>2484.126006</v>
+        <v>0.054294</v>
       </c>
       <c r="F44" t="n">
-        <v>930.419503</v>
+        <v>0.050976</v>
       </c>
       <c r="G44" t="n">
-        <v>1047.499389</v>
+        <v>0.03979466666666667</v>
       </c>
       <c r="H44" t="n">
-        <v>1121.877582</v>
+        <v>0.044147</v>
       </c>
       <c r="I44" t="n">
-        <v>832.779625</v>
+        <v>0.110113</v>
       </c>
       <c r="J44" t="n">
-        <v>939.653986</v>
-      </c>
-      <c r="K44" t="n">
-        <v>1444.134285</v>
+        <v>0.051935</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>建材營造右下上櫃</t>
+          <t>建材營造平上市</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>105.337666</v>
       </c>
       <c r="C45" t="n">
-        <v>0.119496</v>
+        <v>2056.975727</v>
       </c>
       <c r="D45" t="n">
-        <v>0.127281</v>
+        <v>581.465077</v>
       </c>
       <c r="E45" t="n">
-        <v>0.094918</v>
+        <v>36.673821</v>
       </c>
       <c r="F45" t="n">
-        <v>0.060662</v>
+        <v>53.262782</v>
       </c>
       <c r="G45" t="n">
-        <v>0.048336</v>
+        <v>166.435499</v>
       </c>
       <c r="H45" t="n">
-        <v>0.053015</v>
+        <v>76.116998</v>
       </c>
       <c r="I45" t="n">
-        <v>0.03701266666666667</v>
+        <v>121.778049</v>
       </c>
       <c r="J45" t="n">
-        <v>0.060752</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0.06973600000000001</v>
+        <v>63.764067</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>建材營造平上市</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
+          <t>建材營造平上櫃</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>0.036039</v>
+      </c>
       <c r="C46" t="n">
-        <v>133.166153</v>
+        <v>0.032516</v>
       </c>
       <c r="D46" t="n">
-        <v>154.491059</v>
+        <v>0.022415</v>
       </c>
       <c r="E46" t="n">
-        <v>209.87792</v>
+        <v>0.010698</v>
       </c>
       <c r="F46" t="n">
-        <v>117.547258</v>
+        <v>0.013407</v>
       </c>
       <c r="G46" t="n">
-        <v>79.524036</v>
+        <v>0.026788</v>
       </c>
       <c r="H46" t="n">
-        <v>119.412784</v>
+        <v>0.023503</v>
       </c>
       <c r="I46" t="n">
-        <v>223.589286</v>
+        <v>0.009675</v>
       </c>
       <c r="J46" t="n">
-        <v>125.055751</v>
-      </c>
-      <c r="K46" t="n">
-        <v>148.370581</v>
+        <v>0.009086</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>建材營造平上櫃</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
+          <t>數位雲端右上上市</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>524.292661</v>
+      </c>
       <c r="C47" t="n">
-        <v>0.006034</v>
+        <v>232.139303</v>
       </c>
       <c r="D47" t="n">
-        <v>0.002899</v>
+        <v>212.845719</v>
       </c>
       <c r="E47" t="n">
-        <v>0.003659</v>
+        <v>131.591225</v>
       </c>
       <c r="F47" t="n">
-        <v>0.001731</v>
+        <v>273.926956</v>
       </c>
       <c r="G47" t="n">
-        <v>0.004705</v>
+        <v>79.373986</v>
       </c>
       <c r="H47" t="n">
-        <v>0.004307</v>
+        <v>81.745813</v>
       </c>
       <c r="I47" t="n">
-        <v>0.014848</v>
+        <v>65.84591899999999</v>
       </c>
       <c r="J47" t="n">
-        <v>0.00322425</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0.019664</v>
+        <v>48.754718</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>數位雲端右上上市</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
+          <t>數位雲端右上上櫃</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>0.324899</v>
+      </c>
       <c r="C48" t="n">
-        <v>49.21963</v>
+        <v>0.506584</v>
       </c>
       <c r="D48" t="n">
-        <v>502.753895</v>
+        <v>0.218607</v>
       </c>
       <c r="E48" t="n">
-        <v>229.721265</v>
+        <v>0.179389</v>
       </c>
       <c r="F48" t="n">
-        <v>201.553671</v>
+        <v>0.296095</v>
       </c>
       <c r="G48" t="n">
-        <v>123.789134</v>
+        <v>0.1936893333333334</v>
       </c>
       <c r="H48" t="n">
-        <v>88.29381600000001</v>
+        <v>0.121387</v>
       </c>
       <c r="I48" t="n">
-        <v>61.638603</v>
+        <v>0.1898</v>
       </c>
       <c r="J48" t="n">
-        <v>71.518085</v>
-      </c>
-      <c r="K48" t="n">
-        <v>62.462198</v>
+        <v>0.209382</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>數位雲端右上上櫃</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
+          <t>數位雲端右下上市</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>25.923961</v>
+      </c>
       <c r="C49" t="n">
-        <v>0.338035</v>
+        <v>25.247635</v>
       </c>
       <c r="D49" t="n">
-        <v>0.324127</v>
+        <v>22.50859</v>
       </c>
       <c r="E49" t="n">
-        <v>0.506271</v>
+        <v>28.703929</v>
       </c>
       <c r="F49" t="n">
-        <v>0.223265</v>
+        <v>24.480949</v>
       </c>
       <c r="G49" t="n">
-        <v>0.166084</v>
+        <v>28.726985</v>
       </c>
       <c r="H49" t="n">
-        <v>0.244618</v>
+        <v>38.646655</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1803</v>
+        <v>102.767056</v>
       </c>
       <c r="J49" t="n">
-        <v>0.115223</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0.19295</v>
+        <v>71.747041</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>數位雲端右下上市</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
+          <t>數位雲端右下上櫃</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>0.205242</v>
+      </c>
       <c r="C50" t="n">
-        <v>133.666363</v>
+        <v>0.179853</v>
       </c>
       <c r="D50" t="n">
-        <v>111.166761</v>
+        <v>0.09177299999999999</v>
       </c>
       <c r="E50" t="n">
-        <v>53.080761</v>
+        <v>0.11663</v>
       </c>
       <c r="F50" t="n">
-        <v>82.262708</v>
+        <v>0.115867</v>
       </c>
       <c r="G50" t="n">
-        <v>65.905101</v>
+        <v>0.173237</v>
       </c>
       <c r="H50" t="n">
-        <v>58.653519</v>
+        <v>0.181664</v>
       </c>
       <c r="I50" t="n">
-        <v>58.105474</v>
+        <v>0.20589275</v>
       </c>
       <c r="J50" t="n">
-        <v>50.751367</v>
-      </c>
-      <c r="K50" t="n">
-        <v>106.150777</v>
+        <v>0.1089243333333333</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>數位雲端右下上櫃</t>
+          <t>數位雲端平上市</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0</v>
+        <v>189.304916</v>
       </c>
       <c r="C51" t="n">
-        <v>0.28790625</v>
+        <v>142.973795</v>
       </c>
       <c r="D51" t="n">
-        <v>0.2053863333333333</v>
+        <v>117.038726</v>
       </c>
       <c r="E51" t="n">
-        <v>0.179874</v>
+        <v>117.851939</v>
       </c>
       <c r="F51" t="n">
-        <v>0.205574</v>
+        <v>132.340216</v>
       </c>
       <c r="G51" t="n">
-        <v>0.267687</v>
+        <v>83.747483</v>
       </c>
       <c r="H51" t="n">
-        <v>0.205313</v>
+        <v>60.660386</v>
       </c>
       <c r="I51" t="n">
-        <v>0.232625</v>
+        <v>133.565777</v>
       </c>
       <c r="J51" t="n">
-        <v>0.210537</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0.25565475</v>
+        <v>100.996203</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>數位雲端平上市</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
+          <t>數位雲端平上櫃</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>0.001018333333333333</v>
+      </c>
       <c r="C52" t="n">
-        <v>141.372521</v>
+        <v>0.000483</v>
       </c>
       <c r="D52" t="n">
-        <v>125.600882</v>
+        <v>0.118701</v>
       </c>
       <c r="E52" t="n">
-        <v>117.558707</v>
+        <v>0.152504</v>
       </c>
       <c r="F52" t="n">
-        <v>68.576656</v>
+        <v>0.093373</v>
       </c>
       <c r="G52" t="n">
-        <v>88.45285800000001</v>
+        <v>0.074028</v>
       </c>
       <c r="H52" t="n">
-        <v>283.800786</v>
+        <v>0.036497</v>
       </c>
       <c r="I52" t="n">
-        <v>72.104377</v>
+        <v>0.059754</v>
       </c>
       <c r="J52" t="n">
-        <v>58.783402</v>
-      </c>
-      <c r="K52" t="n">
-        <v>133.565777</v>
+        <v>0.07814400000000001</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>數位雲端平上櫃</t>
+          <t>文化創意業右上上櫃</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
+      <c r="D53" t="n">
+        <v>4.373877</v>
+      </c>
+      <c r="E53" t="n">
+        <v>2.718566</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1.632479</v>
+      </c>
       <c r="G53" t="n">
-        <v>0.013305</v>
+        <v>4.801571</v>
       </c>
       <c r="H53" t="n">
-        <v>0.053744</v>
+        <v>2.438659</v>
       </c>
       <c r="I53" t="n">
-        <v>0.01615433333333333</v>
+        <v>1.087361</v>
       </c>
       <c r="J53" t="n">
-        <v>0.007483</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0.005895</v>
+        <v>1.167006</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>文化創意業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
+          <t>文化創意業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>0.057446</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.0641065</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.0408735</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.06168375</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.073361</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.049902</v>
+      </c>
       <c r="H54" t="n">
-        <v>1.632479</v>
+        <v>0.05330483333333334</v>
       </c>
       <c r="I54" t="n">
-        <v>4.801571</v>
+        <v>0.072182</v>
       </c>
       <c r="J54" t="n">
-        <v>2.438659</v>
-      </c>
-      <c r="K54" t="n">
-        <v>1.087361</v>
+        <v>0.06181725</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>文化創意業右下上櫃</t>
+          <t>文化創意業平上櫃</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0</v>
+        <v>0.853862</v>
       </c>
       <c r="C55" t="n">
-        <v>0.8757652500000001</v>
+        <v>0.596025</v>
       </c>
       <c r="D55" t="n">
-        <v>0.897614</v>
+        <v>0.008586999999999999</v>
       </c>
       <c r="E55" t="n">
-        <v>0.6511585</v>
+        <v>0.003479</v>
       </c>
       <c r="F55" t="n">
-        <v>0.0456975</v>
+        <v>0.001894</v>
       </c>
       <c r="G55" t="n">
-        <v>0.06317775</v>
+        <v>0.011794</v>
       </c>
       <c r="H55" t="n">
-        <v>0.06902700000000001</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0.052756</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0.05194683333333334</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0.068241</v>
-      </c>
+        <v>0.004545</v>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>文化創意業平上櫃</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr"/>
+          <t>橡膠工業右上上市</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>74.300687</v>
+      </c>
       <c r="C56" t="n">
-        <v>0.010959</v>
+        <v>380.284936</v>
       </c>
       <c r="D56" t="n">
-        <v>0.011212</v>
+        <v>59.31454</v>
       </c>
       <c r="E56" t="n">
-        <v>0.00653</v>
+        <v>91.80184300000001</v>
       </c>
       <c r="F56" t="n">
-        <v>4.376937</v>
+        <v>91.7514</v>
       </c>
       <c r="G56" t="n">
-        <v>2.718797</v>
+        <v>64.15203700000001</v>
       </c>
       <c r="H56" t="n">
-        <v>0.001631</v>
+        <v>159.079605</v>
       </c>
       <c r="I56" t="n">
-        <v>0.007647</v>
+        <v>130.843053</v>
       </c>
       <c r="J56" t="n">
-        <v>0.003466</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0.000139</v>
+        <v>111.431133</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>橡膠工業右上上市</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr"/>
+          <t>橡膠工業右下上市</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>234.544684</v>
+      </c>
       <c r="C57" t="n">
-        <v>62.371494</v>
+        <v>147.169752</v>
       </c>
       <c r="D57" t="n">
-        <v>72.667136</v>
+        <v>116.233975</v>
       </c>
       <c r="E57" t="n">
-        <v>134.681077</v>
+        <v>165.105133</v>
       </c>
       <c r="F57" t="n">
-        <v>53.153067</v>
+        <v>65.736844</v>
       </c>
       <c r="G57" t="n">
-        <v>89.79392199999999</v>
+        <v>172.168685</v>
       </c>
       <c r="H57" t="n">
-        <v>90.27554600000001</v>
+        <v>235.463628</v>
       </c>
       <c r="I57" t="n">
-        <v>63.309303</v>
+        <v>359.573597</v>
       </c>
       <c r="J57" t="n">
-        <v>156.840719</v>
-      </c>
-      <c r="K57" t="n">
-        <v>128.352831</v>
+        <v>137.69556</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>橡膠工業右下上市</t>
+          <t>橡膠工業平上市</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0</v>
-      </c>
-      <c r="C58" t="n">
-        <v>342.115921</v>
-      </c>
+        <v>0.448149</v>
+      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="n">
-        <v>199.233712</v>
+        <v>110.326311</v>
       </c>
       <c r="E58" t="n">
-        <v>150.43609</v>
+        <v>67.582936</v>
       </c>
       <c r="F58" t="n">
-        <v>116.233975</v>
+        <v>210.676112</v>
       </c>
       <c r="G58" t="n">
-        <v>165.105133</v>
+        <v>34.688359</v>
       </c>
       <c r="H58" t="n">
-        <v>219.105697</v>
+        <v>20.422541</v>
       </c>
       <c r="I58" t="n">
-        <v>172.168685</v>
+        <v>54.74745</v>
       </c>
       <c r="J58" t="n">
-        <v>235.463628</v>
-      </c>
-      <c r="K58" t="n">
-        <v>359.573597</v>
+        <v>34.823483</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>橡膠工業平上市</t>
+          <t>水泥工業右上上市</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="n">
-        <v>2.628045</v>
+        <v>3742.980955</v>
       </c>
       <c r="D59" t="n">
-        <v>1.633551</v>
+        <v>995.089243</v>
       </c>
       <c r="E59" t="n">
-        <v>4.689042</v>
+        <v>796.559063</v>
       </c>
       <c r="F59" t="n">
-        <v>6.161473</v>
+        <v>2967.114292</v>
       </c>
       <c r="G59" t="n">
-        <v>2.007921</v>
+        <v>1412.587301</v>
       </c>
       <c r="H59" t="n">
-        <v>1.475854</v>
+        <v>641.982484</v>
       </c>
       <c r="I59" t="n">
-        <v>0.842734</v>
+        <v>900.0369920000001</v>
       </c>
       <c r="J59" t="n">
-        <v>2.238886</v>
-      </c>
-      <c r="K59" t="n">
-        <v>2.490222</v>
+        <v>674.559882</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>水泥工業右上上市</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr"/>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
+          <t>水泥工業右下上市</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>23.131303</v>
+      </c>
+      <c r="C60" t="n">
+        <v>27.97068</v>
+      </c>
+      <c r="D60" t="n">
+        <v>23.890866</v>
+      </c>
       <c r="E60" t="n">
-        <v>3336.742112</v>
+        <v>36.108083</v>
       </c>
       <c r="F60" t="n">
-        <v>995.089243</v>
+        <v>25.533089</v>
       </c>
       <c r="G60" t="n">
-        <v>796.559063</v>
+        <v>24.011971</v>
       </c>
       <c r="H60" t="n">
-        <v>2745.271403</v>
+        <v>17.212754</v>
       </c>
       <c r="I60" t="n">
-        <v>1412.587301</v>
+        <v>19.640078</v>
       </c>
       <c r="J60" t="n">
-        <v>641.982484</v>
-      </c>
-      <c r="K60" t="inlineStr"/>
+        <v>20.295194</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>水泥工業右下上市</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr"/>
-      <c r="C61" t="n">
-        <v>195.322445</v>
-      </c>
+          <t>水泥工業平上市</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>949.079145</v>
+      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="n">
-        <v>249.15688</v>
+        <v>265.593417</v>
       </c>
       <c r="E61" t="n">
-        <v>27.97068</v>
-      </c>
-      <c r="F61" t="n">
-        <v>289.484283</v>
-      </c>
+        <v>339.290351</v>
+      </c>
+      <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
-        <v>375.398434</v>
+        <v>420.783956</v>
       </c>
       <c r="H61" t="n">
-        <v>247.375978</v>
+        <v>174.267952</v>
       </c>
       <c r="I61" t="n">
-        <v>444.795927</v>
+        <v>181.634068</v>
       </c>
       <c r="J61" t="n">
-        <v>191.480706</v>
-      </c>
-      <c r="K61" t="n">
-        <v>201.274146</v>
+        <v>245.309947</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>水泥工業平上市</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr"/>
+          <t>汽車工業右上上市</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>806.547029</v>
+      </c>
       <c r="C62" t="n">
-        <v>300.58702</v>
+        <v>1669.721101</v>
       </c>
       <c r="D62" t="n">
-        <v>723.053568</v>
+        <v>1001.153987</v>
       </c>
       <c r="E62" t="n">
-        <v>406.238843</v>
-      </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="n">
-        <v>900.0369920000001</v>
+        <v>1376.904598</v>
+      </c>
+      <c r="F62" t="n">
+        <v>2530.817868</v>
+      </c>
+      <c r="G62" t="n">
+        <v>894.608758</v>
+      </c>
+      <c r="H62" t="n">
+        <v>1258.292474</v>
+      </c>
+      <c r="I62" t="n">
+        <v>2023.334911</v>
+      </c>
+      <c r="J62" t="n">
+        <v>2376.922796</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>汽車工業右上上市</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr"/>
+          <t>汽車工業右下上市</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>420.177898</v>
+      </c>
       <c r="C63" t="n">
-        <v>811.908445</v>
+        <v>295.1171815</v>
       </c>
       <c r="D63" t="n">
-        <v>736.432685</v>
+        <v>270.273582</v>
       </c>
       <c r="E63" t="n">
-        <v>1376.488449</v>
+        <v>464.299762</v>
       </c>
       <c r="F63" t="n">
-        <v>739.149461</v>
+        <v>412.71605</v>
       </c>
       <c r="G63" t="n">
-        <v>1116.671849</v>
+        <v>323.712412</v>
       </c>
       <c r="H63" t="n">
-        <v>2266.668821</v>
+        <v>377.708464</v>
       </c>
       <c r="I63" t="n">
-        <v>703.694757</v>
+        <v>620.992344</v>
       </c>
       <c r="J63" t="n">
-        <v>1006.860223</v>
-      </c>
-      <c r="K63" t="n">
-        <v>1741.231331</v>
+        <v>714.964128</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>汽車工業右下上市</t>
+          <t>汽車工業平上市</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0</v>
+        <v>269.349393</v>
       </c>
       <c r="C64" t="n">
-        <v>427.38797</v>
+        <v>199.842169</v>
       </c>
       <c r="D64" t="n">
-        <v>486.394346</v>
+        <v>208.878708</v>
       </c>
       <c r="E64" t="n">
-        <v>442.6297595</v>
+        <v>198.14848</v>
       </c>
       <c r="F64" t="n">
-        <v>418.980136</v>
+        <v>284.679117</v>
       </c>
       <c r="G64" t="n">
-        <v>481.024679</v>
+        <v>244.890534</v>
       </c>
       <c r="H64" t="n">
-        <v>639.632731</v>
+        <v>391.432299</v>
       </c>
       <c r="I64" t="n">
-        <v>482.415312</v>
+        <v>183.768815</v>
       </c>
       <c r="J64" t="n">
-        <v>672.995857</v>
-      </c>
-      <c r="K64" t="n">
-        <v>647.508377</v>
+        <v>116.196973</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>汽車工業平上市</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr"/>
+          <t>油電燃氣業右上上市</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>1563.610846</v>
+      </c>
       <c r="C65" t="n">
-        <v>56.104699</v>
+        <v>1120.951175</v>
       </c>
       <c r="D65" t="n">
-        <v>41.807062</v>
+        <v>1016.909933</v>
       </c>
       <c r="E65" t="n">
-        <v>12.430991</v>
+        <v>3827.737724</v>
       </c>
       <c r="F65" t="n">
-        <v>20.413591</v>
+        <v>3768.070051</v>
       </c>
       <c r="G65" t="n">
-        <v>46.925254</v>
+        <v>2657.525003</v>
       </c>
       <c r="H65" t="n">
-        <v>77.7034</v>
+        <v>3632.530573</v>
       </c>
       <c r="I65" t="n">
-        <v>54.51133</v>
+        <v>2115.763698</v>
       </c>
       <c r="J65" t="n">
-        <v>46.653295</v>
-      </c>
-      <c r="K65" t="n">
-        <v>79.294453</v>
+        <v>2490.682467</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業右上上市</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr"/>
+          <t>油電燃氣業右下上市</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>4.976994</v>
+      </c>
       <c r="C66" t="n">
-        <v>1540.444376</v>
+        <v>4.671305</v>
       </c>
       <c r="D66" t="n">
-        <v>1564.428917</v>
+        <v>4.464252</v>
       </c>
       <c r="E66" t="n">
-        <v>1207.454396</v>
+        <v>6.8068</v>
       </c>
       <c r="F66" t="n">
-        <v>1016.909933</v>
+        <v>5.852749</v>
       </c>
       <c r="G66" t="n">
-        <v>3902.406555</v>
+        <v>3.578119</v>
       </c>
       <c r="H66" t="n">
-        <v>3768.592343</v>
+        <v>6.830817</v>
       </c>
       <c r="I66" t="n">
-        <v>2658.038261</v>
+        <v>6.653482</v>
       </c>
       <c r="J66" t="n">
-        <v>3633.52439</v>
-      </c>
-      <c r="K66" t="n">
-        <v>2116.46865</v>
+        <v>13.578305</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業右下上市</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr"/>
+          <t>油電燃氣業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>0.004074</v>
+      </c>
       <c r="C67" t="n">
-        <v>6.854077</v>
+        <v>0.00622</v>
       </c>
       <c r="D67" t="n">
-        <v>5.220213</v>
+        <v>0.003165</v>
       </c>
       <c r="E67" t="n">
-        <v>4.671305</v>
+        <v>0.003294</v>
       </c>
       <c r="F67" t="n">
-        <v>4.464252</v>
+        <v>0.002846</v>
       </c>
       <c r="G67" t="n">
-        <v>6.8068</v>
+        <v>0.00394</v>
       </c>
       <c r="H67" t="n">
-        <v>5.852749</v>
+        <v>0.0022</v>
       </c>
       <c r="I67" t="n">
-        <v>3.578119</v>
+        <v>0.007126</v>
       </c>
       <c r="J67" t="n">
-        <v>6.830817</v>
-      </c>
-      <c r="K67" t="n">
-        <v>6.653482</v>
+        <v>0.005304</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr"/>
+          <t>油電燃氣業平上市</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>1.06129</v>
+      </c>
       <c r="C68" t="n">
-        <v>0.012637</v>
+        <v>88.001926</v>
       </c>
       <c r="D68" t="n">
-        <v>0.006094</v>
+        <v>0.416998</v>
       </c>
       <c r="E68" t="n">
-        <v>0.010957</v>
+        <v>75.293695</v>
       </c>
       <c r="F68" t="n">
-        <v>0.015956</v>
+        <v>1.0206</v>
       </c>
       <c r="G68" t="n">
-        <v>0.007131</v>
+        <v>0.687299</v>
       </c>
       <c r="H68" t="n">
-        <v>0.013587</v>
+        <v>0.993817</v>
       </c>
       <c r="I68" t="n">
-        <v>0.004641</v>
+        <v>0.704952</v>
       </c>
       <c r="J68" t="n">
-        <v>0.003086</v>
-      </c>
-      <c r="K68" t="n">
-        <v>0.007185</v>
+        <v>3.028703</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業平上市</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr"/>
+          <t>油電燃氣業平上櫃</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>0.00202</v>
+      </c>
       <c r="C69" t="n">
-        <v>0.102422</v>
-      </c>
-      <c r="D69" t="inlineStr"/>
+        <v>0.004737</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0.012791</v>
+      </c>
       <c r="E69" t="n">
-        <v>1.498705</v>
+        <v>0.003837</v>
       </c>
       <c r="F69" t="n">
-        <v>0.416998</v>
+        <v>0.010741</v>
       </c>
       <c r="G69" t="n">
-        <v>0.624864</v>
+        <v>0.000701</v>
       </c>
       <c r="H69" t="n">
-        <v>0.498308</v>
+        <v>0.000886</v>
       </c>
       <c r="I69" t="n">
-        <v>0.174041</v>
-      </c>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
+        <v>5.9e-05</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.012012</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
@@ -2831,33 +2782,32 @@
           <t>玻璃陶瓷右上上市</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr"/>
+      <c r="B70" t="n">
+        <v>180.249203</v>
+      </c>
       <c r="C70" t="n">
-        <v>1201.340143</v>
+        <v>308.760818</v>
       </c>
       <c r="D70" t="n">
-        <v>1622.333522</v>
+        <v>336.767867</v>
       </c>
       <c r="E70" t="n">
-        <v>960.244794</v>
+        <v>1394.507219</v>
       </c>
       <c r="F70" t="n">
-        <v>484.323571</v>
+        <v>980.572891</v>
       </c>
       <c r="G70" t="n">
-        <v>485.054299</v>
+        <v>297.549161</v>
       </c>
       <c r="H70" t="n">
-        <v>1474.814442</v>
+        <v>572.510755</v>
       </c>
       <c r="I70" t="n">
-        <v>944.915521</v>
+        <v>255.941381</v>
       </c>
       <c r="J70" t="n">
-        <v>745.171033</v>
-      </c>
-      <c r="K70" t="n">
-        <v>1425.148387</v>
+        <v>148.635317</v>
       </c>
     </row>
     <row r="71">
@@ -2867,34 +2817,31 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0</v>
+        <v>1.292641</v>
       </c>
       <c r="C71" t="n">
-        <v>0.751342</v>
+        <v>0.469083</v>
       </c>
       <c r="D71" t="n">
-        <v>1.292641</v>
+        <v>0.521244</v>
       </c>
       <c r="E71" t="n">
-        <v>0.469083</v>
+        <v>0.500364</v>
       </c>
       <c r="F71" t="n">
-        <v>0.521244</v>
+        <v>1.209878</v>
       </c>
       <c r="G71" t="n">
-        <v>0.500364</v>
+        <v>2.726514</v>
       </c>
       <c r="H71" t="n">
-        <v>1.209878</v>
+        <v>0.8914299999999999</v>
       </c>
       <c r="I71" t="n">
-        <v>2.726514</v>
+        <v>1.117833</v>
       </c>
       <c r="J71" t="n">
-        <v>0.8914299999999999</v>
-      </c>
-      <c r="K71" t="n">
-        <v>1.117833</v>
+        <v>2.289033</v>
       </c>
     </row>
     <row r="72">
@@ -2903,27 +2850,32 @@
           <t>玻璃陶瓷平上市</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr"/>
-      <c r="C72" t="inlineStr"/>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
+      <c r="B72" t="n">
+        <v>1593.900291</v>
+      </c>
+      <c r="C72" t="n">
+        <v>931.223287</v>
+      </c>
+      <c r="D72" t="n">
+        <v>464.349189</v>
+      </c>
+      <c r="E72" t="n">
+        <v>460.082038</v>
+      </c>
       <c r="F72" t="n">
-        <v>0.744384</v>
+        <v>1411.506215</v>
       </c>
       <c r="G72" t="n">
-        <v>1.920693</v>
+        <v>913.096038</v>
       </c>
       <c r="H72" t="n">
-        <v>1.202745</v>
+        <v>716.628303</v>
       </c>
       <c r="I72" t="n">
-        <v>0.680389</v>
+        <v>1391.651459</v>
       </c>
       <c r="J72" t="n">
-        <v>0.440229</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0.617168</v>
+        <v>1434.343204</v>
       </c>
     </row>
     <row r="73">
@@ -2932,33 +2884,32 @@
           <t>生技醫療業右上上市</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr"/>
+      <c r="B73" t="n">
+        <v>6022.66941</v>
+      </c>
       <c r="C73" t="n">
-        <v>5530.108833</v>
+        <v>5969.716865</v>
       </c>
       <c r="D73" t="n">
-        <v>5999.20372</v>
+        <v>4097.608961</v>
       </c>
       <c r="E73" t="n">
-        <v>5951.907732</v>
+        <v>3867.64655</v>
       </c>
       <c r="F73" t="n">
-        <v>3086.100039</v>
+        <v>4196.073425</v>
       </c>
       <c r="G73" t="n">
-        <v>3550.154512</v>
+        <v>6374.150305</v>
       </c>
       <c r="H73" t="n">
-        <v>4177.965948</v>
+        <v>2873.532273</v>
       </c>
       <c r="I73" t="n">
-        <v>6361.363512</v>
+        <v>3358.834664</v>
       </c>
       <c r="J73" t="n">
-        <v>2845.412558</v>
-      </c>
-      <c r="K73" t="n">
-        <v>3329.460827</v>
+        <v>3005.278808</v>
       </c>
     </row>
     <row r="74">
@@ -2967,33 +2918,32 @@
           <t>生技醫療業右上上櫃</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr"/>
+      <c r="B74" t="n">
+        <v>1.27838</v>
+      </c>
       <c r="C74" t="n">
-        <v>1.269344</v>
+        <v>0.974698</v>
       </c>
       <c r="D74" t="n">
-        <v>1.218987</v>
+        <v>0.796296</v>
       </c>
       <c r="E74" t="n">
-        <v>0.8600989999999999</v>
+        <v>0.814196</v>
       </c>
       <c r="F74" t="n">
-        <v>0.669752</v>
+        <v>1.607912</v>
       </c>
       <c r="G74" t="n">
-        <v>0.773203</v>
+        <v>1.910936</v>
       </c>
       <c r="H74" t="n">
-        <v>1.585432</v>
+        <v>1.355821</v>
       </c>
       <c r="I74" t="n">
-        <v>1.823919</v>
+        <v>1.149426</v>
       </c>
       <c r="J74" t="n">
-        <v>1.303966</v>
-      </c>
-      <c r="K74" t="n">
-        <v>1.141856</v>
+        <v>1.307722</v>
       </c>
     </row>
     <row r="75">
@@ -3003,34 +2953,31 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0</v>
+        <v>1420.340333</v>
       </c>
       <c r="C75" t="n">
-        <v>1394.507632</v>
+        <v>790.299203</v>
       </c>
       <c r="D75" t="n">
-        <v>1439.696257</v>
+        <v>882.589772</v>
       </c>
       <c r="E75" t="n">
-        <v>1221.898304</v>
+        <v>831.72542</v>
       </c>
       <c r="F75" t="n">
-        <v>932.288263</v>
+        <v>987.591167</v>
       </c>
       <c r="G75" t="n">
-        <v>871.923425</v>
+        <v>570.880037</v>
       </c>
       <c r="H75" t="n">
-        <v>1063.75342</v>
+        <v>1361.174952</v>
       </c>
       <c r="I75" t="n">
-        <v>929.41603</v>
+        <v>952.7902769999999</v>
       </c>
       <c r="J75" t="n">
-        <v>1420.761809</v>
-      </c>
-      <c r="K75" t="n">
-        <v>967.64696</v>
+        <v>783.46231</v>
       </c>
     </row>
     <row r="76">
@@ -3039,33 +2986,32 @@
           <t>生技醫療業右下上櫃</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr"/>
+      <c r="B76" t="n">
+        <v>0.40359625</v>
+      </c>
       <c r="C76" t="n">
-        <v>0.289821</v>
+        <v>0.345726</v>
       </c>
       <c r="D76" t="n">
-        <v>0.36148825</v>
+        <v>0.3164330833333333</v>
       </c>
       <c r="E76" t="n">
-        <v>0.306347</v>
+        <v>0.3441363333333333</v>
       </c>
       <c r="F76" t="n">
-        <v>0.3893810833333333</v>
+        <v>0.3782826666666667</v>
       </c>
       <c r="G76" t="n">
-        <v>0.3151093333333333</v>
+        <v>0.3214551666666667</v>
       </c>
       <c r="H76" t="n">
-        <v>0.4294376666666667</v>
+        <v>0.3575395</v>
       </c>
       <c r="I76" t="n">
-        <v>0.4170741666666667</v>
+        <v>0.7056954166666666</v>
       </c>
       <c r="J76" t="n">
-        <v>0.3776865</v>
-      </c>
-      <c r="K76" t="n">
-        <v>0.7297864166666667</v>
+        <v>0.512689</v>
       </c>
     </row>
     <row r="77">
@@ -3074,33 +3020,32 @@
           <t>生技醫療業平上市</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr"/>
+      <c r="B77" t="n">
+        <v>52.616483</v>
+      </c>
       <c r="C77" t="n">
-        <v>37.474575</v>
+        <v>466.542454</v>
       </c>
       <c r="D77" t="n">
-        <v>42.889883</v>
+        <v>85.77894999999999</v>
       </c>
       <c r="E77" t="n">
-        <v>46.709506</v>
+        <v>121.884585</v>
       </c>
       <c r="F77" t="n">
-        <v>1042.089824</v>
+        <v>149.655613</v>
       </c>
       <c r="G77" t="n">
-        <v>385.855107</v>
+        <v>393.7089</v>
       </c>
       <c r="H77" t="n">
-        <v>80.16861400000001</v>
+        <v>129.548609</v>
       </c>
       <c r="I77" t="n">
-        <v>40.646904</v>
+        <v>80.302712</v>
       </c>
       <c r="J77" t="n">
-        <v>87.079731</v>
-      </c>
-      <c r="K77" t="n">
-        <v>80.315482</v>
+        <v>63.975701</v>
       </c>
     </row>
     <row r="78">
@@ -3109,33 +3054,32 @@
           <t>生技醫療業平上櫃</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr"/>
+      <c r="B78" t="n">
+        <v>0.164759</v>
+      </c>
       <c r="C78" t="n">
-        <v>0.228616</v>
+        <v>0.165728</v>
       </c>
       <c r="D78" t="n">
-        <v>0.217362</v>
+        <v>0.1738</v>
       </c>
       <c r="E78" t="n">
-        <v>0.275593</v>
+        <v>0.06646000000000001</v>
       </c>
       <c r="F78" t="n">
-        <v>0.190755</v>
+        <v>0.181862</v>
       </c>
       <c r="G78" t="n">
-        <v>0.104061</v>
+        <v>0.126775</v>
       </c>
       <c r="H78" t="n">
-        <v>0.121558</v>
+        <v>0.097179</v>
       </c>
       <c r="I78" t="n">
-        <v>0.08987299999999999</v>
+        <v>0.148083</v>
       </c>
       <c r="J78" t="n">
-        <v>0.09468699999999999</v>
-      </c>
-      <c r="K78" t="n">
-        <v>0.090987</v>
+        <v>0.09477774999999999</v>
       </c>
     </row>
     <row r="79">
@@ -3144,33 +3088,32 @@
           <t>紡織纖維右上上市</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr"/>
+      <c r="B79" t="n">
+        <v>243.927543</v>
+      </c>
       <c r="C79" t="n">
-        <v>191.889821</v>
+        <v>156.612433</v>
       </c>
       <c r="D79" t="n">
-        <v>254.467923</v>
+        <v>292.472929</v>
       </c>
       <c r="E79" t="n">
-        <v>167.925014</v>
+        <v>185.653581</v>
       </c>
       <c r="F79" t="n">
-        <v>144.37402</v>
+        <v>680.52637</v>
       </c>
       <c r="G79" t="n">
-        <v>192.102061</v>
+        <v>253.387223</v>
       </c>
       <c r="H79" t="n">
-        <v>486.835413</v>
+        <v>522.9243310000001</v>
       </c>
       <c r="I79" t="n">
-        <v>255.407393</v>
+        <v>698.51841</v>
       </c>
       <c r="J79" t="n">
-        <v>389.4149</v>
-      </c>
-      <c r="K79" t="n">
-        <v>699.954172</v>
+        <v>474.371744</v>
       </c>
     </row>
     <row r="80">
@@ -3179,33 +3122,32 @@
           <t>紡織纖維右上上櫃</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr"/>
+      <c r="B80" t="n">
+        <v>0.004252</v>
+      </c>
       <c r="C80" t="n">
-        <v>0.002949</v>
+        <v>0.002614</v>
       </c>
       <c r="D80" t="n">
-        <v>0.004252</v>
+        <v>0.003562</v>
       </c>
       <c r="E80" t="n">
-        <v>0.002614</v>
+        <v>0.002342</v>
       </c>
       <c r="F80" t="n">
-        <v>0.003562</v>
+        <v>0.003026</v>
       </c>
       <c r="G80" t="n">
-        <v>0.002342</v>
+        <v>0.000842</v>
       </c>
       <c r="H80" t="n">
-        <v>0.003026</v>
+        <v>0.001892</v>
       </c>
       <c r="I80" t="n">
-        <v>0.000842</v>
+        <v>0.001417</v>
       </c>
       <c r="J80" t="n">
-        <v>0.001892</v>
-      </c>
-      <c r="K80" t="n">
-        <v>0.001417</v>
+        <v>0.003551</v>
       </c>
     </row>
     <row r="81">
@@ -3214,33 +3156,32 @@
           <t>紡織纖維右下上市</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr"/>
+      <c r="B81" t="n">
+        <v>1029.650505</v>
+      </c>
       <c r="C81" t="n">
-        <v>538.748886</v>
+        <v>529.1533889999999</v>
       </c>
       <c r="D81" t="n">
-        <v>1029.650505</v>
+        <v>559.467184</v>
       </c>
       <c r="E81" t="n">
-        <v>528.422161</v>
+        <v>497.35158</v>
       </c>
       <c r="F81" t="n">
-        <v>563.181368</v>
+        <v>690.9260829999999</v>
       </c>
       <c r="G81" t="n">
-        <v>498.794683</v>
+        <v>429.938206</v>
       </c>
       <c r="H81" t="n">
-        <v>691.878292</v>
+        <v>409.600498</v>
       </c>
       <c r="I81" t="n">
-        <v>430.52915</v>
+        <v>925.605107</v>
       </c>
       <c r="J81" t="n">
-        <v>409.086257</v>
-      </c>
-      <c r="K81" t="n">
-        <v>926.442956</v>
+        <v>1273.61289</v>
       </c>
     </row>
     <row r="82">
@@ -3249,33 +3190,32 @@
           <t>紡織纖維右下上櫃</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr"/>
+      <c r="B82" t="n">
+        <v>0.009835</v>
+      </c>
       <c r="C82" t="n">
-        <v>0.005398</v>
+        <v>0.003755</v>
       </c>
       <c r="D82" t="n">
-        <v>0.0078</v>
+        <v>0.003866</v>
       </c>
       <c r="E82" t="n">
-        <v>0.003755</v>
+        <v>0.002449</v>
       </c>
       <c r="F82" t="n">
-        <v>0.003316</v>
+        <v>0.005551</v>
       </c>
       <c r="G82" t="n">
-        <v>0.001696</v>
+        <v>0.003023</v>
       </c>
       <c r="H82" t="n">
-        <v>0.005551</v>
+        <v>0.002772</v>
       </c>
       <c r="I82" t="n">
-        <v>0.001959</v>
+        <v>0.004978</v>
       </c>
       <c r="J82" t="n">
-        <v>0.002287</v>
-      </c>
-      <c r="K82" t="n">
-        <v>0.004319</v>
+        <v>0.006434</v>
       </c>
     </row>
     <row r="83">
@@ -3284,33 +3224,32 @@
           <t>紡織纖維平上市</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr"/>
+      <c r="B83" t="n">
+        <v>181.637446</v>
+      </c>
       <c r="C83" t="n">
-        <v>192.910397</v>
+        <v>195.153821</v>
       </c>
       <c r="D83" t="n">
-        <v>171.097066</v>
+        <v>89.492357</v>
       </c>
       <c r="E83" t="n">
-        <v>184.572468</v>
+        <v>225.18276</v>
       </c>
       <c r="F83" t="n">
-        <v>233.877082</v>
+        <v>15.404155</v>
       </c>
       <c r="G83" t="n">
-        <v>217.291177</v>
+        <v>464.799887</v>
       </c>
       <c r="H83" t="n">
-        <v>208.142903</v>
+        <v>41.503846</v>
       </c>
       <c r="I83" t="n">
-        <v>462.188773</v>
+        <v>244.633057</v>
       </c>
       <c r="J83" t="n">
-        <v>175.527518</v>
-      </c>
-      <c r="K83" t="n">
-        <v>242.359446</v>
+        <v>160.028175</v>
       </c>
     </row>
     <row r="84">
@@ -3319,33 +3258,32 @@
           <t>紡織纖維平上櫃</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr"/>
+      <c r="B84" t="n">
+        <v>0.002626</v>
+      </c>
       <c r="C84" t="n">
-        <v>0.002764</v>
+        <v>0.003386</v>
       </c>
       <c r="D84" t="n">
-        <v>0.004661</v>
+        <v>0.001247</v>
       </c>
       <c r="E84" t="n">
-        <v>0.003386</v>
+        <v>0.002145</v>
       </c>
       <c r="F84" t="n">
-        <v>0.001797</v>
+        <v>0.003993</v>
       </c>
       <c r="G84" t="n">
-        <v>0.002898</v>
+        <v>0.001704</v>
       </c>
       <c r="H84" t="n">
-        <v>0.003993</v>
+        <v>0.001875</v>
       </c>
       <c r="I84" t="n">
-        <v>0.002768</v>
+        <v>0.004246</v>
       </c>
       <c r="J84" t="n">
-        <v>0.00236</v>
-      </c>
-      <c r="K84" t="n">
-        <v>0.004905</v>
+        <v>0.0024</v>
       </c>
     </row>
     <row r="85">
@@ -3354,33 +3292,32 @@
           <t>綠能環保右上上市</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr"/>
+      <c r="B85" t="n">
+        <v>1169.933032</v>
+      </c>
       <c r="C85" t="n">
-        <v>1362.620758</v>
+        <v>1083.445147</v>
       </c>
       <c r="D85" t="n">
-        <v>1242.464558</v>
+        <v>987.254875</v>
       </c>
       <c r="E85" t="n">
-        <v>1080.528652</v>
+        <v>1065.228574</v>
       </c>
       <c r="F85" t="n">
-        <v>1417.01767</v>
+        <v>1461.418548</v>
       </c>
       <c r="G85" t="n">
-        <v>1587.058712</v>
+        <v>1090.069752</v>
       </c>
       <c r="H85" t="n">
-        <v>1847.634114</v>
+        <v>1296.447198</v>
       </c>
       <c r="I85" t="n">
-        <v>1606.405262</v>
+        <v>2458.697829</v>
       </c>
       <c r="J85" t="n">
-        <v>1655.750715</v>
-      </c>
-      <c r="K85" t="n">
-        <v>2934.521909</v>
+        <v>1089.254445</v>
       </c>
     </row>
     <row r="86">
@@ -3389,33 +3326,32 @@
           <t>綠能環保右上上櫃</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr"/>
+      <c r="B86" t="n">
+        <v>0.056319</v>
+      </c>
       <c r="C86" t="n">
-        <v>0.490202</v>
+        <v>0.08539099999999999</v>
       </c>
       <c r="D86" t="n">
-        <v>0.06761399999999999</v>
+        <v>0.08933199999999999</v>
       </c>
       <c r="E86" t="n">
-        <v>0.08539099999999999</v>
+        <v>0.031627</v>
       </c>
       <c r="F86" t="n">
-        <v>0.08933199999999999</v>
+        <v>0.034733</v>
       </c>
       <c r="G86" t="n">
-        <v>0.210435</v>
+        <v>0.06268700000000001</v>
       </c>
       <c r="H86" t="n">
-        <v>0.210932</v>
+        <v>0.668552</v>
       </c>
       <c r="I86" t="n">
-        <v>0.278157</v>
+        <v>0.483589</v>
       </c>
       <c r="J86" t="n">
-        <v>0.668552</v>
-      </c>
-      <c r="K86" t="n">
-        <v>0.483589</v>
+        <v>0.361396</v>
       </c>
     </row>
     <row r="87">
@@ -3424,33 +3360,32 @@
           <t>綠能環保右下上市</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr"/>
+      <c r="B87" t="n">
+        <v>621.8295010000001</v>
+      </c>
       <c r="C87" t="n">
-        <v>340.975202</v>
+        <v>539.273703</v>
       </c>
       <c r="D87" t="n">
-        <v>377.61428</v>
+        <v>278.616048</v>
       </c>
       <c r="E87" t="n">
-        <v>308.43768</v>
+        <v>274.468824</v>
       </c>
       <c r="F87" t="n">
-        <v>287.683514</v>
+        <v>246.334542</v>
       </c>
       <c r="G87" t="n">
-        <v>274.468824</v>
+        <v>273.107014</v>
       </c>
       <c r="H87" t="n">
-        <v>248.735441</v>
+        <v>308.175048</v>
       </c>
       <c r="I87" t="n">
-        <v>280.548546</v>
+        <v>514.506952</v>
       </c>
       <c r="J87" t="n">
-        <v>316.477195</v>
-      </c>
-      <c r="K87" t="n">
-        <v>515.226859</v>
+        <v>314.34913</v>
       </c>
     </row>
     <row r="88">
@@ -3459,33 +3394,32 @@
           <t>綠能環保右下上櫃</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr"/>
+      <c r="B88" t="n">
+        <v>0.223725</v>
+      </c>
       <c r="C88" t="n">
-        <v>0.028041</v>
+        <v>0.2862343333333333</v>
       </c>
       <c r="D88" t="n">
-        <v>0.035772</v>
+        <v>0.114534</v>
       </c>
       <c r="E88" t="n">
-        <v>0.02672833333333334</v>
+        <v>0.06042566666666667</v>
       </c>
       <c r="F88" t="n">
-        <v>0.016288</v>
+        <v>0.040755</v>
       </c>
       <c r="G88" t="n">
-        <v>0.03483266666666667</v>
+        <v>0.03678</v>
       </c>
       <c r="H88" t="n">
-        <v>0.024313</v>
+        <v>0.041197</v>
       </c>
       <c r="I88" t="n">
-        <v>0.017407</v>
+        <v>0.112541</v>
       </c>
       <c r="J88" t="n">
-        <v>0.023258</v>
-      </c>
-      <c r="K88" t="n">
-        <v>0.049814</v>
+        <v>0.09009399999999999</v>
       </c>
     </row>
     <row r="89">
@@ -3494,33 +3428,32 @@
           <t>綠能環保平上市</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr"/>
+      <c r="B89" t="n">
+        <v>87.93873600000001</v>
+      </c>
       <c r="C89" t="n">
-        <v>193.637222</v>
+        <v>13.809897</v>
       </c>
       <c r="D89" t="n">
-        <v>259.622431</v>
+        <v>456.031398</v>
       </c>
       <c r="E89" t="n">
-        <v>247.562415</v>
+        <v>544.36019</v>
       </c>
       <c r="F89" t="n">
-        <v>17.201137</v>
+        <v>411.932598</v>
       </c>
       <c r="G89" t="n">
-        <v>22.530052</v>
+        <v>545.813419</v>
       </c>
       <c r="H89" t="n">
-        <v>23.316133</v>
+        <v>390.621942</v>
       </c>
       <c r="I89" t="n">
-        <v>22.036377</v>
+        <v>514.185082</v>
       </c>
       <c r="J89" t="n">
-        <v>23.016278</v>
-      </c>
-      <c r="K89" t="n">
-        <v>37.641095</v>
+        <v>441.689948</v>
       </c>
     </row>
     <row r="90">
@@ -3529,33 +3462,32 @@
           <t>綠能環保平上櫃</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr"/>
+      <c r="B90" t="n">
+        <v>0.013315</v>
+      </c>
       <c r="C90" t="n">
-        <v>0.000898</v>
+        <v>0.001381</v>
       </c>
       <c r="D90" t="n">
-        <v>0.189973</v>
+        <v>0.000392</v>
       </c>
       <c r="E90" t="n">
-        <v>0.260887</v>
+        <v>0.179047</v>
       </c>
       <c r="F90" t="n">
-        <v>0.098638</v>
+        <v>0.177882</v>
       </c>
       <c r="G90" t="n">
-        <v>0.025832</v>
+        <v>0.215974</v>
       </c>
       <c r="H90" t="n">
-        <v>0.018125</v>
+        <v>0.001</v>
       </c>
       <c r="I90" t="n">
-        <v>0.019877</v>
+        <v>0.001579</v>
       </c>
       <c r="J90" t="n">
-        <v>0.018939</v>
-      </c>
-      <c r="K90" t="n">
-        <v>0.064306</v>
+        <v>1e-05</v>
       </c>
     </row>
     <row r="91">
@@ -3564,33 +3496,32 @@
           <t>航運業右上上市</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr"/>
+      <c r="B91" t="n">
+        <v>5391.171935</v>
+      </c>
       <c r="C91" t="n">
-        <v>6458.851736</v>
+        <v>6706.51643</v>
       </c>
       <c r="D91" t="n">
-        <v>4536.012146</v>
+        <v>4550.993342</v>
       </c>
       <c r="E91" t="n">
-        <v>5141.094921</v>
+        <v>6235.148024</v>
       </c>
       <c r="F91" t="n">
-        <v>3937.638722</v>
+        <v>5045.109869</v>
       </c>
       <c r="G91" t="n">
-        <v>4902.34093</v>
+        <v>4288.824517</v>
       </c>
       <c r="H91" t="n">
-        <v>4162.974965</v>
+        <v>4613.845504</v>
       </c>
       <c r="I91" t="n">
-        <v>3628.725363</v>
+        <v>5575.912177</v>
       </c>
       <c r="J91" t="n">
-        <v>4015.794107</v>
-      </c>
-      <c r="K91" t="n">
-        <v>4930.886461</v>
+        <v>4810.449258</v>
       </c>
     </row>
     <row r="92">
@@ -3599,33 +3530,32 @@
           <t>航運業右下上市</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr"/>
+      <c r="B92" t="n">
+        <v>321.987568</v>
+      </c>
       <c r="C92" t="n">
-        <v>186.139995</v>
+        <v>323.013159</v>
       </c>
       <c r="D92" t="n">
-        <v>264.35394</v>
+        <v>223.085712</v>
       </c>
       <c r="E92" t="n">
-        <v>201.193499</v>
+        <v>319.29705</v>
       </c>
       <c r="F92" t="n">
-        <v>172.265618</v>
+        <v>272.893445</v>
       </c>
       <c r="G92" t="n">
-        <v>246.817529</v>
+        <v>227.609198</v>
       </c>
       <c r="H92" t="n">
-        <v>207.837683</v>
+        <v>252.512685</v>
       </c>
       <c r="I92" t="n">
-        <v>149.091351</v>
+        <v>366.233668</v>
       </c>
       <c r="J92" t="n">
-        <v>190.484063</v>
-      </c>
-      <c r="K92" t="n">
-        <v>276.736665</v>
+        <v>309.11194</v>
       </c>
     </row>
     <row r="93">
@@ -3634,33 +3564,32 @@
           <t>航運業右下上櫃</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr"/>
+      <c r="B93" t="n">
+        <v>0.017652</v>
+      </c>
       <c r="C93" t="n">
-        <v>0.023707</v>
+        <v>0.0187445</v>
       </c>
       <c r="D93" t="n">
-        <v>0.017652</v>
+        <v>0.015171</v>
       </c>
       <c r="E93" t="n">
-        <v>0.0187445</v>
+        <v>0.027518</v>
       </c>
       <c r="F93" t="n">
-        <v>0.012347</v>
+        <v>0.031577</v>
       </c>
       <c r="G93" t="n">
-        <v>0.018943</v>
+        <v>0.018536</v>
       </c>
       <c r="H93" t="n">
-        <v>0.021786</v>
+        <v>0.021268</v>
       </c>
       <c r="I93" t="n">
-        <v>0.018536</v>
+        <v>0.0430535</v>
       </c>
       <c r="J93" t="n">
-        <v>0.021268</v>
-      </c>
-      <c r="K93" t="n">
-        <v>0.0430535</v>
+        <v>0.043256</v>
       </c>
     </row>
     <row r="94">
@@ -3669,33 +3598,32 @@
           <t>航運業平上市</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr"/>
+      <c r="B94" t="n">
+        <v>637.521775</v>
+      </c>
       <c r="C94" t="n">
-        <v>295.44217</v>
+        <v>901.599531</v>
       </c>
       <c r="D94" t="n">
-        <v>1550.315192</v>
+        <v>692.5978699999999</v>
       </c>
       <c r="E94" t="n">
-        <v>2588.8407</v>
+        <v>291.581164</v>
       </c>
       <c r="F94" t="n">
-        <v>1356.772584</v>
+        <v>526.1090380000001</v>
       </c>
       <c r="G94" t="n">
-        <v>1696.867779</v>
+        <v>397.091163</v>
       </c>
       <c r="H94" t="n">
-        <v>1473.299704</v>
+        <v>293.732243</v>
       </c>
       <c r="I94" t="n">
-        <v>1135.708164</v>
+        <v>528.0670229999999</v>
       </c>
       <c r="J94" t="n">
-        <v>953.812262</v>
-      </c>
-      <c r="K94" t="n">
-        <v>1262.589742</v>
+        <v>341.479453</v>
       </c>
     </row>
     <row r="95">
@@ -3704,28 +3632,19 @@
           <t>航運業平上櫃</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr"/>
+      <c r="B95" t="n">
+        <v>0.003387</v>
+      </c>
       <c r="C95" t="n">
-        <v>0.007715</v>
-      </c>
-      <c r="D95" t="n">
-        <v>0.003387</v>
-      </c>
-      <c r="E95" t="n">
         <v>0.003643</v>
       </c>
-      <c r="F95" t="n">
-        <v>0.002824</v>
-      </c>
-      <c r="G95" t="n">
-        <v>0.008574999999999999</v>
-      </c>
-      <c r="H95" t="n">
-        <v>0.009790999999999999</v>
-      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
@@ -3733,33 +3652,32 @@
           <t>觀光事業右上上市</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr"/>
+      <c r="B96" t="n">
+        <v>17.981812</v>
+      </c>
       <c r="C96" t="n">
-        <v>18.052509</v>
+        <v>12.021829</v>
       </c>
       <c r="D96" t="n">
-        <v>14.958555</v>
+        <v>135.017384</v>
       </c>
       <c r="E96" t="n">
-        <v>11.00032</v>
+        <v>139.47937</v>
       </c>
       <c r="F96" t="n">
-        <v>8.780357</v>
+        <v>81.415419</v>
       </c>
       <c r="G96" t="n">
-        <v>105.657624</v>
+        <v>52.444073</v>
       </c>
       <c r="H96" t="n">
-        <v>79.71870199999999</v>
+        <v>95.54313500000001</v>
       </c>
       <c r="I96" t="n">
-        <v>49.868836</v>
+        <v>62.716002</v>
       </c>
       <c r="J96" t="n">
-        <v>57.785976</v>
-      </c>
-      <c r="K96" t="n">
-        <v>42.157955</v>
+        <v>27.640307</v>
       </c>
     </row>
     <row r="97">
@@ -3768,33 +3686,32 @@
           <t>觀光事業右上上櫃</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr"/>
+      <c r="B97" t="n">
+        <v>0.002788</v>
+      </c>
       <c r="C97" t="n">
-        <v>0.010267</v>
+        <v>0.005511</v>
       </c>
       <c r="D97" t="n">
-        <v>0.002791</v>
+        <v>0.005694</v>
       </c>
       <c r="E97" t="n">
-        <v>0.005545</v>
+        <v>0.009537</v>
       </c>
       <c r="F97" t="n">
-        <v>0.005721</v>
+        <v>0.028504</v>
       </c>
       <c r="G97" t="n">
-        <v>0.009771999999999999</v>
+        <v>0.0221175</v>
       </c>
       <c r="H97" t="n">
-        <v>0.028757</v>
+        <v>0.00347</v>
       </c>
       <c r="I97" t="n">
-        <v>0.0221915</v>
+        <v>0.001891</v>
       </c>
       <c r="J97" t="n">
-        <v>0.003814</v>
-      </c>
-      <c r="K97" t="n">
-        <v>0.002144</v>
+        <v>0.002712</v>
       </c>
     </row>
     <row r="98">
@@ -3804,34 +3721,31 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0</v>
+        <v>70.396855</v>
       </c>
       <c r="C98" t="n">
-        <v>57.379966</v>
+        <v>73.746514</v>
       </c>
       <c r="D98" t="n">
-        <v>94.060181</v>
+        <v>57.692754</v>
       </c>
       <c r="E98" t="n">
-        <v>72.018058</v>
+        <v>82.187201</v>
       </c>
       <c r="F98" t="n">
-        <v>56.471815</v>
+        <v>75.432047</v>
       </c>
       <c r="G98" t="n">
-        <v>81.909038</v>
+        <v>40.885461</v>
       </c>
       <c r="H98" t="n">
-        <v>74.94547900000001</v>
+        <v>48.094337</v>
       </c>
       <c r="I98" t="n">
-        <v>40.343542</v>
+        <v>76.15819</v>
       </c>
       <c r="J98" t="n">
-        <v>47.711996</v>
-      </c>
-      <c r="K98" t="n">
-        <v>75.638076</v>
+        <v>61.827034</v>
       </c>
     </row>
     <row r="99">
@@ -3840,33 +3754,32 @@
           <t>觀光事業右下上櫃</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr"/>
+      <c r="B99" t="n">
+        <v>0.035491</v>
+      </c>
       <c r="C99" t="n">
-        <v>0.039119</v>
+        <v>0.0379</v>
       </c>
       <c r="D99" t="n">
-        <v>0.036983</v>
+        <v>0.031141</v>
       </c>
       <c r="E99" t="n">
-        <v>0.03807</v>
+        <v>0.025722</v>
       </c>
       <c r="F99" t="n">
-        <v>0.031206</v>
+        <v>0.025105</v>
       </c>
       <c r="G99" t="n">
-        <v>0.025503</v>
+        <v>0.021688</v>
       </c>
       <c r="H99" t="n">
-        <v>0.026615</v>
+        <v>0.02571725</v>
       </c>
       <c r="I99" t="n">
-        <v>0.021823</v>
+        <v>0.035702</v>
       </c>
       <c r="J99" t="n">
-        <v>0.02542625</v>
-      </c>
-      <c r="K99" t="n">
-        <v>0.036685</v>
+        <v>0.051818</v>
       </c>
     </row>
     <row r="100">
@@ -3875,33 +3788,28 @@
           <t>觀光事業平上市</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr"/>
+      <c r="B100" t="n">
+        <v>63.217595</v>
+      </c>
       <c r="C100" t="n">
-        <v>27.989284</v>
+        <v>42.480294</v>
       </c>
       <c r="D100" t="n">
-        <v>41.997589</v>
+        <v>0.38104</v>
       </c>
       <c r="E100" t="n">
-        <v>43.501803</v>
-      </c>
-      <c r="F100" t="n">
-        <v>126.618067</v>
-      </c>
+        <v>0.7070109999999999</v>
+      </c>
+      <c r="F100" t="inlineStr"/>
       <c r="G100" t="n">
-        <v>34.528757</v>
-      </c>
-      <c r="H100" t="n">
-        <v>1.696717</v>
-      </c>
+        <v>70.926901</v>
+      </c>
+      <c r="H100" t="inlineStr"/>
       <c r="I100" t="n">
-        <v>73.502138</v>
+        <v>16.415354</v>
       </c>
       <c r="J100" t="n">
-        <v>37.757159</v>
-      </c>
-      <c r="K100" t="n">
-        <v>36.973401</v>
+        <v>20.866151</v>
       </c>
     </row>
     <row r="101">
@@ -3910,31 +3818,32 @@
           <t>觀光事業平上櫃</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr"/>
+      <c r="B101" t="n">
+        <v>0.002429</v>
+      </c>
       <c r="C101" t="n">
-        <v>3.7e-05</v>
+        <v>0.002757</v>
       </c>
       <c r="D101" t="n">
-        <v>5e-05</v>
+        <v>0.001633</v>
       </c>
       <c r="E101" t="n">
-        <v>0.001799</v>
+        <v>0.00077975</v>
       </c>
       <c r="F101" t="n">
-        <v>0.000703</v>
+        <v>0.002487</v>
       </c>
       <c r="G101" t="n">
-        <v>0.00026275</v>
+        <v>0.000375</v>
       </c>
       <c r="H101" t="n">
-        <v>0.000408</v>
-      </c>
-      <c r="I101" t="inlineStr"/>
+        <v>0.00052</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0.001889</v>
+      </c>
       <c r="J101" t="n">
-        <v>0.000231</v>
-      </c>
-      <c r="K101" t="n">
-        <v>0.000167</v>
+        <v>0.000857</v>
       </c>
     </row>
     <row r="102">
@@ -3943,33 +3852,32 @@
           <t>貿易百貨右上上市</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr"/>
+      <c r="B102" t="n">
+        <v>134.583649</v>
+      </c>
       <c r="C102" t="n">
-        <v>118.607371</v>
+        <v>173.191176</v>
       </c>
       <c r="D102" t="n">
-        <v>129.736089</v>
+        <v>124.12725</v>
       </c>
       <c r="E102" t="n">
-        <v>172.011245</v>
+        <v>123.87734</v>
       </c>
       <c r="F102" t="n">
-        <v>123.089602</v>
+        <v>101.572075</v>
       </c>
       <c r="G102" t="n">
-        <v>123.734111</v>
+        <v>97.257312</v>
       </c>
       <c r="H102" t="n">
-        <v>101.188944</v>
+        <v>116.831751</v>
       </c>
       <c r="I102" t="n">
-        <v>96.374189</v>
+        <v>120.134948</v>
       </c>
       <c r="J102" t="n">
-        <v>114.310155</v>
-      </c>
-      <c r="K102" t="n">
-        <v>117.16523</v>
+        <v>75.797059</v>
       </c>
     </row>
     <row r="103">
@@ -3978,33 +3886,32 @@
           <t>貿易百貨右下上市</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr"/>
+      <c r="B103" t="n">
+        <v>228.051738</v>
+      </c>
       <c r="C103" t="n">
-        <v>283.905508</v>
+        <v>545.00246</v>
       </c>
       <c r="D103" t="n">
-        <v>219.459544</v>
+        <v>502.007682</v>
       </c>
       <c r="E103" t="n">
-        <v>530.455793</v>
+        <v>353.8224913333333</v>
       </c>
       <c r="F103" t="n">
-        <v>482.217237</v>
+        <v>405.806172</v>
       </c>
       <c r="G103" t="n">
-        <v>354.9255993333333</v>
+        <v>516.970554</v>
       </c>
       <c r="H103" t="n">
-        <v>368.929928</v>
+        <v>676.738581</v>
       </c>
       <c r="I103" t="n">
-        <v>516.631265</v>
+        <v>292.238365</v>
       </c>
       <c r="J103" t="n">
-        <v>677.631095</v>
-      </c>
-      <c r="K103" t="n">
-        <v>293.270035</v>
+        <v>369.115774</v>
       </c>
     </row>
     <row r="104">
@@ -4013,33 +3920,32 @@
           <t>貿易百貨平上市</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr"/>
+      <c r="B104" t="n">
+        <v>1.363332</v>
+      </c>
       <c r="C104" t="n">
-        <v>31.444853</v>
+        <v>9.015001</v>
       </c>
       <c r="D104" t="n">
-        <v>14.803086</v>
+        <v>0.238075</v>
       </c>
       <c r="E104" t="n">
-        <v>24.741599</v>
+        <v>1.958319</v>
       </c>
       <c r="F104" t="n">
-        <v>21.066168</v>
+        <v>3.482226</v>
       </c>
       <c r="G104" t="n">
-        <v>0.99844</v>
+        <v>1.073951</v>
       </c>
       <c r="H104" t="n">
-        <v>40.741601</v>
+        <v>2.602827</v>
       </c>
       <c r="I104" t="n">
-        <v>2.296363</v>
+        <v>1.84696</v>
       </c>
       <c r="J104" t="n">
-        <v>4.231909</v>
-      </c>
-      <c r="K104" t="n">
-        <v>3.785008</v>
+        <v>1.850054</v>
       </c>
     </row>
     <row r="105">
@@ -4048,33 +3954,32 @@
           <t>資訊服務業右上上市</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr"/>
+      <c r="B105" t="n">
+        <v>999.44839</v>
+      </c>
       <c r="C105" t="n">
-        <v>796.716895</v>
+        <v>816.0570310000001</v>
       </c>
       <c r="D105" t="n">
-        <v>719.680639</v>
+        <v>921.361164</v>
       </c>
       <c r="E105" t="n">
-        <v>684.8656130000001</v>
+        <v>525.655053</v>
       </c>
       <c r="F105" t="n">
-        <v>733.865583</v>
+        <v>637.545508</v>
       </c>
       <c r="G105" t="n">
-        <v>418.030885</v>
+        <v>335.86408</v>
       </c>
       <c r="H105" t="n">
-        <v>547.916906</v>
+        <v>309.39226</v>
       </c>
       <c r="I105" t="n">
-        <v>262.218864</v>
+        <v>538.491268</v>
       </c>
       <c r="J105" t="n">
-        <v>217.2931</v>
-      </c>
-      <c r="K105" t="n">
-        <v>345.014255</v>
+        <v>622.022591</v>
       </c>
     </row>
     <row r="106">
@@ -4083,33 +3988,32 @@
           <t>資訊服務業右上上櫃</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr"/>
+      <c r="B106" t="n">
+        <v>0.28803</v>
+      </c>
       <c r="C106" t="n">
-        <v>0.157991</v>
+        <v>0.180248</v>
       </c>
       <c r="D106" t="n">
-        <v>0.153279</v>
+        <v>0.624803</v>
       </c>
       <c r="E106" t="n">
-        <v>0.06589</v>
+        <v>0.272337</v>
       </c>
       <c r="F106" t="n">
-        <v>0.316551</v>
+        <v>0.270188</v>
       </c>
       <c r="G106" t="n">
-        <v>0.151087</v>
+        <v>0.531964</v>
       </c>
       <c r="H106" t="n">
-        <v>0.145614</v>
+        <v>0.654319</v>
       </c>
       <c r="I106" t="n">
-        <v>0.440767</v>
+        <v>0.479901</v>
       </c>
       <c r="J106" t="n">
-        <v>0.579151</v>
-      </c>
-      <c r="K106" t="n">
-        <v>0.405653</v>
+        <v>1.319274</v>
       </c>
     </row>
     <row r="107">
@@ -4118,33 +4022,32 @@
           <t>資訊服務業右下上市</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr"/>
+      <c r="B107" t="n">
+        <v>5.549619</v>
+      </c>
       <c r="C107" t="n">
-        <v>49.539169</v>
+        <v>4.066226</v>
       </c>
       <c r="D107" t="n">
-        <v>38.143733</v>
+        <v>6.540235</v>
       </c>
       <c r="E107" t="n">
-        <v>31.30314</v>
+        <v>16.557683</v>
       </c>
       <c r="F107" t="n">
-        <v>32.514739</v>
+        <v>8.925591000000001</v>
       </c>
       <c r="G107" t="n">
-        <v>30.620833</v>
+        <v>4.865924</v>
       </c>
       <c r="H107" t="n">
-        <v>33.041287</v>
+        <v>13.219645</v>
       </c>
       <c r="I107" t="n">
-        <v>23.291445</v>
+        <v>64.06024600000001</v>
       </c>
       <c r="J107" t="n">
-        <v>26.608812</v>
-      </c>
-      <c r="K107" t="n">
-        <v>204.47693</v>
+        <v>42.807068</v>
       </c>
     </row>
     <row r="108">
@@ -4154,34 +4057,31 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0</v>
+        <v>0.16141</v>
       </c>
       <c r="C108" t="n">
-        <v>0.254495</v>
+        <v>0.112514</v>
       </c>
       <c r="D108" t="n">
-        <v>0.181211</v>
+        <v>0.06328499999999999</v>
       </c>
       <c r="E108" t="n">
-        <v>0.07320699999999999</v>
+        <v>0.0534</v>
       </c>
       <c r="F108" t="n">
-        <v>0.038081</v>
+        <v>0.09637</v>
       </c>
       <c r="G108" t="n">
-        <v>0.035812</v>
+        <v>0.060962</v>
       </c>
       <c r="H108" t="n">
-        <v>0.108406</v>
+        <v>0.066687</v>
       </c>
       <c r="I108" t="n">
-        <v>0.096425</v>
+        <v>0.221183</v>
       </c>
       <c r="J108" t="n">
-        <v>0.056801</v>
-      </c>
-      <c r="K108" t="n">
-        <v>0.102778</v>
+        <v>0.10333425</v>
       </c>
     </row>
     <row r="109">
@@ -4190,33 +4090,32 @@
           <t>資訊服務業平上市</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr"/>
+      <c r="B109" t="n">
+        <v>32.594114</v>
+      </c>
       <c r="C109" t="n">
-        <v>1541.660961</v>
+        <v>39.491765</v>
       </c>
       <c r="D109" t="n">
-        <v>279.767751</v>
+        <v>48.614308</v>
       </c>
       <c r="E109" t="n">
-        <v>143.446269</v>
+        <v>23.721963</v>
       </c>
       <c r="F109" t="n">
-        <v>210.135385</v>
+        <v>32.069459</v>
       </c>
       <c r="G109" t="n">
-        <v>117.282981</v>
+        <v>18.425521</v>
       </c>
       <c r="H109" t="n">
-        <v>97.582365</v>
+        <v>18.234497</v>
       </c>
       <c r="I109" t="n">
-        <v>73.645216</v>
+        <v>140.416684</v>
       </c>
       <c r="J109" t="n">
-        <v>96.94449</v>
-      </c>
-      <c r="K109" t="n">
-        <v>193.477013</v>
+        <v>82.37651700000001</v>
       </c>
     </row>
     <row r="110">
@@ -4225,33 +4124,32 @@
           <t>資訊服務業平上櫃</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr"/>
+      <c r="B110" t="n">
+        <v>0.077565</v>
+      </c>
       <c r="C110" t="n">
-        <v>0.698663</v>
+        <v>0.03208</v>
       </c>
       <c r="D110" t="n">
-        <v>0.173308</v>
+        <v>0.183793</v>
       </c>
       <c r="E110" t="n">
-        <v>0.177853</v>
+        <v>0.171734</v>
       </c>
       <c r="F110" t="n">
-        <v>0.496781</v>
+        <v>0.128434</v>
       </c>
       <c r="G110" t="n">
-        <v>0.302936</v>
+        <v>0.07986699999999999</v>
       </c>
       <c r="H110" t="n">
-        <v>0.231086</v>
+        <v>0.114254</v>
       </c>
       <c r="I110" t="n">
-        <v>0.130729</v>
+        <v>0.106079</v>
       </c>
       <c r="J110" t="n">
-        <v>0.194487</v>
-      </c>
-      <c r="K110" t="n">
-        <v>0.291962</v>
+        <v>0.076611</v>
       </c>
     </row>
     <row r="111">
@@ -4260,32 +4158,33 @@
           <t>農業科技業右上上櫃</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr"/>
+      <c r="B111" t="n">
+        <v>0.010882</v>
+      </c>
       <c r="C111" t="n">
-        <v>0.035455</v>
+        <v>0.003346</v>
       </c>
       <c r="D111" t="n">
-        <v>0.010882</v>
+        <v>0.00109</v>
       </c>
       <c r="E111" t="n">
-        <v>0.003346</v>
+        <v>0.000695</v>
       </c>
       <c r="F111" t="n">
-        <v>0.00109</v>
+        <v>0.000838</v>
       </c>
       <c r="G111" t="n">
-        <v>0.000695</v>
+        <v>0.00054</v>
       </c>
       <c r="H111" t="n">
-        <v>0.000838</v>
+        <v>0.00107</v>
       </c>
       <c r="I111" t="n">
-        <v>0.00054</v>
+        <v>0.00094</v>
       </c>
       <c r="J111" t="n">
-        <v>0.00107</v>
-      </c>
-      <c r="K111" t="inlineStr"/>
+        <v>0.00105</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
@@ -4293,752 +4192,746 @@
           <t>農業科技業右下上櫃</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr"/>
+      <c r="B112" t="n">
+        <v>0.00152</v>
+      </c>
       <c r="C112" t="n">
-        <v>0.001512</v>
+        <v>0.00236</v>
       </c>
       <c r="D112" t="n">
-        <v>0.00152</v>
+        <v>0.004261</v>
       </c>
       <c r="E112" t="n">
-        <v>0.00236</v>
+        <v>0.002522</v>
       </c>
       <c r="F112" t="n">
-        <v>0.004261</v>
+        <v>0.002449</v>
       </c>
       <c r="G112" t="n">
-        <v>0.002522</v>
+        <v>0.00161</v>
       </c>
       <c r="H112" t="n">
-        <v>0.002449</v>
+        <v>0.001331</v>
       </c>
       <c r="I112" t="n">
-        <v>0.00161</v>
+        <v>0.007381</v>
       </c>
       <c r="J112" t="n">
-        <v>0.001331</v>
-      </c>
-      <c r="K112" t="n">
-        <v>0.007381</v>
+        <v>0.003454</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>農業科技業平上櫃</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr"/>
-      <c r="C113" t="inlineStr"/>
-      <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr"/>
-      <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="n">
-        <v>0.00094</v>
+          <t>通信網路業右上上市</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>16622.501014</v>
+      </c>
+      <c r="C113" t="n">
+        <v>6095.028413</v>
+      </c>
+      <c r="D113" t="n">
+        <v>6082.970456</v>
+      </c>
+      <c r="E113" t="n">
+        <v>6103.551493</v>
+      </c>
+      <c r="F113" t="n">
+        <v>6732.41476</v>
+      </c>
+      <c r="G113" t="n">
+        <v>5664.386803</v>
+      </c>
+      <c r="H113" t="n">
+        <v>8245.252662000001</v>
+      </c>
+      <c r="I113" t="n">
+        <v>22743.754038</v>
+      </c>
+      <c r="J113" t="n">
+        <v>18508.769204</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>通信網路業右上上市</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr"/>
+          <t>通信網路業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>16.6943</v>
+      </c>
       <c r="C114" t="n">
-        <v>24264.042483</v>
+        <v>22.811269</v>
       </c>
       <c r="D114" t="n">
-        <v>27098.836424</v>
+        <v>13.550945</v>
       </c>
       <c r="E114" t="n">
-        <v>17046.602242</v>
+        <v>7.615602</v>
       </c>
       <c r="F114" t="n">
-        <v>12598.586921</v>
+        <v>7.114229</v>
       </c>
       <c r="G114" t="n">
-        <v>15290.862009</v>
+        <v>8.893762000000001</v>
       </c>
       <c r="H114" t="n">
-        <v>21928.342371</v>
+        <v>18.312942</v>
       </c>
       <c r="I114" t="n">
-        <v>16945.150652</v>
+        <v>30.87572</v>
       </c>
       <c r="J114" t="n">
-        <v>25518.394772</v>
-      </c>
-      <c r="K114" t="n">
-        <v>31299.192109</v>
+        <v>24.380481</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>通信網路業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr"/>
+          <t>通信網路業右下上市</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>2800.97613</v>
+      </c>
       <c r="C115" t="n">
-        <v>24.320434</v>
+        <v>3905.975775</v>
       </c>
       <c r="D115" t="n">
-        <v>22.476129</v>
+        <v>2277.09085</v>
       </c>
       <c r="E115" t="n">
-        <v>26.213372</v>
+        <v>1946.021499</v>
       </c>
       <c r="F115" t="n">
-        <v>15.436857</v>
+        <v>2780.216216</v>
       </c>
       <c r="G115" t="n">
-        <v>9.591949</v>
+        <v>2244.085252</v>
       </c>
       <c r="H115" t="n">
-        <v>9.349261</v>
+        <v>592.812061</v>
       </c>
       <c r="I115" t="n">
-        <v>11.691037</v>
+        <v>1032.313313</v>
       </c>
       <c r="J115" t="n">
-        <v>26.466939</v>
-      </c>
-      <c r="K115" t="n">
-        <v>36.447042</v>
+        <v>3136.206759</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>通信網路業右下上市</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr"/>
+          <t>通信網路業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>0.108687</v>
+      </c>
       <c r="C116" t="n">
-        <v>831.251491</v>
+        <v>0.177069</v>
       </c>
       <c r="D116" t="n">
-        <v>967.636108</v>
+        <v>0.092809</v>
       </c>
       <c r="E116" t="n">
-        <v>1572.925061</v>
+        <v>0.139641</v>
       </c>
       <c r="F116" t="n">
-        <v>834.745993</v>
+        <v>0.121491</v>
       </c>
       <c r="G116" t="n">
-        <v>496.605319</v>
+        <v>0.078808</v>
       </c>
       <c r="H116" t="n">
-        <v>627.669129</v>
+        <v>0.084409</v>
       </c>
       <c r="I116" t="n">
-        <v>511.843469</v>
+        <v>0.171764</v>
       </c>
       <c r="J116" t="n">
-        <v>427.332467</v>
-      </c>
-      <c r="K116" t="n">
-        <v>823.802486</v>
+        <v>0.188484</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>通信網路業右下上櫃</t>
+          <t>通信網路業平上市</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0</v>
+        <v>8748.802201</v>
       </c>
       <c r="C117" t="n">
-        <v>0.112218</v>
+        <v>8856.093255</v>
       </c>
       <c r="D117" t="n">
-        <v>0.112675</v>
+        <v>5162.65965</v>
       </c>
       <c r="E117" t="n">
-        <v>0.177407</v>
+        <v>8297.360316</v>
       </c>
       <c r="F117" t="n">
-        <v>0.095875</v>
+        <v>13988.662308</v>
       </c>
       <c r="G117" t="n">
-        <v>0.14341</v>
+        <v>12339.661725</v>
       </c>
       <c r="H117" t="n">
-        <v>0.116765</v>
+        <v>17667.338244</v>
       </c>
       <c r="I117" t="n">
-        <v>0.109925</v>
+        <v>8652.535905000001</v>
       </c>
       <c r="J117" t="n">
-        <v>0.117526</v>
-      </c>
-      <c r="K117" t="n">
-        <v>0.131012</v>
+        <v>10680.328469</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>通信網路業平上市</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr"/>
+          <t>通信網路業平上櫃</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>6.538407</v>
+      </c>
       <c r="C118" t="n">
-        <v>135.391345</v>
+        <v>3.420577</v>
       </c>
       <c r="D118" t="n">
-        <v>105.806813</v>
+        <v>2.262053</v>
       </c>
       <c r="E118" t="n">
-        <v>237.57014</v>
+        <v>2.291996</v>
       </c>
       <c r="F118" t="n">
-        <v>89.388042</v>
+        <v>2.261277</v>
       </c>
       <c r="G118" t="n">
-        <v>559.4659799999999</v>
+        <v>3.489899</v>
       </c>
       <c r="H118" t="n">
-        <v>945.281784</v>
+        <v>8.566473999999999</v>
       </c>
       <c r="I118" t="n">
-        <v>2791.139659</v>
+        <v>6.319699</v>
       </c>
       <c r="J118" t="n">
-        <v>559.675728</v>
-      </c>
-      <c r="K118" t="n">
-        <v>305.608661</v>
+        <v>5.424032</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>通信網路業平上櫃</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr"/>
+          <t>造紙工業右上上市</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>64.522261</v>
+      </c>
       <c r="C119" t="n">
-        <v>0.8952059999999999</v>
+        <v>41.474092</v>
       </c>
       <c r="D119" t="n">
-        <v>0.751752</v>
+        <v>57.019267</v>
       </c>
       <c r="E119" t="n">
-        <v>0.017126</v>
+        <v>95.750647</v>
       </c>
       <c r="F119" t="n">
-        <v>0.372699</v>
+        <v>70.719487</v>
       </c>
       <c r="G119" t="n">
-        <v>0.310555</v>
+        <v>92.464285</v>
       </c>
       <c r="H119" t="n">
-        <v>0.029576</v>
+        <v>63.28767</v>
       </c>
       <c r="I119" t="n">
-        <v>0.660886</v>
+        <v>58.167627</v>
       </c>
       <c r="J119" t="n">
-        <v>0.378057</v>
-      </c>
-      <c r="K119" t="n">
-        <v>0.788558</v>
+        <v>54.269276</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>造紙工業右上上市</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr"/>
+          <t>造紙工業右下上市</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>8.746762</v>
+      </c>
       <c r="C120" t="n">
-        <v>51.079864</v>
+        <v>8.611516999999999</v>
       </c>
       <c r="D120" t="n">
-        <v>77.23409100000001</v>
+        <v>4.116534</v>
       </c>
       <c r="E120" t="n">
-        <v>55.228139</v>
+        <v>8.170572</v>
       </c>
       <c r="F120" t="n">
-        <v>67.6173</v>
+        <v>6.624743</v>
       </c>
       <c r="G120" t="n">
-        <v>95.750647</v>
+        <v>6.312246</v>
       </c>
       <c r="H120" t="n">
-        <v>70.719487</v>
+        <v>7.259808</v>
       </c>
       <c r="I120" t="n">
-        <v>92.464285</v>
+        <v>13.316509</v>
       </c>
       <c r="J120" t="n">
-        <v>79.71619</v>
-      </c>
-      <c r="K120" t="n">
-        <v>58.167627</v>
+        <v>6.283155</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>造紙工業右下上市</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr"/>
+          <t>造紙工業平上市</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>39.868425</v>
+      </c>
       <c r="C121" t="n">
-        <v>5.766187</v>
+        <v>31.600935</v>
       </c>
       <c r="D121" t="n">
-        <v>8.746762</v>
+        <v>23.263533</v>
       </c>
       <c r="E121" t="n">
-        <v>8.611516999999999</v>
+        <v>54.222929</v>
       </c>
       <c r="F121" t="n">
-        <v>4.116534</v>
+        <v>27.470921</v>
       </c>
       <c r="G121" t="n">
-        <v>8.170572</v>
+        <v>54.140034</v>
       </c>
       <c r="H121" t="n">
-        <v>6.624743</v>
+        <v>31.758988</v>
       </c>
       <c r="I121" t="n">
-        <v>6.312246</v>
+        <v>46.895959</v>
       </c>
       <c r="J121" t="n">
-        <v>7.259808</v>
-      </c>
-      <c r="K121" t="n">
-        <v>13.316509</v>
+        <v>43.005756</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>造紙工業平上市</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr"/>
+          <t>運動休閒右上上市</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>161.276417</v>
+      </c>
       <c r="C122" t="n">
-        <v>14.430171</v>
+        <v>156.233187</v>
       </c>
       <c r="D122" t="n">
-        <v>27.156595</v>
+        <v>127.930135</v>
       </c>
       <c r="E122" t="n">
-        <v>17.846888</v>
+        <v>222.315562</v>
       </c>
       <c r="F122" t="n">
-        <v>12.6655</v>
+        <v>159.66203</v>
       </c>
       <c r="G122" t="n">
-        <v>54.222929</v>
+        <v>173.07071</v>
       </c>
       <c r="H122" t="n">
-        <v>27.470921</v>
+        <v>149.450741</v>
       </c>
       <c r="I122" t="n">
-        <v>54.140034</v>
+        <v>133.981208</v>
       </c>
       <c r="J122" t="n">
-        <v>15.330468</v>
-      </c>
-      <c r="K122" t="n">
-        <v>46.895959</v>
+        <v>117.484132</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右上上市</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr"/>
+          <t>運動休閒右上上櫃</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>0.008544</v>
+      </c>
       <c r="C123" t="n">
-        <v>3.173968</v>
+        <v>0.007512</v>
       </c>
       <c r="D123" t="n">
-        <v>6.829026</v>
+        <v>0.008066</v>
       </c>
       <c r="E123" t="n">
-        <v>14.189534</v>
+        <v>0.00397</v>
       </c>
       <c r="F123" t="n">
-        <v>8.780303999999999</v>
+        <v>0.003778</v>
       </c>
       <c r="G123" t="n">
-        <v>8.784293999999999</v>
+        <v>0.006495</v>
       </c>
       <c r="H123" t="n">
-        <v>4.563235</v>
+        <v>0.002192</v>
       </c>
       <c r="I123" t="n">
-        <v>19.402717</v>
+        <v>0.001731</v>
       </c>
       <c r="J123" t="n">
-        <v>10.267939</v>
-      </c>
-      <c r="K123" t="n">
-        <v>4.269063</v>
+        <v>0.001133</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右上上櫃</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr"/>
+          <t>運動休閒右下上市</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>431.198429</v>
+      </c>
       <c r="C124" t="n">
-        <v>0.003218</v>
+        <v>574.917972</v>
       </c>
       <c r="D124" t="n">
-        <v>0.007213</v>
+        <v>437.072996</v>
       </c>
       <c r="E124" t="n">
-        <v>0.006858</v>
+        <v>441.590088</v>
       </c>
       <c r="F124" t="n">
-        <v>0.008021</v>
+        <v>449.552373</v>
       </c>
       <c r="G124" t="n">
-        <v>0.003447</v>
+        <v>413.635324</v>
       </c>
       <c r="H124" t="n">
-        <v>0.003155</v>
+        <v>473.00502</v>
       </c>
       <c r="I124" t="n">
-        <v>0.006757</v>
+        <v>809.13311</v>
       </c>
       <c r="J124" t="n">
-        <v>0.002266</v>
-      </c>
-      <c r="K124" t="n">
-        <v>0.000998</v>
+        <v>424.018495</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右下上市</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr"/>
+          <t>運動休閒右下上櫃</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>0.012284</v>
+      </c>
       <c r="C125" t="n">
-        <v>534.171991</v>
+        <v>0.005907</v>
       </c>
       <c r="D125" t="n">
-        <v>465.256605</v>
+        <v>0.005639</v>
       </c>
       <c r="E125" t="n">
-        <v>612.98116</v>
+        <v>0.004976</v>
       </c>
       <c r="F125" t="n">
-        <v>505.281862</v>
+        <v>0.003873</v>
       </c>
       <c r="G125" t="n">
-        <v>528.3968640000001</v>
+        <v>0.00535</v>
       </c>
       <c r="H125" t="n">
-        <v>526.544919</v>
+        <v>0.005399</v>
       </c>
       <c r="I125" t="n">
-        <v>466.358989</v>
+        <v>0.010485</v>
       </c>
       <c r="J125" t="n">
-        <v>513.529666</v>
-      </c>
-      <c r="K125" t="n">
-        <v>849.426072</v>
+        <v>0.005742</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右下上櫃</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr"/>
+          <t>運動休閒平上市</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>11.696813</v>
+      </c>
       <c r="C126" t="n">
-        <v>0.008888</v>
+        <v>8.888235</v>
       </c>
       <c r="D126" t="n">
-        <v>0.012488</v>
+        <v>47.479196</v>
       </c>
       <c r="E126" t="n">
-        <v>0.00653</v>
+        <v>88.51274100000001</v>
       </c>
       <c r="F126" t="n">
-        <v>0.005962</v>
+        <v>83.666366</v>
       </c>
       <c r="G126" t="n">
-        <v>0.005354</v>
+        <v>59.722284</v>
       </c>
       <c r="H126" t="n">
-        <v>0.004094</v>
+        <v>42.191244</v>
       </c>
       <c r="I126" t="n">
-        <v>0.005517</v>
+        <v>71.724283</v>
       </c>
       <c r="J126" t="n">
-        <v>0.005495</v>
-      </c>
-      <c r="K126" t="n">
-        <v>0.011286</v>
+        <v>80.792382</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>運動休閒平上市</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr"/>
+          <t>運動休閒平上櫃</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>0.000204</v>
+      </c>
       <c r="C127" t="n">
-        <v>109.737681</v>
+        <v>0.000623</v>
       </c>
       <c r="D127" t="n">
-        <v>132.086028</v>
+        <v>0.001134</v>
       </c>
       <c r="E127" t="n">
-        <v>112.8687</v>
+        <v>0.000725</v>
       </c>
       <c r="F127" t="n">
-        <v>98.42016099999999</v>
+        <v>0.000571</v>
       </c>
       <c r="G127" t="n">
-        <v>215.237233</v>
+        <v>0.00091</v>
       </c>
       <c r="H127" t="n">
-        <v>161.772615</v>
+        <v>0.000621</v>
       </c>
       <c r="I127" t="n">
-        <v>160.666612</v>
+        <v>0.000918</v>
       </c>
       <c r="J127" t="n">
-        <v>140.8494</v>
-      </c>
-      <c r="K127" t="n">
-        <v>161.143466</v>
+        <v>0.000413</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>運動休閒平上櫃</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr"/>
+          <t>金融保險右上上市</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>16987.289529</v>
+      </c>
       <c r="C128" t="n">
-        <v>0.001208</v>
+        <v>17478.522511</v>
       </c>
       <c r="D128" t="n">
-        <v>0.001331</v>
+        <v>10882.35721</v>
       </c>
       <c r="E128" t="n">
-        <v>0.000654</v>
+        <v>19643.829874</v>
       </c>
       <c r="F128" t="n">
-        <v>0.000856</v>
+        <v>17163.268297</v>
       </c>
       <c r="G128" t="n">
-        <v>0.00087</v>
+        <v>24618.524731</v>
       </c>
       <c r="H128" t="n">
-        <v>0.000973</v>
+        <v>16298.205375</v>
       </c>
       <c r="I128" t="n">
-        <v>0.000481</v>
+        <v>13807.946575</v>
       </c>
       <c r="J128" t="n">
-        <v>0.000451</v>
-      </c>
-      <c r="K128" t="n">
-        <v>0.00085</v>
+        <v>14981.031046</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>金融保險右上上市</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr"/>
+          <t>金融保險右下上市</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>189.086642</v>
+      </c>
       <c r="C129" t="n">
-        <v>17943.773972</v>
+        <v>205.909852</v>
       </c>
       <c r="D129" t="n">
-        <v>17340.268633</v>
+        <v>244.900842</v>
       </c>
       <c r="E129" t="n">
-        <v>17688.882236</v>
+        <v>387.63469</v>
       </c>
       <c r="F129" t="n">
-        <v>11082.751805</v>
+        <v>265.348802</v>
       </c>
       <c r="G129" t="n">
-        <v>19921.687985</v>
+        <v>233.42015</v>
       </c>
       <c r="H129" t="n">
-        <v>17409.609172</v>
+        <v>116.899227</v>
       </c>
       <c r="I129" t="n">
-        <v>24968.988046</v>
+        <v>626.85414</v>
       </c>
       <c r="J129" t="n">
-        <v>16528.964768</v>
-      </c>
-      <c r="K129" t="n">
-        <v>14024.486224</v>
+        <v>181.039781</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>金融保險右下上市</t>
+          <t>金融保險平上市</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0</v>
+        <v>354.572106</v>
       </c>
       <c r="C130" t="n">
-        <v>274.286538</v>
+        <v>228.885439</v>
       </c>
       <c r="D130" t="n">
-        <v>189.086642</v>
+        <v>209.691372</v>
       </c>
       <c r="E130" t="n">
-        <v>205.909852</v>
+        <v>280.204653</v>
       </c>
       <c r="F130" t="n">
-        <v>244.900842</v>
+        <v>256.305102</v>
       </c>
       <c r="G130" t="n">
-        <v>365.107306</v>
+        <v>351.325567</v>
       </c>
       <c r="H130" t="n">
-        <v>265.348802</v>
+        <v>464.231308</v>
       </c>
       <c r="I130" t="n">
-        <v>210.851143</v>
+        <v>366.678001</v>
       </c>
       <c r="J130" t="n">
-        <v>100.665858</v>
-      </c>
-      <c r="K130" t="n">
-        <v>581.610311</v>
+        <v>91.760988</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>金融保險平上市</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr"/>
-      <c r="C131" t="inlineStr"/>
-      <c r="D131" t="inlineStr"/>
+          <t>金融業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>0.511979</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.300829</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.200969</v>
+      </c>
       <c r="E131" t="n">
-        <v>16.324356</v>
+        <v>0.161656</v>
       </c>
       <c r="F131" t="n">
-        <v>6.437949</v>
+        <v>0.400318</v>
       </c>
       <c r="G131" t="n">
-        <v>22.527384</v>
+        <v>0.34688</v>
       </c>
       <c r="H131" t="n">
-        <v>7.187692</v>
+        <v>0.207437</v>
       </c>
       <c r="I131" t="n">
-        <v>22.569007</v>
+        <v>0.32817</v>
       </c>
       <c r="J131" t="n">
-        <v>245.982012</v>
-      </c>
-      <c r="K131" t="n">
-        <v>192.893999</v>
+        <v>0.370971</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>金融業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr"/>
+          <t>金融業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>0.02408566666666667</v>
+      </c>
       <c r="C132" t="n">
-        <v>0.503962</v>
+        <v>0.043228</v>
       </c>
       <c r="D132" t="n">
-        <v>0.512541</v>
+        <v>0.102314</v>
       </c>
       <c r="E132" t="n">
-        <v>0.301573</v>
+        <v>0.038874</v>
       </c>
       <c r="F132" t="n">
-        <v>0.201194</v>
+        <v>0.064808</v>
       </c>
       <c r="G132" t="n">
-        <v>0.161718</v>
+        <v>0.08569</v>
       </c>
       <c r="H132" t="n">
-        <v>0.400568</v>
+        <v>0.030934</v>
       </c>
       <c r="I132" t="n">
-        <v>0.347004</v>
+        <v>0.062779</v>
       </c>
       <c r="J132" t="n">
-        <v>0.207685</v>
-      </c>
-      <c r="K132" t="n">
-        <v>0.328599</v>
+        <v>0.015258</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>金融業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr"/>
+          <t>金融業平上櫃</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>0.000562</v>
+      </c>
       <c r="C133" t="n">
-        <v>0.053885</v>
+        <v>0.000744</v>
       </c>
       <c r="D133" t="n">
-        <v>0.02408566666666667</v>
+        <v>0.000225</v>
       </c>
       <c r="E133" t="n">
-        <v>0.043228</v>
+        <v>6.2e-05</v>
       </c>
       <c r="F133" t="n">
-        <v>0.102314</v>
+        <v>0.00025</v>
       </c>
       <c r="G133" t="n">
-        <v>0.038874</v>
+        <v>0.000124</v>
       </c>
       <c r="H133" t="n">
-        <v>0.064808</v>
+        <v>0.000248</v>
       </c>
       <c r="I133" t="n">
-        <v>0.08569</v>
+        <v>0.000429</v>
       </c>
       <c r="J133" t="n">
-        <v>0.030934</v>
-      </c>
-      <c r="K133" t="n">
-        <v>0.062779</v>
+        <v>0.000127</v>
       </c>
     </row>
     <row r="134">
@@ -5047,33 +4940,32 @@
           <t>鋼鐵工業右上上市</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr"/>
+      <c r="B134" t="n">
+        <v>1244.936603</v>
+      </c>
       <c r="C134" t="n">
-        <v>539.900084</v>
+        <v>1702.258596</v>
       </c>
       <c r="D134" t="n">
-        <v>1123.675553</v>
+        <v>1668.035173</v>
       </c>
       <c r="E134" t="n">
-        <v>1454.599133</v>
+        <v>2123.299819</v>
       </c>
       <c r="F134" t="n">
-        <v>1512.060135</v>
+        <v>2472.356878</v>
       </c>
       <c r="G134" t="n">
-        <v>1695.675298</v>
+        <v>4794.875688</v>
       </c>
       <c r="H134" t="n">
-        <v>2390.322117</v>
+        <v>1359.890176</v>
       </c>
       <c r="I134" t="n">
-        <v>4730.164716</v>
+        <v>1769.709532</v>
       </c>
       <c r="J134" t="n">
-        <v>1295.19524</v>
-      </c>
-      <c r="K134" t="n">
-        <v>1318.849101</v>
+        <v>836.966153</v>
       </c>
     </row>
     <row r="135">
@@ -5082,33 +4974,32 @@
           <t>鋼鐵工業右上上櫃</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr"/>
+      <c r="B135" t="n">
+        <v>0.017194</v>
+      </c>
       <c r="C135" t="n">
-        <v>0.009807</v>
+        <v>0.012871</v>
       </c>
       <c r="D135" t="n">
-        <v>0.017194</v>
+        <v>0.006391</v>
       </c>
       <c r="E135" t="n">
-        <v>0.016825</v>
+        <v>0.044205</v>
       </c>
       <c r="F135" t="n">
-        <v>0.013359</v>
+        <v>0.05524</v>
       </c>
       <c r="G135" t="n">
-        <v>0.06475</v>
+        <v>0.032969</v>
       </c>
       <c r="H135" t="n">
-        <v>0.072867</v>
+        <v>0.090244</v>
       </c>
       <c r="I135" t="n">
-        <v>0.049926</v>
+        <v>0.047232</v>
       </c>
       <c r="J135" t="n">
-        <v>0.097998</v>
-      </c>
-      <c r="K135" t="n">
-        <v>0.06363175</v>
+        <v>0.263393</v>
       </c>
     </row>
     <row r="136">
@@ -5118,34 +5009,31 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0</v>
+        <v>845.004486</v>
       </c>
       <c r="C136" t="n">
-        <v>693.307398</v>
+        <v>788.213784</v>
       </c>
       <c r="D136" t="n">
-        <v>730.516352</v>
+        <v>690.654503</v>
       </c>
       <c r="E136" t="n">
-        <v>628.6383509999999</v>
+        <v>1034.546462</v>
       </c>
       <c r="F136" t="n">
-        <v>580.553522</v>
+        <v>233.418087</v>
       </c>
       <c r="G136" t="n">
-        <v>893.3883949999999</v>
+        <v>217.573193</v>
       </c>
       <c r="H136" t="n">
-        <v>130.607766</v>
+        <v>147.093842</v>
       </c>
       <c r="I136" t="n">
-        <v>871.420516</v>
+        <v>766.217797</v>
       </c>
       <c r="J136" t="n">
-        <v>96.25299099999999</v>
-      </c>
-      <c r="K136" t="n">
-        <v>672.790444</v>
+        <v>141.456491</v>
       </c>
     </row>
     <row r="137">
@@ -5155,34 +5043,31 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0</v>
+        <v>0.043378</v>
       </c>
       <c r="C137" t="n">
-        <v>0.034314</v>
+        <v>0.02903</v>
       </c>
       <c r="D137" t="n">
-        <v>0.035174</v>
+        <v>0.0357425</v>
       </c>
       <c r="E137" t="n">
-        <v>0.024203</v>
+        <v>0.066598</v>
       </c>
       <c r="F137" t="n">
-        <v>0.0274235</v>
+        <v>0.01580233333333333</v>
       </c>
       <c r="G137" t="n">
-        <v>0.062666</v>
+        <v>0.07816099999999999</v>
       </c>
       <c r="H137" t="n">
-        <v>0.2150343333333334</v>
+        <v>0.008527</v>
       </c>
       <c r="I137" t="n">
-        <v>0.071273</v>
+        <v>0.08859475</v>
       </c>
       <c r="J137" t="n">
-        <v>0.048009</v>
-      </c>
-      <c r="K137" t="n">
-        <v>0.085073</v>
+        <v>0.04056825</v>
       </c>
     </row>
     <row r="138">
@@ -5191,33 +5076,32 @@
           <t>鋼鐵工業平上市</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr"/>
+      <c r="B138" t="n">
+        <v>35.389744</v>
+      </c>
       <c r="C138" t="n">
-        <v>90.580046</v>
+        <v>25.446863</v>
       </c>
       <c r="D138" t="n">
-        <v>124.504458</v>
+        <v>51.27883</v>
       </c>
       <c r="E138" t="n">
-        <v>175.143425</v>
+        <v>69.504525</v>
       </c>
       <c r="F138" t="n">
-        <v>124.788869</v>
+        <v>1959.791285</v>
       </c>
       <c r="G138" t="n">
-        <v>310.398103</v>
+        <v>880.248299</v>
       </c>
       <c r="H138" t="n">
-        <v>1871.130716</v>
+        <v>474.633615</v>
       </c>
       <c r="I138" t="n">
-        <v>126.17484</v>
+        <v>120.192436</v>
       </c>
       <c r="J138" t="n">
-        <v>464.115664</v>
-      </c>
-      <c r="K138" t="n">
-        <v>191.129801</v>
+        <v>416.713208</v>
       </c>
     </row>
     <row r="139">
@@ -5226,28 +5110,33 @@
           <t>鋼鐵工業平上櫃</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr"/>
+      <c r="B139" t="n">
+        <v>0.009734</v>
+      </c>
       <c r="C139" t="n">
-        <v>0.024233</v>
+        <v>0.003954</v>
       </c>
       <c r="D139" t="n">
-        <v>0.009988</v>
+        <v>0.007728</v>
       </c>
       <c r="E139" t="n">
-        <v>0.000393</v>
+        <v>0.022195</v>
       </c>
       <c r="F139" t="n">
-        <v>1.7e-05</v>
+        <v>0.22675</v>
       </c>
       <c r="G139" t="n">
-        <v>7.499999999999999e-05</v>
+        <v>0.017764</v>
       </c>
       <c r="H139" t="n">
-        <v>0.003635</v>
-      </c>
-      <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
+        <v>0.049575</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.016499</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.01842</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
@@ -5255,33 +5144,32 @@
           <t>電器電纜右上上市</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr"/>
+      <c r="B140" t="n">
+        <v>783.843303</v>
+      </c>
       <c r="C140" t="n">
-        <v>548.098926</v>
+        <v>459.979709</v>
       </c>
       <c r="D140" t="n">
-        <v>824.3166649999999</v>
+        <v>243.385274</v>
       </c>
       <c r="E140" t="n">
-        <v>527.970243</v>
+        <v>221.164725</v>
       </c>
       <c r="F140" t="n">
-        <v>281.900372</v>
+        <v>2022.93564</v>
       </c>
       <c r="G140" t="n">
-        <v>431.899672</v>
+        <v>1815.128022</v>
       </c>
       <c r="H140" t="n">
-        <v>1832.071461</v>
+        <v>1400.305424</v>
       </c>
       <c r="I140" t="n">
-        <v>1627.572588</v>
+        <v>1121.620276</v>
       </c>
       <c r="J140" t="n">
-        <v>1287.999043</v>
-      </c>
-      <c r="K140" t="n">
-        <v>1121.620276</v>
+        <v>771.32349</v>
       </c>
     </row>
     <row r="141">
@@ -5290,33 +5178,32 @@
           <t>電器電纜右上上櫃</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr"/>
+      <c r="B141" t="n">
+        <v>0.111628</v>
+      </c>
       <c r="C141" t="n">
-        <v>0.108179</v>
+        <v>0.09124</v>
       </c>
       <c r="D141" t="n">
-        <v>0.111628</v>
+        <v>0.091242</v>
       </c>
       <c r="E141" t="n">
-        <v>0.09124</v>
+        <v>0.112558</v>
       </c>
       <c r="F141" t="n">
-        <v>0.091242</v>
+        <v>0.294298</v>
       </c>
       <c r="G141" t="n">
-        <v>0.112558</v>
+        <v>0.204111</v>
       </c>
       <c r="H141" t="n">
-        <v>0.294298</v>
+        <v>0.346172</v>
       </c>
       <c r="I141" t="n">
-        <v>0.204111</v>
+        <v>0.360224</v>
       </c>
       <c r="J141" t="n">
-        <v>0.346172</v>
-      </c>
-      <c r="K141" t="n">
-        <v>0.360224</v>
+        <v>0.179417</v>
       </c>
     </row>
     <row r="142">
@@ -5326,34 +5213,31 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0</v>
+        <v>65.49185300000001</v>
       </c>
       <c r="C142" t="n">
-        <v>91.36336300000001</v>
+        <v>41.538122</v>
       </c>
       <c r="D142" t="n">
-        <v>68.343518</v>
+        <v>39.275066</v>
       </c>
       <c r="E142" t="n">
-        <v>43.787224</v>
+        <v>40.346396</v>
       </c>
       <c r="F142" t="n">
-        <v>39.275066</v>
+        <v>55.382448</v>
       </c>
       <c r="G142" t="n">
-        <v>40.346396</v>
+        <v>41.834918</v>
       </c>
       <c r="H142" t="n">
-        <v>55.382448</v>
+        <v>50.073944</v>
       </c>
       <c r="I142" t="n">
-        <v>41.834918</v>
+        <v>62.3224</v>
       </c>
       <c r="J142" t="n">
-        <v>50.073944</v>
-      </c>
-      <c r="K142" t="n">
-        <v>62.3224</v>
+        <v>50.570646</v>
       </c>
     </row>
     <row r="143">
@@ -5362,33 +5246,32 @@
           <t>電器電纜平上市</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr"/>
+      <c r="B143" t="n">
+        <v>197.780769</v>
+      </c>
       <c r="C143" t="n">
-        <v>102.379057</v>
+        <v>170.127462</v>
       </c>
       <c r="D143" t="n">
-        <v>144.381005</v>
+        <v>116.254235</v>
       </c>
       <c r="E143" t="n">
-        <v>90.858828</v>
+        <v>420.560636</v>
       </c>
       <c r="F143" t="n">
-        <v>65.189415</v>
+        <v>44.797637</v>
       </c>
       <c r="G143" t="n">
-        <v>190.952255</v>
+        <v>21.090587</v>
       </c>
       <c r="H143" t="n">
-        <v>190.864179</v>
+        <v>11.466549</v>
       </c>
       <c r="I143" t="n">
-        <v>187.555434</v>
+        <v>148.512708</v>
       </c>
       <c r="J143" t="n">
-        <v>112.306381</v>
-      </c>
-      <c r="K143" t="n">
-        <v>134.839047</v>
+        <v>17.022326</v>
       </c>
     </row>
     <row r="144">
@@ -5397,33 +5280,32 @@
           <t>電子通路業右上上市</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr"/>
+      <c r="B144" t="n">
+        <v>3533.092438</v>
+      </c>
       <c r="C144" t="n">
-        <v>4267.165228</v>
+        <v>7357.524566</v>
       </c>
       <c r="D144" t="n">
-        <v>5878.449564</v>
+        <v>3162.15291</v>
       </c>
       <c r="E144" t="n">
-        <v>8812.877887000001</v>
+        <v>3504.588651</v>
       </c>
       <c r="F144" t="n">
-        <v>5102.029062</v>
+        <v>4790.204438</v>
       </c>
       <c r="G144" t="n">
-        <v>4956.241487</v>
+        <v>2482.396615</v>
       </c>
       <c r="H144" t="n">
-        <v>6977.782428</v>
+        <v>2318.877637</v>
       </c>
       <c r="I144" t="n">
-        <v>5324.52747</v>
+        <v>2511.741979</v>
       </c>
       <c r="J144" t="n">
-        <v>4295.648634</v>
-      </c>
-      <c r="K144" t="n">
-        <v>4441.152525</v>
+        <v>1612.453768</v>
       </c>
     </row>
     <row r="145">
@@ -5432,33 +5314,32 @@
           <t>電子通路業右上上櫃</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr"/>
+      <c r="B145" t="n">
+        <v>0.291336</v>
+      </c>
       <c r="C145" t="n">
-        <v>0.20052</v>
+        <v>0.107882</v>
       </c>
       <c r="D145" t="n">
-        <v>0.372864</v>
+        <v>0.127115</v>
       </c>
       <c r="E145" t="n">
-        <v>0.16613</v>
+        <v>0.114703</v>
       </c>
       <c r="F145" t="n">
-        <v>0.175534</v>
+        <v>0.131196</v>
       </c>
       <c r="G145" t="n">
-        <v>0.5631930000000001</v>
+        <v>0.332757</v>
       </c>
       <c r="H145" t="n">
-        <v>0.470245</v>
+        <v>0.374888</v>
       </c>
       <c r="I145" t="n">
-        <v>0.335974</v>
+        <v>0.545445</v>
       </c>
       <c r="J145" t="n">
-        <v>0.56393</v>
-      </c>
-      <c r="K145" t="n">
-        <v>0.809244</v>
+        <v>0.119233</v>
       </c>
     </row>
     <row r="146">
@@ -5467,33 +5348,32 @@
           <t>電子通路業右下上市</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr"/>
+      <c r="B146" t="n">
+        <v>10.344134</v>
+      </c>
       <c r="C146" t="n">
-        <v>28.032008</v>
+        <v>5.689849</v>
       </c>
       <c r="D146" t="n">
-        <v>25.137513</v>
+        <v>6.727905</v>
       </c>
       <c r="E146" t="n">
-        <v>5.689849</v>
+        <v>18.247482</v>
       </c>
       <c r="F146" t="n">
-        <v>27.712111</v>
+        <v>12.283079</v>
       </c>
       <c r="G146" t="n">
-        <v>18.247482</v>
+        <v>13.321644</v>
       </c>
       <c r="H146" t="n">
-        <v>12.283079</v>
+        <v>11.089148</v>
       </c>
       <c r="I146" t="n">
-        <v>13.321644</v>
+        <v>13.469439</v>
       </c>
       <c r="J146" t="n">
-        <v>11.089148</v>
-      </c>
-      <c r="K146" t="n">
-        <v>13.469439</v>
+        <v>11.420697</v>
       </c>
     </row>
     <row r="147">
@@ -5503,34 +5383,31 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0</v>
+        <v>0.033982</v>
       </c>
       <c r="C147" t="n">
-        <v>0.032335</v>
+        <v>0.173565</v>
       </c>
       <c r="D147" t="n">
-        <v>0.033982</v>
+        <v>0.06376800000000001</v>
       </c>
       <c r="E147" t="n">
-        <v>0.173565</v>
+        <v>0.0418</v>
       </c>
       <c r="F147" t="n">
-        <v>0.06376800000000001</v>
+        <v>0.04535</v>
       </c>
       <c r="G147" t="n">
-        <v>0.0418</v>
+        <v>0.081911</v>
       </c>
       <c r="H147" t="n">
-        <v>0.04535</v>
+        <v>0.022376</v>
       </c>
       <c r="I147" t="n">
-        <v>0.081911</v>
+        <v>0.01177</v>
       </c>
       <c r="J147" t="n">
-        <v>0.022376</v>
-      </c>
-      <c r="K147" t="n">
-        <v>0.01177</v>
+        <v>0.012023</v>
       </c>
     </row>
     <row r="148">
@@ -5539,33 +5416,32 @@
           <t>電子通路業平上市</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr"/>
+      <c r="B148" t="n">
+        <v>2400.502435</v>
+      </c>
       <c r="C148" t="n">
-        <v>46.300898</v>
+        <v>1537.856671</v>
       </c>
       <c r="D148" t="n">
-        <v>40.35193</v>
+        <v>2036.568067</v>
       </c>
       <c r="E148" t="n">
-        <v>82.50335</v>
+        <v>1544.029191</v>
       </c>
       <c r="F148" t="n">
-        <v>75.70770899999999</v>
+        <v>2244.493983</v>
       </c>
       <c r="G148" t="n">
-        <v>92.376355</v>
+        <v>2879.512206</v>
       </c>
       <c r="H148" t="n">
-        <v>56.915993</v>
+        <v>2031.06244</v>
       </c>
       <c r="I148" t="n">
-        <v>37.381351</v>
+        <v>1994.714516</v>
       </c>
       <c r="J148" t="n">
-        <v>54.291443</v>
-      </c>
-      <c r="K148" t="n">
-        <v>65.30397000000001</v>
+        <v>1739.529586</v>
       </c>
     </row>
     <row r="149">
@@ -5574,30 +5450,33 @@
           <t>電子通路業平上櫃</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr"/>
+      <c r="B149" t="n">
+        <v>0.481713</v>
+      </c>
       <c r="C149" t="n">
-        <v>0.226128</v>
+        <v>0.334162</v>
       </c>
       <c r="D149" t="n">
-        <v>0.372122</v>
+        <v>0.277588</v>
       </c>
       <c r="E149" t="n">
-        <v>0.266881</v>
+        <v>0.466732</v>
       </c>
       <c r="F149" t="n">
-        <v>0.223138</v>
+        <v>0.359879</v>
       </c>
       <c r="G149" t="n">
-        <v>0.000586</v>
+        <v>0.272872</v>
       </c>
       <c r="H149" t="n">
-        <v>0.001673</v>
+        <v>0.205556</v>
       </c>
       <c r="I149" t="n">
-        <v>0.263543</v>
-      </c>
-      <c r="J149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
+        <v>0.297367</v>
+      </c>
+      <c r="J149" t="n">
+        <v>0.258832</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
@@ -5605,33 +5484,32 @@
           <t>電子零組件業右上上市</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr"/>
+      <c r="B150" t="n">
+        <v>165334.465168</v>
+      </c>
       <c r="C150" t="n">
-        <v>189211.270418</v>
+        <v>202291.836966</v>
       </c>
       <c r="D150" t="n">
-        <v>204156.092618</v>
+        <v>189680.575138</v>
       </c>
       <c r="E150" t="n">
-        <v>203798.645385</v>
+        <v>168759.788961</v>
       </c>
       <c r="F150" t="n">
-        <v>192674.347327</v>
+        <v>175055.014039</v>
       </c>
       <c r="G150" t="n">
-        <v>192587.977924</v>
+        <v>219810.875587</v>
       </c>
       <c r="H150" t="n">
-        <v>189802.722785</v>
+        <v>295285.351175</v>
       </c>
       <c r="I150" t="n">
-        <v>238921.442908</v>
+        <v>328265.311909</v>
       </c>
       <c r="J150" t="n">
-        <v>303665.836696</v>
-      </c>
-      <c r="K150" t="n">
-        <v>337220.178575</v>
+        <v>288190.134832</v>
       </c>
     </row>
     <row r="151">
@@ -5640,33 +5518,32 @@
           <t>電子零組件業右上上櫃</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr"/>
+      <c r="B151" t="n">
+        <v>41.06388</v>
+      </c>
       <c r="C151" t="n">
-        <v>40.781232</v>
+        <v>25.823852</v>
       </c>
       <c r="D151" t="n">
-        <v>44.057549</v>
+        <v>37.603645</v>
       </c>
       <c r="E151" t="n">
-        <v>26.401065</v>
+        <v>29.674985</v>
       </c>
       <c r="F151" t="n">
-        <v>37.422991</v>
+        <v>28.779912</v>
       </c>
       <c r="G151" t="n">
-        <v>25.173246</v>
+        <v>49.045555</v>
       </c>
       <c r="H151" t="n">
-        <v>28.553205</v>
+        <v>64.95413499999999</v>
       </c>
       <c r="I151" t="n">
-        <v>43.43267</v>
+        <v>73.40257800000001</v>
       </c>
       <c r="J151" t="n">
-        <v>57.674496</v>
-      </c>
-      <c r="K151" t="n">
-        <v>54.274901</v>
+        <v>67.14289100000001</v>
       </c>
     </row>
     <row r="152">
@@ -5676,34 +5553,31 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0</v>
+        <v>4168.602855</v>
       </c>
       <c r="C152" t="n">
-        <v>900.024335</v>
+        <v>7165.028589</v>
       </c>
       <c r="D152" t="n">
-        <v>1389.904697</v>
+        <v>3340.325803</v>
       </c>
       <c r="E152" t="n">
-        <v>929.4195989999999</v>
+        <v>5280.673074</v>
       </c>
       <c r="F152" t="n">
-        <v>729.336978</v>
+        <v>2364.317114</v>
       </c>
       <c r="G152" t="n">
-        <v>949.087115</v>
+        <v>2046.42661</v>
       </c>
       <c r="H152" t="n">
-        <v>1106.993769</v>
+        <v>2344.140071</v>
       </c>
       <c r="I152" t="n">
-        <v>929.206581</v>
+        <v>3827.341422</v>
       </c>
       <c r="J152" t="n">
-        <v>823.3309410000001</v>
-      </c>
-      <c r="K152" t="n">
-        <v>1348.323574</v>
+        <v>3178.747745</v>
       </c>
     </row>
     <row r="153">
@@ -5713,34 +5587,31 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0</v>
+        <v>1.339275</v>
       </c>
       <c r="C153" t="n">
-        <v>0.536405</v>
+        <v>0.87322</v>
       </c>
       <c r="D153" t="n">
-        <v>0.644922</v>
+        <v>0.901962</v>
       </c>
       <c r="E153" t="n">
-        <v>0.564061</v>
+        <v>0.574451</v>
       </c>
       <c r="F153" t="n">
-        <v>0.605889</v>
+        <v>1.249787</v>
       </c>
       <c r="G153" t="n">
-        <v>0.32839</v>
+        <v>1.073411</v>
       </c>
       <c r="H153" t="n">
-        <v>0.904235</v>
+        <v>0.757948</v>
       </c>
       <c r="I153" t="n">
-        <v>0.619853</v>
+        <v>1.243945</v>
       </c>
       <c r="J153" t="n">
-        <v>0.56917</v>
-      </c>
-      <c r="K153" t="n">
-        <v>1.030055</v>
+        <v>1.071785</v>
       </c>
     </row>
     <row r="154">
@@ -5749,33 +5620,32 @@
           <t>電子零組件業平上市</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr"/>
+      <c r="B154" t="n">
+        <v>40934.241108</v>
+      </c>
       <c r="C154" t="n">
-        <v>2792.735522</v>
+        <v>2613.190429</v>
       </c>
       <c r="D154" t="n">
-        <v>4865.581261</v>
+        <v>3730.19601</v>
       </c>
       <c r="E154" t="n">
-        <v>7314.585275</v>
+        <v>24390.125611</v>
       </c>
       <c r="F154" t="n">
-        <v>3323.928044</v>
+        <v>19899.378642</v>
       </c>
       <c r="G154" t="n">
-        <v>4869.715431</v>
+        <v>19626.115267</v>
       </c>
       <c r="H154" t="n">
-        <v>6364.882629</v>
+        <v>8858.221991</v>
       </c>
       <c r="I154" t="n">
-        <v>1607.896464</v>
+        <v>9777.164191</v>
       </c>
       <c r="J154" t="n">
-        <v>1967.018327</v>
-      </c>
-      <c r="K154" t="n">
-        <v>3271.617284</v>
+        <v>9862.512565000001</v>
       </c>
     </row>
     <row r="155">
@@ -5784,33 +5654,32 @@
           <t>電子零組件業平上櫃</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr"/>
+      <c r="B155" t="n">
+        <v>3.729705</v>
+      </c>
       <c r="C155" t="n">
-        <v>0.342766</v>
+        <v>1.601472</v>
       </c>
       <c r="D155" t="n">
-        <v>0.27792</v>
+        <v>1.503673</v>
       </c>
       <c r="E155" t="n">
-        <v>0.266301</v>
+        <v>3.26944</v>
       </c>
       <c r="F155" t="n">
-        <v>0.322656</v>
+        <v>4.11166</v>
       </c>
       <c r="G155" t="n">
-        <v>1.00409</v>
+        <v>3.518995</v>
       </c>
       <c r="H155" t="n">
-        <v>0.317373</v>
+        <v>3.443462</v>
       </c>
       <c r="I155" t="n">
-        <v>0.421761</v>
+        <v>4.972175</v>
       </c>
       <c r="J155" t="n">
-        <v>0.366252</v>
-      </c>
-      <c r="K155" t="n">
-        <v>0.498292</v>
+        <v>2.336314</v>
       </c>
     </row>
     <row r="156">
@@ -5819,33 +5688,32 @@
           <t>電機機械右上上市</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr"/>
+      <c r="B156" t="n">
+        <v>20018.210526</v>
+      </c>
       <c r="C156" t="n">
-        <v>13952.53928</v>
+        <v>19665.379644</v>
       </c>
       <c r="D156" t="n">
-        <v>21941.412373</v>
+        <v>16041.960584</v>
       </c>
       <c r="E156" t="n">
-        <v>20653.023269</v>
+        <v>16397.971383</v>
       </c>
       <c r="F156" t="n">
-        <v>17783.28272</v>
+        <v>15648.185563</v>
       </c>
       <c r="G156" t="n">
-        <v>17698.696071</v>
+        <v>20759.210972</v>
       </c>
       <c r="H156" t="n">
-        <v>17107.566288</v>
+        <v>19153.740726</v>
       </c>
       <c r="I156" t="n">
-        <v>21736.79682</v>
+        <v>8966.400874999999</v>
       </c>
       <c r="J156" t="n">
-        <v>20870.148901</v>
-      </c>
-      <c r="K156" t="n">
-        <v>9721.052197000001</v>
+        <v>5616.545071</v>
       </c>
     </row>
     <row r="157">
@@ -5854,33 +5722,32 @@
           <t>電機機械右上上櫃</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr"/>
+      <c r="B157" t="n">
+        <v>0.406659</v>
+      </c>
       <c r="C157" t="n">
-        <v>0.9784</v>
+        <v>0.255269</v>
       </c>
       <c r="D157" t="n">
-        <v>1.234403</v>
+        <v>0.281269</v>
       </c>
       <c r="E157" t="n">
-        <v>0.736514</v>
+        <v>1.930055</v>
       </c>
       <c r="F157" t="n">
-        <v>0.901869</v>
+        <v>1.779102</v>
       </c>
       <c r="G157" t="n">
-        <v>2.045405</v>
+        <v>3.481795</v>
       </c>
       <c r="H157" t="n">
-        <v>1.835066</v>
+        <v>2.240837</v>
       </c>
       <c r="I157" t="n">
-        <v>3.495789</v>
+        <v>1.575423</v>
       </c>
       <c r="J157" t="n">
-        <v>2.265916</v>
-      </c>
-      <c r="K157" t="n">
-        <v>1.696695</v>
+        <v>1.048016</v>
       </c>
     </row>
     <row r="158">
@@ -5889,33 +5756,32 @@
           <t>電機機械右下上市</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr"/>
+      <c r="B158" t="n">
+        <v>960.535046</v>
+      </c>
       <c r="C158" t="n">
-        <v>859.034638</v>
+        <v>1205.127393</v>
       </c>
       <c r="D158" t="n">
-        <v>522.534125</v>
+        <v>1278.56809225</v>
       </c>
       <c r="E158" t="n">
-        <v>560.189292</v>
+        <v>1352.800315</v>
       </c>
       <c r="F158" t="n">
-        <v>497.79934625</v>
+        <v>1402.402289</v>
       </c>
       <c r="G158" t="n">
-        <v>484.273872</v>
+        <v>904.3769</v>
       </c>
       <c r="H158" t="n">
-        <v>1003.984237</v>
+        <v>1280.301169</v>
       </c>
       <c r="I158" t="n">
-        <v>1204.163042</v>
+        <v>1389.069581</v>
       </c>
       <c r="J158" t="n">
-        <v>803.446879</v>
-      </c>
-      <c r="K158" t="n">
-        <v>871.467301</v>
+        <v>981.387952</v>
       </c>
     </row>
     <row r="159">
@@ -5925,34 +5791,31 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0</v>
+        <v>0.100141</v>
       </c>
       <c r="C159" t="n">
-        <v>0.07742599999999999</v>
+        <v>0.1047293333333333</v>
       </c>
       <c r="D159" t="n">
-        <v>0.080253</v>
+        <v>0.070176</v>
       </c>
       <c r="E159" t="n">
-        <v>0.07188633333333333</v>
+        <v>0.085379</v>
       </c>
       <c r="F159" t="n">
-        <v>0.065122</v>
+        <v>0.128986</v>
       </c>
       <c r="G159" t="n">
-        <v>0.079804</v>
+        <v>0.09494175000000001</v>
       </c>
       <c r="H159" t="n">
-        <v>0.105622</v>
+        <v>0.145845</v>
       </c>
       <c r="I159" t="n">
-        <v>0.08888875</v>
+        <v>0.17716775</v>
       </c>
       <c r="J159" t="n">
-        <v>0.08030900000000001</v>
-      </c>
-      <c r="K159" t="n">
-        <v>0.14932475</v>
+        <v>0.144214</v>
       </c>
     </row>
     <row r="160">
@@ -5961,33 +5824,32 @@
           <t>電機機械平上市</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr"/>
+      <c r="B160" t="n">
+        <v>2449.834377</v>
+      </c>
       <c r="C160" t="n">
-        <v>923.531349</v>
+        <v>1136.442185</v>
       </c>
       <c r="D160" t="n">
-        <v>964.633451</v>
+        <v>1901.489896</v>
       </c>
       <c r="E160" t="n">
-        <v>793.736661</v>
+        <v>1746.753474</v>
       </c>
       <c r="F160" t="n">
-        <v>940.936506</v>
+        <v>2660.71323</v>
       </c>
       <c r="G160" t="n">
-        <v>1314.555229</v>
+        <v>2418.585817</v>
       </c>
       <c r="H160" t="n">
-        <v>1599.750557</v>
+        <v>2536.58318</v>
       </c>
       <c r="I160" t="n">
-        <v>1141.213827</v>
+        <v>1626.27787</v>
       </c>
       <c r="J160" t="n">
-        <v>1297.029295</v>
-      </c>
-      <c r="K160" t="n">
-        <v>1389.228828</v>
+        <v>2322.683934</v>
       </c>
     </row>
     <row r="161">
@@ -5996,33 +5858,32 @@
           <t>電機機械平上櫃</t>
         </is>
       </c>
-      <c r="B161" t="inlineStr"/>
+      <c r="B161" t="n">
+        <v>0.979351</v>
+      </c>
       <c r="C161" t="n">
-        <v>0.091183</v>
+        <v>0.675076</v>
       </c>
       <c r="D161" t="n">
-        <v>0.152994</v>
+        <v>0.768943</v>
       </c>
       <c r="E161" t="n">
-        <v>0.196578</v>
+        <v>0.155259</v>
       </c>
       <c r="F161" t="n">
-        <v>0.138342</v>
+        <v>0.127739</v>
       </c>
       <c r="G161" t="n">
-        <v>0.033899</v>
+        <v>0.081984</v>
       </c>
       <c r="H161" t="n">
-        <v>0.080669</v>
+        <v>0.084762</v>
       </c>
       <c r="I161" t="n">
-        <v>0.06519899999999999</v>
+        <v>0.158662</v>
       </c>
       <c r="J161" t="n">
-        <v>0.099492</v>
-      </c>
-      <c r="K161" t="n">
-        <v>0.047676</v>
+        <v>0.106951</v>
       </c>
     </row>
     <row r="162">
@@ -6031,33 +5892,32 @@
           <t>電腦及週邊設備業右上上市</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr"/>
+      <c r="B162" t="n">
+        <v>43335.107824</v>
+      </c>
       <c r="C162" t="n">
-        <v>33027.484691</v>
+        <v>31110.029175</v>
       </c>
       <c r="D162" t="n">
-        <v>42588.00656</v>
+        <v>31285.393991</v>
       </c>
       <c r="E162" t="n">
-        <v>30947.277086</v>
+        <v>43834.111024</v>
       </c>
       <c r="F162" t="n">
-        <v>31226.702936</v>
+        <v>38144.865106</v>
       </c>
       <c r="G162" t="n">
-        <v>43544.851477</v>
+        <v>42702.884281</v>
       </c>
       <c r="H162" t="n">
-        <v>38030.459823</v>
+        <v>38943.162022</v>
       </c>
       <c r="I162" t="n">
-        <v>43116.131312</v>
+        <v>57897.018994</v>
       </c>
       <c r="J162" t="n">
-        <v>38475.016145</v>
-      </c>
-      <c r="K162" t="n">
-        <v>57387.377591</v>
+        <v>41469.300152</v>
       </c>
     </row>
     <row r="163">
@@ -6066,33 +5926,32 @@
           <t>電腦及週邊設備業右上上櫃</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr"/>
+      <c r="B163" t="n">
+        <v>6.813135</v>
+      </c>
       <c r="C163" t="n">
-        <v>7.514641</v>
+        <v>3.458445</v>
       </c>
       <c r="D163" t="n">
-        <v>6.604121</v>
+        <v>3.286976</v>
       </c>
       <c r="E163" t="n">
-        <v>4.522535</v>
+        <v>5.63341</v>
       </c>
       <c r="F163" t="n">
-        <v>3.231759</v>
+        <v>7.647517</v>
       </c>
       <c r="G163" t="n">
-        <v>5.96795</v>
+        <v>4.386462</v>
       </c>
       <c r="H163" t="n">
-        <v>8.116228</v>
+        <v>3.744373</v>
       </c>
       <c r="I163" t="n">
-        <v>3.257771</v>
+        <v>4.552767</v>
       </c>
       <c r="J163" t="n">
-        <v>4.518528</v>
-      </c>
-      <c r="K163" t="n">
-        <v>5.078686</v>
+        <v>9.666439</v>
       </c>
     </row>
     <row r="164">
@@ -6101,33 +5960,32 @@
           <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr"/>
+      <c r="B164" t="n">
+        <v>15058.478097</v>
+      </c>
       <c r="C164" t="n">
-        <v>7475.184712</v>
+        <v>8090.653738</v>
       </c>
       <c r="D164" t="n">
-        <v>13609.225923</v>
+        <v>8372.407546</v>
       </c>
       <c r="E164" t="n">
-        <v>6486.051783</v>
+        <v>5011.133429</v>
       </c>
       <c r="F164" t="n">
-        <v>7857.032012</v>
+        <v>9046.637635999999</v>
       </c>
       <c r="G164" t="n">
-        <v>3699.843837</v>
+        <v>6167.77495</v>
       </c>
       <c r="H164" t="n">
-        <v>4448.901824</v>
+        <v>7418.865709</v>
       </c>
       <c r="I164" t="n">
-        <v>3383.67531</v>
+        <v>12062.739108</v>
       </c>
       <c r="J164" t="n">
-        <v>5495.817378</v>
-      </c>
-      <c r="K164" t="n">
-        <v>6999.368153</v>
+        <v>15563.819925</v>
       </c>
     </row>
     <row r="165">
@@ -6137,34 +5995,31 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>0</v>
+        <v>0.168679</v>
       </c>
       <c r="C165" t="n">
-        <v>0.117566</v>
+        <v>0.1089475</v>
       </c>
       <c r="D165" t="n">
-        <v>0.151613</v>
+        <v>0.087995</v>
       </c>
       <c r="E165" t="n">
-        <v>0.1123185</v>
+        <v>0.151576</v>
       </c>
       <c r="F165" t="n">
-        <v>0.078399</v>
+        <v>0.163469</v>
       </c>
       <c r="G165" t="n">
-        <v>0.139536</v>
+        <v>0.09155199999999999</v>
       </c>
       <c r="H165" t="n">
-        <v>0.133896</v>
+        <v>0.15035425</v>
       </c>
       <c r="I165" t="n">
-        <v>0.0814</v>
+        <v>0.321696</v>
       </c>
       <c r="J165" t="n">
-        <v>0.14195925</v>
-      </c>
-      <c r="K165" t="n">
-        <v>0.287144</v>
+        <v>0.144102</v>
       </c>
     </row>
     <row r="166">
@@ -6173,33 +6028,32 @@
           <t>電腦及週邊設備業平上市</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr"/>
+      <c r="B166" t="n">
+        <v>429.318786</v>
+      </c>
       <c r="C166" t="n">
-        <v>2257.553972</v>
+        <v>328.729665</v>
       </c>
       <c r="D166" t="n">
-        <v>2625.672224</v>
+        <v>642.189541</v>
       </c>
       <c r="E166" t="n">
-        <v>2096.083709</v>
+        <v>458.611679</v>
       </c>
       <c r="F166" t="n">
-        <v>1216.25613</v>
+        <v>610.820832</v>
       </c>
       <c r="G166" t="n">
-        <v>2059.160818</v>
+        <v>904.703303</v>
       </c>
       <c r="H166" t="n">
-        <v>5322.961927</v>
+        <v>424.428801</v>
       </c>
       <c r="I166" t="n">
-        <v>3275.555912</v>
+        <v>459.768489</v>
       </c>
       <c r="J166" t="n">
-        <v>2815.623009</v>
-      </c>
-      <c r="K166" t="n">
-        <v>6032.780847</v>
+        <v>468.411875</v>
       </c>
     </row>
     <row r="167">
@@ -6208,33 +6062,32 @@
           <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
-      <c r="B167" t="inlineStr"/>
+      <c r="B167" t="n">
+        <v>1.749221</v>
+      </c>
       <c r="C167" t="n">
-        <v>0.208538</v>
+        <v>3.07077</v>
       </c>
       <c r="D167" t="n">
-        <v>0.456795</v>
+        <v>1.472591</v>
       </c>
       <c r="E167" t="n">
-        <v>0.239754</v>
+        <v>1.429916</v>
       </c>
       <c r="F167" t="n">
-        <v>0.102567</v>
+        <v>1.54623</v>
       </c>
       <c r="G167" t="n">
-        <v>0.160217</v>
+        <v>0.896875</v>
       </c>
       <c r="H167" t="n">
-        <v>0.216791</v>
+        <v>1.494557</v>
       </c>
       <c r="I167" t="n">
-        <v>0.146328</v>
+        <v>1.832703</v>
       </c>
       <c r="J167" t="n">
-        <v>0.150315</v>
-      </c>
-      <c r="K167" t="n">
-        <v>0.28927</v>
+        <v>2.195671</v>
       </c>
     </row>
     <row r="168">
@@ -6243,33 +6096,32 @@
           <t>食品工業右上上市</t>
         </is>
       </c>
-      <c r="B168" t="inlineStr"/>
+      <c r="B168" t="n">
+        <v>10.989736</v>
+      </c>
       <c r="C168" t="n">
-        <v>12.361364</v>
+        <v>586.277846</v>
       </c>
       <c r="D168" t="n">
-        <v>24.985346</v>
+        <v>7.264615</v>
       </c>
       <c r="E168" t="n">
-        <v>19.176035</v>
+        <v>8.02271</v>
       </c>
       <c r="F168" t="n">
-        <v>18.254504</v>
+        <v>11.865974</v>
       </c>
       <c r="G168" t="n">
-        <v>15.030035</v>
+        <v>16.580074</v>
       </c>
       <c r="H168" t="n">
-        <v>22.714533</v>
+        <v>7.674888</v>
       </c>
       <c r="I168" t="n">
-        <v>18.953213</v>
+        <v>9.180273</v>
       </c>
       <c r="J168" t="n">
-        <v>13.274733</v>
-      </c>
-      <c r="K168" t="n">
-        <v>16.692089</v>
+        <v>15.211594</v>
       </c>
     </row>
     <row r="169">
@@ -6278,33 +6130,32 @@
           <t>食品工業右上上櫃</t>
         </is>
       </c>
-      <c r="B169" t="inlineStr"/>
+      <c r="B169" t="n">
+        <v>0.004336</v>
+      </c>
       <c r="C169" t="n">
-        <v>0.003652</v>
+        <v>0.002534</v>
       </c>
       <c r="D169" t="n">
-        <v>0.005167</v>
+        <v>0.001886</v>
       </c>
       <c r="E169" t="n">
-        <v>0.002534</v>
+        <v>0.003556</v>
       </c>
       <c r="F169" t="n">
-        <v>0.004008</v>
+        <v>0.004412</v>
       </c>
       <c r="G169" t="n">
-        <v>0.005365</v>
+        <v>0.005225</v>
       </c>
       <c r="H169" t="n">
-        <v>0.005112</v>
+        <v>0.005884</v>
       </c>
       <c r="I169" t="n">
-        <v>0.007178</v>
+        <v>0.005327</v>
       </c>
       <c r="J169" t="n">
-        <v>0.006919</v>
-      </c>
-      <c r="K169" t="n">
-        <v>0.008226000000000001</v>
+        <v>0.00641</v>
       </c>
     </row>
     <row r="170">
@@ -6313,33 +6164,32 @@
           <t>食品工業右下上市</t>
         </is>
       </c>
-      <c r="B170" t="inlineStr"/>
+      <c r="B170" t="n">
+        <v>412.232246</v>
+      </c>
       <c r="C170" t="n">
-        <v>622.669405</v>
+        <v>284.234782</v>
       </c>
       <c r="D170" t="n">
-        <v>898.831877</v>
+        <v>286.797627</v>
       </c>
       <c r="E170" t="n">
-        <v>293.333234</v>
+        <v>318.886002</v>
       </c>
       <c r="F170" t="n">
-        <v>649.727039</v>
+        <v>261.472583</v>
       </c>
       <c r="G170" t="n">
-        <v>802.013354</v>
+        <v>264.272879</v>
       </c>
       <c r="H170" t="n">
-        <v>777.085777</v>
+        <v>1688.815661</v>
       </c>
       <c r="I170" t="n">
-        <v>703.082083</v>
+        <v>1095.910492</v>
       </c>
       <c r="J170" t="n">
-        <v>1688.815661</v>
-      </c>
-      <c r="K170" t="n">
-        <v>1095.910492</v>
+        <v>307.941446</v>
       </c>
     </row>
     <row r="171">
@@ -6349,34 +6199,31 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0</v>
+        <v>0.014792</v>
       </c>
       <c r="C171" t="n">
-        <v>0.006211</v>
+        <v>0.01134</v>
       </c>
       <c r="D171" t="n">
-        <v>0.013842</v>
+        <v>0.010856</v>
       </c>
       <c r="E171" t="n">
-        <v>0.010018</v>
+        <v>0.005911</v>
       </c>
       <c r="F171" t="n">
-        <v>0.005706</v>
+        <v>0.010054</v>
       </c>
       <c r="G171" t="n">
-        <v>0.004506</v>
+        <v>0.006973</v>
       </c>
       <c r="H171" t="n">
-        <v>0.008725999999999999</v>
+        <v>0.010705</v>
       </c>
       <c r="I171" t="n">
-        <v>0.006001</v>
+        <v>0.016031</v>
       </c>
       <c r="J171" t="n">
-        <v>0.007215</v>
-      </c>
-      <c r="K171" t="n">
-        <v>0.013382</v>
+        <v>0.010104</v>
       </c>
     </row>
     <row r="172">
@@ -6385,18 +6232,33 @@
           <t>食品工業平上市</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr"/>
-      <c r="C172" t="inlineStr"/>
-      <c r="D172" t="inlineStr"/>
+      <c r="B172" t="n">
+        <v>500.595241</v>
+      </c>
+      <c r="C172" t="n">
+        <v>17.710497</v>
+      </c>
+      <c r="D172" t="n">
+        <v>373.919301</v>
+      </c>
       <c r="E172" t="n">
-        <v>575.713856</v>
-      </c>
-      <c r="F172" t="inlineStr"/>
-      <c r="G172" t="inlineStr"/>
-      <c r="H172" t="inlineStr"/>
-      <c r="I172" t="inlineStr"/>
-      <c r="J172" t="inlineStr"/>
-      <c r="K172" t="inlineStr"/>
+        <v>490.134677</v>
+      </c>
+      <c r="F172" t="n">
+        <v>526.461753</v>
+      </c>
+      <c r="G172" t="n">
+        <v>441.182343</v>
+      </c>
+      <c r="H172" t="n">
+        <v>5.599845</v>
+      </c>
+      <c r="I172" t="n">
+        <v>7.511816</v>
+      </c>
+      <c r="J172" t="n">
+        <v>949.30633</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
@@ -6404,22 +6266,33 @@
           <t>食品工業平上櫃</t>
         </is>
       </c>
-      <c r="B173" t="inlineStr"/>
-      <c r="C173" t="inlineStr"/>
-      <c r="D173" t="inlineStr"/>
+      <c r="B173" t="n">
+        <v>0.000831</v>
+      </c>
+      <c r="C173" t="n">
+        <v>0.002383</v>
+      </c>
+      <c r="D173" t="n">
+        <v>0.004609</v>
+      </c>
       <c r="E173" t="n">
-        <v>0.002383</v>
+        <v>0.003325</v>
       </c>
       <c r="F173" t="n">
-        <v>0.002487</v>
+        <v>0.0007</v>
       </c>
       <c r="G173" t="n">
-        <v>0.001516</v>
-      </c>
-      <c r="H173" t="inlineStr"/>
-      <c r="I173" t="inlineStr"/>
-      <c r="J173" t="inlineStr"/>
-      <c r="K173" t="inlineStr"/>
+        <v>0.001953</v>
+      </c>
+      <c r="H173" t="n">
+        <v>0.001035</v>
+      </c>
+      <c r="I173" t="n">
+        <v>0.002899</v>
+      </c>
+      <c r="J173" t="n">
+        <v>0.007135</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Result/analyze_2.xlsx
+++ b/Result/analyze_2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J173"/>
+  <dimension ref="A1:K172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,7 +436,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -477,6 +477,11 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -486,32 +491,33 @@
           <t>光電業右上上市</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>115422.481566</v>
-      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>75436.525366</v>
+        <v>77016.14013699999</v>
       </c>
       <c r="D2" t="n">
-        <v>46586.686312</v>
+        <v>47630.618118</v>
       </c>
       <c r="E2" t="n">
-        <v>51636.891594</v>
+        <v>52329.13654</v>
       </c>
       <c r="F2" t="n">
-        <v>86070.802371</v>
+        <v>87049.123955</v>
       </c>
       <c r="G2" t="n">
-        <v>106432.610774</v>
+        <v>107133.497541</v>
       </c>
       <c r="H2" t="n">
-        <v>74175.14004899999</v>
+        <v>74782.54464199999</v>
       </c>
       <c r="I2" t="n">
-        <v>106634.769564</v>
+        <v>107205.401757</v>
       </c>
       <c r="J2" t="n">
-        <v>72074.281301</v>
+        <v>72654.152778</v>
+      </c>
+      <c r="K2" t="n">
+        <v>66320.88806300001</v>
       </c>
     </row>
     <row r="3">
@@ -520,32 +526,33 @@
           <t>光電業右上上櫃</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>4.93632</v>
-      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>1.988611</v>
+        <v>2.333941</v>
       </c>
       <c r="D3" t="n">
-        <v>4.200368</v>
+        <v>4.980801</v>
       </c>
       <c r="E3" t="n">
-        <v>6.813472</v>
+        <v>6.981326</v>
       </c>
       <c r="F3" t="n">
-        <v>6.721156</v>
+        <v>7.06809</v>
       </c>
       <c r="G3" t="n">
-        <v>6.072605</v>
+        <v>6.161525</v>
       </c>
       <c r="H3" t="n">
-        <v>12.53609</v>
+        <v>12.623548</v>
       </c>
       <c r="I3" t="n">
-        <v>11.669936</v>
+        <v>11.680688</v>
       </c>
       <c r="J3" t="n">
-        <v>12.236182</v>
+        <v>12.179591</v>
+      </c>
+      <c r="K3" t="n">
+        <v>15.56866</v>
       </c>
     </row>
     <row r="4">
@@ -554,32 +561,33 @@
           <t>光電業右下上市</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>2192.450429</v>
-      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>1103.326977</v>
+        <v>803.809093</v>
       </c>
       <c r="D4" t="n">
-        <v>1742.583713</v>
+        <v>1122.927252</v>
       </c>
       <c r="E4" t="n">
-        <v>898.356579</v>
+        <v>488.403628</v>
       </c>
       <c r="F4" t="n">
-        <v>1542.59659</v>
+        <v>990.094939</v>
       </c>
       <c r="G4" t="n">
-        <v>627.005644</v>
+        <v>674.890955</v>
       </c>
       <c r="H4" t="n">
-        <v>809.753993</v>
+        <v>246.925746</v>
       </c>
       <c r="I4" t="n">
-        <v>874.586958</v>
+        <v>510.69576</v>
       </c>
       <c r="J4" t="n">
-        <v>1018.523287</v>
+        <v>321.265563</v>
+      </c>
+      <c r="K4" t="n">
+        <v>244.648133</v>
       </c>
     </row>
     <row r="5">
@@ -589,31 +597,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.026978</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>1.008579</v>
+        <v>0.921492</v>
       </c>
       <c r="D5" t="n">
-        <v>0.944307</v>
+        <v>0.880448</v>
       </c>
       <c r="E5" t="n">
-        <v>1.31829225</v>
+        <v>1.27465725</v>
       </c>
       <c r="F5" t="n">
-        <v>0.866345</v>
+        <v>0.842423</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9060865</v>
+        <v>0.7876445</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9748790000000001</v>
+        <v>0.886626</v>
       </c>
       <c r="I5" t="n">
-        <v>1.483324</v>
+        <v>1.197747</v>
       </c>
       <c r="J5" t="n">
-        <v>1.933499</v>
+        <v>1.896713</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.171862</v>
       </c>
     </row>
     <row r="6">
@@ -622,32 +633,33 @@
           <t>光電業平上市</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>3533.057299</v>
-      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>1768.985805</v>
+        <v>485.820215</v>
       </c>
       <c r="D6" t="n">
-        <v>1177.582203</v>
+        <v>749.766723</v>
       </c>
       <c r="E6" t="n">
-        <v>866.71379</v>
+        <v>579.313011</v>
       </c>
       <c r="F6" t="n">
-        <v>1194.916813</v>
+        <v>753.51323</v>
       </c>
       <c r="G6" t="n">
-        <v>1063.781628</v>
+        <v>309.619091</v>
       </c>
       <c r="H6" t="n">
-        <v>1114.478124</v>
+        <v>1063.887458</v>
       </c>
       <c r="I6" t="n">
-        <v>1524.632189</v>
+        <v>1306.479152</v>
       </c>
       <c r="J6" t="n">
-        <v>1117.499227</v>
+        <v>1226.272</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1457.47218</v>
       </c>
     </row>
     <row r="7">
@@ -656,32 +668,33 @@
           <t>光電業平上櫃</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>0.684599</v>
-      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>0.510082</v>
+        <v>0.247272</v>
       </c>
       <c r="D7" t="n">
-        <v>0.936181</v>
+        <v>0.215378</v>
       </c>
       <c r="E7" t="n">
-        <v>0.296713</v>
+        <v>0.163001</v>
       </c>
       <c r="F7" t="n">
-        <v>0.507507</v>
+        <v>0.173609</v>
       </c>
       <c r="G7" t="n">
-        <v>0.161472</v>
+        <v>0.180915</v>
       </c>
       <c r="H7" t="n">
-        <v>0.230956</v>
+        <v>0.219701</v>
       </c>
       <c r="I7" t="n">
-        <v>0.216312</v>
+        <v>0.485999</v>
       </c>
       <c r="J7" t="n">
-        <v>0.178666</v>
+        <v>0.266975</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.201829</v>
       </c>
     </row>
     <row r="8">
@@ -690,32 +703,33 @@
           <t>其他右上上市</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>708.754765</v>
-      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>695.467022</v>
+        <v>718.182277</v>
       </c>
       <c r="D8" t="n">
-        <v>804.3266159999999</v>
+        <v>808.951334</v>
       </c>
       <c r="E8" t="n">
-        <v>945.081587</v>
+        <v>653.1447899999999</v>
       </c>
       <c r="F8" t="n">
-        <v>1026.433541</v>
+        <v>806.822822</v>
       </c>
       <c r="G8" t="n">
-        <v>1319.534296</v>
+        <v>1166.586888</v>
       </c>
       <c r="H8" t="n">
-        <v>1653.5761</v>
+        <v>1535.231402</v>
       </c>
       <c r="I8" t="n">
-        <v>2214.886948</v>
+        <v>1831.969767</v>
       </c>
       <c r="J8" t="n">
-        <v>1182.599023</v>
+        <v>989.796277</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1073.978075</v>
       </c>
     </row>
     <row r="9">
@@ -724,32 +738,33 @@
           <t>其他右上上櫃</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>1.733862</v>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>4.251473</v>
+        <v>4.256129</v>
       </c>
       <c r="D9" t="n">
-        <v>1.366303</v>
+        <v>1.379422</v>
       </c>
       <c r="E9" t="n">
-        <v>1.71218</v>
+        <v>1.720251</v>
       </c>
       <c r="F9" t="n">
-        <v>1.99472</v>
+        <v>2.001527</v>
       </c>
       <c r="G9" t="n">
-        <v>1.926111</v>
+        <v>1.927461</v>
       </c>
       <c r="H9" t="n">
-        <v>1.867746</v>
+        <v>1.869765</v>
       </c>
       <c r="I9" t="n">
-        <v>1.821556</v>
+        <v>1.821577</v>
       </c>
       <c r="J9" t="n">
-        <v>1.777786</v>
+        <v>1.759134</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.410704</v>
       </c>
     </row>
     <row r="10">
@@ -758,32 +773,33 @@
           <t>其他右下上市</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>1887.073794</v>
-      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>1367.403104</v>
+        <v>1537.147381</v>
       </c>
       <c r="D10" t="n">
-        <v>821.838253</v>
+        <v>840.695142</v>
       </c>
       <c r="E10" t="n">
-        <v>957.630659</v>
+        <v>956.589307</v>
       </c>
       <c r="F10" t="n">
-        <v>1092.657216</v>
+        <v>1092.69051</v>
       </c>
       <c r="G10" t="n">
-        <v>1151.470527</v>
+        <v>1279.983284</v>
       </c>
       <c r="H10" t="n">
-        <v>1061.894658</v>
+        <v>1091.299464</v>
       </c>
       <c r="I10" t="n">
-        <v>986.5640090000001</v>
+        <v>916.9355430000001</v>
       </c>
       <c r="J10" t="n">
-        <v>1214.916591</v>
+        <v>1089.606229</v>
+      </c>
+      <c r="K10" t="n">
+        <v>777.277031</v>
       </c>
     </row>
     <row r="11">
@@ -793,31 +809,34 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7884640000000001</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0.36906525</v>
+        <v>0.37018525</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2415985</v>
+        <v>0.2667605</v>
       </c>
       <c r="E11" t="n">
-        <v>0.308221</v>
+        <v>0.311672</v>
       </c>
       <c r="F11" t="n">
-        <v>0.341959</v>
+        <v>0.403889</v>
       </c>
       <c r="G11" t="n">
-        <v>2.512299</v>
+        <v>2.514648</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9609550833333333</v>
+        <v>1.023775083333333</v>
       </c>
       <c r="I11" t="n">
-        <v>1.05431</v>
+        <v>1.053565</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6217311666666666</v>
+        <v>0.6235891666666666</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.702704</v>
       </c>
     </row>
     <row r="12">
@@ -826,32 +845,33 @@
           <t>其他平上市</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>368.675684</v>
-      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>281.544287</v>
+        <v>89.084755</v>
       </c>
       <c r="D12" t="n">
-        <v>142.31445</v>
+        <v>118.832843</v>
       </c>
       <c r="E12" t="n">
-        <v>164.8614</v>
+        <v>457.839549</v>
       </c>
       <c r="F12" t="n">
-        <v>148.657663</v>
+        <v>368.235088</v>
       </c>
       <c r="G12" t="n">
-        <v>246.467539</v>
+        <v>270.90219</v>
       </c>
       <c r="H12" t="n">
-        <v>179.031457</v>
+        <v>267.971349</v>
       </c>
       <c r="I12" t="n">
-        <v>146.276942</v>
+        <v>598.822589</v>
       </c>
       <c r="J12" t="n">
-        <v>53.90317</v>
+        <v>372.016278</v>
+      </c>
+      <c r="K12" t="n">
+        <v>379.898457</v>
       </c>
     </row>
     <row r="13">
@@ -860,32 +880,33 @@
           <t>其他平上櫃</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>0.045488</v>
-      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>0.053156</v>
+        <v>0.028894</v>
       </c>
       <c r="D13" t="n">
-        <v>0.07677200000000001</v>
+        <v>0.028113</v>
       </c>
       <c r="E13" t="n">
-        <v>0.073134</v>
+        <v>0.048891</v>
       </c>
       <c r="F13" t="n">
-        <v>0.10516</v>
+        <v>0.01526</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0696565</v>
+        <v>0.0596845</v>
       </c>
       <c r="H13" t="n">
-        <v>0.085149</v>
+        <v>0.010407</v>
       </c>
       <c r="I13" t="n">
-        <v>0.121839</v>
+        <v>0.107255</v>
       </c>
       <c r="J13" t="n">
-        <v>0.077456</v>
+        <v>0.080383</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.06454600000000001</v>
       </c>
     </row>
     <row r="14">
@@ -894,32 +915,33 @@
           <t>其他電子業右上上市</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>43866.035113</v>
-      </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>39906.027565</v>
+        <v>40603.861329</v>
       </c>
       <c r="D14" t="n">
-        <v>36079.271484</v>
+        <v>36308.402063</v>
       </c>
       <c r="E14" t="n">
-        <v>35352.869423</v>
+        <v>35956.648033</v>
       </c>
       <c r="F14" t="n">
-        <v>43844.505121</v>
+        <v>43873.810083</v>
       </c>
       <c r="G14" t="n">
-        <v>33855.922663</v>
+        <v>34212.143456</v>
       </c>
       <c r="H14" t="n">
-        <v>39818.732</v>
+        <v>41155.164782</v>
       </c>
       <c r="I14" t="n">
-        <v>58636.091601</v>
+        <v>58812.202222</v>
       </c>
       <c r="J14" t="n">
-        <v>61933.541822</v>
+        <v>62064.56041</v>
+      </c>
+      <c r="K14" t="n">
+        <v>43386.568025</v>
       </c>
     </row>
     <row r="15">
@@ -928,32 +950,33 @@
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>11.431169</v>
-      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
-        <v>9.114428</v>
+        <v>10.728227</v>
       </c>
       <c r="D15" t="n">
-        <v>13.437214</v>
+        <v>14.393279</v>
       </c>
       <c r="E15" t="n">
-        <v>8.991203000000001</v>
+        <v>10.543249</v>
       </c>
       <c r="F15" t="n">
-        <v>10.506049</v>
+        <v>13.73935</v>
       </c>
       <c r="G15" t="n">
-        <v>6.719846</v>
+        <v>9.655246</v>
       </c>
       <c r="H15" t="n">
-        <v>7.302763</v>
+        <v>9.871612000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>9.339683000000001</v>
+        <v>13.484624</v>
       </c>
       <c r="J15" t="n">
-        <v>8.56776</v>
+        <v>13.175972</v>
+      </c>
+      <c r="K15" t="n">
+        <v>12.520574</v>
       </c>
     </row>
     <row r="16">
@@ -962,32 +985,33 @@
           <t>其他電子業右下上市</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>204.045792</v>
-      </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>156.255981</v>
+        <v>418.121535</v>
       </c>
       <c r="D16" t="n">
-        <v>122.188769</v>
+        <v>387.959514</v>
       </c>
       <c r="E16" t="n">
-        <v>173.258883</v>
+        <v>388.689652</v>
       </c>
       <c r="F16" t="n">
-        <v>167.846943</v>
+        <v>437.686363</v>
       </c>
       <c r="G16" t="n">
-        <v>162.343206</v>
+        <v>342.637731</v>
       </c>
       <c r="H16" t="n">
-        <v>190.95954</v>
+        <v>368.704943</v>
       </c>
       <c r="I16" t="n">
-        <v>302.511449</v>
+        <v>772.19219</v>
       </c>
       <c r="J16" t="n">
-        <v>368.526172</v>
+        <v>495.021773</v>
+      </c>
+      <c r="K16" t="n">
+        <v>466.160291</v>
       </c>
     </row>
     <row r="17">
@@ -997,31 +1021,34 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.2174656666666667</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.184608</v>
+        <v>0.029398</v>
       </c>
       <c r="D17" t="n">
-        <v>0.238945</v>
+        <v>0.010612</v>
       </c>
       <c r="E17" t="n">
-        <v>0.102638</v>
+        <v>0.015014</v>
       </c>
       <c r="F17" t="n">
-        <v>0.075781</v>
+        <v>0.016208</v>
       </c>
       <c r="G17" t="n">
-        <v>0.087064</v>
+        <v>0.03004</v>
       </c>
       <c r="H17" t="n">
-        <v>0.114932</v>
+        <v>0.019506</v>
       </c>
       <c r="I17" t="n">
-        <v>0.107558</v>
+        <v>0.064744</v>
       </c>
       <c r="J17" t="n">
-        <v>0.082695</v>
+        <v>0.044652</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.044543</v>
       </c>
     </row>
     <row r="18">
@@ -1030,32 +1057,33 @@
           <t>其他電子業平上市</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>2269.923561</v>
-      </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>1069.607557</v>
+        <v>109.908239</v>
       </c>
       <c r="D18" t="n">
-        <v>733.0549140000001</v>
+        <v>238.15359</v>
       </c>
       <c r="E18" t="n">
-        <v>1399.054171</v>
+        <v>579.844792</v>
       </c>
       <c r="F18" t="n">
-        <v>662.797492</v>
+        <v>363.65311</v>
       </c>
       <c r="G18" t="n">
-        <v>756.907611</v>
+        <v>220.392293</v>
       </c>
       <c r="H18" t="n">
-        <v>1625.270931</v>
+        <v>111.092746</v>
       </c>
       <c r="I18" t="n">
-        <v>803.294501</v>
+        <v>157.503139</v>
       </c>
       <c r="J18" t="n">
-        <v>1393.298319</v>
+        <v>1135.78413</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1190.777741</v>
       </c>
     </row>
     <row r="19">
@@ -1064,32 +1092,33 @@
           <t>其他電子業平上櫃</t>
         </is>
       </c>
-      <c r="B19" t="n">
-        <v>3.218028</v>
-      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>2.334074</v>
+        <v>0.772418</v>
       </c>
       <c r="D19" t="n">
-        <v>1.500443</v>
+        <v>0.545838</v>
       </c>
       <c r="E19" t="n">
-        <v>1.856242</v>
+        <v>0.301245</v>
       </c>
       <c r="F19" t="n">
-        <v>3.652731</v>
+        <v>0.42844</v>
       </c>
       <c r="G19" t="n">
-        <v>3.487986</v>
+        <v>0.342263</v>
       </c>
       <c r="H19" t="n">
-        <v>3.057712</v>
+        <v>0.285571</v>
       </c>
       <c r="I19" t="n">
-        <v>4.558452</v>
+        <v>0.27148</v>
       </c>
       <c r="J19" t="n">
-        <v>5.827706</v>
+        <v>0.079899</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.088772</v>
       </c>
     </row>
     <row r="20">
@@ -1098,32 +1127,33 @@
           <t>化學工業右上上市</t>
         </is>
       </c>
-      <c r="B20" t="n">
-        <v>5043.756829</v>
-      </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>8292.582050000001</v>
+        <v>8562.394875</v>
       </c>
       <c r="D20" t="n">
-        <v>9882.511367999999</v>
+        <v>10231.82806</v>
       </c>
       <c r="E20" t="n">
-        <v>6355.062814</v>
+        <v>6917.31368</v>
       </c>
       <c r="F20" t="n">
-        <v>8542.054827</v>
+        <v>8922.589506</v>
       </c>
       <c r="G20" t="n">
-        <v>5022.470767</v>
+        <v>5951.538249</v>
       </c>
       <c r="H20" t="n">
-        <v>10431.09168</v>
+        <v>10798.870931</v>
       </c>
       <c r="I20" t="n">
-        <v>10362.427802</v>
+        <v>11033.84295</v>
       </c>
       <c r="J20" t="n">
-        <v>12846.881223</v>
+        <v>13584.934835</v>
+      </c>
+      <c r="K20" t="n">
+        <v>11756.550361</v>
       </c>
     </row>
     <row r="21">
@@ -1132,32 +1162,33 @@
           <t>化學工業右上上櫃</t>
         </is>
       </c>
-      <c r="B21" t="n">
-        <v>0.104806</v>
-      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
-        <v>0.08237700000000001</v>
+        <v>0.108029</v>
       </c>
       <c r="D21" t="n">
-        <v>0.129619</v>
+        <v>0.253387</v>
       </c>
       <c r="E21" t="n">
-        <v>0.08554200000000001</v>
+        <v>0.776633</v>
       </c>
       <c r="F21" t="n">
-        <v>0.243057</v>
+        <v>1.370963</v>
       </c>
       <c r="G21" t="n">
-        <v>0.089675</v>
+        <v>0.982088</v>
       </c>
       <c r="H21" t="n">
-        <v>0.294889</v>
+        <v>0.809154</v>
       </c>
       <c r="I21" t="n">
-        <v>0.334746</v>
+        <v>0.733225</v>
       </c>
       <c r="J21" t="n">
-        <v>0.574137</v>
+        <v>0.955928</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.199357</v>
       </c>
     </row>
     <row r="22">
@@ -1166,33 +1197,34 @@
           <t>化學工業右下上市</t>
         </is>
       </c>
-      <c r="B22" t="n">
-        <v>231.748497</v>
-      </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
         <v>142.264442</v>
       </c>
       <c r="D22" t="n">
-        <v>386.917159</v>
+        <v>237.191771</v>
       </c>
       <c r="E22" t="n">
-        <v>174.154573</v>
+        <v>149.722673</v>
       </c>
       <c r="F22" t="n">
-        <v>137.624827</v>
+        <v>106.444353</v>
       </c>
       <c r="G22" t="n">
-        <v>104.854825</v>
+        <v>86.6267</v>
       </c>
       <c r="H22" t="n">
-        <v>196.898298</v>
+        <v>86.507775</v>
       </c>
       <c r="I22" t="n">
-        <v>217.971558</v>
+        <v>184.554769</v>
       </c>
       <c r="J22" t="n">
         <v>105.367152</v>
       </c>
+      <c r="K22" t="n">
+        <v>102.198641</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -1200,32 +1232,33 @@
           <t>化學工業右下上櫃</t>
         </is>
       </c>
-      <c r="B23" t="n">
-        <v>0.251038</v>
-      </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
-        <v>0.425178</v>
+        <v>0.08731899999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>0.302992</v>
+        <v>0.102565</v>
       </c>
       <c r="E23" t="n">
-        <v>0.75597</v>
+        <v>0.009887999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>0.639278</v>
+        <v>0.009261</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2668</v>
+        <v>0.008884</v>
       </c>
       <c r="H23" t="n">
-        <v>0.024437</v>
+        <v>0.025501</v>
       </c>
       <c r="I23" t="n">
-        <v>0.024472</v>
+        <v>0.025438</v>
       </c>
       <c r="J23" t="n">
-        <v>0.236392</v>
+        <v>0.007489</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.011008</v>
       </c>
     </row>
     <row r="24">
@@ -1234,32 +1267,33 @@
           <t>化學工業平上市</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>1732.131633</v>
-      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
-        <v>996.066389</v>
+        <v>726.253564</v>
       </c>
       <c r="D24" t="n">
-        <v>749.073516</v>
+        <v>549.482212</v>
       </c>
       <c r="E24" t="n">
-        <v>1063.384379</v>
+        <v>525.565413</v>
       </c>
       <c r="F24" t="n">
-        <v>1014.584463</v>
+        <v>665.230258</v>
       </c>
       <c r="G24" t="n">
-        <v>1574.244514</v>
+        <v>663.405157</v>
       </c>
       <c r="H24" t="n">
-        <v>723.970323</v>
+        <v>466.581595</v>
       </c>
       <c r="I24" t="n">
-        <v>1038.512025</v>
+        <v>400.513666</v>
       </c>
       <c r="J24" t="n">
-        <v>762.959099</v>
+        <v>267.905487</v>
+      </c>
+      <c r="K24" t="n">
+        <v>456.28072</v>
       </c>
     </row>
     <row r="25">
@@ -1268,32 +1302,33 @@
           <t>化學工業平上櫃</t>
         </is>
       </c>
-      <c r="B25" t="n">
-        <v>0.053762</v>
-      </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
-        <v>0.049746</v>
+        <v>0.361953</v>
       </c>
       <c r="D25" t="n">
-        <v>0.178292</v>
+        <v>0.254951</v>
       </c>
       <c r="E25" t="n">
-        <v>0.693905</v>
+        <v>0.748896</v>
       </c>
       <c r="F25" t="n">
-        <v>1.141352</v>
+        <v>0.643463</v>
       </c>
       <c r="G25" t="n">
-        <v>0.89294</v>
+        <v>0.258443</v>
       </c>
       <c r="H25" t="n">
-        <v>2.197642</v>
+        <v>1.682313</v>
       </c>
       <c r="I25" t="n">
-        <v>1.170657</v>
+        <v>0.771212</v>
       </c>
       <c r="J25" t="n">
-        <v>0.382493</v>
+        <v>0.229605</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.242105</v>
       </c>
     </row>
     <row r="26">
@@ -1302,32 +1337,33 @@
           <t>半導體業右上上市</t>
         </is>
       </c>
-      <c r="B26" t="n">
-        <v>380269.750197</v>
-      </c>
+      <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>301340.906928</v>
+        <v>318052.933265</v>
       </c>
       <c r="D26" t="n">
-        <v>270822.403683</v>
+        <v>276782.943875</v>
       </c>
       <c r="E26" t="n">
-        <v>285493.879323</v>
+        <v>291222.114528</v>
       </c>
       <c r="F26" t="n">
-        <v>307574.643404</v>
+        <v>315731.938489</v>
       </c>
       <c r="G26" t="n">
-        <v>229451.108898</v>
+        <v>234999.013285</v>
       </c>
       <c r="H26" t="n">
-        <v>247862.218384</v>
+        <v>260849.70102</v>
       </c>
       <c r="I26" t="n">
-        <v>366999.998588</v>
+        <v>373990.407141</v>
       </c>
       <c r="J26" t="n">
-        <v>309715.52784</v>
+        <v>314672.290155</v>
+      </c>
+      <c r="K26" t="n">
+        <v>270597.391357</v>
       </c>
     </row>
     <row r="27">
@@ -1336,32 +1372,33 @@
           <t>半導體業右上上櫃</t>
         </is>
       </c>
-      <c r="B27" t="n">
-        <v>155.644348</v>
-      </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
-        <v>154.61431</v>
+        <v>161.377952</v>
       </c>
       <c r="D27" t="n">
-        <v>90.226675</v>
+        <v>99.192314</v>
       </c>
       <c r="E27" t="n">
-        <v>79.75349</v>
+        <v>88.485629</v>
       </c>
       <c r="F27" t="n">
-        <v>123.720141</v>
+        <v>139.661966</v>
       </c>
       <c r="G27" t="n">
-        <v>128.044739</v>
+        <v>140.310446</v>
       </c>
       <c r="H27" t="n">
-        <v>116.418771</v>
+        <v>123.47523</v>
       </c>
       <c r="I27" t="n">
-        <v>141.135673</v>
+        <v>149.925874</v>
       </c>
       <c r="J27" t="n">
-        <v>110.221825</v>
+        <v>117.120813</v>
+      </c>
+      <c r="K27" t="n">
+        <v>122.464242</v>
       </c>
     </row>
     <row r="28">
@@ -1370,32 +1407,33 @@
           <t>半導體業右下上市</t>
         </is>
       </c>
-      <c r="B28" t="n">
-        <v>3777.169563</v>
-      </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
-        <v>982.275547</v>
+        <v>952.7060279999999</v>
       </c>
       <c r="D28" t="n">
-        <v>1190.705722</v>
+        <v>828.899846</v>
       </c>
       <c r="E28" t="n">
-        <v>1215.495016</v>
+        <v>983.773998</v>
       </c>
       <c r="F28" t="n">
-        <v>1089.004733</v>
+        <v>1098.479363</v>
       </c>
       <c r="G28" t="n">
-        <v>957.057733</v>
+        <v>1145.708272</v>
       </c>
       <c r="H28" t="n">
-        <v>621.03682</v>
+        <v>698.642332</v>
       </c>
       <c r="I28" t="n">
-        <v>1274.322432</v>
+        <v>1003.434086</v>
       </c>
       <c r="J28" t="n">
-        <v>1297.387778</v>
+        <v>1071.201193</v>
+      </c>
+      <c r="K28" t="n">
+        <v>870.262156</v>
       </c>
     </row>
     <row r="29">
@@ -1404,32 +1442,33 @@
           <t>半導體業右下上櫃</t>
         </is>
       </c>
-      <c r="B29" t="n">
-        <v>1.655054</v>
-      </c>
+      <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
-        <v>1.558873</v>
+        <v>1.2883</v>
       </c>
       <c r="D29" t="n">
-        <v>0.8938</v>
+        <v>0.900543</v>
       </c>
       <c r="E29" t="n">
-        <v>1.46473325</v>
+        <v>3.02567825</v>
       </c>
       <c r="F29" t="n">
-        <v>2.935031</v>
+        <v>1.791331</v>
       </c>
       <c r="G29" t="n">
-        <v>3.985883</v>
+        <v>3.077671</v>
       </c>
       <c r="H29" t="n">
-        <v>4.857131</v>
+        <v>2.445535</v>
       </c>
       <c r="I29" t="n">
-        <v>3.515911</v>
+        <v>2.415741</v>
       </c>
       <c r="J29" t="n">
-        <v>2.824977</v>
+        <v>2.248432</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.581245</v>
       </c>
     </row>
     <row r="30">
@@ -1438,32 +1477,33 @@
           <t>半導體業平上市</t>
         </is>
       </c>
-      <c r="B30" t="n">
-        <v>30973.84923</v>
-      </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>28779.054187</v>
+        <v>12092.675741</v>
       </c>
       <c r="D30" t="n">
-        <v>18447.333554</v>
+        <v>12845.093375</v>
       </c>
       <c r="E30" t="n">
-        <v>16209.80837</v>
+        <v>10705.973014</v>
       </c>
       <c r="F30" t="n">
-        <v>18913.857904</v>
+        <v>10741.106846</v>
       </c>
       <c r="G30" t="n">
-        <v>12874.398476</v>
+        <v>7129.630298</v>
       </c>
       <c r="H30" t="n">
-        <v>16711.163602</v>
+        <v>3639.240211</v>
       </c>
       <c r="I30" t="n">
-        <v>12336.164244</v>
+        <v>5598.691249</v>
       </c>
       <c r="J30" t="n">
-        <v>11623.162005</v>
+        <v>6885.810662</v>
+      </c>
+      <c r="K30" t="n">
+        <v>16283.378266</v>
       </c>
     </row>
     <row r="31">
@@ -1472,32 +1512,33 @@
           <t>半導體業平上櫃</t>
         </is>
       </c>
-      <c r="B31" t="n">
-        <v>8.887751</v>
-      </c>
+      <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
-        <v>7.381023</v>
+        <v>0.887954</v>
       </c>
       <c r="D31" t="n">
-        <v>9.350882</v>
+        <v>0.3785</v>
       </c>
       <c r="E31" t="n">
-        <v>11.343493</v>
+        <v>1.050409</v>
       </c>
       <c r="F31" t="n">
-        <v>16.393483</v>
+        <v>1.595358</v>
       </c>
       <c r="G31" t="n">
-        <v>14.89894</v>
+        <v>1.14472</v>
       </c>
       <c r="H31" t="n">
-        <v>10.04876</v>
+        <v>2.602207</v>
       </c>
       <c r="I31" t="n">
-        <v>11.599118</v>
+        <v>1.534524</v>
       </c>
       <c r="J31" t="n">
-        <v>10.643007</v>
+        <v>0.693098</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.448907</v>
       </c>
     </row>
     <row r="32">
@@ -1506,32 +1547,33 @@
           <t>塑膠工業右上上市</t>
         </is>
       </c>
-      <c r="B32" t="n">
-        <v>20403.743481</v>
-      </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>15904.156976</v>
+        <v>15919.198001</v>
       </c>
       <c r="D32" t="n">
-        <v>18414.422521</v>
+        <v>18456.769403</v>
       </c>
       <c r="E32" t="n">
-        <v>23993.723144</v>
+        <v>24003.311254</v>
       </c>
       <c r="F32" t="n">
-        <v>38398.115906</v>
+        <v>38446.327975</v>
       </c>
       <c r="G32" t="n">
-        <v>17613.517817</v>
+        <v>17643.26033</v>
       </c>
       <c r="H32" t="n">
-        <v>17741.971142</v>
+        <v>17880.73366</v>
       </c>
       <c r="I32" t="n">
-        <v>29521.399492</v>
+        <v>29591.396337</v>
       </c>
       <c r="J32" t="n">
-        <v>37282.689887</v>
+        <v>37329.451211</v>
+      </c>
+      <c r="K32" t="n">
+        <v>51456.204675</v>
       </c>
     </row>
     <row r="33">
@@ -1540,32 +1582,33 @@
           <t>塑膠工業右下上市</t>
         </is>
       </c>
-      <c r="B33" t="n">
-        <v>43.737029</v>
-      </c>
+      <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
-        <v>26.41518</v>
+        <v>20.141526</v>
       </c>
       <c r="D33" t="n">
-        <v>21.393921</v>
+        <v>14.711618</v>
       </c>
       <c r="E33" t="n">
-        <v>39.355459</v>
+        <v>29.039463</v>
       </c>
       <c r="F33" t="n">
-        <v>34.904345</v>
+        <v>37.351237</v>
       </c>
       <c r="G33" t="n">
-        <v>28.912333</v>
+        <v>22.338546</v>
       </c>
       <c r="H33" t="n">
-        <v>15.643569</v>
+        <v>17.20861</v>
       </c>
       <c r="I33" t="n">
-        <v>41.277259</v>
+        <v>43.752679</v>
       </c>
       <c r="J33" t="n">
-        <v>56.90155</v>
+        <v>64.905923</v>
+      </c>
+      <c r="K33" t="n">
+        <v>19.274904</v>
       </c>
     </row>
     <row r="34">
@@ -1574,32 +1617,33 @@
           <t>塑膠工業右下上櫃</t>
         </is>
       </c>
-      <c r="B34" t="n">
-        <v>0.02357733333333333</v>
-      </c>
+      <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
-        <v>0.0225495</v>
+        <v>0.0145135</v>
       </c>
       <c r="D34" t="n">
-        <v>0.043256</v>
+        <v>0.041813</v>
       </c>
       <c r="E34" t="n">
-        <v>0.028786</v>
+        <v>0.028097</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0244545</v>
+        <v>0.0236345</v>
       </c>
       <c r="G34" t="n">
-        <v>0.029761</v>
+        <v>0.029495</v>
       </c>
       <c r="H34" t="n">
-        <v>0.016262</v>
+        <v>0.015748</v>
       </c>
       <c r="I34" t="n">
-        <v>0.0393105</v>
+        <v>0.0384175</v>
       </c>
       <c r="J34" t="n">
-        <v>0.03161</v>
+        <v>0.031051</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.014736</v>
       </c>
     </row>
     <row r="35">
@@ -1608,168 +1652,171 @@
           <t>塑膠工業平上市</t>
         </is>
       </c>
-      <c r="B35" t="n">
-        <v>51.638723</v>
-      </c>
+      <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
-        <v>78.35193200000001</v>
+        <v>69.58456099999999</v>
       </c>
       <c r="D35" t="n">
-        <v>86.148461</v>
+        <v>50.483882</v>
       </c>
       <c r="E35" t="n">
-        <v>105.869253</v>
+        <v>106.597139</v>
       </c>
       <c r="F35" t="n">
-        <v>159.785773</v>
+        <v>109.126812</v>
       </c>
       <c r="G35" t="n">
-        <v>84.431816</v>
+        <v>61.26309</v>
       </c>
       <c r="H35" t="n">
-        <v>244.212676</v>
+        <v>103.885117</v>
       </c>
       <c r="I35" t="n">
-        <v>121.00438</v>
+        <v>48.532115</v>
       </c>
       <c r="J35" t="n">
-        <v>87.37659499999999</v>
+        <v>32.610898</v>
+      </c>
+      <c r="K35" t="n">
+        <v>100.132271</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>居家生活右上上櫃</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>0.0013</v>
-      </c>
+          <t>塑膠工業平上櫃</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>0.004544</v>
+        <v>0.008036</v>
       </c>
       <c r="D36" t="n">
-        <v>0.002171</v>
+        <v>0.001443</v>
       </c>
       <c r="E36" t="n">
-        <v>0.001119</v>
+        <v>0.0006890000000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>0.000906</v>
+        <v>0.00082</v>
       </c>
       <c r="G36" t="n">
-        <v>0.000283</v>
+        <v>0.000266</v>
       </c>
       <c r="H36" t="n">
-        <v>0.001482</v>
+        <v>0.000514</v>
       </c>
       <c r="I36" t="n">
-        <v>0.00025</v>
+        <v>0.000893</v>
       </c>
       <c r="J36" t="n">
-        <v>0.00049</v>
-      </c>
+        <v>0.000559</v>
+      </c>
+      <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>居家生活右下上市</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>37.008341</v>
-      </c>
+          <t>居家生活右上上櫃</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
-        <v>22.73136</v>
+        <v>0.005049</v>
       </c>
       <c r="D37" t="n">
-        <v>20.023105</v>
+        <v>0.002355</v>
       </c>
       <c r="E37" t="n">
-        <v>29.842921</v>
+        <v>0.001119</v>
       </c>
       <c r="F37" t="n">
-        <v>27.947611</v>
+        <v>0.001147</v>
       </c>
       <c r="G37" t="n">
-        <v>20.812951</v>
+        <v>0.000283</v>
       </c>
       <c r="H37" t="n">
-        <v>28.538201</v>
+        <v>0.001482</v>
       </c>
       <c r="I37" t="n">
-        <v>52.805219</v>
+        <v>0.00025</v>
       </c>
       <c r="J37" t="n">
-        <v>33.439189</v>
+        <v>0.00049</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.000346</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>居家生活右下上櫃</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>0.540394</v>
-      </c>
+          <t>居家生活右下上市</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>0.367615</v>
+        <v>110.308606</v>
       </c>
       <c r="D38" t="n">
-        <v>0.55962575</v>
+        <v>84.51718099999999</v>
       </c>
       <c r="E38" t="n">
-        <v>0.3257003333333333</v>
+        <v>225.681646</v>
       </c>
       <c r="F38" t="n">
-        <v>0.3575955</v>
+        <v>157.080028</v>
       </c>
       <c r="G38" t="n">
-        <v>0.2460553333333333</v>
+        <v>89.773652</v>
       </c>
       <c r="H38" t="n">
-        <v>0.312833</v>
+        <v>85.743891</v>
       </c>
       <c r="I38" t="n">
-        <v>0.226244</v>
+        <v>94.456698</v>
       </c>
       <c r="J38" t="n">
-        <v>0.217029</v>
+        <v>102.227215</v>
+      </c>
+      <c r="K38" t="n">
+        <v>136.048295</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>居家生活平上市</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>144.489178</v>
-      </c>
+          <t>居家生活右下上櫃</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
-        <v>87.577246</v>
+        <v>0.366794</v>
       </c>
       <c r="D39" t="n">
-        <v>64.49407600000001</v>
+        <v>0.55957575</v>
       </c>
       <c r="E39" t="n">
-        <v>195.838725</v>
+        <v>0.3252453333333333</v>
       </c>
       <c r="F39" t="n">
-        <v>129.132417</v>
+        <v>0.3573575</v>
       </c>
       <c r="G39" t="n">
-        <v>68.960701</v>
+        <v>0.245567</v>
       </c>
       <c r="H39" t="n">
-        <v>57.20569</v>
+        <v>0.307899</v>
       </c>
       <c r="I39" t="n">
-        <v>41.651479</v>
+        <v>0.226301</v>
       </c>
       <c r="J39" t="n">
-        <v>68.788026</v>
+        <v>0.216663</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.246389</v>
       </c>
     </row>
     <row r="40">
@@ -1778,32 +1825,33 @@
           <t>居家生活平上櫃</t>
         </is>
       </c>
-      <c r="B40" t="n">
-        <v>0.003229</v>
-      </c>
+      <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
-        <v>0.001043</v>
+        <v>0.001359</v>
       </c>
       <c r="D40" t="n">
-        <v>0.00075</v>
+        <v>0.000616</v>
       </c>
       <c r="E40" t="n">
-        <v>0.000768</v>
+        <v>0.001223</v>
       </c>
       <c r="F40" t="n">
-        <v>0.000901</v>
+        <v>0.000898</v>
       </c>
       <c r="G40" t="n">
-        <v>0.004289</v>
+        <v>0.004777333333333333</v>
       </c>
       <c r="H40" t="n">
-        <v>0.003008</v>
+        <v>0.007941999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>0.001225</v>
+        <v>0.001168</v>
       </c>
       <c r="J40" t="n">
-        <v>0.001313</v>
+        <v>0.001679</v>
+      </c>
+      <c r="K40" t="n">
+        <v>5.3e-05</v>
       </c>
     </row>
     <row r="41">
@@ -1812,32 +1860,33 @@
           <t>建材營造右上上市</t>
         </is>
       </c>
-      <c r="B41" t="n">
-        <v>1311.540773</v>
-      </c>
+      <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
-        <v>142.096299</v>
+        <v>102.798544</v>
       </c>
       <c r="D41" t="n">
-        <v>149.45803</v>
+        <v>111.02575</v>
       </c>
       <c r="E41" t="n">
-        <v>124.981634</v>
+        <v>76.98213</v>
       </c>
       <c r="F41" t="n">
-        <v>201.107528</v>
+        <v>130.417564</v>
       </c>
       <c r="G41" t="n">
-        <v>147.807027</v>
+        <v>87.222176</v>
       </c>
       <c r="H41" t="n">
-        <v>164.04647</v>
+        <v>110.783978</v>
       </c>
       <c r="I41" t="n">
-        <v>186.246527</v>
+        <v>152.611407</v>
       </c>
       <c r="J41" t="n">
-        <v>142.771721</v>
+        <v>119.741025</v>
+      </c>
+      <c r="K41" t="n">
+        <v>85.81657199999999</v>
       </c>
     </row>
     <row r="42">
@@ -1846,32 +1895,33 @@
           <t>建材營造右上上櫃</t>
         </is>
       </c>
-      <c r="B42" t="n">
-        <v>0.008525</v>
-      </c>
+      <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>0.008455000000000001</v>
+        <v>0.015812</v>
       </c>
       <c r="D42" t="n">
-        <v>0.007346</v>
+        <v>0.015308</v>
       </c>
       <c r="E42" t="n">
-        <v>0.012669</v>
+        <v>0.012671</v>
       </c>
       <c r="F42" t="n">
-        <v>0.015847</v>
+        <v>0.016945</v>
       </c>
       <c r="G42" t="n">
-        <v>0.020326</v>
+        <v>0.022928</v>
       </c>
       <c r="H42" t="n">
-        <v>0.01373125</v>
+        <v>0.014092</v>
       </c>
       <c r="I42" t="n">
-        <v>0.007236</v>
+        <v>0.005928</v>
       </c>
       <c r="J42" t="n">
-        <v>0.006054</v>
+        <v>0.0045</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.003917</v>
       </c>
     </row>
     <row r="43">
@@ -1881,31 +1931,34 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>457.357728</v>
+        <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>597.730444</v>
+        <v>2483.378532</v>
       </c>
       <c r="D43" t="n">
-        <v>428.069404</v>
+        <v>929.73395</v>
       </c>
       <c r="E43" t="n">
-        <v>1042.3501</v>
+        <v>1045.564463</v>
       </c>
       <c r="F43" t="n">
-        <v>1117.33762</v>
+        <v>1120.578741</v>
       </c>
       <c r="G43" t="n">
-        <v>829.348561</v>
+        <v>832.507251</v>
       </c>
       <c r="H43" t="n">
-        <v>935.330247</v>
+        <v>938.6619030000001</v>
       </c>
       <c r="I43" t="n">
-        <v>1437.091697</v>
+        <v>1443.73629</v>
       </c>
       <c r="J43" t="n">
-        <v>904.735288</v>
+        <v>917.500231</v>
+      </c>
+      <c r="K43" t="n">
+        <v>825.253692</v>
       </c>
     </row>
     <row r="44">
@@ -1914,32 +1967,33 @@
           <t>建材營造右下上櫃</t>
         </is>
       </c>
-      <c r="B44" t="n">
-        <v>0.108894</v>
-      </c>
+      <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>0.076583</v>
+        <v>0.098083</v>
       </c>
       <c r="D44" t="n">
-        <v>0.06238</v>
+        <v>0.075102</v>
       </c>
       <c r="E44" t="n">
-        <v>0.054294</v>
+        <v>0.060285</v>
       </c>
       <c r="F44" t="n">
-        <v>0.050976</v>
+        <v>0.058978</v>
       </c>
       <c r="G44" t="n">
-        <v>0.03979466666666667</v>
+        <v>0.04913266666666666</v>
       </c>
       <c r="H44" t="n">
-        <v>0.044147</v>
+        <v>0.064065</v>
       </c>
       <c r="I44" t="n">
-        <v>0.110113</v>
+        <v>0.101432</v>
       </c>
       <c r="J44" t="n">
-        <v>0.051935</v>
+        <v>0.046603</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.05454366666666666</v>
       </c>
     </row>
     <row r="45">
@@ -1948,32 +2002,33 @@
           <t>建材營造平上市</t>
         </is>
       </c>
-      <c r="B45" t="n">
-        <v>105.337666</v>
-      </c>
+      <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
-        <v>2056.975727</v>
+        <v>209.87792</v>
       </c>
       <c r="D45" t="n">
-        <v>581.465077</v>
+        <v>117.547258</v>
       </c>
       <c r="E45" t="n">
-        <v>36.673821</v>
+        <v>79.524036</v>
       </c>
       <c r="F45" t="n">
-        <v>53.262782</v>
+        <v>119.412784</v>
       </c>
       <c r="G45" t="n">
-        <v>166.435499</v>
+        <v>223.589286</v>
       </c>
       <c r="H45" t="n">
-        <v>76.116998</v>
+        <v>125.055751</v>
       </c>
       <c r="I45" t="n">
-        <v>121.778049</v>
+        <v>148.370581</v>
       </c>
       <c r="J45" t="n">
-        <v>63.764067</v>
+        <v>73.41445</v>
+      </c>
+      <c r="K45" t="n">
+        <v>276.038861</v>
       </c>
     </row>
     <row r="46">
@@ -1982,32 +2037,33 @@
           <t>建材營造平上櫃</t>
         </is>
       </c>
-      <c r="B46" t="n">
-        <v>0.036039</v>
-      </c>
+      <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>0.032516</v>
+        <v>0.003659</v>
       </c>
       <c r="D46" t="n">
-        <v>0.022415</v>
+        <v>0.001731</v>
       </c>
       <c r="E46" t="n">
-        <v>0.010698</v>
+        <v>0.004705</v>
       </c>
       <c r="F46" t="n">
-        <v>0.013407</v>
+        <v>0.004307</v>
       </c>
       <c r="G46" t="n">
-        <v>0.026788</v>
+        <v>0.014848</v>
       </c>
       <c r="H46" t="n">
-        <v>0.023503</v>
+        <v>0.00322425</v>
       </c>
       <c r="I46" t="n">
-        <v>0.009675</v>
+        <v>0.019664</v>
       </c>
       <c r="J46" t="n">
-        <v>0.009086</v>
+        <v>0.015972</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.036654</v>
       </c>
     </row>
     <row r="47">
@@ -2016,33 +2072,34 @@
           <t>數位雲端右上上市</t>
         </is>
       </c>
-      <c r="B47" t="n">
-        <v>524.292661</v>
-      </c>
+      <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
-        <v>232.139303</v>
+        <v>229.721265</v>
       </c>
       <c r="D47" t="n">
-        <v>212.845719</v>
+        <v>201.553671</v>
       </c>
       <c r="E47" t="n">
-        <v>131.591225</v>
+        <v>123.789134</v>
       </c>
       <c r="F47" t="n">
-        <v>273.926956</v>
+        <v>88.29381600000001</v>
       </c>
       <c r="G47" t="n">
-        <v>79.373986</v>
+        <v>61.638603</v>
       </c>
       <c r="H47" t="n">
-        <v>81.745813</v>
+        <v>71.518085</v>
       </c>
       <c r="I47" t="n">
-        <v>65.84591899999999</v>
+        <v>62.462198</v>
       </c>
       <c r="J47" t="n">
         <v>48.754718</v>
       </c>
+      <c r="K47" t="n">
+        <v>76.16837200000001</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
@@ -2050,32 +2107,33 @@
           <t>數位雲端右上上櫃</t>
         </is>
       </c>
-      <c r="B48" t="n">
-        <v>0.324899</v>
-      </c>
+      <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
-        <v>0.506584</v>
+        <v>0.507046</v>
       </c>
       <c r="D48" t="n">
-        <v>0.218607</v>
+        <v>0.223421</v>
       </c>
       <c r="E48" t="n">
-        <v>0.179389</v>
+        <v>0.166084</v>
       </c>
       <c r="F48" t="n">
-        <v>0.296095</v>
+        <v>0.244618</v>
       </c>
       <c r="G48" t="n">
-        <v>0.1936893333333334</v>
+        <v>0.1803</v>
       </c>
       <c r="H48" t="n">
-        <v>0.121387</v>
+        <v>0.115223</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1898</v>
+        <v>0.19295</v>
       </c>
       <c r="J48" t="n">
-        <v>0.209382</v>
+        <v>0.212665</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0.429491</v>
       </c>
     </row>
     <row r="49">
@@ -2084,32 +2142,33 @@
           <t>數位雲端右下上市</t>
         </is>
       </c>
-      <c r="B49" t="n">
-        <v>25.923961</v>
-      </c>
+      <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
-        <v>25.247635</v>
+        <v>53.080761</v>
       </c>
       <c r="D49" t="n">
-        <v>22.50859</v>
+        <v>82.262708</v>
       </c>
       <c r="E49" t="n">
-        <v>28.703929</v>
+        <v>65.905101</v>
       </c>
       <c r="F49" t="n">
-        <v>24.480949</v>
+        <v>58.653519</v>
       </c>
       <c r="G49" t="n">
-        <v>28.726985</v>
+        <v>58.105474</v>
       </c>
       <c r="H49" t="n">
-        <v>38.646655</v>
+        <v>50.751367</v>
       </c>
       <c r="I49" t="n">
-        <v>102.767056</v>
+        <v>106.150777</v>
       </c>
       <c r="J49" t="n">
-        <v>71.747041</v>
+        <v>106.566545</v>
+      </c>
+      <c r="K49" t="n">
+        <v>212.804395</v>
       </c>
     </row>
     <row r="50">
@@ -2118,32 +2177,33 @@
           <t>數位雲端右下上櫃</t>
         </is>
       </c>
-      <c r="B50" t="n">
-        <v>0.205242</v>
-      </c>
+      <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
-        <v>0.179853</v>
+        <v>0.179874</v>
       </c>
       <c r="D50" t="n">
-        <v>0.09177299999999999</v>
+        <v>0.205574</v>
       </c>
       <c r="E50" t="n">
-        <v>0.11663</v>
+        <v>0.267687</v>
       </c>
       <c r="F50" t="n">
-        <v>0.115867</v>
+        <v>0.205313</v>
       </c>
       <c r="G50" t="n">
-        <v>0.173237</v>
+        <v>0.232625</v>
       </c>
       <c r="H50" t="n">
-        <v>0.181664</v>
+        <v>0.210537</v>
       </c>
       <c r="I50" t="n">
-        <v>0.20589275</v>
+        <v>0.25565475</v>
       </c>
       <c r="J50" t="n">
-        <v>0.1089243333333333</v>
+        <v>0.1826113333333333</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0.1052481666666667</v>
       </c>
     </row>
     <row r="51">
@@ -2152,32 +2212,33 @@
           <t>數位雲端平上市</t>
         </is>
       </c>
-      <c r="B51" t="n">
-        <v>189.304916</v>
-      </c>
+      <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
-        <v>142.973795</v>
+        <v>117.558707</v>
       </c>
       <c r="D51" t="n">
-        <v>117.038726</v>
+        <v>68.576656</v>
       </c>
       <c r="E51" t="n">
-        <v>117.851939</v>
+        <v>88.45285800000001</v>
       </c>
       <c r="F51" t="n">
-        <v>132.340216</v>
+        <v>283.800786</v>
       </c>
       <c r="G51" t="n">
-        <v>83.747483</v>
+        <v>72.104377</v>
       </c>
       <c r="H51" t="n">
-        <v>60.660386</v>
+        <v>58.783402</v>
       </c>
       <c r="I51" t="n">
         <v>133.565777</v>
       </c>
       <c r="J51" t="n">
-        <v>100.996203</v>
+        <v>66.176699</v>
+      </c>
+      <c r="K51" t="n">
+        <v>74.896503</v>
       </c>
     </row>
     <row r="52">
@@ -2186,32 +2247,31 @@
           <t>數位雲端平上櫃</t>
         </is>
       </c>
-      <c r="B52" t="n">
-        <v>0.001018333333333333</v>
-      </c>
-      <c r="C52" t="n">
-        <v>0.000483</v>
-      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="n">
-        <v>0.118701</v>
+        <v>8.6e-05</v>
       </c>
       <c r="E52" t="n">
-        <v>0.152504</v>
+        <v>0.014752</v>
       </c>
       <c r="F52" t="n">
-        <v>0.093373</v>
+        <v>0.055404</v>
       </c>
       <c r="G52" t="n">
-        <v>0.074028</v>
+        <v>0.02802933333333334</v>
       </c>
       <c r="H52" t="n">
-        <v>0.036497</v>
+        <v>0.013788</v>
       </c>
       <c r="I52" t="n">
-        <v>0.059754</v>
+        <v>0.006842</v>
       </c>
       <c r="J52" t="n">
-        <v>0.07814400000000001</v>
+        <v>0.001174</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0.000633</v>
       </c>
     </row>
     <row r="53">
@@ -2222,12 +2282,8 @@
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr"/>
-      <c r="D53" t="n">
-        <v>4.373877</v>
-      </c>
-      <c r="E53" t="n">
-        <v>2.718566</v>
-      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="n">
         <v>1.632479</v>
       </c>
@@ -2241,7 +2297,10 @@
         <v>1.087361</v>
       </c>
       <c r="J53" t="n">
-        <v>1.167006</v>
+        <v>0.002388</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0.000195</v>
       </c>
     </row>
     <row r="54">
@@ -2251,31 +2310,34 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.057446</v>
+        <v>0</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0641065</v>
+        <v>0.6455865</v>
       </c>
       <c r="D54" t="n">
-        <v>0.0408735</v>
+        <v>0.0401525</v>
       </c>
       <c r="E54" t="n">
-        <v>0.06168375</v>
+        <v>0.06167775</v>
       </c>
       <c r="F54" t="n">
-        <v>0.073361</v>
+        <v>0.069564</v>
       </c>
       <c r="G54" t="n">
-        <v>0.049902</v>
+        <v>0.05069</v>
       </c>
       <c r="H54" t="n">
-        <v>0.05330483333333334</v>
+        <v>0.04797983333333333</v>
       </c>
       <c r="I54" t="n">
-        <v>0.072182</v>
+        <v>0.063098</v>
       </c>
       <c r="J54" t="n">
-        <v>0.06181725</v>
+        <v>0.05676425</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0.070881</v>
       </c>
     </row>
     <row r="55">
@@ -2284,29 +2346,34 @@
           <t>文化創意業平上櫃</t>
         </is>
       </c>
-      <c r="B55" t="n">
-        <v>0.853862</v>
-      </c>
+      <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
-        <v>0.596025</v>
+        <v>0.00653</v>
       </c>
       <c r="D55" t="n">
-        <v>0.008586999999999999</v>
+        <v>4.376937</v>
       </c>
       <c r="E55" t="n">
-        <v>0.003479</v>
+        <v>2.718797</v>
       </c>
       <c r="F55" t="n">
-        <v>0.001894</v>
+        <v>0.001631</v>
       </c>
       <c r="G55" t="n">
-        <v>0.011794</v>
+        <v>0.007647</v>
       </c>
       <c r="H55" t="n">
-        <v>0.004545</v>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+        <v>0.003466</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.000139</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1.165108</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0.49153</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
@@ -2314,32 +2381,33 @@
           <t>橡膠工業右上上市</t>
         </is>
       </c>
-      <c r="B56" t="n">
-        <v>74.300687</v>
-      </c>
+      <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>380.284936</v>
+        <v>372.329556</v>
       </c>
       <c r="D56" t="n">
-        <v>59.31454</v>
+        <v>53.153067</v>
       </c>
       <c r="E56" t="n">
-        <v>91.80184300000001</v>
+        <v>89.79392199999999</v>
       </c>
       <c r="F56" t="n">
-        <v>91.7514</v>
+        <v>90.27554600000001</v>
       </c>
       <c r="G56" t="n">
-        <v>64.15203700000001</v>
+        <v>63.309303</v>
       </c>
       <c r="H56" t="n">
-        <v>159.079605</v>
+        <v>156.840719</v>
       </c>
       <c r="I56" t="n">
-        <v>130.843053</v>
+        <v>128.352831</v>
       </c>
       <c r="J56" t="n">
-        <v>111.431133</v>
+        <v>108.687858</v>
+      </c>
+      <c r="K56" t="n">
+        <v>286.4072</v>
       </c>
     </row>
     <row r="57">
@@ -2348,11 +2416,9 @@
           <t>橡膠工業右下上市</t>
         </is>
       </c>
-      <c r="B57" t="n">
-        <v>234.544684</v>
-      </c>
+      <c r="B57" t="inlineStr"/>
       <c r="C57" t="n">
-        <v>147.169752</v>
+        <v>150.43609</v>
       </c>
       <c r="D57" t="n">
         <v>116.233975</v>
@@ -2361,7 +2427,7 @@
         <v>165.105133</v>
       </c>
       <c r="F57" t="n">
-        <v>65.736844</v>
+        <v>219.105697</v>
       </c>
       <c r="G57" t="n">
         <v>172.168685</v>
@@ -2375,6 +2441,9 @@
       <c r="J57" t="n">
         <v>137.69556</v>
       </c>
+      <c r="K57" t="n">
+        <v>185.673611</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
@@ -2382,30 +2451,33 @@
           <t>橡膠工業平上市</t>
         </is>
       </c>
-      <c r="B58" t="n">
-        <v>0.448149</v>
-      </c>
-      <c r="C58" t="inlineStr"/>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="n">
+        <v>4.689042</v>
+      </c>
       <c r="D58" t="n">
-        <v>110.326311</v>
+        <v>116.487784</v>
       </c>
       <c r="E58" t="n">
-        <v>67.582936</v>
+        <v>69.590857</v>
       </c>
       <c r="F58" t="n">
-        <v>210.676112</v>
+        <v>58.783113</v>
       </c>
       <c r="G58" t="n">
-        <v>34.688359</v>
+        <v>35.531093</v>
       </c>
       <c r="H58" t="n">
-        <v>20.422541</v>
+        <v>22.661427</v>
       </c>
       <c r="I58" t="n">
-        <v>54.74745</v>
+        <v>57.237672</v>
       </c>
       <c r="J58" t="n">
-        <v>34.823483</v>
+        <v>37.566758</v>
+      </c>
+      <c r="K58" t="n">
+        <v>1.604544</v>
       </c>
     </row>
     <row r="59">
@@ -2416,7 +2488,7 @@
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="n">
-        <v>3742.980955</v>
+        <v>3336.742112</v>
       </c>
       <c r="D59" t="n">
         <v>995.089243</v>
@@ -2425,7 +2497,7 @@
         <v>796.559063</v>
       </c>
       <c r="F59" t="n">
-        <v>2967.114292</v>
+        <v>2745.271403</v>
       </c>
       <c r="G59" t="n">
         <v>1412.587301</v>
@@ -2433,12 +2505,13 @@
       <c r="H59" t="n">
         <v>641.982484</v>
       </c>
-      <c r="I59" t="n">
-        <v>900.0369920000001</v>
-      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="n">
         <v>674.559882</v>
       </c>
+      <c r="K59" t="n">
+        <v>632.455261</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
@@ -2446,32 +2519,33 @@
           <t>水泥工業右下上市</t>
         </is>
       </c>
-      <c r="B60" t="n">
-        <v>23.131303</v>
-      </c>
+      <c r="B60" t="inlineStr"/>
       <c r="C60" t="n">
         <v>27.97068</v>
       </c>
       <c r="D60" t="n">
-        <v>23.890866</v>
+        <v>289.484283</v>
       </c>
       <c r="E60" t="n">
-        <v>36.108083</v>
+        <v>375.398434</v>
       </c>
       <c r="F60" t="n">
-        <v>25.533089</v>
+        <v>247.375978</v>
       </c>
       <c r="G60" t="n">
-        <v>24.011971</v>
+        <v>444.795927</v>
       </c>
       <c r="H60" t="n">
-        <v>17.212754</v>
+        <v>191.480706</v>
       </c>
       <c r="I60" t="n">
-        <v>19.640078</v>
+        <v>201.274146</v>
       </c>
       <c r="J60" t="n">
-        <v>20.295194</v>
+        <v>265.605141</v>
+      </c>
+      <c r="K60" t="n">
+        <v>18.918191</v>
       </c>
     </row>
     <row r="61">
@@ -2480,28 +2554,21 @@
           <t>水泥工業平上市</t>
         </is>
       </c>
-      <c r="B61" t="n">
-        <v>949.079145</v>
-      </c>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="n">
-        <v>265.593417</v>
-      </c>
-      <c r="E61" t="n">
-        <v>339.290351</v>
-      </c>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" t="n">
+        <v>406.238843</v>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
-      <c r="G61" t="n">
-        <v>420.783956</v>
-      </c>
-      <c r="H61" t="n">
-        <v>174.267952</v>
-      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
-        <v>181.634068</v>
-      </c>
-      <c r="J61" t="n">
-        <v>245.309947</v>
+        <v>900.0369920000001</v>
+      </c>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="n">
+        <v>205.285898</v>
       </c>
     </row>
     <row r="62">
@@ -2510,32 +2577,33 @@
           <t>汽車工業右上上市</t>
         </is>
       </c>
-      <c r="B62" t="n">
-        <v>806.547029</v>
-      </c>
+      <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>1669.721101</v>
+        <v>1667.061733</v>
       </c>
       <c r="D62" t="n">
-        <v>1001.153987</v>
+        <v>986.9098729999999</v>
       </c>
       <c r="E62" t="n">
-        <v>1376.904598</v>
+        <v>1350.231246</v>
       </c>
       <c r="F62" t="n">
-        <v>2530.817868</v>
+        <v>2481.360539</v>
       </c>
       <c r="G62" t="n">
-        <v>894.608758</v>
+        <v>875.090538</v>
       </c>
       <c r="H62" t="n">
-        <v>1258.292474</v>
+        <v>1240.896853</v>
       </c>
       <c r="I62" t="n">
-        <v>2023.334911</v>
+        <v>1986.204073</v>
       </c>
       <c r="J62" t="n">
-        <v>2376.922796</v>
+        <v>2334.527893</v>
+      </c>
+      <c r="K62" t="n">
+        <v>2380.995649</v>
       </c>
     </row>
     <row r="63">
@@ -2544,32 +2612,33 @@
           <t>汽車工業右下上市</t>
         </is>
       </c>
-      <c r="B63" t="n">
-        <v>420.177898</v>
-      </c>
+      <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
-        <v>295.1171815</v>
+        <v>450.3842975</v>
       </c>
       <c r="D63" t="n">
-        <v>270.273582</v>
+        <v>421.929744</v>
       </c>
       <c r="E63" t="n">
-        <v>464.299762</v>
+        <v>483.645075</v>
       </c>
       <c r="F63" t="n">
-        <v>412.71605</v>
+        <v>643.883054</v>
       </c>
       <c r="G63" t="n">
-        <v>323.712412</v>
+        <v>489.08889</v>
       </c>
       <c r="H63" t="n">
-        <v>377.708464</v>
+        <v>679.042829</v>
       </c>
       <c r="I63" t="n">
-        <v>620.992344</v>
+        <v>762.597544</v>
       </c>
       <c r="J63" t="n">
-        <v>714.964128</v>
+        <v>824.872317</v>
+      </c>
+      <c r="K63" t="n">
+        <v>809.163751</v>
       </c>
     </row>
     <row r="64">
@@ -2578,32 +2647,33 @@
           <t>汽車工業平上市</t>
         </is>
       </c>
-      <c r="B64" t="n">
-        <v>269.349393</v>
-      </c>
+      <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
-        <v>199.842169</v>
+        <v>47.234421</v>
       </c>
       <c r="D64" t="n">
-        <v>208.878708</v>
+        <v>71.46666</v>
       </c>
       <c r="E64" t="n">
-        <v>198.14848</v>
+        <v>205.476519</v>
       </c>
       <c r="F64" t="n">
-        <v>284.679117</v>
+        <v>102.969442</v>
       </c>
       <c r="G64" t="n">
-        <v>244.890534</v>
+        <v>99.032276</v>
       </c>
       <c r="H64" t="n">
-        <v>391.432299</v>
+        <v>107.493555</v>
       </c>
       <c r="I64" t="n">
-        <v>183.768815</v>
+        <v>79.294453</v>
       </c>
       <c r="J64" t="n">
-        <v>116.196973</v>
+        <v>48.683687</v>
+      </c>
+      <c r="K64" t="n">
+        <v>245.669527</v>
       </c>
     </row>
     <row r="65">
@@ -2612,32 +2682,33 @@
           <t>油電燃氣業右上上市</t>
         </is>
       </c>
-      <c r="B65" t="n">
-        <v>1563.610846</v>
-      </c>
+      <c r="B65" t="inlineStr"/>
       <c r="C65" t="n">
-        <v>1120.951175</v>
+        <v>1207.454396</v>
       </c>
       <c r="D65" t="n">
         <v>1016.909933</v>
       </c>
       <c r="E65" t="n">
-        <v>3827.737724</v>
+        <v>3902.406555</v>
       </c>
       <c r="F65" t="n">
-        <v>3768.070051</v>
+        <v>3768.592343</v>
       </c>
       <c r="G65" t="n">
-        <v>2657.525003</v>
+        <v>2658.038261</v>
       </c>
       <c r="H65" t="n">
-        <v>3632.530573</v>
+        <v>3633.52439</v>
       </c>
       <c r="I65" t="n">
-        <v>2115.763698</v>
+        <v>2116.46865</v>
       </c>
       <c r="J65" t="n">
-        <v>2490.682467</v>
+        <v>2492.209885</v>
+      </c>
+      <c r="K65" t="n">
+        <v>3813.334009</v>
       </c>
     </row>
     <row r="66">
@@ -2646,9 +2717,7 @@
           <t>油電燃氣業右下上市</t>
         </is>
       </c>
-      <c r="B66" t="n">
-        <v>4.976994</v>
-      </c>
+      <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
         <v>4.671305</v>
       </c>
@@ -2671,7 +2740,10 @@
         <v>6.653482</v>
       </c>
       <c r="J66" t="n">
-        <v>13.578305</v>
+        <v>14.371924</v>
+      </c>
+      <c r="K66" t="n">
+        <v>7.965361</v>
       </c>
     </row>
     <row r="67">
@@ -2680,32 +2752,33 @@
           <t>油電燃氣業右下上櫃</t>
         </is>
       </c>
-      <c r="B67" t="n">
-        <v>0.004074</v>
-      </c>
+      <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
-        <v>0.00622</v>
+        <v>0.010957</v>
       </c>
       <c r="D67" t="n">
-        <v>0.003165</v>
+        <v>0.015956</v>
       </c>
       <c r="E67" t="n">
-        <v>0.003294</v>
+        <v>0.007131</v>
       </c>
       <c r="F67" t="n">
-        <v>0.002846</v>
+        <v>0.013587</v>
       </c>
       <c r="G67" t="n">
-        <v>0.00394</v>
+        <v>0.004641</v>
       </c>
       <c r="H67" t="n">
-        <v>0.0022</v>
+        <v>0.003086</v>
       </c>
       <c r="I67" t="n">
-        <v>0.007126</v>
+        <v>0.007185</v>
       </c>
       <c r="J67" t="n">
-        <v>0.005304</v>
+        <v>0.017316</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0.005177</v>
       </c>
     </row>
     <row r="68">
@@ -2714,1511 +2787,1542 @@
           <t>油電燃氣業平上市</t>
         </is>
       </c>
-      <c r="B68" t="n">
-        <v>1.06129</v>
-      </c>
+      <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>88.001926</v>
+        <v>1.498705</v>
       </c>
       <c r="D68" t="n">
         <v>0.416998</v>
       </c>
       <c r="E68" t="n">
-        <v>75.293695</v>
+        <v>0.624864</v>
       </c>
       <c r="F68" t="n">
-        <v>1.0206</v>
+        <v>0.498308</v>
       </c>
       <c r="G68" t="n">
-        <v>0.687299</v>
-      </c>
-      <c r="H68" t="n">
-        <v>0.993817</v>
-      </c>
-      <c r="I68" t="n">
-        <v>0.704952</v>
-      </c>
+        <v>0.174041</v>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
       <c r="J68" t="n">
-        <v>3.028703</v>
-      </c>
+        <v>0.707666</v>
+      </c>
+      <c r="K68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業平上櫃</t>
-        </is>
-      </c>
-      <c r="B69" t="n">
-        <v>0.00202</v>
-      </c>
+          <t>玻璃陶瓷右上上市</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
-        <v>0.004737</v>
+        <v>1239.984105</v>
       </c>
       <c r="D69" t="n">
-        <v>0.012791</v>
+        <v>800.372672</v>
       </c>
       <c r="E69" t="n">
-        <v>0.003837</v>
+        <v>1852.668564</v>
       </c>
       <c r="F69" t="n">
-        <v>0.010741</v>
+        <v>2390.876361</v>
       </c>
       <c r="G69" t="n">
-        <v>0.000701</v>
+        <v>1209.96481</v>
       </c>
       <c r="H69" t="n">
-        <v>0.000886</v>
+        <v>1288.698829</v>
       </c>
       <c r="I69" t="n">
-        <v>5.9e-05</v>
+        <v>1646.975672</v>
       </c>
       <c r="J69" t="n">
-        <v>0.012012</v>
+        <v>1582.051215</v>
+      </c>
+      <c r="K69" t="n">
+        <v>7133.346991</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷右上上市</t>
-        </is>
-      </c>
-      <c r="B70" t="n">
-        <v>180.249203</v>
-      </c>
+          <t>玻璃陶瓷右下上市</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
-        <v>308.760818</v>
+        <v>0.469083</v>
       </c>
       <c r="D70" t="n">
-        <v>336.767867</v>
+        <v>0.521244</v>
       </c>
       <c r="E70" t="n">
-        <v>1394.507219</v>
+        <v>0.500364</v>
       </c>
       <c r="F70" t="n">
-        <v>980.572891</v>
+        <v>1.209878</v>
       </c>
       <c r="G70" t="n">
-        <v>297.549161</v>
+        <v>2.726514</v>
       </c>
       <c r="H70" t="n">
-        <v>572.510755</v>
+        <v>0.8914299999999999</v>
       </c>
       <c r="I70" t="n">
-        <v>255.941381</v>
+        <v>1.117833</v>
       </c>
       <c r="J70" t="n">
-        <v>148.635317</v>
+        <v>2.289033</v>
+      </c>
+      <c r="K70" t="n">
+        <v>2.318782</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷右下上市</t>
-        </is>
-      </c>
-      <c r="B71" t="n">
-        <v>1.292641</v>
-      </c>
-      <c r="C71" t="n">
-        <v>0.469083</v>
-      </c>
+          <t>玻璃陶瓷平上市</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr"/>
       <c r="D71" t="n">
-        <v>0.521244</v>
+        <v>0.744384</v>
       </c>
       <c r="E71" t="n">
-        <v>0.500364</v>
+        <v>1.920693</v>
       </c>
       <c r="F71" t="n">
-        <v>1.209878</v>
+        <v>1.202745</v>
       </c>
       <c r="G71" t="n">
-        <v>2.726514</v>
+        <v>0.680389</v>
       </c>
       <c r="H71" t="n">
-        <v>0.8914299999999999</v>
+        <v>0.440229</v>
       </c>
       <c r="I71" t="n">
-        <v>1.117833</v>
+        <v>0.617168</v>
       </c>
       <c r="J71" t="n">
-        <v>2.289033</v>
+        <v>0.927306</v>
+      </c>
+      <c r="K71" t="n">
+        <v>2.054035</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷平上市</t>
-        </is>
-      </c>
-      <c r="B72" t="n">
-        <v>1593.900291</v>
-      </c>
+          <t>生技醫療業右上上市</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
       <c r="C72" t="n">
-        <v>931.223287</v>
+        <v>5953.466659</v>
       </c>
       <c r="D72" t="n">
-        <v>464.349189</v>
+        <v>3086.680274</v>
       </c>
       <c r="E72" t="n">
-        <v>460.082038</v>
+        <v>3551.562761</v>
       </c>
       <c r="F72" t="n">
-        <v>1411.506215</v>
+        <v>4179.722896</v>
       </c>
       <c r="G72" t="n">
-        <v>913.096038</v>
+        <v>6362.124208</v>
       </c>
       <c r="H72" t="n">
-        <v>716.628303</v>
+        <v>2847.010004</v>
       </c>
       <c r="I72" t="n">
-        <v>1391.651459</v>
+        <v>3330.562763</v>
       </c>
       <c r="J72" t="n">
-        <v>1434.343204</v>
+        <v>2953.448239</v>
+      </c>
+      <c r="K72" t="n">
+        <v>2975.550287</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右上上市</t>
-        </is>
-      </c>
-      <c r="B73" t="n">
-        <v>6022.66941</v>
-      </c>
+          <t>生技醫療業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
       <c r="C73" t="n">
-        <v>5969.716865</v>
+        <v>0.8600989999999999</v>
       </c>
       <c r="D73" t="n">
-        <v>4097.608961</v>
+        <v>0.669752</v>
       </c>
       <c r="E73" t="n">
-        <v>3867.64655</v>
+        <v>0.773203</v>
       </c>
       <c r="F73" t="n">
-        <v>4196.073425</v>
+        <v>1.585432</v>
       </c>
       <c r="G73" t="n">
-        <v>6374.150305</v>
+        <v>1.823919</v>
       </c>
       <c r="H73" t="n">
-        <v>2873.532273</v>
+        <v>1.303966</v>
       </c>
       <c r="I73" t="n">
-        <v>3358.834664</v>
+        <v>1.141856</v>
       </c>
       <c r="J73" t="n">
-        <v>3005.278808</v>
+        <v>1.251938</v>
+      </c>
+      <c r="K73" t="n">
+        <v>1.146116</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右上上櫃</t>
+          <t>生技醫療業右下上市</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1.27838</v>
+        <v>0</v>
       </c>
       <c r="C74" t="n">
-        <v>0.974698</v>
+        <v>1221.898304</v>
       </c>
       <c r="D74" t="n">
-        <v>0.796296</v>
+        <v>932.288263</v>
       </c>
       <c r="E74" t="n">
-        <v>0.814196</v>
+        <v>879.903049</v>
       </c>
       <c r="F74" t="n">
-        <v>1.607912</v>
+        <v>1066.893617</v>
       </c>
       <c r="G74" t="n">
-        <v>1.910936</v>
+        <v>929.41603</v>
       </c>
       <c r="H74" t="n">
-        <v>1.355821</v>
+        <v>1420.761809</v>
       </c>
       <c r="I74" t="n">
-        <v>1.149426</v>
+        <v>950.170583</v>
       </c>
       <c r="J74" t="n">
-        <v>1.307722</v>
+        <v>788.7546620000001</v>
+      </c>
+      <c r="K74" t="n">
+        <v>1005.774936</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右下上市</t>
-        </is>
-      </c>
-      <c r="B75" t="n">
-        <v>1420.340333</v>
-      </c>
+          <t>生技醫療業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
       <c r="C75" t="n">
-        <v>790.299203</v>
+        <v>0.35046</v>
       </c>
       <c r="D75" t="n">
-        <v>882.589772</v>
+        <v>0.3230690833333333</v>
       </c>
       <c r="E75" t="n">
-        <v>831.72542</v>
+        <v>0.3475283333333333</v>
       </c>
       <c r="F75" t="n">
-        <v>987.591167</v>
+        <v>0.4610666666666667</v>
       </c>
       <c r="G75" t="n">
-        <v>570.880037</v>
+        <v>0.4453741666666667</v>
       </c>
       <c r="H75" t="n">
-        <v>1361.174952</v>
+        <v>0.4118865</v>
       </c>
       <c r="I75" t="n">
-        <v>952.7902769999999</v>
+        <v>0.7703614166666666</v>
       </c>
       <c r="J75" t="n">
-        <v>783.46231</v>
+        <v>0.54641775</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0.443528</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B76" t="n">
-        <v>0.40359625</v>
-      </c>
+          <t>生技醫療業平上市</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
-        <v>0.345726</v>
+        <v>44.7846</v>
       </c>
       <c r="D76" t="n">
-        <v>0.3164330833333333</v>
+        <v>1040.041374</v>
       </c>
       <c r="E76" t="n">
-        <v>0.3441363333333333</v>
+        <v>381.292726</v>
       </c>
       <c r="F76" t="n">
-        <v>0.3782826666666667</v>
+        <v>71.53824299999999</v>
       </c>
       <c r="G76" t="n">
-        <v>0.3214551666666667</v>
+        <v>37.690678</v>
       </c>
       <c r="H76" t="n">
-        <v>0.3575395</v>
+        <v>86.67742800000001</v>
       </c>
       <c r="I76" t="n">
-        <v>0.7056954166666666</v>
+        <v>90.371803</v>
       </c>
       <c r="J76" t="n">
-        <v>0.512689</v>
+        <v>92.51034799999999</v>
+      </c>
+      <c r="K76" t="n">
+        <v>45.753829</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業平上市</t>
-        </is>
-      </c>
-      <c r="B77" t="n">
-        <v>52.616483</v>
-      </c>
+          <t>生技醫療業平上櫃</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
       <c r="C77" t="n">
-        <v>466.542454</v>
+        <v>0.275593</v>
       </c>
       <c r="D77" t="n">
-        <v>85.77894999999999</v>
+        <v>0.293708</v>
       </c>
       <c r="E77" t="n">
-        <v>121.884585</v>
+        <v>0.104061</v>
       </c>
       <c r="F77" t="n">
-        <v>149.655613</v>
+        <v>0.121558</v>
       </c>
       <c r="G77" t="n">
-        <v>393.7089</v>
+        <v>0.08987299999999999</v>
       </c>
       <c r="H77" t="n">
-        <v>129.548609</v>
+        <v>0.09468699999999999</v>
       </c>
       <c r="I77" t="n">
-        <v>80.302712</v>
+        <v>0.090987</v>
       </c>
       <c r="J77" t="n">
-        <v>63.975701</v>
+        <v>0.116833</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0.046627</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業平上櫃</t>
-        </is>
-      </c>
-      <c r="B78" t="n">
-        <v>0.164759</v>
-      </c>
+          <t>紡織纖維右上上市</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
       <c r="C78" t="n">
-        <v>0.165728</v>
+        <v>167.925014</v>
       </c>
       <c r="D78" t="n">
-        <v>0.1738</v>
+        <v>144.37402</v>
       </c>
       <c r="E78" t="n">
-        <v>0.06646000000000001</v>
+        <v>192.102061</v>
       </c>
       <c r="F78" t="n">
-        <v>0.181862</v>
+        <v>486.835413</v>
       </c>
       <c r="G78" t="n">
-        <v>0.126775</v>
+        <v>255.407393</v>
       </c>
       <c r="H78" t="n">
-        <v>0.097179</v>
+        <v>389.4149</v>
       </c>
       <c r="I78" t="n">
-        <v>0.148083</v>
+        <v>699.954172</v>
       </c>
       <c r="J78" t="n">
-        <v>0.09477774999999999</v>
+        <v>482.482272</v>
+      </c>
+      <c r="K78" t="n">
+        <v>1599.570799</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右上上市</t>
-        </is>
-      </c>
-      <c r="B79" t="n">
-        <v>243.927543</v>
-      </c>
+          <t>紡織纖維右上上櫃</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
       <c r="C79" t="n">
-        <v>156.612433</v>
+        <v>0.002614</v>
       </c>
       <c r="D79" t="n">
-        <v>292.472929</v>
+        <v>0.003562</v>
       </c>
       <c r="E79" t="n">
-        <v>185.653581</v>
+        <v>0.002342</v>
       </c>
       <c r="F79" t="n">
-        <v>680.52637</v>
+        <v>0.003026</v>
       </c>
       <c r="G79" t="n">
-        <v>253.387223</v>
+        <v>0.000842</v>
       </c>
       <c r="H79" t="n">
-        <v>522.9243310000001</v>
+        <v>0.001892</v>
       </c>
       <c r="I79" t="n">
-        <v>698.51841</v>
+        <v>0.001417</v>
       </c>
       <c r="J79" t="n">
-        <v>474.371744</v>
+        <v>0.003773</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0.009072</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右上上櫃</t>
-        </is>
-      </c>
-      <c r="B80" t="n">
-        <v>0.004252</v>
-      </c>
+          <t>紡織纖維右下上市</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
       <c r="C80" t="n">
-        <v>0.002614</v>
+        <v>528.422161</v>
       </c>
       <c r="D80" t="n">
-        <v>0.003562</v>
+        <v>563.181368</v>
       </c>
       <c r="E80" t="n">
-        <v>0.002342</v>
+        <v>498.794683</v>
       </c>
       <c r="F80" t="n">
-        <v>0.003026</v>
+        <v>691.878292</v>
       </c>
       <c r="G80" t="n">
-        <v>0.000842</v>
+        <v>430.52915</v>
       </c>
       <c r="H80" t="n">
-        <v>0.001892</v>
+        <v>409.086257</v>
       </c>
       <c r="I80" t="n">
-        <v>0.001417</v>
+        <v>926.442956</v>
       </c>
       <c r="J80" t="n">
-        <v>0.003551</v>
+        <v>1354.297717</v>
+      </c>
+      <c r="K80" t="n">
+        <v>1338.355974</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右下上市</t>
-        </is>
-      </c>
-      <c r="B81" t="n">
-        <v>1029.650505</v>
-      </c>
+          <t>紡織纖維右下上櫃</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
-        <v>529.1533889999999</v>
+        <v>0.003755</v>
       </c>
       <c r="D81" t="n">
-        <v>559.467184</v>
+        <v>0.003316</v>
       </c>
       <c r="E81" t="n">
-        <v>497.35158</v>
+        <v>0.001696</v>
       </c>
       <c r="F81" t="n">
-        <v>690.9260829999999</v>
+        <v>0.005551</v>
       </c>
       <c r="G81" t="n">
-        <v>429.938206</v>
+        <v>0.001959</v>
       </c>
       <c r="H81" t="n">
-        <v>409.600498</v>
+        <v>0.002287</v>
       </c>
       <c r="I81" t="n">
-        <v>925.605107</v>
+        <v>0.004319</v>
       </c>
       <c r="J81" t="n">
-        <v>1273.61289</v>
+        <v>0.005732</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0.001899</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右下上櫃</t>
-        </is>
-      </c>
-      <c r="B82" t="n">
-        <v>0.009835</v>
-      </c>
+          <t>紡織纖維平上市</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
       <c r="C82" t="n">
-        <v>0.003755</v>
+        <v>184.572468</v>
       </c>
       <c r="D82" t="n">
-        <v>0.003866</v>
+        <v>233.877082</v>
       </c>
       <c r="E82" t="n">
-        <v>0.002449</v>
+        <v>217.291177</v>
       </c>
       <c r="F82" t="n">
-        <v>0.005551</v>
+        <v>208.142903</v>
       </c>
       <c r="G82" t="n">
-        <v>0.003023</v>
+        <v>462.188773</v>
       </c>
       <c r="H82" t="n">
-        <v>0.002772</v>
+        <v>175.527518</v>
       </c>
       <c r="I82" t="n">
-        <v>0.004978</v>
+        <v>242.359446</v>
       </c>
       <c r="J82" t="n">
-        <v>0.006434</v>
+        <v>151.501059</v>
+      </c>
+      <c r="K82" t="n">
+        <v>262.854959</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維平上市</t>
-        </is>
-      </c>
-      <c r="B83" t="n">
-        <v>181.637446</v>
-      </c>
+          <t>紡織纖維平上櫃</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
-        <v>195.153821</v>
+        <v>0.003386</v>
       </c>
       <c r="D83" t="n">
-        <v>89.492357</v>
+        <v>0.001797</v>
       </c>
       <c r="E83" t="n">
-        <v>225.18276</v>
+        <v>0.002898</v>
       </c>
       <c r="F83" t="n">
-        <v>15.404155</v>
+        <v>0.003993</v>
       </c>
       <c r="G83" t="n">
-        <v>464.799887</v>
+        <v>0.002768</v>
       </c>
       <c r="H83" t="n">
-        <v>41.503846</v>
+        <v>0.00236</v>
       </c>
       <c r="I83" t="n">
-        <v>244.633057</v>
+        <v>0.004905</v>
       </c>
       <c r="J83" t="n">
-        <v>160.028175</v>
+        <v>0.00288</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0.008343</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維平上櫃</t>
-        </is>
-      </c>
-      <c r="B84" t="n">
-        <v>0.002626</v>
-      </c>
+          <t>綠能環保右上上市</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
       <c r="C84" t="n">
-        <v>0.003386</v>
+        <v>1080.528652</v>
       </c>
       <c r="D84" t="n">
-        <v>0.001247</v>
+        <v>1065.762051</v>
       </c>
       <c r="E84" t="n">
-        <v>0.002145</v>
+        <v>1587.058712</v>
       </c>
       <c r="F84" t="n">
-        <v>0.003993</v>
+        <v>1847.634114</v>
       </c>
       <c r="G84" t="n">
-        <v>0.001704</v>
+        <v>1606.405262</v>
       </c>
       <c r="H84" t="n">
-        <v>0.001875</v>
+        <v>1655.750715</v>
       </c>
       <c r="I84" t="n">
-        <v>0.004246</v>
+        <v>2934.521909</v>
       </c>
       <c r="J84" t="n">
-        <v>0.0024</v>
+        <v>1506.37993</v>
+      </c>
+      <c r="K84" t="n">
+        <v>3645.680742</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右上上市</t>
-        </is>
-      </c>
-      <c r="B85" t="n">
-        <v>1169.933032</v>
-      </c>
+          <t>綠能環保右上上櫃</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
-        <v>1083.445147</v>
+        <v>0.08539099999999999</v>
       </c>
       <c r="D85" t="n">
-        <v>987.254875</v>
+        <v>0.08933199999999999</v>
       </c>
       <c r="E85" t="n">
-        <v>1065.228574</v>
+        <v>0.210435</v>
       </c>
       <c r="F85" t="n">
-        <v>1461.418548</v>
+        <v>0.210932</v>
       </c>
       <c r="G85" t="n">
-        <v>1090.069752</v>
+        <v>0.278157</v>
       </c>
       <c r="H85" t="n">
-        <v>1296.447198</v>
+        <v>0.668552</v>
       </c>
       <c r="I85" t="n">
-        <v>2458.697829</v>
+        <v>0.483589</v>
       </c>
       <c r="J85" t="n">
-        <v>1089.254445</v>
+        <v>0.411683</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0.483954</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右上上櫃</t>
-        </is>
-      </c>
-      <c r="B86" t="n">
-        <v>0.056319</v>
-      </c>
+          <t>綠能環保右下上市</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
       <c r="C86" t="n">
-        <v>0.08539099999999999</v>
+        <v>308.43768</v>
       </c>
       <c r="D86" t="n">
-        <v>0.08933199999999999</v>
+        <v>287.683514</v>
       </c>
       <c r="E86" t="n">
-        <v>0.031627</v>
+        <v>274.468824</v>
       </c>
       <c r="F86" t="n">
-        <v>0.034733</v>
+        <v>248.735441</v>
       </c>
       <c r="G86" t="n">
-        <v>0.06268700000000001</v>
+        <v>280.548546</v>
       </c>
       <c r="H86" t="n">
-        <v>0.668552</v>
+        <v>316.477195</v>
       </c>
       <c r="I86" t="n">
-        <v>0.483589</v>
+        <v>515.226859</v>
       </c>
       <c r="J86" t="n">
-        <v>0.361396</v>
+        <v>319.441993</v>
+      </c>
+      <c r="K86" t="n">
+        <v>274.473049</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右下上市</t>
-        </is>
-      </c>
-      <c r="B87" t="n">
-        <v>621.8295010000001</v>
-      </c>
+          <t>綠能環保右下上櫃</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
-        <v>539.273703</v>
+        <v>0.02672833333333334</v>
       </c>
       <c r="D87" t="n">
-        <v>278.616048</v>
+        <v>0.016288</v>
       </c>
       <c r="E87" t="n">
-        <v>274.468824</v>
+        <v>0.03483266666666667</v>
       </c>
       <c r="F87" t="n">
-        <v>246.334542</v>
+        <v>0.024313</v>
       </c>
       <c r="G87" t="n">
-        <v>273.107014</v>
+        <v>0.017407</v>
       </c>
       <c r="H87" t="n">
-        <v>308.175048</v>
+        <v>0.023258</v>
       </c>
       <c r="I87" t="n">
-        <v>514.506952</v>
+        <v>0.049814</v>
       </c>
       <c r="J87" t="n">
-        <v>314.34913</v>
+        <v>0.038306</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0.036366</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右下上櫃</t>
-        </is>
-      </c>
-      <c r="B88" t="n">
-        <v>0.223725</v>
-      </c>
+          <t>綠能環保平上市</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
-        <v>0.2862343333333333</v>
+        <v>247.562415</v>
       </c>
       <c r="D88" t="n">
-        <v>0.114534</v>
+        <v>368.456756</v>
       </c>
       <c r="E88" t="n">
-        <v>0.06042566666666667</v>
+        <v>22.530052</v>
       </c>
       <c r="F88" t="n">
-        <v>0.040755</v>
+        <v>23.316133</v>
       </c>
       <c r="G88" t="n">
-        <v>0.03678</v>
+        <v>22.036377</v>
       </c>
       <c r="H88" t="n">
-        <v>0.041197</v>
+        <v>23.016278</v>
       </c>
       <c r="I88" t="n">
-        <v>0.112541</v>
+        <v>37.641095</v>
       </c>
       <c r="J88" t="n">
-        <v>0.09009399999999999</v>
+        <v>19.4716</v>
+      </c>
+      <c r="K88" t="n">
+        <v>13.093158</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>綠能環保平上市</t>
-        </is>
-      </c>
-      <c r="B89" t="n">
-        <v>87.93873600000001</v>
-      </c>
+          <t>綠能環保平上櫃</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>13.809897</v>
+        <v>0.260887</v>
       </c>
       <c r="D89" t="n">
-        <v>456.031398</v>
+        <v>0.098638</v>
       </c>
       <c r="E89" t="n">
-        <v>544.36019</v>
+        <v>0.025832</v>
       </c>
       <c r="F89" t="n">
-        <v>411.932598</v>
+        <v>0.018125</v>
       </c>
       <c r="G89" t="n">
-        <v>545.813419</v>
+        <v>0.019877</v>
       </c>
       <c r="H89" t="n">
-        <v>390.621942</v>
+        <v>0.018939</v>
       </c>
       <c r="I89" t="n">
-        <v>514.185082</v>
+        <v>0.064306</v>
       </c>
       <c r="J89" t="n">
-        <v>441.689948</v>
+        <v>0.001511</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0.00081</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>綠能環保平上櫃</t>
-        </is>
-      </c>
-      <c r="B90" t="n">
-        <v>0.013315</v>
-      </c>
+          <t>航運業右上上市</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
-        <v>0.001381</v>
+        <v>5141.094921</v>
       </c>
       <c r="D90" t="n">
-        <v>0.000392</v>
+        <v>3937.638722</v>
       </c>
       <c r="E90" t="n">
-        <v>0.179047</v>
+        <v>4902.34093</v>
       </c>
       <c r="F90" t="n">
-        <v>0.177882</v>
+        <v>4162.974965</v>
       </c>
       <c r="G90" t="n">
-        <v>0.215974</v>
+        <v>3628.725363</v>
       </c>
       <c r="H90" t="n">
-        <v>0.001</v>
+        <v>4015.794107</v>
       </c>
       <c r="I90" t="n">
-        <v>0.001579</v>
+        <v>4930.886461</v>
       </c>
       <c r="J90" t="n">
-        <v>1e-05</v>
+        <v>4047.080616</v>
+      </c>
+      <c r="K90" t="n">
+        <v>4045.095073</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>航運業右上上市</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>5391.171935</v>
-      </c>
+          <t>航運業右下上市</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>6706.51643</v>
+        <v>201.193499</v>
       </c>
       <c r="D91" t="n">
-        <v>4550.993342</v>
+        <v>172.265618</v>
       </c>
       <c r="E91" t="n">
-        <v>6235.148024</v>
+        <v>246.817529</v>
       </c>
       <c r="F91" t="n">
-        <v>5045.109869</v>
+        <v>207.837683</v>
       </c>
       <c r="G91" t="n">
-        <v>4288.824517</v>
+        <v>149.091351</v>
       </c>
       <c r="H91" t="n">
-        <v>4613.845504</v>
+        <v>190.484063</v>
       </c>
       <c r="I91" t="n">
-        <v>5575.912177</v>
+        <v>276.736665</v>
       </c>
       <c r="J91" t="n">
-        <v>4810.449258</v>
+        <v>249.350191</v>
+      </c>
+      <c r="K91" t="n">
+        <v>161.448402</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>航運業右下上市</t>
-        </is>
-      </c>
-      <c r="B92" t="n">
-        <v>321.987568</v>
-      </c>
+          <t>航運業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
-        <v>323.013159</v>
+        <v>0.0187445</v>
       </c>
       <c r="D92" t="n">
-        <v>223.085712</v>
+        <v>0.012347</v>
       </c>
       <c r="E92" t="n">
-        <v>319.29705</v>
+        <v>0.018943</v>
       </c>
       <c r="F92" t="n">
-        <v>272.893445</v>
+        <v>0.021786</v>
       </c>
       <c r="G92" t="n">
-        <v>227.609198</v>
+        <v>0.018536</v>
       </c>
       <c r="H92" t="n">
-        <v>252.512685</v>
+        <v>0.021268</v>
       </c>
       <c r="I92" t="n">
-        <v>366.233668</v>
+        <v>0.0430535</v>
       </c>
       <c r="J92" t="n">
-        <v>309.11194</v>
+        <v>0.023512</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0.01764933333333333</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>航運業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B93" t="n">
-        <v>0.017652</v>
-      </c>
+          <t>航運業平上市</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>0.0187445</v>
+        <v>2588.8407</v>
       </c>
       <c r="D93" t="n">
-        <v>0.015171</v>
+        <v>1356.772584</v>
       </c>
       <c r="E93" t="n">
-        <v>0.027518</v>
+        <v>1696.867779</v>
       </c>
       <c r="F93" t="n">
-        <v>0.031577</v>
+        <v>1473.299704</v>
       </c>
       <c r="G93" t="n">
-        <v>0.018536</v>
+        <v>1135.708164</v>
       </c>
       <c r="H93" t="n">
-        <v>0.021268</v>
+        <v>953.812262</v>
       </c>
       <c r="I93" t="n">
-        <v>0.0430535</v>
+        <v>1262.589742</v>
       </c>
       <c r="J93" t="n">
-        <v>0.043256</v>
+        <v>1164.609844</v>
+      </c>
+      <c r="K93" t="n">
+        <v>889.168131</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>航運業平上市</t>
-        </is>
-      </c>
-      <c r="B94" t="n">
-        <v>637.521775</v>
-      </c>
+          <t>航運業平上櫃</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>901.599531</v>
+        <v>0.003643</v>
       </c>
       <c r="D94" t="n">
-        <v>692.5978699999999</v>
+        <v>0.002824</v>
       </c>
       <c r="E94" t="n">
-        <v>291.581164</v>
+        <v>0.008574999999999999</v>
       </c>
       <c r="F94" t="n">
-        <v>526.1090380000001</v>
-      </c>
-      <c r="G94" t="n">
-        <v>397.091163</v>
-      </c>
-      <c r="H94" t="n">
-        <v>293.732243</v>
-      </c>
-      <c r="I94" t="n">
-        <v>528.0670229999999</v>
-      </c>
+        <v>0.009790999999999999</v>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
       <c r="J94" t="n">
-        <v>341.479453</v>
+        <v>0.019744</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0.01569</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>航運業平上櫃</t>
-        </is>
-      </c>
-      <c r="B95" t="n">
-        <v>0.003387</v>
-      </c>
+          <t>觀光事業右上上市</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>0.003643</v>
-      </c>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
+        <v>11.00032</v>
+      </c>
+      <c r="D95" t="n">
+        <v>8.780357</v>
+      </c>
+      <c r="E95" t="n">
+        <v>105.657624</v>
+      </c>
+      <c r="F95" t="n">
+        <v>79.71870199999999</v>
+      </c>
+      <c r="G95" t="n">
+        <v>49.868836</v>
+      </c>
+      <c r="H95" t="n">
+        <v>57.785976</v>
+      </c>
+      <c r="I95" t="n">
+        <v>42.157955</v>
+      </c>
+      <c r="J95" t="n">
+        <v>24.130511</v>
+      </c>
+      <c r="K95" t="n">
+        <v>69.97319400000001</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右上上市</t>
-        </is>
-      </c>
-      <c r="B96" t="n">
-        <v>17.981812</v>
-      </c>
+          <t>觀光事業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>12.021829</v>
+        <v>0.005545</v>
       </c>
       <c r="D96" t="n">
-        <v>135.017384</v>
+        <v>0.005721</v>
       </c>
       <c r="E96" t="n">
-        <v>139.47937</v>
+        <v>0.009771999999999999</v>
       </c>
       <c r="F96" t="n">
-        <v>81.415419</v>
+        <v>0.028757</v>
       </c>
       <c r="G96" t="n">
-        <v>52.444073</v>
+        <v>0.0221915</v>
       </c>
       <c r="H96" t="n">
-        <v>95.54313500000001</v>
+        <v>0.003814</v>
       </c>
       <c r="I96" t="n">
-        <v>62.716002</v>
+        <v>0.002144</v>
       </c>
       <c r="J96" t="n">
-        <v>27.640307</v>
+        <v>0.002969</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0.002034</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B97" t="n">
-        <v>0.002788</v>
-      </c>
+          <t>觀光事業右下上市</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>0.005511</v>
+        <v>73.746514</v>
       </c>
       <c r="D97" t="n">
-        <v>0.005694</v>
+        <v>57.692754</v>
       </c>
       <c r="E97" t="n">
-        <v>0.009537</v>
+        <v>82.187201</v>
       </c>
       <c r="F97" t="n">
-        <v>0.028504</v>
+        <v>75.432047</v>
       </c>
       <c r="G97" t="n">
-        <v>0.0221175</v>
+        <v>40.885461</v>
       </c>
       <c r="H97" t="n">
-        <v>0.00347</v>
+        <v>48.094337</v>
       </c>
       <c r="I97" t="n">
-        <v>0.001891</v>
+        <v>76.15819</v>
       </c>
       <c r="J97" t="n">
-        <v>0.002712</v>
+        <v>80.90887600000001</v>
+      </c>
+      <c r="K97" t="n">
+        <v>48.119094</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右下上市</t>
-        </is>
-      </c>
-      <c r="B98" t="n">
-        <v>70.396855</v>
-      </c>
+          <t>觀光事業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
       <c r="C98" t="n">
-        <v>73.746514</v>
+        <v>0.038824</v>
       </c>
       <c r="D98" t="n">
-        <v>57.692754</v>
+        <v>0.031206</v>
       </c>
       <c r="E98" t="n">
-        <v>82.187201</v>
+        <v>0.026004</v>
       </c>
       <c r="F98" t="n">
-        <v>75.432047</v>
+        <v>0.026931</v>
       </c>
       <c r="G98" t="n">
-        <v>40.885461</v>
+        <v>0.02033</v>
       </c>
       <c r="H98" t="n">
-        <v>48.094337</v>
+        <v>0.02405725</v>
       </c>
       <c r="I98" t="n">
-        <v>76.15819</v>
+        <v>0.033866</v>
       </c>
       <c r="J98" t="n">
-        <v>61.827034</v>
+        <v>0.048066</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0.045128</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B99" t="n">
-        <v>0.035491</v>
-      </c>
+          <t>觀光事業平上市</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
-        <v>0.0379</v>
+        <v>43.501803</v>
       </c>
       <c r="D99" t="n">
-        <v>0.031141</v>
+        <v>126.618067</v>
       </c>
       <c r="E99" t="n">
-        <v>0.025722</v>
+        <v>34.528757</v>
       </c>
       <c r="F99" t="n">
-        <v>0.025105</v>
+        <v>1.696717</v>
       </c>
       <c r="G99" t="n">
-        <v>0.021688</v>
+        <v>73.502138</v>
       </c>
       <c r="H99" t="n">
-        <v>0.02571725</v>
+        <v>37.757159</v>
       </c>
       <c r="I99" t="n">
-        <v>0.035702</v>
+        <v>36.973401</v>
       </c>
       <c r="J99" t="n">
-        <v>0.051818</v>
+        <v>5.294105</v>
+      </c>
+      <c r="K99" t="n">
+        <v>22.853852</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>觀光事業平上市</t>
-        </is>
-      </c>
-      <c r="B100" t="n">
-        <v>63.217595</v>
-      </c>
+          <t>觀光事業平上櫃</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
       <c r="C100" t="n">
-        <v>42.480294</v>
+        <v>0.001799</v>
       </c>
       <c r="D100" t="n">
-        <v>0.38104</v>
+        <v>0.001541</v>
       </c>
       <c r="E100" t="n">
-        <v>0.7070109999999999</v>
-      </c>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="n">
-        <v>70.926901</v>
-      </c>
-      <c r="H100" t="inlineStr"/>
+        <v>0.00026275</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0.000408</v>
+      </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="n">
+        <v>0.000231</v>
+      </c>
       <c r="I100" t="n">
-        <v>16.415354</v>
+        <v>0.000167</v>
       </c>
       <c r="J100" t="n">
-        <v>20.866151</v>
+        <v>4.8e-05</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0.000685</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>觀光事業平上櫃</t>
-        </is>
-      </c>
-      <c r="B101" t="n">
-        <v>0.002429</v>
-      </c>
+          <t>貿易百貨右上上市</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
       <c r="C101" t="n">
-        <v>0.002757</v>
+        <v>172.011245</v>
       </c>
       <c r="D101" t="n">
-        <v>0.001633</v>
+        <v>123.089602</v>
       </c>
       <c r="E101" t="n">
-        <v>0.00077975</v>
+        <v>123.734111</v>
       </c>
       <c r="F101" t="n">
-        <v>0.002487</v>
+        <v>101.188944</v>
       </c>
       <c r="G101" t="n">
-        <v>0.000375</v>
+        <v>96.374189</v>
       </c>
       <c r="H101" t="n">
-        <v>0.00052</v>
+        <v>114.310155</v>
       </c>
       <c r="I101" t="n">
-        <v>0.001889</v>
+        <v>117.16523</v>
       </c>
       <c r="J101" t="n">
-        <v>0.000857</v>
+        <v>72.46779100000001</v>
+      </c>
+      <c r="K101" t="n">
+        <v>97.059353</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨右上上市</t>
-        </is>
-      </c>
-      <c r="B102" t="n">
-        <v>134.583649</v>
-      </c>
+          <t>貿易百貨右下上市</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
       <c r="C102" t="n">
-        <v>173.191176</v>
+        <v>530.455793</v>
       </c>
       <c r="D102" t="n">
-        <v>124.12725</v>
+        <v>482.217237</v>
       </c>
       <c r="E102" t="n">
-        <v>123.87734</v>
+        <v>354.9255993333333</v>
       </c>
       <c r="F102" t="n">
-        <v>101.572075</v>
+        <v>368.929928</v>
       </c>
       <c r="G102" t="n">
-        <v>97.257312</v>
+        <v>516.631265</v>
       </c>
       <c r="H102" t="n">
-        <v>116.831751</v>
+        <v>677.631095</v>
       </c>
       <c r="I102" t="n">
-        <v>120.134948</v>
+        <v>293.270035</v>
       </c>
       <c r="J102" t="n">
-        <v>75.797059</v>
+        <v>369.115774</v>
+      </c>
+      <c r="K102" t="n">
+        <v>448.56876</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨右下上市</t>
-        </is>
-      </c>
-      <c r="B103" t="n">
-        <v>228.051738</v>
-      </c>
+          <t>貿易百貨平上市</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr"/>
       <c r="C103" t="n">
-        <v>545.00246</v>
+        <v>24.741599</v>
       </c>
       <c r="D103" t="n">
-        <v>502.007682</v>
+        <v>21.066168</v>
       </c>
       <c r="E103" t="n">
-        <v>353.8224913333333</v>
+        <v>0.99844</v>
       </c>
       <c r="F103" t="n">
-        <v>405.806172</v>
+        <v>40.741601</v>
       </c>
       <c r="G103" t="n">
-        <v>516.970554</v>
+        <v>2.296363</v>
       </c>
       <c r="H103" t="n">
-        <v>676.738581</v>
+        <v>4.231909</v>
       </c>
       <c r="I103" t="n">
-        <v>292.238365</v>
+        <v>3.785008</v>
       </c>
       <c r="J103" t="n">
-        <v>369.115774</v>
+        <v>5.179322</v>
+      </c>
+      <c r="K103" t="n">
+        <v>4.211703</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨平上市</t>
-        </is>
-      </c>
-      <c r="B104" t="n">
-        <v>1.363332</v>
-      </c>
+          <t>資訊服務業右上上市</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr"/>
       <c r="C104" t="n">
-        <v>9.015001</v>
+        <v>684.8656130000001</v>
       </c>
       <c r="D104" t="n">
-        <v>0.238075</v>
+        <v>733.865583</v>
       </c>
       <c r="E104" t="n">
-        <v>1.958319</v>
+        <v>418.030885</v>
       </c>
       <c r="F104" t="n">
-        <v>3.482226</v>
+        <v>547.916906</v>
       </c>
       <c r="G104" t="n">
-        <v>1.073951</v>
+        <v>262.218864</v>
       </c>
       <c r="H104" t="n">
-        <v>2.602827</v>
+        <v>217.2931</v>
       </c>
       <c r="I104" t="n">
-        <v>1.84696</v>
+        <v>345.014255</v>
       </c>
       <c r="J104" t="n">
-        <v>1.850054</v>
+        <v>256.285556</v>
+      </c>
+      <c r="K104" t="n">
+        <v>448.100883</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右上上市</t>
-        </is>
-      </c>
-      <c r="B105" t="n">
-        <v>999.44839</v>
-      </c>
+          <t>資訊服務業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
       <c r="C105" t="n">
-        <v>816.0570310000001</v>
+        <v>0.06589</v>
       </c>
       <c r="D105" t="n">
-        <v>921.361164</v>
+        <v>0.316551</v>
       </c>
       <c r="E105" t="n">
-        <v>525.655053</v>
+        <v>0.151087</v>
       </c>
       <c r="F105" t="n">
-        <v>637.545508</v>
+        <v>0.145614</v>
       </c>
       <c r="G105" t="n">
-        <v>335.86408</v>
+        <v>0.440767</v>
       </c>
       <c r="H105" t="n">
-        <v>309.39226</v>
+        <v>0.579151</v>
       </c>
       <c r="I105" t="n">
-        <v>538.491268</v>
+        <v>0.405653</v>
       </c>
       <c r="J105" t="n">
-        <v>622.022591</v>
+        <v>1.006223</v>
+      </c>
+      <c r="K105" t="n">
+        <v>0.495084</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B106" t="n">
-        <v>0.28803</v>
-      </c>
+          <t>資訊服務業右下上市</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr"/>
       <c r="C106" t="n">
-        <v>0.180248</v>
+        <v>31.30314</v>
       </c>
       <c r="D106" t="n">
-        <v>0.624803</v>
+        <v>32.514739</v>
       </c>
       <c r="E106" t="n">
-        <v>0.272337</v>
+        <v>30.620833</v>
       </c>
       <c r="F106" t="n">
-        <v>0.270188</v>
+        <v>33.041287</v>
       </c>
       <c r="G106" t="n">
-        <v>0.531964</v>
+        <v>23.291445</v>
       </c>
       <c r="H106" t="n">
-        <v>0.654319</v>
+        <v>26.608812</v>
       </c>
       <c r="I106" t="n">
-        <v>0.479901</v>
+        <v>204.47693</v>
       </c>
       <c r="J106" t="n">
-        <v>1.319274</v>
+        <v>125.183585</v>
+      </c>
+      <c r="K106" t="n">
+        <v>62.836432</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右下上市</t>
-        </is>
-      </c>
-      <c r="B107" t="n">
-        <v>5.549619</v>
-      </c>
+          <t>資訊服務業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
       <c r="C107" t="n">
-        <v>4.066226</v>
+        <v>0.080763</v>
       </c>
       <c r="D107" t="n">
-        <v>6.540235</v>
+        <v>0.05816</v>
       </c>
       <c r="E107" t="n">
-        <v>16.557683</v>
+        <v>0.042404</v>
       </c>
       <c r="F107" t="n">
-        <v>8.925591000000001</v>
+        <v>0.046353</v>
       </c>
       <c r="G107" t="n">
-        <v>4.865924</v>
+        <v>0.100276</v>
       </c>
       <c r="H107" t="n">
-        <v>13.219645</v>
+        <v>0.061166</v>
       </c>
       <c r="I107" t="n">
-        <v>64.06024600000001</v>
+        <v>0.108952</v>
       </c>
       <c r="J107" t="n">
-        <v>42.807068</v>
+        <v>0.15871675</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0.092221</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B108" t="n">
-        <v>0.16141</v>
-      </c>
+          <t>資訊服務業平上市</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr"/>
       <c r="C108" t="n">
-        <v>0.112514</v>
+        <v>143.446269</v>
       </c>
       <c r="D108" t="n">
-        <v>0.06328499999999999</v>
+        <v>210.135385</v>
       </c>
       <c r="E108" t="n">
-        <v>0.0534</v>
+        <v>117.282981</v>
       </c>
       <c r="F108" t="n">
-        <v>0.09637</v>
+        <v>97.582365</v>
       </c>
       <c r="G108" t="n">
-        <v>0.060962</v>
+        <v>73.645216</v>
       </c>
       <c r="H108" t="n">
-        <v>0.066687</v>
+        <v>96.94449</v>
       </c>
       <c r="I108" t="n">
-        <v>0.221183</v>
+        <v>193.477013</v>
       </c>
       <c r="J108" t="n">
-        <v>0.10333425</v>
+        <v>365.737035</v>
+      </c>
+      <c r="K108" t="n">
+        <v>118.763697</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業平上市</t>
-        </is>
-      </c>
-      <c r="B109" t="n">
-        <v>32.594114</v>
-      </c>
+          <t>資訊服務業平上櫃</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr"/>
       <c r="C109" t="n">
-        <v>39.491765</v>
+        <v>0.178189</v>
       </c>
       <c r="D109" t="n">
-        <v>48.614308</v>
+        <v>0.49717</v>
       </c>
       <c r="E109" t="n">
-        <v>23.721963</v>
+        <v>0.30398</v>
       </c>
       <c r="F109" t="n">
-        <v>32.069459</v>
+        <v>0.303025</v>
       </c>
       <c r="G109" t="n">
-        <v>18.425521</v>
+        <v>0.13175</v>
       </c>
       <c r="H109" t="n">
-        <v>18.234497</v>
+        <v>0.194943</v>
       </c>
       <c r="I109" t="n">
-        <v>140.416684</v>
+        <v>0.292558</v>
       </c>
       <c r="J109" t="n">
-        <v>82.37651700000001</v>
+        <v>0.3342795</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0.148242</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業平上櫃</t>
-        </is>
-      </c>
-      <c r="B110" t="n">
-        <v>0.077565</v>
-      </c>
+          <t>農業科技業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr"/>
       <c r="C110" t="n">
-        <v>0.03208</v>
+        <v>0.003346</v>
       </c>
       <c r="D110" t="n">
-        <v>0.183793</v>
+        <v>0.00109</v>
       </c>
       <c r="E110" t="n">
-        <v>0.171734</v>
+        <v>0.000695</v>
       </c>
       <c r="F110" t="n">
-        <v>0.128434</v>
+        <v>0.000838</v>
       </c>
       <c r="G110" t="n">
-        <v>0.07986699999999999</v>
+        <v>0.00054</v>
       </c>
       <c r="H110" t="n">
-        <v>0.114254</v>
-      </c>
-      <c r="I110" t="n">
-        <v>0.106079</v>
-      </c>
-      <c r="J110" t="n">
-        <v>0.076611</v>
+        <v>0.00107</v>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="n">
+        <v>0.000827</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>農業科技業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B111" t="n">
-        <v>0.010882</v>
-      </c>
+          <t>農業科技業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr"/>
       <c r="C111" t="n">
-        <v>0.003346</v>
+        <v>0.00236</v>
       </c>
       <c r="D111" t="n">
-        <v>0.00109</v>
+        <v>0.004261</v>
       </c>
       <c r="E111" t="n">
-        <v>0.000695</v>
+        <v>0.002522</v>
       </c>
       <c r="F111" t="n">
-        <v>0.000838</v>
+        <v>0.002449</v>
       </c>
       <c r="G111" t="n">
-        <v>0.00054</v>
+        <v>0.00161</v>
       </c>
       <c r="H111" t="n">
-        <v>0.00107</v>
+        <v>0.001331</v>
       </c>
       <c r="I111" t="n">
-        <v>0.00094</v>
+        <v>0.007381</v>
       </c>
       <c r="J111" t="n">
-        <v>0.00105</v>
+        <v>0.003454</v>
+      </c>
+      <c r="K111" t="n">
+        <v>0.02229</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>農業科技業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B112" t="n">
-        <v>0.00152</v>
-      </c>
-      <c r="C112" t="n">
-        <v>0.00236</v>
-      </c>
-      <c r="D112" t="n">
-        <v>0.004261</v>
-      </c>
-      <c r="E112" t="n">
-        <v>0.002522</v>
-      </c>
-      <c r="F112" t="n">
-        <v>0.002449</v>
-      </c>
-      <c r="G112" t="n">
-        <v>0.00161</v>
-      </c>
-      <c r="H112" t="n">
-        <v>0.001331</v>
-      </c>
+          <t>農業科技業平上櫃</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr"/>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
       <c r="I112" t="n">
-        <v>0.007381</v>
+        <v>0.00094</v>
       </c>
       <c r="J112" t="n">
-        <v>0.003454</v>
-      </c>
+        <v>0.00105</v>
+      </c>
+      <c r="K112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
@@ -4226,32 +4330,33 @@
           <t>通信網路業右上上市</t>
         </is>
       </c>
-      <c r="B113" t="n">
-        <v>16622.501014</v>
-      </c>
+      <c r="B113" t="inlineStr"/>
       <c r="C113" t="n">
-        <v>6095.028413</v>
+        <v>17046.602242</v>
       </c>
       <c r="D113" t="n">
-        <v>6082.970456</v>
+        <v>12598.586921</v>
       </c>
       <c r="E113" t="n">
-        <v>6103.551493</v>
+        <v>15290.862009</v>
       </c>
       <c r="F113" t="n">
-        <v>6732.41476</v>
+        <v>21928.342371</v>
       </c>
       <c r="G113" t="n">
-        <v>5664.386803</v>
+        <v>16945.150652</v>
       </c>
       <c r="H113" t="n">
-        <v>8245.252662000001</v>
+        <v>25518.394772</v>
       </c>
       <c r="I113" t="n">
-        <v>22743.754038</v>
+        <v>31299.192109</v>
       </c>
       <c r="J113" t="n">
-        <v>18508.769204</v>
+        <v>29029.74642</v>
+      </c>
+      <c r="K113" t="n">
+        <v>35810.28133</v>
       </c>
     </row>
     <row r="114">
@@ -4260,32 +4365,33 @@
           <t>通信網路業右上上櫃</t>
         </is>
       </c>
-      <c r="B114" t="n">
-        <v>16.6943</v>
-      </c>
+      <c r="B114" t="inlineStr"/>
       <c r="C114" t="n">
-        <v>22.811269</v>
+        <v>26.213372</v>
       </c>
       <c r="D114" t="n">
-        <v>13.550945</v>
+        <v>15.436857</v>
       </c>
       <c r="E114" t="n">
-        <v>7.615602</v>
+        <v>9.591949</v>
       </c>
       <c r="F114" t="n">
-        <v>7.114229</v>
+        <v>9.349261</v>
       </c>
       <c r="G114" t="n">
-        <v>8.893762000000001</v>
+        <v>11.691037</v>
       </c>
       <c r="H114" t="n">
-        <v>18.312942</v>
+        <v>26.466939</v>
       </c>
       <c r="I114" t="n">
-        <v>30.87572</v>
+        <v>36.447042</v>
       </c>
       <c r="J114" t="n">
-        <v>24.380481</v>
+        <v>27.578384</v>
+      </c>
+      <c r="K114" t="n">
+        <v>41.824289</v>
       </c>
     </row>
     <row r="115">
@@ -4294,32 +4400,33 @@
           <t>通信網路業右下上市</t>
         </is>
       </c>
-      <c r="B115" t="n">
-        <v>2800.97613</v>
-      </c>
+      <c r="B115" t="inlineStr"/>
       <c r="C115" t="n">
-        <v>3905.975775</v>
+        <v>1572.925061</v>
       </c>
       <c r="D115" t="n">
-        <v>2277.09085</v>
+        <v>834.745993</v>
       </c>
       <c r="E115" t="n">
-        <v>1946.021499</v>
+        <v>496.605319</v>
       </c>
       <c r="F115" t="n">
-        <v>2780.216216</v>
+        <v>610.987922</v>
       </c>
       <c r="G115" t="n">
-        <v>2244.085252</v>
+        <v>511.843469</v>
       </c>
       <c r="H115" t="n">
-        <v>592.812061</v>
+        <v>427.332467</v>
       </c>
       <c r="I115" t="n">
-        <v>1032.313313</v>
+        <v>823.802486</v>
       </c>
       <c r="J115" t="n">
-        <v>3136.206759</v>
+        <v>1070.016387</v>
+      </c>
+      <c r="K115" t="n">
+        <v>1203.082757</v>
       </c>
     </row>
     <row r="116">
@@ -4328,32 +4435,33 @@
           <t>通信網路業右下上櫃</t>
         </is>
       </c>
-      <c r="B116" t="n">
-        <v>0.108687</v>
-      </c>
+      <c r="B116" t="inlineStr"/>
       <c r="C116" t="n">
-        <v>0.177069</v>
+        <v>0.178417</v>
       </c>
       <c r="D116" t="n">
-        <v>0.092809</v>
+        <v>0.096251</v>
       </c>
       <c r="E116" t="n">
-        <v>0.139641</v>
+        <v>0.144735</v>
       </c>
       <c r="F116" t="n">
-        <v>0.121491</v>
+        <v>0.11816</v>
       </c>
       <c r="G116" t="n">
-        <v>0.078808</v>
+        <v>0.110546</v>
       </c>
       <c r="H116" t="n">
-        <v>0.084409</v>
+        <v>0.118829</v>
       </c>
       <c r="I116" t="n">
-        <v>0.171764</v>
+        <v>0.131583</v>
       </c>
       <c r="J116" t="n">
-        <v>0.188484</v>
+        <v>0.177965</v>
+      </c>
+      <c r="K116" t="n">
+        <v>0.169226</v>
       </c>
     </row>
     <row r="117">
@@ -4362,32 +4470,33 @@
           <t>通信網路業平上市</t>
         </is>
       </c>
-      <c r="B117" t="n">
-        <v>8748.802201</v>
-      </c>
+      <c r="B117" t="inlineStr"/>
       <c r="C117" t="n">
-        <v>8856.093255</v>
+        <v>237.57014</v>
       </c>
       <c r="D117" t="n">
-        <v>5162.65965</v>
+        <v>89.388042</v>
       </c>
       <c r="E117" t="n">
-        <v>8297.360316</v>
+        <v>559.4659799999999</v>
       </c>
       <c r="F117" t="n">
-        <v>13988.662308</v>
+        <v>961.962991</v>
       </c>
       <c r="G117" t="n">
-        <v>12339.661725</v>
+        <v>2791.139659</v>
       </c>
       <c r="H117" t="n">
-        <v>17667.338244</v>
+        <v>559.675728</v>
       </c>
       <c r="I117" t="n">
-        <v>8652.535905000001</v>
+        <v>305.608661</v>
       </c>
       <c r="J117" t="n">
-        <v>10680.328469</v>
+        <v>2225.541625</v>
+      </c>
+      <c r="K117" t="n">
+        <v>142.893685</v>
       </c>
     </row>
     <row r="118">
@@ -4396,32 +4505,33 @@
           <t>通信網路業平上櫃</t>
         </is>
       </c>
-      <c r="B118" t="n">
-        <v>6.538407</v>
-      </c>
+      <c r="B118" t="inlineStr"/>
       <c r="C118" t="n">
-        <v>3.420577</v>
+        <v>0.017126</v>
       </c>
       <c r="D118" t="n">
-        <v>2.262053</v>
+        <v>0.372699</v>
       </c>
       <c r="E118" t="n">
-        <v>2.291996</v>
+        <v>0.310555</v>
       </c>
       <c r="F118" t="n">
-        <v>2.261277</v>
+        <v>0.029576</v>
       </c>
       <c r="G118" t="n">
-        <v>3.489899</v>
+        <v>0.660886</v>
       </c>
       <c r="H118" t="n">
-        <v>8.566473999999999</v>
+        <v>0.378057</v>
       </c>
       <c r="I118" t="n">
-        <v>6.319699</v>
+        <v>0.788558</v>
       </c>
       <c r="J118" t="n">
-        <v>5.424032</v>
+        <v>2.236648</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.029767</v>
       </c>
     </row>
     <row r="119">
@@ -4430,14 +4540,12 @@
           <t>造紙工業右上上市</t>
         </is>
       </c>
-      <c r="B119" t="n">
-        <v>64.522261</v>
-      </c>
+      <c r="B119" t="inlineStr"/>
       <c r="C119" t="n">
-        <v>41.474092</v>
+        <v>55.228139</v>
       </c>
       <c r="D119" t="n">
-        <v>57.019267</v>
+        <v>67.6173</v>
       </c>
       <c r="E119" t="n">
         <v>95.750647</v>
@@ -4449,13 +4557,16 @@
         <v>92.464285</v>
       </c>
       <c r="H119" t="n">
-        <v>63.28767</v>
+        <v>79.71619</v>
       </c>
       <c r="I119" t="n">
         <v>58.167627</v>
       </c>
       <c r="J119" t="n">
-        <v>54.269276</v>
+        <v>79.133607</v>
+      </c>
+      <c r="K119" t="n">
+        <v>616.862361</v>
       </c>
     </row>
     <row r="120">
@@ -4464,9 +4575,7 @@
           <t>造紙工業右下上市</t>
         </is>
       </c>
-      <c r="B120" t="n">
-        <v>8.746762</v>
-      </c>
+      <c r="B120" t="inlineStr"/>
       <c r="C120" t="n">
         <v>8.611516999999999</v>
       </c>
@@ -4491,6 +4600,9 @@
       <c r="J120" t="n">
         <v>6.283155</v>
       </c>
+      <c r="K120" t="n">
+        <v>6.420234</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
@@ -4498,14 +4610,12 @@
           <t>造紙工業平上市</t>
         </is>
       </c>
-      <c r="B121" t="n">
-        <v>39.868425</v>
-      </c>
+      <c r="B121" t="inlineStr"/>
       <c r="C121" t="n">
-        <v>31.600935</v>
+        <v>17.846888</v>
       </c>
       <c r="D121" t="n">
-        <v>23.263533</v>
+        <v>12.6655</v>
       </c>
       <c r="E121" t="n">
         <v>54.222929</v>
@@ -4517,13 +4627,16 @@
         <v>54.140034</v>
       </c>
       <c r="H121" t="n">
-        <v>31.758988</v>
+        <v>15.330468</v>
       </c>
       <c r="I121" t="n">
         <v>46.895959</v>
       </c>
       <c r="J121" t="n">
-        <v>43.005756</v>
+        <v>18.141425</v>
+      </c>
+      <c r="K121" t="n">
+        <v>23.10272</v>
       </c>
     </row>
     <row r="122">
@@ -4532,32 +4645,33 @@
           <t>運動休閒右上上市</t>
         </is>
       </c>
-      <c r="B122" t="n">
-        <v>161.276417</v>
-      </c>
+      <c r="B122" t="inlineStr"/>
       <c r="C122" t="n">
-        <v>156.233187</v>
+        <v>14.189534</v>
       </c>
       <c r="D122" t="n">
-        <v>127.930135</v>
+        <v>8.780303999999999</v>
       </c>
       <c r="E122" t="n">
-        <v>222.315562</v>
+        <v>8.784293999999999</v>
       </c>
       <c r="F122" t="n">
-        <v>159.66203</v>
+        <v>4.563235</v>
       </c>
       <c r="G122" t="n">
-        <v>173.07071</v>
+        <v>19.402717</v>
       </c>
       <c r="H122" t="n">
-        <v>149.450741</v>
+        <v>10.267939</v>
       </c>
       <c r="I122" t="n">
-        <v>133.981208</v>
+        <v>4.269063</v>
       </c>
       <c r="J122" t="n">
-        <v>117.484132</v>
+        <v>6.51182</v>
+      </c>
+      <c r="K122" t="n">
+        <v>3.759139</v>
       </c>
     </row>
     <row r="123">
@@ -4566,32 +4680,33 @@
           <t>運動休閒右上上櫃</t>
         </is>
       </c>
-      <c r="B123" t="n">
-        <v>0.008544</v>
-      </c>
+      <c r="B123" t="inlineStr"/>
       <c r="C123" t="n">
-        <v>0.007512</v>
+        <v>0.006858</v>
       </c>
       <c r="D123" t="n">
-        <v>0.008066</v>
+        <v>0.008021</v>
       </c>
       <c r="E123" t="n">
-        <v>0.00397</v>
+        <v>0.003447</v>
       </c>
       <c r="F123" t="n">
-        <v>0.003778</v>
+        <v>0.003155</v>
       </c>
       <c r="G123" t="n">
-        <v>0.006495</v>
+        <v>0.006757</v>
       </c>
       <c r="H123" t="n">
-        <v>0.002192</v>
+        <v>0.002266</v>
       </c>
       <c r="I123" t="n">
-        <v>0.001731</v>
+        <v>0.000998</v>
       </c>
       <c r="J123" t="n">
-        <v>0.001133</v>
+        <v>0.000494</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.002208</v>
       </c>
     </row>
     <row r="124">
@@ -4600,32 +4715,33 @@
           <t>運動休閒右下上市</t>
         </is>
       </c>
-      <c r="B124" t="n">
-        <v>431.198429</v>
-      </c>
+      <c r="B124" t="inlineStr"/>
       <c r="C124" t="n">
-        <v>574.917972</v>
+        <v>612.98116</v>
       </c>
       <c r="D124" t="n">
-        <v>437.072996</v>
+        <v>505.281862</v>
       </c>
       <c r="E124" t="n">
-        <v>441.590088</v>
+        <v>528.3968640000001</v>
       </c>
       <c r="F124" t="n">
-        <v>449.552373</v>
+        <v>526.544919</v>
       </c>
       <c r="G124" t="n">
-        <v>413.635324</v>
+        <v>466.358989</v>
       </c>
       <c r="H124" t="n">
-        <v>473.00502</v>
+        <v>513.529666</v>
       </c>
       <c r="I124" t="n">
-        <v>809.13311</v>
+        <v>849.426072</v>
       </c>
       <c r="J124" t="n">
-        <v>424.018495</v>
+        <v>436.34571</v>
+      </c>
+      <c r="K124" t="n">
+        <v>848.133164</v>
       </c>
     </row>
     <row r="125">
@@ -4634,33 +4750,34 @@
           <t>運動休閒右下上櫃</t>
         </is>
       </c>
-      <c r="B125" t="n">
-        <v>0.012284</v>
-      </c>
+      <c r="B125" t="inlineStr"/>
       <c r="C125" t="n">
-        <v>0.005907</v>
+        <v>0.00653</v>
       </c>
       <c r="D125" t="n">
-        <v>0.005639</v>
+        <v>0.005962</v>
       </c>
       <c r="E125" t="n">
-        <v>0.004976</v>
+        <v>0.005354</v>
       </c>
       <c r="F125" t="n">
-        <v>0.003873</v>
+        <v>0.004094</v>
       </c>
       <c r="G125" t="n">
-        <v>0.00535</v>
+        <v>0.005517</v>
       </c>
       <c r="H125" t="n">
-        <v>0.005399</v>
+        <v>0.005495</v>
       </c>
       <c r="I125" t="n">
-        <v>0.010485</v>
+        <v>0.011286</v>
       </c>
       <c r="J125" t="n">
         <v>0.005742</v>
       </c>
+      <c r="K125" t="n">
+        <v>0.015415</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
@@ -4668,32 +4785,33 @@
           <t>運動休閒平上市</t>
         </is>
       </c>
-      <c r="B126" t="n">
-        <v>11.696813</v>
-      </c>
+      <c r="B126" t="inlineStr"/>
       <c r="C126" t="n">
-        <v>8.888235</v>
+        <v>112.8687</v>
       </c>
       <c r="D126" t="n">
-        <v>47.479196</v>
+        <v>98.42016099999999</v>
       </c>
       <c r="E126" t="n">
-        <v>88.51274100000001</v>
+        <v>215.237233</v>
       </c>
       <c r="F126" t="n">
-        <v>83.666366</v>
+        <v>161.772615</v>
       </c>
       <c r="G126" t="n">
-        <v>59.722284</v>
+        <v>160.666612</v>
       </c>
       <c r="H126" t="n">
-        <v>42.191244</v>
+        <v>140.8494</v>
       </c>
       <c r="I126" t="n">
-        <v>71.724283</v>
+        <v>161.143466</v>
       </c>
       <c r="J126" t="n">
-        <v>80.792382</v>
+        <v>179.437479</v>
+      </c>
+      <c r="K126" t="n">
+        <v>125.994775</v>
       </c>
     </row>
     <row r="127">
@@ -4702,32 +4820,33 @@
           <t>運動休閒平上櫃</t>
         </is>
       </c>
-      <c r="B127" t="n">
-        <v>0.000204</v>
-      </c>
+      <c r="B127" t="inlineStr"/>
       <c r="C127" t="n">
-        <v>0.000623</v>
+        <v>0.000654</v>
       </c>
       <c r="D127" t="n">
-        <v>0.001134</v>
+        <v>0.000856</v>
       </c>
       <c r="E127" t="n">
-        <v>0.000725</v>
+        <v>0.00087</v>
       </c>
       <c r="F127" t="n">
-        <v>0.000571</v>
+        <v>0.000973</v>
       </c>
       <c r="G127" t="n">
-        <v>0.00091</v>
+        <v>0.000481</v>
       </c>
       <c r="H127" t="n">
-        <v>0.000621</v>
+        <v>0.000451</v>
       </c>
       <c r="I127" t="n">
-        <v>0.000918</v>
+        <v>0.00085</v>
       </c>
       <c r="J127" t="n">
-        <v>0.000413</v>
+        <v>0.001052</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.001937</v>
       </c>
     </row>
     <row r="128">
@@ -4736,32 +4855,33 @@
           <t>金融保險右上上市</t>
         </is>
       </c>
-      <c r="B128" t="n">
-        <v>16987.289529</v>
-      </c>
+      <c r="B128" t="inlineStr"/>
       <c r="C128" t="n">
-        <v>17478.522511</v>
+        <v>17691.083594</v>
       </c>
       <c r="D128" t="n">
-        <v>10882.35721</v>
+        <v>11085.610633</v>
       </c>
       <c r="E128" t="n">
-        <v>19643.829874</v>
+        <v>19924.034527</v>
       </c>
       <c r="F128" t="n">
-        <v>17163.268297</v>
+        <v>17412.385707</v>
       </c>
       <c r="G128" t="n">
-        <v>24618.524731</v>
+        <v>24969.850298</v>
       </c>
       <c r="H128" t="n">
-        <v>16298.205375</v>
+        <v>16532.68804</v>
       </c>
       <c r="I128" t="n">
-        <v>13807.946575</v>
+        <v>14026.974406</v>
       </c>
       <c r="J128" t="n">
-        <v>14981.031046</v>
+        <v>15006.892268</v>
+      </c>
+      <c r="K128" t="n">
+        <v>14677.86912</v>
       </c>
     </row>
     <row r="129">
@@ -4770,9 +4890,7 @@
           <t>金融保險右下上市</t>
         </is>
       </c>
-      <c r="B129" t="n">
-        <v>189.086642</v>
-      </c>
+      <c r="B129" t="inlineStr"/>
       <c r="C129" t="n">
         <v>205.909852</v>
       </c>
@@ -4780,22 +4898,25 @@
         <v>244.900842</v>
       </c>
       <c r="E129" t="n">
-        <v>387.63469</v>
+        <v>365.107306</v>
       </c>
       <c r="F129" t="n">
         <v>265.348802</v>
       </c>
       <c r="G129" t="n">
-        <v>233.42015</v>
+        <v>210.851143</v>
       </c>
       <c r="H129" t="n">
-        <v>116.899227</v>
+        <v>100.665858</v>
       </c>
       <c r="I129" t="n">
-        <v>626.85414</v>
+        <v>581.610311</v>
       </c>
       <c r="J129" t="n">
-        <v>181.039781</v>
+        <v>146.252249</v>
+      </c>
+      <c r="K129" t="n">
+        <v>193.566498</v>
       </c>
     </row>
     <row r="130">
@@ -4804,32 +4925,33 @@
           <t>金融保險平上市</t>
         </is>
       </c>
-      <c r="B130" t="n">
-        <v>354.572106</v>
-      </c>
+      <c r="B130" t="inlineStr"/>
       <c r="C130" t="n">
-        <v>228.885439</v>
+        <v>16.324356</v>
       </c>
       <c r="D130" t="n">
-        <v>209.691372</v>
+        <v>6.437949</v>
       </c>
       <c r="E130" t="n">
-        <v>280.204653</v>
+        <v>22.527384</v>
       </c>
       <c r="F130" t="n">
-        <v>256.305102</v>
+        <v>7.187692</v>
       </c>
       <c r="G130" t="n">
-        <v>351.325567</v>
+        <v>22.569007</v>
       </c>
       <c r="H130" t="n">
-        <v>464.231308</v>
+        <v>245.982012</v>
       </c>
       <c r="I130" t="n">
-        <v>366.678001</v>
+        <v>192.893999</v>
       </c>
       <c r="J130" t="n">
-        <v>91.760988</v>
+        <v>100.687298</v>
+      </c>
+      <c r="K130" t="n">
+        <v>69.90204900000001</v>
       </c>
     </row>
     <row r="131">
@@ -4838,32 +4960,33 @@
           <t>金融業右上上櫃</t>
         </is>
       </c>
-      <c r="B131" t="n">
-        <v>0.511979</v>
-      </c>
+      <c r="B131" t="inlineStr"/>
       <c r="C131" t="n">
-        <v>0.300829</v>
+        <v>0.301573</v>
       </c>
       <c r="D131" t="n">
-        <v>0.200969</v>
+        <v>0.201194</v>
       </c>
       <c r="E131" t="n">
-        <v>0.161656</v>
+        <v>0.161718</v>
       </c>
       <c r="F131" t="n">
-        <v>0.400318</v>
+        <v>0.400568</v>
       </c>
       <c r="G131" t="n">
-        <v>0.34688</v>
+        <v>0.347004</v>
       </c>
       <c r="H131" t="n">
-        <v>0.207437</v>
+        <v>0.207685</v>
       </c>
       <c r="I131" t="n">
-        <v>0.32817</v>
+        <v>0.328599</v>
       </c>
       <c r="J131" t="n">
-        <v>0.370971</v>
+        <v>0.371098</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.225088</v>
       </c>
     </row>
     <row r="132">
@@ -4872,9 +4995,7 @@
           <t>金融業右下上櫃</t>
         </is>
       </c>
-      <c r="B132" t="n">
-        <v>0.02408566666666667</v>
-      </c>
+      <c r="B132" t="inlineStr"/>
       <c r="C132" t="n">
         <v>0.043228</v>
       </c>
@@ -4899,1399 +5020,1380 @@
       <c r="J132" t="n">
         <v>0.015258</v>
       </c>
+      <c r="K132" t="n">
+        <v>0.021759</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>金融業平上櫃</t>
-        </is>
-      </c>
-      <c r="B133" t="n">
-        <v>0.000562</v>
-      </c>
+          <t>鋼鐵工業右上上市</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr"/>
       <c r="C133" t="n">
-        <v>0.000744</v>
+        <v>1696.815892</v>
       </c>
       <c r="D133" t="n">
-        <v>0.000225</v>
+        <v>1694.081261</v>
       </c>
       <c r="E133" t="n">
-        <v>6.2e-05</v>
+        <v>2007.695822</v>
       </c>
       <c r="F133" t="n">
-        <v>0.00025</v>
+        <v>2646.077804</v>
       </c>
       <c r="G133" t="n">
-        <v>0.000124</v>
+        <v>4868.16816</v>
       </c>
       <c r="H133" t="n">
-        <v>0.000248</v>
+        <v>1398.788211</v>
       </c>
       <c r="I133" t="n">
-        <v>0.000429</v>
+        <v>1782.575434</v>
       </c>
       <c r="J133" t="n">
-        <v>0.000127</v>
+        <v>836.800999</v>
+      </c>
+      <c r="K133" t="n">
+        <v>1068.783048</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上上市</t>
-        </is>
-      </c>
-      <c r="B134" t="n">
-        <v>1244.936603</v>
-      </c>
+          <t>鋼鐵工業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr"/>
       <c r="C134" t="n">
-        <v>1702.258596</v>
+        <v>0.016825</v>
       </c>
       <c r="D134" t="n">
-        <v>1668.035173</v>
+        <v>0.013359</v>
       </c>
       <c r="E134" t="n">
-        <v>2123.299819</v>
+        <v>0.06475</v>
       </c>
       <c r="F134" t="n">
-        <v>2472.356878</v>
+        <v>0.072867</v>
       </c>
       <c r="G134" t="n">
-        <v>4794.875688</v>
+        <v>0.049926</v>
       </c>
       <c r="H134" t="n">
-        <v>1359.890176</v>
+        <v>0.097998</v>
       </c>
       <c r="I134" t="n">
-        <v>1769.709532</v>
+        <v>0.06363175</v>
       </c>
       <c r="J134" t="n">
-        <v>836.966153</v>
+        <v>0.271254</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.194194</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B135" t="n">
-        <v>0.017194</v>
-      </c>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr"/>
       <c r="C135" t="n">
-        <v>0.012871</v>
+        <v>634.783</v>
       </c>
       <c r="D135" t="n">
-        <v>0.006391</v>
+        <v>591.098376</v>
       </c>
       <c r="E135" t="n">
-        <v>0.044205</v>
+        <v>909.256881</v>
       </c>
       <c r="F135" t="n">
-        <v>0.05524</v>
+        <v>148.35773</v>
       </c>
       <c r="G135" t="n">
-        <v>0.032969</v>
+        <v>169.164864</v>
       </c>
       <c r="H135" t="n">
-        <v>0.090244</v>
+        <v>118.713758</v>
       </c>
       <c r="I135" t="n">
-        <v>0.047232</v>
+        <v>682.41453</v>
       </c>
       <c r="J135" t="n">
-        <v>0.263393</v>
+        <v>114.442318</v>
+      </c>
+      <c r="K135" t="n">
+        <v>96.754739</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右下上市</t>
-        </is>
-      </c>
-      <c r="B136" t="n">
-        <v>845.004486</v>
-      </c>
+          <t>鋼鐵工業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr"/>
       <c r="C136" t="n">
-        <v>788.213784</v>
+        <v>0.028637</v>
       </c>
       <c r="D136" t="n">
-        <v>690.654503</v>
+        <v>0.0364855</v>
       </c>
       <c r="E136" t="n">
-        <v>1034.546462</v>
+        <v>0.068173</v>
       </c>
       <c r="F136" t="n">
-        <v>233.418087</v>
+        <v>0.2212903333333333</v>
       </c>
       <c r="G136" t="n">
-        <v>217.573193</v>
+        <v>0.078968</v>
       </c>
       <c r="H136" t="n">
-        <v>147.093842</v>
+        <v>0.050348</v>
       </c>
       <c r="I136" t="n">
-        <v>766.217797</v>
+        <v>0.088694</v>
       </c>
       <c r="J136" t="n">
-        <v>141.456491</v>
+        <v>0.05103625</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.047083</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B137" t="n">
-        <v>0.043378</v>
-      </c>
+          <t>鋼鐵工業平上市</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr"/>
       <c r="C137" t="n">
-        <v>0.02903</v>
+        <v>184.320351</v>
       </c>
       <c r="D137" t="n">
-        <v>0.0357425</v>
+        <v>124.788869</v>
       </c>
       <c r="E137" t="n">
-        <v>0.066598</v>
+        <v>310.398103</v>
       </c>
       <c r="F137" t="n">
-        <v>0.01580233333333333</v>
+        <v>1871.130716</v>
       </c>
       <c r="G137" t="n">
-        <v>0.07816099999999999</v>
+        <v>855.364156</v>
       </c>
       <c r="H137" t="n">
-        <v>0.008527</v>
+        <v>464.115664</v>
       </c>
       <c r="I137" t="n">
-        <v>0.08859475</v>
+        <v>191.129801</v>
       </c>
       <c r="J137" t="n">
-        <v>0.04056825</v>
+        <v>443.892535</v>
+      </c>
+      <c r="K137" t="n">
+        <v>542.6945930000001</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業平上市</t>
-        </is>
-      </c>
-      <c r="B138" t="n">
-        <v>35.389744</v>
-      </c>
+          <t>鋼鐵工業平上櫃</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr"/>
       <c r="C138" t="n">
-        <v>25.446863</v>
+        <v>0.000393</v>
       </c>
       <c r="D138" t="n">
-        <v>51.27883</v>
+        <v>1.7e-05</v>
       </c>
       <c r="E138" t="n">
-        <v>69.504525</v>
+        <v>7.499999999999999e-05</v>
       </c>
       <c r="F138" t="n">
-        <v>1959.791285</v>
-      </c>
-      <c r="G138" t="n">
-        <v>880.248299</v>
-      </c>
-      <c r="H138" t="n">
-        <v>474.633615</v>
-      </c>
-      <c r="I138" t="n">
-        <v>120.192436</v>
-      </c>
+        <v>0.003635</v>
+      </c>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
       <c r="J138" t="n">
-        <v>416.713208</v>
+        <v>9.1e-05</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.000178</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業平上櫃</t>
-        </is>
-      </c>
-      <c r="B139" t="n">
-        <v>0.009734</v>
-      </c>
+          <t>電器電纜右上上市</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr"/>
       <c r="C139" t="n">
-        <v>0.003954</v>
+        <v>527.970243</v>
       </c>
       <c r="D139" t="n">
-        <v>0.007728</v>
+        <v>281.900372</v>
       </c>
       <c r="E139" t="n">
-        <v>0.022195</v>
+        <v>431.899672</v>
       </c>
       <c r="F139" t="n">
-        <v>0.22675</v>
+        <v>1832.071461</v>
       </c>
       <c r="G139" t="n">
-        <v>0.017764</v>
+        <v>1627.572588</v>
       </c>
       <c r="H139" t="n">
-        <v>0.049575</v>
+        <v>1287.999043</v>
       </c>
       <c r="I139" t="n">
-        <v>0.016499</v>
+        <v>1121.620276</v>
       </c>
       <c r="J139" t="n">
-        <v>0.01842</v>
+        <v>672.758657</v>
+      </c>
+      <c r="K139" t="n">
+        <v>2109.068374</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右上上市</t>
-        </is>
-      </c>
-      <c r="B140" t="n">
-        <v>783.843303</v>
-      </c>
+          <t>電器電纜右上上櫃</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
       <c r="C140" t="n">
-        <v>459.979709</v>
+        <v>0.09124</v>
       </c>
       <c r="D140" t="n">
-        <v>243.385274</v>
+        <v>0.091242</v>
       </c>
       <c r="E140" t="n">
-        <v>221.164725</v>
+        <v>0.112558</v>
       </c>
       <c r="F140" t="n">
-        <v>2022.93564</v>
+        <v>0.294298</v>
       </c>
       <c r="G140" t="n">
-        <v>1815.128022</v>
+        <v>0.204111</v>
       </c>
       <c r="H140" t="n">
-        <v>1400.305424</v>
+        <v>0.346172</v>
       </c>
       <c r="I140" t="n">
-        <v>1121.620276</v>
+        <v>0.360224</v>
       </c>
       <c r="J140" t="n">
-        <v>771.32349</v>
+        <v>0.179417</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.243985</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右上上櫃</t>
-        </is>
-      </c>
-      <c r="B141" t="n">
-        <v>0.111628</v>
-      </c>
+          <t>電器電纜右下上市</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr"/>
       <c r="C141" t="n">
-        <v>0.09124</v>
+        <v>43.787224</v>
       </c>
       <c r="D141" t="n">
-        <v>0.091242</v>
+        <v>39.275066</v>
       </c>
       <c r="E141" t="n">
-        <v>0.112558</v>
+        <v>40.346396</v>
       </c>
       <c r="F141" t="n">
-        <v>0.294298</v>
+        <v>55.382448</v>
       </c>
       <c r="G141" t="n">
-        <v>0.204111</v>
+        <v>41.834918</v>
       </c>
       <c r="H141" t="n">
-        <v>0.346172</v>
+        <v>50.073944</v>
       </c>
       <c r="I141" t="n">
-        <v>0.360224</v>
+        <v>62.3224</v>
       </c>
       <c r="J141" t="n">
-        <v>0.179417</v>
+        <v>67.592972</v>
+      </c>
+      <c r="K141" t="n">
+        <v>43.980049</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右下上市</t>
-        </is>
-      </c>
-      <c r="B142" t="n">
-        <v>65.49185300000001</v>
-      </c>
+          <t>電器電纜平上市</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
       <c r="C142" t="n">
-        <v>41.538122</v>
+        <v>99.887826</v>
       </c>
       <c r="D142" t="n">
-        <v>39.275066</v>
+        <v>77.739137</v>
       </c>
       <c r="E142" t="n">
-        <v>40.346396</v>
+        <v>209.825689</v>
       </c>
       <c r="F142" t="n">
-        <v>55.382448</v>
+        <v>235.661816</v>
       </c>
       <c r="G142" t="n">
-        <v>41.834918</v>
+        <v>208.646021</v>
       </c>
       <c r="H142" t="n">
-        <v>50.073944</v>
+        <v>123.77293</v>
       </c>
       <c r="I142" t="n">
-        <v>62.3224</v>
+        <v>148.512708</v>
       </c>
       <c r="J142" t="n">
-        <v>50.570646</v>
+        <v>98.56483299999999</v>
+      </c>
+      <c r="K142" t="n">
+        <v>263.119998</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>電器電纜平上市</t>
-        </is>
-      </c>
-      <c r="B143" t="n">
-        <v>197.780769</v>
-      </c>
+          <t>電子通路業右上上市</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
       <c r="C143" t="n">
-        <v>170.127462</v>
+        <v>8812.877887000001</v>
       </c>
       <c r="D143" t="n">
-        <v>116.254235</v>
+        <v>5102.029062</v>
       </c>
       <c r="E143" t="n">
-        <v>420.560636</v>
+        <v>4956.241487</v>
       </c>
       <c r="F143" t="n">
-        <v>44.797637</v>
+        <v>6977.782428</v>
       </c>
       <c r="G143" t="n">
-        <v>21.090587</v>
+        <v>5324.52747</v>
       </c>
       <c r="H143" t="n">
-        <v>11.466549</v>
+        <v>4295.648634</v>
       </c>
       <c r="I143" t="n">
-        <v>148.512708</v>
+        <v>4441.152525</v>
       </c>
       <c r="J143" t="n">
-        <v>17.022326</v>
+        <v>3165.79443</v>
+      </c>
+      <c r="K143" t="n">
+        <v>3731.960483</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右上上市</t>
-        </is>
-      </c>
-      <c r="B144" t="n">
-        <v>3533.092438</v>
-      </c>
+          <t>電子通路業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr"/>
       <c r="C144" t="n">
-        <v>7357.524566</v>
+        <v>0.175163</v>
       </c>
       <c r="D144" t="n">
-        <v>3162.15291</v>
+        <v>0.181565</v>
       </c>
       <c r="E144" t="n">
-        <v>3504.588651</v>
+        <v>0.5808489999999999</v>
       </c>
       <c r="F144" t="n">
-        <v>4790.204438</v>
+        <v>0.489402</v>
       </c>
       <c r="G144" t="n">
-        <v>2482.396615</v>
+        <v>0.342086</v>
       </c>
       <c r="H144" t="n">
-        <v>2318.877637</v>
+        <v>0.580444</v>
       </c>
       <c r="I144" t="n">
-        <v>2511.741979</v>
+        <v>0.842812</v>
       </c>
       <c r="J144" t="n">
-        <v>1612.453768</v>
+        <v>0.375448</v>
+      </c>
+      <c r="K144" t="n">
+        <v>0.283862</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B145" t="n">
-        <v>0.291336</v>
-      </c>
+          <t>電子通路業右下上市</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
       <c r="C145" t="n">
-        <v>0.107882</v>
+        <v>5.689849</v>
       </c>
       <c r="D145" t="n">
-        <v>0.127115</v>
+        <v>27.712111</v>
       </c>
       <c r="E145" t="n">
-        <v>0.114703</v>
+        <v>18.247482</v>
       </c>
       <c r="F145" t="n">
-        <v>0.131196</v>
+        <v>12.283079</v>
       </c>
       <c r="G145" t="n">
-        <v>0.332757</v>
+        <v>13.321644</v>
       </c>
       <c r="H145" t="n">
-        <v>0.374888</v>
+        <v>11.089148</v>
       </c>
       <c r="I145" t="n">
-        <v>0.545445</v>
+        <v>13.469439</v>
       </c>
       <c r="J145" t="n">
-        <v>0.119233</v>
+        <v>11.420697</v>
+      </c>
+      <c r="K145" t="n">
+        <v>8.435860999999999</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右下上市</t>
-        </is>
-      </c>
-      <c r="B146" t="n">
-        <v>10.344134</v>
-      </c>
+          <t>電子通路業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
       <c r="C146" t="n">
-        <v>5.689849</v>
+        <v>0.173565</v>
       </c>
       <c r="D146" t="n">
-        <v>6.727905</v>
+        <v>0.06376800000000001</v>
       </c>
       <c r="E146" t="n">
-        <v>18.247482</v>
+        <v>0.0418</v>
       </c>
       <c r="F146" t="n">
-        <v>12.283079</v>
+        <v>0.04535</v>
       </c>
       <c r="G146" t="n">
-        <v>13.321644</v>
+        <v>0.081911</v>
       </c>
       <c r="H146" t="n">
-        <v>11.089148</v>
+        <v>0.022376</v>
       </c>
       <c r="I146" t="n">
-        <v>13.469439</v>
+        <v>0.01177</v>
       </c>
       <c r="J146" t="n">
-        <v>11.420697</v>
+        <v>0.012023</v>
+      </c>
+      <c r="K146" t="n">
+        <v>0.015477</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B147" t="n">
-        <v>0.033982</v>
-      </c>
+          <t>電子通路業平上市</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
       <c r="C147" t="n">
-        <v>0.173565</v>
+        <v>82.50335</v>
       </c>
       <c r="D147" t="n">
-        <v>0.06376800000000001</v>
+        <v>75.70770899999999</v>
       </c>
       <c r="E147" t="n">
-        <v>0.0418</v>
+        <v>92.376355</v>
       </c>
       <c r="F147" t="n">
-        <v>0.04535</v>
+        <v>56.915993</v>
       </c>
       <c r="G147" t="n">
-        <v>0.081911</v>
+        <v>37.381351</v>
       </c>
       <c r="H147" t="n">
-        <v>0.022376</v>
+        <v>54.291443</v>
       </c>
       <c r="I147" t="n">
-        <v>0.01177</v>
+        <v>65.30397000000001</v>
       </c>
       <c r="J147" t="n">
-        <v>0.012023</v>
+        <v>186.188924</v>
+      </c>
+      <c r="K147" t="n">
+        <v>99.144873</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>電子通路業平上市</t>
-        </is>
-      </c>
-      <c r="B148" t="n">
-        <v>2400.502435</v>
-      </c>
+          <t>電子通路業平上櫃</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
       <c r="C148" t="n">
-        <v>1537.856671</v>
+        <v>0.266881</v>
       </c>
       <c r="D148" t="n">
-        <v>2036.568067</v>
+        <v>0.223138</v>
       </c>
       <c r="E148" t="n">
-        <v>1544.029191</v>
+        <v>0.000586</v>
       </c>
       <c r="F148" t="n">
-        <v>2244.493983</v>
+        <v>0.001673</v>
       </c>
       <c r="G148" t="n">
-        <v>2879.512206</v>
-      </c>
-      <c r="H148" t="n">
-        <v>2031.06244</v>
-      </c>
-      <c r="I148" t="n">
-        <v>1994.714516</v>
-      </c>
+        <v>0.263543</v>
+      </c>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
       <c r="J148" t="n">
-        <v>1739.529586</v>
+        <v>0.002617</v>
+      </c>
+      <c r="K148" t="n">
+        <v>0.001266</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>電子通路業平上櫃</t>
-        </is>
-      </c>
-      <c r="B149" t="n">
-        <v>0.481713</v>
-      </c>
+          <t>電子零組件業右上上市</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
       <c r="C149" t="n">
-        <v>0.334162</v>
+        <v>203807.94402</v>
       </c>
       <c r="D149" t="n">
-        <v>0.277588</v>
+        <v>192682.277067</v>
       </c>
       <c r="E149" t="n">
-        <v>0.466732</v>
+        <v>192593.179829</v>
       </c>
       <c r="F149" t="n">
-        <v>0.359879</v>
+        <v>189811.564786</v>
       </c>
       <c r="G149" t="n">
-        <v>0.272872</v>
+        <v>238926.971192</v>
       </c>
       <c r="H149" t="n">
-        <v>0.205556</v>
+        <v>303673.461318</v>
       </c>
       <c r="I149" t="n">
-        <v>0.297367</v>
+        <v>337227.393779</v>
       </c>
       <c r="J149" t="n">
-        <v>0.258832</v>
+        <v>297664.221548</v>
+      </c>
+      <c r="K149" t="n">
+        <v>289353.972438</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右上上市</t>
-        </is>
-      </c>
-      <c r="B150" t="n">
-        <v>165334.465168</v>
-      </c>
+          <t>電子零組件業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
       <c r="C150" t="n">
-        <v>202291.836966</v>
+        <v>27.426623</v>
       </c>
       <c r="D150" t="n">
-        <v>189680.575138</v>
+        <v>39.0586</v>
       </c>
       <c r="E150" t="n">
-        <v>168759.788961</v>
+        <v>32.142848</v>
       </c>
       <c r="F150" t="n">
-        <v>175055.014039</v>
+        <v>32.894592</v>
       </c>
       <c r="G150" t="n">
-        <v>219810.875587</v>
+        <v>52.55861</v>
       </c>
       <c r="H150" t="n">
-        <v>295285.351175</v>
+        <v>68.182243</v>
       </c>
       <c r="I150" t="n">
-        <v>328265.311909</v>
+        <v>78.045886</v>
       </c>
       <c r="J150" t="n">
-        <v>288190.134832</v>
+        <v>69.266969</v>
+      </c>
+      <c r="K150" t="n">
+        <v>71.62496</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B151" t="n">
-        <v>41.06388</v>
-      </c>
+          <t>電子零組件業右下上市</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
       <c r="C151" t="n">
-        <v>25.823852</v>
+        <v>947.526689</v>
       </c>
       <c r="D151" t="n">
-        <v>37.603645</v>
+        <v>744.89184</v>
       </c>
       <c r="E151" t="n">
-        <v>29.674985</v>
+        <v>967.6923860000001</v>
       </c>
       <c r="F151" t="n">
-        <v>28.779912</v>
+        <v>1142.26238</v>
       </c>
       <c r="G151" t="n">
-        <v>49.045555</v>
+        <v>948.549808</v>
       </c>
       <c r="H151" t="n">
-        <v>64.95413499999999</v>
+        <v>847.233592</v>
       </c>
       <c r="I151" t="n">
-        <v>73.40257800000001</v>
+        <v>1370.806459</v>
       </c>
       <c r="J151" t="n">
-        <v>67.14289100000001</v>
+        <v>1013.098361</v>
+      </c>
+      <c r="K151" t="n">
+        <v>1434.948491</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右下上市</t>
-        </is>
-      </c>
-      <c r="B152" t="n">
-        <v>4168.602855</v>
-      </c>
+          <t>電子零組件業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
       <c r="C152" t="n">
-        <v>7165.028589</v>
+        <v>0.564804</v>
       </c>
       <c r="D152" t="n">
-        <v>3340.325803</v>
+        <v>0.606082</v>
       </c>
       <c r="E152" t="n">
-        <v>5280.673074</v>
+        <v>0.328547</v>
       </c>
       <c r="F152" t="n">
-        <v>2364.317114</v>
+        <v>0.904578</v>
       </c>
       <c r="G152" t="n">
-        <v>2046.42661</v>
+        <v>0.62054</v>
       </c>
       <c r="H152" t="n">
-        <v>2344.140071</v>
+        <v>0.569536</v>
       </c>
       <c r="I152" t="n">
-        <v>3827.341422</v>
+        <v>1.031513</v>
       </c>
       <c r="J152" t="n">
-        <v>3178.747745</v>
+        <v>0.948043</v>
+      </c>
+      <c r="K152" t="n">
+        <v>0.728827</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B153" t="n">
-        <v>1.339275</v>
-      </c>
+          <t>電子零組件業平上市</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr"/>
       <c r="C153" t="n">
-        <v>0.87322</v>
+        <v>7314.585275</v>
       </c>
       <c r="D153" t="n">
-        <v>0.901962</v>
+        <v>3323.928044</v>
       </c>
       <c r="E153" t="n">
-        <v>0.574451</v>
+        <v>4869.715431</v>
       </c>
       <c r="F153" t="n">
-        <v>1.249787</v>
+        <v>6364.882629</v>
       </c>
       <c r="G153" t="n">
-        <v>1.073411</v>
+        <v>1607.896464</v>
       </c>
       <c r="H153" t="n">
-        <v>0.757948</v>
+        <v>1967.018327</v>
       </c>
       <c r="I153" t="n">
-        <v>1.243945</v>
+        <v>3271.617284</v>
       </c>
       <c r="J153" t="n">
-        <v>1.071785</v>
+        <v>2554.075233</v>
+      </c>
+      <c r="K153" t="n">
+        <v>3198.448681</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業平上市</t>
-        </is>
-      </c>
-      <c r="B154" t="n">
-        <v>40934.241108</v>
-      </c>
+          <t>電子零組件業平上櫃</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr"/>
       <c r="C154" t="n">
-        <v>2613.190429</v>
+        <v>0.307117</v>
       </c>
       <c r="D154" t="n">
-        <v>3730.19601</v>
+        <v>0.344598</v>
       </c>
       <c r="E154" t="n">
-        <v>24390.125611</v>
+        <v>1.047481</v>
       </c>
       <c r="F154" t="n">
-        <v>19899.378642</v>
+        <v>0.342189</v>
       </c>
       <c r="G154" t="n">
-        <v>19626.115267</v>
+        <v>0.458811</v>
       </c>
       <c r="H154" t="n">
-        <v>8858.221991</v>
+        <v>0.403766</v>
       </c>
       <c r="I154" t="n">
-        <v>9777.164191</v>
+        <v>0.541299</v>
       </c>
       <c r="J154" t="n">
-        <v>9862.512565000001</v>
+        <v>0.335978</v>
+      </c>
+      <c r="K154" t="n">
+        <v>0.282854</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業平上櫃</t>
-        </is>
-      </c>
-      <c r="B155" t="n">
-        <v>3.729705</v>
-      </c>
+          <t>電機機械右上上市</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr"/>
       <c r="C155" t="n">
-        <v>1.601472</v>
+        <v>20653.023269</v>
       </c>
       <c r="D155" t="n">
-        <v>1.503673</v>
+        <v>17783.28272</v>
       </c>
       <c r="E155" t="n">
-        <v>3.26944</v>
+        <v>17698.696071</v>
       </c>
       <c r="F155" t="n">
-        <v>4.11166</v>
+        <v>17107.566288</v>
       </c>
       <c r="G155" t="n">
-        <v>3.518995</v>
+        <v>21736.79682</v>
       </c>
       <c r="H155" t="n">
-        <v>3.443462</v>
+        <v>20870.148901</v>
       </c>
       <c r="I155" t="n">
-        <v>4.972175</v>
+        <v>9721.052197000001</v>
       </c>
       <c r="J155" t="n">
-        <v>2.336314</v>
+        <v>6786.646732</v>
+      </c>
+      <c r="K155" t="n">
+        <v>8013.519252</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>電機機械右上上市</t>
-        </is>
-      </c>
-      <c r="B156" t="n">
-        <v>20018.210526</v>
-      </c>
+          <t>電機機械右上上櫃</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr"/>
       <c r="C156" t="n">
-        <v>19665.379644</v>
+        <v>0.736514</v>
       </c>
       <c r="D156" t="n">
-        <v>16041.960584</v>
+        <v>0.901869</v>
       </c>
       <c r="E156" t="n">
-        <v>16397.971383</v>
+        <v>2.045405</v>
       </c>
       <c r="F156" t="n">
-        <v>15648.185563</v>
+        <v>1.835066</v>
       </c>
       <c r="G156" t="n">
-        <v>20759.210972</v>
+        <v>3.495789</v>
       </c>
       <c r="H156" t="n">
-        <v>19153.740726</v>
+        <v>2.265916</v>
       </c>
       <c r="I156" t="n">
-        <v>8966.400874999999</v>
+        <v>1.696695</v>
       </c>
       <c r="J156" t="n">
-        <v>5616.545071</v>
+        <v>1.120019</v>
+      </c>
+      <c r="K156" t="n">
+        <v>0.915351</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>電機機械右上上櫃</t>
-        </is>
-      </c>
-      <c r="B157" t="n">
-        <v>0.406659</v>
-      </c>
+          <t>電機機械右下上市</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr"/>
       <c r="C157" t="n">
-        <v>0.255269</v>
+        <v>560.189292</v>
       </c>
       <c r="D157" t="n">
-        <v>0.281269</v>
+        <v>497.79934625</v>
       </c>
       <c r="E157" t="n">
-        <v>1.930055</v>
+        <v>484.273872</v>
       </c>
       <c r="F157" t="n">
-        <v>1.779102</v>
+        <v>1003.984237</v>
       </c>
       <c r="G157" t="n">
-        <v>3.481795</v>
+        <v>1204.163042</v>
       </c>
       <c r="H157" t="n">
-        <v>2.240837</v>
+        <v>803.446879</v>
       </c>
       <c r="I157" t="n">
-        <v>1.575423</v>
+        <v>871.467301</v>
       </c>
       <c r="J157" t="n">
-        <v>1.048016</v>
+        <v>587.305118</v>
+      </c>
+      <c r="K157" t="n">
+        <v>819.2347559999999</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>電機機械右下上市</t>
+          <t>電機機械右下上櫃</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>960.535046</v>
+        <v>0</v>
       </c>
       <c r="C158" t="n">
-        <v>1205.127393</v>
+        <v>0.07478633333333333</v>
       </c>
       <c r="D158" t="n">
-        <v>1278.56809225</v>
+        <v>0.065455</v>
       </c>
       <c r="E158" t="n">
-        <v>1352.800315</v>
+        <v>0.080192</v>
       </c>
       <c r="F158" t="n">
-        <v>1402.402289</v>
+        <v>0.106241</v>
       </c>
       <c r="G158" t="n">
-        <v>904.3769</v>
+        <v>0.07116375</v>
       </c>
       <c r="H158" t="n">
-        <v>1280.301169</v>
+        <v>0.08146200000000001</v>
       </c>
       <c r="I158" t="n">
-        <v>1389.069581</v>
+        <v>0.14959675</v>
       </c>
       <c r="J158" t="n">
-        <v>981.387952</v>
+        <v>0.111443</v>
+      </c>
+      <c r="K158" t="n">
+        <v>0.097276</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>電機機械右下上櫃</t>
-        </is>
-      </c>
-      <c r="B159" t="n">
-        <v>0.100141</v>
-      </c>
+          <t>電機機械平上市</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr"/>
       <c r="C159" t="n">
-        <v>0.1047293333333333</v>
+        <v>793.736661</v>
       </c>
       <c r="D159" t="n">
-        <v>0.070176</v>
+        <v>940.936506</v>
       </c>
       <c r="E159" t="n">
-        <v>0.085379</v>
+        <v>1314.555229</v>
       </c>
       <c r="F159" t="n">
-        <v>0.128986</v>
+        <v>1599.750557</v>
       </c>
       <c r="G159" t="n">
-        <v>0.09494175000000001</v>
+        <v>1141.213827</v>
       </c>
       <c r="H159" t="n">
-        <v>0.145845</v>
+        <v>1297.029295</v>
       </c>
       <c r="I159" t="n">
-        <v>0.17716775</v>
+        <v>1389.228828</v>
       </c>
       <c r="J159" t="n">
-        <v>0.144214</v>
+        <v>1546.665107</v>
+      </c>
+      <c r="K159" t="n">
+        <v>3782.111008</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>電機機械平上市</t>
-        </is>
-      </c>
-      <c r="B160" t="n">
-        <v>2449.834377</v>
-      </c>
+          <t>電機機械平上櫃</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr"/>
       <c r="C160" t="n">
-        <v>1136.442185</v>
+        <v>0.222908</v>
       </c>
       <c r="D160" t="n">
-        <v>1901.489896</v>
+        <v>0.152168</v>
       </c>
       <c r="E160" t="n">
-        <v>1746.753474</v>
+        <v>0.040177</v>
       </c>
       <c r="F160" t="n">
-        <v>2660.71323</v>
+        <v>0.09173000000000001</v>
       </c>
       <c r="G160" t="n">
-        <v>2418.585817</v>
+        <v>0.086632</v>
       </c>
       <c r="H160" t="n">
-        <v>2536.58318</v>
+        <v>0.121969</v>
       </c>
       <c r="I160" t="n">
-        <v>1626.27787</v>
+        <v>0.061874</v>
       </c>
       <c r="J160" t="n">
-        <v>2322.683934</v>
+        <v>0.06553</v>
+      </c>
+      <c r="K160" t="n">
+        <v>0.053388</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>電機機械平上櫃</t>
-        </is>
-      </c>
-      <c r="B161" t="n">
-        <v>0.979351</v>
-      </c>
+          <t>電腦及週邊設備業右上上市</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr"/>
       <c r="C161" t="n">
-        <v>0.675076</v>
+        <v>30947.277086</v>
       </c>
       <c r="D161" t="n">
-        <v>0.768943</v>
+        <v>31226.702936</v>
       </c>
       <c r="E161" t="n">
-        <v>0.155259</v>
+        <v>43544.851477</v>
       </c>
       <c r="F161" t="n">
-        <v>0.127739</v>
+        <v>38030.459823</v>
       </c>
       <c r="G161" t="n">
-        <v>0.081984</v>
+        <v>43116.131312</v>
       </c>
       <c r="H161" t="n">
-        <v>0.084762</v>
+        <v>38475.016145</v>
       </c>
       <c r="I161" t="n">
-        <v>0.158662</v>
+        <v>57387.377591</v>
       </c>
       <c r="J161" t="n">
-        <v>0.106951</v>
+        <v>40776.142185</v>
+      </c>
+      <c r="K161" t="n">
+        <v>42240.877192</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上上市</t>
-        </is>
-      </c>
-      <c r="B162" t="n">
-        <v>43335.107824</v>
-      </c>
+          <t>電腦及週邊設備業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr"/>
       <c r="C162" t="n">
-        <v>31110.029175</v>
+        <v>6.282676</v>
       </c>
       <c r="D162" t="n">
-        <v>31285.393991</v>
+        <v>4.662939</v>
       </c>
       <c r="E162" t="n">
-        <v>43834.111024</v>
+        <v>6.909672</v>
       </c>
       <c r="F162" t="n">
-        <v>38144.865106</v>
+        <v>9.003401</v>
       </c>
       <c r="G162" t="n">
-        <v>42702.884281</v>
+        <v>5.14031</v>
       </c>
       <c r="H162" t="n">
-        <v>38943.162022</v>
+        <v>5.0927</v>
       </c>
       <c r="I162" t="n">
-        <v>57897.018994</v>
+        <v>6.116877</v>
       </c>
       <c r="J162" t="n">
-        <v>41469.300152</v>
+        <v>11.366636</v>
+      </c>
+      <c r="K162" t="n">
+        <v>7.158511</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上上櫃</t>
+          <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>6.813135</v>
+        <v>0</v>
       </c>
       <c r="C163" t="n">
-        <v>3.458445</v>
+        <v>6486.051783</v>
       </c>
       <c r="D163" t="n">
-        <v>3.286976</v>
+        <v>7857.032012</v>
       </c>
       <c r="E163" t="n">
-        <v>5.63341</v>
+        <v>3699.843837</v>
       </c>
       <c r="F163" t="n">
-        <v>7.647517</v>
+        <v>4448.901824</v>
       </c>
       <c r="G163" t="n">
-        <v>4.386462</v>
+        <v>3383.67531</v>
       </c>
       <c r="H163" t="n">
-        <v>3.744373</v>
+        <v>5495.817378</v>
       </c>
       <c r="I163" t="n">
-        <v>4.552767</v>
+        <v>6999.368153</v>
       </c>
       <c r="J163" t="n">
-        <v>9.666439</v>
+        <v>12966.009578</v>
+      </c>
+      <c r="K163" t="n">
+        <v>9166.494794</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上市</t>
-        </is>
-      </c>
-      <c r="B164" t="n">
-        <v>15058.478097</v>
-      </c>
+          <t>電腦及週邊設備業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr"/>
       <c r="C164" t="n">
-        <v>8090.653738</v>
+        <v>0.1157325</v>
       </c>
       <c r="D164" t="n">
-        <v>8372.407546</v>
+        <v>0.082056</v>
       </c>
       <c r="E164" t="n">
-        <v>5011.133429</v>
+        <v>0.145013</v>
       </c>
       <c r="F164" t="n">
-        <v>9046.637635999999</v>
+        <v>0.137024</v>
       </c>
       <c r="G164" t="n">
-        <v>6167.77495</v>
+        <v>0.088251</v>
       </c>
       <c r="H164" t="n">
-        <v>7418.865709</v>
+        <v>0.14626925</v>
       </c>
       <c r="I164" t="n">
-        <v>12062.739108</v>
+        <v>0.301019</v>
       </c>
       <c r="J164" t="n">
-        <v>15563.819925</v>
+        <v>0.14562</v>
+      </c>
+      <c r="K164" t="n">
+        <v>0.125388</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B165" t="n">
-        <v>0.168679</v>
-      </c>
+          <t>電腦及週邊設備業平上市</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr"/>
       <c r="C165" t="n">
-        <v>0.1089475</v>
+        <v>2084.363452</v>
       </c>
       <c r="D165" t="n">
-        <v>0.087995</v>
+        <v>1207.281724</v>
       </c>
       <c r="E165" t="n">
-        <v>0.151576</v>
+        <v>2001.170332</v>
       </c>
       <c r="F165" t="n">
-        <v>0.163469</v>
+        <v>5258.593556</v>
       </c>
       <c r="G165" t="n">
-        <v>0.09155199999999999</v>
+        <v>3224.870738</v>
       </c>
       <c r="H165" t="n">
-        <v>0.15035425</v>
+        <v>2770.292382</v>
       </c>
       <c r="I165" t="n">
-        <v>0.321696</v>
+        <v>5976.974793</v>
       </c>
       <c r="J165" t="n">
-        <v>0.144102</v>
+        <v>3705.261968</v>
+      </c>
+      <c r="K165" t="n">
+        <v>3041.954715</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上市</t>
-        </is>
-      </c>
-      <c r="B166" t="n">
-        <v>429.318786</v>
-      </c>
+          <t>電腦及週邊設備業平上櫃</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr"/>
       <c r="C166" t="n">
-        <v>328.729665</v>
+        <v>0.239754</v>
       </c>
       <c r="D166" t="n">
-        <v>642.189541</v>
+        <v>0.102567</v>
       </c>
       <c r="E166" t="n">
-        <v>458.611679</v>
+        <v>0.160217</v>
       </c>
       <c r="F166" t="n">
-        <v>610.820832</v>
+        <v>0.216791</v>
       </c>
       <c r="G166" t="n">
-        <v>904.703303</v>
+        <v>0.146328</v>
       </c>
       <c r="H166" t="n">
-        <v>424.428801</v>
+        <v>0.150315</v>
       </c>
       <c r="I166" t="n">
-        <v>459.768489</v>
+        <v>0.28927</v>
       </c>
       <c r="J166" t="n">
-        <v>468.411875</v>
+        <v>0.493956</v>
+      </c>
+      <c r="K166" t="n">
+        <v>0.158057</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上櫃</t>
-        </is>
-      </c>
-      <c r="B167" t="n">
-        <v>1.749221</v>
-      </c>
+          <t>食品工業右上上市</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr"/>
       <c r="C167" t="n">
-        <v>3.07077</v>
+        <v>19.176035</v>
       </c>
       <c r="D167" t="n">
-        <v>1.472591</v>
+        <v>18.254504</v>
       </c>
       <c r="E167" t="n">
-        <v>1.429916</v>
+        <v>15.030035</v>
       </c>
       <c r="F167" t="n">
-        <v>1.54623</v>
+        <v>22.714533</v>
       </c>
       <c r="G167" t="n">
-        <v>0.896875</v>
+        <v>18.953213</v>
       </c>
       <c r="H167" t="n">
-        <v>1.494557</v>
+        <v>13.274733</v>
       </c>
       <c r="I167" t="n">
-        <v>1.832703</v>
+        <v>16.692089</v>
       </c>
       <c r="J167" t="n">
-        <v>2.195671</v>
+        <v>21.559752</v>
+      </c>
+      <c r="K167" t="n">
+        <v>18.253658</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>食品工業右上上市</t>
-        </is>
-      </c>
-      <c r="B168" t="n">
-        <v>10.989736</v>
-      </c>
+          <t>食品工業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr"/>
       <c r="C168" t="n">
-        <v>586.277846</v>
+        <v>0.002534</v>
       </c>
       <c r="D168" t="n">
-        <v>7.264615</v>
+        <v>0.004008</v>
       </c>
       <c r="E168" t="n">
-        <v>8.02271</v>
+        <v>0.005365</v>
       </c>
       <c r="F168" t="n">
-        <v>11.865974</v>
+        <v>0.005112</v>
       </c>
       <c r="G168" t="n">
-        <v>16.580074</v>
+        <v>0.007178</v>
       </c>
       <c r="H168" t="n">
-        <v>7.674888</v>
+        <v>0.006919</v>
       </c>
       <c r="I168" t="n">
-        <v>9.180273</v>
+        <v>0.008226000000000001</v>
       </c>
       <c r="J168" t="n">
-        <v>15.211594</v>
+        <v>0.011837</v>
+      </c>
+      <c r="K168" t="n">
+        <v>0.005358</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>食品工業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B169" t="n">
-        <v>0.004336</v>
-      </c>
+          <t>食品工業右下上市</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr"/>
       <c r="C169" t="n">
-        <v>0.002534</v>
+        <v>293.333234</v>
       </c>
       <c r="D169" t="n">
-        <v>0.001886</v>
+        <v>649.727039</v>
       </c>
       <c r="E169" t="n">
-        <v>0.003556</v>
+        <v>802.013354</v>
       </c>
       <c r="F169" t="n">
-        <v>0.004412</v>
+        <v>777.085777</v>
       </c>
       <c r="G169" t="n">
-        <v>0.005225</v>
+        <v>703.082083</v>
       </c>
       <c r="H169" t="n">
-        <v>0.005884</v>
+        <v>1688.815661</v>
       </c>
       <c r="I169" t="n">
-        <v>0.005327</v>
+        <v>1095.910492</v>
       </c>
       <c r="J169" t="n">
-        <v>0.00641</v>
+        <v>1250.899618</v>
+      </c>
+      <c r="K169" t="n">
+        <v>238.762793</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>食品工業右下上市</t>
-        </is>
-      </c>
-      <c r="B170" t="n">
-        <v>412.232246</v>
-      </c>
+          <t>食品工業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr"/>
       <c r="C170" t="n">
-        <v>284.234782</v>
+        <v>0.01134</v>
       </c>
       <c r="D170" t="n">
-        <v>286.797627</v>
+        <v>0.010856</v>
       </c>
       <c r="E170" t="n">
-        <v>318.886002</v>
+        <v>0.005911</v>
       </c>
       <c r="F170" t="n">
-        <v>261.472583</v>
+        <v>0.010054</v>
       </c>
       <c r="G170" t="n">
-        <v>264.272879</v>
+        <v>0.006973</v>
       </c>
       <c r="H170" t="n">
-        <v>1688.815661</v>
+        <v>0.010705</v>
       </c>
       <c r="I170" t="n">
-        <v>1095.910492</v>
+        <v>0.016031</v>
       </c>
       <c r="J170" t="n">
-        <v>307.941446</v>
+        <v>0.010104</v>
+      </c>
+      <c r="K170" t="n">
+        <v>0.017923</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t>食品工業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B171" t="n">
-        <v>0.014792</v>
-      </c>
+          <t>食品工業平上市</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr"/>
       <c r="C171" t="n">
-        <v>0.01134</v>
-      </c>
-      <c r="D171" t="n">
-        <v>0.010856</v>
-      </c>
-      <c r="E171" t="n">
-        <v>0.005911</v>
-      </c>
-      <c r="F171" t="n">
-        <v>0.010054</v>
-      </c>
-      <c r="G171" t="n">
-        <v>0.006973</v>
-      </c>
-      <c r="H171" t="n">
-        <v>0.010705</v>
-      </c>
-      <c r="I171" t="n">
-        <v>0.016031</v>
-      </c>
-      <c r="J171" t="n">
-        <v>0.010104</v>
+        <v>575.713856</v>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="n">
+        <v>1172.593425</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t>食品工業平上市</t>
-        </is>
-      </c>
-      <c r="B172" t="n">
-        <v>500.595241</v>
-      </c>
+          <t>食品工業平上櫃</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr"/>
       <c r="C172" t="n">
-        <v>17.710497</v>
+        <v>0.002383</v>
       </c>
       <c r="D172" t="n">
-        <v>373.919301</v>
+        <v>0.002487</v>
       </c>
       <c r="E172" t="n">
-        <v>490.134677</v>
-      </c>
-      <c r="F172" t="n">
-        <v>526.461753</v>
-      </c>
-      <c r="G172" t="n">
-        <v>441.182343</v>
-      </c>
-      <c r="H172" t="n">
-        <v>5.599845</v>
-      </c>
-      <c r="I172" t="n">
-        <v>7.511816</v>
-      </c>
+        <v>0.001516</v>
+      </c>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
       <c r="J172" t="n">
-        <v>949.30633</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="1" t="inlineStr">
-        <is>
-          <t>食品工業平上櫃</t>
-        </is>
-      </c>
-      <c r="B173" t="n">
-        <v>0.000831</v>
-      </c>
-      <c r="C173" t="n">
-        <v>0.002383</v>
-      </c>
-      <c r="D173" t="n">
-        <v>0.004609</v>
-      </c>
-      <c r="E173" t="n">
-        <v>0.003325</v>
-      </c>
-      <c r="F173" t="n">
-        <v>0.0007</v>
-      </c>
-      <c r="G173" t="n">
-        <v>0.001953</v>
-      </c>
-      <c r="H173" t="n">
-        <v>0.001035</v>
-      </c>
-      <c r="I173" t="n">
-        <v>0.002899</v>
-      </c>
-      <c r="J173" t="n">
-        <v>0.007135</v>
+        <v>0.001708</v>
+      </c>
+      <c r="K172" t="n">
+        <v>0.001524</v>
       </c>
     </row>
   </sheetData>

--- a/Result/analyze_2.xlsx
+++ b/Result/analyze_2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K172"/>
+  <dimension ref="A1:J175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,52 +436,47 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -491,33 +486,32 @@
           <t>光電業右上上市</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="n">
+        <v>46586.686312</v>
+      </c>
       <c r="C2" t="n">
-        <v>77016.14013699999</v>
+        <v>51636.891594</v>
       </c>
       <c r="D2" t="n">
-        <v>47630.618118</v>
+        <v>86070.802371</v>
       </c>
       <c r="E2" t="n">
-        <v>52329.13654</v>
+        <v>106432.610774</v>
       </c>
       <c r="F2" t="n">
-        <v>87049.123955</v>
+        <v>74175.14004899999</v>
       </c>
       <c r="G2" t="n">
-        <v>107133.497541</v>
+        <v>106634.769564</v>
       </c>
       <c r="H2" t="n">
-        <v>74782.54464199999</v>
+        <v>72074.281301</v>
       </c>
       <c r="I2" t="n">
-        <v>107205.401757</v>
+        <v>66207.42778300001</v>
       </c>
       <c r="J2" t="n">
-        <v>72654.152778</v>
-      </c>
-      <c r="K2" t="n">
-        <v>66320.88806300001</v>
+        <v>47919.945116</v>
       </c>
     </row>
     <row r="3">
@@ -526,33 +520,32 @@
           <t>光電業右上上櫃</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="n">
+        <v>4.200368</v>
+      </c>
       <c r="C3" t="n">
-        <v>2.333941</v>
+        <v>6.813472</v>
       </c>
       <c r="D3" t="n">
-        <v>4.980801</v>
+        <v>6.721156</v>
       </c>
       <c r="E3" t="n">
-        <v>6.981326</v>
+        <v>6.072605</v>
       </c>
       <c r="F3" t="n">
-        <v>7.06809</v>
+        <v>12.53609</v>
       </c>
       <c r="G3" t="n">
-        <v>6.161525</v>
+        <v>11.669936</v>
       </c>
       <c r="H3" t="n">
-        <v>12.623548</v>
+        <v>12.236182</v>
       </c>
       <c r="I3" t="n">
-        <v>11.680688</v>
+        <v>15.627309</v>
       </c>
       <c r="J3" t="n">
-        <v>12.179591</v>
-      </c>
-      <c r="K3" t="n">
-        <v>15.56866</v>
+        <v>3.781644</v>
       </c>
     </row>
     <row r="4">
@@ -561,33 +554,32 @@
           <t>光電業右下上市</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="n">
+        <v>1742.583713</v>
+      </c>
       <c r="C4" t="n">
-        <v>803.809093</v>
+        <v>898.356579</v>
       </c>
       <c r="D4" t="n">
-        <v>1122.927252</v>
+        <v>1542.59659</v>
       </c>
       <c r="E4" t="n">
-        <v>488.403628</v>
+        <v>627.005644</v>
       </c>
       <c r="F4" t="n">
-        <v>990.094939</v>
+        <v>809.753993</v>
       </c>
       <c r="G4" t="n">
-        <v>674.890955</v>
+        <v>874.586958</v>
       </c>
       <c r="H4" t="n">
-        <v>246.925746</v>
+        <v>1018.523287</v>
       </c>
       <c r="I4" t="n">
-        <v>510.69576</v>
+        <v>1005.810188</v>
       </c>
       <c r="J4" t="n">
-        <v>321.265563</v>
-      </c>
-      <c r="K4" t="n">
-        <v>244.648133</v>
+        <v>663.324609</v>
       </c>
     </row>
     <row r="5">
@@ -597,34 +589,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>0.944307</v>
       </c>
       <c r="C5" t="n">
-        <v>0.921492</v>
+        <v>1.31829225</v>
       </c>
       <c r="D5" t="n">
-        <v>0.880448</v>
+        <v>0.866345</v>
       </c>
       <c r="E5" t="n">
-        <v>1.27465725</v>
+        <v>0.9060865</v>
       </c>
       <c r="F5" t="n">
-        <v>0.842423</v>
+        <v>0.9748790000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7876445</v>
+        <v>1.483324</v>
       </c>
       <c r="H5" t="n">
-        <v>0.886626</v>
+        <v>1.933499</v>
       </c>
       <c r="I5" t="n">
-        <v>1.197747</v>
+        <v>1.197032</v>
       </c>
       <c r="J5" t="n">
-        <v>1.896713</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1.171862</v>
+        <v>0.740969</v>
       </c>
     </row>
     <row r="6">
@@ -633,33 +622,32 @@
           <t>光電業平上市</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="n">
+        <v>1177.582203</v>
+      </c>
       <c r="C6" t="n">
-        <v>485.820215</v>
+        <v>866.71379</v>
       </c>
       <c r="D6" t="n">
-        <v>749.766723</v>
+        <v>1194.916813</v>
       </c>
       <c r="E6" t="n">
-        <v>579.313011</v>
+        <v>1063.781628</v>
       </c>
       <c r="F6" t="n">
-        <v>753.51323</v>
+        <v>1114.478124</v>
       </c>
       <c r="G6" t="n">
-        <v>309.619091</v>
+        <v>1524.632189</v>
       </c>
       <c r="H6" t="n">
-        <v>1063.887458</v>
+        <v>1117.499227</v>
       </c>
       <c r="I6" t="n">
-        <v>1306.479152</v>
+        <v>814.384108</v>
       </c>
       <c r="J6" t="n">
-        <v>1226.272</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1457.47218</v>
+        <v>788.4981749999999</v>
       </c>
     </row>
     <row r="7">
@@ -668,33 +656,32 @@
           <t>光電業平上櫃</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="B7" t="n">
+        <v>0.936181</v>
+      </c>
       <c r="C7" t="n">
-        <v>0.247272</v>
+        <v>0.296713</v>
       </c>
       <c r="D7" t="n">
-        <v>0.215378</v>
+        <v>0.507507</v>
       </c>
       <c r="E7" t="n">
-        <v>0.163001</v>
+        <v>0.161472</v>
       </c>
       <c r="F7" t="n">
-        <v>0.173609</v>
+        <v>0.230956</v>
       </c>
       <c r="G7" t="n">
-        <v>0.180915</v>
+        <v>0.216312</v>
       </c>
       <c r="H7" t="n">
-        <v>0.219701</v>
+        <v>0.178666</v>
       </c>
       <c r="I7" t="n">
-        <v>0.485999</v>
+        <v>0.124367</v>
       </c>
       <c r="J7" t="n">
-        <v>0.266975</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.201829</v>
+        <v>0.076694</v>
       </c>
     </row>
     <row r="8">
@@ -703,33 +690,32 @@
           <t>其他右上上市</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" t="n">
+        <v>804.3266159999999</v>
+      </c>
       <c r="C8" t="n">
-        <v>718.182277</v>
+        <v>945.081587</v>
       </c>
       <c r="D8" t="n">
-        <v>808.951334</v>
+        <v>1026.433541</v>
       </c>
       <c r="E8" t="n">
-        <v>653.1447899999999</v>
+        <v>1319.534296</v>
       </c>
       <c r="F8" t="n">
-        <v>806.822822</v>
+        <v>1653.5761</v>
       </c>
       <c r="G8" t="n">
-        <v>1166.586888</v>
+        <v>2214.886948</v>
       </c>
       <c r="H8" t="n">
-        <v>1535.231402</v>
+        <v>1182.599023</v>
       </c>
       <c r="I8" t="n">
-        <v>1831.969767</v>
+        <v>1306.290477</v>
       </c>
       <c r="J8" t="n">
-        <v>989.796277</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1073.978075</v>
+        <v>1170.114009</v>
       </c>
     </row>
     <row r="9">
@@ -738,33 +724,32 @@
           <t>其他右上上櫃</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="n">
+        <v>1.36937</v>
+      </c>
       <c r="C9" t="n">
-        <v>4.256129</v>
+        <v>1.71218</v>
       </c>
       <c r="D9" t="n">
-        <v>1.379422</v>
+        <v>1.99472</v>
       </c>
       <c r="E9" t="n">
-        <v>1.720251</v>
+        <v>1.926111</v>
       </c>
       <c r="F9" t="n">
-        <v>2.001527</v>
+        <v>1.867746</v>
       </c>
       <c r="G9" t="n">
-        <v>1.927461</v>
+        <v>1.821556</v>
       </c>
       <c r="H9" t="n">
-        <v>1.869765</v>
+        <v>1.777786</v>
       </c>
       <c r="I9" t="n">
-        <v>1.821577</v>
+        <v>1.404748</v>
       </c>
       <c r="J9" t="n">
-        <v>1.759134</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1.410704</v>
+        <v>1.858279</v>
       </c>
     </row>
     <row r="10">
@@ -773,33 +758,32 @@
           <t>其他右下上市</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="n">
+        <v>821.838253</v>
+      </c>
       <c r="C10" t="n">
-        <v>1537.147381</v>
+        <v>957.630659</v>
       </c>
       <c r="D10" t="n">
-        <v>840.695142</v>
+        <v>1092.657216</v>
       </c>
       <c r="E10" t="n">
-        <v>956.589307</v>
+        <v>1151.470527</v>
       </c>
       <c r="F10" t="n">
-        <v>1092.69051</v>
+        <v>1061.894658</v>
       </c>
       <c r="G10" t="n">
-        <v>1279.983284</v>
+        <v>986.5640090000001</v>
       </c>
       <c r="H10" t="n">
-        <v>1091.299464</v>
+        <v>1214.916591</v>
       </c>
       <c r="I10" t="n">
-        <v>916.9355430000001</v>
+        <v>853.108369</v>
       </c>
       <c r="J10" t="n">
-        <v>1089.606229</v>
-      </c>
-      <c r="K10" t="n">
-        <v>777.277031</v>
+        <v>690.962795</v>
       </c>
     </row>
     <row r="11">
@@ -809,34 +793,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>0.2415985</v>
       </c>
       <c r="C11" t="n">
-        <v>0.37018525</v>
+        <v>0.308221</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2667605</v>
+        <v>0.341959</v>
       </c>
       <c r="E11" t="n">
-        <v>0.311672</v>
+        <v>2.512299</v>
       </c>
       <c r="F11" t="n">
-        <v>0.403889</v>
+        <v>0.9609550833333333</v>
       </c>
       <c r="G11" t="n">
-        <v>2.514648</v>
+        <v>1.05431</v>
       </c>
       <c r="H11" t="n">
-        <v>1.023775083333333</v>
+        <v>0.6217311666666666</v>
       </c>
       <c r="I11" t="n">
-        <v>1.053565</v>
+        <v>0.703083</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6235891666666666</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.702704</v>
+        <v>0.465413</v>
       </c>
     </row>
     <row r="12">
@@ -845,33 +826,32 @@
           <t>其他平上市</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="n">
+        <v>142.31445</v>
+      </c>
       <c r="C12" t="n">
-        <v>89.084755</v>
+        <v>164.8614</v>
       </c>
       <c r="D12" t="n">
-        <v>118.832843</v>
+        <v>148.657663</v>
       </c>
       <c r="E12" t="n">
-        <v>457.839549</v>
+        <v>246.467539</v>
       </c>
       <c r="F12" t="n">
-        <v>368.235088</v>
+        <v>179.031457</v>
       </c>
       <c r="G12" t="n">
-        <v>270.90219</v>
+        <v>146.276942</v>
       </c>
       <c r="H12" t="n">
-        <v>267.971349</v>
+        <v>53.90317</v>
       </c>
       <c r="I12" t="n">
-        <v>598.822589</v>
+        <v>71.754717</v>
       </c>
       <c r="J12" t="n">
-        <v>372.016278</v>
-      </c>
-      <c r="K12" t="n">
-        <v>379.898457</v>
+        <v>89.155992</v>
       </c>
     </row>
     <row r="13">
@@ -880,33 +860,32 @@
           <t>其他平上櫃</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
+      <c r="B13" t="n">
+        <v>0.07370500000000001</v>
+      </c>
       <c r="C13" t="n">
-        <v>0.028894</v>
+        <v>0.073134</v>
       </c>
       <c r="D13" t="n">
-        <v>0.028113</v>
+        <v>0.10516</v>
       </c>
       <c r="E13" t="n">
-        <v>0.048891</v>
+        <v>0.0696565</v>
       </c>
       <c r="F13" t="n">
-        <v>0.01526</v>
+        <v>0.085149</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0596845</v>
+        <v>0.121839</v>
       </c>
       <c r="H13" t="n">
-        <v>0.010407</v>
+        <v>0.077456</v>
       </c>
       <c r="I13" t="n">
-        <v>0.107255</v>
+        <v>0.082701</v>
       </c>
       <c r="J13" t="n">
-        <v>0.080383</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.06454600000000001</v>
+        <v>0.1222045</v>
       </c>
     </row>
     <row r="14">
@@ -915,33 +894,32 @@
           <t>其他電子業右上上市</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
+      <c r="B14" t="n">
+        <v>36079.271484</v>
+      </c>
       <c r="C14" t="n">
-        <v>40603.861329</v>
+        <v>35352.869423</v>
       </c>
       <c r="D14" t="n">
-        <v>36308.402063</v>
+        <v>43844.505121</v>
       </c>
       <c r="E14" t="n">
-        <v>35956.648033</v>
+        <v>33855.922663</v>
       </c>
       <c r="F14" t="n">
-        <v>43873.810083</v>
+        <v>39818.732</v>
       </c>
       <c r="G14" t="n">
-        <v>34212.143456</v>
+        <v>58636.091601</v>
       </c>
       <c r="H14" t="n">
-        <v>41155.164782</v>
+        <v>61933.541822</v>
       </c>
       <c r="I14" t="n">
-        <v>58812.202222</v>
+        <v>43238.70328</v>
       </c>
       <c r="J14" t="n">
-        <v>62064.56041</v>
-      </c>
-      <c r="K14" t="n">
-        <v>43386.568025</v>
+        <v>34965.378984</v>
       </c>
     </row>
     <row r="15">
@@ -950,33 +928,32 @@
           <t>其他電子業右上上櫃</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
+      <c r="B15" t="n">
+        <v>13.437214</v>
+      </c>
       <c r="C15" t="n">
-        <v>10.728227</v>
+        <v>8.991203000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>14.393279</v>
+        <v>10.365959</v>
       </c>
       <c r="E15" t="n">
-        <v>10.543249</v>
+        <v>6.611521</v>
       </c>
       <c r="F15" t="n">
-        <v>13.73935</v>
+        <v>7.297555</v>
       </c>
       <c r="G15" t="n">
-        <v>9.655246</v>
+        <v>9.339683000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>9.871612000000001</v>
+        <v>8.56776</v>
       </c>
       <c r="I15" t="n">
-        <v>13.484624</v>
+        <v>10.401768</v>
       </c>
       <c r="J15" t="n">
-        <v>13.175972</v>
-      </c>
-      <c r="K15" t="n">
-        <v>12.520574</v>
+        <v>14.928423</v>
       </c>
     </row>
     <row r="16">
@@ -985,33 +962,32 @@
           <t>其他電子業右下上市</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
+      <c r="B16" t="n">
+        <v>122.188769</v>
+      </c>
       <c r="C16" t="n">
-        <v>418.121535</v>
+        <v>173.258883</v>
       </c>
       <c r="D16" t="n">
-        <v>387.959514</v>
+        <v>167.846943</v>
       </c>
       <c r="E16" t="n">
-        <v>388.689652</v>
+        <v>162.343206</v>
       </c>
       <c r="F16" t="n">
-        <v>437.686363</v>
+        <v>190.95954</v>
       </c>
       <c r="G16" t="n">
-        <v>342.637731</v>
+        <v>302.511449</v>
       </c>
       <c r="H16" t="n">
-        <v>368.704943</v>
+        <v>368.526172</v>
       </c>
       <c r="I16" t="n">
-        <v>772.19219</v>
+        <v>122.158988</v>
       </c>
       <c r="J16" t="n">
-        <v>495.021773</v>
-      </c>
-      <c r="K16" t="n">
-        <v>466.160291</v>
+        <v>589.136943</v>
       </c>
     </row>
     <row r="17">
@@ -1021,34 +997,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>0.238945</v>
       </c>
       <c r="C17" t="n">
-        <v>0.029398</v>
+        <v>0.102638</v>
       </c>
       <c r="D17" t="n">
-        <v>0.010612</v>
+        <v>0.075781</v>
       </c>
       <c r="E17" t="n">
-        <v>0.015014</v>
+        <v>0.087064</v>
       </c>
       <c r="F17" t="n">
-        <v>0.016208</v>
+        <v>0.114932</v>
       </c>
       <c r="G17" t="n">
-        <v>0.03004</v>
+        <v>0.07022200000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>0.019506</v>
+        <v>0.082695</v>
       </c>
       <c r="I17" t="n">
-        <v>0.064744</v>
+        <v>0.07177500000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>0.044652</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.044543</v>
+        <v>0.086113</v>
       </c>
     </row>
     <row r="18">
@@ -1057,33 +1030,32 @@
           <t>其他電子業平上市</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
+      <c r="B18" t="n">
+        <v>733.0549140000001</v>
+      </c>
       <c r="C18" t="n">
-        <v>109.908239</v>
+        <v>1399.054171</v>
       </c>
       <c r="D18" t="n">
-        <v>238.15359</v>
+        <v>662.797492</v>
       </c>
       <c r="E18" t="n">
-        <v>579.844792</v>
+        <v>756.907611</v>
       </c>
       <c r="F18" t="n">
-        <v>363.65311</v>
+        <v>1625.270931</v>
       </c>
       <c r="G18" t="n">
-        <v>220.392293</v>
+        <v>803.294501</v>
       </c>
       <c r="H18" t="n">
-        <v>111.092746</v>
+        <v>1393.298319</v>
       </c>
       <c r="I18" t="n">
-        <v>157.503139</v>
+        <v>1682.643789</v>
       </c>
       <c r="J18" t="n">
-        <v>1135.78413</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1190.777741</v>
+        <v>998.461128</v>
       </c>
     </row>
     <row r="19">
@@ -1092,33 +1064,32 @@
           <t>其他電子業平上櫃</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
+      <c r="B19" t="n">
+        <v>1.500443</v>
+      </c>
       <c r="C19" t="n">
-        <v>0.772418</v>
+        <v>1.856242</v>
       </c>
       <c r="D19" t="n">
-        <v>0.545838</v>
+        <v>3.792821</v>
       </c>
       <c r="E19" t="n">
-        <v>0.301245</v>
+        <v>3.596311</v>
       </c>
       <c r="F19" t="n">
-        <v>0.42844</v>
+        <v>3.06292</v>
       </c>
       <c r="G19" t="n">
-        <v>0.342263</v>
+        <v>4.595788</v>
       </c>
       <c r="H19" t="n">
-        <v>0.285571</v>
+        <v>5.827706</v>
       </c>
       <c r="I19" t="n">
-        <v>0.27148</v>
+        <v>2.903894</v>
       </c>
       <c r="J19" t="n">
-        <v>0.079899</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.088772</v>
+        <v>1.903904</v>
       </c>
     </row>
     <row r="20">
@@ -1127,33 +1098,32 @@
           <t>化學工業右上上市</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
+      <c r="B20" t="n">
+        <v>9882.511367999999</v>
+      </c>
       <c r="C20" t="n">
-        <v>8562.394875</v>
+        <v>6355.062814</v>
       </c>
       <c r="D20" t="n">
-        <v>10231.82806</v>
+        <v>8542.054827</v>
       </c>
       <c r="E20" t="n">
-        <v>6917.31368</v>
+        <v>5022.470767</v>
       </c>
       <c r="F20" t="n">
-        <v>8922.589506</v>
+        <v>10431.09168</v>
       </c>
       <c r="G20" t="n">
-        <v>5951.538249</v>
+        <v>10362.427802</v>
       </c>
       <c r="H20" t="n">
-        <v>10798.870931</v>
+        <v>13089.881223</v>
       </c>
       <c r="I20" t="n">
-        <v>11033.84295</v>
+        <v>10887.337122</v>
       </c>
       <c r="J20" t="n">
-        <v>13584.934835</v>
-      </c>
-      <c r="K20" t="n">
-        <v>11756.550361</v>
+        <v>8709.227973999999</v>
       </c>
     </row>
     <row r="21">
@@ -1162,33 +1132,32 @@
           <t>化學工業右上上櫃</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="n">
+        <v>0.129619</v>
+      </c>
       <c r="C21" t="n">
-        <v>0.108029</v>
+        <v>0.08554200000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>0.253387</v>
+        <v>0.243057</v>
       </c>
       <c r="E21" t="n">
-        <v>0.776633</v>
+        <v>0.089675</v>
       </c>
       <c r="F21" t="n">
-        <v>1.370963</v>
+        <v>0.294889</v>
       </c>
       <c r="G21" t="n">
-        <v>0.982088</v>
+        <v>0.334746</v>
       </c>
       <c r="H21" t="n">
-        <v>0.809154</v>
+        <v>0.574137</v>
       </c>
       <c r="I21" t="n">
-        <v>0.733225</v>
+        <v>0.863293</v>
       </c>
       <c r="J21" t="n">
-        <v>0.955928</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1.199357</v>
+        <v>0.422091</v>
       </c>
     </row>
     <row r="22">
@@ -1197,33 +1166,32 @@
           <t>化學工業右下上市</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="n">
+        <v>419.428425</v>
+      </c>
       <c r="C22" t="n">
-        <v>142.264442</v>
+        <v>174.154573</v>
       </c>
       <c r="D22" t="n">
-        <v>237.191771</v>
+        <v>137.624827</v>
       </c>
       <c r="E22" t="n">
-        <v>149.722673</v>
+        <v>104.854825</v>
       </c>
       <c r="F22" t="n">
-        <v>106.444353</v>
+        <v>196.898298</v>
       </c>
       <c r="G22" t="n">
-        <v>86.6267</v>
+        <v>217.971558</v>
       </c>
       <c r="H22" t="n">
-        <v>86.507775</v>
+        <v>105.367152</v>
       </c>
       <c r="I22" t="n">
-        <v>184.554769</v>
+        <v>86.809005</v>
       </c>
       <c r="J22" t="n">
-        <v>105.367152</v>
-      </c>
-      <c r="K22" t="n">
-        <v>102.198641</v>
+        <v>92.88312999999999</v>
       </c>
     </row>
     <row r="23">
@@ -1232,33 +1200,32 @@
           <t>化學工業右下上櫃</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
+      <c r="B23" t="n">
+        <v>0.302992</v>
+      </c>
       <c r="C23" t="n">
-        <v>0.08731899999999999</v>
+        <v>0.75597</v>
       </c>
       <c r="D23" t="n">
-        <v>0.102565</v>
+        <v>0.639278</v>
       </c>
       <c r="E23" t="n">
-        <v>0.009887999999999999</v>
+        <v>0.2668</v>
       </c>
       <c r="F23" t="n">
-        <v>0.009261</v>
+        <v>0.024437</v>
       </c>
       <c r="G23" t="n">
-        <v>0.008884</v>
+        <v>0.024472</v>
       </c>
       <c r="H23" t="n">
-        <v>0.025501</v>
+        <v>0.236392</v>
       </c>
       <c r="I23" t="n">
-        <v>0.025438</v>
+        <v>0.251624</v>
       </c>
       <c r="J23" t="n">
-        <v>0.007489</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0.011008</v>
+        <v>0.229291</v>
       </c>
     </row>
     <row r="24">
@@ -1267,33 +1234,32 @@
           <t>化學工業平上市</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="n">
+        <v>716.5622499999999</v>
+      </c>
       <c r="C24" t="n">
-        <v>726.253564</v>
+        <v>1063.384379</v>
       </c>
       <c r="D24" t="n">
-        <v>549.482212</v>
+        <v>1014.584463</v>
       </c>
       <c r="E24" t="n">
-        <v>525.565413</v>
+        <v>1574.244514</v>
       </c>
       <c r="F24" t="n">
-        <v>665.230258</v>
+        <v>723.970323</v>
       </c>
       <c r="G24" t="n">
-        <v>663.405157</v>
+        <v>1038.512025</v>
       </c>
       <c r="H24" t="n">
-        <v>466.581595</v>
+        <v>762.959099</v>
       </c>
       <c r="I24" t="n">
-        <v>400.513666</v>
+        <v>1340.883595</v>
       </c>
       <c r="J24" t="n">
-        <v>267.905487</v>
-      </c>
-      <c r="K24" t="n">
-        <v>456.28072</v>
+        <v>1143.293299</v>
       </c>
     </row>
     <row r="25">
@@ -1302,33 +1268,32 @@
           <t>化學工業平上櫃</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
+      <c r="B25" t="n">
+        <v>0.178292</v>
+      </c>
       <c r="C25" t="n">
-        <v>0.361953</v>
+        <v>0.693905</v>
       </c>
       <c r="D25" t="n">
-        <v>0.254951</v>
+        <v>1.141352</v>
       </c>
       <c r="E25" t="n">
-        <v>0.748896</v>
+        <v>0.89294</v>
       </c>
       <c r="F25" t="n">
-        <v>0.643463</v>
+        <v>2.197642</v>
       </c>
       <c r="G25" t="n">
-        <v>0.258443</v>
+        <v>1.170657</v>
       </c>
       <c r="H25" t="n">
-        <v>1.682313</v>
+        <v>0.382493</v>
       </c>
       <c r="I25" t="n">
-        <v>0.771212</v>
+        <v>0.337553</v>
       </c>
       <c r="J25" t="n">
-        <v>0.229605</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0.242105</v>
+        <v>0.162364</v>
       </c>
     </row>
     <row r="26">
@@ -1337,33 +1302,32 @@
           <t>半導體業右上上市</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="n">
+        <v>270822.403683</v>
+      </c>
       <c r="C26" t="n">
-        <v>318052.933265</v>
+        <v>285493.879323</v>
       </c>
       <c r="D26" t="n">
-        <v>276782.943875</v>
+        <v>307574.643404</v>
       </c>
       <c r="E26" t="n">
-        <v>291222.114528</v>
+        <v>229451.108898</v>
       </c>
       <c r="F26" t="n">
-        <v>315731.938489</v>
+        <v>247862.218384</v>
       </c>
       <c r="G26" t="n">
-        <v>234999.013285</v>
+        <v>366999.998588</v>
       </c>
       <c r="H26" t="n">
-        <v>260849.70102</v>
+        <v>309715.52784</v>
       </c>
       <c r="I26" t="n">
-        <v>373990.407141</v>
+        <v>267014.602251</v>
       </c>
       <c r="J26" t="n">
-        <v>314672.290155</v>
-      </c>
-      <c r="K26" t="n">
-        <v>270597.391357</v>
+        <v>292808.61959</v>
       </c>
     </row>
     <row r="27">
@@ -1372,33 +1336,32 @@
           <t>半導體業右上上櫃</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
+      <c r="B27" t="n">
+        <v>90.226675</v>
+      </c>
       <c r="C27" t="n">
-        <v>161.377952</v>
+        <v>79.75349</v>
       </c>
       <c r="D27" t="n">
-        <v>99.192314</v>
+        <v>123.720141</v>
       </c>
       <c r="E27" t="n">
-        <v>88.485629</v>
+        <v>128.044739</v>
       </c>
       <c r="F27" t="n">
-        <v>139.661966</v>
+        <v>116.418771</v>
       </c>
       <c r="G27" t="n">
-        <v>140.310446</v>
+        <v>141.135673</v>
       </c>
       <c r="H27" t="n">
-        <v>123.47523</v>
+        <v>107.774604</v>
       </c>
       <c r="I27" t="n">
-        <v>149.925874</v>
+        <v>120.92481</v>
       </c>
       <c r="J27" t="n">
-        <v>117.120813</v>
-      </c>
-      <c r="K27" t="n">
-        <v>122.464242</v>
+        <v>112.366037</v>
       </c>
     </row>
     <row r="28">
@@ -1407,33 +1370,32 @@
           <t>半導體業右下上市</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="n">
+        <v>1190.705722</v>
+      </c>
       <c r="C28" t="n">
-        <v>952.7060279999999</v>
+        <v>1215.495016</v>
       </c>
       <c r="D28" t="n">
-        <v>828.899846</v>
+        <v>1089.004733</v>
       </c>
       <c r="E28" t="n">
-        <v>983.773998</v>
+        <v>957.057733</v>
       </c>
       <c r="F28" t="n">
-        <v>1098.479363</v>
+        <v>621.03682</v>
       </c>
       <c r="G28" t="n">
-        <v>1145.708272</v>
+        <v>1274.322432</v>
       </c>
       <c r="H28" t="n">
-        <v>698.642332</v>
+        <v>1297.387778</v>
       </c>
       <c r="I28" t="n">
-        <v>1003.434086</v>
+        <v>13301.340597</v>
       </c>
       <c r="J28" t="n">
-        <v>1071.201193</v>
-      </c>
-      <c r="K28" t="n">
-        <v>870.262156</v>
+        <v>7556.680408</v>
       </c>
     </row>
     <row r="29">
@@ -1442,33 +1404,32 @@
           <t>半導體業右下上櫃</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
+      <c r="B29" t="n">
+        <v>0.8938</v>
+      </c>
       <c r="C29" t="n">
-        <v>1.2883</v>
+        <v>1.53330125</v>
       </c>
       <c r="D29" t="n">
-        <v>0.900543</v>
+        <v>2.935031</v>
       </c>
       <c r="E29" t="n">
-        <v>3.02567825</v>
+        <v>3.985883</v>
       </c>
       <c r="F29" t="n">
-        <v>1.791331</v>
+        <v>4.857131</v>
       </c>
       <c r="G29" t="n">
-        <v>3.077671</v>
+        <v>3.515911</v>
       </c>
       <c r="H29" t="n">
-        <v>2.445535</v>
+        <v>2.824977</v>
       </c>
       <c r="I29" t="n">
-        <v>2.415741</v>
+        <v>0.904744</v>
       </c>
       <c r="J29" t="n">
-        <v>2.248432</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0.581245</v>
+        <v>3.859594</v>
       </c>
     </row>
     <row r="30">
@@ -1477,33 +1438,32 @@
           <t>半導體業平上市</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="n">
+        <v>18447.333554</v>
+      </c>
       <c r="C30" t="n">
-        <v>12092.675741</v>
+        <v>16209.80837</v>
       </c>
       <c r="D30" t="n">
-        <v>12845.093375</v>
+        <v>18913.857904</v>
       </c>
       <c r="E30" t="n">
-        <v>10705.973014</v>
+        <v>12874.398476</v>
       </c>
       <c r="F30" t="n">
-        <v>10741.106846</v>
+        <v>16711.163602</v>
       </c>
       <c r="G30" t="n">
-        <v>7129.630298</v>
+        <v>12336.164244</v>
       </c>
       <c r="H30" t="n">
-        <v>3639.240211</v>
+        <v>11623.162005</v>
       </c>
       <c r="I30" t="n">
-        <v>5598.691249</v>
+        <v>7439.994847</v>
       </c>
       <c r="J30" t="n">
-        <v>6885.810662</v>
-      </c>
-      <c r="K30" t="n">
-        <v>16283.378266</v>
+        <v>9099.743048</v>
       </c>
     </row>
     <row r="31">
@@ -1512,33 +1472,32 @@
           <t>半導體業平上櫃</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
+      <c r="B31" t="n">
+        <v>9.350882</v>
+      </c>
       <c r="C31" t="n">
-        <v>0.887954</v>
+        <v>11.274925</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3785</v>
+        <v>16.393483</v>
       </c>
       <c r="E31" t="n">
-        <v>1.050409</v>
+        <v>14.89894</v>
       </c>
       <c r="F31" t="n">
-        <v>1.595358</v>
+        <v>10.04876</v>
       </c>
       <c r="G31" t="n">
-        <v>1.14472</v>
+        <v>11.599118</v>
       </c>
       <c r="H31" t="n">
-        <v>2.602207</v>
+        <v>13.090228</v>
       </c>
       <c r="I31" t="n">
-        <v>1.534524</v>
+        <v>13.168476</v>
       </c>
       <c r="J31" t="n">
-        <v>0.693098</v>
-      </c>
-      <c r="K31" t="n">
-        <v>3.448907</v>
+        <v>16.784504</v>
       </c>
     </row>
     <row r="32">
@@ -1547,33 +1506,32 @@
           <t>塑膠工業右上上市</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="n">
+        <v>18414.422521</v>
+      </c>
       <c r="C32" t="n">
-        <v>15919.198001</v>
+        <v>23993.723144</v>
       </c>
       <c r="D32" t="n">
-        <v>18456.769403</v>
+        <v>38398.115906</v>
       </c>
       <c r="E32" t="n">
-        <v>24003.311254</v>
+        <v>17613.517817</v>
       </c>
       <c r="F32" t="n">
-        <v>38446.327975</v>
+        <v>17741.971142</v>
       </c>
       <c r="G32" t="n">
-        <v>17643.26033</v>
+        <v>29521.399492</v>
       </c>
       <c r="H32" t="n">
-        <v>17880.73366</v>
+        <v>37282.689887</v>
       </c>
       <c r="I32" t="n">
-        <v>29591.396337</v>
+        <v>51336.878614</v>
       </c>
       <c r="J32" t="n">
-        <v>37329.451211</v>
-      </c>
-      <c r="K32" t="n">
-        <v>51456.204675</v>
+        <v>49957.318591</v>
       </c>
     </row>
     <row r="33">
@@ -1582,33 +1540,32 @@
           <t>塑膠工業右下上市</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
+      <c r="B33" t="n">
+        <v>21.393921</v>
+      </c>
       <c r="C33" t="n">
-        <v>20.141526</v>
+        <v>39.355459</v>
       </c>
       <c r="D33" t="n">
-        <v>14.711618</v>
+        <v>34.904345</v>
       </c>
       <c r="E33" t="n">
-        <v>29.039463</v>
+        <v>28.912333</v>
       </c>
       <c r="F33" t="n">
-        <v>37.351237</v>
+        <v>15.643569</v>
       </c>
       <c r="G33" t="n">
-        <v>22.338546</v>
+        <v>41.277259</v>
       </c>
       <c r="H33" t="n">
-        <v>17.20861</v>
+        <v>56.90155</v>
       </c>
       <c r="I33" t="n">
-        <v>43.752679</v>
+        <v>15.000231</v>
       </c>
       <c r="J33" t="n">
-        <v>64.905923</v>
-      </c>
-      <c r="K33" t="n">
-        <v>19.274904</v>
+        <v>12.142566</v>
       </c>
     </row>
     <row r="34">
@@ -1617,33 +1574,32 @@
           <t>塑膠工業右下上櫃</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="n">
+        <v>0.043256</v>
+      </c>
       <c r="C34" t="n">
-        <v>0.0145135</v>
+        <v>0.028786</v>
       </c>
       <c r="D34" t="n">
-        <v>0.041813</v>
+        <v>0.0244545</v>
       </c>
       <c r="E34" t="n">
-        <v>0.028097</v>
+        <v>0.029761</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0236345</v>
+        <v>0.016262</v>
       </c>
       <c r="G34" t="n">
-        <v>0.029495</v>
+        <v>0.0393105</v>
       </c>
       <c r="H34" t="n">
-        <v>0.015748</v>
+        <v>0.03161</v>
       </c>
       <c r="I34" t="n">
-        <v>0.0384175</v>
+        <v>0.014736</v>
       </c>
       <c r="J34" t="n">
-        <v>0.031051</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0.014736</v>
+        <v>0.039382</v>
       </c>
     </row>
     <row r="35">
@@ -1652,67 +1608,51 @@
           <t>塑膠工業平上市</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
+      <c r="B35" t="n">
+        <v>86.148461</v>
+      </c>
       <c r="C35" t="n">
-        <v>69.58456099999999</v>
+        <v>105.869253</v>
       </c>
       <c r="D35" t="n">
-        <v>50.483882</v>
+        <v>159.785773</v>
       </c>
       <c r="E35" t="n">
-        <v>106.597139</v>
+        <v>84.431816</v>
       </c>
       <c r="F35" t="n">
-        <v>109.126812</v>
+        <v>244.212676</v>
       </c>
       <c r="G35" t="n">
-        <v>61.26309</v>
+        <v>121.00438</v>
       </c>
       <c r="H35" t="n">
-        <v>103.885117</v>
+        <v>87.37659499999999</v>
       </c>
       <c r="I35" t="n">
-        <v>48.532115</v>
+        <v>223.733005</v>
       </c>
       <c r="J35" t="n">
-        <v>32.610898</v>
-      </c>
-      <c r="K35" t="n">
-        <v>100.132271</v>
+        <v>188.528186</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>塑膠工業平上櫃</t>
+          <t>居家生活右上上市</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
-      <c r="C36" t="n">
-        <v>0.008036</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0.001443</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.0006890000000000001</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.00082</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.000266</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0.000514</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0.000893</v>
-      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="n">
-        <v>0.000559</v>
-      </c>
-      <c r="K36" t="inlineStr"/>
+        <v>0.099395</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -1720,33 +1660,32 @@
           <t>居家生活右上上櫃</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
+      <c r="B37" t="n">
+        <v>0.002171</v>
+      </c>
       <c r="C37" t="n">
-        <v>0.005049</v>
+        <v>0.001119</v>
       </c>
       <c r="D37" t="n">
-        <v>0.002355</v>
+        <v>0.000906</v>
       </c>
       <c r="E37" t="n">
-        <v>0.001119</v>
+        <v>0.000283</v>
       </c>
       <c r="F37" t="n">
-        <v>0.001147</v>
+        <v>0.001482</v>
       </c>
       <c r="G37" t="n">
-        <v>0.000283</v>
+        <v>0.00025</v>
       </c>
       <c r="H37" t="n">
-        <v>0.001482</v>
+        <v>0.00049</v>
       </c>
       <c r="I37" t="n">
-        <v>0.00025</v>
+        <v>0.000346</v>
       </c>
       <c r="J37" t="n">
-        <v>0.00049</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0.000346</v>
+        <v>0.00124</v>
       </c>
     </row>
     <row r="38">
@@ -1755,33 +1694,32 @@
           <t>居家生活右下上市</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
+      <c r="B38" t="n">
+        <v>20.023105</v>
+      </c>
       <c r="C38" t="n">
-        <v>110.308606</v>
+        <v>29.842921</v>
       </c>
       <c r="D38" t="n">
-        <v>84.51718099999999</v>
+        <v>27.947611</v>
       </c>
       <c r="E38" t="n">
-        <v>225.681646</v>
+        <v>20.812951</v>
       </c>
       <c r="F38" t="n">
-        <v>157.080028</v>
+        <v>28.538201</v>
       </c>
       <c r="G38" t="n">
-        <v>89.773652</v>
+        <v>52.805219</v>
       </c>
       <c r="H38" t="n">
-        <v>85.743891</v>
+        <v>33.439189</v>
       </c>
       <c r="I38" t="n">
-        <v>94.456698</v>
+        <v>32.172167</v>
       </c>
       <c r="J38" t="n">
-        <v>102.227215</v>
-      </c>
-      <c r="K38" t="n">
-        <v>136.048295</v>
+        <v>29.480435</v>
       </c>
     </row>
     <row r="39">
@@ -1790,4610 +1728,4602 @@
           <t>居家生活右下上櫃</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
+      <c r="B39" t="n">
+        <v>0.55962575</v>
+      </c>
       <c r="C39" t="n">
-        <v>0.366794</v>
+        <v>0.3257003333333333</v>
       </c>
       <c r="D39" t="n">
-        <v>0.55957575</v>
+        <v>0.3575955</v>
       </c>
       <c r="E39" t="n">
-        <v>0.3252453333333333</v>
+        <v>0.2460553333333333</v>
       </c>
       <c r="F39" t="n">
-        <v>0.3573575</v>
+        <v>0.312833</v>
       </c>
       <c r="G39" t="n">
-        <v>0.245567</v>
+        <v>0.226244</v>
       </c>
       <c r="H39" t="n">
-        <v>0.307899</v>
+        <v>0.217029</v>
       </c>
       <c r="I39" t="n">
-        <v>0.226301</v>
+        <v>0.246371</v>
       </c>
       <c r="J39" t="n">
-        <v>0.216663</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0.246389</v>
+        <v>0.175662</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>居家生活平上櫃</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
+          <t>居家生活平上市</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>64.49407600000001</v>
+      </c>
       <c r="C40" t="n">
-        <v>0.001359</v>
+        <v>195.838725</v>
       </c>
       <c r="D40" t="n">
-        <v>0.000616</v>
+        <v>129.132417</v>
       </c>
       <c r="E40" t="n">
-        <v>0.001223</v>
+        <v>68.960701</v>
       </c>
       <c r="F40" t="n">
-        <v>0.000898</v>
+        <v>57.20569</v>
       </c>
       <c r="G40" t="n">
-        <v>0.004777333333333333</v>
+        <v>41.651479</v>
       </c>
       <c r="H40" t="n">
-        <v>0.007941999999999999</v>
+        <v>68.788026</v>
       </c>
       <c r="I40" t="n">
-        <v>0.001168</v>
+        <v>103.876128</v>
       </c>
       <c r="J40" t="n">
-        <v>0.001679</v>
-      </c>
-      <c r="K40" t="n">
-        <v>5.3e-05</v>
+        <v>82.606009</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>建材營造右上上市</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
+          <t>居家生活平上櫃</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0.00075</v>
+      </c>
       <c r="C41" t="n">
-        <v>102.798544</v>
+        <v>0.000768</v>
       </c>
       <c r="D41" t="n">
-        <v>111.02575</v>
+        <v>0.000901</v>
       </c>
       <c r="E41" t="n">
-        <v>76.98213</v>
+        <v>0.004289</v>
       </c>
       <c r="F41" t="n">
-        <v>130.417564</v>
+        <v>0.003008</v>
       </c>
       <c r="G41" t="n">
-        <v>87.222176</v>
+        <v>0.001225</v>
       </c>
       <c r="H41" t="n">
-        <v>110.783978</v>
+        <v>0.001313</v>
       </c>
       <c r="I41" t="n">
-        <v>152.611407</v>
+        <v>7.1e-05</v>
       </c>
       <c r="J41" t="n">
-        <v>119.741025</v>
-      </c>
-      <c r="K41" t="n">
-        <v>85.81657199999999</v>
+        <v>0.000416</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>建材營造右上上櫃</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
+          <t>建材營造右上上市</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>149.45803</v>
+      </c>
       <c r="C42" t="n">
-        <v>0.015812</v>
+        <v>124.981634</v>
       </c>
       <c r="D42" t="n">
-        <v>0.015308</v>
+        <v>201.107528</v>
       </c>
       <c r="E42" t="n">
-        <v>0.012671</v>
+        <v>147.807027</v>
       </c>
       <c r="F42" t="n">
-        <v>0.016945</v>
+        <v>164.04647</v>
       </c>
       <c r="G42" t="n">
-        <v>0.022928</v>
+        <v>186.246527</v>
       </c>
       <c r="H42" t="n">
-        <v>0.014092</v>
+        <v>142.771721</v>
       </c>
       <c r="I42" t="n">
-        <v>0.005928</v>
+        <v>108.367262</v>
       </c>
       <c r="J42" t="n">
-        <v>0.0045</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0.003917</v>
+        <v>199.957192</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>建材營造右下上市</t>
+          <t>建材營造右上上櫃</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>0.007346</v>
       </c>
       <c r="C43" t="n">
-        <v>2483.378532</v>
+        <v>0.012669</v>
       </c>
       <c r="D43" t="n">
-        <v>929.73395</v>
+        <v>0.015847</v>
       </c>
       <c r="E43" t="n">
-        <v>1045.564463</v>
+        <v>0.020326</v>
       </c>
       <c r="F43" t="n">
-        <v>1120.578741</v>
+        <v>0.01373125</v>
       </c>
       <c r="G43" t="n">
-        <v>832.507251</v>
+        <v>0.007236</v>
       </c>
       <c r="H43" t="n">
-        <v>938.6619030000001</v>
+        <v>0.006054</v>
       </c>
       <c r="I43" t="n">
-        <v>1443.73629</v>
+        <v>0.032965</v>
       </c>
       <c r="J43" t="n">
-        <v>917.500231</v>
-      </c>
-      <c r="K43" t="n">
-        <v>825.253692</v>
+        <v>0.010129</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>建材營造右下上櫃</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
+          <t>建材營造右下上市</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>428.069404</v>
+      </c>
       <c r="C44" t="n">
-        <v>0.098083</v>
+        <v>1042.3501</v>
       </c>
       <c r="D44" t="n">
-        <v>0.075102</v>
+        <v>1117.33762</v>
       </c>
       <c r="E44" t="n">
-        <v>0.060285</v>
+        <v>829.348561</v>
       </c>
       <c r="F44" t="n">
-        <v>0.058978</v>
+        <v>935.330247</v>
       </c>
       <c r="G44" t="n">
-        <v>0.04913266666666666</v>
+        <v>1437.091697</v>
       </c>
       <c r="H44" t="n">
-        <v>0.064065</v>
+        <v>904.735288</v>
       </c>
       <c r="I44" t="n">
-        <v>0.101432</v>
+        <v>970.827238</v>
       </c>
       <c r="J44" t="n">
-        <v>0.046603</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0.05454366666666666</v>
+        <v>785.610801</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>建材營造平上市</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
+          <t>建材營造右下上櫃</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>0.06238</v>
+      </c>
       <c r="C45" t="n">
-        <v>209.87792</v>
+        <v>0.054294</v>
       </c>
       <c r="D45" t="n">
-        <v>117.547258</v>
+        <v>0.050976</v>
       </c>
       <c r="E45" t="n">
-        <v>79.524036</v>
+        <v>0.03979466666666667</v>
       </c>
       <c r="F45" t="n">
-        <v>119.412784</v>
+        <v>0.044147</v>
       </c>
       <c r="G45" t="n">
-        <v>223.589286</v>
+        <v>0.110113</v>
       </c>
       <c r="H45" t="n">
-        <v>125.055751</v>
+        <v>0.051935</v>
       </c>
       <c r="I45" t="n">
-        <v>148.370581</v>
+        <v>0.04488866666666667</v>
       </c>
       <c r="J45" t="n">
-        <v>73.41445</v>
-      </c>
-      <c r="K45" t="n">
-        <v>276.038861</v>
+        <v>0.04910066666666667</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>建材營造平上櫃</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
+          <t>建材營造平上市</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>581.465077</v>
+      </c>
       <c r="C46" t="n">
-        <v>0.003659</v>
+        <v>36.673821</v>
       </c>
       <c r="D46" t="n">
-        <v>0.001731</v>
+        <v>53.262782</v>
       </c>
       <c r="E46" t="n">
-        <v>0.004705</v>
+        <v>166.435499</v>
       </c>
       <c r="F46" t="n">
-        <v>0.004307</v>
+        <v>76.116998</v>
       </c>
       <c r="G46" t="n">
-        <v>0.014848</v>
+        <v>121.778049</v>
       </c>
       <c r="H46" t="n">
-        <v>0.00322425</v>
+        <v>63.764067</v>
       </c>
       <c r="I46" t="n">
-        <v>0.019664</v>
+        <v>108.656523</v>
       </c>
       <c r="J46" t="n">
-        <v>0.015972</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0.036654</v>
+        <v>61.486283</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>數位雲端右上上市</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
+          <t>建材營造平上櫃</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>0.022415</v>
+      </c>
       <c r="C47" t="n">
-        <v>229.721265</v>
+        <v>0.010698</v>
       </c>
       <c r="D47" t="n">
-        <v>201.553671</v>
+        <v>0.013407</v>
       </c>
       <c r="E47" t="n">
-        <v>123.789134</v>
+        <v>0.026788</v>
       </c>
       <c r="F47" t="n">
-        <v>88.29381600000001</v>
+        <v>0.023503</v>
       </c>
       <c r="G47" t="n">
-        <v>61.638603</v>
+        <v>0.009675</v>
       </c>
       <c r="H47" t="n">
-        <v>71.518085</v>
+        <v>0.009086</v>
       </c>
       <c r="I47" t="n">
-        <v>62.462198</v>
+        <v>0.017261</v>
       </c>
       <c r="J47" t="n">
-        <v>48.754718</v>
-      </c>
-      <c r="K47" t="n">
-        <v>76.16837200000001</v>
+        <v>0.02706</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>數位雲端右上上櫃</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
+          <t>數位雲端右上上市</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>212.845719</v>
+      </c>
       <c r="C48" t="n">
-        <v>0.507046</v>
+        <v>131.591225</v>
       </c>
       <c r="D48" t="n">
-        <v>0.223421</v>
+        <v>273.926956</v>
       </c>
       <c r="E48" t="n">
-        <v>0.166084</v>
+        <v>79.373986</v>
       </c>
       <c r="F48" t="n">
-        <v>0.244618</v>
+        <v>81.745813</v>
       </c>
       <c r="G48" t="n">
-        <v>0.1803</v>
+        <v>65.84591899999999</v>
       </c>
       <c r="H48" t="n">
-        <v>0.115223</v>
+        <v>48.754718</v>
       </c>
       <c r="I48" t="n">
-        <v>0.19295</v>
+        <v>76.16837200000001</v>
       </c>
       <c r="J48" t="n">
-        <v>0.212665</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0.429491</v>
+        <v>38.724278</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>數位雲端右下上市</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
+          <t>數位雲端右上上櫃</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>0.218607</v>
+      </c>
       <c r="C49" t="n">
-        <v>53.080761</v>
+        <v>0.179389</v>
       </c>
       <c r="D49" t="n">
-        <v>82.262708</v>
+        <v>0.296095</v>
       </c>
       <c r="E49" t="n">
-        <v>65.905101</v>
+        <v>0.1936893333333334</v>
       </c>
       <c r="F49" t="n">
-        <v>58.653519</v>
+        <v>0.121387</v>
       </c>
       <c r="G49" t="n">
-        <v>58.105474</v>
+        <v>0.1898</v>
       </c>
       <c r="H49" t="n">
-        <v>50.751367</v>
+        <v>0.209382</v>
       </c>
       <c r="I49" t="n">
-        <v>106.150777</v>
+        <v>0.425433</v>
       </c>
       <c r="J49" t="n">
-        <v>106.566545</v>
-      </c>
-      <c r="K49" t="n">
-        <v>212.804395</v>
+        <v>0.66971</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>數位雲端右下上櫃</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
+          <t>數位雲端右下上市</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>22.50859</v>
+      </c>
       <c r="C50" t="n">
-        <v>0.179874</v>
+        <v>28.703929</v>
       </c>
       <c r="D50" t="n">
-        <v>0.205574</v>
+        <v>24.480949</v>
       </c>
       <c r="E50" t="n">
-        <v>0.267687</v>
+        <v>28.726985</v>
       </c>
       <c r="F50" t="n">
-        <v>0.205313</v>
+        <v>38.646655</v>
       </c>
       <c r="G50" t="n">
-        <v>0.232625</v>
+        <v>102.767056</v>
       </c>
       <c r="H50" t="n">
-        <v>0.210537</v>
+        <v>71.747041</v>
       </c>
       <c r="I50" t="n">
-        <v>0.25565475</v>
+        <v>59.996493</v>
       </c>
       <c r="J50" t="n">
-        <v>0.1826113333333333</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0.1052481666666667</v>
+        <v>25.052612</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>數位雲端平上市</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr"/>
+          <t>數位雲端右下上櫃</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0.09177299999999999</v>
+      </c>
       <c r="C51" t="n">
-        <v>117.558707</v>
+        <v>0.11663</v>
       </c>
       <c r="D51" t="n">
-        <v>68.576656</v>
+        <v>0.115867</v>
       </c>
       <c r="E51" t="n">
-        <v>88.45285800000001</v>
+        <v>0.173237</v>
       </c>
       <c r="F51" t="n">
-        <v>283.800786</v>
+        <v>0.181664</v>
       </c>
       <c r="G51" t="n">
-        <v>72.104377</v>
+        <v>0.20589275</v>
       </c>
       <c r="H51" t="n">
-        <v>58.783402</v>
+        <v>0.1089243333333333</v>
       </c>
       <c r="I51" t="n">
-        <v>133.565777</v>
+        <v>0.08171249999999999</v>
       </c>
       <c r="J51" t="n">
-        <v>66.176699</v>
-      </c>
-      <c r="K51" t="n">
-        <v>74.896503</v>
+        <v>0.253108</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>數位雲端平上櫃</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr"/>
+          <t>數位雲端平上市</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>117.038726</v>
+      </c>
+      <c r="C52" t="n">
+        <v>117.851939</v>
+      </c>
       <c r="D52" t="n">
-        <v>8.6e-05</v>
+        <v>132.340216</v>
       </c>
       <c r="E52" t="n">
-        <v>0.014752</v>
+        <v>83.747483</v>
       </c>
       <c r="F52" t="n">
-        <v>0.055404</v>
+        <v>60.660386</v>
       </c>
       <c r="G52" t="n">
-        <v>0.02802933333333334</v>
+        <v>133.565777</v>
       </c>
       <c r="H52" t="n">
-        <v>0.013788</v>
+        <v>100.996203</v>
       </c>
       <c r="I52" t="n">
-        <v>0.006842</v>
+        <v>227.704405</v>
       </c>
       <c r="J52" t="n">
-        <v>0.001174</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0.000633</v>
+        <v>62.706548</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>文化創意業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr"/>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
+          <t>數位雲端平上櫃</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>0.118701</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.152504</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.093373</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.074028</v>
+      </c>
       <c r="F53" t="n">
-        <v>1.632479</v>
+        <v>0.036497</v>
       </c>
       <c r="G53" t="n">
-        <v>4.801571</v>
+        <v>0.059754</v>
       </c>
       <c r="H53" t="n">
-        <v>2.438659</v>
+        <v>0.07814400000000001</v>
       </c>
       <c r="I53" t="n">
-        <v>1.087361</v>
+        <v>0.02822666666666667</v>
       </c>
       <c r="J53" t="n">
-        <v>0.002388</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0.000195</v>
+        <v>0.03855</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>文化創意業右下上櫃</t>
+          <t>文化創意業右上上櫃</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0</v>
+        <v>4.373877</v>
       </c>
       <c r="C54" t="n">
-        <v>0.6455865</v>
+        <v>2.718566</v>
       </c>
       <c r="D54" t="n">
-        <v>0.0401525</v>
+        <v>1.632479</v>
       </c>
       <c r="E54" t="n">
-        <v>0.06167775</v>
+        <v>4.801571</v>
       </c>
       <c r="F54" t="n">
-        <v>0.069564</v>
+        <v>2.438659</v>
       </c>
       <c r="G54" t="n">
-        <v>0.05069</v>
+        <v>1.087361</v>
       </c>
       <c r="H54" t="n">
-        <v>0.04797983333333333</v>
+        <v>1.167006</v>
       </c>
       <c r="I54" t="n">
-        <v>0.063098</v>
+        <v>0.468098</v>
       </c>
       <c r="J54" t="n">
-        <v>0.05676425</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0.070881</v>
+        <v>0.835421</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>文化創意業平上櫃</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr"/>
+          <t>文化創意業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>0.0408735</v>
+      </c>
       <c r="C55" t="n">
-        <v>0.00653</v>
+        <v>0.06168375</v>
       </c>
       <c r="D55" t="n">
-        <v>4.376937</v>
+        <v>0.073361</v>
       </c>
       <c r="E55" t="n">
-        <v>2.718797</v>
+        <v>0.049902</v>
       </c>
       <c r="F55" t="n">
-        <v>0.001631</v>
+        <v>0.05330483333333334</v>
       </c>
       <c r="G55" t="n">
-        <v>0.007647</v>
+        <v>0.072182</v>
       </c>
       <c r="H55" t="n">
-        <v>0.003466</v>
+        <v>0.06181725</v>
       </c>
       <c r="I55" t="n">
-        <v>0.000139</v>
+        <v>0.077178</v>
       </c>
       <c r="J55" t="n">
-        <v>1.165108</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0.49153</v>
+        <v>0.057784</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>橡膠工業右上上市</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr"/>
+          <t>文化創意業平上櫃</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>0.008586999999999999</v>
+      </c>
       <c r="C56" t="n">
-        <v>372.329556</v>
+        <v>0.003479</v>
       </c>
       <c r="D56" t="n">
-        <v>53.153067</v>
+        <v>0.001894</v>
       </c>
       <c r="E56" t="n">
-        <v>89.79392199999999</v>
+        <v>0.011794</v>
       </c>
       <c r="F56" t="n">
-        <v>90.27554600000001</v>
-      </c>
-      <c r="G56" t="n">
-        <v>63.309303</v>
-      </c>
-      <c r="H56" t="n">
-        <v>156.840719</v>
-      </c>
+        <v>0.004545</v>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="n">
-        <v>128.352831</v>
+        <v>0.023403</v>
       </c>
       <c r="J56" t="n">
-        <v>108.687858</v>
-      </c>
-      <c r="K56" t="n">
-        <v>286.4072</v>
+        <v>0.100166</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>橡膠工業右下上市</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr"/>
+          <t>橡膠工業右上上市</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>59.31454</v>
+      </c>
       <c r="C57" t="n">
-        <v>150.43609</v>
+        <v>91.80184300000001</v>
       </c>
       <c r="D57" t="n">
-        <v>116.233975</v>
+        <v>91.7514</v>
       </c>
       <c r="E57" t="n">
-        <v>165.105133</v>
+        <v>64.15203700000001</v>
       </c>
       <c r="F57" t="n">
-        <v>219.105697</v>
+        <v>159.079605</v>
       </c>
       <c r="G57" t="n">
-        <v>172.168685</v>
+        <v>130.843053</v>
       </c>
       <c r="H57" t="n">
-        <v>235.463628</v>
+        <v>111.431133</v>
       </c>
       <c r="I57" t="n">
-        <v>359.573597</v>
+        <v>256.674547</v>
       </c>
       <c r="J57" t="n">
-        <v>137.69556</v>
-      </c>
-      <c r="K57" t="n">
-        <v>185.673611</v>
+        <v>342.591606</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>橡膠工業平上市</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr"/>
+          <t>橡膠工業右下上市</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>116.233975</v>
+      </c>
       <c r="C58" t="n">
-        <v>4.689042</v>
+        <v>165.105133</v>
       </c>
       <c r="D58" t="n">
-        <v>116.487784</v>
+        <v>65.736844</v>
       </c>
       <c r="E58" t="n">
-        <v>69.590857</v>
+        <v>172.168685</v>
       </c>
       <c r="F58" t="n">
-        <v>58.783113</v>
+        <v>235.463628</v>
       </c>
       <c r="G58" t="n">
-        <v>35.531093</v>
+        <v>359.573597</v>
       </c>
       <c r="H58" t="n">
-        <v>22.661427</v>
+        <v>137.69556</v>
       </c>
       <c r="I58" t="n">
-        <v>57.237672</v>
+        <v>185.673611</v>
       </c>
       <c r="J58" t="n">
-        <v>37.566758</v>
-      </c>
-      <c r="K58" t="n">
-        <v>1.604544</v>
+        <v>213.587596</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>水泥工業右上上市</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr"/>
+          <t>橡膠工業平上市</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>110.326311</v>
+      </c>
       <c r="C59" t="n">
-        <v>3336.742112</v>
+        <v>67.582936</v>
       </c>
       <c r="D59" t="n">
-        <v>995.089243</v>
+        <v>210.676112</v>
       </c>
       <c r="E59" t="n">
-        <v>796.559063</v>
+        <v>34.688359</v>
       </c>
       <c r="F59" t="n">
-        <v>2745.271403</v>
+        <v>20.422541</v>
       </c>
       <c r="G59" t="n">
-        <v>1412.587301</v>
+        <v>54.74745</v>
       </c>
       <c r="H59" t="n">
-        <v>641.982484</v>
-      </c>
-      <c r="I59" t="inlineStr"/>
+        <v>34.823483</v>
+      </c>
+      <c r="I59" t="n">
+        <v>31.337197</v>
+      </c>
       <c r="J59" t="n">
-        <v>674.559882</v>
-      </c>
-      <c r="K59" t="n">
-        <v>632.455261</v>
+        <v>3.517407</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>水泥工業右下上市</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr"/>
+          <t>水泥工業右上上市</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>995.089243</v>
+      </c>
       <c r="C60" t="n">
-        <v>27.97068</v>
+        <v>796.559063</v>
       </c>
       <c r="D60" t="n">
-        <v>289.484283</v>
+        <v>2967.114292</v>
       </c>
       <c r="E60" t="n">
-        <v>375.398434</v>
+        <v>1412.587301</v>
       </c>
       <c r="F60" t="n">
-        <v>247.375978</v>
+        <v>641.982484</v>
       </c>
       <c r="G60" t="n">
-        <v>444.795927</v>
+        <v>900.0369920000001</v>
       </c>
       <c r="H60" t="n">
-        <v>191.480706</v>
+        <v>674.559882</v>
       </c>
       <c r="I60" t="n">
-        <v>201.274146</v>
+        <v>837.741159</v>
       </c>
       <c r="J60" t="n">
-        <v>265.605141</v>
-      </c>
-      <c r="K60" t="n">
-        <v>18.918191</v>
+        <v>1241.194317</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>水泥工業平上市</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr"/>
+          <t>水泥工業右下上市</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>23.890866</v>
+      </c>
       <c r="C61" t="n">
-        <v>406.238843</v>
-      </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+        <v>36.108083</v>
+      </c>
+      <c r="D61" t="n">
+        <v>25.533089</v>
+      </c>
+      <c r="E61" t="n">
+        <v>24.011971</v>
+      </c>
+      <c r="F61" t="n">
+        <v>17.212754</v>
+      </c>
+      <c r="G61" t="n">
+        <v>19.640078</v>
+      </c>
+      <c r="H61" t="n">
+        <v>20.295194</v>
+      </c>
       <c r="I61" t="n">
-        <v>900.0369920000001</v>
-      </c>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="n">
-        <v>205.285898</v>
+        <v>18.918191</v>
+      </c>
+      <c r="J61" t="n">
+        <v>14.150035</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>汽車工業右上上市</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr"/>
+          <t>水泥工業平上市</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>265.593417</v>
+      </c>
       <c r="C62" t="n">
-        <v>1667.061733</v>
-      </c>
-      <c r="D62" t="n">
-        <v>986.9098729999999</v>
-      </c>
+        <v>339.290351</v>
+      </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="n">
-        <v>1350.231246</v>
+        <v>420.783956</v>
       </c>
       <c r="F62" t="n">
-        <v>2481.360539</v>
+        <v>174.267952</v>
       </c>
       <c r="G62" t="n">
-        <v>875.090538</v>
+        <v>181.634068</v>
       </c>
       <c r="H62" t="n">
-        <v>1240.896853</v>
-      </c>
-      <c r="I62" t="n">
-        <v>1986.204073</v>
-      </c>
-      <c r="J62" t="n">
-        <v>2334.527893</v>
-      </c>
-      <c r="K62" t="n">
-        <v>2380.995649</v>
-      </c>
+        <v>245.309947</v>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>汽車工業右下上市</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr"/>
+          <t>汽車工業右上上市</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>835.009685</v>
+      </c>
       <c r="C63" t="n">
-        <v>450.3842975</v>
+        <v>1376.904598</v>
       </c>
       <c r="D63" t="n">
-        <v>421.929744</v>
+        <v>2530.817868</v>
       </c>
       <c r="E63" t="n">
-        <v>483.645075</v>
+        <v>894.608758</v>
       </c>
       <c r="F63" t="n">
-        <v>643.883054</v>
+        <v>1258.292474</v>
       </c>
       <c r="G63" t="n">
-        <v>489.08889</v>
+        <v>2023.334911</v>
       </c>
       <c r="H63" t="n">
-        <v>679.042829</v>
+        <v>2376.922796</v>
       </c>
       <c r="I63" t="n">
-        <v>762.597544</v>
+        <v>2425.893933</v>
       </c>
       <c r="J63" t="n">
-        <v>824.872317</v>
-      </c>
-      <c r="K63" t="n">
-        <v>809.163751</v>
+        <v>2445.453189</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>汽車工業平上市</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr"/>
+          <t>汽車工業右下上市</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>270.273582</v>
+      </c>
       <c r="C64" t="n">
-        <v>47.234421</v>
+        <v>464.299762</v>
       </c>
       <c r="D64" t="n">
-        <v>71.46666</v>
+        <v>412.71605</v>
       </c>
       <c r="E64" t="n">
-        <v>205.476519</v>
+        <v>323.712412</v>
       </c>
       <c r="F64" t="n">
-        <v>102.969442</v>
+        <v>374.118405</v>
       </c>
       <c r="G64" t="n">
-        <v>99.032276</v>
+        <v>620.992344</v>
       </c>
       <c r="H64" t="n">
-        <v>107.493555</v>
+        <v>714.964128</v>
       </c>
       <c r="I64" t="n">
-        <v>79.294453</v>
+        <v>731.875396</v>
       </c>
       <c r="J64" t="n">
-        <v>48.683687</v>
-      </c>
-      <c r="K64" t="n">
-        <v>245.669527</v>
+        <v>407.045715</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業右上上市</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr"/>
+          <t>汽車工業平上市</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>375.02301</v>
+      </c>
       <c r="C65" t="n">
-        <v>1207.454396</v>
+        <v>198.14848</v>
       </c>
       <c r="D65" t="n">
-        <v>1016.909933</v>
+        <v>284.679117</v>
       </c>
       <c r="E65" t="n">
-        <v>3902.406555</v>
+        <v>244.890534</v>
       </c>
       <c r="F65" t="n">
-        <v>3768.592343</v>
+        <v>395.022358</v>
       </c>
       <c r="G65" t="n">
-        <v>2658.038261</v>
+        <v>183.768815</v>
       </c>
       <c r="H65" t="n">
-        <v>3633.52439</v>
+        <v>116.196973</v>
       </c>
       <c r="I65" t="n">
-        <v>2116.46865</v>
+        <v>278.059598</v>
       </c>
       <c r="J65" t="n">
-        <v>2492.209885</v>
-      </c>
-      <c r="K65" t="n">
-        <v>3813.334009</v>
+        <v>175.608212</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業右下上市</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr"/>
+          <t>油電燃氣業右上上市</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>1016.909933</v>
+      </c>
       <c r="C66" t="n">
-        <v>4.671305</v>
+        <v>3827.737724</v>
       </c>
       <c r="D66" t="n">
-        <v>4.464252</v>
+        <v>3768.070051</v>
       </c>
       <c r="E66" t="n">
-        <v>6.8068</v>
+        <v>2657.525003</v>
       </c>
       <c r="F66" t="n">
-        <v>5.852749</v>
+        <v>3632.530573</v>
       </c>
       <c r="G66" t="n">
-        <v>3.578119</v>
+        <v>2115.763698</v>
       </c>
       <c r="H66" t="n">
-        <v>6.830817</v>
+        <v>2490.682467</v>
       </c>
       <c r="I66" t="n">
-        <v>6.653482</v>
+        <v>3811.980424</v>
       </c>
       <c r="J66" t="n">
-        <v>14.371924</v>
-      </c>
-      <c r="K66" t="n">
-        <v>7.965361</v>
+        <v>4743.536751</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr"/>
+          <t>油電燃氣業右下上市</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>4.464252</v>
+      </c>
       <c r="C67" t="n">
-        <v>0.010957</v>
+        <v>6.8068</v>
       </c>
       <c r="D67" t="n">
-        <v>0.015956</v>
+        <v>5.852749</v>
       </c>
       <c r="E67" t="n">
-        <v>0.007131</v>
+        <v>3.578119</v>
       </c>
       <c r="F67" t="n">
-        <v>0.013587</v>
+        <v>6.830817</v>
       </c>
       <c r="G67" t="n">
-        <v>0.004641</v>
+        <v>6.653482</v>
       </c>
       <c r="H67" t="n">
-        <v>0.003086</v>
+        <v>13.578305</v>
       </c>
       <c r="I67" t="n">
-        <v>0.007185</v>
+        <v>7.965361</v>
       </c>
       <c r="J67" t="n">
-        <v>0.017316</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0.005177</v>
+        <v>6.502614</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業平上市</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr"/>
+          <t>油電燃氣業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>0.003165</v>
+      </c>
       <c r="C68" t="n">
-        <v>1.498705</v>
+        <v>0.003294</v>
       </c>
       <c r="D68" t="n">
-        <v>0.416998</v>
+        <v>0.002846</v>
       </c>
       <c r="E68" t="n">
-        <v>0.624864</v>
+        <v>0.00394</v>
       </c>
       <c r="F68" t="n">
-        <v>0.498308</v>
+        <v>0.0022</v>
       </c>
       <c r="G68" t="n">
-        <v>0.174041</v>
-      </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
+        <v>0.007126</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.005304</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.005177</v>
+      </c>
       <c r="J68" t="n">
-        <v>0.707666</v>
-      </c>
-      <c r="K68" t="inlineStr"/>
+        <v>0.007192</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷右上上市</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr"/>
+          <t>油電燃氣業平上市</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>0.416998</v>
+      </c>
       <c r="C69" t="n">
-        <v>1239.984105</v>
+        <v>75.293695</v>
       </c>
       <c r="D69" t="n">
-        <v>800.372672</v>
+        <v>1.0206</v>
       </c>
       <c r="E69" t="n">
-        <v>1852.668564</v>
+        <v>0.687299</v>
       </c>
       <c r="F69" t="n">
-        <v>2390.876361</v>
+        <v>0.993817</v>
       </c>
       <c r="G69" t="n">
-        <v>1209.96481</v>
+        <v>0.704952</v>
       </c>
       <c r="H69" t="n">
-        <v>1288.698829</v>
+        <v>3.028703</v>
       </c>
       <c r="I69" t="n">
-        <v>1646.975672</v>
+        <v>1.353585</v>
       </c>
       <c r="J69" t="n">
-        <v>1582.051215</v>
-      </c>
-      <c r="K69" t="n">
-        <v>7133.346991</v>
+        <v>0.145691</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷右下上市</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr"/>
+          <t>油電燃氣業平上櫃</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>0.012791</v>
+      </c>
       <c r="C70" t="n">
-        <v>0.469083</v>
+        <v>0.003837</v>
       </c>
       <c r="D70" t="n">
-        <v>0.521244</v>
+        <v>0.010741</v>
       </c>
       <c r="E70" t="n">
-        <v>0.500364</v>
+        <v>0.000701</v>
       </c>
       <c r="F70" t="n">
-        <v>1.209878</v>
+        <v>0.000886</v>
       </c>
       <c r="G70" t="n">
-        <v>2.726514</v>
+        <v>5.9e-05</v>
       </c>
       <c r="H70" t="n">
-        <v>0.8914299999999999</v>
-      </c>
-      <c r="I70" t="n">
-        <v>1.117833</v>
-      </c>
-      <c r="J70" t="n">
-        <v>2.289033</v>
-      </c>
-      <c r="K70" t="n">
-        <v>2.318782</v>
-      </c>
+        <v>0.012012</v>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>玻璃陶瓷平上市</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr"/>
-      <c r="C71" t="inlineStr"/>
+          <t>玻璃陶瓷右上上市</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>336.767867</v>
+      </c>
+      <c r="C71" t="n">
+        <v>1394.507219</v>
+      </c>
       <c r="D71" t="n">
-        <v>0.744384</v>
+        <v>980.572891</v>
       </c>
       <c r="E71" t="n">
-        <v>1.920693</v>
+        <v>297.549161</v>
       </c>
       <c r="F71" t="n">
-        <v>1.202745</v>
+        <v>572.510755</v>
       </c>
       <c r="G71" t="n">
-        <v>0.680389</v>
+        <v>255.941381</v>
       </c>
       <c r="H71" t="n">
-        <v>0.440229</v>
+        <v>148.635317</v>
       </c>
       <c r="I71" t="n">
-        <v>0.617168</v>
+        <v>7135.401026</v>
       </c>
       <c r="J71" t="n">
-        <v>0.927306</v>
-      </c>
-      <c r="K71" t="n">
-        <v>2.054035</v>
+        <v>10430.466674</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右上上市</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr"/>
+          <t>玻璃陶瓷右下上市</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>0.521244</v>
+      </c>
       <c r="C72" t="n">
-        <v>5953.466659</v>
+        <v>0.500364</v>
       </c>
       <c r="D72" t="n">
-        <v>3086.680274</v>
+        <v>1.209878</v>
       </c>
       <c r="E72" t="n">
-        <v>3551.562761</v>
+        <v>2.726514</v>
       </c>
       <c r="F72" t="n">
-        <v>4179.722896</v>
+        <v>0.8914299999999999</v>
       </c>
       <c r="G72" t="n">
-        <v>6362.124208</v>
+        <v>1.117833</v>
       </c>
       <c r="H72" t="n">
-        <v>2847.010004</v>
+        <v>2.289033</v>
       </c>
       <c r="I72" t="n">
-        <v>3330.562763</v>
+        <v>2.318782</v>
       </c>
       <c r="J72" t="n">
-        <v>2953.448239</v>
-      </c>
-      <c r="K72" t="n">
-        <v>2975.550287</v>
+        <v>1.373989</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr"/>
+          <t>玻璃陶瓷平上市</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>464.349189</v>
+      </c>
       <c r="C73" t="n">
-        <v>0.8600989999999999</v>
+        <v>460.082038</v>
       </c>
       <c r="D73" t="n">
-        <v>0.669752</v>
+        <v>1411.506215</v>
       </c>
       <c r="E73" t="n">
-        <v>0.773203</v>
+        <v>913.096038</v>
       </c>
       <c r="F73" t="n">
-        <v>1.585432</v>
+        <v>716.628303</v>
       </c>
       <c r="G73" t="n">
-        <v>1.823919</v>
+        <v>1391.651459</v>
       </c>
       <c r="H73" t="n">
-        <v>1.303966</v>
-      </c>
-      <c r="I73" t="n">
-        <v>1.141856</v>
-      </c>
-      <c r="J73" t="n">
-        <v>1.251938</v>
-      </c>
-      <c r="K73" t="n">
-        <v>1.146116</v>
-      </c>
+        <v>1434.343204</v>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右下上市</t>
+          <t>生技醫療業右上上市</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0</v>
+        <v>4088.387545</v>
       </c>
       <c r="C74" t="n">
-        <v>1221.898304</v>
+        <v>3867.64655</v>
       </c>
       <c r="D74" t="n">
-        <v>932.288263</v>
+        <v>4196.073425</v>
       </c>
       <c r="E74" t="n">
-        <v>879.903049</v>
+        <v>6374.150305</v>
       </c>
       <c r="F74" t="n">
-        <v>1066.893617</v>
+        <v>2873.532273</v>
       </c>
       <c r="G74" t="n">
-        <v>929.41603</v>
+        <v>3358.834664</v>
       </c>
       <c r="H74" t="n">
-        <v>1420.761809</v>
+        <v>3005.278808</v>
       </c>
       <c r="I74" t="n">
-        <v>950.170583</v>
+        <v>3002.379064</v>
       </c>
       <c r="J74" t="n">
-        <v>788.7546620000001</v>
-      </c>
-      <c r="K74" t="n">
-        <v>1005.774936</v>
+        <v>3214.573675</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr"/>
+          <t>生技醫療業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>0.796296</v>
+      </c>
       <c r="C75" t="n">
-        <v>0.35046</v>
+        <v>0.814196</v>
       </c>
       <c r="D75" t="n">
-        <v>0.3230690833333333</v>
+        <v>1.607912</v>
       </c>
       <c r="E75" t="n">
-        <v>0.3475283333333333</v>
+        <v>1.910936</v>
       </c>
       <c r="F75" t="n">
-        <v>0.4610666666666667</v>
+        <v>1.355821</v>
       </c>
       <c r="G75" t="n">
-        <v>0.4453741666666667</v>
+        <v>1.149426</v>
       </c>
       <c r="H75" t="n">
-        <v>0.4118865</v>
+        <v>1.307722</v>
       </c>
       <c r="I75" t="n">
-        <v>0.7703614166666666</v>
+        <v>1.194648</v>
       </c>
       <c r="J75" t="n">
-        <v>0.54641775</v>
-      </c>
-      <c r="K75" t="n">
-        <v>0.443528</v>
+        <v>1.118477</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業平上市</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr"/>
+          <t>生技醫療業右下上市</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>882.589772</v>
+      </c>
       <c r="C76" t="n">
-        <v>44.7846</v>
+        <v>831.72542</v>
       </c>
       <c r="D76" t="n">
-        <v>1040.041374</v>
+        <v>987.591167</v>
       </c>
       <c r="E76" t="n">
-        <v>381.292726</v>
+        <v>570.880037</v>
       </c>
       <c r="F76" t="n">
-        <v>71.53824299999999</v>
+        <v>1361.174952</v>
       </c>
       <c r="G76" t="n">
-        <v>37.690678</v>
+        <v>948.955914</v>
       </c>
       <c r="H76" t="n">
-        <v>86.67742800000001</v>
+        <v>783.46231</v>
       </c>
       <c r="I76" t="n">
-        <v>90.371803</v>
+        <v>732.128429</v>
       </c>
       <c r="J76" t="n">
-        <v>92.51034799999999</v>
-      </c>
-      <c r="K76" t="n">
-        <v>45.753829</v>
+        <v>838.967899</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>生技醫療業平上櫃</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr"/>
+          <t>生技醫療業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>0.3164330833333333</v>
+      </c>
       <c r="C77" t="n">
-        <v>0.275593</v>
+        <v>0.3441363333333333</v>
       </c>
       <c r="D77" t="n">
-        <v>0.293708</v>
+        <v>0.3782826666666667</v>
       </c>
       <c r="E77" t="n">
-        <v>0.104061</v>
+        <v>0.3214551666666667</v>
       </c>
       <c r="F77" t="n">
-        <v>0.121558</v>
+        <v>0.3575395</v>
       </c>
       <c r="G77" t="n">
-        <v>0.08987299999999999</v>
+        <v>0.7056954166666666</v>
       </c>
       <c r="H77" t="n">
-        <v>0.09468699999999999</v>
+        <v>0.512689</v>
       </c>
       <c r="I77" t="n">
-        <v>0.090987</v>
+        <v>0.4181756666666667</v>
       </c>
       <c r="J77" t="n">
-        <v>0.116833</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0.046627</v>
+        <v>0.6329100833333333</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右上上市</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr"/>
+          <t>生技醫療業平上市</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>95.000366</v>
+      </c>
       <c r="C78" t="n">
-        <v>167.925014</v>
+        <v>121.884585</v>
       </c>
       <c r="D78" t="n">
-        <v>144.37402</v>
+        <v>149.655613</v>
       </c>
       <c r="E78" t="n">
-        <v>192.102061</v>
+        <v>393.7089</v>
       </c>
       <c r="F78" t="n">
-        <v>486.835413</v>
+        <v>129.548609</v>
       </c>
       <c r="G78" t="n">
-        <v>255.407393</v>
+        <v>84.137075</v>
       </c>
       <c r="H78" t="n">
-        <v>389.4149</v>
+        <v>63.975701</v>
       </c>
       <c r="I78" t="n">
-        <v>699.954172</v>
+        <v>302.440094</v>
       </c>
       <c r="J78" t="n">
-        <v>482.482272</v>
-      </c>
-      <c r="K78" t="n">
-        <v>1599.570799</v>
+        <v>96.23086600000001</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右上上櫃</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr"/>
+          <t>生技醫療業平上櫃</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>0.1738</v>
+      </c>
       <c r="C79" t="n">
-        <v>0.002614</v>
+        <v>0.06646000000000001</v>
       </c>
       <c r="D79" t="n">
-        <v>0.003562</v>
+        <v>0.181862</v>
       </c>
       <c r="E79" t="n">
-        <v>0.002342</v>
+        <v>0.126775</v>
       </c>
       <c r="F79" t="n">
-        <v>0.003026</v>
+        <v>0.097179</v>
       </c>
       <c r="G79" t="n">
-        <v>0.000842</v>
+        <v>0.148083</v>
       </c>
       <c r="H79" t="n">
-        <v>0.001892</v>
+        <v>0.09477774999999999</v>
       </c>
       <c r="I79" t="n">
-        <v>0.001417</v>
+        <v>0.02344733333333334</v>
       </c>
       <c r="J79" t="n">
-        <v>0.003773</v>
-      </c>
-      <c r="K79" t="n">
-        <v>0.009072</v>
+        <v>0.032002</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右下上市</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr"/>
+          <t>紡織纖維右上上市</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>292.472929</v>
+      </c>
       <c r="C80" t="n">
-        <v>528.422161</v>
+        <v>185.653581</v>
       </c>
       <c r="D80" t="n">
-        <v>563.181368</v>
+        <v>680.52637</v>
       </c>
       <c r="E80" t="n">
-        <v>498.794683</v>
+        <v>253.387223</v>
       </c>
       <c r="F80" t="n">
-        <v>691.878292</v>
+        <v>522.9243310000001</v>
       </c>
       <c r="G80" t="n">
-        <v>430.52915</v>
+        <v>698.51841</v>
       </c>
       <c r="H80" t="n">
-        <v>409.086257</v>
+        <v>474.371744</v>
       </c>
       <c r="I80" t="n">
-        <v>926.442956</v>
+        <v>1814.314575</v>
       </c>
       <c r="J80" t="n">
-        <v>1354.297717</v>
-      </c>
-      <c r="K80" t="n">
-        <v>1338.355974</v>
+        <v>1050.98659</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維右下上櫃</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr"/>
+          <t>紡織纖維右上上櫃</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>0.003562</v>
+      </c>
       <c r="C81" t="n">
-        <v>0.003755</v>
+        <v>0.002342</v>
       </c>
       <c r="D81" t="n">
-        <v>0.003316</v>
+        <v>0.003026</v>
       </c>
       <c r="E81" t="n">
-        <v>0.001696</v>
+        <v>0.000842</v>
       </c>
       <c r="F81" t="n">
-        <v>0.005551</v>
+        <v>0.001892</v>
       </c>
       <c r="G81" t="n">
-        <v>0.001959</v>
+        <v>0.001417</v>
       </c>
       <c r="H81" t="n">
-        <v>0.002287</v>
+        <v>0.003551</v>
       </c>
       <c r="I81" t="n">
-        <v>0.004319</v>
+        <v>0.002177</v>
       </c>
       <c r="J81" t="n">
-        <v>0.005732</v>
-      </c>
-      <c r="K81" t="n">
-        <v>0.001899</v>
+        <v>0.002726</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維平上市</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr"/>
+          <t>紡織纖維右下上市</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>559.467184</v>
+      </c>
       <c r="C82" t="n">
-        <v>184.572468</v>
+        <v>497.35158</v>
       </c>
       <c r="D82" t="n">
-        <v>233.877082</v>
+        <v>690.9260829999999</v>
       </c>
       <c r="E82" t="n">
-        <v>217.291177</v>
+        <v>429.938206</v>
       </c>
       <c r="F82" t="n">
-        <v>208.142903</v>
+        <v>409.600498</v>
       </c>
       <c r="G82" t="n">
-        <v>462.188773</v>
+        <v>925.605107</v>
       </c>
       <c r="H82" t="n">
-        <v>175.527518</v>
+        <v>1353.881129</v>
       </c>
       <c r="I82" t="n">
-        <v>242.359446</v>
+        <v>1441.814826</v>
       </c>
       <c r="J82" t="n">
-        <v>151.501059</v>
-      </c>
-      <c r="K82" t="n">
-        <v>262.854959</v>
+        <v>1645.888639</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>紡織纖維平上櫃</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr"/>
+          <t>紡織纖維右下上櫃</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>0.003866</v>
+      </c>
       <c r="C83" t="n">
-        <v>0.003386</v>
+        <v>0.002449</v>
       </c>
       <c r="D83" t="n">
-        <v>0.001797</v>
+        <v>0.005551</v>
       </c>
       <c r="E83" t="n">
-        <v>0.002898</v>
+        <v>0.003023</v>
       </c>
       <c r="F83" t="n">
-        <v>0.003993</v>
+        <v>0.002772</v>
       </c>
       <c r="G83" t="n">
-        <v>0.002768</v>
+        <v>0.004978</v>
       </c>
       <c r="H83" t="n">
-        <v>0.00236</v>
+        <v>0.006434</v>
       </c>
       <c r="I83" t="n">
-        <v>0.004905</v>
+        <v>0.003073</v>
       </c>
       <c r="J83" t="n">
-        <v>0.00288</v>
-      </c>
-      <c r="K83" t="n">
-        <v>0.008343</v>
+        <v>0.004224</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右上上市</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr"/>
+          <t>紡織纖維平上市</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>89.492357</v>
+      </c>
       <c r="C84" t="n">
-        <v>1080.528652</v>
+        <v>225.18276</v>
       </c>
       <c r="D84" t="n">
-        <v>1065.762051</v>
+        <v>15.404155</v>
       </c>
       <c r="E84" t="n">
-        <v>1587.058712</v>
+        <v>464.799887</v>
       </c>
       <c r="F84" t="n">
-        <v>1847.634114</v>
+        <v>41.503846</v>
       </c>
       <c r="G84" t="n">
-        <v>1606.405262</v>
+        <v>244.633057</v>
       </c>
       <c r="H84" t="n">
-        <v>1655.750715</v>
+        <v>160.028175</v>
       </c>
       <c r="I84" t="n">
-        <v>2934.521909</v>
+        <v>47.701511</v>
       </c>
       <c r="J84" t="n">
-        <v>1506.37993</v>
-      </c>
-      <c r="K84" t="n">
-        <v>3645.680742</v>
+        <v>11.080909</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右上上櫃</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr"/>
+          <t>紡織纖維平上櫃</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>0.001247</v>
+      </c>
       <c r="C85" t="n">
-        <v>0.08539099999999999</v>
+        <v>0.002145</v>
       </c>
       <c r="D85" t="n">
-        <v>0.08933199999999999</v>
+        <v>0.003993</v>
       </c>
       <c r="E85" t="n">
-        <v>0.210435</v>
+        <v>0.001704</v>
       </c>
       <c r="F85" t="n">
-        <v>0.210932</v>
+        <v>0.001875</v>
       </c>
       <c r="G85" t="n">
-        <v>0.278157</v>
+        <v>0.004246</v>
       </c>
       <c r="H85" t="n">
-        <v>0.668552</v>
+        <v>0.0024</v>
       </c>
       <c r="I85" t="n">
-        <v>0.483589</v>
+        <v>0.014064</v>
       </c>
       <c r="J85" t="n">
-        <v>0.411683</v>
-      </c>
-      <c r="K85" t="n">
-        <v>0.483954</v>
+        <v>0.001411</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右下上市</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr"/>
+          <t>綠能環保右上上市</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>987.254875</v>
+      </c>
       <c r="C86" t="n">
-        <v>308.43768</v>
+        <v>1065.228574</v>
       </c>
       <c r="D86" t="n">
-        <v>287.683514</v>
+        <v>1461.418548</v>
       </c>
       <c r="E86" t="n">
-        <v>274.468824</v>
+        <v>1090.069752</v>
       </c>
       <c r="F86" t="n">
-        <v>248.735441</v>
+        <v>1296.447198</v>
       </c>
       <c r="G86" t="n">
-        <v>280.548546</v>
+        <v>2458.697829</v>
       </c>
       <c r="H86" t="n">
-        <v>316.477195</v>
+        <v>1089.254445</v>
       </c>
       <c r="I86" t="n">
-        <v>515.226859</v>
+        <v>3645.680742</v>
       </c>
       <c r="J86" t="n">
-        <v>319.441993</v>
-      </c>
-      <c r="K86" t="n">
-        <v>274.473049</v>
+        <v>2522.789547</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>綠能環保右下上櫃</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr"/>
+          <t>綠能環保右上上櫃</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>0.08933199999999999</v>
+      </c>
       <c r="C87" t="n">
-        <v>0.02672833333333334</v>
+        <v>0.031627</v>
       </c>
       <c r="D87" t="n">
-        <v>0.016288</v>
+        <v>0.034733</v>
       </c>
       <c r="E87" t="n">
-        <v>0.03483266666666667</v>
+        <v>0.06268700000000001</v>
       </c>
       <c r="F87" t="n">
-        <v>0.024313</v>
+        <v>0.668552</v>
       </c>
       <c r="G87" t="n">
-        <v>0.017407</v>
+        <v>0.483589</v>
       </c>
       <c r="H87" t="n">
-        <v>0.023258</v>
+        <v>0.361396</v>
       </c>
       <c r="I87" t="n">
-        <v>0.049814</v>
+        <v>0.4501</v>
       </c>
       <c r="J87" t="n">
-        <v>0.038306</v>
-      </c>
-      <c r="K87" t="n">
-        <v>0.036366</v>
+        <v>0.240485</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>綠能環保平上市</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr"/>
+          <t>綠能環保右下上市</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>278.616048</v>
+      </c>
       <c r="C88" t="n">
-        <v>247.562415</v>
+        <v>274.468824</v>
       </c>
       <c r="D88" t="n">
-        <v>368.456756</v>
+        <v>246.334542</v>
       </c>
       <c r="E88" t="n">
-        <v>22.530052</v>
+        <v>273.107014</v>
       </c>
       <c r="F88" t="n">
-        <v>23.316133</v>
+        <v>308.175048</v>
       </c>
       <c r="G88" t="n">
-        <v>22.036377</v>
+        <v>514.506952</v>
       </c>
       <c r="H88" t="n">
-        <v>23.016278</v>
+        <v>314.34913</v>
       </c>
       <c r="I88" t="n">
-        <v>37.641095</v>
+        <v>273.137988</v>
       </c>
       <c r="J88" t="n">
-        <v>19.4716</v>
-      </c>
-      <c r="K88" t="n">
-        <v>13.093158</v>
+        <v>276.479222</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>綠能環保平上櫃</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr"/>
+          <t>綠能環保右下上櫃</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>0.114534</v>
+      </c>
       <c r="C89" t="n">
-        <v>0.260887</v>
+        <v>0.06042566666666667</v>
       </c>
       <c r="D89" t="n">
-        <v>0.098638</v>
+        <v>0.040755</v>
       </c>
       <c r="E89" t="n">
-        <v>0.025832</v>
+        <v>0.03678</v>
       </c>
       <c r="F89" t="n">
-        <v>0.018125</v>
+        <v>0.041197</v>
       </c>
       <c r="G89" t="n">
-        <v>0.019877</v>
+        <v>0.112541</v>
       </c>
       <c r="H89" t="n">
-        <v>0.018939</v>
+        <v>0.09009399999999999</v>
       </c>
       <c r="I89" t="n">
-        <v>0.064306</v>
+        <v>0.070425</v>
       </c>
       <c r="J89" t="n">
-        <v>0.001511</v>
-      </c>
-      <c r="K89" t="n">
-        <v>0.00081</v>
+        <v>0.06356924999999999</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>航運業右上上市</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr"/>
+          <t>綠能環保平上市</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>456.031398</v>
+      </c>
       <c r="C90" t="n">
-        <v>5141.094921</v>
+        <v>544.36019</v>
       </c>
       <c r="D90" t="n">
-        <v>3937.638722</v>
+        <v>411.932598</v>
       </c>
       <c r="E90" t="n">
-        <v>4902.34093</v>
+        <v>545.813419</v>
       </c>
       <c r="F90" t="n">
-        <v>4162.974965</v>
+        <v>390.621942</v>
       </c>
       <c r="G90" t="n">
-        <v>3628.725363</v>
+        <v>514.185082</v>
       </c>
       <c r="H90" t="n">
-        <v>4015.794107</v>
+        <v>441.689948</v>
       </c>
       <c r="I90" t="n">
-        <v>4930.886461</v>
+        <v>14.428219</v>
       </c>
       <c r="J90" t="n">
-        <v>4047.080616</v>
-      </c>
-      <c r="K90" t="n">
-        <v>4045.095073</v>
+        <v>14.834161</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>航運業右下上市</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr"/>
+          <t>綠能環保平上櫃</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>0.000392</v>
+      </c>
       <c r="C91" t="n">
-        <v>201.193499</v>
+        <v>0.179047</v>
       </c>
       <c r="D91" t="n">
-        <v>172.265618</v>
+        <v>0.177882</v>
       </c>
       <c r="E91" t="n">
-        <v>246.817529</v>
+        <v>0.215974</v>
       </c>
       <c r="F91" t="n">
-        <v>207.837683</v>
+        <v>0.001</v>
       </c>
       <c r="G91" t="n">
-        <v>149.091351</v>
+        <v>0.001579</v>
       </c>
       <c r="H91" t="n">
-        <v>190.484063</v>
+        <v>1e-05</v>
       </c>
       <c r="I91" t="n">
-        <v>276.736665</v>
+        <v>0.000605</v>
       </c>
       <c r="J91" t="n">
-        <v>249.350191</v>
-      </c>
-      <c r="K91" t="n">
-        <v>161.448402</v>
+        <v>0.000511</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>航運業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr"/>
+          <t>航運業右上上市</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>4550.993342</v>
+      </c>
       <c r="C92" t="n">
-        <v>0.0187445</v>
+        <v>6235.148024</v>
       </c>
       <c r="D92" t="n">
-        <v>0.012347</v>
+        <v>5045.109869</v>
       </c>
       <c r="E92" t="n">
-        <v>0.018943</v>
+        <v>4288.824517</v>
       </c>
       <c r="F92" t="n">
-        <v>0.021786</v>
+        <v>4613.845504</v>
       </c>
       <c r="G92" t="n">
-        <v>0.018536</v>
+        <v>5575.912177</v>
       </c>
       <c r="H92" t="n">
-        <v>0.021268</v>
+        <v>4810.449258</v>
       </c>
       <c r="I92" t="n">
-        <v>0.0430535</v>
+        <v>4540.463065</v>
       </c>
       <c r="J92" t="n">
-        <v>0.023512</v>
-      </c>
-      <c r="K92" t="n">
-        <v>0.01764933333333333</v>
+        <v>3709.174479</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>航運業平上市</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr"/>
+          <t>航運業右下上市</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>223.085712</v>
+      </c>
       <c r="C93" t="n">
-        <v>2588.8407</v>
+        <v>319.29705</v>
       </c>
       <c r="D93" t="n">
-        <v>1356.772584</v>
+        <v>272.893445</v>
       </c>
       <c r="E93" t="n">
-        <v>1696.867779</v>
+        <v>227.609198</v>
       </c>
       <c r="F93" t="n">
-        <v>1473.299704</v>
+        <v>252.512685</v>
       </c>
       <c r="G93" t="n">
-        <v>1135.708164</v>
+        <v>366.233668</v>
       </c>
       <c r="H93" t="n">
-        <v>953.812262</v>
+        <v>309.11194</v>
       </c>
       <c r="I93" t="n">
-        <v>1262.589742</v>
+        <v>207.834935</v>
       </c>
       <c r="J93" t="n">
-        <v>1164.609844</v>
-      </c>
-      <c r="K93" t="n">
-        <v>889.168131</v>
+        <v>263.86298</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>航運業平上櫃</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr"/>
+          <t>航運業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>0.015171</v>
+      </c>
       <c r="C94" t="n">
-        <v>0.003643</v>
+        <v>0.027518</v>
       </c>
       <c r="D94" t="n">
-        <v>0.002824</v>
+        <v>0.031577</v>
       </c>
       <c r="E94" t="n">
-        <v>0.008574999999999999</v>
+        <v>0.018536</v>
       </c>
       <c r="F94" t="n">
-        <v>0.009790999999999999</v>
-      </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
+        <v>0.021268</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0.0430535</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0.043256</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0.01764933333333333</v>
+      </c>
       <c r="J94" t="n">
-        <v>0.019744</v>
-      </c>
-      <c r="K94" t="n">
-        <v>0.01569</v>
+        <v>0.013256</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右上上市</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr"/>
+          <t>航運業平上市</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>692.5978699999999</v>
+      </c>
       <c r="C95" t="n">
-        <v>11.00032</v>
+        <v>291.581164</v>
       </c>
       <c r="D95" t="n">
-        <v>8.780357</v>
+        <v>526.1090380000001</v>
       </c>
       <c r="E95" t="n">
-        <v>105.657624</v>
+        <v>397.091163</v>
       </c>
       <c r="F95" t="n">
-        <v>79.71870199999999</v>
+        <v>293.732243</v>
       </c>
       <c r="G95" t="n">
-        <v>49.868836</v>
+        <v>528.0670229999999</v>
       </c>
       <c r="H95" t="n">
-        <v>57.785976</v>
+        <v>341.479453</v>
       </c>
       <c r="I95" t="n">
-        <v>42.157955</v>
+        <v>347.413606</v>
       </c>
       <c r="J95" t="n">
-        <v>24.130511</v>
-      </c>
-      <c r="K95" t="n">
-        <v>69.97319400000001</v>
+        <v>342.991155</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右上上櫃</t>
+          <t>航運業平上櫃</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
-      <c r="C96" t="n">
-        <v>0.005545</v>
-      </c>
-      <c r="D96" t="n">
-        <v>0.005721</v>
-      </c>
-      <c r="E96" t="n">
-        <v>0.009771999999999999</v>
-      </c>
-      <c r="F96" t="n">
-        <v>0.028757</v>
-      </c>
-      <c r="G96" t="n">
-        <v>0.0221915</v>
-      </c>
-      <c r="H96" t="n">
-        <v>0.003814</v>
-      </c>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
       <c r="I96" t="n">
-        <v>0.002144</v>
+        <v>0.01569</v>
       </c>
       <c r="J96" t="n">
-        <v>0.002969</v>
-      </c>
-      <c r="K96" t="n">
-        <v>0.002034</v>
+        <v>0.013006</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右下上市</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr"/>
+          <t>觀光事業右上上市</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>135.017384</v>
+      </c>
       <c r="C97" t="n">
-        <v>73.746514</v>
+        <v>139.47937</v>
       </c>
       <c r="D97" t="n">
-        <v>57.692754</v>
+        <v>81.415419</v>
       </c>
       <c r="E97" t="n">
-        <v>82.187201</v>
+        <v>52.444073</v>
       </c>
       <c r="F97" t="n">
-        <v>75.432047</v>
+        <v>95.54313500000001</v>
       </c>
       <c r="G97" t="n">
-        <v>40.885461</v>
+        <v>62.716002</v>
       </c>
       <c r="H97" t="n">
-        <v>48.094337</v>
+        <v>27.640307</v>
       </c>
       <c r="I97" t="n">
-        <v>76.15819</v>
+        <v>72.461392</v>
       </c>
       <c r="J97" t="n">
-        <v>80.90887600000001</v>
-      </c>
-      <c r="K97" t="n">
-        <v>48.119094</v>
+        <v>154.0976</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>觀光事業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr"/>
+          <t>觀光事業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>0.005694</v>
+      </c>
       <c r="C98" t="n">
-        <v>0.038824</v>
+        <v>0.009537</v>
       </c>
       <c r="D98" t="n">
-        <v>0.031206</v>
+        <v>0.028504</v>
       </c>
       <c r="E98" t="n">
-        <v>0.026004</v>
+        <v>0.0221175</v>
       </c>
       <c r="F98" t="n">
-        <v>0.026931</v>
+        <v>0.00347</v>
       </c>
       <c r="G98" t="n">
-        <v>0.02033</v>
+        <v>0.001891</v>
       </c>
       <c r="H98" t="n">
-        <v>0.02405725</v>
+        <v>0.002712</v>
       </c>
       <c r="I98" t="n">
-        <v>0.033866</v>
+        <v>0.001863</v>
       </c>
       <c r="J98" t="n">
-        <v>0.048066</v>
-      </c>
-      <c r="K98" t="n">
-        <v>0.045128</v>
+        <v>0.003763</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>觀光事業平上市</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr"/>
+          <t>觀光事業右下上市</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>57.692754</v>
+      </c>
       <c r="C99" t="n">
-        <v>43.501803</v>
+        <v>82.187201</v>
       </c>
       <c r="D99" t="n">
-        <v>126.618067</v>
+        <v>75.432047</v>
       </c>
       <c r="E99" t="n">
-        <v>34.528757</v>
+        <v>40.885461</v>
       </c>
       <c r="F99" t="n">
-        <v>1.696717</v>
+        <v>48.094337</v>
       </c>
       <c r="G99" t="n">
-        <v>73.502138</v>
+        <v>76.15819</v>
       </c>
       <c r="H99" t="n">
-        <v>37.757159</v>
+        <v>61.827034</v>
       </c>
       <c r="I99" t="n">
-        <v>36.973401</v>
+        <v>48.119094</v>
       </c>
       <c r="J99" t="n">
-        <v>5.294105</v>
-      </c>
-      <c r="K99" t="n">
-        <v>22.853852</v>
+        <v>70.66310900000001</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>觀光事業平上櫃</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr"/>
+          <t>觀光事業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>0.031141</v>
+      </c>
       <c r="C100" t="n">
-        <v>0.001799</v>
+        <v>0.025722</v>
       </c>
       <c r="D100" t="n">
-        <v>0.001541</v>
+        <v>0.025105</v>
       </c>
       <c r="E100" t="n">
-        <v>0.00026275</v>
+        <v>0.021688</v>
       </c>
       <c r="F100" t="n">
-        <v>0.000408</v>
-      </c>
-      <c r="G100" t="inlineStr"/>
+        <v>0.02571725</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0.035702</v>
+      </c>
       <c r="H100" t="n">
-        <v>0.000231</v>
+        <v>0.051818</v>
       </c>
       <c r="I100" t="n">
-        <v>0.000167</v>
+        <v>0.046472</v>
       </c>
       <c r="J100" t="n">
-        <v>4.8e-05</v>
-      </c>
-      <c r="K100" t="n">
-        <v>0.000685</v>
+        <v>0.044677</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨右上上市</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr"/>
+          <t>觀光事業平上市</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>0.38104</v>
+      </c>
       <c r="C101" t="n">
-        <v>172.011245</v>
-      </c>
-      <c r="D101" t="n">
-        <v>123.089602</v>
-      </c>
+        <v>0.7070109999999999</v>
+      </c>
+      <c r="D101" t="inlineStr"/>
       <c r="E101" t="n">
-        <v>123.734111</v>
-      </c>
-      <c r="F101" t="n">
-        <v>101.188944</v>
-      </c>
+        <v>70.926901</v>
+      </c>
+      <c r="F101" t="inlineStr"/>
       <c r="G101" t="n">
-        <v>96.374189</v>
+        <v>16.415354</v>
       </c>
       <c r="H101" t="n">
-        <v>114.310155</v>
+        <v>20.866151</v>
       </c>
       <c r="I101" t="n">
-        <v>117.16523</v>
-      </c>
-      <c r="J101" t="n">
-        <v>72.46779100000001</v>
-      </c>
-      <c r="K101" t="n">
-        <v>97.059353</v>
-      </c>
+        <v>20.365654</v>
+      </c>
+      <c r="J101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨右下上市</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr"/>
+          <t>觀光事業平上櫃</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>0.001633</v>
+      </c>
       <c r="C102" t="n">
-        <v>530.455793</v>
+        <v>0.00077975</v>
       </c>
       <c r="D102" t="n">
-        <v>482.217237</v>
+        <v>0.002487</v>
       </c>
       <c r="E102" t="n">
-        <v>354.9255993333333</v>
+        <v>0.000375</v>
       </c>
       <c r="F102" t="n">
-        <v>368.929928</v>
+        <v>0.00052</v>
       </c>
       <c r="G102" t="n">
-        <v>516.631265</v>
+        <v>0.001889</v>
       </c>
       <c r="H102" t="n">
-        <v>677.631095</v>
+        <v>0.000857</v>
       </c>
       <c r="I102" t="n">
-        <v>293.270035</v>
+        <v>0.001086</v>
       </c>
       <c r="J102" t="n">
-        <v>369.115774</v>
-      </c>
-      <c r="K102" t="n">
-        <v>448.56876</v>
+        <v>0.003676</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>貿易百貨平上市</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr"/>
+          <t>貿易百貨右上上市</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>124.12725</v>
+      </c>
       <c r="C103" t="n">
-        <v>24.741599</v>
+        <v>123.87734</v>
       </c>
       <c r="D103" t="n">
-        <v>21.066168</v>
+        <v>101.572075</v>
       </c>
       <c r="E103" t="n">
-        <v>0.99844</v>
+        <v>97.257312</v>
       </c>
       <c r="F103" t="n">
-        <v>40.741601</v>
+        <v>116.831751</v>
       </c>
       <c r="G103" t="n">
-        <v>2.296363</v>
+        <v>120.134948</v>
       </c>
       <c r="H103" t="n">
-        <v>4.231909</v>
+        <v>75.797059</v>
       </c>
       <c r="I103" t="n">
-        <v>3.785008</v>
+        <v>100.231123</v>
       </c>
       <c r="J103" t="n">
-        <v>5.179322</v>
-      </c>
-      <c r="K103" t="n">
-        <v>4.211703</v>
+        <v>122.263959</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右上上市</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr"/>
+          <t>貿易百貨右下上市</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>502.007682</v>
+      </c>
       <c r="C104" t="n">
-        <v>684.8656130000001</v>
+        <v>353.8224913333333</v>
       </c>
       <c r="D104" t="n">
-        <v>733.865583</v>
+        <v>405.806172</v>
       </c>
       <c r="E104" t="n">
-        <v>418.030885</v>
+        <v>516.970554</v>
       </c>
       <c r="F104" t="n">
-        <v>547.916906</v>
+        <v>676.738581</v>
       </c>
       <c r="G104" t="n">
-        <v>262.218864</v>
+        <v>292.238365</v>
       </c>
       <c r="H104" t="n">
-        <v>217.2931</v>
+        <v>369.115774</v>
       </c>
       <c r="I104" t="n">
-        <v>345.014255</v>
+        <v>448.220202</v>
       </c>
       <c r="J104" t="n">
-        <v>256.285556</v>
-      </c>
-      <c r="K104" t="n">
-        <v>448.100883</v>
+        <v>441.994205</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr"/>
+          <t>貿易百貨平上市</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>0.238075</v>
+      </c>
       <c r="C105" t="n">
-        <v>0.06589</v>
+        <v>1.958319</v>
       </c>
       <c r="D105" t="n">
-        <v>0.316551</v>
+        <v>3.482226</v>
       </c>
       <c r="E105" t="n">
-        <v>0.151087</v>
+        <v>1.073951</v>
       </c>
       <c r="F105" t="n">
-        <v>0.145614</v>
+        <v>2.602827</v>
       </c>
       <c r="G105" t="n">
-        <v>0.440767</v>
+        <v>1.84696</v>
       </c>
       <c r="H105" t="n">
-        <v>0.579151</v>
+        <v>1.850054</v>
       </c>
       <c r="I105" t="n">
-        <v>0.405653</v>
+        <v>1.388491</v>
       </c>
       <c r="J105" t="n">
-        <v>1.006223</v>
-      </c>
-      <c r="K105" t="n">
-        <v>0.495084</v>
+        <v>0.335951</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右下上市</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr"/>
+          <t>資訊服務業右上上市</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>921.361164</v>
+      </c>
       <c r="C106" t="n">
-        <v>31.30314</v>
+        <v>525.655053</v>
       </c>
       <c r="D106" t="n">
-        <v>32.514739</v>
+        <v>637.545508</v>
       </c>
       <c r="E106" t="n">
-        <v>30.620833</v>
+        <v>335.86408</v>
       </c>
       <c r="F106" t="n">
-        <v>33.041287</v>
+        <v>309.39226</v>
       </c>
       <c r="G106" t="n">
-        <v>23.291445</v>
+        <v>538.491268</v>
       </c>
       <c r="H106" t="n">
-        <v>26.608812</v>
+        <v>622.022591</v>
       </c>
       <c r="I106" t="n">
-        <v>204.47693</v>
+        <v>564.146935</v>
       </c>
       <c r="J106" t="n">
-        <v>125.183585</v>
-      </c>
-      <c r="K106" t="n">
-        <v>62.836432</v>
+        <v>399.894101</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr"/>
+          <t>資訊服務業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>0.624803</v>
+      </c>
       <c r="C107" t="n">
-        <v>0.080763</v>
+        <v>0.272337</v>
       </c>
       <c r="D107" t="n">
-        <v>0.05816</v>
+        <v>0.270188</v>
       </c>
       <c r="E107" t="n">
-        <v>0.042404</v>
+        <v>0.531964</v>
       </c>
       <c r="F107" t="n">
-        <v>0.046353</v>
+        <v>0.654319</v>
       </c>
       <c r="G107" t="n">
-        <v>0.100276</v>
+        <v>0.479901</v>
       </c>
       <c r="H107" t="n">
-        <v>0.061166</v>
+        <v>1.319274</v>
       </c>
       <c r="I107" t="n">
-        <v>0.108952</v>
+        <v>0.570715</v>
       </c>
       <c r="J107" t="n">
-        <v>0.15871675</v>
-      </c>
-      <c r="K107" t="n">
-        <v>0.092221</v>
+        <v>0.845659</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業平上市</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr"/>
+          <t>資訊服務業右下上市</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>6.540235</v>
+      </c>
       <c r="C108" t="n">
-        <v>143.446269</v>
+        <v>16.557683</v>
       </c>
       <c r="D108" t="n">
-        <v>210.135385</v>
+        <v>8.925591000000001</v>
       </c>
       <c r="E108" t="n">
-        <v>117.282981</v>
+        <v>4.865924</v>
       </c>
       <c r="F108" t="n">
-        <v>97.582365</v>
+        <v>13.219645</v>
       </c>
       <c r="G108" t="n">
-        <v>73.645216</v>
+        <v>64.06024600000001</v>
       </c>
       <c r="H108" t="n">
-        <v>96.94449</v>
+        <v>42.807068</v>
       </c>
       <c r="I108" t="n">
-        <v>193.477013</v>
+        <v>33.664185</v>
       </c>
       <c r="J108" t="n">
-        <v>365.737035</v>
-      </c>
-      <c r="K108" t="n">
-        <v>118.763697</v>
+        <v>32.140272</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>資訊服務業平上櫃</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr"/>
+          <t>資訊服務業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>0.06328499999999999</v>
+      </c>
       <c r="C109" t="n">
-        <v>0.178189</v>
+        <v>0.0534</v>
       </c>
       <c r="D109" t="n">
-        <v>0.49717</v>
+        <v>0.09637</v>
       </c>
       <c r="E109" t="n">
-        <v>0.30398</v>
+        <v>0.060962</v>
       </c>
       <c r="F109" t="n">
-        <v>0.303025</v>
+        <v>0.066687</v>
       </c>
       <c r="G109" t="n">
-        <v>0.13175</v>
+        <v>0.221183</v>
       </c>
       <c r="H109" t="n">
-        <v>0.194943</v>
+        <v>0.10333425</v>
       </c>
       <c r="I109" t="n">
-        <v>0.292558</v>
+        <v>0.079579</v>
       </c>
       <c r="J109" t="n">
-        <v>0.3342795</v>
-      </c>
-      <c r="K109" t="n">
-        <v>0.148242</v>
+        <v>0.121471</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>農業科技業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr"/>
+          <t>資訊服務業平上市</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>48.614308</v>
+      </c>
       <c r="C110" t="n">
-        <v>0.003346</v>
+        <v>23.721963</v>
       </c>
       <c r="D110" t="n">
-        <v>0.00109</v>
+        <v>32.069459</v>
       </c>
       <c r="E110" t="n">
-        <v>0.000695</v>
+        <v>18.425521</v>
       </c>
       <c r="F110" t="n">
-        <v>0.000838</v>
+        <v>18.234497</v>
       </c>
       <c r="G110" t="n">
-        <v>0.00054</v>
+        <v>140.416684</v>
       </c>
       <c r="H110" t="n">
-        <v>0.00107</v>
-      </c>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="n">
-        <v>0.000827</v>
+        <v>82.37651700000001</v>
+      </c>
+      <c r="I110" t="n">
+        <v>31.889892</v>
+      </c>
+      <c r="J110" t="n">
+        <v>18.274081</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>農業科技業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr"/>
+          <t>資訊服務業平上櫃</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>0.183793</v>
+      </c>
       <c r="C111" t="n">
-        <v>0.00236</v>
+        <v>0.171734</v>
       </c>
       <c r="D111" t="n">
-        <v>0.004261</v>
+        <v>0.128434</v>
       </c>
       <c r="E111" t="n">
-        <v>0.002522</v>
+        <v>0.07986699999999999</v>
       </c>
       <c r="F111" t="n">
-        <v>0.002449</v>
+        <v>0.114254</v>
       </c>
       <c r="G111" t="n">
-        <v>0.00161</v>
+        <v>0.106079</v>
       </c>
       <c r="H111" t="n">
-        <v>0.001331</v>
+        <v>0.076611</v>
       </c>
       <c r="I111" t="n">
-        <v>0.007381</v>
+        <v>0.085253</v>
       </c>
       <c r="J111" t="n">
-        <v>0.003454</v>
-      </c>
-      <c r="K111" t="n">
-        <v>0.02229</v>
+        <v>0.074637</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>農業科技業平上櫃</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr"/>
-      <c r="C112" t="inlineStr"/>
-      <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr"/>
+          <t>農業科技業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>0.00109</v>
+      </c>
+      <c r="C112" t="n">
+        <v>0.000695</v>
+      </c>
+      <c r="D112" t="n">
+        <v>0.000838</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0.00054</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0.00107</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0.00094</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0.00105</v>
+      </c>
       <c r="I112" t="n">
-        <v>0.00094</v>
+        <v>0.000827</v>
       </c>
       <c r="J112" t="n">
-        <v>0.00105</v>
-      </c>
-      <c r="K112" t="inlineStr"/>
+        <v>0.051904</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>通信網路業右上上市</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr"/>
+          <t>農業科技業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>0.004261</v>
+      </c>
       <c r="C113" t="n">
-        <v>17046.602242</v>
+        <v>0.002522</v>
       </c>
       <c r="D113" t="n">
-        <v>12598.586921</v>
+        <v>0.002449</v>
       </c>
       <c r="E113" t="n">
-        <v>15290.862009</v>
+        <v>0.00161</v>
       </c>
       <c r="F113" t="n">
-        <v>21928.342371</v>
+        <v>0.001331</v>
       </c>
       <c r="G113" t="n">
-        <v>16945.150652</v>
+        <v>0.007381</v>
       </c>
       <c r="H113" t="n">
-        <v>25518.394772</v>
+        <v>0.003454</v>
       </c>
       <c r="I113" t="n">
-        <v>31299.192109</v>
+        <v>0.003542</v>
       </c>
       <c r="J113" t="n">
-        <v>29029.74642</v>
-      </c>
-      <c r="K113" t="n">
-        <v>35810.28133</v>
+        <v>0.001365</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>通信網路業右上上櫃</t>
+          <t>農業科技業平上櫃</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
-      <c r="C114" t="n">
-        <v>26.213372</v>
-      </c>
-      <c r="D114" t="n">
-        <v>15.436857</v>
-      </c>
-      <c r="E114" t="n">
-        <v>9.591949</v>
-      </c>
-      <c r="F114" t="n">
-        <v>9.349261</v>
-      </c>
-      <c r="G114" t="n">
-        <v>11.691037</v>
-      </c>
-      <c r="H114" t="n">
-        <v>26.466939</v>
-      </c>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
       <c r="I114" t="n">
-        <v>36.447042</v>
-      </c>
-      <c r="J114" t="n">
-        <v>27.578384</v>
-      </c>
-      <c r="K114" t="n">
-        <v>41.824289</v>
-      </c>
+        <v>0.018748</v>
+      </c>
+      <c r="J114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>通信網路業右下上市</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr"/>
+          <t>通信網路業右上上市</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>6082.970456</v>
+      </c>
       <c r="C115" t="n">
-        <v>1572.925061</v>
+        <v>6103.551493</v>
       </c>
       <c r="D115" t="n">
-        <v>834.745993</v>
+        <v>6732.41476</v>
       </c>
       <c r="E115" t="n">
-        <v>496.605319</v>
+        <v>5664.386803</v>
       </c>
       <c r="F115" t="n">
-        <v>610.987922</v>
+        <v>8245.252662000001</v>
       </c>
       <c r="G115" t="n">
-        <v>511.843469</v>
+        <v>22743.754038</v>
       </c>
       <c r="H115" t="n">
-        <v>427.332467</v>
+        <v>18508.769204</v>
       </c>
       <c r="I115" t="n">
-        <v>823.802486</v>
+        <v>23340.049248</v>
       </c>
       <c r="J115" t="n">
-        <v>1070.016387</v>
-      </c>
-      <c r="K115" t="n">
-        <v>1203.082757</v>
+        <v>18464.629005</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>通信網路業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr"/>
+          <t>通信網路業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>13.550458</v>
+      </c>
       <c r="C116" t="n">
-        <v>0.178417</v>
+        <v>7.615602</v>
       </c>
       <c r="D116" t="n">
-        <v>0.096251</v>
+        <v>7.114229</v>
       </c>
       <c r="E116" t="n">
-        <v>0.144735</v>
+        <v>8.893762000000001</v>
       </c>
       <c r="F116" t="n">
-        <v>0.11816</v>
+        <v>17.404423</v>
       </c>
       <c r="G116" t="n">
-        <v>0.110546</v>
+        <v>30.87572</v>
       </c>
       <c r="H116" t="n">
-        <v>0.118829</v>
+        <v>24.380481</v>
       </c>
       <c r="I116" t="n">
-        <v>0.131583</v>
+        <v>38.145686</v>
       </c>
       <c r="J116" t="n">
-        <v>0.177965</v>
-      </c>
-      <c r="K116" t="n">
-        <v>0.169226</v>
+        <v>17.986601</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>通信網路業平上市</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr"/>
+          <t>通信網路業右下上市</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>2277.09085</v>
+      </c>
       <c r="C117" t="n">
-        <v>237.57014</v>
+        <v>1946.021499</v>
       </c>
       <c r="D117" t="n">
-        <v>89.388042</v>
+        <v>2780.216216</v>
       </c>
       <c r="E117" t="n">
-        <v>559.4659799999999</v>
+        <v>2244.085252</v>
       </c>
       <c r="F117" t="n">
-        <v>961.962991</v>
+        <v>592.812061</v>
       </c>
       <c r="G117" t="n">
-        <v>2791.139659</v>
+        <v>1032.313313</v>
       </c>
       <c r="H117" t="n">
-        <v>559.675728</v>
+        <v>3136.206759</v>
       </c>
       <c r="I117" t="n">
-        <v>305.608661</v>
+        <v>1142.814228</v>
       </c>
       <c r="J117" t="n">
-        <v>2225.541625</v>
-      </c>
-      <c r="K117" t="n">
-        <v>142.893685</v>
+        <v>1476.668651</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>通信網路業平上櫃</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr"/>
+          <t>通信網路業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>0.092809</v>
+      </c>
       <c r="C118" t="n">
-        <v>0.017126</v>
+        <v>0.139641</v>
       </c>
       <c r="D118" t="n">
-        <v>0.372699</v>
+        <v>0.121491</v>
       </c>
       <c r="E118" t="n">
-        <v>0.310555</v>
+        <v>0.078808</v>
       </c>
       <c r="F118" t="n">
-        <v>0.029576</v>
+        <v>0.084409</v>
       </c>
       <c r="G118" t="n">
-        <v>0.660886</v>
+        <v>0.171764</v>
       </c>
       <c r="H118" t="n">
-        <v>0.378057</v>
+        <v>0.188484</v>
       </c>
       <c r="I118" t="n">
-        <v>0.788558</v>
+        <v>0.114978</v>
       </c>
       <c r="J118" t="n">
-        <v>2.236648</v>
-      </c>
-      <c r="K118" t="n">
-        <v>0.029767</v>
+        <v>0.144703</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>造紙工業右上上市</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr"/>
+          <t>通信網路業平上市</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>5162.65965</v>
+      </c>
       <c r="C119" t="n">
-        <v>55.228139</v>
+        <v>8297.360316</v>
       </c>
       <c r="D119" t="n">
-        <v>67.6173</v>
+        <v>13988.662308</v>
       </c>
       <c r="E119" t="n">
-        <v>95.750647</v>
+        <v>12339.661725</v>
       </c>
       <c r="F119" t="n">
-        <v>70.719487</v>
+        <v>17667.338244</v>
       </c>
       <c r="G119" t="n">
-        <v>92.464285</v>
+        <v>8652.535905000001</v>
       </c>
       <c r="H119" t="n">
-        <v>79.71619</v>
+        <v>10680.328469</v>
       </c>
       <c r="I119" t="n">
-        <v>58.167627</v>
+        <v>12673.394296</v>
       </c>
       <c r="J119" t="n">
-        <v>79.133607</v>
-      </c>
-      <c r="K119" t="n">
-        <v>616.862361</v>
+        <v>6792.216042</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>造紙工業右下上市</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr"/>
+          <t>通信網路業平上櫃</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>2.26254</v>
+      </c>
       <c r="C120" t="n">
-        <v>8.611516999999999</v>
+        <v>2.291996</v>
       </c>
       <c r="D120" t="n">
-        <v>4.116534</v>
+        <v>2.261277</v>
       </c>
       <c r="E120" t="n">
-        <v>8.170572</v>
+        <v>3.489899</v>
       </c>
       <c r="F120" t="n">
-        <v>6.624743</v>
+        <v>9.474993</v>
       </c>
       <c r="G120" t="n">
-        <v>6.312246</v>
+        <v>6.319699</v>
       </c>
       <c r="H120" t="n">
-        <v>7.259808</v>
+        <v>5.424032</v>
       </c>
       <c r="I120" t="n">
-        <v>13.316509</v>
+        <v>3.762618</v>
       </c>
       <c r="J120" t="n">
-        <v>6.283155</v>
-      </c>
-      <c r="K120" t="n">
-        <v>6.420234</v>
+        <v>2.664755</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>造紙工業平上市</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr"/>
+          <t>造紙工業右上上市</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>57.019267</v>
+      </c>
       <c r="C121" t="n">
-        <v>17.846888</v>
+        <v>95.750647</v>
       </c>
       <c r="D121" t="n">
-        <v>12.6655</v>
+        <v>70.719487</v>
       </c>
       <c r="E121" t="n">
-        <v>54.222929</v>
+        <v>92.464285</v>
       </c>
       <c r="F121" t="n">
-        <v>27.470921</v>
+        <v>63.28767</v>
       </c>
       <c r="G121" t="n">
-        <v>54.140034</v>
+        <v>58.167627</v>
       </c>
       <c r="H121" t="n">
-        <v>15.330468</v>
+        <v>54.269276</v>
       </c>
       <c r="I121" t="n">
-        <v>46.895959</v>
+        <v>602.393444</v>
       </c>
       <c r="J121" t="n">
-        <v>18.141425</v>
-      </c>
-      <c r="K121" t="n">
-        <v>23.10272</v>
+        <v>56.860276</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右上上市</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr"/>
+          <t>造紙工業右下上市</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>4.116534</v>
+      </c>
       <c r="C122" t="n">
-        <v>14.189534</v>
+        <v>8.170572</v>
       </c>
       <c r="D122" t="n">
-        <v>8.780303999999999</v>
+        <v>6.624743</v>
       </c>
       <c r="E122" t="n">
-        <v>8.784293999999999</v>
+        <v>6.312246</v>
       </c>
       <c r="F122" t="n">
-        <v>4.563235</v>
+        <v>7.259808</v>
       </c>
       <c r="G122" t="n">
-        <v>19.402717</v>
+        <v>13.316509</v>
       </c>
       <c r="H122" t="n">
-        <v>10.267939</v>
+        <v>6.283155</v>
       </c>
       <c r="I122" t="n">
-        <v>4.269063</v>
+        <v>6.420234</v>
       </c>
       <c r="J122" t="n">
-        <v>6.51182</v>
-      </c>
-      <c r="K122" t="n">
-        <v>3.759139</v>
+        <v>8.628501999999999</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右上上櫃</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr"/>
+          <t>造紙工業平上市</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>23.263533</v>
+      </c>
       <c r="C123" t="n">
-        <v>0.006858</v>
+        <v>54.222929</v>
       </c>
       <c r="D123" t="n">
-        <v>0.008021</v>
+        <v>27.470921</v>
       </c>
       <c r="E123" t="n">
-        <v>0.003447</v>
+        <v>54.140034</v>
       </c>
       <c r="F123" t="n">
-        <v>0.003155</v>
+        <v>31.758988</v>
       </c>
       <c r="G123" t="n">
-        <v>0.006757</v>
+        <v>46.895959</v>
       </c>
       <c r="H123" t="n">
-        <v>0.002266</v>
+        <v>43.005756</v>
       </c>
       <c r="I123" t="n">
-        <v>0.000998</v>
+        <v>37.571637</v>
       </c>
       <c r="J123" t="n">
-        <v>0.000494</v>
-      </c>
-      <c r="K123" t="n">
-        <v>0.002208</v>
+        <v>13.522615</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右下上市</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr"/>
+          <t>運動休閒右上上市</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>127.930135</v>
+      </c>
       <c r="C124" t="n">
-        <v>612.98116</v>
+        <v>222.315562</v>
       </c>
       <c r="D124" t="n">
-        <v>505.281862</v>
+        <v>159.66203</v>
       </c>
       <c r="E124" t="n">
-        <v>528.3968640000001</v>
+        <v>173.07071</v>
       </c>
       <c r="F124" t="n">
-        <v>526.544919</v>
+        <v>149.450741</v>
       </c>
       <c r="G124" t="n">
-        <v>466.358989</v>
+        <v>133.981208</v>
       </c>
       <c r="H124" t="n">
-        <v>513.529666</v>
+        <v>117.484132</v>
       </c>
       <c r="I124" t="n">
-        <v>849.426072</v>
+        <v>128.504357</v>
       </c>
       <c r="J124" t="n">
-        <v>436.34571</v>
-      </c>
-      <c r="K124" t="n">
-        <v>848.133164</v>
+        <v>199.996151</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>運動休閒右下上櫃</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr"/>
+          <t>運動休閒右上上櫃</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>0.008066</v>
+      </c>
       <c r="C125" t="n">
-        <v>0.00653</v>
+        <v>0.00397</v>
       </c>
       <c r="D125" t="n">
-        <v>0.005962</v>
+        <v>0.003778</v>
       </c>
       <c r="E125" t="n">
-        <v>0.005354</v>
+        <v>0.006495</v>
       </c>
       <c r="F125" t="n">
-        <v>0.004094</v>
+        <v>0.002192</v>
       </c>
       <c r="G125" t="n">
-        <v>0.005517</v>
+        <v>0.001731</v>
       </c>
       <c r="H125" t="n">
-        <v>0.005495</v>
+        <v>0.001133</v>
       </c>
       <c r="I125" t="n">
-        <v>0.011286</v>
+        <v>0.003832</v>
       </c>
       <c r="J125" t="n">
-        <v>0.005742</v>
-      </c>
-      <c r="K125" t="n">
-        <v>0.015415</v>
+        <v>0.002279</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>運動休閒平上市</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr"/>
+          <t>運動休閒右下上市</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>437.072996</v>
+      </c>
       <c r="C126" t="n">
-        <v>112.8687</v>
+        <v>441.590088</v>
       </c>
       <c r="D126" t="n">
-        <v>98.42016099999999</v>
+        <v>449.552373</v>
       </c>
       <c r="E126" t="n">
-        <v>215.237233</v>
+        <v>413.635324</v>
       </c>
       <c r="F126" t="n">
-        <v>161.772615</v>
+        <v>473.00502</v>
       </c>
       <c r="G126" t="n">
-        <v>160.666612</v>
+        <v>809.13311</v>
       </c>
       <c r="H126" t="n">
-        <v>140.8494</v>
+        <v>424.018495</v>
       </c>
       <c r="I126" t="n">
-        <v>161.143466</v>
+        <v>830.7774439999999</v>
       </c>
       <c r="J126" t="n">
-        <v>179.437479</v>
-      </c>
-      <c r="K126" t="n">
-        <v>125.994775</v>
+        <v>641.801303</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>運動休閒平上櫃</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr"/>
+          <t>運動休閒右下上櫃</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>0.005639</v>
+      </c>
       <c r="C127" t="n">
-        <v>0.000654</v>
+        <v>0.004976</v>
       </c>
       <c r="D127" t="n">
-        <v>0.000856</v>
+        <v>0.003873</v>
       </c>
       <c r="E127" t="n">
-        <v>0.00087</v>
+        <v>0.00535</v>
       </c>
       <c r="F127" t="n">
-        <v>0.000973</v>
+        <v>0.005399</v>
       </c>
       <c r="G127" t="n">
-        <v>0.000481</v>
+        <v>0.010485</v>
       </c>
       <c r="H127" t="n">
-        <v>0.000451</v>
+        <v>0.005742</v>
       </c>
       <c r="I127" t="n">
-        <v>0.00085</v>
+        <v>0.015207</v>
       </c>
       <c r="J127" t="n">
-        <v>0.001052</v>
-      </c>
-      <c r="K127" t="n">
-        <v>0.001937</v>
+        <v>0.007009</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>金融保險右上上市</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr"/>
+          <t>運動休閒平上市</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>47.479196</v>
+      </c>
       <c r="C128" t="n">
-        <v>17691.083594</v>
+        <v>88.51274100000001</v>
       </c>
       <c r="D128" t="n">
-        <v>11085.610633</v>
+        <v>83.666366</v>
       </c>
       <c r="E128" t="n">
-        <v>19924.034527</v>
+        <v>59.722284</v>
       </c>
       <c r="F128" t="n">
-        <v>17412.385707</v>
+        <v>42.191244</v>
       </c>
       <c r="G128" t="n">
-        <v>24969.850298</v>
+        <v>71.724283</v>
       </c>
       <c r="H128" t="n">
-        <v>16532.68804</v>
+        <v>80.792382</v>
       </c>
       <c r="I128" t="n">
-        <v>14026.974406</v>
+        <v>18.605277</v>
       </c>
       <c r="J128" t="n">
-        <v>15006.892268</v>
-      </c>
-      <c r="K128" t="n">
-        <v>14677.86912</v>
+        <v>16.449773</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>金融保險右下上市</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr"/>
+          <t>運動休閒平上櫃</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>0.001134</v>
+      </c>
       <c r="C129" t="n">
-        <v>205.909852</v>
+        <v>0.000725</v>
       </c>
       <c r="D129" t="n">
-        <v>244.900842</v>
+        <v>0.000571</v>
       </c>
       <c r="E129" t="n">
-        <v>365.107306</v>
+        <v>0.00091</v>
       </c>
       <c r="F129" t="n">
-        <v>265.348802</v>
+        <v>0.000621</v>
       </c>
       <c r="G129" t="n">
-        <v>210.851143</v>
+        <v>0.000918</v>
       </c>
       <c r="H129" t="n">
-        <v>100.665858</v>
+        <v>0.000413</v>
       </c>
       <c r="I129" t="n">
-        <v>581.610311</v>
+        <v>0.000521</v>
       </c>
       <c r="J129" t="n">
-        <v>146.252249</v>
-      </c>
-      <c r="K129" t="n">
-        <v>193.566498</v>
+        <v>0.000179</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>金融保險平上市</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr"/>
+          <t>金融保險右上上市</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>10882.35721</v>
+      </c>
       <c r="C130" t="n">
-        <v>16.324356</v>
+        <v>19643.829874</v>
       </c>
       <c r="D130" t="n">
-        <v>6.437949</v>
+        <v>17163.268297</v>
       </c>
       <c r="E130" t="n">
-        <v>22.527384</v>
+        <v>24618.524731</v>
       </c>
       <c r="F130" t="n">
-        <v>7.187692</v>
+        <v>16298.205375</v>
       </c>
       <c r="G130" t="n">
-        <v>22.569007</v>
+        <v>13807.946575</v>
       </c>
       <c r="H130" t="n">
-        <v>245.982012</v>
+        <v>14981.031046</v>
       </c>
       <c r="I130" t="n">
-        <v>192.893999</v>
+        <v>14479.266296</v>
       </c>
       <c r="J130" t="n">
-        <v>100.687298</v>
-      </c>
-      <c r="K130" t="n">
-        <v>69.90204900000001</v>
+        <v>16904.108798</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>金融業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr"/>
+          <t>金融保險右下上市</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>244.900842</v>
+      </c>
       <c r="C131" t="n">
-        <v>0.301573</v>
+        <v>387.63469</v>
       </c>
       <c r="D131" t="n">
-        <v>0.201194</v>
+        <v>265.348802</v>
       </c>
       <c r="E131" t="n">
-        <v>0.161718</v>
+        <v>233.42015</v>
       </c>
       <c r="F131" t="n">
-        <v>0.400568</v>
+        <v>116.899227</v>
       </c>
       <c r="G131" t="n">
-        <v>0.347004</v>
+        <v>626.85414</v>
       </c>
       <c r="H131" t="n">
-        <v>0.207685</v>
+        <v>181.039781</v>
       </c>
       <c r="I131" t="n">
-        <v>0.328599</v>
+        <v>193.566498</v>
       </c>
       <c r="J131" t="n">
-        <v>0.371098</v>
-      </c>
-      <c r="K131" t="n">
-        <v>0.225088</v>
+        <v>87.746871</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>金融業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr"/>
+          <t>金融保險平上市</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>209.691372</v>
+      </c>
       <c r="C132" t="n">
-        <v>0.043228</v>
+        <v>280.204653</v>
       </c>
       <c r="D132" t="n">
-        <v>0.102314</v>
+        <v>256.305102</v>
       </c>
       <c r="E132" t="n">
-        <v>0.038874</v>
+        <v>351.325567</v>
       </c>
       <c r="F132" t="n">
-        <v>0.064808</v>
+        <v>464.231308</v>
       </c>
       <c r="G132" t="n">
-        <v>0.08569</v>
+        <v>366.678001</v>
       </c>
       <c r="H132" t="n">
-        <v>0.030934</v>
+        <v>91.760988</v>
       </c>
       <c r="I132" t="n">
-        <v>0.062779</v>
+        <v>268.504873</v>
       </c>
       <c r="J132" t="n">
-        <v>0.015258</v>
-      </c>
-      <c r="K132" t="n">
-        <v>0.021759</v>
+        <v>289.394256</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上上市</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr"/>
+          <t>金融業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>0.200969</v>
+      </c>
       <c r="C133" t="n">
-        <v>1696.815892</v>
+        <v>0.161656</v>
       </c>
       <c r="D133" t="n">
-        <v>1694.081261</v>
+        <v>0.400318</v>
       </c>
       <c r="E133" t="n">
-        <v>2007.695822</v>
+        <v>0.34688</v>
       </c>
       <c r="F133" t="n">
-        <v>2646.077804</v>
+        <v>0.207437</v>
       </c>
       <c r="G133" t="n">
-        <v>4868.16816</v>
+        <v>0.32817</v>
       </c>
       <c r="H133" t="n">
-        <v>1398.788211</v>
+        <v>0.370971</v>
       </c>
       <c r="I133" t="n">
-        <v>1782.575434</v>
+        <v>0.224957</v>
       </c>
       <c r="J133" t="n">
-        <v>836.800999</v>
-      </c>
-      <c r="K133" t="n">
-        <v>1068.783048</v>
+        <v>0.321354</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr"/>
+          <t>金融業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>0.102314</v>
+      </c>
       <c r="C134" t="n">
-        <v>0.016825</v>
+        <v>0.038874</v>
       </c>
       <c r="D134" t="n">
-        <v>0.013359</v>
+        <v>0.064808</v>
       </c>
       <c r="E134" t="n">
-        <v>0.06475</v>
+        <v>0.08569</v>
       </c>
       <c r="F134" t="n">
-        <v>0.072867</v>
+        <v>0.030934</v>
       </c>
       <c r="G134" t="n">
-        <v>0.049926</v>
+        <v>0.062779</v>
       </c>
       <c r="H134" t="n">
-        <v>0.097998</v>
+        <v>0.015258</v>
       </c>
       <c r="I134" t="n">
-        <v>0.06363175</v>
+        <v>0.021759</v>
       </c>
       <c r="J134" t="n">
-        <v>0.271254</v>
-      </c>
-      <c r="K134" t="n">
-        <v>0.194194</v>
+        <v>0.018194</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右下上市</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr"/>
+          <t>金融業平上櫃</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>0.000225</v>
+      </c>
       <c r="C135" t="n">
-        <v>634.783</v>
+        <v>6.2e-05</v>
       </c>
       <c r="D135" t="n">
-        <v>591.098376</v>
+        <v>0.00025</v>
       </c>
       <c r="E135" t="n">
-        <v>909.256881</v>
+        <v>0.000124</v>
       </c>
       <c r="F135" t="n">
-        <v>148.35773</v>
+        <v>0.000248</v>
       </c>
       <c r="G135" t="n">
-        <v>169.164864</v>
+        <v>0.000429</v>
       </c>
       <c r="H135" t="n">
-        <v>118.713758</v>
+        <v>0.000127</v>
       </c>
       <c r="I135" t="n">
-        <v>682.41453</v>
+        <v>0.000131</v>
       </c>
       <c r="J135" t="n">
-        <v>114.442318</v>
-      </c>
-      <c r="K135" t="n">
-        <v>96.754739</v>
+        <v>0.000103</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr"/>
+          <t>鋼鐵工業右上上市</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>1668.035173</v>
+      </c>
       <c r="C136" t="n">
-        <v>0.028637</v>
+        <v>2123.299819</v>
       </c>
       <c r="D136" t="n">
-        <v>0.0364855</v>
+        <v>2472.356878</v>
       </c>
       <c r="E136" t="n">
-        <v>0.068173</v>
+        <v>4794.875688</v>
       </c>
       <c r="F136" t="n">
-        <v>0.2212903333333333</v>
+        <v>1359.890176</v>
       </c>
       <c r="G136" t="n">
-        <v>0.078968</v>
+        <v>1769.709532</v>
       </c>
       <c r="H136" t="n">
-        <v>0.050348</v>
+        <v>836.966153</v>
       </c>
       <c r="I136" t="n">
-        <v>0.088694</v>
+        <v>1061.566529</v>
       </c>
       <c r="J136" t="n">
-        <v>0.05103625</v>
-      </c>
-      <c r="K136" t="n">
-        <v>0.047083</v>
+        <v>979.023702</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業平上市</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr"/>
+          <t>鋼鐵工業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>0.006391</v>
+      </c>
       <c r="C137" t="n">
-        <v>184.320351</v>
+        <v>0.044205</v>
       </c>
       <c r="D137" t="n">
-        <v>124.788869</v>
+        <v>0.05524</v>
       </c>
       <c r="E137" t="n">
-        <v>310.398103</v>
+        <v>0.032969</v>
       </c>
       <c r="F137" t="n">
-        <v>1871.130716</v>
+        <v>0.090244</v>
       </c>
       <c r="G137" t="n">
-        <v>855.364156</v>
+        <v>0.047232</v>
       </c>
       <c r="H137" t="n">
-        <v>464.115664</v>
+        <v>0.263393</v>
       </c>
       <c r="I137" t="n">
-        <v>191.129801</v>
+        <v>0.187232</v>
       </c>
       <c r="J137" t="n">
-        <v>443.892535</v>
-      </c>
-      <c r="K137" t="n">
-        <v>542.6945930000001</v>
+        <v>0.07041</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業平上櫃</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr"/>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>690.654503</v>
+      </c>
       <c r="C138" t="n">
-        <v>0.000393</v>
+        <v>1034.546462</v>
       </c>
       <c r="D138" t="n">
-        <v>1.7e-05</v>
+        <v>233.418087</v>
       </c>
       <c r="E138" t="n">
-        <v>7.499999999999999e-05</v>
+        <v>217.573193</v>
       </c>
       <c r="F138" t="n">
-        <v>0.003635</v>
-      </c>
-      <c r="G138" t="inlineStr"/>
-      <c r="H138" t="inlineStr"/>
-      <c r="I138" t="inlineStr"/>
+        <v>147.093842</v>
+      </c>
+      <c r="G138" t="n">
+        <v>766.217797</v>
+      </c>
+      <c r="H138" t="n">
+        <v>141.456491</v>
+      </c>
+      <c r="I138" t="n">
+        <v>152.003774</v>
+      </c>
       <c r="J138" t="n">
-        <v>9.1e-05</v>
-      </c>
-      <c r="K138" t="n">
-        <v>0.000178</v>
+        <v>118.986738</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右上上市</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr"/>
+          <t>鋼鐵工業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>0.0357425</v>
+      </c>
       <c r="C139" t="n">
-        <v>527.970243</v>
+        <v>0.066598</v>
       </c>
       <c r="D139" t="n">
-        <v>281.900372</v>
+        <v>0.01580233333333333</v>
       </c>
       <c r="E139" t="n">
-        <v>431.899672</v>
+        <v>0.07816099999999999</v>
       </c>
       <c r="F139" t="n">
-        <v>1832.071461</v>
+        <v>0.008527</v>
       </c>
       <c r="G139" t="n">
-        <v>1627.572588</v>
+        <v>0.08859475</v>
       </c>
       <c r="H139" t="n">
-        <v>1287.999043</v>
+        <v>0.04056825</v>
       </c>
       <c r="I139" t="n">
-        <v>1121.620276</v>
+        <v>0.036631</v>
       </c>
       <c r="J139" t="n">
-        <v>672.758657</v>
-      </c>
-      <c r="K139" t="n">
-        <v>2109.068374</v>
+        <v>0.004337</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右上上櫃</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr"/>
+          <t>鋼鐵工業平上市</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>51.27883</v>
+      </c>
       <c r="C140" t="n">
-        <v>0.09124</v>
+        <v>69.504525</v>
       </c>
       <c r="D140" t="n">
-        <v>0.091242</v>
+        <v>1959.791285</v>
       </c>
       <c r="E140" t="n">
-        <v>0.112558</v>
+        <v>880.248299</v>
       </c>
       <c r="F140" t="n">
-        <v>0.294298</v>
+        <v>474.633615</v>
       </c>
       <c r="G140" t="n">
-        <v>0.204111</v>
+        <v>120.192436</v>
       </c>
       <c r="H140" t="n">
-        <v>0.346172</v>
+        <v>416.713208</v>
       </c>
       <c r="I140" t="n">
-        <v>0.360224</v>
+        <v>494.662077</v>
       </c>
       <c r="J140" t="n">
-        <v>0.179417</v>
-      </c>
-      <c r="K140" t="n">
-        <v>0.243985</v>
+        <v>553.600374</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右下上市</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr"/>
+          <t>鋼鐵工業平上櫃</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>0.007728</v>
+      </c>
       <c r="C141" t="n">
-        <v>43.787224</v>
+        <v>0.022195</v>
       </c>
       <c r="D141" t="n">
-        <v>39.275066</v>
+        <v>0.22675</v>
       </c>
       <c r="E141" t="n">
-        <v>40.346396</v>
+        <v>0.017764</v>
       </c>
       <c r="F141" t="n">
-        <v>55.382448</v>
+        <v>0.049575</v>
       </c>
       <c r="G141" t="n">
-        <v>41.834918</v>
+        <v>0.016499</v>
       </c>
       <c r="H141" t="n">
-        <v>50.073944</v>
+        <v>0.01842</v>
       </c>
       <c r="I141" t="n">
-        <v>62.3224</v>
+        <v>0.017592</v>
       </c>
       <c r="J141" t="n">
-        <v>67.592972</v>
-      </c>
-      <c r="K141" t="n">
-        <v>43.980049</v>
+        <v>0.144883</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>電器電纜平上市</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr"/>
+          <t>電器電纜右上上市</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>243.385274</v>
+      </c>
       <c r="C142" t="n">
-        <v>99.887826</v>
+        <v>221.164725</v>
       </c>
       <c r="D142" t="n">
-        <v>77.739137</v>
+        <v>2022.93564</v>
       </c>
       <c r="E142" t="n">
-        <v>209.825689</v>
+        <v>1815.128022</v>
       </c>
       <c r="F142" t="n">
-        <v>235.661816</v>
+        <v>1400.305424</v>
       </c>
       <c r="G142" t="n">
-        <v>208.646021</v>
+        <v>1065.650025</v>
       </c>
       <c r="H142" t="n">
-        <v>123.77293</v>
+        <v>771.32349</v>
       </c>
       <c r="I142" t="n">
-        <v>148.512708</v>
+        <v>2344.32493</v>
       </c>
       <c r="J142" t="n">
-        <v>98.56483299999999</v>
-      </c>
-      <c r="K142" t="n">
-        <v>263.119998</v>
+        <v>1041.428629</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右上上市</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr"/>
+          <t>電器電纜右上上櫃</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>0.091242</v>
+      </c>
       <c r="C143" t="n">
-        <v>8812.877887000001</v>
+        <v>0.112558</v>
       </c>
       <c r="D143" t="n">
-        <v>5102.029062</v>
+        <v>0.294298</v>
       </c>
       <c r="E143" t="n">
-        <v>4956.241487</v>
+        <v>0.204111</v>
       </c>
       <c r="F143" t="n">
-        <v>6977.782428</v>
+        <v>0.346172</v>
       </c>
       <c r="G143" t="n">
-        <v>5324.52747</v>
+        <v>0.360224</v>
       </c>
       <c r="H143" t="n">
-        <v>4295.648634</v>
+        <v>0.179417</v>
       </c>
       <c r="I143" t="n">
-        <v>4441.152525</v>
+        <v>0.243985</v>
       </c>
       <c r="J143" t="n">
-        <v>3165.79443</v>
-      </c>
-      <c r="K143" t="n">
-        <v>3731.960483</v>
+        <v>0.150452</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr"/>
+          <t>電器電纜右下上市</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>39.275066</v>
+      </c>
       <c r="C144" t="n">
-        <v>0.175163</v>
+        <v>40.346396</v>
       </c>
       <c r="D144" t="n">
-        <v>0.181565</v>
+        <v>55.382448</v>
       </c>
       <c r="E144" t="n">
-        <v>0.5808489999999999</v>
+        <v>41.834918</v>
       </c>
       <c r="F144" t="n">
-        <v>0.489402</v>
+        <v>50.073944</v>
       </c>
       <c r="G144" t="n">
-        <v>0.342086</v>
+        <v>62.3224</v>
       </c>
       <c r="H144" t="n">
-        <v>0.580444</v>
+        <v>50.570646</v>
       </c>
       <c r="I144" t="n">
-        <v>0.842812</v>
+        <v>43.980049</v>
       </c>
       <c r="J144" t="n">
-        <v>0.375448</v>
-      </c>
-      <c r="K144" t="n">
-        <v>0.283862</v>
+        <v>107.991145</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右下上市</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr"/>
+          <t>電器電纜平上市</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>116.254235</v>
+      </c>
       <c r="C145" t="n">
-        <v>5.689849</v>
+        <v>420.560636</v>
       </c>
       <c r="D145" t="n">
-        <v>27.712111</v>
+        <v>44.797637</v>
       </c>
       <c r="E145" t="n">
-        <v>18.247482</v>
+        <v>21.090587</v>
       </c>
       <c r="F145" t="n">
-        <v>12.283079</v>
+        <v>11.466549</v>
       </c>
       <c r="G145" t="n">
-        <v>13.321644</v>
+        <v>204.482959</v>
       </c>
       <c r="H145" t="n">
-        <v>11.089148</v>
+        <v>17.022326</v>
       </c>
       <c r="I145" t="n">
-        <v>13.469439</v>
+        <v>27.863442</v>
       </c>
       <c r="J145" t="n">
-        <v>11.420697</v>
-      </c>
-      <c r="K145" t="n">
-        <v>8.435860999999999</v>
+        <v>194.703472</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr"/>
+          <t>電子通路業右上上市</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>3162.15291</v>
+      </c>
       <c r="C146" t="n">
-        <v>0.173565</v>
+        <v>3504.588651</v>
       </c>
       <c r="D146" t="n">
-        <v>0.06376800000000001</v>
+        <v>4790.204438</v>
       </c>
       <c r="E146" t="n">
-        <v>0.0418</v>
+        <v>2482.396615</v>
       </c>
       <c r="F146" t="n">
-        <v>0.04535</v>
+        <v>2318.877637</v>
       </c>
       <c r="G146" t="n">
-        <v>0.081911</v>
+        <v>2511.741979</v>
       </c>
       <c r="H146" t="n">
-        <v>0.022376</v>
+        <v>1612.453768</v>
       </c>
       <c r="I146" t="n">
-        <v>0.01177</v>
+        <v>1942.566081</v>
       </c>
       <c r="J146" t="n">
-        <v>0.012023</v>
-      </c>
-      <c r="K146" t="n">
-        <v>0.015477</v>
+        <v>2625.004186</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>電子通路業平上市</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr"/>
+          <t>電子通路業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>0.127115</v>
+      </c>
       <c r="C147" t="n">
-        <v>82.50335</v>
+        <v>0.114703</v>
       </c>
       <c r="D147" t="n">
-        <v>75.70770899999999</v>
+        <v>0.131196</v>
       </c>
       <c r="E147" t="n">
-        <v>92.376355</v>
+        <v>0.332757</v>
       </c>
       <c r="F147" t="n">
-        <v>56.915993</v>
+        <v>0.374888</v>
       </c>
       <c r="G147" t="n">
-        <v>37.381351</v>
+        <v>0.545445</v>
       </c>
       <c r="H147" t="n">
-        <v>54.291443</v>
+        <v>0.119233</v>
       </c>
       <c r="I147" t="n">
-        <v>65.30397000000001</v>
+        <v>0.143438</v>
       </c>
       <c r="J147" t="n">
-        <v>186.188924</v>
-      </c>
-      <c r="K147" t="n">
-        <v>99.144873</v>
+        <v>0.125264</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>電子通路業平上櫃</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr"/>
+          <t>電子通路業右下上市</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>6.727905</v>
+      </c>
       <c r="C148" t="n">
-        <v>0.266881</v>
+        <v>18.247482</v>
       </c>
       <c r="D148" t="n">
-        <v>0.223138</v>
+        <v>12.283079</v>
       </c>
       <c r="E148" t="n">
-        <v>0.000586</v>
+        <v>13.321644</v>
       </c>
       <c r="F148" t="n">
-        <v>0.001673</v>
+        <v>11.089148</v>
       </c>
       <c r="G148" t="n">
-        <v>0.263543</v>
-      </c>
-      <c r="H148" t="inlineStr"/>
-      <c r="I148" t="inlineStr"/>
+        <v>13.469439</v>
+      </c>
+      <c r="H148" t="n">
+        <v>11.420697</v>
+      </c>
+      <c r="I148" t="n">
+        <v>8.435860999999999</v>
+      </c>
       <c r="J148" t="n">
-        <v>0.002617</v>
-      </c>
-      <c r="K148" t="n">
-        <v>0.001266</v>
+        <v>9.756826999999999</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右上上市</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr"/>
+          <t>電子通路業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>0.06376800000000001</v>
+      </c>
       <c r="C149" t="n">
-        <v>203807.94402</v>
+        <v>0.0418</v>
       </c>
       <c r="D149" t="n">
-        <v>192682.277067</v>
+        <v>0.04535</v>
       </c>
       <c r="E149" t="n">
-        <v>192593.179829</v>
+        <v>0.081911</v>
       </c>
       <c r="F149" t="n">
-        <v>189811.564786</v>
+        <v>0.022376</v>
       </c>
       <c r="G149" t="n">
-        <v>238926.971192</v>
+        <v>0.01177</v>
       </c>
       <c r="H149" t="n">
-        <v>303673.461318</v>
+        <v>0.012023</v>
       </c>
       <c r="I149" t="n">
-        <v>337227.393779</v>
+        <v>0.015477</v>
       </c>
       <c r="J149" t="n">
-        <v>297664.221548</v>
-      </c>
-      <c r="K149" t="n">
-        <v>289353.972438</v>
+        <v>0.057118</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr"/>
+          <t>電子通路業平上市</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>2036.568067</v>
+      </c>
       <c r="C150" t="n">
-        <v>27.426623</v>
+        <v>1544.029191</v>
       </c>
       <c r="D150" t="n">
-        <v>39.0586</v>
+        <v>2244.493983</v>
       </c>
       <c r="E150" t="n">
-        <v>32.142848</v>
+        <v>2879.512206</v>
       </c>
       <c r="F150" t="n">
-        <v>32.894592</v>
+        <v>2031.06244</v>
       </c>
       <c r="G150" t="n">
-        <v>52.55861</v>
+        <v>1994.714516</v>
       </c>
       <c r="H150" t="n">
-        <v>68.182243</v>
+        <v>1739.529586</v>
       </c>
       <c r="I150" t="n">
-        <v>78.045886</v>
+        <v>1888.539275</v>
       </c>
       <c r="J150" t="n">
-        <v>69.266969</v>
-      </c>
-      <c r="K150" t="n">
-        <v>71.62496</v>
+        <v>2344.75392</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右下上市</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr"/>
+          <t>電子通路業平上櫃</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>0.277588</v>
+      </c>
       <c r="C151" t="n">
-        <v>947.526689</v>
+        <v>0.466732</v>
       </c>
       <c r="D151" t="n">
-        <v>744.89184</v>
+        <v>0.359879</v>
       </c>
       <c r="E151" t="n">
-        <v>967.6923860000001</v>
+        <v>0.272872</v>
       </c>
       <c r="F151" t="n">
-        <v>1142.26238</v>
+        <v>0.205556</v>
       </c>
       <c r="G151" t="n">
-        <v>948.549808</v>
+        <v>0.297367</v>
       </c>
       <c r="H151" t="n">
-        <v>847.233592</v>
+        <v>0.258832</v>
       </c>
       <c r="I151" t="n">
-        <v>1370.806459</v>
+        <v>0.14169</v>
       </c>
       <c r="J151" t="n">
-        <v>1013.098361</v>
-      </c>
-      <c r="K151" t="n">
-        <v>1434.948491</v>
+        <v>0.182436</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr"/>
+          <t>電子零組件業右上上市</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>189680.575138</v>
+      </c>
       <c r="C152" t="n">
-        <v>0.564804</v>
+        <v>168759.788961</v>
       </c>
       <c r="D152" t="n">
-        <v>0.606082</v>
+        <v>175055.014039</v>
       </c>
       <c r="E152" t="n">
-        <v>0.328547</v>
+        <v>219810.875587</v>
       </c>
       <c r="F152" t="n">
-        <v>0.904578</v>
+        <v>295285.351175</v>
       </c>
       <c r="G152" t="n">
-        <v>0.62054</v>
+        <v>328265.311909</v>
       </c>
       <c r="H152" t="n">
-        <v>0.569536</v>
+        <v>288190.134832</v>
       </c>
       <c r="I152" t="n">
-        <v>1.031513</v>
+        <v>280157.533381</v>
       </c>
       <c r="J152" t="n">
-        <v>0.948043</v>
-      </c>
-      <c r="K152" t="n">
-        <v>0.728827</v>
+        <v>237824.950979</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業平上市</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr"/>
+          <t>電子零組件業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>37.603645</v>
+      </c>
       <c r="C153" t="n">
-        <v>7314.585275</v>
+        <v>29.674985</v>
       </c>
       <c r="D153" t="n">
-        <v>3323.928044</v>
+        <v>28.779912</v>
       </c>
       <c r="E153" t="n">
-        <v>4869.715431</v>
+        <v>49.01851</v>
       </c>
       <c r="F153" t="n">
-        <v>6364.882629</v>
+        <v>64.95413499999999</v>
       </c>
       <c r="G153" t="n">
-        <v>1607.896464</v>
+        <v>73.40257800000001</v>
       </c>
       <c r="H153" t="n">
-        <v>1967.018327</v>
+        <v>67.14289100000001</v>
       </c>
       <c r="I153" t="n">
-        <v>3271.617284</v>
+        <v>67.12150200000001</v>
       </c>
       <c r="J153" t="n">
-        <v>2554.075233</v>
-      </c>
-      <c r="K153" t="n">
-        <v>3198.448681</v>
+        <v>51.621843</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業平上櫃</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr"/>
+          <t>電子零組件業右下上市</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>3340.325803</v>
+      </c>
       <c r="C154" t="n">
-        <v>0.307117</v>
+        <v>5280.673074</v>
       </c>
       <c r="D154" t="n">
-        <v>0.344598</v>
+        <v>2364.317114</v>
       </c>
       <c r="E154" t="n">
-        <v>1.047481</v>
+        <v>2046.42661</v>
       </c>
       <c r="F154" t="n">
-        <v>0.342189</v>
+        <v>2344.140071</v>
       </c>
       <c r="G154" t="n">
-        <v>0.458811</v>
+        <v>3827.341422</v>
       </c>
       <c r="H154" t="n">
-        <v>0.403766</v>
+        <v>3178.747745</v>
       </c>
       <c r="I154" t="n">
-        <v>0.541299</v>
+        <v>1795.89688</v>
       </c>
       <c r="J154" t="n">
-        <v>0.335978</v>
-      </c>
-      <c r="K154" t="n">
-        <v>0.282854</v>
+        <v>1403.505428</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>電機機械右上上市</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr"/>
+          <t>電子零組件業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>0.901962</v>
+      </c>
       <c r="C155" t="n">
-        <v>20653.023269</v>
+        <v>0.571503</v>
       </c>
       <c r="D155" t="n">
-        <v>17783.28272</v>
+        <v>1.249787</v>
       </c>
       <c r="E155" t="n">
-        <v>17698.696071</v>
+        <v>1.073411</v>
       </c>
       <c r="F155" t="n">
-        <v>17107.566288</v>
+        <v>0.755271</v>
       </c>
       <c r="G155" t="n">
-        <v>21736.79682</v>
+        <v>1.243945</v>
       </c>
       <c r="H155" t="n">
-        <v>20870.148901</v>
+        <v>1.071785</v>
       </c>
       <c r="I155" t="n">
-        <v>9721.052197000001</v>
+        <v>0.89056</v>
       </c>
       <c r="J155" t="n">
-        <v>6786.646732</v>
-      </c>
-      <c r="K155" t="n">
-        <v>8013.519252</v>
+        <v>0.798391</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>電機機械右上上櫃</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr"/>
+          <t>電子零組件業平上市</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>3730.19601</v>
+      </c>
       <c r="C156" t="n">
-        <v>0.736514</v>
+        <v>24390.125611</v>
       </c>
       <c r="D156" t="n">
-        <v>0.901869</v>
+        <v>19899.378642</v>
       </c>
       <c r="E156" t="n">
-        <v>2.045405</v>
+        <v>19626.115267</v>
       </c>
       <c r="F156" t="n">
-        <v>1.835066</v>
+        <v>8858.221991</v>
       </c>
       <c r="G156" t="n">
-        <v>3.495789</v>
+        <v>9777.164191</v>
       </c>
       <c r="H156" t="n">
-        <v>2.265916</v>
+        <v>9862.512565000001</v>
       </c>
       <c r="I156" t="n">
-        <v>1.696695</v>
+        <v>12033.939349</v>
       </c>
       <c r="J156" t="n">
-        <v>1.120019</v>
-      </c>
-      <c r="K156" t="n">
-        <v>0.915351</v>
+        <v>8999.788871999999</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>電機機械右下上市</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr"/>
+          <t>電子零組件業平上櫃</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>1.503673</v>
+      </c>
       <c r="C157" t="n">
-        <v>560.189292</v>
+        <v>3.272388</v>
       </c>
       <c r="D157" t="n">
-        <v>497.79934625</v>
+        <v>4.11166</v>
       </c>
       <c r="E157" t="n">
-        <v>484.273872</v>
+        <v>3.54604</v>
       </c>
       <c r="F157" t="n">
-        <v>1003.984237</v>
+        <v>3.446139</v>
       </c>
       <c r="G157" t="n">
-        <v>1204.163042</v>
+        <v>4.972175</v>
       </c>
       <c r="H157" t="n">
-        <v>803.446879</v>
+        <v>2.336314</v>
       </c>
       <c r="I157" t="n">
-        <v>871.467301</v>
+        <v>4.624579</v>
       </c>
       <c r="J157" t="n">
-        <v>587.305118</v>
-      </c>
-      <c r="K157" t="n">
-        <v>819.2347559999999</v>
+        <v>5.858506</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>電機機械右下上櫃</t>
+          <t>電機機械右上上市</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0</v>
+        <v>16041.960584</v>
       </c>
       <c r="C158" t="n">
-        <v>0.07478633333333333</v>
+        <v>16397.971383</v>
       </c>
       <c r="D158" t="n">
-        <v>0.065455</v>
+        <v>15648.185563</v>
       </c>
       <c r="E158" t="n">
-        <v>0.080192</v>
+        <v>20759.210972</v>
       </c>
       <c r="F158" t="n">
-        <v>0.106241</v>
+        <v>19153.740726</v>
       </c>
       <c r="G158" t="n">
-        <v>0.07116375</v>
+        <v>8966.400874999999</v>
       </c>
       <c r="H158" t="n">
-        <v>0.08146200000000001</v>
+        <v>5616.545071</v>
       </c>
       <c r="I158" t="n">
-        <v>0.14959675</v>
+        <v>7242.436367</v>
       </c>
       <c r="J158" t="n">
-        <v>0.111443</v>
-      </c>
-      <c r="K158" t="n">
-        <v>0.097276</v>
+        <v>5050.538461</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>電機機械平上市</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr"/>
+          <t>電機機械右上上櫃</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>0.232632</v>
+      </c>
       <c r="C159" t="n">
-        <v>793.736661</v>
+        <v>1.930055</v>
       </c>
       <c r="D159" t="n">
-        <v>940.936506</v>
+        <v>1.779102</v>
       </c>
       <c r="E159" t="n">
-        <v>1314.555229</v>
+        <v>3.481795</v>
       </c>
       <c r="F159" t="n">
-        <v>1599.750557</v>
+        <v>2.240837</v>
       </c>
       <c r="G159" t="n">
-        <v>1141.213827</v>
+        <v>1.575423</v>
       </c>
       <c r="H159" t="n">
-        <v>1297.029295</v>
+        <v>1.048016</v>
       </c>
       <c r="I159" t="n">
-        <v>1389.228828</v>
+        <v>0.874125</v>
       </c>
       <c r="J159" t="n">
-        <v>1546.665107</v>
-      </c>
-      <c r="K159" t="n">
-        <v>3782.111008</v>
+        <v>0.8919280000000001</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>電機機械平上櫃</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr"/>
+          <t>電機機械右下上市</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>1278.56809225</v>
+      </c>
       <c r="C160" t="n">
-        <v>0.222908</v>
+        <v>1352.800315</v>
       </c>
       <c r="D160" t="n">
-        <v>0.152168</v>
+        <v>1402.402289</v>
       </c>
       <c r="E160" t="n">
-        <v>0.040177</v>
+        <v>904.3769</v>
       </c>
       <c r="F160" t="n">
-        <v>0.09173000000000001</v>
+        <v>1280.301169</v>
       </c>
       <c r="G160" t="n">
-        <v>0.086632</v>
+        <v>1389.069581</v>
       </c>
       <c r="H160" t="n">
-        <v>0.121969</v>
+        <v>981.387952</v>
       </c>
       <c r="I160" t="n">
-        <v>0.061874</v>
+        <v>1626.124408</v>
       </c>
       <c r="J160" t="n">
-        <v>0.06553</v>
-      </c>
-      <c r="K160" t="n">
-        <v>0.053388</v>
+        <v>961.62406</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上上市</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr"/>
+          <t>電機機械右下上櫃</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>0.070176</v>
+      </c>
       <c r="C161" t="n">
-        <v>30947.277086</v>
+        <v>0.085379</v>
       </c>
       <c r="D161" t="n">
-        <v>31226.702936</v>
+        <v>0.128986</v>
       </c>
       <c r="E161" t="n">
-        <v>43544.851477</v>
+        <v>0.09494175000000001</v>
       </c>
       <c r="F161" t="n">
-        <v>38030.459823</v>
+        <v>0.145845</v>
       </c>
       <c r="G161" t="n">
-        <v>43116.131312</v>
+        <v>0.17716775</v>
       </c>
       <c r="H161" t="n">
-        <v>38475.016145</v>
+        <v>0.173026</v>
       </c>
       <c r="I161" t="n">
-        <v>57387.377591</v>
+        <v>0.115561</v>
       </c>
       <c r="J161" t="n">
-        <v>40776.142185</v>
-      </c>
-      <c r="K161" t="n">
-        <v>42240.877192</v>
+        <v>0.137959</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr"/>
+          <t>電機機械平上市</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>1901.489896</v>
+      </c>
       <c r="C162" t="n">
-        <v>6.282676</v>
+        <v>1746.753474</v>
       </c>
       <c r="D162" t="n">
-        <v>4.662939</v>
+        <v>2660.71323</v>
       </c>
       <c r="E162" t="n">
-        <v>6.909672</v>
+        <v>2418.585817</v>
       </c>
       <c r="F162" t="n">
-        <v>9.003401</v>
+        <v>2536.58318</v>
       </c>
       <c r="G162" t="n">
-        <v>5.14031</v>
+        <v>1626.27787</v>
       </c>
       <c r="H162" t="n">
-        <v>5.0927</v>
+        <v>2322.683934</v>
       </c>
       <c r="I162" t="n">
-        <v>6.116877</v>
+        <v>3746.304241</v>
       </c>
       <c r="J162" t="n">
-        <v>11.366636</v>
-      </c>
-      <c r="K162" t="n">
-        <v>7.158511</v>
+        <v>3890.220374</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上市</t>
+          <t>電機機械平上櫃</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>0</v>
+        <v>0.81758</v>
       </c>
       <c r="C163" t="n">
-        <v>6486.051783</v>
+        <v>0.155259</v>
       </c>
       <c r="D163" t="n">
-        <v>7857.032012</v>
+        <v>0.127739</v>
       </c>
       <c r="E163" t="n">
-        <v>3699.843837</v>
+        <v>0.081984</v>
       </c>
       <c r="F163" t="n">
-        <v>4448.901824</v>
+        <v>0.084762</v>
       </c>
       <c r="G163" t="n">
-        <v>3383.67531</v>
+        <v>0.158662</v>
       </c>
       <c r="H163" t="n">
-        <v>5495.817378</v>
+        <v>0.106951</v>
       </c>
       <c r="I163" t="n">
-        <v>6999.368153</v>
+        <v>0.103865</v>
       </c>
       <c r="J163" t="n">
-        <v>12966.009578</v>
-      </c>
-      <c r="K163" t="n">
-        <v>9166.494794</v>
+        <v>0.052421</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr"/>
+          <t>電腦及週邊設備業右上上市</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>31285.393991</v>
+      </c>
       <c r="C164" t="n">
-        <v>0.1157325</v>
+        <v>43834.111024</v>
       </c>
       <c r="D164" t="n">
-        <v>0.082056</v>
+        <v>38144.865106</v>
       </c>
       <c r="E164" t="n">
-        <v>0.145013</v>
+        <v>42702.884281</v>
       </c>
       <c r="F164" t="n">
-        <v>0.137024</v>
+        <v>38943.162022</v>
       </c>
       <c r="G164" t="n">
-        <v>0.088251</v>
+        <v>57013.387679</v>
       </c>
       <c r="H164" t="n">
-        <v>0.14626925</v>
+        <v>41469.300152</v>
       </c>
       <c r="I164" t="n">
-        <v>0.301019</v>
+        <v>41967.279919</v>
       </c>
       <c r="J164" t="n">
-        <v>0.14562</v>
-      </c>
-      <c r="K164" t="n">
-        <v>0.125388</v>
+        <v>33540.564254</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上市</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr"/>
+          <t>電腦及週邊設備業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>3.286976</v>
+      </c>
       <c r="C165" t="n">
-        <v>2084.363452</v>
+        <v>5.63341</v>
       </c>
       <c r="D165" t="n">
-        <v>1207.281724</v>
+        <v>7.647517</v>
       </c>
       <c r="E165" t="n">
-        <v>2001.170332</v>
+        <v>4.386462</v>
       </c>
       <c r="F165" t="n">
-        <v>5258.593556</v>
+        <v>3.744373</v>
       </c>
       <c r="G165" t="n">
-        <v>3224.870738</v>
+        <v>4.552767</v>
       </c>
       <c r="H165" t="n">
-        <v>2770.292382</v>
+        <v>9.666439</v>
       </c>
       <c r="I165" t="n">
-        <v>5976.974793</v>
+        <v>5.359016</v>
       </c>
       <c r="J165" t="n">
-        <v>3705.261968</v>
-      </c>
-      <c r="K165" t="n">
-        <v>3041.954715</v>
+        <v>8.512370000000001</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上櫃</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr"/>
+          <t>電腦及週邊設備業右下上市</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>8372.407546</v>
+      </c>
       <c r="C166" t="n">
-        <v>0.239754</v>
+        <v>5011.133429</v>
       </c>
       <c r="D166" t="n">
-        <v>0.102567</v>
+        <v>9046.637635999999</v>
       </c>
       <c r="E166" t="n">
-        <v>0.160217</v>
+        <v>6167.77495</v>
       </c>
       <c r="F166" t="n">
-        <v>0.216791</v>
+        <v>7418.865709</v>
       </c>
       <c r="G166" t="n">
-        <v>0.146328</v>
+        <v>12062.739108</v>
       </c>
       <c r="H166" t="n">
-        <v>0.150315</v>
+        <v>15563.819925</v>
       </c>
       <c r="I166" t="n">
-        <v>0.28927</v>
+        <v>11608.621111</v>
       </c>
       <c r="J166" t="n">
-        <v>0.493956</v>
-      </c>
-      <c r="K166" t="n">
-        <v>0.158057</v>
+        <v>8102.186924</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>食品工業右上上市</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr"/>
+          <t>電腦及週邊設備業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>0.087995</v>
+      </c>
       <c r="C167" t="n">
-        <v>19.176035</v>
+        <v>0.151576</v>
       </c>
       <c r="D167" t="n">
-        <v>18.254504</v>
+        <v>0.163469</v>
       </c>
       <c r="E167" t="n">
-        <v>15.030035</v>
+        <v>0.09155199999999999</v>
       </c>
       <c r="F167" t="n">
-        <v>22.714533</v>
+        <v>0.15035425</v>
       </c>
       <c r="G167" t="n">
-        <v>18.953213</v>
+        <v>0.321696</v>
       </c>
       <c r="H167" t="n">
-        <v>13.274733</v>
+        <v>0.144102</v>
       </c>
       <c r="I167" t="n">
-        <v>16.692089</v>
+        <v>0.123032</v>
       </c>
       <c r="J167" t="n">
-        <v>21.559752</v>
-      </c>
-      <c r="K167" t="n">
-        <v>18.253658</v>
+        <v>0.150653</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>食品工業右上上櫃</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr"/>
+          <t>電腦及週邊設備業平上市</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>642.189541</v>
+      </c>
       <c r="C168" t="n">
-        <v>0.002534</v>
+        <v>458.611679</v>
       </c>
       <c r="D168" t="n">
-        <v>0.004008</v>
+        <v>610.820832</v>
       </c>
       <c r="E168" t="n">
-        <v>0.005365</v>
+        <v>904.703303</v>
       </c>
       <c r="F168" t="n">
-        <v>0.005112</v>
+        <v>424.428801</v>
       </c>
       <c r="G168" t="n">
-        <v>0.007178</v>
+        <v>1343.399804</v>
       </c>
       <c r="H168" t="n">
-        <v>0.006919</v>
+        <v>468.411875</v>
       </c>
       <c r="I168" t="n">
-        <v>0.008226000000000001</v>
+        <v>903.343404</v>
       </c>
       <c r="J168" t="n">
-        <v>0.011837</v>
-      </c>
-      <c r="K168" t="n">
-        <v>0.005358</v>
+        <v>7325.470778</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>食品工業右下上市</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr"/>
+          <t>電腦及週邊設備業平上櫃</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>1.472591</v>
+      </c>
       <c r="C169" t="n">
-        <v>293.333234</v>
+        <v>1.429916</v>
       </c>
       <c r="D169" t="n">
-        <v>649.727039</v>
+        <v>1.54623</v>
       </c>
       <c r="E169" t="n">
-        <v>802.013354</v>
+        <v>0.896875</v>
       </c>
       <c r="F169" t="n">
-        <v>777.085777</v>
+        <v>1.494557</v>
       </c>
       <c r="G169" t="n">
-        <v>703.082083</v>
+        <v>1.832703</v>
       </c>
       <c r="H169" t="n">
-        <v>1688.815661</v>
+        <v>2.195671</v>
       </c>
       <c r="I169" t="n">
-        <v>1095.910492</v>
+        <v>1.959908</v>
       </c>
       <c r="J169" t="n">
-        <v>1250.899618</v>
-      </c>
-      <c r="K169" t="n">
-        <v>238.762793</v>
+        <v>2.018571</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>食品工業右下上櫃</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr"/>
+          <t>食品工業右上上市</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>7.264615</v>
+      </c>
       <c r="C170" t="n">
-        <v>0.01134</v>
+        <v>8.02271</v>
       </c>
       <c r="D170" t="n">
-        <v>0.010856</v>
+        <v>11.865974</v>
       </c>
       <c r="E170" t="n">
-        <v>0.005911</v>
+        <v>16.580074</v>
       </c>
       <c r="F170" t="n">
-        <v>0.010054</v>
+        <v>7.674888</v>
       </c>
       <c r="G170" t="n">
-        <v>0.006973</v>
+        <v>9.180273</v>
       </c>
       <c r="H170" t="n">
-        <v>0.010705</v>
+        <v>15.211594</v>
       </c>
       <c r="I170" t="n">
-        <v>0.016031</v>
+        <v>1185.560206</v>
       </c>
       <c r="J170" t="n">
-        <v>0.010104</v>
-      </c>
-      <c r="K170" t="n">
-        <v>0.017923</v>
+        <v>780.105951</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t>食品工業平上市</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr"/>
+          <t>食品工業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>0.001886</v>
+      </c>
       <c r="C171" t="n">
-        <v>575.713856</v>
-      </c>
-      <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr"/>
-      <c r="F171" t="inlineStr"/>
-      <c r="G171" t="inlineStr"/>
-      <c r="H171" t="inlineStr"/>
-      <c r="I171" t="inlineStr"/>
-      <c r="J171" t="inlineStr"/>
-      <c r="K171" t="n">
-        <v>1172.593425</v>
+        <v>0.003556</v>
+      </c>
+      <c r="D171" t="n">
+        <v>0.004412</v>
+      </c>
+      <c r="E171" t="n">
+        <v>0.005225</v>
+      </c>
+      <c r="F171" t="n">
+        <v>0.005884</v>
+      </c>
+      <c r="G171" t="n">
+        <v>0.005327</v>
+      </c>
+      <c r="H171" t="n">
+        <v>0.00641</v>
+      </c>
+      <c r="I171" t="n">
+        <v>0.00389</v>
+      </c>
+      <c r="J171" t="n">
+        <v>0.003337</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
         <is>
+          <t>食品工業右下上市</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>286.797627</v>
+      </c>
+      <c r="C172" t="n">
+        <v>318.886002</v>
+      </c>
+      <c r="D172" t="n">
+        <v>261.472583</v>
+      </c>
+      <c r="E172" t="n">
+        <v>264.272879</v>
+      </c>
+      <c r="F172" t="n">
+        <v>1688.815661</v>
+      </c>
+      <c r="G172" t="n">
+        <v>1095.910492</v>
+      </c>
+      <c r="H172" t="n">
+        <v>307.941446</v>
+      </c>
+      <c r="I172" t="n">
+        <v>238.762793</v>
+      </c>
+      <c r="J172" t="n">
+        <v>269.747139</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="inlineStr">
+        <is>
+          <t>食品工業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>0.010856</v>
+      </c>
+      <c r="C173" t="n">
+        <v>0.005911</v>
+      </c>
+      <c r="D173" t="n">
+        <v>0.010054</v>
+      </c>
+      <c r="E173" t="n">
+        <v>0.006973</v>
+      </c>
+      <c r="F173" t="n">
+        <v>0.010705</v>
+      </c>
+      <c r="G173" t="n">
+        <v>0.016031</v>
+      </c>
+      <c r="H173" t="n">
+        <v>0.010104</v>
+      </c>
+      <c r="I173" t="n">
+        <v>0.017923</v>
+      </c>
+      <c r="J173" t="n">
+        <v>0.014538</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="inlineStr">
+        <is>
+          <t>食品工業平上市</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>373.919301</v>
+      </c>
+      <c r="C174" t="n">
+        <v>490.134677</v>
+      </c>
+      <c r="D174" t="n">
+        <v>526.461753</v>
+      </c>
+      <c r="E174" t="n">
+        <v>441.182343</v>
+      </c>
+      <c r="F174" t="n">
+        <v>5.599845</v>
+      </c>
+      <c r="G174" t="n">
+        <v>7.511816</v>
+      </c>
+      <c r="H174" t="n">
+        <v>949.30633</v>
+      </c>
+      <c r="I174" t="n">
+        <v>5.286877</v>
+      </c>
+      <c r="J174" t="n">
+        <v>3.870029</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="inlineStr">
+        <is>
           <t>食品工業平上櫃</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr"/>
-      <c r="C172" t="n">
-        <v>0.002383</v>
-      </c>
-      <c r="D172" t="n">
-        <v>0.002487</v>
-      </c>
-      <c r="E172" t="n">
-        <v>0.001516</v>
-      </c>
-      <c r="F172" t="inlineStr"/>
-      <c r="G172" t="inlineStr"/>
-      <c r="H172" t="inlineStr"/>
-      <c r="I172" t="inlineStr"/>
-      <c r="J172" t="n">
-        <v>0.001708</v>
-      </c>
-      <c r="K172" t="n">
-        <v>0.001524</v>
+      <c r="B175" t="n">
+        <v>0.004609</v>
+      </c>
+      <c r="C175" t="n">
+        <v>0.003325</v>
+      </c>
+      <c r="D175" t="n">
+        <v>0.0007</v>
+      </c>
+      <c r="E175" t="n">
+        <v>0.001953</v>
+      </c>
+      <c r="F175" t="n">
+        <v>0.001035</v>
+      </c>
+      <c r="G175" t="n">
+        <v>0.002899</v>
+      </c>
+      <c r="H175" t="n">
+        <v>0.007135</v>
+      </c>
+      <c r="I175" t="n">
+        <v>0.002992</v>
+      </c>
+      <c r="J175" t="n">
+        <v>0.005319</v>
       </c>
     </row>
   </sheetData>

--- a/Result/analyze_2.xlsx
+++ b/Result/analyze_2.xlsx
@@ -5520,16 +5520,16 @@
         <v>189680.575138</v>
       </c>
       <c r="C152" t="n">
-        <v>168759.788961</v>
+        <v>166503.267279</v>
       </c>
       <c r="D152" t="n">
-        <v>175055.014039</v>
+        <v>172115.252274</v>
       </c>
       <c r="E152" t="n">
-        <v>219810.875587</v>
+        <v>218271.158035</v>
       </c>
       <c r="F152" t="n">
-        <v>295285.351175</v>
+        <v>293331.951884</v>
       </c>
       <c r="G152" t="n">
         <v>328265.311909</v>
@@ -5656,16 +5656,16 @@
         <v>3730.19601</v>
       </c>
       <c r="C156" t="n">
-        <v>24390.125611</v>
+        <v>26646.647293</v>
       </c>
       <c r="D156" t="n">
-        <v>19899.378642</v>
+        <v>22839.140407</v>
       </c>
       <c r="E156" t="n">
-        <v>19626.115267</v>
+        <v>21165.832819</v>
       </c>
       <c r="F156" t="n">
-        <v>8858.221991</v>
+        <v>10811.621282</v>
       </c>
       <c r="G156" t="n">
         <v>9777.164191</v>

--- a/Result/analyze_2.xlsx
+++ b/Result/analyze_2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J175"/>
+  <dimension ref="A1:K174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,47 +436,52 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -487,31 +492,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>46586.686312</v>
+        <v>48181.200738</v>
       </c>
       <c r="C2" t="n">
-        <v>51636.891594</v>
+        <v>87072.641175</v>
       </c>
       <c r="D2" t="n">
-        <v>86070.802371</v>
+        <v>101424.550246</v>
       </c>
       <c r="E2" t="n">
-        <v>106432.610774</v>
+        <v>74826.461972</v>
       </c>
       <c r="F2" t="n">
-        <v>74175.14004899999</v>
+        <v>88885.523634</v>
       </c>
       <c r="G2" t="n">
-        <v>106634.769564</v>
+        <v>92586.35597600001</v>
       </c>
       <c r="H2" t="n">
-        <v>72074.281301</v>
+        <v>54637.518222</v>
       </c>
       <c r="I2" t="n">
-        <v>66207.42778300001</v>
+        <v>65405.359272</v>
       </c>
       <c r="J2" t="n">
-        <v>47919.945116</v>
+        <v>64353.140658</v>
+      </c>
+      <c r="K2" t="n">
+        <v>70386.353499</v>
       </c>
     </row>
     <row r="3">
@@ -521,31 +529,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.200368</v>
+        <v>3.778768</v>
       </c>
       <c r="C3" t="n">
-        <v>6.813472</v>
+        <v>4.866736</v>
       </c>
       <c r="D3" t="n">
-        <v>6.721156</v>
+        <v>4.473407</v>
       </c>
       <c r="E3" t="n">
-        <v>6.072605</v>
+        <v>5.485964</v>
       </c>
       <c r="F3" t="n">
-        <v>12.53609</v>
+        <v>3.670187</v>
       </c>
       <c r="G3" t="n">
-        <v>11.669936</v>
+        <v>4.065067</v>
       </c>
       <c r="H3" t="n">
-        <v>12.236182</v>
+        <v>3.332657</v>
       </c>
       <c r="I3" t="n">
-        <v>15.627309</v>
+        <v>5.134843</v>
       </c>
       <c r="J3" t="n">
-        <v>3.781644</v>
+        <v>12.88341</v>
+      </c>
+      <c r="K3" t="n">
+        <v>6.306559</v>
       </c>
     </row>
     <row r="4">
@@ -555,31 +566,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1742.583713</v>
+        <v>455.471706</v>
       </c>
       <c r="C4" t="n">
-        <v>898.356579</v>
+        <v>418.86892</v>
       </c>
       <c r="D4" t="n">
-        <v>1542.59659</v>
+        <v>1109.99311</v>
       </c>
       <c r="E4" t="n">
-        <v>627.005644</v>
+        <v>817.067633</v>
       </c>
       <c r="F4" t="n">
-        <v>809.753993</v>
+        <v>1117.670322</v>
       </c>
       <c r="G4" t="n">
-        <v>874.586958</v>
+        <v>855.579436</v>
       </c>
       <c r="H4" t="n">
-        <v>1018.523287</v>
+        <v>767.424752</v>
       </c>
       <c r="I4" t="n">
-        <v>1005.810188</v>
+        <v>741.0858030000001</v>
       </c>
       <c r="J4" t="n">
-        <v>663.324609</v>
+        <v>968.803388</v>
+      </c>
+      <c r="K4" t="n">
+        <v>780.990329</v>
       </c>
     </row>
     <row r="5">
@@ -589,31 +603,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.944307</v>
+        <v>0.588751</v>
       </c>
       <c r="C5" t="n">
-        <v>1.31829225</v>
+        <v>1.406122</v>
       </c>
       <c r="D5" t="n">
-        <v>0.866345</v>
+        <v>1.312462</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9060865</v>
+        <v>1.452728</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9748790000000001</v>
+        <v>1.450457</v>
       </c>
       <c r="G5" t="n">
-        <v>1.483324</v>
+        <v>2.381268</v>
       </c>
       <c r="H5" t="n">
-        <v>1.933499</v>
+        <v>1.721428</v>
       </c>
       <c r="I5" t="n">
-        <v>1.197032</v>
+        <v>1.167368</v>
       </c>
       <c r="J5" t="n">
-        <v>0.740969</v>
+        <v>1.082715</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.167036</v>
       </c>
     </row>
     <row r="6">
@@ -623,31 +640,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1177.582203</v>
+        <v>735.095456</v>
       </c>
       <c r="C6" t="n">
-        <v>866.71379</v>
+        <v>804.510868</v>
       </c>
       <c r="D6" t="n">
-        <v>1194.916813</v>
+        <v>202.725195</v>
       </c>
       <c r="E6" t="n">
-        <v>1063.781628</v>
+        <v>266.145606</v>
       </c>
       <c r="F6" t="n">
-        <v>1114.478124</v>
+        <v>488.255341</v>
       </c>
       <c r="G6" t="n">
-        <v>1524.632189</v>
+        <v>348.954905</v>
       </c>
       <c r="H6" t="n">
-        <v>1117.499227</v>
+        <v>1521.70643</v>
       </c>
       <c r="I6" t="n">
-        <v>814.384108</v>
+        <v>756.272438</v>
       </c>
       <c r="J6" t="n">
-        <v>788.4981749999999</v>
+        <v>1073.492406</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1162.39281</v>
       </c>
     </row>
     <row r="7">
@@ -657,31 +677,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.936181</v>
+        <v>0.231788</v>
       </c>
       <c r="C7" t="n">
-        <v>0.296713</v>
+        <v>0.115903</v>
       </c>
       <c r="D7" t="n">
-        <v>0.507507</v>
+        <v>0.184735</v>
       </c>
       <c r="E7" t="n">
-        <v>0.161472</v>
+        <v>0.144311</v>
       </c>
       <c r="F7" t="n">
-        <v>0.230956</v>
+        <v>0.146814</v>
       </c>
       <c r="G7" t="n">
-        <v>0.216312</v>
+        <v>0.597955</v>
       </c>
       <c r="H7" t="n">
-        <v>0.178666</v>
+        <v>0.075878</v>
       </c>
       <c r="I7" t="n">
-        <v>0.124367</v>
+        <v>0.228206</v>
       </c>
       <c r="J7" t="n">
-        <v>0.076694</v>
+        <v>0.270917</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.253571</v>
       </c>
     </row>
     <row r="8">
@@ -691,31 +714,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>804.3266159999999</v>
+        <v>951.274139</v>
       </c>
       <c r="C8" t="n">
-        <v>945.081587</v>
+        <v>982.283182</v>
       </c>
       <c r="D8" t="n">
-        <v>1026.433541</v>
+        <v>706.3377410000001</v>
       </c>
       <c r="E8" t="n">
-        <v>1319.534296</v>
+        <v>497.939169</v>
       </c>
       <c r="F8" t="n">
-        <v>1653.5761</v>
+        <v>980.069929</v>
       </c>
       <c r="G8" t="n">
-        <v>2214.886948</v>
+        <v>926.218018</v>
       </c>
       <c r="H8" t="n">
-        <v>1182.599023</v>
+        <v>1063.032343</v>
       </c>
       <c r="I8" t="n">
-        <v>1306.290477</v>
+        <v>1369.200591</v>
       </c>
       <c r="J8" t="n">
-        <v>1170.114009</v>
+        <v>942.0624299999999</v>
+      </c>
+      <c r="K8" t="n">
+        <v>895.523136</v>
       </c>
     </row>
     <row r="9">
@@ -725,31 +751,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.36937</v>
+        <v>1.858282</v>
       </c>
       <c r="C9" t="n">
-        <v>1.71218</v>
+        <v>1.4557415</v>
       </c>
       <c r="D9" t="n">
-        <v>1.99472</v>
+        <v>1.517993</v>
       </c>
       <c r="E9" t="n">
-        <v>1.926111</v>
+        <v>2.403135</v>
       </c>
       <c r="F9" t="n">
-        <v>1.867746</v>
+        <v>1.772869</v>
       </c>
       <c r="G9" t="n">
-        <v>1.821556</v>
+        <v>2.490978</v>
       </c>
       <c r="H9" t="n">
-        <v>1.777786</v>
+        <v>1.17748075</v>
       </c>
       <c r="I9" t="n">
-        <v>1.404748</v>
+        <v>1.39837225</v>
       </c>
       <c r="J9" t="n">
-        <v>1.858279</v>
+        <v>1.435431</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.181994</v>
       </c>
     </row>
     <row r="10">
@@ -759,31 +788,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>821.838253</v>
+        <v>609.741537</v>
       </c>
       <c r="C10" t="n">
-        <v>957.630659</v>
+        <v>994.0388809999999</v>
       </c>
       <c r="D10" t="n">
-        <v>1092.657216</v>
+        <v>977.807549</v>
       </c>
       <c r="E10" t="n">
-        <v>1151.470527</v>
+        <v>1132.076528</v>
       </c>
       <c r="F10" t="n">
-        <v>1061.894658</v>
+        <v>2232.320575</v>
       </c>
       <c r="G10" t="n">
-        <v>986.5640090000001</v>
+        <v>1119.634381</v>
       </c>
       <c r="H10" t="n">
-        <v>1214.916591</v>
+        <v>850.886402</v>
       </c>
       <c r="I10" t="n">
-        <v>853.108369</v>
+        <v>720.495889</v>
       </c>
       <c r="J10" t="n">
-        <v>690.962795</v>
+        <v>767.397998</v>
+      </c>
+      <c r="K10" t="n">
+        <v>882.20808</v>
       </c>
     </row>
     <row r="11">
@@ -793,31 +825,34 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2415985</v>
+        <v>0.478104</v>
       </c>
       <c r="C11" t="n">
-        <v>0.308221</v>
+        <v>0.505336</v>
       </c>
       <c r="D11" t="n">
-        <v>0.341959</v>
+        <v>0.923007</v>
       </c>
       <c r="E11" t="n">
-        <v>2.512299</v>
+        <v>0.40590475</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9609550833333333</v>
+        <v>0.7544403333333334</v>
       </c>
       <c r="G11" t="n">
-        <v>1.05431</v>
+        <v>0.600169</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6217311666666666</v>
+        <v>1.807453</v>
       </c>
       <c r="I11" t="n">
-        <v>0.703083</v>
+        <v>0.788442</v>
       </c>
       <c r="J11" t="n">
-        <v>0.465413</v>
+        <v>0.49820625</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.7551346666666666</v>
       </c>
     </row>
     <row r="12">
@@ -827,31 +862,34 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>142.31445</v>
+        <v>389.21712</v>
       </c>
       <c r="C12" t="n">
-        <v>164.8614</v>
+        <v>174.528281</v>
       </c>
       <c r="D12" t="n">
-        <v>148.657663</v>
+        <v>572.380825</v>
       </c>
       <c r="E12" t="n">
-        <v>246.467539</v>
+        <v>331.512968</v>
       </c>
       <c r="F12" t="n">
-        <v>179.031457</v>
+        <v>303.313328</v>
       </c>
       <c r="G12" t="n">
-        <v>146.276942</v>
+        <v>113.302968</v>
       </c>
       <c r="H12" t="n">
-        <v>53.90317</v>
+        <v>122.996559</v>
       </c>
       <c r="I12" t="n">
-        <v>71.754717</v>
+        <v>87.73246399999999</v>
       </c>
       <c r="J12" t="n">
-        <v>89.155992</v>
+        <v>301.656644</v>
+      </c>
+      <c r="K12" t="n">
+        <v>222.464648</v>
       </c>
     </row>
     <row r="13">
@@ -861,31 +899,34 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.07370500000000001</v>
+        <v>0.1095105</v>
       </c>
       <c r="C13" t="n">
-        <v>0.073134</v>
+        <v>0.092378</v>
       </c>
       <c r="D13" t="n">
-        <v>0.10516</v>
+        <v>0.06740500000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0696565</v>
+        <v>0.04596566666666666</v>
       </c>
       <c r="F13" t="n">
-        <v>0.085149</v>
+        <v>0.062015</v>
       </c>
       <c r="G13" t="n">
-        <v>0.121839</v>
+        <v>0.059453</v>
       </c>
       <c r="H13" t="n">
-        <v>0.077456</v>
+        <v>0.046284</v>
       </c>
       <c r="I13" t="n">
-        <v>0.082701</v>
+        <v>0.035646</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1222045</v>
+        <v>0.044337</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.065011</v>
       </c>
     </row>
     <row r="14">
@@ -895,31 +936,34 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>36079.271484</v>
+        <v>35025.473962</v>
       </c>
       <c r="C14" t="n">
-        <v>35352.869423</v>
+        <v>34672.533649</v>
       </c>
       <c r="D14" t="n">
-        <v>43844.505121</v>
+        <v>34640.422918</v>
       </c>
       <c r="E14" t="n">
-        <v>33855.922663</v>
+        <v>28579.811562</v>
       </c>
       <c r="F14" t="n">
-        <v>39818.732</v>
+        <v>38606.288991</v>
       </c>
       <c r="G14" t="n">
-        <v>58636.091601</v>
+        <v>33005.329183</v>
       </c>
       <c r="H14" t="n">
-        <v>61933.541822</v>
+        <v>31624.413326</v>
       </c>
       <c r="I14" t="n">
-        <v>43238.70328</v>
+        <v>25649.875489</v>
       </c>
       <c r="J14" t="n">
-        <v>34965.378984</v>
+        <v>36829.671726</v>
+      </c>
+      <c r="K14" t="n">
+        <v>24951.208776</v>
       </c>
     </row>
     <row r="15">
@@ -929,31 +973,34 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13.437214</v>
+        <v>16.651599</v>
       </c>
       <c r="C15" t="n">
-        <v>8.991203000000001</v>
+        <v>10.828634</v>
       </c>
       <c r="D15" t="n">
-        <v>10.365959</v>
+        <v>10.220403</v>
       </c>
       <c r="E15" t="n">
-        <v>6.611521</v>
+        <v>8.537651</v>
       </c>
       <c r="F15" t="n">
-        <v>7.297555</v>
+        <v>9.192671000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>9.339683000000001</v>
+        <v>8.302375</v>
       </c>
       <c r="H15" t="n">
-        <v>8.56776</v>
+        <v>7.101097</v>
       </c>
       <c r="I15" t="n">
-        <v>10.401768</v>
+        <v>7.906817</v>
       </c>
       <c r="J15" t="n">
-        <v>14.928423</v>
+        <v>11.450579</v>
+      </c>
+      <c r="K15" t="n">
+        <v>9.621321999999999</v>
       </c>
     </row>
     <row r="16">
@@ -963,31 +1010,34 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>122.188769</v>
+        <v>1023.459603</v>
       </c>
       <c r="C16" t="n">
-        <v>173.258883</v>
+        <v>954.477749</v>
       </c>
       <c r="D16" t="n">
-        <v>167.846943</v>
+        <v>904.9705740000001</v>
       </c>
       <c r="E16" t="n">
-        <v>162.343206</v>
+        <v>955.47672</v>
       </c>
       <c r="F16" t="n">
-        <v>190.95954</v>
+        <v>1229.037194</v>
       </c>
       <c r="G16" t="n">
-        <v>302.511449</v>
+        <v>592.8472839999999</v>
       </c>
       <c r="H16" t="n">
-        <v>368.526172</v>
+        <v>1068.677673</v>
       </c>
       <c r="I16" t="n">
-        <v>122.158988</v>
+        <v>593.969129</v>
       </c>
       <c r="J16" t="n">
-        <v>589.136943</v>
+        <v>760.486909</v>
+      </c>
+      <c r="K16" t="n">
+        <v>666.830693</v>
       </c>
     </row>
     <row r="17">
@@ -997,31 +1047,34 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.238945</v>
+        <v>0.042913</v>
       </c>
       <c r="C17" t="n">
-        <v>0.102638</v>
+        <v>0.047639</v>
       </c>
       <c r="D17" t="n">
-        <v>0.075781</v>
+        <v>0.07234599999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>0.087064</v>
+        <v>0.03776</v>
       </c>
       <c r="F17" t="n">
-        <v>0.114932</v>
+        <v>0.09390900000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>0.07022200000000001</v>
+        <v>0.070607</v>
       </c>
       <c r="H17" t="n">
-        <v>0.082695</v>
+        <v>0.058583</v>
       </c>
       <c r="I17" t="n">
-        <v>0.07177500000000001</v>
+        <v>0.047846</v>
       </c>
       <c r="J17" t="n">
-        <v>0.086113</v>
+        <v>0.049209</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.056001</v>
       </c>
     </row>
     <row r="18">
@@ -1031,31 +1084,34 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>733.0549140000001</v>
+        <v>504.04349</v>
       </c>
       <c r="C18" t="n">
-        <v>1399.054171</v>
+        <v>486.994612</v>
       </c>
       <c r="D18" t="n">
-        <v>662.797492</v>
+        <v>394.909571</v>
       </c>
       <c r="E18" t="n">
-        <v>756.907611</v>
+        <v>390.909335</v>
       </c>
       <c r="F18" t="n">
-        <v>1625.270931</v>
+        <v>433.142001</v>
       </c>
       <c r="G18" t="n">
-        <v>803.294501</v>
+        <v>460.333694</v>
       </c>
       <c r="H18" t="n">
-        <v>1393.298319</v>
+        <v>263.870993</v>
       </c>
       <c r="I18" t="n">
-        <v>1682.643789</v>
+        <v>257.258089</v>
       </c>
       <c r="J18" t="n">
-        <v>998.461128</v>
+        <v>700.153453</v>
+      </c>
+      <c r="K18" t="n">
+        <v>784.406296</v>
       </c>
     </row>
     <row r="19">
@@ -1065,31 +1121,34 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.500443</v>
+        <v>0.223928</v>
       </c>
       <c r="C19" t="n">
-        <v>1.856242</v>
+        <v>0.277059</v>
       </c>
       <c r="D19" t="n">
-        <v>3.792821</v>
+        <v>0.282796</v>
       </c>
       <c r="E19" t="n">
-        <v>3.596311</v>
+        <v>0.138331</v>
       </c>
       <c r="F19" t="n">
-        <v>3.06292</v>
+        <v>0.421391</v>
       </c>
       <c r="G19" t="n">
-        <v>4.595788</v>
+        <v>0.666552</v>
       </c>
       <c r="H19" t="n">
-        <v>5.827706</v>
+        <v>2.212432</v>
       </c>
       <c r="I19" t="n">
-        <v>2.903894</v>
+        <v>1.201581</v>
       </c>
       <c r="J19" t="n">
-        <v>1.903904</v>
+        <v>1.251488</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.633723</v>
       </c>
     </row>
     <row r="20">
@@ -1099,31 +1158,34 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>9882.511367999999</v>
+        <v>9372.369471</v>
       </c>
       <c r="C20" t="n">
-        <v>6355.062814</v>
+        <v>5795.358255</v>
       </c>
       <c r="D20" t="n">
-        <v>8542.054827</v>
+        <v>5553.061939</v>
       </c>
       <c r="E20" t="n">
-        <v>5022.470767</v>
+        <v>6898.458472</v>
       </c>
       <c r="F20" t="n">
-        <v>10431.09168</v>
+        <v>5661.701177</v>
       </c>
       <c r="G20" t="n">
-        <v>10362.427802</v>
+        <v>5259.441078</v>
       </c>
       <c r="H20" t="n">
-        <v>13089.881223</v>
+        <v>3353.306981</v>
       </c>
       <c r="I20" t="n">
-        <v>10887.337122</v>
+        <v>4705.864866</v>
       </c>
       <c r="J20" t="n">
-        <v>8709.227973999999</v>
+        <v>7314.547126</v>
+      </c>
+      <c r="K20" t="n">
+        <v>5379.148063</v>
       </c>
     </row>
     <row r="21">
@@ -1133,31 +1195,34 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.129619</v>
+        <v>0.58366</v>
       </c>
       <c r="C21" t="n">
-        <v>0.08554200000000001</v>
+        <v>0.5509770000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>0.243057</v>
+        <v>0.480382</v>
       </c>
       <c r="E21" t="n">
-        <v>0.089675</v>
+        <v>0.411562</v>
       </c>
       <c r="F21" t="n">
-        <v>0.294889</v>
+        <v>0.407707</v>
       </c>
       <c r="G21" t="n">
-        <v>0.334746</v>
+        <v>0.297397</v>
       </c>
       <c r="H21" t="n">
-        <v>0.574137</v>
+        <v>0.337121</v>
       </c>
       <c r="I21" t="n">
-        <v>0.863293</v>
+        <v>0.381888</v>
       </c>
       <c r="J21" t="n">
-        <v>0.422091</v>
+        <v>0.236467</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.231797</v>
       </c>
     </row>
     <row r="22">
@@ -1167,31 +1232,34 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>419.428425</v>
+        <v>91.716739</v>
       </c>
       <c r="C22" t="n">
-        <v>174.154573</v>
+        <v>123.792569</v>
       </c>
       <c r="D22" t="n">
-        <v>137.624827</v>
+        <v>134.661671</v>
       </c>
       <c r="E22" t="n">
-        <v>104.854825</v>
+        <v>151.510135</v>
       </c>
       <c r="F22" t="n">
-        <v>196.898298</v>
+        <v>173.457935</v>
       </c>
       <c r="G22" t="n">
-        <v>217.971558</v>
+        <v>96.576919</v>
       </c>
       <c r="H22" t="n">
-        <v>105.367152</v>
+        <v>134.912417</v>
       </c>
       <c r="I22" t="n">
-        <v>86.809005</v>
+        <v>136.023827</v>
       </c>
       <c r="J22" t="n">
-        <v>92.88312999999999</v>
+        <v>109.538916</v>
+      </c>
+      <c r="K22" t="n">
+        <v>91.082618</v>
       </c>
     </row>
     <row r="23">
@@ -1201,31 +1269,34 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.302992</v>
+        <v>0.048921</v>
       </c>
       <c r="C23" t="n">
-        <v>0.75597</v>
+        <v>0.016302</v>
       </c>
       <c r="D23" t="n">
-        <v>0.639278</v>
+        <v>0.246868</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2668</v>
+        <v>0.032635</v>
       </c>
       <c r="F23" t="n">
-        <v>0.024437</v>
+        <v>0.181323</v>
       </c>
       <c r="G23" t="n">
-        <v>0.024472</v>
+        <v>0.020694</v>
       </c>
       <c r="H23" t="n">
-        <v>0.236392</v>
+        <v>0.231682</v>
       </c>
       <c r="I23" t="n">
-        <v>0.251624</v>
+        <v>0.198653</v>
       </c>
       <c r="J23" t="n">
-        <v>0.229291</v>
+        <v>0.012894</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.179984</v>
       </c>
     </row>
     <row r="24">
@@ -1235,31 +1306,34 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>716.5622499999999</v>
+        <v>481.318193</v>
       </c>
       <c r="C24" t="n">
-        <v>1063.384379</v>
+        <v>322.691328</v>
       </c>
       <c r="D24" t="n">
-        <v>1014.584463</v>
+        <v>254.539785</v>
       </c>
       <c r="E24" t="n">
-        <v>1574.244514</v>
+        <v>184.41174</v>
       </c>
       <c r="F24" t="n">
-        <v>723.970323</v>
+        <v>272.575433</v>
       </c>
       <c r="G24" t="n">
-        <v>1038.512025</v>
+        <v>413.901252</v>
       </c>
       <c r="H24" t="n">
-        <v>762.959099</v>
+        <v>559.953737</v>
       </c>
       <c r="I24" t="n">
-        <v>1340.883595</v>
+        <v>609.50382</v>
       </c>
       <c r="J24" t="n">
-        <v>1143.293299</v>
+        <v>376.309095</v>
+      </c>
+      <c r="K24" t="n">
+        <v>566.956783</v>
       </c>
     </row>
     <row r="25">
@@ -1269,31 +1343,34 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.178292</v>
+        <v>0.181165</v>
       </c>
       <c r="C25" t="n">
-        <v>0.693905</v>
+        <v>0.14632</v>
       </c>
       <c r="D25" t="n">
-        <v>1.141352</v>
+        <v>0.048634</v>
       </c>
       <c r="E25" t="n">
-        <v>0.89294</v>
+        <v>0.154381</v>
       </c>
       <c r="F25" t="n">
-        <v>2.197642</v>
+        <v>0.069926</v>
       </c>
       <c r="G25" t="n">
-        <v>1.170657</v>
+        <v>0.167024</v>
       </c>
       <c r="H25" t="n">
-        <v>0.382493</v>
+        <v>0.037174</v>
       </c>
       <c r="I25" t="n">
-        <v>0.337553</v>
+        <v>0.02765</v>
       </c>
       <c r="J25" t="n">
-        <v>0.162364</v>
+        <v>0.287736</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.19613</v>
       </c>
     </row>
     <row r="26">
@@ -1303,31 +1380,34 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>270822.403683</v>
+        <v>301007.353581</v>
       </c>
       <c r="C26" t="n">
-        <v>285493.879323</v>
+        <v>266223.514266</v>
       </c>
       <c r="D26" t="n">
-        <v>307574.643404</v>
+        <v>382668.06568</v>
       </c>
       <c r="E26" t="n">
-        <v>229451.108898</v>
+        <v>282986.660315</v>
       </c>
       <c r="F26" t="n">
-        <v>247862.218384</v>
+        <v>444793.551669</v>
       </c>
       <c r="G26" t="n">
-        <v>366999.998588</v>
+        <v>288293.793547</v>
       </c>
       <c r="H26" t="n">
-        <v>309715.52784</v>
+        <v>230232.353759</v>
       </c>
       <c r="I26" t="n">
-        <v>267014.602251</v>
+        <v>191182.562802</v>
       </c>
       <c r="J26" t="n">
-        <v>292808.61959</v>
+        <v>229960.560629</v>
+      </c>
+      <c r="K26" t="n">
+        <v>233466.654463</v>
       </c>
     </row>
     <row r="27">
@@ -1337,31 +1417,34 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>90.226675</v>
+        <v>131.142732</v>
       </c>
       <c r="C27" t="n">
-        <v>79.75349</v>
+        <v>112.328491</v>
       </c>
       <c r="D27" t="n">
-        <v>123.720141</v>
+        <v>122.518992</v>
       </c>
       <c r="E27" t="n">
-        <v>128.044739</v>
+        <v>94.45443299999999</v>
       </c>
       <c r="F27" t="n">
-        <v>116.418771</v>
+        <v>110.047906</v>
       </c>
       <c r="G27" t="n">
-        <v>141.135673</v>
+        <v>88.645197</v>
       </c>
       <c r="H27" t="n">
-        <v>107.774604</v>
+        <v>76.91721200000001</v>
       </c>
       <c r="I27" t="n">
-        <v>120.92481</v>
+        <v>72.951875</v>
       </c>
       <c r="J27" t="n">
-        <v>112.366037</v>
+        <v>68.364958</v>
+      </c>
+      <c r="K27" t="n">
+        <v>73.215756</v>
       </c>
     </row>
     <row r="28">
@@ -1371,31 +1454,34 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1190.705722</v>
+        <v>860.014813</v>
       </c>
       <c r="C28" t="n">
-        <v>1215.495016</v>
+        <v>949.647206</v>
       </c>
       <c r="D28" t="n">
-        <v>1089.004733</v>
+        <v>1120.753614</v>
       </c>
       <c r="E28" t="n">
-        <v>957.057733</v>
+        <v>783.0559500000001</v>
       </c>
       <c r="F28" t="n">
-        <v>621.03682</v>
+        <v>1207.303954</v>
       </c>
       <c r="G28" t="n">
-        <v>1274.322432</v>
+        <v>797.577685</v>
       </c>
       <c r="H28" t="n">
-        <v>1297.387778</v>
+        <v>797.388914</v>
       </c>
       <c r="I28" t="n">
-        <v>13301.340597</v>
+        <v>592.914996</v>
       </c>
       <c r="J28" t="n">
-        <v>7556.680408</v>
+        <v>581.181292</v>
+      </c>
+      <c r="K28" t="n">
+        <v>760.684691</v>
       </c>
     </row>
     <row r="29">
@@ -1405,31 +1491,34 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8938</v>
+        <v>0.5465680000000001</v>
       </c>
       <c r="C29" t="n">
-        <v>1.53330125</v>
+        <v>1.25852</v>
       </c>
       <c r="D29" t="n">
-        <v>2.935031</v>
+        <v>3.43964375</v>
       </c>
       <c r="E29" t="n">
-        <v>3.985883</v>
+        <v>2.799962</v>
       </c>
       <c r="F29" t="n">
-        <v>4.857131</v>
+        <v>3.870842</v>
       </c>
       <c r="G29" t="n">
-        <v>3.515911</v>
+        <v>3.314639</v>
       </c>
       <c r="H29" t="n">
-        <v>2.824977</v>
+        <v>2.798222</v>
       </c>
       <c r="I29" t="n">
-        <v>0.904744</v>
+        <v>1.921964</v>
       </c>
       <c r="J29" t="n">
-        <v>3.859594</v>
+        <v>1.392017</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.065627</v>
       </c>
     </row>
     <row r="30">
@@ -1439,31 +1528,34 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>18447.333554</v>
+        <v>7597.674652</v>
       </c>
       <c r="C30" t="n">
-        <v>16209.80837</v>
+        <v>2917.366962</v>
       </c>
       <c r="D30" t="n">
-        <v>18913.857904</v>
+        <v>2308.976704</v>
       </c>
       <c r="E30" t="n">
-        <v>12874.398476</v>
+        <v>8542.126894999999</v>
       </c>
       <c r="F30" t="n">
-        <v>16711.163602</v>
+        <v>22596.585642</v>
       </c>
       <c r="G30" t="n">
-        <v>12336.164244</v>
+        <v>16387.243</v>
       </c>
       <c r="H30" t="n">
-        <v>11623.162005</v>
+        <v>11929.565547</v>
       </c>
       <c r="I30" t="n">
-        <v>7439.994847</v>
+        <v>10260.117717</v>
       </c>
       <c r="J30" t="n">
-        <v>9099.743048</v>
+        <v>10867.276106</v>
+      </c>
+      <c r="K30" t="n">
+        <v>13748.727764</v>
       </c>
     </row>
     <row r="31">
@@ -1473,31 +1565,34 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>9.350882</v>
+        <v>1.320835</v>
       </c>
       <c r="C31" t="n">
-        <v>11.274925</v>
+        <v>4.32494</v>
       </c>
       <c r="D31" t="n">
-        <v>16.393483</v>
+        <v>1.249045</v>
       </c>
       <c r="E31" t="n">
-        <v>14.89894</v>
+        <v>0.5613050000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>10.04876</v>
+        <v>5.344747</v>
       </c>
       <c r="G31" t="n">
-        <v>11.599118</v>
+        <v>1.14103</v>
       </c>
       <c r="H31" t="n">
-        <v>13.090228</v>
+        <v>4.486392</v>
       </c>
       <c r="I31" t="n">
-        <v>13.168476</v>
+        <v>2.811034</v>
       </c>
       <c r="J31" t="n">
-        <v>16.784504</v>
+        <v>3.864096</v>
+      </c>
+      <c r="K31" t="n">
+        <v>5.05311</v>
       </c>
     </row>
     <row r="32">
@@ -1507,1294 +1602,1405 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>18414.422521</v>
+        <v>50101.503575</v>
       </c>
       <c r="C32" t="n">
-        <v>23993.723144</v>
+        <v>42180.98931</v>
       </c>
       <c r="D32" t="n">
-        <v>38398.115906</v>
+        <v>55899.029209</v>
       </c>
       <c r="E32" t="n">
-        <v>17613.517817</v>
+        <v>90999.25553900001</v>
       </c>
       <c r="F32" t="n">
-        <v>17741.971142</v>
+        <v>56568.545658</v>
       </c>
       <c r="G32" t="n">
-        <v>29521.399492</v>
+        <v>51459.656456</v>
       </c>
       <c r="H32" t="n">
-        <v>37282.689887</v>
+        <v>39037.126155</v>
       </c>
       <c r="I32" t="n">
-        <v>51336.878614</v>
+        <v>39486.980971</v>
       </c>
       <c r="J32" t="n">
-        <v>49957.318591</v>
+        <v>45724.884283</v>
+      </c>
+      <c r="K32" t="n">
+        <v>37322.962106</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>塑膠工業右下上市</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>21.393921</v>
-      </c>
-      <c r="C33" t="n">
-        <v>39.355459</v>
-      </c>
-      <c r="D33" t="n">
-        <v>34.904345</v>
-      </c>
-      <c r="E33" t="n">
-        <v>28.912333</v>
-      </c>
-      <c r="F33" t="n">
-        <v>15.643569</v>
-      </c>
-      <c r="G33" t="n">
-        <v>41.277259</v>
-      </c>
-      <c r="H33" t="n">
-        <v>56.90155</v>
-      </c>
-      <c r="I33" t="n">
-        <v>15.000231</v>
-      </c>
+          <t>塑膠工業右上上櫃</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="n">
-        <v>12.142566</v>
+        <v>0.002798</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.003253</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>塑膠工業右下上櫃</t>
+          <t>塑膠工業右下上市</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.043256</v>
+        <v>15.404189</v>
       </c>
       <c r="C34" t="n">
-        <v>0.028786</v>
+        <v>16.601022</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0244545</v>
+        <v>23.758345</v>
       </c>
       <c r="E34" t="n">
-        <v>0.029761</v>
+        <v>33.668754</v>
       </c>
       <c r="F34" t="n">
-        <v>0.016262</v>
+        <v>31.301015</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0393105</v>
+        <v>12.398804</v>
       </c>
       <c r="H34" t="n">
-        <v>0.03161</v>
+        <v>47.413407</v>
       </c>
       <c r="I34" t="n">
-        <v>0.014736</v>
+        <v>49.485111</v>
       </c>
       <c r="J34" t="n">
-        <v>0.039382</v>
+        <v>24.236528</v>
+      </c>
+      <c r="K34" t="n">
+        <v>39.447818</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>塑膠工業平上市</t>
+          <t>塑膠工業右下上櫃</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>86.148461</v>
+        <v>0.03893</v>
       </c>
       <c r="C35" t="n">
-        <v>105.869253</v>
+        <v>0.01564</v>
       </c>
       <c r="D35" t="n">
-        <v>159.785773</v>
+        <v>0.0376</v>
       </c>
       <c r="E35" t="n">
-        <v>84.431816</v>
+        <v>0.015035</v>
       </c>
       <c r="F35" t="n">
-        <v>244.212676</v>
+        <v>0.023263</v>
       </c>
       <c r="G35" t="n">
-        <v>121.00438</v>
+        <v>0.018657</v>
       </c>
       <c r="H35" t="n">
-        <v>87.37659499999999</v>
+        <v>0.014902</v>
       </c>
       <c r="I35" t="n">
-        <v>223.733005</v>
+        <v>0.02465</v>
       </c>
       <c r="J35" t="n">
-        <v>188.528186</v>
+        <v>0.012504</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.01397333333333333</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>居家生活右上上市</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
+          <t>塑膠工業平上市</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>41.081579</v>
+      </c>
+      <c r="C36" t="n">
+        <v>35.111708</v>
+      </c>
+      <c r="D36" t="n">
+        <v>6.776158</v>
+      </c>
+      <c r="E36" t="n">
+        <v>108.41809</v>
+      </c>
+      <c r="F36" t="n">
+        <v>162.490625</v>
+      </c>
+      <c r="G36" t="n">
+        <v>41.126397</v>
+      </c>
+      <c r="H36" t="n">
+        <v>40.174258</v>
+      </c>
+      <c r="I36" t="n">
+        <v>54.384911</v>
+      </c>
       <c r="J36" t="n">
-        <v>0.099395</v>
+        <v>55.723207</v>
+      </c>
+      <c r="K36" t="n">
+        <v>61.02265</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>居家生活右上上櫃</t>
+          <t>塑膠工業平上櫃</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.002171</v>
+        <v>0.000452</v>
       </c>
       <c r="C37" t="n">
-        <v>0.001119</v>
+        <v>0.000501</v>
       </c>
       <c r="D37" t="n">
-        <v>0.000906</v>
+        <v>0.000252</v>
       </c>
       <c r="E37" t="n">
-        <v>0.000283</v>
+        <v>0.000121</v>
       </c>
       <c r="F37" t="n">
-        <v>0.001482</v>
+        <v>0.000437</v>
       </c>
       <c r="G37" t="n">
-        <v>0.00025</v>
+        <v>0.000169</v>
       </c>
       <c r="H37" t="n">
-        <v>0.00049</v>
+        <v>0.003312</v>
       </c>
       <c r="I37" t="n">
-        <v>0.000346</v>
+        <v>0.00536</v>
       </c>
       <c r="J37" t="n">
-        <v>0.00124</v>
+        <v>0.000182</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.002672</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>居家生活右下上市</t>
+          <t>居家生活右上上櫃</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>20.023105</v>
+        <v>0.00124</v>
       </c>
       <c r="C38" t="n">
-        <v>29.842921</v>
+        <v>0.005921</v>
       </c>
       <c r="D38" t="n">
-        <v>27.947611</v>
+        <v>0.000149</v>
       </c>
       <c r="E38" t="n">
-        <v>20.812951</v>
-      </c>
-      <c r="F38" t="n">
-        <v>28.538201</v>
-      </c>
+        <v>0.000654</v>
+      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
-        <v>52.805219</v>
-      </c>
-      <c r="H38" t="n">
-        <v>33.439189</v>
-      </c>
+        <v>0.000374</v>
+      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="n">
-        <v>32.172167</v>
+        <v>0.000566</v>
       </c>
       <c r="J38" t="n">
-        <v>29.480435</v>
+        <v>0.000794</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.000838</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>居家生活右下上櫃</t>
+          <t>居家生活右下上市</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.55962575</v>
+        <v>112.086444</v>
       </c>
       <c r="C39" t="n">
-        <v>0.3257003333333333</v>
+        <v>218.849283</v>
       </c>
       <c r="D39" t="n">
-        <v>0.3575955</v>
+        <v>45.219145</v>
       </c>
       <c r="E39" t="n">
-        <v>0.2460553333333333</v>
+        <v>333.169382</v>
       </c>
       <c r="F39" t="n">
-        <v>0.312833</v>
+        <v>370.89283</v>
       </c>
       <c r="G39" t="n">
-        <v>0.226244</v>
+        <v>334.364303</v>
       </c>
       <c r="H39" t="n">
-        <v>0.217029</v>
+        <v>478.504812</v>
       </c>
       <c r="I39" t="n">
-        <v>0.246371</v>
+        <v>327.742795</v>
       </c>
       <c r="J39" t="n">
-        <v>0.175662</v>
+        <v>283.350769</v>
+      </c>
+      <c r="K39" t="n">
+        <v>357.214741</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>居家生活平上市</t>
+          <t>居家生活右下上櫃</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>64.49407600000001</v>
+        <v>0.17568</v>
       </c>
       <c r="C40" t="n">
-        <v>195.838725</v>
+        <v>0.6648365000000001</v>
       </c>
       <c r="D40" t="n">
-        <v>129.132417</v>
+        <v>0.2781855</v>
       </c>
       <c r="E40" t="n">
-        <v>68.960701</v>
+        <v>0.1941435</v>
       </c>
       <c r="F40" t="n">
-        <v>57.20569</v>
+        <v>0.681119</v>
       </c>
       <c r="G40" t="n">
-        <v>41.651479</v>
+        <v>0.551221</v>
       </c>
       <c r="H40" t="n">
-        <v>68.788026</v>
+        <v>0.374704</v>
       </c>
       <c r="I40" t="n">
-        <v>103.876128</v>
+        <v>0.15335</v>
       </c>
       <c r="J40" t="n">
-        <v>82.606009</v>
+        <v>0.254119</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.377294</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>居家生活平上櫃</t>
+          <t>居家生活平上市</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.00075</v>
+        <v>0.099395</v>
       </c>
       <c r="C41" t="n">
-        <v>0.000768</v>
+        <v>0.052789</v>
       </c>
       <c r="D41" t="n">
-        <v>0.000901</v>
+        <v>175.402923</v>
       </c>
       <c r="E41" t="n">
-        <v>0.004289</v>
+        <v>0.162383</v>
       </c>
       <c r="F41" t="n">
-        <v>0.003008</v>
+        <v>0.151178</v>
       </c>
       <c r="G41" t="n">
-        <v>0.001225</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0.001313</v>
-      </c>
-      <c r="I41" t="n">
-        <v>7.1e-05</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0.000416</v>
-      </c>
+        <v>5.927249</v>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>建材營造右上上市</t>
+          <t>居家生活平上櫃</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>149.45803</v>
+        <v>0.000398</v>
       </c>
       <c r="C42" t="n">
-        <v>124.981634</v>
+        <v>0.001559</v>
       </c>
       <c r="D42" t="n">
-        <v>201.107528</v>
+        <v>0.003731</v>
       </c>
       <c r="E42" t="n">
-        <v>147.807027</v>
+        <v>0.001263</v>
       </c>
       <c r="F42" t="n">
-        <v>164.04647</v>
+        <v>0.001168</v>
       </c>
       <c r="G42" t="n">
-        <v>186.246527</v>
+        <v>0.005161</v>
       </c>
       <c r="H42" t="n">
-        <v>142.771721</v>
+        <v>0.000919</v>
       </c>
       <c r="I42" t="n">
-        <v>108.367262</v>
+        <v>2e-06</v>
       </c>
       <c r="J42" t="n">
-        <v>199.957192</v>
+        <v>1.525e-05</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.00086</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>建材營造右上上櫃</t>
+          <t>建材營造右上上市</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.007346</v>
+        <v>99.41713900000001</v>
       </c>
       <c r="C43" t="n">
-        <v>0.012669</v>
+        <v>228.340317</v>
       </c>
       <c r="D43" t="n">
-        <v>0.015847</v>
+        <v>258.123264</v>
       </c>
       <c r="E43" t="n">
-        <v>0.020326</v>
+        <v>173.414347</v>
       </c>
       <c r="F43" t="n">
-        <v>0.01373125</v>
+        <v>183.641381</v>
       </c>
       <c r="G43" t="n">
-        <v>0.007236</v>
+        <v>119.483677</v>
       </c>
       <c r="H43" t="n">
-        <v>0.006054</v>
+        <v>155.635763</v>
       </c>
       <c r="I43" t="n">
-        <v>0.032965</v>
+        <v>94.819248</v>
       </c>
       <c r="J43" t="n">
-        <v>0.010129</v>
+        <v>106.908919</v>
+      </c>
+      <c r="K43" t="n">
+        <v>150.02383</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>建材營造右下上市</t>
+          <t>建材營造右上上櫃</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>428.069404</v>
+        <v>0.017281</v>
       </c>
       <c r="C44" t="n">
-        <v>1042.3501</v>
+        <v>0.009006999999999999</v>
       </c>
       <c r="D44" t="n">
-        <v>1117.33762</v>
+        <v>0.010999</v>
       </c>
       <c r="E44" t="n">
-        <v>829.348561</v>
+        <v>0.014612</v>
       </c>
       <c r="F44" t="n">
-        <v>935.330247</v>
+        <v>0.015947</v>
       </c>
       <c r="G44" t="n">
-        <v>1437.091697</v>
+        <v>0.017943</v>
       </c>
       <c r="H44" t="n">
-        <v>904.735288</v>
+        <v>0.010616</v>
       </c>
       <c r="I44" t="n">
-        <v>970.827238</v>
+        <v>0.007229</v>
       </c>
       <c r="J44" t="n">
-        <v>785.610801</v>
+        <v>0.008765999999999999</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.0073135</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>建材營造右下上櫃</t>
+          <t>建材營造右下上市</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.06238</v>
+        <v>822.034456</v>
       </c>
       <c r="C45" t="n">
-        <v>0.054294</v>
+        <v>594.209527</v>
       </c>
       <c r="D45" t="n">
-        <v>0.050976</v>
+        <v>1065.118136</v>
       </c>
       <c r="E45" t="n">
-        <v>0.03979466666666667</v>
+        <v>726.277963</v>
       </c>
       <c r="F45" t="n">
-        <v>0.044147</v>
+        <v>1157.936493</v>
       </c>
       <c r="G45" t="n">
-        <v>0.110113</v>
+        <v>748.572722</v>
       </c>
       <c r="H45" t="n">
-        <v>0.051935</v>
+        <v>636.517282</v>
       </c>
       <c r="I45" t="n">
-        <v>0.04488866666666667</v>
+        <v>630.8495809999999</v>
       </c>
       <c r="J45" t="n">
-        <v>0.04910066666666667</v>
+        <v>517.395887</v>
+      </c>
+      <c r="K45" t="n">
+        <v>645.389143</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>建材營造平上市</t>
+          <t>建材營造右下上櫃</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>581.465077</v>
+        <v>0.05922616666666666</v>
       </c>
       <c r="C46" t="n">
-        <v>36.673821</v>
+        <v>0.06313766666666666</v>
       </c>
       <c r="D46" t="n">
-        <v>53.262782</v>
+        <v>0.052888</v>
       </c>
       <c r="E46" t="n">
-        <v>166.435499</v>
+        <v>0.03973</v>
       </c>
       <c r="F46" t="n">
-        <v>76.116998</v>
+        <v>0.081526</v>
       </c>
       <c r="G46" t="n">
-        <v>121.778049</v>
+        <v>0.049072</v>
       </c>
       <c r="H46" t="n">
-        <v>63.764067</v>
+        <v>0.056935</v>
       </c>
       <c r="I46" t="n">
-        <v>108.656523</v>
+        <v>0.036186</v>
       </c>
       <c r="J46" t="n">
-        <v>61.486283</v>
+        <v>0.035261</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.056238</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>建材營造平上櫃</t>
+          <t>建材營造平上市</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.022415</v>
+        <v>125.602681</v>
       </c>
       <c r="C47" t="n">
-        <v>0.010698</v>
+        <v>752.955744</v>
       </c>
       <c r="D47" t="n">
-        <v>0.013407</v>
+        <v>32.368992</v>
       </c>
       <c r="E47" t="n">
-        <v>0.026788</v>
+        <v>48.812522</v>
       </c>
       <c r="F47" t="n">
-        <v>0.023503</v>
+        <v>140.201432</v>
       </c>
       <c r="G47" t="n">
-        <v>0.009675</v>
+        <v>53.098055</v>
       </c>
       <c r="H47" t="n">
-        <v>0.009086</v>
+        <v>495.524957</v>
       </c>
       <c r="I47" t="n">
-        <v>0.017261</v>
+        <v>372.014927</v>
       </c>
       <c r="J47" t="n">
-        <v>0.02706</v>
+        <v>384.266306</v>
+      </c>
+      <c r="K47" t="n">
+        <v>428.254098</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>數位雲端右上上市</t>
+          <t>建材營造平上櫃</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>212.845719</v>
+        <v>0.009823</v>
       </c>
       <c r="C48" t="n">
-        <v>131.591225</v>
+        <v>0.009965999999999999</v>
       </c>
       <c r="D48" t="n">
-        <v>273.926956</v>
+        <v>0.006973</v>
       </c>
       <c r="E48" t="n">
-        <v>79.373986</v>
+        <v>0.002181</v>
       </c>
       <c r="F48" t="n">
-        <v>81.745813</v>
+        <v>0.009468000000000001</v>
       </c>
       <c r="G48" t="n">
-        <v>65.84591899999999</v>
+        <v>0.005543</v>
       </c>
       <c r="H48" t="n">
-        <v>48.754718</v>
+        <v>0.004668</v>
       </c>
       <c r="I48" t="n">
-        <v>76.16837200000001</v>
+        <v>0.001414</v>
       </c>
       <c r="J48" t="n">
-        <v>38.724278</v>
+        <v>0.00808</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0.004919</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>數位雲端右上上櫃</t>
+          <t>數位雲端右上上市</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.218607</v>
+        <v>38.724278</v>
       </c>
       <c r="C49" t="n">
-        <v>0.179389</v>
+        <v>23.253894</v>
       </c>
       <c r="D49" t="n">
-        <v>0.296095</v>
+        <v>69.83696999999999</v>
       </c>
       <c r="E49" t="n">
-        <v>0.1936893333333334</v>
+        <v>27.846748</v>
       </c>
       <c r="F49" t="n">
-        <v>0.121387</v>
+        <v>26.152505</v>
       </c>
       <c r="G49" t="n">
-        <v>0.1898</v>
+        <v>38.033875</v>
       </c>
       <c r="H49" t="n">
-        <v>0.209382</v>
+        <v>38.339969</v>
       </c>
       <c r="I49" t="n">
-        <v>0.425433</v>
+        <v>129.269941</v>
       </c>
       <c r="J49" t="n">
-        <v>0.66971</v>
+        <v>385.506143</v>
+      </c>
+      <c r="K49" t="n">
+        <v>312.441913</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>數位雲端右下上市</t>
+          <t>數位雲端右上上櫃</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>22.50859</v>
+        <v>0.671671</v>
       </c>
       <c r="C50" t="n">
-        <v>28.703929</v>
+        <v>0.218515</v>
       </c>
       <c r="D50" t="n">
-        <v>24.480949</v>
+        <v>0.424912</v>
       </c>
       <c r="E50" t="n">
-        <v>28.726985</v>
+        <v>0.2734</v>
       </c>
       <c r="F50" t="n">
-        <v>38.646655</v>
+        <v>0.216161</v>
       </c>
       <c r="G50" t="n">
-        <v>102.767056</v>
+        <v>0.323812</v>
       </c>
       <c r="H50" t="n">
-        <v>71.747041</v>
+        <v>0.260287</v>
       </c>
       <c r="I50" t="n">
-        <v>59.996493</v>
+        <v>0.232099</v>
       </c>
       <c r="J50" t="n">
-        <v>25.052612</v>
+        <v>0.304774</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0.383423</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>數位雲端右下上櫃</t>
+          <t>數位雲端右下上市</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.09177299999999999</v>
+        <v>48.424674</v>
       </c>
       <c r="C51" t="n">
-        <v>0.11663</v>
+        <v>69.61456099999999</v>
       </c>
       <c r="D51" t="n">
-        <v>0.115867</v>
+        <v>64.845489</v>
       </c>
       <c r="E51" t="n">
-        <v>0.173237</v>
+        <v>46.309135</v>
       </c>
       <c r="F51" t="n">
-        <v>0.181664</v>
+        <v>111.115525</v>
       </c>
       <c r="G51" t="n">
-        <v>0.20589275</v>
+        <v>119.635095</v>
       </c>
       <c r="H51" t="n">
-        <v>0.1089243333333333</v>
+        <v>74.35132900000001</v>
       </c>
       <c r="I51" t="n">
-        <v>0.08171249999999999</v>
+        <v>51.034447</v>
       </c>
       <c r="J51" t="n">
-        <v>0.253108</v>
+        <v>36.921702</v>
+      </c>
+      <c r="K51" t="n">
+        <v>83.705129</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>數位雲端平上市</t>
+          <t>數位雲端右下上櫃</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>117.038726</v>
+        <v>0.288828</v>
       </c>
       <c r="C52" t="n">
-        <v>117.851939</v>
+        <v>0.469014</v>
       </c>
       <c r="D52" t="n">
-        <v>132.340216</v>
+        <v>0.520174</v>
       </c>
       <c r="E52" t="n">
-        <v>83.747483</v>
+        <v>0.23410225</v>
       </c>
       <c r="F52" t="n">
-        <v>60.660386</v>
+        <v>0.316047</v>
       </c>
       <c r="G52" t="n">
-        <v>133.565777</v>
+        <v>0.3032035</v>
       </c>
       <c r="H52" t="n">
-        <v>100.996203</v>
+        <v>0.184877</v>
       </c>
       <c r="I52" t="n">
-        <v>227.704405</v>
+        <v>0.165061</v>
       </c>
       <c r="J52" t="n">
-        <v>62.706548</v>
+        <v>0.3296095</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0.263438</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>數位雲端平上櫃</t>
+          <t>數位雲端平上市</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.118701</v>
+        <v>39.334486</v>
       </c>
       <c r="C53" t="n">
-        <v>0.152504</v>
+        <v>39.982419</v>
       </c>
       <c r="D53" t="n">
-        <v>0.093373</v>
+        <v>53.018351</v>
       </c>
       <c r="E53" t="n">
-        <v>0.074028</v>
+        <v>98.42041399999999</v>
       </c>
       <c r="F53" t="n">
-        <v>0.036497</v>
+        <v>167.665225</v>
       </c>
       <c r="G53" t="n">
-        <v>0.059754</v>
+        <v>250.919163</v>
       </c>
       <c r="H53" t="n">
-        <v>0.07814400000000001</v>
+        <v>325.752664</v>
       </c>
       <c r="I53" t="n">
-        <v>0.02822666666666667</v>
+        <v>232.060711</v>
       </c>
       <c r="J53" t="n">
-        <v>0.03855</v>
+        <v>78.332365</v>
+      </c>
+      <c r="K53" t="n">
+        <v>224.088917</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>文化創意業右上上櫃</t>
+          <t>數位雲端平上櫃</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4.373877</v>
+        <v>0.000869</v>
       </c>
       <c r="C54" t="n">
-        <v>2.718566</v>
+        <v>0.001298</v>
       </c>
       <c r="D54" t="n">
-        <v>1.632479</v>
+        <v>0.001023</v>
       </c>
       <c r="E54" t="n">
-        <v>4.801571</v>
+        <v>0.0008</v>
       </c>
       <c r="F54" t="n">
-        <v>2.438659</v>
+        <v>0.170077</v>
       </c>
       <c r="G54" t="n">
-        <v>1.087361</v>
+        <v>0.182745</v>
       </c>
       <c r="H54" t="n">
-        <v>1.167006</v>
+        <v>0.479193</v>
       </c>
       <c r="I54" t="n">
-        <v>0.468098</v>
+        <v>0.237065</v>
       </c>
       <c r="J54" t="n">
-        <v>0.835421</v>
+        <v>0.001109</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0.891181</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>文化創意業右下上櫃</t>
+          <t>文化創意業右上上櫃</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.0408735</v>
+        <v>0.835421</v>
       </c>
       <c r="C55" t="n">
-        <v>0.06168375</v>
+        <v>1.651831</v>
       </c>
       <c r="D55" t="n">
-        <v>0.073361</v>
+        <v>1.495517</v>
       </c>
       <c r="E55" t="n">
-        <v>0.049902</v>
+        <v>1.981826</v>
       </c>
       <c r="F55" t="n">
-        <v>0.05330483333333334</v>
+        <v>2.493209</v>
       </c>
       <c r="G55" t="n">
-        <v>0.072182</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0.06181725</v>
-      </c>
+        <v>2.770772</v>
+      </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="n">
-        <v>0.077178</v>
+        <v>0.001327</v>
       </c>
       <c r="J55" t="n">
-        <v>0.057784</v>
+        <v>0.000384</v>
+      </c>
+      <c r="K55" t="n">
+        <v>1.014694</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>文化創意業平上櫃</t>
+          <t>文化創意業右下上櫃</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.008586999999999999</v>
+        <v>0.06775100000000001</v>
       </c>
       <c r="C56" t="n">
-        <v>0.003479</v>
+        <v>0.13099975</v>
       </c>
       <c r="D56" t="n">
-        <v>0.001894</v>
+        <v>0.1751533333333334</v>
       </c>
       <c r="E56" t="n">
-        <v>0.011794</v>
+        <v>0.08835850000000001</v>
       </c>
       <c r="F56" t="n">
-        <v>0.004545</v>
-      </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+        <v>0.09723825</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.060699</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.06481525</v>
+      </c>
       <c r="I56" t="n">
-        <v>0.023403</v>
+        <v>0.05732625</v>
       </c>
       <c r="J56" t="n">
-        <v>0.100166</v>
+        <v>0.066925</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0.07106899999999999</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>橡膠工業右上上市</t>
+          <t>文化創意業平上櫃</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>59.31454</v>
+        <v>0.090199</v>
       </c>
       <c r="C57" t="n">
-        <v>91.80184300000001</v>
+        <v>0.000243</v>
       </c>
       <c r="D57" t="n">
-        <v>91.7514</v>
+        <v>0.000547</v>
       </c>
       <c r="E57" t="n">
-        <v>64.15203700000001</v>
+        <v>0.001062</v>
       </c>
       <c r="F57" t="n">
-        <v>159.079605</v>
+        <v>0.040001</v>
       </c>
       <c r="G57" t="n">
-        <v>130.843053</v>
+        <v>0.002196</v>
       </c>
       <c r="H57" t="n">
-        <v>111.431133</v>
+        <v>1.407788</v>
       </c>
       <c r="I57" t="n">
-        <v>256.674547</v>
+        <v>1.261628</v>
       </c>
       <c r="J57" t="n">
-        <v>342.591606</v>
+        <v>0.914431</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0.00028</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>橡膠工業右下上市</t>
+          <t>橡膠工業右上上市</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>116.233975</v>
+        <v>340.685002</v>
       </c>
       <c r="C58" t="n">
-        <v>165.105133</v>
+        <v>409.85475</v>
       </c>
       <c r="D58" t="n">
-        <v>65.736844</v>
+        <v>190.591132</v>
       </c>
       <c r="E58" t="n">
-        <v>172.168685</v>
+        <v>326.506455</v>
       </c>
       <c r="F58" t="n">
-        <v>235.463628</v>
+        <v>256.784831</v>
       </c>
       <c r="G58" t="n">
-        <v>359.573597</v>
+        <v>120.587872</v>
       </c>
       <c r="H58" t="n">
-        <v>137.69556</v>
+        <v>127.325474</v>
       </c>
       <c r="I58" t="n">
-        <v>185.673611</v>
+        <v>98.65007799999999</v>
       </c>
       <c r="J58" t="n">
-        <v>213.587596</v>
+        <v>121.043682</v>
+      </c>
+      <c r="K58" t="n">
+        <v>114.620812</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>橡膠工業平上市</t>
+          <t>橡膠工業右下上市</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>110.326311</v>
+        <v>217.105003</v>
       </c>
       <c r="C59" t="n">
-        <v>67.582936</v>
+        <v>176.797709</v>
       </c>
       <c r="D59" t="n">
-        <v>210.676112</v>
+        <v>217.899501</v>
       </c>
       <c r="E59" t="n">
-        <v>34.688359</v>
+        <v>365.805861</v>
       </c>
       <c r="F59" t="n">
-        <v>20.422541</v>
+        <v>577.052413</v>
       </c>
       <c r="G59" t="n">
-        <v>54.74745</v>
+        <v>95.38098100000001</v>
       </c>
       <c r="H59" t="n">
-        <v>34.823483</v>
+        <v>347.636927</v>
       </c>
       <c r="I59" t="n">
-        <v>31.337197</v>
+        <v>256.729258</v>
       </c>
       <c r="J59" t="n">
-        <v>3.517407</v>
+        <v>206.727109</v>
+      </c>
+      <c r="K59" t="n">
+        <v>193.267517</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>水泥工業右上上市</t>
+          <t>橡膠工業平上市</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>995.089243</v>
+        <v>1.906604</v>
       </c>
       <c r="C60" t="n">
-        <v>796.559063</v>
+        <v>4.559692</v>
       </c>
       <c r="D60" t="n">
-        <v>2967.114292</v>
+        <v>3.426164</v>
       </c>
       <c r="E60" t="n">
-        <v>1412.587301</v>
+        <v>1.569808</v>
       </c>
       <c r="F60" t="n">
-        <v>641.982484</v>
+        <v>1.16153</v>
       </c>
       <c r="G60" t="n">
-        <v>900.0369920000001</v>
-      </c>
-      <c r="H60" t="n">
-        <v>674.559882</v>
-      </c>
+        <v>445.658223</v>
+      </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
-        <v>837.741159</v>
-      </c>
-      <c r="J60" t="n">
-        <v>1241.194317</v>
-      </c>
+        <v>1.439041</v>
+      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>水泥工業右下上市</t>
+          <t>水泥工業右上上市</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>23.890866</v>
+        <v>851.041282</v>
       </c>
       <c r="C61" t="n">
-        <v>36.108083</v>
+        <v>3440.262713</v>
       </c>
       <c r="D61" t="n">
-        <v>25.533089</v>
+        <v>1459.107193</v>
       </c>
       <c r="E61" t="n">
-        <v>24.011971</v>
+        <v>2191.943596</v>
       </c>
       <c r="F61" t="n">
-        <v>17.212754</v>
+        <v>1131.441578</v>
       </c>
       <c r="G61" t="n">
-        <v>19.640078</v>
+        <v>1574.086796</v>
       </c>
       <c r="H61" t="n">
-        <v>20.295194</v>
+        <v>804.543034</v>
       </c>
       <c r="I61" t="n">
-        <v>18.918191</v>
+        <v>894.802743</v>
       </c>
       <c r="J61" t="n">
-        <v>14.150035</v>
+        <v>799.8201350000001</v>
+      </c>
+      <c r="K61" t="n">
+        <v>3345.855402</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>水泥工業平上市</t>
+          <t>水泥工業右下上市</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>265.593417</v>
+        <v>14.150035</v>
       </c>
       <c r="C62" t="n">
-        <v>339.290351</v>
-      </c>
-      <c r="D62" t="inlineStr"/>
+        <v>25.917989</v>
+      </c>
+      <c r="D62" t="n">
+        <v>30.703446</v>
+      </c>
       <c r="E62" t="n">
-        <v>420.783956</v>
+        <v>21.030979</v>
       </c>
       <c r="F62" t="n">
-        <v>174.267952</v>
+        <v>29.200467</v>
       </c>
       <c r="G62" t="n">
-        <v>181.634068</v>
+        <v>21.43664</v>
       </c>
       <c r="H62" t="n">
-        <v>245.309947</v>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
+        <v>26.94314</v>
+      </c>
+      <c r="I62" t="n">
+        <v>17.410946</v>
+      </c>
+      <c r="J62" t="n">
+        <v>17.89129</v>
+      </c>
+      <c r="K62" t="n">
+        <v>16.365514</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>汽車工業右上上市</t>
+          <t>水泥工業平上市</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>835.009685</v>
+        <v>390.153035</v>
       </c>
       <c r="C63" t="n">
-        <v>1376.904598</v>
+        <v>212.902267</v>
       </c>
       <c r="D63" t="n">
-        <v>2530.817868</v>
+        <v>292.80074</v>
       </c>
       <c r="E63" t="n">
-        <v>894.608758</v>
+        <v>263.684776</v>
       </c>
       <c r="F63" t="n">
-        <v>1258.292474</v>
+        <v>507.826902</v>
       </c>
       <c r="G63" t="n">
-        <v>2023.334911</v>
+        <v>310.82796</v>
       </c>
       <c r="H63" t="n">
-        <v>2376.922796</v>
+        <v>274.869932</v>
       </c>
       <c r="I63" t="n">
-        <v>2425.893933</v>
+        <v>290.659288</v>
       </c>
       <c r="J63" t="n">
-        <v>2445.453189</v>
+        <v>164.303141</v>
+      </c>
+      <c r="K63" t="n">
+        <v>14.864183</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>汽車工業右下上市</t>
+          <t>汽車工業右上上市</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>270.273582</v>
+        <v>2426.643378</v>
       </c>
       <c r="C64" t="n">
-        <v>464.299762</v>
+        <v>1540.818611</v>
       </c>
       <c r="D64" t="n">
-        <v>412.71605</v>
+        <v>1935.242207</v>
       </c>
       <c r="E64" t="n">
-        <v>323.712412</v>
+        <v>1557.773388</v>
       </c>
       <c r="F64" t="n">
-        <v>374.118405</v>
+        <v>1244.79658</v>
       </c>
       <c r="G64" t="n">
-        <v>620.992344</v>
+        <v>1001.21699</v>
       </c>
       <c r="H64" t="n">
-        <v>714.964128</v>
+        <v>859.27977</v>
       </c>
       <c r="I64" t="n">
-        <v>731.875396</v>
+        <v>1130.074831</v>
       </c>
       <c r="J64" t="n">
-        <v>407.045715</v>
+        <v>773.779114</v>
+      </c>
+      <c r="K64" t="n">
+        <v>771.234021</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>汽車工業平上市</t>
+          <t>汽車工業右下上市</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>375.02301</v>
+        <v>570.641566</v>
       </c>
       <c r="C65" t="n">
-        <v>198.14848</v>
+        <v>542.7140900000001</v>
       </c>
       <c r="D65" t="n">
-        <v>284.679117</v>
+        <v>1446.864378</v>
       </c>
       <c r="E65" t="n">
-        <v>244.890534</v>
+        <v>455.494981</v>
       </c>
       <c r="F65" t="n">
-        <v>395.022358</v>
+        <v>787.909998</v>
       </c>
       <c r="G65" t="n">
-        <v>183.768815</v>
+        <v>631.922905</v>
       </c>
       <c r="H65" t="n">
-        <v>116.196973</v>
+        <v>519.952883</v>
       </c>
       <c r="I65" t="n">
-        <v>278.059598</v>
+        <v>373.690509</v>
       </c>
       <c r="J65" t="n">
-        <v>175.608212</v>
+        <v>520.635439</v>
+      </c>
+      <c r="K65" t="n">
+        <v>560.9419685</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業右上上市</t>
+          <t>汽車工業平上市</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1016.909933</v>
+        <v>30.822172</v>
       </c>
       <c r="C66" t="n">
-        <v>3827.737724</v>
+        <v>120.44585</v>
       </c>
       <c r="D66" t="n">
-        <v>3768.070051</v>
+        <v>206.870462</v>
       </c>
       <c r="E66" t="n">
-        <v>2657.525003</v>
+        <v>231.283392</v>
       </c>
       <c r="F66" t="n">
-        <v>3632.530573</v>
+        <v>229.226956</v>
       </c>
       <c r="G66" t="n">
-        <v>2115.763698</v>
+        <v>213.05279</v>
       </c>
       <c r="H66" t="n">
-        <v>2490.682467</v>
+        <v>66.733133</v>
       </c>
       <c r="I66" t="n">
-        <v>3811.980424</v>
+        <v>136.075142</v>
       </c>
       <c r="J66" t="n">
-        <v>4743.536751</v>
+        <v>110.807762</v>
+      </c>
+      <c r="K66" t="n">
+        <v>105.866611</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業右下上市</t>
+          <t>油電燃氣業右上上市</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>4.464252</v>
+        <v>4743.682442</v>
       </c>
       <c r="C67" t="n">
-        <v>6.8068</v>
+        <v>4671.907708</v>
       </c>
       <c r="D67" t="n">
-        <v>5.852749</v>
+        <v>8215.694162</v>
       </c>
       <c r="E67" t="n">
-        <v>3.578119</v>
+        <v>17337.946637</v>
       </c>
       <c r="F67" t="n">
-        <v>6.830817</v>
+        <v>6750.49278</v>
       </c>
       <c r="G67" t="n">
-        <v>6.653482</v>
+        <v>6032.672945</v>
       </c>
       <c r="H67" t="n">
-        <v>13.578305</v>
+        <v>9123.656804</v>
       </c>
       <c r="I67" t="n">
-        <v>7.965361</v>
+        <v>5948.821357</v>
       </c>
       <c r="J67" t="n">
-        <v>6.502614</v>
+        <v>4361.375109</v>
+      </c>
+      <c r="K67" t="n">
+        <v>3988.662239</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業右下上櫃</t>
+          <t>油電燃氣業右下上市</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.003165</v>
+        <v>5.855854</v>
       </c>
       <c r="C68" t="n">
-        <v>0.003294</v>
+        <v>6.94692</v>
       </c>
       <c r="D68" t="n">
-        <v>0.002846</v>
+        <v>7.921055</v>
       </c>
       <c r="E68" t="n">
-        <v>0.00394</v>
+        <v>5.661461</v>
       </c>
       <c r="F68" t="n">
-        <v>0.0022</v>
+        <v>9.086698</v>
       </c>
       <c r="G68" t="n">
-        <v>0.007126</v>
+        <v>6.074252</v>
       </c>
       <c r="H68" t="n">
-        <v>0.005304</v>
+        <v>7.701942</v>
       </c>
       <c r="I68" t="n">
-        <v>0.005177</v>
+        <v>9.683154</v>
       </c>
       <c r="J68" t="n">
-        <v>0.007192</v>
+        <v>7.176474</v>
+      </c>
+      <c r="K68" t="n">
+        <v>8.333875000000001</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業平上市</t>
+          <t>油電燃氣業右下上櫃</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.416998</v>
+        <v>0.004674</v>
       </c>
       <c r="C69" t="n">
-        <v>75.293695</v>
+        <v>0.00381</v>
       </c>
       <c r="D69" t="n">
-        <v>1.0206</v>
+        <v>0.005626</v>
       </c>
       <c r="E69" t="n">
-        <v>0.687299</v>
+        <v>0.008741000000000001</v>
       </c>
       <c r="F69" t="n">
-        <v>0.993817</v>
+        <v>0.005453</v>
       </c>
       <c r="G69" t="n">
-        <v>0.704952</v>
+        <v>0.0043975</v>
       </c>
       <c r="H69" t="n">
-        <v>3.028703</v>
+        <v>0.008373</v>
       </c>
       <c r="I69" t="n">
-        <v>1.353585</v>
+        <v>0.008206</v>
       </c>
       <c r="J69" t="n">
-        <v>0.145691</v>
+        <v>0.004415</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0.004137</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>油電燃氣業平上櫃</t>
+          <t>油電燃氣業平上市</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.012791</v>
+        <v>0.64676</v>
       </c>
       <c r="C70" t="n">
-        <v>0.003837</v>
+        <v>0.9210660000000001</v>
       </c>
       <c r="D70" t="n">
-        <v>0.010741</v>
+        <v>0.345815</v>
       </c>
       <c r="E70" t="n">
-        <v>0.000701</v>
+        <v>0.257067</v>
       </c>
       <c r="F70" t="n">
-        <v>0.000886</v>
+        <v>1.652656</v>
       </c>
       <c r="G70" t="n">
-        <v>5.9e-05</v>
+        <v>0.548177</v>
       </c>
       <c r="H70" t="n">
-        <v>0.012012</v>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
+        <v>0.693272</v>
+      </c>
+      <c r="I70" t="n">
+        <v>1.371864</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.911798</v>
+      </c>
+      <c r="K70" t="n">
+        <v>1.43441</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
@@ -2803,31 +3009,34 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>336.767867</v>
+        <v>10429.506015</v>
       </c>
       <c r="C71" t="n">
-        <v>1394.507219</v>
+        <v>6504.096007</v>
       </c>
       <c r="D71" t="n">
-        <v>980.572891</v>
+        <v>2926.049538</v>
       </c>
       <c r="E71" t="n">
-        <v>297.549161</v>
+        <v>12613.655741</v>
       </c>
       <c r="F71" t="n">
-        <v>572.510755</v>
+        <v>5292.823429</v>
       </c>
       <c r="G71" t="n">
-        <v>255.941381</v>
+        <v>9590.965711000001</v>
       </c>
       <c r="H71" t="n">
-        <v>148.635317</v>
+        <v>14522.891958</v>
       </c>
       <c r="I71" t="n">
-        <v>7135.401026</v>
+        <v>14761.244176</v>
       </c>
       <c r="J71" t="n">
-        <v>10430.466674</v>
+        <v>10579.17522</v>
+      </c>
+      <c r="K71" t="n">
+        <v>19617.035707</v>
       </c>
     </row>
     <row r="72">
@@ -2837,31 +3046,34 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.521244</v>
+        <v>1.373989</v>
       </c>
       <c r="C72" t="n">
-        <v>0.500364</v>
+        <v>0.730162</v>
       </c>
       <c r="D72" t="n">
-        <v>1.209878</v>
+        <v>0.593838</v>
       </c>
       <c r="E72" t="n">
-        <v>2.726514</v>
+        <v>1.36128</v>
       </c>
       <c r="F72" t="n">
-        <v>0.8914299999999999</v>
+        <v>1.613938</v>
       </c>
       <c r="G72" t="n">
-        <v>1.117833</v>
+        <v>1.940996</v>
       </c>
       <c r="H72" t="n">
-        <v>2.289033</v>
+        <v>1.564369</v>
       </c>
       <c r="I72" t="n">
-        <v>2.318782</v>
+        <v>2.889618</v>
       </c>
       <c r="J72" t="n">
-        <v>1.373989</v>
+        <v>1.366585</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0.917232</v>
       </c>
     </row>
     <row r="73">
@@ -2871,28 +3083,35 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>464.349189</v>
+        <v>0.960659</v>
       </c>
       <c r="C73" t="n">
-        <v>460.082038</v>
+        <v>1.418611</v>
       </c>
       <c r="D73" t="n">
-        <v>1411.506215</v>
+        <v>1.087056</v>
       </c>
       <c r="E73" t="n">
-        <v>913.096038</v>
+        <v>0.997908</v>
       </c>
       <c r="F73" t="n">
-        <v>716.628303</v>
+        <v>1.290888</v>
       </c>
       <c r="G73" t="n">
-        <v>1391.651459</v>
+        <v>0.199999</v>
       </c>
       <c r="H73" t="n">
-        <v>1434.343204</v>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
+        <v>0.625051</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.754844</v>
+      </c>
+      <c r="J73" t="n">
+        <v>1.74787</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0.605754</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
@@ -2901,31 +3120,34 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>4088.387545</v>
+        <v>3190.48216</v>
       </c>
       <c r="C74" t="n">
-        <v>3867.64655</v>
+        <v>2261.789606</v>
       </c>
       <c r="D74" t="n">
-        <v>4196.073425</v>
+        <v>2069.752334</v>
       </c>
       <c r="E74" t="n">
-        <v>6374.150305</v>
+        <v>1920.469622</v>
       </c>
       <c r="F74" t="n">
-        <v>2873.532273</v>
+        <v>5166.152157</v>
       </c>
       <c r="G74" t="n">
-        <v>3358.834664</v>
+        <v>5234.524655</v>
       </c>
       <c r="H74" t="n">
-        <v>3005.278808</v>
+        <v>3678.540566</v>
       </c>
       <c r="I74" t="n">
-        <v>3002.379064</v>
+        <v>2748.894623</v>
       </c>
       <c r="J74" t="n">
-        <v>3214.573675</v>
+        <v>2934.638464</v>
+      </c>
+      <c r="K74" t="n">
+        <v>2238.815385</v>
       </c>
     </row>
     <row r="75">
@@ -2935,31 +3157,34 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.796296</v>
+        <v>1.094319</v>
       </c>
       <c r="C75" t="n">
-        <v>0.814196</v>
+        <v>1.20142</v>
       </c>
       <c r="D75" t="n">
-        <v>1.607912</v>
+        <v>0.925351</v>
       </c>
       <c r="E75" t="n">
-        <v>1.910936</v>
+        <v>0.903649</v>
       </c>
       <c r="F75" t="n">
-        <v>1.355821</v>
+        <v>1.461627</v>
       </c>
       <c r="G75" t="n">
-        <v>1.149426</v>
+        <v>1.342721</v>
       </c>
       <c r="H75" t="n">
-        <v>1.307722</v>
+        <v>1.05523375</v>
       </c>
       <c r="I75" t="n">
-        <v>1.194648</v>
+        <v>0.7004629999999999</v>
       </c>
       <c r="J75" t="n">
-        <v>1.118477</v>
+        <v>0.4989105</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0.84087425</v>
       </c>
     </row>
     <row r="76">
@@ -2969,31 +3194,34 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>882.589772</v>
+        <v>912.773399</v>
       </c>
       <c r="C76" t="n">
-        <v>831.72542</v>
+        <v>989.217021</v>
       </c>
       <c r="D76" t="n">
-        <v>987.591167</v>
+        <v>1409.015519</v>
       </c>
       <c r="E76" t="n">
-        <v>570.880037</v>
+        <v>1305.899836</v>
       </c>
       <c r="F76" t="n">
-        <v>1361.174952</v>
+        <v>1353.186506</v>
       </c>
       <c r="G76" t="n">
-        <v>948.955914</v>
+        <v>915.494014</v>
       </c>
       <c r="H76" t="n">
-        <v>783.46231</v>
+        <v>1086.809912</v>
       </c>
       <c r="I76" t="n">
-        <v>732.128429</v>
+        <v>804.787636</v>
       </c>
       <c r="J76" t="n">
-        <v>838.967899</v>
+        <v>1135.632125</v>
+      </c>
+      <c r="K76" t="n">
+        <v>825.077547</v>
       </c>
     </row>
     <row r="77">
@@ -3003,31 +3231,34 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.3164330833333333</v>
+        <v>0.5777460833333333</v>
       </c>
       <c r="C77" t="n">
-        <v>0.3441363333333333</v>
+        <v>0.60334775</v>
       </c>
       <c r="D77" t="n">
-        <v>0.3782826666666667</v>
+        <v>0.612161</v>
       </c>
       <c r="E77" t="n">
-        <v>0.3214551666666667</v>
+        <v>0.35998</v>
       </c>
       <c r="F77" t="n">
-        <v>0.3575395</v>
+        <v>0.632834</v>
       </c>
       <c r="G77" t="n">
-        <v>0.7056954166666666</v>
+        <v>0.61683075</v>
       </c>
       <c r="H77" t="n">
-        <v>0.512689</v>
+        <v>0.4672313333333333</v>
       </c>
       <c r="I77" t="n">
-        <v>0.4181756666666667</v>
+        <v>0.30532175</v>
       </c>
       <c r="J77" t="n">
-        <v>0.6329100833333333</v>
+        <v>0.312439</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0.400125</v>
       </c>
     </row>
     <row r="78">
@@ -3037,31 +3268,34 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>95.000366</v>
+        <v>46.516881</v>
       </c>
       <c r="C78" t="n">
-        <v>121.884585</v>
+        <v>472.4874</v>
       </c>
       <c r="D78" t="n">
-        <v>149.655613</v>
+        <v>710.873299</v>
       </c>
       <c r="E78" t="n">
-        <v>393.7089</v>
+        <v>230.843733</v>
       </c>
       <c r="F78" t="n">
-        <v>129.548609</v>
+        <v>468.304146</v>
       </c>
       <c r="G78" t="n">
-        <v>84.137075</v>
+        <v>243.10656</v>
       </c>
       <c r="H78" t="n">
-        <v>63.975701</v>
+        <v>254.632793</v>
       </c>
       <c r="I78" t="n">
-        <v>302.440094</v>
+        <v>182.406695</v>
       </c>
       <c r="J78" t="n">
-        <v>96.23086600000001</v>
+        <v>150.674331</v>
+      </c>
+      <c r="K78" t="n">
+        <v>155.330988</v>
       </c>
     </row>
     <row r="79">
@@ -3071,31 +3305,34 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.1738</v>
+        <v>0.111324</v>
       </c>
       <c r="C79" t="n">
-        <v>0.06646000000000001</v>
+        <v>0.04212</v>
       </c>
       <c r="D79" t="n">
-        <v>0.181862</v>
+        <v>0.112595</v>
       </c>
       <c r="E79" t="n">
-        <v>0.126775</v>
+        <v>0.050569</v>
       </c>
       <c r="F79" t="n">
-        <v>0.097179</v>
+        <v>0.08527</v>
       </c>
       <c r="G79" t="n">
-        <v>0.148083</v>
+        <v>0.060649</v>
       </c>
       <c r="H79" t="n">
-        <v>0.09477774999999999</v>
+        <v>0.098855</v>
       </c>
       <c r="I79" t="n">
-        <v>0.02344733333333334</v>
+        <v>0.06333800000000001</v>
       </c>
       <c r="J79" t="n">
-        <v>0.032002</v>
+        <v>0.08888699999999999</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0.035027</v>
       </c>
     </row>
     <row r="80">
@@ -3105,31 +3342,34 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>292.472929</v>
+        <v>931.901439</v>
       </c>
       <c r="C80" t="n">
-        <v>185.653581</v>
+        <v>597.561423</v>
       </c>
       <c r="D80" t="n">
-        <v>680.52637</v>
+        <v>527.572399</v>
       </c>
       <c r="E80" t="n">
-        <v>253.387223</v>
+        <v>2294.561808</v>
       </c>
       <c r="F80" t="n">
-        <v>522.9243310000001</v>
+        <v>1345.254825</v>
       </c>
       <c r="G80" t="n">
-        <v>698.51841</v>
+        <v>608.9787894999999</v>
       </c>
       <c r="H80" t="n">
-        <v>474.371744</v>
+        <v>295.797683</v>
       </c>
       <c r="I80" t="n">
-        <v>1814.314575</v>
+        <v>248.637091</v>
       </c>
       <c r="J80" t="n">
-        <v>1050.98659</v>
+        <v>191.868858</v>
+      </c>
+      <c r="K80" t="n">
+        <v>212.699101</v>
       </c>
     </row>
     <row r="81">
@@ -3139,31 +3379,34 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.003562</v>
+        <v>0.002726</v>
       </c>
       <c r="C81" t="n">
-        <v>0.002342</v>
+        <v>0.002507</v>
       </c>
       <c r="D81" t="n">
-        <v>0.003026</v>
+        <v>0.001812</v>
       </c>
       <c r="E81" t="n">
-        <v>0.000842</v>
+        <v>0.002089</v>
       </c>
       <c r="F81" t="n">
-        <v>0.001892</v>
+        <v>0.002773</v>
       </c>
       <c r="G81" t="n">
-        <v>0.001417</v>
+        <v>0.003866</v>
       </c>
       <c r="H81" t="n">
-        <v>0.003551</v>
+        <v>0.002113</v>
       </c>
       <c r="I81" t="n">
-        <v>0.002177</v>
+        <v>0.002928</v>
       </c>
       <c r="J81" t="n">
-        <v>0.002726</v>
+        <v>0.002257</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0.004953</v>
       </c>
     </row>
     <row r="82">
@@ -3173,31 +3416,34 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>559.467184</v>
+        <v>1645.574401</v>
       </c>
       <c r="C82" t="n">
-        <v>497.35158</v>
+        <v>1060.785575</v>
       </c>
       <c r="D82" t="n">
-        <v>690.9260829999999</v>
+        <v>788.708321</v>
       </c>
       <c r="E82" t="n">
-        <v>429.938206</v>
+        <v>729.383301</v>
       </c>
       <c r="F82" t="n">
-        <v>409.600498</v>
+        <v>1546.280262</v>
       </c>
       <c r="G82" t="n">
-        <v>925.605107</v>
+        <v>1017.26617</v>
       </c>
       <c r="H82" t="n">
-        <v>1353.881129</v>
+        <v>567.45573</v>
       </c>
       <c r="I82" t="n">
-        <v>1441.814826</v>
+        <v>703.43878</v>
       </c>
       <c r="J82" t="n">
-        <v>1645.888639</v>
+        <v>544.980269</v>
+      </c>
+      <c r="K82" t="n">
+        <v>524.011943</v>
       </c>
     </row>
     <row r="83">
@@ -3207,31 +3453,34 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.003866</v>
+        <v>0.003897</v>
       </c>
       <c r="C83" t="n">
-        <v>0.002449</v>
+        <v>0.005206</v>
       </c>
       <c r="D83" t="n">
-        <v>0.005551</v>
+        <v>0.004338</v>
       </c>
       <c r="E83" t="n">
-        <v>0.003023</v>
+        <v>0.004179</v>
       </c>
       <c r="F83" t="n">
-        <v>0.002772</v>
+        <v>0.005595</v>
       </c>
       <c r="G83" t="n">
-        <v>0.004978</v>
+        <v>0.004067</v>
       </c>
       <c r="H83" t="n">
-        <v>0.006434</v>
+        <v>0.00165</v>
       </c>
       <c r="I83" t="n">
-        <v>0.003073</v>
+        <v>0.004333</v>
       </c>
       <c r="J83" t="n">
-        <v>0.004224</v>
+        <v>0.003745</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0.004421</v>
       </c>
     </row>
     <row r="84">
@@ -3241,31 +3490,34 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>89.492357</v>
+        <v>130.480298</v>
       </c>
       <c r="C84" t="n">
-        <v>225.18276</v>
+        <v>286.14389</v>
       </c>
       <c r="D84" t="n">
-        <v>15.404155</v>
+        <v>142.265332</v>
       </c>
       <c r="E84" t="n">
-        <v>464.799887</v>
+        <v>2.956679</v>
       </c>
       <c r="F84" t="n">
-        <v>41.503846</v>
+        <v>27.262329</v>
       </c>
       <c r="G84" t="n">
-        <v>244.633057</v>
+        <v>13.30453</v>
       </c>
       <c r="H84" t="n">
-        <v>160.028175</v>
+        <v>208.289501</v>
       </c>
       <c r="I84" t="n">
-        <v>47.701511</v>
+        <v>195.224665</v>
       </c>
       <c r="J84" t="n">
-        <v>11.080909</v>
+        <v>138.419356</v>
+      </c>
+      <c r="K84" t="n">
+        <v>222.888126</v>
       </c>
     </row>
     <row r="85">
@@ -3275,31 +3527,34 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.001247</v>
+        <v>0.001738</v>
       </c>
       <c r="C85" t="n">
-        <v>0.002145</v>
+        <v>0.01827</v>
       </c>
       <c r="D85" t="n">
-        <v>0.003993</v>
+        <v>0.025966</v>
       </c>
       <c r="E85" t="n">
-        <v>0.001704</v>
+        <v>0.002587</v>
       </c>
       <c r="F85" t="n">
-        <v>0.001875</v>
+        <v>0.001754</v>
       </c>
       <c r="G85" t="n">
-        <v>0.004246</v>
+        <v>0.002481</v>
       </c>
       <c r="H85" t="n">
-        <v>0.0024</v>
+        <v>0.00147</v>
       </c>
       <c r="I85" t="n">
-        <v>0.014064</v>
+        <v>0.000663</v>
       </c>
       <c r="J85" t="n">
-        <v>0.001411</v>
+        <v>0.001107</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0.003034</v>
       </c>
     </row>
     <row r="86">
@@ -3309,31 +3564,34 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>987.254875</v>
+        <v>2522.789547</v>
       </c>
       <c r="C86" t="n">
-        <v>1065.228574</v>
+        <v>1771.625518</v>
       </c>
       <c r="D86" t="n">
-        <v>1461.418548</v>
+        <v>1942.64528</v>
       </c>
       <c r="E86" t="n">
-        <v>1090.069752</v>
+        <v>989.842979</v>
       </c>
       <c r="F86" t="n">
-        <v>1296.447198</v>
+        <v>2046.733668</v>
       </c>
       <c r="G86" t="n">
-        <v>2458.697829</v>
+        <v>1276.134651</v>
       </c>
       <c r="H86" t="n">
-        <v>1089.254445</v>
+        <v>1051.752425</v>
       </c>
       <c r="I86" t="n">
-        <v>3645.680742</v>
+        <v>618.413716</v>
       </c>
       <c r="J86" t="n">
-        <v>2522.789547</v>
+        <v>634.992787</v>
+      </c>
+      <c r="K86" t="n">
+        <v>720.727899</v>
       </c>
     </row>
     <row r="87">
@@ -3343,31 +3601,34 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.08933199999999999</v>
+        <v>0.240485</v>
       </c>
       <c r="C87" t="n">
-        <v>0.031627</v>
+        <v>0.404338</v>
       </c>
       <c r="D87" t="n">
-        <v>0.034733</v>
+        <v>0.241715</v>
       </c>
       <c r="E87" t="n">
-        <v>0.06268700000000001</v>
+        <v>0.427297</v>
       </c>
       <c r="F87" t="n">
-        <v>0.668552</v>
+        <v>0.265565</v>
       </c>
       <c r="G87" t="n">
-        <v>0.483589</v>
+        <v>0.162309</v>
       </c>
       <c r="H87" t="n">
-        <v>0.361396</v>
+        <v>0.097995</v>
       </c>
       <c r="I87" t="n">
-        <v>0.4501</v>
+        <v>0.210654</v>
       </c>
       <c r="J87" t="n">
-        <v>0.240485</v>
+        <v>0.340931</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0.169087</v>
       </c>
     </row>
     <row r="88">
@@ -3377,31 +3638,34 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>278.616048</v>
+        <v>280.293823</v>
       </c>
       <c r="C88" t="n">
-        <v>274.468824</v>
+        <v>419.955127</v>
       </c>
       <c r="D88" t="n">
-        <v>246.334542</v>
+        <v>346.311045</v>
       </c>
       <c r="E88" t="n">
-        <v>273.107014</v>
+        <v>243.104347</v>
       </c>
       <c r="F88" t="n">
-        <v>308.175048</v>
+        <v>409.612579</v>
       </c>
       <c r="G88" t="n">
-        <v>514.506952</v>
+        <v>259.245057</v>
       </c>
       <c r="H88" t="n">
-        <v>314.34913</v>
+        <v>670.640525</v>
       </c>
       <c r="I88" t="n">
-        <v>273.137988</v>
+        <v>435.219971</v>
       </c>
       <c r="J88" t="n">
-        <v>276.479222</v>
+        <v>345.353824</v>
+      </c>
+      <c r="K88" t="n">
+        <v>482.492748</v>
       </c>
     </row>
     <row r="89">
@@ -3411,31 +3675,34 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.114534</v>
+        <v>0.03328925</v>
       </c>
       <c r="C89" t="n">
-        <v>0.06042566666666667</v>
+        <v>0.044408</v>
       </c>
       <c r="D89" t="n">
-        <v>0.040755</v>
+        <v>0.041502</v>
       </c>
       <c r="E89" t="n">
-        <v>0.03678</v>
+        <v>0.025163</v>
       </c>
       <c r="F89" t="n">
-        <v>0.041197</v>
+        <v>0.059544</v>
       </c>
       <c r="G89" t="n">
-        <v>0.112541</v>
+        <v>0.02936425</v>
       </c>
       <c r="H89" t="n">
-        <v>0.09009399999999999</v>
+        <v>0.030471</v>
       </c>
       <c r="I89" t="n">
-        <v>0.070425</v>
+        <v>0.022361</v>
       </c>
       <c r="J89" t="n">
-        <v>0.06356924999999999</v>
+        <v>0.02103</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0.025786</v>
       </c>
     </row>
     <row r="90">
@@ -3445,31 +3712,34 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>456.031398</v>
+        <v>11.01956</v>
       </c>
       <c r="C90" t="n">
-        <v>544.36019</v>
+        <v>16.720189</v>
       </c>
       <c r="D90" t="n">
-        <v>411.932598</v>
+        <v>27.391598</v>
       </c>
       <c r="E90" t="n">
-        <v>545.813419</v>
+        <v>13.047469</v>
       </c>
       <c r="F90" t="n">
-        <v>390.621942</v>
+        <v>19.279893</v>
       </c>
       <c r="G90" t="n">
-        <v>514.185082</v>
+        <v>10.540074</v>
       </c>
       <c r="H90" t="n">
-        <v>441.689948</v>
+        <v>23.53453</v>
       </c>
       <c r="I90" t="n">
-        <v>14.428219</v>
+        <v>190.558933</v>
       </c>
       <c r="J90" t="n">
-        <v>14.834161</v>
+        <v>20.400783</v>
+      </c>
+      <c r="K90" t="n">
+        <v>205.505945</v>
       </c>
     </row>
     <row r="91">
@@ -3479,31 +3749,34 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.000392</v>
+        <v>0.030791</v>
       </c>
       <c r="C91" t="n">
-        <v>0.179047</v>
+        <v>0.001162</v>
       </c>
       <c r="D91" t="n">
-        <v>0.177882</v>
+        <v>0.028388</v>
       </c>
       <c r="E91" t="n">
-        <v>0.215974</v>
+        <v>0.011932</v>
       </c>
       <c r="F91" t="n">
-        <v>0.001</v>
+        <v>0.031456</v>
       </c>
       <c r="G91" t="n">
-        <v>0.001579</v>
+        <v>0.077955</v>
       </c>
       <c r="H91" t="n">
-        <v>1e-05</v>
+        <v>0.09163300000000001</v>
       </c>
       <c r="I91" t="n">
-        <v>0.000605</v>
+        <v>0.061321</v>
       </c>
       <c r="J91" t="n">
-        <v>0.000511</v>
+        <v>0.048884</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0.08021399999999999</v>
       </c>
     </row>
     <row r="92">
@@ -3513,31 +3786,34 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>4550.993342</v>
+        <v>3846.12291</v>
       </c>
       <c r="C92" t="n">
-        <v>6235.148024</v>
+        <v>26414.590776</v>
       </c>
       <c r="D92" t="n">
-        <v>5045.109869</v>
+        <v>27550.622289</v>
       </c>
       <c r="E92" t="n">
-        <v>4288.824517</v>
+        <v>15617.149245</v>
       </c>
       <c r="F92" t="n">
-        <v>4613.845504</v>
+        <v>10543.385209</v>
       </c>
       <c r="G92" t="n">
-        <v>5575.912177</v>
+        <v>11486.848972</v>
       </c>
       <c r="H92" t="n">
-        <v>4810.449258</v>
+        <v>7024.241639</v>
       </c>
       <c r="I92" t="n">
-        <v>4540.463065</v>
+        <v>5990.20021</v>
       </c>
       <c r="J92" t="n">
-        <v>3709.174479</v>
+        <v>6626.258885</v>
+      </c>
+      <c r="K92" t="n">
+        <v>5855.753238</v>
       </c>
     </row>
     <row r="93">
@@ -3547,31 +3823,34 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>223.085712</v>
+        <v>231.373712</v>
       </c>
       <c r="C93" t="n">
-        <v>319.29705</v>
+        <v>305.095399</v>
       </c>
       <c r="D93" t="n">
-        <v>272.893445</v>
+        <v>322.839717</v>
       </c>
       <c r="E93" t="n">
-        <v>227.609198</v>
+        <v>251.972746</v>
       </c>
       <c r="F93" t="n">
-        <v>252.512685</v>
+        <v>428.272493</v>
       </c>
       <c r="G93" t="n">
-        <v>366.233668</v>
+        <v>381.294679</v>
       </c>
       <c r="H93" t="n">
-        <v>309.11194</v>
+        <v>333.717318</v>
       </c>
       <c r="I93" t="n">
-        <v>207.834935</v>
+        <v>285.267483</v>
       </c>
       <c r="J93" t="n">
-        <v>263.86298</v>
+        <v>272.056872</v>
+      </c>
+      <c r="K93" t="n">
+        <v>324.828823</v>
       </c>
     </row>
     <row r="94">
@@ -3581,31 +3860,34 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.015171</v>
+        <v>0.013256</v>
       </c>
       <c r="C94" t="n">
-        <v>0.027518</v>
+        <v>0.0430005</v>
       </c>
       <c r="D94" t="n">
-        <v>0.031577</v>
+        <v>0.027128</v>
       </c>
       <c r="E94" t="n">
-        <v>0.018536</v>
+        <v>0.018892</v>
       </c>
       <c r="F94" t="n">
-        <v>0.021268</v>
+        <v>0.026711</v>
       </c>
       <c r="G94" t="n">
-        <v>0.0430535</v>
+        <v>0.013497</v>
       </c>
       <c r="H94" t="n">
-        <v>0.043256</v>
+        <v>0.02439075</v>
       </c>
       <c r="I94" t="n">
-        <v>0.01764933333333333</v>
+        <v>0.017441</v>
       </c>
       <c r="J94" t="n">
-        <v>0.013256</v>
+        <v>0.0139595</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0.013798</v>
       </c>
     </row>
     <row r="95">
@@ -3615,31 +3897,34 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>692.5978699999999</v>
+        <v>1316.93016</v>
       </c>
       <c r="C95" t="n">
-        <v>291.581164</v>
+        <v>607.436062</v>
       </c>
       <c r="D95" t="n">
-        <v>526.1090380000001</v>
+        <v>456.993702</v>
       </c>
       <c r="E95" t="n">
-        <v>397.091163</v>
+        <v>414.442603</v>
       </c>
       <c r="F95" t="n">
-        <v>293.732243</v>
+        <v>504.812143</v>
       </c>
       <c r="G95" t="n">
-        <v>528.0670229999999</v>
+        <v>1053.949158</v>
       </c>
       <c r="H95" t="n">
-        <v>341.479453</v>
+        <v>429.448187</v>
       </c>
       <c r="I95" t="n">
-        <v>347.413606</v>
+        <v>405.79081</v>
       </c>
       <c r="J95" t="n">
-        <v>342.991155</v>
+        <v>336.288928</v>
+      </c>
+      <c r="K95" t="n">
+        <v>316.722726</v>
       </c>
     </row>
     <row r="96">
@@ -3648,18 +3933,35 @@
           <t>航運業平上櫃</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr"/>
-      <c r="C96" t="inlineStr"/>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
+      <c r="B96" t="n">
+        <v>0.013006</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0.020498</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0.010843</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0.014403</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0.013613</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0.011385</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0.008755000000000001</v>
+      </c>
       <c r="I96" t="n">
-        <v>0.01569</v>
+        <v>0.005496</v>
       </c>
       <c r="J96" t="n">
-        <v>0.013006</v>
+        <v>0.009808000000000001</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0.009979999999999999</v>
       </c>
     </row>
     <row r="97">
@@ -3669,31 +3971,34 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>135.017384</v>
+        <v>124.568896</v>
       </c>
       <c r="C97" t="n">
-        <v>139.47937</v>
+        <v>192.598552</v>
       </c>
       <c r="D97" t="n">
-        <v>81.415419</v>
+        <v>161.266218</v>
       </c>
       <c r="E97" t="n">
-        <v>52.444073</v>
+        <v>67.864903</v>
       </c>
       <c r="F97" t="n">
-        <v>95.54313500000001</v>
+        <v>319.876891</v>
       </c>
       <c r="G97" t="n">
-        <v>62.716002</v>
+        <v>147.465323</v>
       </c>
       <c r="H97" t="n">
-        <v>27.640307</v>
+        <v>105.537485</v>
       </c>
       <c r="I97" t="n">
-        <v>72.461392</v>
+        <v>94.891927</v>
       </c>
       <c r="J97" t="n">
-        <v>154.0976</v>
+        <v>95.083974</v>
+      </c>
+      <c r="K97" t="n">
+        <v>100.186322</v>
       </c>
     </row>
     <row r="98">
@@ -3703,31 +4008,34 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.005694</v>
+        <v>0.003916</v>
       </c>
       <c r="C98" t="n">
-        <v>0.009537</v>
+        <v>0.0095345</v>
       </c>
       <c r="D98" t="n">
-        <v>0.028504</v>
+        <v>0.004104</v>
       </c>
       <c r="E98" t="n">
-        <v>0.0221175</v>
+        <v>0.00209</v>
       </c>
       <c r="F98" t="n">
-        <v>0.00347</v>
+        <v>0.015079</v>
       </c>
       <c r="G98" t="n">
-        <v>0.001891</v>
+        <v>0.003464666666666667</v>
       </c>
       <c r="H98" t="n">
-        <v>0.002712</v>
+        <v>0.002068666666666667</v>
       </c>
       <c r="I98" t="n">
-        <v>0.001863</v>
+        <v>0.004654</v>
       </c>
       <c r="J98" t="n">
-        <v>0.003763</v>
+        <v>0.003868</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0.006015</v>
       </c>
     </row>
     <row r="99">
@@ -3737,31 +4045,34 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>57.692754</v>
+        <v>70.1717</v>
       </c>
       <c r="C99" t="n">
-        <v>82.187201</v>
+        <v>69.915561</v>
       </c>
       <c r="D99" t="n">
-        <v>75.432047</v>
+        <v>107.661405</v>
       </c>
       <c r="E99" t="n">
-        <v>40.885461</v>
+        <v>95.802745</v>
       </c>
       <c r="F99" t="n">
-        <v>48.094337</v>
+        <v>156.495259</v>
       </c>
       <c r="G99" t="n">
-        <v>76.15819</v>
+        <v>102.21092</v>
       </c>
       <c r="H99" t="n">
-        <v>61.827034</v>
+        <v>64.102439</v>
       </c>
       <c r="I99" t="n">
-        <v>48.119094</v>
+        <v>93.322474</v>
       </c>
       <c r="J99" t="n">
-        <v>70.66310900000001</v>
+        <v>55.077038</v>
+      </c>
+      <c r="K99" t="n">
+        <v>95.97843399999999</v>
       </c>
     </row>
     <row r="100">
@@ -3771,31 +4082,34 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.031141</v>
+        <v>0.048153</v>
       </c>
       <c r="C100" t="n">
-        <v>0.025722</v>
+        <v>0.04267725</v>
       </c>
       <c r="D100" t="n">
-        <v>0.025105</v>
+        <v>0.03791033333333334</v>
       </c>
       <c r="E100" t="n">
-        <v>0.021688</v>
+        <v>0.041525</v>
       </c>
       <c r="F100" t="n">
-        <v>0.02571725</v>
+        <v>0.046628</v>
       </c>
       <c r="G100" t="n">
-        <v>0.035702</v>
+        <v>0.035645</v>
       </c>
       <c r="H100" t="n">
-        <v>0.051818</v>
+        <v>0.024784</v>
       </c>
       <c r="I100" t="n">
-        <v>0.046472</v>
+        <v>0.02873575</v>
       </c>
       <c r="J100" t="n">
-        <v>0.044677</v>
+        <v>0.02663225</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0.02465833333333333</v>
       </c>
     </row>
     <row r="101">
@@ -3805,26 +4119,35 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.38104</v>
+        <v>30.020113</v>
       </c>
       <c r="C101" t="n">
-        <v>0.7070109999999999</v>
-      </c>
-      <c r="D101" t="inlineStr"/>
+        <v>28.001421</v>
+      </c>
+      <c r="D101" t="n">
+        <v>19.469583</v>
+      </c>
       <c r="E101" t="n">
-        <v>70.926901</v>
-      </c>
-      <c r="F101" t="inlineStr"/>
+        <v>14.502247</v>
+      </c>
+      <c r="F101" t="n">
+        <v>34.262758</v>
+      </c>
       <c r="G101" t="n">
-        <v>16.415354</v>
+        <v>22.889902</v>
       </c>
       <c r="H101" t="n">
-        <v>20.866151</v>
+        <v>22.613706</v>
       </c>
       <c r="I101" t="n">
-        <v>20.365654</v>
-      </c>
-      <c r="J101" t="inlineStr"/>
+        <v>19.89963</v>
+      </c>
+      <c r="J101" t="n">
+        <v>30.053022</v>
+      </c>
+      <c r="K101" t="n">
+        <v>1.783048</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
@@ -3833,32 +4156,29 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.001633</v>
+        <v>4.7e-05</v>
       </c>
       <c r="C102" t="n">
-        <v>0.00077975</v>
+        <v>0.000183</v>
       </c>
       <c r="D102" t="n">
-        <v>0.002487</v>
+        <v>0.000411</v>
       </c>
       <c r="E102" t="n">
-        <v>0.000375</v>
+        <v>0.000332</v>
       </c>
       <c r="F102" t="n">
-        <v>0.00052</v>
+        <v>4.9e-05</v>
       </c>
       <c r="G102" t="n">
-        <v>0.001889</v>
+        <v>0.000116</v>
       </c>
       <c r="H102" t="n">
-        <v>0.000857</v>
-      </c>
-      <c r="I102" t="n">
-        <v>0.001086</v>
-      </c>
-      <c r="J102" t="n">
-        <v>0.003676</v>
-      </c>
+        <v>6.7e-05</v>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
@@ -3867,31 +4187,34 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>124.12725</v>
+        <v>112.510673</v>
       </c>
       <c r="C103" t="n">
-        <v>123.87734</v>
+        <v>126.678757</v>
       </c>
       <c r="D103" t="n">
-        <v>101.572075</v>
+        <v>131.743272</v>
       </c>
       <c r="E103" t="n">
-        <v>97.257312</v>
+        <v>89.381399</v>
       </c>
       <c r="F103" t="n">
-        <v>116.831751</v>
+        <v>137.588249</v>
       </c>
       <c r="G103" t="n">
-        <v>120.134948</v>
+        <v>128.75096475</v>
       </c>
       <c r="H103" t="n">
-        <v>75.797059</v>
+        <v>140.190352</v>
       </c>
       <c r="I103" t="n">
-        <v>100.231123</v>
+        <v>116.670222</v>
       </c>
       <c r="J103" t="n">
-        <v>122.263959</v>
+        <v>131.438059</v>
+      </c>
+      <c r="K103" t="n">
+        <v>116.348776</v>
       </c>
     </row>
     <row r="104">
@@ -3901,31 +4224,34 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>502.007682</v>
+        <v>414.486803</v>
       </c>
       <c r="C104" t="n">
-        <v>353.8224913333333</v>
+        <v>463.344724</v>
       </c>
       <c r="D104" t="n">
-        <v>405.806172</v>
+        <v>423.679191</v>
       </c>
       <c r="E104" t="n">
-        <v>516.970554</v>
+        <v>784.190293</v>
       </c>
       <c r="F104" t="n">
-        <v>676.738581</v>
+        <v>1500.974829</v>
       </c>
       <c r="G104" t="n">
-        <v>292.238365</v>
+        <v>1270.345084</v>
       </c>
       <c r="H104" t="n">
-        <v>369.115774</v>
+        <v>1276.408497</v>
       </c>
       <c r="I104" t="n">
-        <v>448.220202</v>
+        <v>434.218828</v>
       </c>
       <c r="J104" t="n">
-        <v>441.994205</v>
+        <v>390.718436</v>
+      </c>
+      <c r="K104" t="n">
+        <v>467.491935</v>
       </c>
     </row>
     <row r="105">
@@ -3935,31 +4261,34 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.238075</v>
+        <v>37.596639</v>
       </c>
       <c r="C105" t="n">
-        <v>1.958319</v>
+        <v>55.336026</v>
       </c>
       <c r="D105" t="n">
-        <v>3.482226</v>
+        <v>29.73499</v>
       </c>
       <c r="E105" t="n">
-        <v>1.073951</v>
+        <v>34.343915</v>
       </c>
       <c r="F105" t="n">
-        <v>2.602827</v>
+        <v>64.42345400000001</v>
       </c>
       <c r="G105" t="n">
-        <v>1.84696</v>
+        <v>41.367954</v>
       </c>
       <c r="H105" t="n">
-        <v>1.850054</v>
+        <v>31.043476</v>
       </c>
       <c r="I105" t="n">
-        <v>1.388491</v>
+        <v>3.13383</v>
       </c>
       <c r="J105" t="n">
-        <v>0.335951</v>
+        <v>2.8508</v>
+      </c>
+      <c r="K105" t="n">
+        <v>3.327093</v>
       </c>
     </row>
     <row r="106">
@@ -3969,31 +4298,34 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>921.361164</v>
+        <v>249.414713</v>
       </c>
       <c r="C106" t="n">
-        <v>525.655053</v>
+        <v>765.439792</v>
       </c>
       <c r="D106" t="n">
-        <v>637.545508</v>
+        <v>924.991957</v>
       </c>
       <c r="E106" t="n">
-        <v>335.86408</v>
+        <v>680.574489</v>
       </c>
       <c r="F106" t="n">
-        <v>309.39226</v>
+        <v>647.83709</v>
       </c>
       <c r="G106" t="n">
-        <v>538.491268</v>
+        <v>1724.96783</v>
       </c>
       <c r="H106" t="n">
-        <v>622.022591</v>
+        <v>432.610359</v>
       </c>
       <c r="I106" t="n">
-        <v>564.146935</v>
+        <v>180.215207</v>
       </c>
       <c r="J106" t="n">
-        <v>399.894101</v>
+        <v>651.772335</v>
+      </c>
+      <c r="K106" t="n">
+        <v>1960.644805</v>
       </c>
     </row>
     <row r="107">
@@ -4003,31 +4335,34 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.624803</v>
+        <v>0.823707</v>
       </c>
       <c r="C107" t="n">
-        <v>0.272337</v>
+        <v>0.575966</v>
       </c>
       <c r="D107" t="n">
-        <v>0.270188</v>
+        <v>0.593033</v>
       </c>
       <c r="E107" t="n">
-        <v>0.531964</v>
+        <v>0.628089</v>
       </c>
       <c r="F107" t="n">
-        <v>0.654319</v>
+        <v>0.336738</v>
       </c>
       <c r="G107" t="n">
-        <v>0.479901</v>
+        <v>0.46604</v>
       </c>
       <c r="H107" t="n">
-        <v>1.319274</v>
+        <v>0.571151</v>
       </c>
       <c r="I107" t="n">
-        <v>0.570715</v>
+        <v>0.259937</v>
       </c>
       <c r="J107" t="n">
-        <v>0.845659</v>
+        <v>0.631062</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0.656298</v>
       </c>
     </row>
     <row r="108">
@@ -4037,31 +4372,34 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>6.540235</v>
+        <v>111.060154</v>
       </c>
       <c r="C108" t="n">
-        <v>16.557683</v>
+        <v>81.041877</v>
       </c>
       <c r="D108" t="n">
-        <v>8.925591000000001</v>
+        <v>72.387227</v>
       </c>
       <c r="E108" t="n">
-        <v>4.865924</v>
+        <v>49.934651</v>
       </c>
       <c r="F108" t="n">
-        <v>13.219645</v>
+        <v>91.55938</v>
       </c>
       <c r="G108" t="n">
-        <v>64.06024600000001</v>
+        <v>50.13991</v>
       </c>
       <c r="H108" t="n">
-        <v>42.807068</v>
+        <v>48.622336</v>
       </c>
       <c r="I108" t="n">
-        <v>33.664185</v>
+        <v>28.670208</v>
       </c>
       <c r="J108" t="n">
-        <v>32.140272</v>
+        <v>33.945377</v>
+      </c>
+      <c r="K108" t="n">
+        <v>69.141695</v>
       </c>
     </row>
     <row r="109">
@@ -4071,31 +4409,34 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.06328499999999999</v>
+        <v>0.043318</v>
       </c>
       <c r="C109" t="n">
-        <v>0.0534</v>
+        <v>0.064952</v>
       </c>
       <c r="D109" t="n">
-        <v>0.09637</v>
+        <v>0.08289199999999999</v>
       </c>
       <c r="E109" t="n">
-        <v>0.060962</v>
+        <v>0.061841</v>
       </c>
       <c r="F109" t="n">
-        <v>0.066687</v>
+        <v>0.091789</v>
       </c>
       <c r="G109" t="n">
-        <v>0.221183</v>
+        <v>0.06341425000000001</v>
       </c>
       <c r="H109" t="n">
-        <v>0.10333425</v>
+        <v>0.043578</v>
       </c>
       <c r="I109" t="n">
-        <v>0.079579</v>
+        <v>0.04419866666666666</v>
       </c>
       <c r="J109" t="n">
-        <v>0.121471</v>
+        <v>0.028136</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0.047992</v>
       </c>
     </row>
     <row r="110">
@@ -4105,31 +4446,34 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>48.614308</v>
+        <v>89.83358699999999</v>
       </c>
       <c r="C110" t="n">
-        <v>23.721963</v>
+        <v>272.924504</v>
       </c>
       <c r="D110" t="n">
-        <v>32.069459</v>
+        <v>846.38107</v>
       </c>
       <c r="E110" t="n">
-        <v>18.425521</v>
+        <v>204.916912</v>
       </c>
       <c r="F110" t="n">
-        <v>18.234497</v>
+        <v>639.366413</v>
       </c>
       <c r="G110" t="n">
-        <v>140.416684</v>
+        <v>437.475353</v>
       </c>
       <c r="H110" t="n">
-        <v>82.37651700000001</v>
+        <v>1358.351665</v>
       </c>
       <c r="I110" t="n">
-        <v>31.889892</v>
+        <v>455.205895</v>
       </c>
       <c r="J110" t="n">
-        <v>18.274081</v>
+        <v>42.162402</v>
+      </c>
+      <c r="K110" t="n">
+        <v>190.401814</v>
       </c>
     </row>
     <row r="111">
@@ -4139,31 +4483,34 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.183793</v>
+        <v>0.174742</v>
       </c>
       <c r="C111" t="n">
-        <v>0.171734</v>
+        <v>0.564962</v>
       </c>
       <c r="D111" t="n">
-        <v>0.128434</v>
+        <v>0.917744</v>
       </c>
       <c r="E111" t="n">
-        <v>0.07986699999999999</v>
+        <v>0.639838</v>
       </c>
       <c r="F111" t="n">
-        <v>0.114254</v>
+        <v>0.789226</v>
       </c>
       <c r="G111" t="n">
-        <v>0.106079</v>
+        <v>0.958326</v>
       </c>
       <c r="H111" t="n">
-        <v>0.076611</v>
+        <v>0.909138</v>
       </c>
       <c r="I111" t="n">
-        <v>0.085253</v>
+        <v>0.363006</v>
       </c>
       <c r="J111" t="n">
-        <v>0.074637</v>
+        <v>0.378988</v>
+      </c>
+      <c r="K111" t="n">
+        <v>1.140258</v>
       </c>
     </row>
     <row r="112">
@@ -4173,31 +4520,30 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.00109</v>
+        <v>0.000958</v>
       </c>
       <c r="C112" t="n">
-        <v>0.000695</v>
+        <v>0.001266</v>
       </c>
       <c r="D112" t="n">
-        <v>0.000838</v>
+        <v>0.00065</v>
       </c>
       <c r="E112" t="n">
-        <v>0.00054</v>
+        <v>0.000269</v>
       </c>
       <c r="F112" t="n">
-        <v>0.00107</v>
+        <v>0.000425</v>
       </c>
       <c r="G112" t="n">
-        <v>0.00094</v>
+        <v>0.000557</v>
       </c>
       <c r="H112" t="n">
-        <v>0.00105</v>
-      </c>
-      <c r="I112" t="n">
-        <v>0.000827</v>
-      </c>
-      <c r="J112" t="n">
-        <v>0.051904</v>
+        <v>0.000392</v>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="n">
+        <v>0.003449</v>
       </c>
     </row>
     <row r="113">
@@ -4207,31 +4553,34 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.004261</v>
+        <v>0.001365</v>
       </c>
       <c r="C113" t="n">
-        <v>0.002522</v>
+        <v>0.002449</v>
       </c>
       <c r="D113" t="n">
-        <v>0.002449</v>
+        <v>0.009594</v>
       </c>
       <c r="E113" t="n">
-        <v>0.00161</v>
+        <v>0.007594</v>
       </c>
       <c r="F113" t="n">
-        <v>0.001331</v>
+        <v>0.006127</v>
       </c>
       <c r="G113" t="n">
-        <v>0.007381</v>
+        <v>0.002604</v>
       </c>
       <c r="H113" t="n">
-        <v>0.003454</v>
+        <v>0.002352</v>
       </c>
       <c r="I113" t="n">
-        <v>0.003542</v>
+        <v>0.002214</v>
       </c>
       <c r="J113" t="n">
-        <v>0.001365</v>
+        <v>0.001819</v>
+      </c>
+      <c r="K113" t="n">
+        <v>0.003116</v>
       </c>
     </row>
     <row r="114">
@@ -4240,17 +4589,24 @@
           <t>農業科技業平上櫃</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr"/>
-      <c r="C114" t="inlineStr"/>
+      <c r="B114" t="n">
+        <v>0.050946</v>
+      </c>
+      <c r="C114" t="n">
+        <v>0.029436</v>
+      </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="n">
-        <v>0.018748</v>
-      </c>
-      <c r="J114" t="inlineStr"/>
+        <v>0.000429</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0.000733</v>
+      </c>
+      <c r="K114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
@@ -4259,31 +4615,34 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>6082.970456</v>
+        <v>25255.472782</v>
       </c>
       <c r="C115" t="n">
-        <v>6103.551493</v>
+        <v>25583.707465</v>
       </c>
       <c r="D115" t="n">
-        <v>6732.41476</v>
+        <v>32739.140457</v>
       </c>
       <c r="E115" t="n">
-        <v>5664.386803</v>
+        <v>24301.194138</v>
       </c>
       <c r="F115" t="n">
-        <v>8245.252662000001</v>
+        <v>29221.238724</v>
       </c>
       <c r="G115" t="n">
-        <v>22743.754038</v>
+        <v>23689.328803</v>
       </c>
       <c r="H115" t="n">
-        <v>18508.769204</v>
+        <v>23865.695498</v>
       </c>
       <c r="I115" t="n">
-        <v>23340.049248</v>
+        <v>18716.52571</v>
       </c>
       <c r="J115" t="n">
-        <v>18464.629005</v>
+        <v>29109.164676</v>
+      </c>
+      <c r="K115" t="n">
+        <v>17026.871017</v>
       </c>
     </row>
     <row r="116">
@@ -4293,31 +4652,34 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>13.550458</v>
+        <v>20.250653</v>
       </c>
       <c r="C116" t="n">
-        <v>7.615602</v>
+        <v>18.582973</v>
       </c>
       <c r="D116" t="n">
-        <v>7.114229</v>
+        <v>24.835122</v>
       </c>
       <c r="E116" t="n">
-        <v>8.893762000000001</v>
+        <v>22.129946</v>
       </c>
       <c r="F116" t="n">
-        <v>17.404423</v>
+        <v>17.786353</v>
       </c>
       <c r="G116" t="n">
-        <v>30.87572</v>
+        <v>21.297676</v>
       </c>
       <c r="H116" t="n">
-        <v>24.380481</v>
+        <v>13.45781</v>
       </c>
       <c r="I116" t="n">
-        <v>38.145686</v>
+        <v>10.86563</v>
       </c>
       <c r="J116" t="n">
-        <v>17.986601</v>
+        <v>10.11165</v>
+      </c>
+      <c r="K116" t="n">
+        <v>13.436873</v>
       </c>
     </row>
     <row r="117">
@@ -4327,31 +4689,34 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>2277.09085</v>
+        <v>893.075661</v>
       </c>
       <c r="C117" t="n">
-        <v>1946.021499</v>
+        <v>805.4858359999999</v>
       </c>
       <c r="D117" t="n">
-        <v>2780.216216</v>
+        <v>826.805561</v>
       </c>
       <c r="E117" t="n">
-        <v>2244.085252</v>
+        <v>928.809391</v>
       </c>
       <c r="F117" t="n">
-        <v>592.812061</v>
+        <v>970.944972</v>
       </c>
       <c r="G117" t="n">
-        <v>1032.313313</v>
+        <v>1232.292849</v>
       </c>
       <c r="H117" t="n">
-        <v>3136.206759</v>
+        <v>813.427695</v>
       </c>
       <c r="I117" t="n">
-        <v>1142.814228</v>
+        <v>616.561423</v>
       </c>
       <c r="J117" t="n">
-        <v>1476.668651</v>
+        <v>765.001264</v>
+      </c>
+      <c r="K117" t="n">
+        <v>795.101355</v>
       </c>
     </row>
     <row r="118">
@@ -4361,31 +4726,34 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.092809</v>
+        <v>0.118458</v>
       </c>
       <c r="C118" t="n">
-        <v>0.139641</v>
+        <v>0.123824</v>
       </c>
       <c r="D118" t="n">
-        <v>0.121491</v>
+        <v>0.13111</v>
       </c>
       <c r="E118" t="n">
-        <v>0.078808</v>
+        <v>0.072089</v>
       </c>
       <c r="F118" t="n">
-        <v>0.084409</v>
+        <v>0.150084</v>
       </c>
       <c r="G118" t="n">
-        <v>0.171764</v>
+        <v>0.119453</v>
       </c>
       <c r="H118" t="n">
-        <v>0.188484</v>
+        <v>0.1368</v>
       </c>
       <c r="I118" t="n">
-        <v>0.114978</v>
+        <v>0.242976</v>
       </c>
       <c r="J118" t="n">
-        <v>0.144703</v>
+        <v>0.15816</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.229197</v>
       </c>
     </row>
     <row r="119">
@@ -4395,31 +4763,34 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>5162.65965</v>
+        <v>584.965255</v>
       </c>
       <c r="C119" t="n">
-        <v>8297.360316</v>
+        <v>392.91339</v>
       </c>
       <c r="D119" t="n">
-        <v>13988.662308</v>
+        <v>405.627643</v>
       </c>
       <c r="E119" t="n">
-        <v>12339.661725</v>
+        <v>199.655727</v>
       </c>
       <c r="F119" t="n">
-        <v>17667.338244</v>
+        <v>237.604652</v>
       </c>
       <c r="G119" t="n">
-        <v>8652.535905000001</v>
+        <v>297.191071</v>
       </c>
       <c r="H119" t="n">
-        <v>10680.328469</v>
+        <v>188.306349</v>
       </c>
       <c r="I119" t="n">
-        <v>12673.394296</v>
+        <v>2009.813657</v>
       </c>
       <c r="J119" t="n">
-        <v>6792.216042</v>
+        <v>334.984352</v>
+      </c>
+      <c r="K119" t="n">
+        <v>2028.738573</v>
       </c>
     </row>
     <row r="120">
@@ -4429,31 +4800,34 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>2.26254</v>
+        <v>0.426948</v>
       </c>
       <c r="C120" t="n">
-        <v>2.291996</v>
+        <v>0.312588</v>
       </c>
       <c r="D120" t="n">
-        <v>2.261277</v>
+        <v>3.423157</v>
       </c>
       <c r="E120" t="n">
-        <v>3.489899</v>
+        <v>1.656723</v>
       </c>
       <c r="F120" t="n">
-        <v>9.474993</v>
+        <v>2.779475</v>
       </c>
       <c r="G120" t="n">
-        <v>6.319699</v>
+        <v>2.073253</v>
       </c>
       <c r="H120" t="n">
-        <v>5.424032</v>
+        <v>2.173097</v>
       </c>
       <c r="I120" t="n">
-        <v>3.762618</v>
+        <v>1.498725</v>
       </c>
       <c r="J120" t="n">
-        <v>2.664755</v>
+        <v>1.880031</v>
+      </c>
+      <c r="K120" t="n">
+        <v>2.860901</v>
       </c>
     </row>
     <row r="121">
@@ -4463,31 +4837,34 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>57.019267</v>
+        <v>56.860276</v>
       </c>
       <c r="C121" t="n">
-        <v>95.750647</v>
+        <v>73.22282199999999</v>
       </c>
       <c r="D121" t="n">
-        <v>70.719487</v>
+        <v>95.43985600000001</v>
       </c>
       <c r="E121" t="n">
-        <v>92.464285</v>
+        <v>620.293591</v>
       </c>
       <c r="F121" t="n">
-        <v>63.28767</v>
+        <v>160.911874</v>
       </c>
       <c r="G121" t="n">
-        <v>58.167627</v>
+        <v>79.776139</v>
       </c>
       <c r="H121" t="n">
-        <v>54.269276</v>
+        <v>58.508732</v>
       </c>
       <c r="I121" t="n">
-        <v>602.393444</v>
+        <v>86.105074</v>
       </c>
       <c r="J121" t="n">
-        <v>56.860276</v>
+        <v>51.561188</v>
+      </c>
+      <c r="K121" t="n">
+        <v>29.226817</v>
       </c>
     </row>
     <row r="122">
@@ -4497,31 +4874,34 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>4.116534</v>
+        <v>8.628501999999999</v>
       </c>
       <c r="C122" t="n">
-        <v>8.170572</v>
+        <v>7.654183</v>
       </c>
       <c r="D122" t="n">
-        <v>6.624743</v>
+        <v>9.449596</v>
       </c>
       <c r="E122" t="n">
-        <v>6.312246</v>
+        <v>6.313389</v>
       </c>
       <c r="F122" t="n">
-        <v>7.259808</v>
+        <v>7.803697</v>
       </c>
       <c r="G122" t="n">
-        <v>13.316509</v>
+        <v>6.192561</v>
       </c>
       <c r="H122" t="n">
-        <v>6.283155</v>
+        <v>8.273391</v>
       </c>
       <c r="I122" t="n">
-        <v>6.420234</v>
+        <v>4.759663</v>
       </c>
       <c r="J122" t="n">
-        <v>8.628501999999999</v>
+        <v>7.401011</v>
+      </c>
+      <c r="K122" t="n">
+        <v>5.426103</v>
       </c>
     </row>
     <row r="123">
@@ -4531,31 +4911,34 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>23.263533</v>
+        <v>13.522615</v>
       </c>
       <c r="C123" t="n">
-        <v>54.222929</v>
+        <v>17.063821</v>
       </c>
       <c r="D123" t="n">
-        <v>27.470921</v>
+        <v>20.429546</v>
       </c>
       <c r="E123" t="n">
-        <v>54.140034</v>
+        <v>29.518382</v>
       </c>
       <c r="F123" t="n">
-        <v>31.758988</v>
+        <v>46.057863</v>
       </c>
       <c r="G123" t="n">
-        <v>46.895959</v>
+        <v>29.321354</v>
       </c>
       <c r="H123" t="n">
-        <v>43.005756</v>
+        <v>25.745741</v>
       </c>
       <c r="I123" t="n">
-        <v>37.571637</v>
+        <v>31.758045</v>
       </c>
       <c r="J123" t="n">
-        <v>13.522615</v>
+        <v>43.067624</v>
+      </c>
+      <c r="K123" t="n">
+        <v>28.785075</v>
       </c>
     </row>
     <row r="124">
@@ -4565,31 +4948,30 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>127.930135</v>
+        <v>19.219588</v>
       </c>
       <c r="C124" t="n">
-        <v>222.315562</v>
-      </c>
-      <c r="D124" t="n">
-        <v>159.66203</v>
-      </c>
-      <c r="E124" t="n">
-        <v>173.07071</v>
-      </c>
+        <v>13.233913</v>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr"/>
       <c r="F124" t="n">
-        <v>149.450741</v>
+        <v>13.454182</v>
       </c>
       <c r="G124" t="n">
-        <v>133.981208</v>
+        <v>9.400376</v>
       </c>
       <c r="H124" t="n">
-        <v>117.484132</v>
+        <v>20.184931</v>
       </c>
       <c r="I124" t="n">
-        <v>128.504357</v>
+        <v>40.641022</v>
       </c>
       <c r="J124" t="n">
-        <v>199.996151</v>
+        <v>104.901909</v>
+      </c>
+      <c r="K124" t="n">
+        <v>35.760378</v>
       </c>
     </row>
     <row r="125">
@@ -4599,31 +4981,34 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.008066</v>
+        <v>0.000762</v>
       </c>
       <c r="C125" t="n">
-        <v>0.00397</v>
+        <v>0.002955</v>
       </c>
       <c r="D125" t="n">
-        <v>0.003778</v>
+        <v>0.001541</v>
       </c>
       <c r="E125" t="n">
-        <v>0.006495</v>
+        <v>0.002365</v>
       </c>
       <c r="F125" t="n">
-        <v>0.002192</v>
+        <v>0.001496</v>
       </c>
       <c r="G125" t="n">
-        <v>0.001731</v>
+        <v>0.005709</v>
       </c>
       <c r="H125" t="n">
-        <v>0.001133</v>
+        <v>0.002274</v>
       </c>
       <c r="I125" t="n">
-        <v>0.003832</v>
+        <v>0.001796</v>
       </c>
       <c r="J125" t="n">
-        <v>0.002279</v>
+        <v>0.001943</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.001247</v>
       </c>
     </row>
     <row r="126">
@@ -4633,31 +5018,34 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>437.072996</v>
+        <v>653.593252</v>
       </c>
       <c r="C126" t="n">
-        <v>441.590088</v>
+        <v>887.262399</v>
       </c>
       <c r="D126" t="n">
-        <v>449.552373</v>
+        <v>950.6537</v>
       </c>
       <c r="E126" t="n">
-        <v>413.635324</v>
+        <v>725.094562</v>
       </c>
       <c r="F126" t="n">
-        <v>473.00502</v>
+        <v>1158.378359</v>
       </c>
       <c r="G126" t="n">
-        <v>809.13311</v>
+        <v>980.0030400000001</v>
       </c>
       <c r="H126" t="n">
-        <v>424.018495</v>
+        <v>793.010167</v>
       </c>
       <c r="I126" t="n">
-        <v>830.7774439999999</v>
+        <v>718.786573</v>
       </c>
       <c r="J126" t="n">
-        <v>641.801303</v>
+        <v>927.2286810000001</v>
+      </c>
+      <c r="K126" t="n">
+        <v>1101.476089</v>
       </c>
     </row>
     <row r="127">
@@ -4667,31 +5055,34 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.005639</v>
+        <v>0.008103000000000001</v>
       </c>
       <c r="C127" t="n">
-        <v>0.004976</v>
+        <v>0.013165</v>
       </c>
       <c r="D127" t="n">
-        <v>0.003873</v>
+        <v>0.01960175</v>
       </c>
       <c r="E127" t="n">
-        <v>0.00535</v>
+        <v>0.008484</v>
       </c>
       <c r="F127" t="n">
-        <v>0.005399</v>
+        <v>0.010944</v>
       </c>
       <c r="G127" t="n">
-        <v>0.010485</v>
+        <v>0.051479</v>
       </c>
       <c r="H127" t="n">
-        <v>0.005742</v>
+        <v>0.019638</v>
       </c>
       <c r="I127" t="n">
-        <v>0.015207</v>
+        <v>0.013057</v>
       </c>
       <c r="J127" t="n">
-        <v>0.007009</v>
+        <v>0.011711</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.01282675</v>
       </c>
     </row>
     <row r="128">
@@ -4701,31 +5092,34 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>47.479196</v>
+        <v>185.434387</v>
       </c>
       <c r="C128" t="n">
-        <v>88.51274100000001</v>
+        <v>181.027348</v>
       </c>
       <c r="D128" t="n">
-        <v>83.666366</v>
+        <v>169.869811</v>
       </c>
       <c r="E128" t="n">
-        <v>59.722284</v>
+        <v>123.151594</v>
       </c>
       <c r="F128" t="n">
-        <v>42.191244</v>
+        <v>362.16461</v>
       </c>
       <c r="G128" t="n">
-        <v>71.724283</v>
+        <v>135.759536</v>
       </c>
       <c r="H128" t="n">
-        <v>80.792382</v>
+        <v>184.75593</v>
       </c>
       <c r="I128" t="n">
-        <v>18.605277</v>
+        <v>143.780451</v>
       </c>
       <c r="J128" t="n">
-        <v>16.449773</v>
+        <v>142.344478</v>
+      </c>
+      <c r="K128" t="n">
+        <v>41.631818</v>
       </c>
     </row>
     <row r="129">
@@ -4735,32 +5129,31 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.001134</v>
+        <v>0.000602</v>
       </c>
       <c r="C129" t="n">
-        <v>0.000725</v>
+        <v>2.1e-05</v>
       </c>
       <c r="D129" t="n">
-        <v>0.000571</v>
+        <v>0.000411</v>
       </c>
       <c r="E129" t="n">
-        <v>0.00091</v>
+        <v>0.001084</v>
       </c>
       <c r="F129" t="n">
-        <v>0.000621</v>
+        <v>7.7e-05</v>
       </c>
       <c r="G129" t="n">
-        <v>0.000918</v>
+        <v>0.000127</v>
       </c>
       <c r="H129" t="n">
+        <v>1.7e-05</v>
+      </c>
+      <c r="I129" t="n">
         <v>0.000413</v>
       </c>
-      <c r="I129" t="n">
-        <v>0.000521</v>
-      </c>
-      <c r="J129" t="n">
-        <v>0.000179</v>
-      </c>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
@@ -4769,31 +5162,34 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>10882.35721</v>
+        <v>17156.764051</v>
       </c>
       <c r="C130" t="n">
-        <v>19643.829874</v>
+        <v>20598.012892</v>
       </c>
       <c r="D130" t="n">
-        <v>17163.268297</v>
+        <v>25109.015918</v>
       </c>
       <c r="E130" t="n">
-        <v>24618.524731</v>
+        <v>23963.659659</v>
       </c>
       <c r="F130" t="n">
-        <v>16298.205375</v>
+        <v>35449.998064</v>
       </c>
       <c r="G130" t="n">
-        <v>13807.946575</v>
+        <v>28927.249252</v>
       </c>
       <c r="H130" t="n">
-        <v>14981.031046</v>
+        <v>20148.564437</v>
       </c>
       <c r="I130" t="n">
-        <v>14479.266296</v>
+        <v>19128.336859</v>
       </c>
       <c r="J130" t="n">
-        <v>16904.108798</v>
+        <v>21837.620673</v>
+      </c>
+      <c r="K130" t="n">
+        <v>19211.706761</v>
       </c>
     </row>
     <row r="131">
@@ -4803,31 +5199,34 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>244.900842</v>
+        <v>74.259749</v>
       </c>
       <c r="C131" t="n">
-        <v>387.63469</v>
+        <v>448.914137</v>
       </c>
       <c r="D131" t="n">
-        <v>265.348802</v>
+        <v>294.731167</v>
       </c>
       <c r="E131" t="n">
-        <v>233.42015</v>
+        <v>133.126017</v>
       </c>
       <c r="F131" t="n">
-        <v>116.899227</v>
+        <v>313.057836</v>
       </c>
       <c r="G131" t="n">
-        <v>626.85414</v>
+        <v>258.249554</v>
       </c>
       <c r="H131" t="n">
-        <v>181.039781</v>
+        <v>190.677356</v>
       </c>
       <c r="I131" t="n">
-        <v>193.566498</v>
+        <v>193.630935</v>
       </c>
       <c r="J131" t="n">
-        <v>87.746871</v>
+        <v>137.66002</v>
+      </c>
+      <c r="K131" t="n">
+        <v>158.800948</v>
       </c>
     </row>
     <row r="132">
@@ -4837,31 +5236,34 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>209.691372</v>
+        <v>50.226125</v>
       </c>
       <c r="C132" t="n">
-        <v>280.204653</v>
+        <v>77.64404500000001</v>
       </c>
       <c r="D132" t="n">
-        <v>256.305102</v>
+        <v>43.13955</v>
       </c>
       <c r="E132" t="n">
-        <v>351.325567</v>
+        <v>54.037073</v>
       </c>
       <c r="F132" t="n">
-        <v>464.231308</v>
+        <v>11.910874</v>
       </c>
       <c r="G132" t="n">
-        <v>366.678001</v>
+        <v>26.483238</v>
       </c>
       <c r="H132" t="n">
-        <v>91.760988</v>
+        <v>130.568197</v>
       </c>
       <c r="I132" t="n">
-        <v>268.504873</v>
+        <v>55.324957</v>
       </c>
       <c r="J132" t="n">
-        <v>289.394256</v>
+        <v>57.040545</v>
+      </c>
+      <c r="K132" t="n">
+        <v>41.800411</v>
       </c>
     </row>
     <row r="133">
@@ -4871,31 +5273,34 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.200969</v>
+        <v>0.321457</v>
       </c>
       <c r="C133" t="n">
-        <v>0.161656</v>
+        <v>0.260748</v>
       </c>
       <c r="D133" t="n">
-        <v>0.400318</v>
+        <v>0.472466</v>
       </c>
       <c r="E133" t="n">
-        <v>0.34688</v>
+        <v>0.6153920000000001</v>
       </c>
       <c r="F133" t="n">
-        <v>0.207437</v>
+        <v>0.463364</v>
       </c>
       <c r="G133" t="n">
-        <v>0.32817</v>
+        <v>0.293248</v>
       </c>
       <c r="H133" t="n">
-        <v>0.370971</v>
+        <v>0.280048</v>
       </c>
       <c r="I133" t="n">
-        <v>0.224957</v>
+        <v>0.205582</v>
       </c>
       <c r="J133" t="n">
-        <v>0.321354</v>
+        <v>0.14767</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.162321</v>
       </c>
     </row>
     <row r="134">
@@ -4905,1425 +5310,1496 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.102314</v>
+        <v>0.018194</v>
       </c>
       <c r="C134" t="n">
-        <v>0.038874</v>
+        <v>0.02048</v>
       </c>
       <c r="D134" t="n">
-        <v>0.064808</v>
+        <v>0.056008</v>
       </c>
       <c r="E134" t="n">
-        <v>0.08569</v>
+        <v>0.026671</v>
       </c>
       <c r="F134" t="n">
-        <v>0.030934</v>
+        <v>0.064164</v>
       </c>
       <c r="G134" t="n">
-        <v>0.062779</v>
+        <v>0.046877</v>
       </c>
       <c r="H134" t="n">
-        <v>0.015258</v>
+        <v>0.052364</v>
       </c>
       <c r="I134" t="n">
-        <v>0.021759</v>
+        <v>0.043636</v>
       </c>
       <c r="J134" t="n">
-        <v>0.018194</v>
+        <v>0.03427</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.021858</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>金融業平上櫃</t>
+          <t>鋼鐵工業右上上市</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.000225</v>
+        <v>962.375631</v>
       </c>
       <c r="C135" t="n">
-        <v>6.2e-05</v>
+        <v>789.719156</v>
       </c>
       <c r="D135" t="n">
-        <v>0.00025</v>
+        <v>1550.176211</v>
       </c>
       <c r="E135" t="n">
-        <v>0.000124</v>
+        <v>1643.28704</v>
       </c>
       <c r="F135" t="n">
-        <v>0.000248</v>
+        <v>1356.040678</v>
       </c>
       <c r="G135" t="n">
-        <v>0.000429</v>
+        <v>2963.163965</v>
       </c>
       <c r="H135" t="n">
-        <v>0.000127</v>
+        <v>1492.10477</v>
       </c>
       <c r="I135" t="n">
-        <v>0.000131</v>
+        <v>2663.206052</v>
       </c>
       <c r="J135" t="n">
-        <v>0.000103</v>
+        <v>2208.951272</v>
+      </c>
+      <c r="K135" t="n">
+        <v>2963.440125</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上上市</t>
+          <t>鋼鐵工業右上上櫃</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>1668.035173</v>
+        <v>0.073502</v>
       </c>
       <c r="C136" t="n">
-        <v>2123.299819</v>
+        <v>0.06665699999999999</v>
       </c>
       <c r="D136" t="n">
-        <v>2472.356878</v>
+        <v>0.06342</v>
       </c>
       <c r="E136" t="n">
-        <v>4794.875688</v>
+        <v>0.059589</v>
       </c>
       <c r="F136" t="n">
-        <v>1359.890176</v>
+        <v>0.058361</v>
       </c>
       <c r="G136" t="n">
-        <v>1769.709532</v>
+        <v>0.064585</v>
       </c>
       <c r="H136" t="n">
-        <v>836.966153</v>
+        <v>0.135021</v>
       </c>
       <c r="I136" t="n">
-        <v>1061.566529</v>
+        <v>0.103216</v>
       </c>
       <c r="J136" t="n">
-        <v>979.023702</v>
+        <v>0.056944</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.20184</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上上櫃</t>
+          <t>鋼鐵工業右下上市</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.006391</v>
+        <v>604.521476</v>
       </c>
       <c r="C137" t="n">
-        <v>0.044205</v>
+        <v>164.932517</v>
       </c>
       <c r="D137" t="n">
-        <v>0.05524</v>
+        <v>134.193253</v>
       </c>
       <c r="E137" t="n">
-        <v>0.032969</v>
+        <v>116.553101</v>
       </c>
       <c r="F137" t="n">
-        <v>0.090244</v>
+        <v>257.71903</v>
       </c>
       <c r="G137" t="n">
-        <v>0.047232</v>
+        <v>244.828967</v>
       </c>
       <c r="H137" t="n">
-        <v>0.263393</v>
+        <v>278.44663</v>
       </c>
       <c r="I137" t="n">
-        <v>0.187232</v>
+        <v>143.434833</v>
       </c>
       <c r="J137" t="n">
-        <v>0.07041</v>
+        <v>161.302958</v>
+      </c>
+      <c r="K137" t="n">
+        <v>170.540974</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右下上市</t>
+          <t>鋼鐵工業右下上櫃</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>690.654503</v>
+        <v>0.145907</v>
       </c>
       <c r="C138" t="n">
-        <v>1034.546462</v>
+        <v>0.00883225</v>
       </c>
       <c r="D138" t="n">
-        <v>233.418087</v>
+        <v>0.062358</v>
       </c>
       <c r="E138" t="n">
-        <v>217.573193</v>
+        <v>0.01344233333333333</v>
       </c>
       <c r="F138" t="n">
-        <v>147.093842</v>
+        <v>0.07928300000000001</v>
       </c>
       <c r="G138" t="n">
-        <v>766.217797</v>
+        <v>0.014179</v>
       </c>
       <c r="H138" t="n">
-        <v>141.456491</v>
+        <v>0.009131</v>
       </c>
       <c r="I138" t="n">
-        <v>152.003774</v>
+        <v>0.033395</v>
       </c>
       <c r="J138" t="n">
-        <v>118.986738</v>
+        <v>0.07098699999999999</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.006889</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右下上櫃</t>
+          <t>鋼鐵工業平上市</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.0357425</v>
+        <v>84.713707</v>
       </c>
       <c r="C139" t="n">
-        <v>0.066598</v>
+        <v>1268.175432</v>
       </c>
       <c r="D139" t="n">
-        <v>0.01580233333333333</v>
+        <v>704.0940450000001</v>
       </c>
       <c r="E139" t="n">
-        <v>0.07816099999999999</v>
+        <v>2190.043855</v>
       </c>
       <c r="F139" t="n">
-        <v>0.008527</v>
+        <v>1097.760524</v>
       </c>
       <c r="G139" t="n">
-        <v>0.08859475</v>
+        <v>53.245693</v>
       </c>
       <c r="H139" t="n">
-        <v>0.04056825</v>
+        <v>896.350784</v>
       </c>
       <c r="I139" t="n">
-        <v>0.036631</v>
+        <v>104.276388</v>
       </c>
       <c r="J139" t="n">
-        <v>0.004337</v>
+        <v>135.167745</v>
+      </c>
+      <c r="K139" t="n">
+        <v>105.526739</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業平上市</t>
+          <t>鋼鐵工業平上櫃</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>51.27883</v>
+        <v>0.000221</v>
       </c>
       <c r="C140" t="n">
-        <v>69.504525</v>
+        <v>0.092358</v>
       </c>
       <c r="D140" t="n">
-        <v>1959.791285</v>
+        <v>0.001838</v>
       </c>
       <c r="E140" t="n">
-        <v>880.248299</v>
+        <v>0.060227</v>
       </c>
       <c r="F140" t="n">
-        <v>474.633615</v>
+        <v>0.001748</v>
       </c>
       <c r="G140" t="n">
-        <v>120.192436</v>
+        <v>0.07703699999999999</v>
       </c>
       <c r="H140" t="n">
-        <v>416.713208</v>
+        <v>0.042344</v>
       </c>
       <c r="I140" t="n">
-        <v>494.662077</v>
+        <v>0.000472</v>
       </c>
       <c r="J140" t="n">
-        <v>553.600374</v>
+        <v>0.000633</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.09809725</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業平上櫃</t>
+          <t>電器電纜右上上市</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.007728</v>
+        <v>1041.428629</v>
       </c>
       <c r="C141" t="n">
-        <v>0.022195</v>
+        <v>2380.416448</v>
       </c>
       <c r="D141" t="n">
-        <v>0.22675</v>
+        <v>1652.845578</v>
       </c>
       <c r="E141" t="n">
-        <v>0.017764</v>
+        <v>3526.040941</v>
       </c>
       <c r="F141" t="n">
-        <v>0.049575</v>
+        <v>3020.377115</v>
       </c>
       <c r="G141" t="n">
-        <v>0.016499</v>
+        <v>1437.331486</v>
       </c>
       <c r="H141" t="n">
-        <v>0.01842</v>
+        <v>1121.222264</v>
       </c>
       <c r="I141" t="n">
-        <v>0.017592</v>
+        <v>597.051374</v>
       </c>
       <c r="J141" t="n">
-        <v>0.144883</v>
+        <v>468.663467</v>
+      </c>
+      <c r="K141" t="n">
+        <v>549.045074</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右上上市</t>
+          <t>電器電纜右上上櫃</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>243.385274</v>
+        <v>0.150452</v>
       </c>
       <c r="C142" t="n">
-        <v>221.164725</v>
+        <v>0.192913</v>
       </c>
       <c r="D142" t="n">
-        <v>2022.93564</v>
+        <v>0.15041</v>
       </c>
       <c r="E142" t="n">
-        <v>1815.128022</v>
+        <v>0.148937</v>
       </c>
       <c r="F142" t="n">
-        <v>1400.305424</v>
+        <v>0.14244</v>
       </c>
       <c r="G142" t="n">
-        <v>1065.650025</v>
+        <v>0.089825</v>
       </c>
       <c r="H142" t="n">
-        <v>771.32349</v>
+        <v>0.08122</v>
       </c>
       <c r="I142" t="n">
-        <v>2344.32493</v>
+        <v>0.06408899999999999</v>
       </c>
       <c r="J142" t="n">
-        <v>1041.428629</v>
+        <v>0.077725</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.063419</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右上上櫃</t>
+          <t>電器電纜右下上市</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.091242</v>
+        <v>187.344101</v>
       </c>
       <c r="C143" t="n">
-        <v>0.112558</v>
+        <v>76.255154</v>
       </c>
       <c r="D143" t="n">
-        <v>0.294298</v>
+        <v>110.812447</v>
       </c>
       <c r="E143" t="n">
-        <v>0.204111</v>
+        <v>60.484787</v>
       </c>
       <c r="F143" t="n">
-        <v>0.346172</v>
+        <v>95.418598</v>
       </c>
       <c r="G143" t="n">
-        <v>0.360224</v>
+        <v>52.871653</v>
       </c>
       <c r="H143" t="n">
-        <v>0.179417</v>
+        <v>81.429742</v>
       </c>
       <c r="I143" t="n">
-        <v>0.243985</v>
+        <v>56.265111</v>
       </c>
       <c r="J143" t="n">
-        <v>0.150452</v>
+        <v>50.845094</v>
+      </c>
+      <c r="K143" t="n">
+        <v>64.46852199999999</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右下上市</t>
+          <t>電器電纜平上市</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>39.275066</v>
-      </c>
-      <c r="C144" t="n">
-        <v>40.346396</v>
-      </c>
+        <v>115.350516</v>
+      </c>
+      <c r="C144" t="inlineStr"/>
       <c r="D144" t="n">
-        <v>55.382448</v>
-      </c>
-      <c r="E144" t="n">
-        <v>41.834918</v>
-      </c>
-      <c r="F144" t="n">
-        <v>50.073944</v>
-      </c>
+        <v>161.179866</v>
+      </c>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr"/>
       <c r="G144" t="n">
-        <v>62.3224</v>
+        <v>140.144075</v>
       </c>
       <c r="H144" t="n">
-        <v>50.570646</v>
+        <v>138.823516</v>
       </c>
       <c r="I144" t="n">
-        <v>43.980049</v>
+        <v>127.229351</v>
       </c>
       <c r="J144" t="n">
-        <v>107.991145</v>
+        <v>88.273901</v>
+      </c>
+      <c r="K144" t="n">
+        <v>106.428955</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>電器電纜平上市</t>
+          <t>電子通路業右上上市</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>116.254235</v>
+        <v>4913.476519</v>
       </c>
       <c r="C145" t="n">
-        <v>420.560636</v>
+        <v>5794.291198</v>
       </c>
       <c r="D145" t="n">
-        <v>44.797637</v>
+        <v>6928.273658</v>
       </c>
       <c r="E145" t="n">
-        <v>21.090587</v>
+        <v>5341.944198</v>
       </c>
       <c r="F145" t="n">
-        <v>11.466549</v>
+        <v>5943.805008</v>
       </c>
       <c r="G145" t="n">
-        <v>204.482959</v>
+        <v>5352.027379</v>
       </c>
       <c r="H145" t="n">
-        <v>17.022326</v>
+        <v>4216.801423</v>
       </c>
       <c r="I145" t="n">
-        <v>27.863442</v>
+        <v>3310.887283</v>
       </c>
       <c r="J145" t="n">
-        <v>194.703472</v>
+        <v>3481.54415</v>
+      </c>
+      <c r="K145" t="n">
+        <v>4224.814142</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右上上市</t>
+          <t>電子通路業右上上櫃</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>3162.15291</v>
+        <v>0.295139</v>
       </c>
       <c r="C146" t="n">
-        <v>3504.588651</v>
+        <v>0.701611</v>
       </c>
       <c r="D146" t="n">
-        <v>4790.204438</v>
+        <v>0.242673</v>
       </c>
       <c r="E146" t="n">
-        <v>2482.396615</v>
+        <v>0.222482</v>
       </c>
       <c r="F146" t="n">
-        <v>2318.877637</v>
+        <v>0.14276</v>
       </c>
       <c r="G146" t="n">
-        <v>2511.741979</v>
+        <v>0.08462</v>
       </c>
       <c r="H146" t="n">
-        <v>1612.453768</v>
+        <v>0.096876</v>
       </c>
       <c r="I146" t="n">
-        <v>1942.566081</v>
+        <v>0.06115</v>
       </c>
       <c r="J146" t="n">
-        <v>2625.004186</v>
+        <v>0.065174</v>
+      </c>
+      <c r="K146" t="n">
+        <v>0.08644300000000001</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右上上櫃</t>
+          <t>電子通路業右下上市</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.127115</v>
+        <v>9.756826999999999</v>
       </c>
       <c r="C147" t="n">
-        <v>0.114703</v>
+        <v>10.861653</v>
       </c>
       <c r="D147" t="n">
-        <v>0.131196</v>
+        <v>9.789550999999999</v>
       </c>
       <c r="E147" t="n">
-        <v>0.332757</v>
+        <v>9.075695</v>
       </c>
       <c r="F147" t="n">
-        <v>0.374888</v>
+        <v>10.41061</v>
       </c>
       <c r="G147" t="n">
-        <v>0.545445</v>
+        <v>9.936412000000001</v>
       </c>
       <c r="H147" t="n">
-        <v>0.119233</v>
+        <v>28.982313</v>
       </c>
       <c r="I147" t="n">
-        <v>0.143438</v>
+        <v>21.588764</v>
       </c>
       <c r="J147" t="n">
-        <v>0.125264</v>
+        <v>18.532432</v>
+      </c>
+      <c r="K147" t="n">
+        <v>24.553908</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右下上市</t>
+          <t>電子通路業右下上櫃</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>6.727905</v>
+        <v>0.057118</v>
       </c>
       <c r="C148" t="n">
-        <v>18.247482</v>
+        <v>0.070995</v>
       </c>
       <c r="D148" t="n">
-        <v>12.283079</v>
+        <v>0.046428</v>
       </c>
       <c r="E148" t="n">
-        <v>13.321644</v>
+        <v>0.029028</v>
       </c>
       <c r="F148" t="n">
-        <v>11.089148</v>
+        <v>0.018248</v>
       </c>
       <c r="G148" t="n">
-        <v>13.469439</v>
+        <v>0.014132</v>
       </c>
       <c r="H148" t="n">
-        <v>11.420697</v>
+        <v>0.01328775</v>
       </c>
       <c r="I148" t="n">
-        <v>8.435860999999999</v>
+        <v>0.023617</v>
       </c>
       <c r="J148" t="n">
-        <v>9.756826999999999</v>
+        <v>0.024176</v>
+      </c>
+      <c r="K148" t="n">
+        <v>0.012349</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右下上櫃</t>
+          <t>電子通路業平上市</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.06376800000000001</v>
+        <v>56.281587</v>
       </c>
       <c r="C149" t="n">
-        <v>0.0418</v>
+        <v>48.466276</v>
       </c>
       <c r="D149" t="n">
-        <v>0.04535</v>
+        <v>146.853345</v>
       </c>
       <c r="E149" t="n">
-        <v>0.081911</v>
+        <v>20.282854</v>
       </c>
       <c r="F149" t="n">
-        <v>0.022376</v>
+        <v>65.88053499999999</v>
       </c>
       <c r="G149" t="n">
-        <v>0.01177</v>
+        <v>105.135225</v>
       </c>
       <c r="H149" t="n">
-        <v>0.012023</v>
+        <v>99.78953</v>
       </c>
       <c r="I149" t="n">
-        <v>0.015477</v>
+        <v>72.068825</v>
       </c>
       <c r="J149" t="n">
-        <v>0.057118</v>
+        <v>46.423877</v>
+      </c>
+      <c r="K149" t="n">
+        <v>51.386202</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>電子通路業平上市</t>
+          <t>電子通路業平上櫃</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>2036.568067</v>
+        <v>0.012561</v>
       </c>
       <c r="C150" t="n">
-        <v>1544.029191</v>
+        <v>0.048949</v>
       </c>
       <c r="D150" t="n">
-        <v>2244.493983</v>
+        <v>0.281443</v>
       </c>
       <c r="E150" t="n">
-        <v>2879.512206</v>
+        <v>0.005076</v>
       </c>
       <c r="F150" t="n">
-        <v>2031.06244</v>
+        <v>0.2213</v>
       </c>
       <c r="G150" t="n">
-        <v>1994.714516</v>
+        <v>0.121082</v>
       </c>
       <c r="H150" t="n">
-        <v>1739.529586</v>
+        <v>0.199947</v>
       </c>
       <c r="I150" t="n">
-        <v>1888.539275</v>
+        <v>0.140783</v>
       </c>
       <c r="J150" t="n">
-        <v>2344.75392</v>
+        <v>0.132337</v>
+      </c>
+      <c r="K150" t="n">
+        <v>0.169785</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>電子通路業平上櫃</t>
+          <t>電子零組件業右上上市</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.277588</v>
+        <v>246129.878716</v>
       </c>
       <c r="C151" t="n">
-        <v>0.466732</v>
+        <v>187567.231862</v>
       </c>
       <c r="D151" t="n">
-        <v>0.359879</v>
+        <v>246211.641797</v>
       </c>
       <c r="E151" t="n">
-        <v>0.272872</v>
+        <v>214113.50732</v>
       </c>
       <c r="F151" t="n">
-        <v>0.205556</v>
+        <v>304889.285723</v>
       </c>
       <c r="G151" t="n">
-        <v>0.297367</v>
+        <v>199573.807519</v>
       </c>
       <c r="H151" t="n">
-        <v>0.258832</v>
+        <v>205300.203721</v>
       </c>
       <c r="I151" t="n">
-        <v>0.14169</v>
+        <v>209163.855494</v>
       </c>
       <c r="J151" t="n">
-        <v>0.182436</v>
+        <v>223851.764794</v>
+      </c>
+      <c r="K151" t="n">
+        <v>255646.88146</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右上上市</t>
+          <t>電子零組件業右上上櫃</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>189680.575138</v>
+        <v>57.358641</v>
       </c>
       <c r="C152" t="n">
-        <v>166503.267279</v>
+        <v>46.172949</v>
       </c>
       <c r="D152" t="n">
-        <v>172115.252274</v>
+        <v>52.237136</v>
       </c>
       <c r="E152" t="n">
-        <v>218271.158035</v>
+        <v>68.77581466666668</v>
       </c>
       <c r="F152" t="n">
-        <v>293331.951884</v>
+        <v>66.413197</v>
       </c>
       <c r="G152" t="n">
-        <v>328265.311909</v>
+        <v>68.66043633333332</v>
       </c>
       <c r="H152" t="n">
-        <v>288190.134832</v>
+        <v>79.239329</v>
       </c>
       <c r="I152" t="n">
-        <v>280157.533381</v>
+        <v>85.90924200000001</v>
       </c>
       <c r="J152" t="n">
-        <v>237824.950979</v>
+        <v>85.52268866666667</v>
+      </c>
+      <c r="K152" t="n">
+        <v>87.55076699999999</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右上上櫃</t>
+          <t>電子零組件業右下上市</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>37.603645</v>
+        <v>1126.014763</v>
       </c>
       <c r="C153" t="n">
-        <v>29.674985</v>
+        <v>2008.675927</v>
       </c>
       <c r="D153" t="n">
-        <v>28.779912</v>
+        <v>930.064726</v>
       </c>
       <c r="E153" t="n">
-        <v>49.01851</v>
+        <v>1510.887253</v>
       </c>
       <c r="F153" t="n">
-        <v>64.95413499999999</v>
+        <v>1778.770117</v>
       </c>
       <c r="G153" t="n">
-        <v>73.40257800000001</v>
+        <v>1610.391026</v>
       </c>
       <c r="H153" t="n">
-        <v>67.14289100000001</v>
+        <v>1986.703971</v>
       </c>
       <c r="I153" t="n">
-        <v>67.12150200000001</v>
+        <v>1729.714195</v>
       </c>
       <c r="J153" t="n">
-        <v>51.621843</v>
+        <v>1608.125564</v>
+      </c>
+      <c r="K153" t="n">
+        <v>1437.164907</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右下上市</t>
+          <t>電子零組件業右下上櫃</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>3340.325803</v>
+        <v>0.711408</v>
       </c>
       <c r="C154" t="n">
-        <v>5280.673074</v>
+        <v>0.696469</v>
       </c>
       <c r="D154" t="n">
-        <v>2364.317114</v>
+        <v>0.950691</v>
       </c>
       <c r="E154" t="n">
-        <v>2046.42661</v>
+        <v>0.527877</v>
       </c>
       <c r="F154" t="n">
-        <v>2344.140071</v>
+        <v>0.541832</v>
       </c>
       <c r="G154" t="n">
-        <v>3827.341422</v>
+        <v>0.466484</v>
       </c>
       <c r="H154" t="n">
-        <v>3178.747745</v>
+        <v>0.559515</v>
       </c>
       <c r="I154" t="n">
-        <v>1795.89688</v>
+        <v>0.472442</v>
       </c>
       <c r="J154" t="n">
-        <v>1403.505428</v>
+        <v>0.395845</v>
+      </c>
+      <c r="K154" t="n">
+        <v>0.582906</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右下上櫃</t>
+          <t>電子零組件業平上市</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.901962</v>
+        <v>972.3518</v>
       </c>
       <c r="C155" t="n">
-        <v>0.571503</v>
+        <v>2047.820503</v>
       </c>
       <c r="D155" t="n">
-        <v>1.249787</v>
+        <v>4539.84803</v>
       </c>
       <c r="E155" t="n">
-        <v>1.073411</v>
+        <v>2366.111101</v>
       </c>
       <c r="F155" t="n">
-        <v>0.755271</v>
+        <v>6820.63797</v>
       </c>
       <c r="G155" t="n">
-        <v>1.243945</v>
+        <v>5748.740213</v>
       </c>
       <c r="H155" t="n">
-        <v>1.071785</v>
+        <v>3979.847094</v>
       </c>
       <c r="I155" t="n">
-        <v>0.89056</v>
+        <v>4143.613972</v>
       </c>
       <c r="J155" t="n">
-        <v>0.798391</v>
+        <v>3245.140944</v>
+      </c>
+      <c r="K155" t="n">
+        <v>29016.078938</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業平上市</t>
+          <t>電子零組件業平上櫃</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>3730.19601</v>
+        <v>0.208691</v>
       </c>
       <c r="C156" t="n">
-        <v>26646.647293</v>
+        <v>0.178582</v>
       </c>
       <c r="D156" t="n">
-        <v>22839.140407</v>
+        <v>0.244586</v>
       </c>
       <c r="E156" t="n">
-        <v>21165.832819</v>
+        <v>0.203788</v>
       </c>
       <c r="F156" t="n">
-        <v>10811.621282</v>
+        <v>0.469598</v>
       </c>
       <c r="G156" t="n">
-        <v>9777.164191</v>
+        <v>0.436916</v>
       </c>
       <c r="H156" t="n">
-        <v>9862.512565000001</v>
+        <v>0.340724</v>
       </c>
       <c r="I156" t="n">
-        <v>12033.939349</v>
+        <v>0.254331</v>
       </c>
       <c r="J156" t="n">
-        <v>8999.788871999999</v>
+        <v>0.277827</v>
+      </c>
+      <c r="K156" t="n">
+        <v>0.526743</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業平上櫃</t>
+          <t>電機機械右上上市</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>1.503673</v>
+        <v>7792.665068</v>
       </c>
       <c r="C157" t="n">
-        <v>3.272388</v>
+        <v>7658.480151</v>
       </c>
       <c r="D157" t="n">
-        <v>4.11166</v>
+        <v>21347.714773</v>
       </c>
       <c r="E157" t="n">
-        <v>3.54604</v>
+        <v>17129.145845</v>
       </c>
       <c r="F157" t="n">
-        <v>3.446139</v>
+        <v>21922.178132</v>
       </c>
       <c r="G157" t="n">
-        <v>4.972175</v>
+        <v>21596.455042</v>
       </c>
       <c r="H157" t="n">
-        <v>2.336314</v>
+        <v>17643.132366</v>
       </c>
       <c r="I157" t="n">
-        <v>4.624579</v>
+        <v>10550.395861</v>
       </c>
       <c r="J157" t="n">
-        <v>5.858506</v>
+        <v>15560.961724</v>
+      </c>
+      <c r="K157" t="n">
+        <v>16569.032242</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>電機機械右上上市</t>
+          <t>電機機械右上上櫃</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>16041.960584</v>
+        <v>0.913235</v>
       </c>
       <c r="C158" t="n">
-        <v>16397.971383</v>
+        <v>1.162125</v>
       </c>
       <c r="D158" t="n">
-        <v>15648.185563</v>
+        <v>1.090835</v>
       </c>
       <c r="E158" t="n">
-        <v>20759.210972</v>
+        <v>0.784849</v>
       </c>
       <c r="F158" t="n">
-        <v>19153.740726</v>
+        <v>0.898227</v>
       </c>
       <c r="G158" t="n">
-        <v>8966.400874999999</v>
+        <v>0.6324689999999999</v>
       </c>
       <c r="H158" t="n">
-        <v>5616.545071</v>
+        <v>0.569712</v>
       </c>
       <c r="I158" t="n">
-        <v>7242.436367</v>
+        <v>0.685992</v>
       </c>
       <c r="J158" t="n">
-        <v>5050.538461</v>
+        <v>0.847919</v>
+      </c>
+      <c r="K158" t="n">
+        <v>0.908417</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>電機機械右上上櫃</t>
+          <t>電機機械右下上市</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0.232632</v>
+        <v>429.733028</v>
       </c>
       <c r="C159" t="n">
-        <v>1.930055</v>
+        <v>456.012036</v>
       </c>
       <c r="D159" t="n">
-        <v>1.779102</v>
+        <v>3814.329931</v>
       </c>
       <c r="E159" t="n">
-        <v>3.481795</v>
+        <v>602.167522</v>
       </c>
       <c r="F159" t="n">
-        <v>2.240837</v>
+        <v>2616.797834</v>
       </c>
       <c r="G159" t="n">
-        <v>1.575423</v>
+        <v>1023.422566</v>
       </c>
       <c r="H159" t="n">
-        <v>1.048016</v>
+        <v>1469.13372</v>
       </c>
       <c r="I159" t="n">
-        <v>0.874125</v>
+        <v>1210.84740475</v>
       </c>
       <c r="J159" t="n">
-        <v>0.8919280000000001</v>
+        <v>1218.192664</v>
+      </c>
+      <c r="K159" t="n">
+        <v>990.296252</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>電機機械右下上市</t>
+          <t>電機機械右下上櫃</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>1278.56809225</v>
+        <v>0.122212</v>
       </c>
       <c r="C160" t="n">
-        <v>1352.800315</v>
+        <v>0.100377</v>
       </c>
       <c r="D160" t="n">
-        <v>1402.402289</v>
+        <v>0.104297</v>
       </c>
       <c r="E160" t="n">
-        <v>904.3769</v>
+        <v>0.094176</v>
       </c>
       <c r="F160" t="n">
-        <v>1280.301169</v>
+        <v>0.144987</v>
       </c>
       <c r="G160" t="n">
-        <v>1389.069581</v>
+        <v>0.0796785</v>
       </c>
       <c r="H160" t="n">
-        <v>981.387952</v>
+        <v>0.091709</v>
       </c>
       <c r="I160" t="n">
-        <v>1626.124408</v>
+        <v>0.07321133333333332</v>
       </c>
       <c r="J160" t="n">
-        <v>961.62406</v>
+        <v>0.12867</v>
+      </c>
+      <c r="K160" t="n">
+        <v>0.134474</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>電機機械右下上櫃</t>
+          <t>電機機械平上市</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0.070176</v>
+        <v>1679.984799</v>
       </c>
       <c r="C161" t="n">
-        <v>0.085379</v>
+        <v>4843.889516</v>
       </c>
       <c r="D161" t="n">
-        <v>0.128986</v>
+        <v>1304.229169</v>
       </c>
       <c r="E161" t="n">
-        <v>0.09494175000000001</v>
+        <v>2373.007466</v>
       </c>
       <c r="F161" t="n">
-        <v>0.145845</v>
+        <v>2132.066124</v>
       </c>
       <c r="G161" t="n">
-        <v>0.17716775</v>
+        <v>1486.959468</v>
       </c>
       <c r="H161" t="n">
-        <v>0.173026</v>
+        <v>1947.052022</v>
       </c>
       <c r="I161" t="n">
-        <v>0.115561</v>
+        <v>2656.890474</v>
       </c>
       <c r="J161" t="n">
-        <v>0.137959</v>
+        <v>2107.081482</v>
+      </c>
+      <c r="K161" t="n">
+        <v>1727.728272</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>電機機械平上市</t>
+          <t>電機機械平上櫃</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>1901.489896</v>
+        <v>0.046861</v>
       </c>
       <c r="C162" t="n">
-        <v>1746.753474</v>
+        <v>0.079084</v>
       </c>
       <c r="D162" t="n">
-        <v>2660.71323</v>
+        <v>0.141759</v>
       </c>
       <c r="E162" t="n">
-        <v>2418.585817</v>
+        <v>0.08741500000000001</v>
       </c>
       <c r="F162" t="n">
-        <v>2536.58318</v>
+        <v>0.11245</v>
       </c>
       <c r="G162" t="n">
-        <v>1626.27787</v>
+        <v>0.085339</v>
       </c>
       <c r="H162" t="n">
-        <v>2322.683934</v>
+        <v>0.112254</v>
       </c>
       <c r="I162" t="n">
-        <v>3746.304241</v>
+        <v>0.196656</v>
       </c>
       <c r="J162" t="n">
-        <v>3890.220374</v>
+        <v>0.059169</v>
+      </c>
+      <c r="K162" t="n">
+        <v>0.185474</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>電機機械平上櫃</t>
+          <t>電腦及週邊設備業右上上市</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>0.81758</v>
+        <v>39388.800034</v>
       </c>
       <c r="C163" t="n">
-        <v>0.155259</v>
+        <v>45205.936905</v>
       </c>
       <c r="D163" t="n">
-        <v>0.127739</v>
+        <v>50654.030068</v>
       </c>
       <c r="E163" t="n">
-        <v>0.081984</v>
+        <v>35359.84671</v>
       </c>
       <c r="F163" t="n">
-        <v>0.084762</v>
+        <v>55753.091306</v>
       </c>
       <c r="G163" t="n">
-        <v>0.158662</v>
+        <v>42056.973253</v>
       </c>
       <c r="H163" t="n">
-        <v>0.106951</v>
+        <v>37134.374792</v>
       </c>
       <c r="I163" t="n">
-        <v>0.103865</v>
+        <v>45284.793045</v>
       </c>
       <c r="J163" t="n">
-        <v>0.052421</v>
+        <v>52953.900936</v>
+      </c>
+      <c r="K163" t="n">
+        <v>35158.19108</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上上市</t>
+          <t>電腦及週邊設備業右上上櫃</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>31285.393991</v>
+        <v>10.27295</v>
       </c>
       <c r="C164" t="n">
-        <v>43834.111024</v>
+        <v>5.087297</v>
       </c>
       <c r="D164" t="n">
-        <v>38144.865106</v>
+        <v>8.945174</v>
       </c>
       <c r="E164" t="n">
-        <v>42702.884281</v>
+        <v>8.168549000000001</v>
       </c>
       <c r="F164" t="n">
-        <v>38943.162022</v>
+        <v>6.122937</v>
       </c>
       <c r="G164" t="n">
-        <v>57013.387679</v>
+        <v>4.828848</v>
       </c>
       <c r="H164" t="n">
-        <v>41469.300152</v>
+        <v>4.39085</v>
       </c>
       <c r="I164" t="n">
-        <v>41967.279919</v>
+        <v>3.992018</v>
       </c>
       <c r="J164" t="n">
-        <v>33540.564254</v>
+        <v>4.706055</v>
+      </c>
+      <c r="K164" t="n">
+        <v>6.825057</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上上櫃</t>
+          <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>3.286976</v>
+        <v>6376.132278</v>
       </c>
       <c r="C165" t="n">
-        <v>5.63341</v>
+        <v>7454.907283</v>
       </c>
       <c r="D165" t="n">
-        <v>7.647517</v>
+        <v>7250.317126</v>
       </c>
       <c r="E165" t="n">
-        <v>4.386462</v>
+        <v>17358.622509</v>
       </c>
       <c r="F165" t="n">
-        <v>3.744373</v>
+        <v>20500.120576</v>
       </c>
       <c r="G165" t="n">
-        <v>4.552767</v>
+        <v>26410.760531</v>
       </c>
       <c r="H165" t="n">
-        <v>9.666439</v>
+        <v>13215.001859</v>
       </c>
       <c r="I165" t="n">
-        <v>5.359016</v>
+        <v>10256.003434</v>
       </c>
       <c r="J165" t="n">
-        <v>8.512370000000001</v>
+        <v>12710.957755</v>
+      </c>
+      <c r="K165" t="n">
+        <v>9663.959551</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上市</t>
+          <t>電腦及週邊設備業右下上櫃</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>8372.407546</v>
+        <v>0.347794</v>
       </c>
       <c r="C166" t="n">
-        <v>5011.133429</v>
+        <v>0.356732</v>
       </c>
       <c r="D166" t="n">
-        <v>9046.637635999999</v>
+        <v>0.662868</v>
       </c>
       <c r="E166" t="n">
-        <v>6167.77495</v>
+        <v>0.51947</v>
       </c>
       <c r="F166" t="n">
-        <v>7418.865709</v>
+        <v>0.265974</v>
       </c>
       <c r="G166" t="n">
-        <v>12062.739108</v>
+        <v>0.253577</v>
       </c>
       <c r="H166" t="n">
-        <v>15563.819925</v>
+        <v>0.238332</v>
       </c>
       <c r="I166" t="n">
-        <v>11608.621111</v>
+        <v>0.12927775</v>
       </c>
       <c r="J166" t="n">
-        <v>8102.186924</v>
+        <v>0.120142</v>
+      </c>
+      <c r="K166" t="n">
+        <v>0.337804</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上櫃</t>
+          <t>電腦及週邊設備業平上市</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>0.087995</v>
+        <v>3203.289644</v>
       </c>
       <c r="C167" t="n">
-        <v>0.151576</v>
+        <v>3363.930259</v>
       </c>
       <c r="D167" t="n">
-        <v>0.163469</v>
+        <v>3590.364343</v>
       </c>
       <c r="E167" t="n">
-        <v>0.09155199999999999</v>
+        <v>2810.956448</v>
       </c>
       <c r="F167" t="n">
-        <v>0.15035425</v>
+        <v>3850.866249</v>
       </c>
       <c r="G167" t="n">
-        <v>0.321696</v>
+        <v>2010.607199</v>
       </c>
       <c r="H167" t="n">
-        <v>0.144102</v>
+        <v>1849.664547</v>
       </c>
       <c r="I167" t="n">
-        <v>0.123032</v>
+        <v>1437.304534</v>
       </c>
       <c r="J167" t="n">
-        <v>0.150653</v>
+        <v>2068.85697</v>
+      </c>
+      <c r="K167" t="n">
+        <v>2373.833127</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上市</t>
+          <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>642.189541</v>
+        <v>0.06085</v>
       </c>
       <c r="C168" t="n">
-        <v>458.611679</v>
+        <v>0.311449</v>
       </c>
       <c r="D168" t="n">
-        <v>610.820832</v>
+        <v>0.028226</v>
       </c>
       <c r="E168" t="n">
-        <v>904.703303</v>
+        <v>0.307002</v>
       </c>
       <c r="F168" t="n">
-        <v>424.428801</v>
+        <v>1.867231</v>
       </c>
       <c r="G168" t="n">
-        <v>1343.399804</v>
+        <v>0.8304</v>
       </c>
       <c r="H168" t="n">
-        <v>468.411875</v>
+        <v>1.067919</v>
       </c>
       <c r="I168" t="n">
-        <v>903.343404</v>
+        <v>1.006393</v>
       </c>
       <c r="J168" t="n">
-        <v>7325.470778</v>
+        <v>1.488073</v>
+      </c>
+      <c r="K168" t="n">
+        <v>1.226363</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上櫃</t>
+          <t>食品工業右上上市</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>1.472591</v>
+        <v>10.297645</v>
       </c>
       <c r="C169" t="n">
-        <v>1.429916</v>
+        <v>15.193654</v>
       </c>
       <c r="D169" t="n">
-        <v>1.54623</v>
+        <v>26.352452</v>
       </c>
       <c r="E169" t="n">
-        <v>0.896875</v>
+        <v>1239.642301</v>
       </c>
       <c r="F169" t="n">
-        <v>1.494557</v>
+        <v>3139.295951</v>
       </c>
       <c r="G169" t="n">
-        <v>1.832703</v>
+        <v>1291.778888</v>
       </c>
       <c r="H169" t="n">
-        <v>2.195671</v>
+        <v>1359.323921</v>
       </c>
       <c r="I169" t="n">
-        <v>1.959908</v>
+        <v>839.6985069999999</v>
       </c>
       <c r="J169" t="n">
-        <v>2.018571</v>
+        <v>894.768297</v>
+      </c>
+      <c r="K169" t="n">
+        <v>815.884941</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>食品工業右上上市</t>
+          <t>食品工業右上上櫃</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>7.264615</v>
+        <v>0.007553</v>
       </c>
       <c r="C170" t="n">
-        <v>8.02271</v>
+        <v>0.003842</v>
       </c>
       <c r="D170" t="n">
-        <v>11.865974</v>
+        <v>0.000674</v>
       </c>
       <c r="E170" t="n">
-        <v>16.580074</v>
+        <v>0.008137999999999999</v>
       </c>
       <c r="F170" t="n">
-        <v>7.674888</v>
+        <v>0.022387</v>
       </c>
       <c r="G170" t="n">
-        <v>9.180273</v>
+        <v>0.001583</v>
       </c>
       <c r="H170" t="n">
-        <v>15.211594</v>
+        <v>0.002333</v>
       </c>
       <c r="I170" t="n">
-        <v>1185.560206</v>
+        <v>0.001329</v>
       </c>
       <c r="J170" t="n">
-        <v>780.105951</v>
+        <v>0.001477</v>
+      </c>
+      <c r="K170" t="n">
+        <v>0.001331</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t>食品工業右上上櫃</t>
+          <t>食品工業右下上市</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0.001886</v>
+        <v>269.747139</v>
       </c>
       <c r="C171" t="n">
-        <v>0.003556</v>
+        <v>297.366972</v>
       </c>
       <c r="D171" t="n">
-        <v>0.004412</v>
+        <v>405.043226</v>
       </c>
       <c r="E171" t="n">
-        <v>0.005225</v>
+        <v>385.907919</v>
       </c>
       <c r="F171" t="n">
-        <v>0.005884</v>
+        <v>551.697779</v>
       </c>
       <c r="G171" t="n">
-        <v>0.005327</v>
+        <v>297.861558</v>
       </c>
       <c r="H171" t="n">
-        <v>0.00641</v>
+        <v>319.044069</v>
       </c>
       <c r="I171" t="n">
-        <v>0.00389</v>
+        <v>351.382043</v>
       </c>
       <c r="J171" t="n">
-        <v>0.003337</v>
+        <v>245.046335</v>
+      </c>
+      <c r="K171" t="n">
+        <v>200.925126</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t>食品工業右下上市</t>
+          <t>食品工業右下上櫃</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>286.797627</v>
+        <v>0.014538</v>
       </c>
       <c r="C172" t="n">
-        <v>318.886002</v>
+        <v>0.010585</v>
       </c>
       <c r="D172" t="n">
-        <v>261.472583</v>
+        <v>0.012698</v>
       </c>
       <c r="E172" t="n">
-        <v>264.272879</v>
+        <v>0.008316</v>
       </c>
       <c r="F172" t="n">
-        <v>1688.815661</v>
+        <v>0.013137</v>
       </c>
       <c r="G172" t="n">
-        <v>1095.910492</v>
+        <v>0.006357</v>
       </c>
       <c r="H172" t="n">
-        <v>307.941446</v>
+        <v>0.021946</v>
       </c>
       <c r="I172" t="n">
-        <v>238.762793</v>
+        <v>0.01032</v>
       </c>
       <c r="J172" t="n">
-        <v>269.747139</v>
+        <v>0.007833</v>
+      </c>
+      <c r="K172" t="n">
+        <v>0.012781</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
         <is>
-          <t>食品工業右下上櫃</t>
+          <t>食品工業平上市</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>0.010856</v>
+        <v>773.6783349999999</v>
       </c>
       <c r="C173" t="n">
-        <v>0.005911</v>
+        <v>753.666049</v>
       </c>
       <c r="D173" t="n">
-        <v>0.010054</v>
-      </c>
-      <c r="E173" t="n">
-        <v>0.006973</v>
-      </c>
-      <c r="F173" t="n">
-        <v>0.010705</v>
-      </c>
-      <c r="G173" t="n">
-        <v>0.016031</v>
-      </c>
-      <c r="H173" t="n">
-        <v>0.010104</v>
-      </c>
-      <c r="I173" t="n">
-        <v>0.017923</v>
-      </c>
+        <v>1312.629839</v>
+      </c>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
       <c r="J173" t="n">
-        <v>0.014538</v>
-      </c>
+        <v>0.735418</v>
+      </c>
+      <c r="K173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
         <is>
-          <t>食品工業平上市</t>
+          <t>食品工業平上櫃</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>373.919301</v>
+        <v>0.001103</v>
       </c>
       <c r="C174" t="n">
-        <v>490.134677</v>
+        <v>0.000891</v>
       </c>
       <c r="D174" t="n">
-        <v>526.461753</v>
+        <v>0.001254</v>
       </c>
       <c r="E174" t="n">
-        <v>441.182343</v>
+        <v>0.003657</v>
       </c>
       <c r="F174" t="n">
-        <v>5.599845</v>
+        <v>0.003119</v>
       </c>
       <c r="G174" t="n">
-        <v>7.511816</v>
+        <v>0.011346</v>
       </c>
       <c r="H174" t="n">
-        <v>949.30633</v>
+        <v>0.002022</v>
       </c>
       <c r="I174" t="n">
-        <v>5.286877</v>
+        <v>0.001098</v>
       </c>
       <c r="J174" t="n">
-        <v>3.870029</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="1" t="inlineStr">
-        <is>
-          <t>食品工業平上櫃</t>
-        </is>
-      </c>
-      <c r="B175" t="n">
-        <v>0.004609</v>
-      </c>
-      <c r="C175" t="n">
-        <v>0.003325</v>
-      </c>
-      <c r="D175" t="n">
-        <v>0.0007</v>
-      </c>
-      <c r="E175" t="n">
-        <v>0.001953</v>
-      </c>
-      <c r="F175" t="n">
-        <v>0.001035</v>
-      </c>
-      <c r="G175" t="n">
-        <v>0.002899</v>
-      </c>
-      <c r="H175" t="n">
-        <v>0.007135</v>
-      </c>
-      <c r="I175" t="n">
-        <v>0.002992</v>
-      </c>
-      <c r="J175" t="n">
-        <v>0.005319</v>
+        <v>0.004141</v>
+      </c>
+      <c r="K174" t="n">
+        <v>0.000752</v>
       </c>
     </row>
   </sheetData>

--- a/Result/analyze_2.xlsx
+++ b/Result/analyze_2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K174"/>
+  <dimension ref="A1:J174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,52 +436,47 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -492,34 +487,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48181.200738</v>
+        <v>88885.523634</v>
       </c>
       <c r="C2" t="n">
-        <v>87072.641175</v>
+        <v>92586.35597600001</v>
       </c>
       <c r="D2" t="n">
-        <v>101424.550246</v>
+        <v>54637.518222</v>
       </c>
       <c r="E2" t="n">
-        <v>74826.461972</v>
+        <v>65405.359272</v>
       </c>
       <c r="F2" t="n">
-        <v>88885.523634</v>
+        <v>64353.140658</v>
       </c>
       <c r="G2" t="n">
-        <v>92586.35597600001</v>
+        <v>70386.353499</v>
       </c>
       <c r="H2" t="n">
-        <v>54637.518222</v>
+        <v>63260.686172</v>
       </c>
       <c r="I2" t="n">
-        <v>65405.359272</v>
+        <v>50896.278191</v>
       </c>
       <c r="J2" t="n">
-        <v>64353.140658</v>
-      </c>
-      <c r="K2" t="n">
-        <v>70386.353499</v>
+        <v>65242.250565</v>
       </c>
     </row>
     <row r="3">
@@ -529,34 +521,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.778768</v>
+        <v>3.670187</v>
       </c>
       <c r="C3" t="n">
-        <v>4.866736</v>
+        <v>4.065067</v>
       </c>
       <c r="D3" t="n">
-        <v>4.473407</v>
+        <v>3.332657</v>
       </c>
       <c r="E3" t="n">
-        <v>5.485964</v>
+        <v>5.134843</v>
       </c>
       <c r="F3" t="n">
-        <v>3.670187</v>
+        <v>12.88341</v>
       </c>
       <c r="G3" t="n">
-        <v>4.065067</v>
+        <v>6.306559</v>
       </c>
       <c r="H3" t="n">
-        <v>3.332657</v>
+        <v>4.813261</v>
       </c>
       <c r="I3" t="n">
-        <v>5.134843</v>
+        <v>6.66071</v>
       </c>
       <c r="J3" t="n">
-        <v>12.88341</v>
-      </c>
-      <c r="K3" t="n">
-        <v>6.306559</v>
+        <v>2.920854</v>
       </c>
     </row>
     <row r="4">
@@ -566,34 +555,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>455.471706</v>
+        <v>1117.670322</v>
       </c>
       <c r="C4" t="n">
-        <v>418.86892</v>
+        <v>855.579436</v>
       </c>
       <c r="D4" t="n">
-        <v>1109.99311</v>
+        <v>767.424752</v>
       </c>
       <c r="E4" t="n">
-        <v>817.067633</v>
+        <v>741.0858030000001</v>
       </c>
       <c r="F4" t="n">
-        <v>1117.670322</v>
+        <v>968.803388</v>
       </c>
       <c r="G4" t="n">
-        <v>855.579436</v>
+        <v>780.990329</v>
       </c>
       <c r="H4" t="n">
-        <v>767.424752</v>
+        <v>844.191047</v>
       </c>
       <c r="I4" t="n">
-        <v>741.0858030000001</v>
+        <v>692.246384</v>
       </c>
       <c r="J4" t="n">
-        <v>968.803388</v>
-      </c>
-      <c r="K4" t="n">
-        <v>780.990329</v>
+        <v>802.887867</v>
       </c>
     </row>
     <row r="5">
@@ -603,34 +589,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.588751</v>
+        <v>1.450457</v>
       </c>
       <c r="C5" t="n">
-        <v>1.406122</v>
+        <v>2.381268</v>
       </c>
       <c r="D5" t="n">
-        <v>1.312462</v>
+        <v>1.721428</v>
       </c>
       <c r="E5" t="n">
-        <v>1.452728</v>
+        <v>1.167368</v>
       </c>
       <c r="F5" t="n">
-        <v>1.450457</v>
+        <v>1.082715</v>
       </c>
       <c r="G5" t="n">
-        <v>2.381268</v>
+        <v>1.167036</v>
       </c>
       <c r="H5" t="n">
-        <v>1.721428</v>
+        <v>2.00258975</v>
       </c>
       <c r="I5" t="n">
-        <v>1.167368</v>
+        <v>1.026739</v>
       </c>
       <c r="J5" t="n">
-        <v>1.082715</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1.167036</v>
+        <v>0.9920183333333333</v>
       </c>
     </row>
     <row r="6">
@@ -640,34 +623,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>735.095456</v>
+        <v>488.255341</v>
       </c>
       <c r="C6" t="n">
-        <v>804.510868</v>
+        <v>348.954905</v>
       </c>
       <c r="D6" t="n">
-        <v>202.725195</v>
+        <v>1521.70643</v>
       </c>
       <c r="E6" t="n">
-        <v>266.145606</v>
+        <v>756.272438</v>
       </c>
       <c r="F6" t="n">
-        <v>488.255341</v>
+        <v>1073.492406</v>
       </c>
       <c r="G6" t="n">
-        <v>348.954905</v>
+        <v>1162.39281</v>
       </c>
       <c r="H6" t="n">
-        <v>1521.70643</v>
+        <v>711.885295</v>
       </c>
       <c r="I6" t="n">
-        <v>756.272438</v>
+        <v>209.789512</v>
       </c>
       <c r="J6" t="n">
-        <v>1073.492406</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1162.39281</v>
+        <v>145.869244</v>
       </c>
     </row>
     <row r="7">
@@ -677,34 +657,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.231788</v>
+        <v>0.146814</v>
       </c>
       <c r="C7" t="n">
-        <v>0.115903</v>
+        <v>0.597955</v>
       </c>
       <c r="D7" t="n">
-        <v>0.184735</v>
+        <v>0.075878</v>
       </c>
       <c r="E7" t="n">
-        <v>0.144311</v>
+        <v>0.228206</v>
       </c>
       <c r="F7" t="n">
-        <v>0.146814</v>
+        <v>0.270917</v>
       </c>
       <c r="G7" t="n">
-        <v>0.597955</v>
+        <v>0.253571</v>
       </c>
       <c r="H7" t="n">
-        <v>0.075878</v>
+        <v>0.134186</v>
       </c>
       <c r="I7" t="n">
-        <v>0.228206</v>
+        <v>0.041858</v>
       </c>
       <c r="J7" t="n">
-        <v>0.270917</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.253571</v>
+        <v>0.097231</v>
       </c>
     </row>
     <row r="8">
@@ -714,34 +691,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>951.274139</v>
+        <v>980.069929</v>
       </c>
       <c r="C8" t="n">
-        <v>982.283182</v>
+        <v>926.218018</v>
       </c>
       <c r="D8" t="n">
-        <v>706.3377410000001</v>
+        <v>1063.032343</v>
       </c>
       <c r="E8" t="n">
-        <v>497.939169</v>
+        <v>1369.200591</v>
       </c>
       <c r="F8" t="n">
-        <v>980.069929</v>
+        <v>942.0624299999999</v>
       </c>
       <c r="G8" t="n">
-        <v>926.218018</v>
+        <v>895.523136</v>
       </c>
       <c r="H8" t="n">
-        <v>1063.032343</v>
+        <v>921.6118750000001</v>
       </c>
       <c r="I8" t="n">
-        <v>1369.200591</v>
+        <v>753.892984</v>
       </c>
       <c r="J8" t="n">
-        <v>942.0624299999999</v>
-      </c>
-      <c r="K8" t="n">
-        <v>895.523136</v>
+        <v>964.354775</v>
       </c>
     </row>
     <row r="9">
@@ -751,34 +725,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.858282</v>
+        <v>1.772869</v>
       </c>
       <c r="C9" t="n">
-        <v>1.4557415</v>
+        <v>2.490978</v>
       </c>
       <c r="D9" t="n">
-        <v>1.517993</v>
+        <v>1.17748075</v>
       </c>
       <c r="E9" t="n">
-        <v>2.403135</v>
+        <v>1.39837225</v>
       </c>
       <c r="F9" t="n">
-        <v>1.772869</v>
+        <v>1.435431</v>
       </c>
       <c r="G9" t="n">
-        <v>2.490978</v>
+        <v>2.181994</v>
       </c>
       <c r="H9" t="n">
-        <v>1.17748075</v>
+        <v>1.714407</v>
       </c>
       <c r="I9" t="n">
-        <v>1.39837225</v>
+        <v>1.99273</v>
       </c>
       <c r="J9" t="n">
-        <v>1.435431</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2.181994</v>
+        <v>2.127602</v>
       </c>
     </row>
     <row r="10">
@@ -788,34 +759,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>609.741537</v>
+        <v>2232.320575</v>
       </c>
       <c r="C10" t="n">
-        <v>994.0388809999999</v>
+        <v>1119.634381</v>
       </c>
       <c r="D10" t="n">
-        <v>977.807549</v>
+        <v>850.886402</v>
       </c>
       <c r="E10" t="n">
-        <v>1132.076528</v>
+        <v>720.495889</v>
       </c>
       <c r="F10" t="n">
-        <v>2232.320575</v>
+        <v>767.397998</v>
       </c>
       <c r="G10" t="n">
-        <v>1119.634381</v>
+        <v>882.20808</v>
       </c>
       <c r="H10" t="n">
-        <v>850.886402</v>
+        <v>1480.214998</v>
       </c>
       <c r="I10" t="n">
-        <v>720.495889</v>
+        <v>1079.407824</v>
       </c>
       <c r="J10" t="n">
-        <v>767.397998</v>
-      </c>
-      <c r="K10" t="n">
-        <v>882.20808</v>
+        <v>1085.078222</v>
       </c>
     </row>
     <row r="11">
@@ -825,34 +793,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.478104</v>
+        <v>0.7544403333333334</v>
       </c>
       <c r="C11" t="n">
-        <v>0.505336</v>
+        <v>0.600169</v>
       </c>
       <c r="D11" t="n">
-        <v>0.923007</v>
+        <v>1.807453</v>
       </c>
       <c r="E11" t="n">
-        <v>0.40590475</v>
+        <v>0.788442</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7544403333333334</v>
+        <v>0.49820625</v>
       </c>
       <c r="G11" t="n">
-        <v>0.600169</v>
+        <v>0.7551346666666666</v>
       </c>
       <c r="H11" t="n">
-        <v>1.807453</v>
+        <v>0.548862</v>
       </c>
       <c r="I11" t="n">
-        <v>0.788442</v>
+        <v>0.384309</v>
       </c>
       <c r="J11" t="n">
-        <v>0.49820625</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.7551346666666666</v>
+        <v>0.353765</v>
       </c>
     </row>
     <row r="12">
@@ -862,34 +827,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>389.21712</v>
+        <v>303.313328</v>
       </c>
       <c r="C12" t="n">
-        <v>174.528281</v>
+        <v>113.302968</v>
       </c>
       <c r="D12" t="n">
-        <v>572.380825</v>
+        <v>122.996559</v>
       </c>
       <c r="E12" t="n">
-        <v>331.512968</v>
+        <v>87.73246399999999</v>
       </c>
       <c r="F12" t="n">
-        <v>303.313328</v>
+        <v>301.656644</v>
       </c>
       <c r="G12" t="n">
-        <v>113.302968</v>
+        <v>222.464648</v>
       </c>
       <c r="H12" t="n">
-        <v>122.996559</v>
+        <v>745.438097</v>
       </c>
       <c r="I12" t="n">
-        <v>87.73246399999999</v>
+        <v>388.15968</v>
       </c>
       <c r="J12" t="n">
-        <v>301.656644</v>
-      </c>
-      <c r="K12" t="n">
-        <v>222.464648</v>
+        <v>299.604215</v>
       </c>
     </row>
     <row r="13">
@@ -899,34 +861,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1095105</v>
+        <v>0.062015</v>
       </c>
       <c r="C13" t="n">
-        <v>0.092378</v>
+        <v>0.059453</v>
       </c>
       <c r="D13" t="n">
-        <v>0.06740500000000001</v>
+        <v>0.046284</v>
       </c>
       <c r="E13" t="n">
-        <v>0.04596566666666666</v>
+        <v>0.035646</v>
       </c>
       <c r="F13" t="n">
-        <v>0.062015</v>
+        <v>0.044337</v>
       </c>
       <c r="G13" t="n">
-        <v>0.059453</v>
+        <v>0.065011</v>
       </c>
       <c r="H13" t="n">
-        <v>0.046284</v>
+        <v>0.04549533333333334</v>
       </c>
       <c r="I13" t="n">
-        <v>0.035646</v>
+        <v>0.030511</v>
       </c>
       <c r="J13" t="n">
-        <v>0.044337</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.065011</v>
+        <v>0.02172666666666667</v>
       </c>
     </row>
     <row r="14">
@@ -936,34 +895,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>35025.473962</v>
+        <v>38606.288991</v>
       </c>
       <c r="C14" t="n">
-        <v>34672.533649</v>
+        <v>33005.329183</v>
       </c>
       <c r="D14" t="n">
-        <v>34640.422918</v>
+        <v>31624.413326</v>
       </c>
       <c r="E14" t="n">
-        <v>28579.811562</v>
+        <v>25649.875489</v>
       </c>
       <c r="F14" t="n">
-        <v>38606.288991</v>
+        <v>36829.671726</v>
       </c>
       <c r="G14" t="n">
-        <v>33005.329183</v>
+        <v>24951.208776</v>
       </c>
       <c r="H14" t="n">
-        <v>31624.413326</v>
+        <v>31455.451221</v>
       </c>
       <c r="I14" t="n">
-        <v>25649.875489</v>
+        <v>33234.465186</v>
       </c>
       <c r="J14" t="n">
-        <v>36829.671726</v>
-      </c>
-      <c r="K14" t="n">
-        <v>24951.208776</v>
+        <v>16962.193849</v>
       </c>
     </row>
     <row r="15">
@@ -973,34 +929,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16.651599</v>
+        <v>9.192671000000001</v>
       </c>
       <c r="C15" t="n">
-        <v>10.828634</v>
+        <v>8.302375</v>
       </c>
       <c r="D15" t="n">
-        <v>10.220403</v>
+        <v>7.101097</v>
       </c>
       <c r="E15" t="n">
-        <v>8.537651</v>
+        <v>7.906817</v>
       </c>
       <c r="F15" t="n">
-        <v>9.192671000000001</v>
+        <v>11.450579</v>
       </c>
       <c r="G15" t="n">
-        <v>8.302375</v>
+        <v>9.621321999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>7.101097</v>
+        <v>6.884802</v>
       </c>
       <c r="I15" t="n">
-        <v>7.906817</v>
+        <v>7.866023</v>
       </c>
       <c r="J15" t="n">
-        <v>11.450579</v>
-      </c>
-      <c r="K15" t="n">
-        <v>9.621321999999999</v>
+        <v>10.947901</v>
       </c>
     </row>
     <row r="16">
@@ -1010,34 +963,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1023.459603</v>
+        <v>1229.037194</v>
       </c>
       <c r="C16" t="n">
-        <v>954.477749</v>
+        <v>592.8472839999999</v>
       </c>
       <c r="D16" t="n">
-        <v>904.9705740000001</v>
+        <v>1068.677673</v>
       </c>
       <c r="E16" t="n">
-        <v>955.47672</v>
+        <v>593.969129</v>
       </c>
       <c r="F16" t="n">
-        <v>1229.037194</v>
+        <v>760.486909</v>
       </c>
       <c r="G16" t="n">
-        <v>592.8472839999999</v>
+        <v>666.830693</v>
       </c>
       <c r="H16" t="n">
-        <v>1068.677673</v>
+        <v>491.303779</v>
       </c>
       <c r="I16" t="n">
-        <v>593.969129</v>
+        <v>1091.990231</v>
       </c>
       <c r="J16" t="n">
-        <v>760.486909</v>
-      </c>
-      <c r="K16" t="n">
-        <v>666.830693</v>
+        <v>697.4192420000001</v>
       </c>
     </row>
     <row r="17">
@@ -1047,34 +997,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.042913</v>
+        <v>0.09390900000000001</v>
       </c>
       <c r="C17" t="n">
-        <v>0.047639</v>
+        <v>0.070607</v>
       </c>
       <c r="D17" t="n">
-        <v>0.07234599999999999</v>
+        <v>0.058583</v>
       </c>
       <c r="E17" t="n">
-        <v>0.03776</v>
+        <v>0.047846</v>
       </c>
       <c r="F17" t="n">
-        <v>0.09390900000000001</v>
+        <v>0.036332</v>
       </c>
       <c r="G17" t="n">
-        <v>0.070607</v>
+        <v>0.056001</v>
       </c>
       <c r="H17" t="n">
-        <v>0.058583</v>
+        <v>0.07004000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>0.047846</v>
+        <v>0.053983</v>
       </c>
       <c r="J17" t="n">
-        <v>0.049209</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.056001</v>
+        <v>0.061414</v>
       </c>
     </row>
     <row r="18">
@@ -1084,34 +1031,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>504.04349</v>
+        <v>433.142001</v>
       </c>
       <c r="C18" t="n">
-        <v>486.994612</v>
+        <v>460.333694</v>
       </c>
       <c r="D18" t="n">
-        <v>394.909571</v>
+        <v>263.870993</v>
       </c>
       <c r="E18" t="n">
-        <v>390.909335</v>
+        <v>257.258089</v>
       </c>
       <c r="F18" t="n">
-        <v>433.142001</v>
+        <v>700.153453</v>
       </c>
       <c r="G18" t="n">
-        <v>460.333694</v>
+        <v>784.406296</v>
       </c>
       <c r="H18" t="n">
-        <v>263.870993</v>
+        <v>12293.964655</v>
       </c>
       <c r="I18" t="n">
-        <v>257.258089</v>
+        <v>620.030246</v>
       </c>
       <c r="J18" t="n">
-        <v>700.153453</v>
-      </c>
-      <c r="K18" t="n">
-        <v>784.406296</v>
+        <v>5728.311345</v>
       </c>
     </row>
     <row r="19">
@@ -1121,34 +1065,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.223928</v>
+        <v>0.421391</v>
       </c>
       <c r="C19" t="n">
-        <v>0.277059</v>
+        <v>0.666552</v>
       </c>
       <c r="D19" t="n">
-        <v>0.282796</v>
+        <v>2.212432</v>
       </c>
       <c r="E19" t="n">
-        <v>0.138331</v>
+        <v>1.201581</v>
       </c>
       <c r="F19" t="n">
-        <v>0.421391</v>
+        <v>1.264365</v>
       </c>
       <c r="G19" t="n">
-        <v>0.666552</v>
+        <v>1.633723</v>
       </c>
       <c r="H19" t="n">
-        <v>2.212432</v>
+        <v>2.234588</v>
       </c>
       <c r="I19" t="n">
-        <v>1.201581</v>
+        <v>1.350974</v>
       </c>
       <c r="J19" t="n">
-        <v>1.251488</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1.633723</v>
+        <v>1.513105</v>
       </c>
     </row>
     <row r="20">
@@ -1158,34 +1099,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>9372.369471</v>
+        <v>5661.701177</v>
       </c>
       <c r="C20" t="n">
-        <v>5795.358255</v>
+        <v>5259.441078</v>
       </c>
       <c r="D20" t="n">
-        <v>5553.061939</v>
+        <v>3353.306981</v>
       </c>
       <c r="E20" t="n">
-        <v>6898.458472</v>
+        <v>4705.864866</v>
       </c>
       <c r="F20" t="n">
-        <v>5661.701177</v>
+        <v>7314.547126</v>
       </c>
       <c r="G20" t="n">
-        <v>5259.441078</v>
+        <v>5379.148063</v>
       </c>
       <c r="H20" t="n">
-        <v>3353.306981</v>
+        <v>3940.727708</v>
       </c>
       <c r="I20" t="n">
-        <v>4705.864866</v>
+        <v>3494.887648</v>
       </c>
       <c r="J20" t="n">
-        <v>7314.547126</v>
-      </c>
-      <c r="K20" t="n">
-        <v>5379.148063</v>
+        <v>2587.82531</v>
       </c>
     </row>
     <row r="21">
@@ -1195,34 +1133,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.58366</v>
+        <v>0.407707</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5509770000000001</v>
+        <v>0.297397</v>
       </c>
       <c r="D21" t="n">
-        <v>0.480382</v>
+        <v>0.337121</v>
       </c>
       <c r="E21" t="n">
-        <v>0.411562</v>
+        <v>0.381888</v>
       </c>
       <c r="F21" t="n">
-        <v>0.407707</v>
+        <v>0.236467</v>
       </c>
       <c r="G21" t="n">
-        <v>0.297397</v>
+        <v>0.231797</v>
       </c>
       <c r="H21" t="n">
-        <v>0.337121</v>
+        <v>0.315485</v>
       </c>
       <c r="I21" t="n">
-        <v>0.381888</v>
+        <v>0.263044</v>
       </c>
       <c r="J21" t="n">
-        <v>0.236467</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.231797</v>
+        <v>0.348404</v>
       </c>
     </row>
     <row r="22">
@@ -1232,34 +1167,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>91.716739</v>
+        <v>173.457935</v>
       </c>
       <c r="C22" t="n">
-        <v>123.792569</v>
+        <v>96.576919</v>
       </c>
       <c r="D22" t="n">
-        <v>134.661671</v>
+        <v>134.912417</v>
       </c>
       <c r="E22" t="n">
-        <v>151.510135</v>
+        <v>136.023827</v>
       </c>
       <c r="F22" t="n">
-        <v>173.457935</v>
+        <v>109.538916</v>
       </c>
       <c r="G22" t="n">
-        <v>96.576919</v>
+        <v>91.082618</v>
       </c>
       <c r="H22" t="n">
-        <v>134.912417</v>
+        <v>312.011029</v>
       </c>
       <c r="I22" t="n">
-        <v>136.023827</v>
+        <v>112.827469</v>
       </c>
       <c r="J22" t="n">
-        <v>109.538916</v>
-      </c>
-      <c r="K22" t="n">
-        <v>91.082618</v>
+        <v>102.299707</v>
       </c>
     </row>
     <row r="23">
@@ -1269,34 +1201,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.048921</v>
+        <v>0.181323</v>
       </c>
       <c r="C23" t="n">
-        <v>0.016302</v>
+        <v>0.020694</v>
       </c>
       <c r="D23" t="n">
-        <v>0.246868</v>
+        <v>0.231682</v>
       </c>
       <c r="E23" t="n">
-        <v>0.032635</v>
+        <v>0.198653</v>
       </c>
       <c r="F23" t="n">
-        <v>0.181323</v>
+        <v>0.012894</v>
       </c>
       <c r="G23" t="n">
-        <v>0.020694</v>
+        <v>0.179984</v>
       </c>
       <c r="H23" t="n">
-        <v>0.231682</v>
+        <v>0.194294</v>
       </c>
       <c r="I23" t="n">
-        <v>0.198653</v>
+        <v>0.155027</v>
       </c>
       <c r="J23" t="n">
-        <v>0.012894</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0.179984</v>
+        <v>0.322795</v>
       </c>
     </row>
     <row r="24">
@@ -1306,34 +1235,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>481.318193</v>
+        <v>272.575433</v>
       </c>
       <c r="C24" t="n">
-        <v>322.691328</v>
+        <v>413.901252</v>
       </c>
       <c r="D24" t="n">
-        <v>254.539785</v>
+        <v>559.953737</v>
       </c>
       <c r="E24" t="n">
-        <v>184.41174</v>
+        <v>609.50382</v>
       </c>
       <c r="F24" t="n">
-        <v>272.575433</v>
+        <v>376.309095</v>
       </c>
       <c r="G24" t="n">
-        <v>413.901252</v>
+        <v>566.956783</v>
       </c>
       <c r="H24" t="n">
-        <v>559.953737</v>
+        <v>736.50087</v>
       </c>
       <c r="I24" t="n">
-        <v>609.50382</v>
+        <v>296.144729</v>
       </c>
       <c r="J24" t="n">
-        <v>376.309095</v>
-      </c>
-      <c r="K24" t="n">
-        <v>566.956783</v>
+        <v>337.969955</v>
       </c>
     </row>
     <row r="25">
@@ -1343,34 +1269,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.181165</v>
+        <v>0.069926</v>
       </c>
       <c r="C25" t="n">
-        <v>0.14632</v>
+        <v>0.167024</v>
       </c>
       <c r="D25" t="n">
-        <v>0.048634</v>
+        <v>0.037174</v>
       </c>
       <c r="E25" t="n">
-        <v>0.154381</v>
+        <v>0.02765</v>
       </c>
       <c r="F25" t="n">
-        <v>0.069926</v>
+        <v>0.287736</v>
       </c>
       <c r="G25" t="n">
-        <v>0.167024</v>
+        <v>0.19613</v>
       </c>
       <c r="H25" t="n">
-        <v>0.037174</v>
+        <v>0.112262</v>
       </c>
       <c r="I25" t="n">
-        <v>0.02765</v>
+        <v>0.129903</v>
       </c>
       <c r="J25" t="n">
-        <v>0.287736</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0.19613</v>
+        <v>0.117631</v>
       </c>
     </row>
     <row r="26">
@@ -1380,34 +1303,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>301007.353581</v>
+        <v>444793.551669</v>
       </c>
       <c r="C26" t="n">
-        <v>266223.514266</v>
+        <v>288293.793547</v>
       </c>
       <c r="D26" t="n">
-        <v>382668.06568</v>
+        <v>230232.353759</v>
       </c>
       <c r="E26" t="n">
-        <v>282986.660315</v>
+        <v>191182.562802</v>
       </c>
       <c r="F26" t="n">
-        <v>444793.551669</v>
+        <v>229960.560629</v>
       </c>
       <c r="G26" t="n">
-        <v>288293.793547</v>
+        <v>233466.654463</v>
       </c>
       <c r="H26" t="n">
-        <v>230232.353759</v>
+        <v>308962.846639</v>
       </c>
       <c r="I26" t="n">
-        <v>191182.562802</v>
+        <v>244308.296052</v>
       </c>
       <c r="J26" t="n">
-        <v>229960.560629</v>
-      </c>
-      <c r="K26" t="n">
-        <v>233466.654463</v>
+        <v>268263.36376</v>
       </c>
     </row>
     <row r="27">
@@ -1417,34 +1337,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>131.142732</v>
+        <v>110.047906</v>
       </c>
       <c r="C27" t="n">
-        <v>112.328491</v>
+        <v>88.645197</v>
       </c>
       <c r="D27" t="n">
-        <v>122.518992</v>
+        <v>76.91721200000001</v>
       </c>
       <c r="E27" t="n">
-        <v>94.45443299999999</v>
+        <v>72.951875</v>
       </c>
       <c r="F27" t="n">
-        <v>110.047906</v>
+        <v>68.364958</v>
       </c>
       <c r="G27" t="n">
-        <v>88.645197</v>
+        <v>73.215756</v>
       </c>
       <c r="H27" t="n">
-        <v>76.91721200000001</v>
+        <v>71.80018</v>
       </c>
       <c r="I27" t="n">
-        <v>72.951875</v>
+        <v>76.080887</v>
       </c>
       <c r="J27" t="n">
-        <v>68.364958</v>
-      </c>
-      <c r="K27" t="n">
-        <v>73.215756</v>
+        <v>100.164704</v>
       </c>
     </row>
     <row r="28">
@@ -1454,34 +1371,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>860.014813</v>
+        <v>1207.303954</v>
       </c>
       <c r="C28" t="n">
-        <v>949.647206</v>
+        <v>797.577685</v>
       </c>
       <c r="D28" t="n">
-        <v>1120.753614</v>
+        <v>797.388914</v>
       </c>
       <c r="E28" t="n">
-        <v>783.0559500000001</v>
+        <v>592.914996</v>
       </c>
       <c r="F28" t="n">
-        <v>1207.303954</v>
+        <v>581.181292</v>
       </c>
       <c r="G28" t="n">
-        <v>797.577685</v>
+        <v>760.684691</v>
       </c>
       <c r="H28" t="n">
-        <v>797.388914</v>
+        <v>981.010322</v>
       </c>
       <c r="I28" t="n">
-        <v>592.914996</v>
+        <v>717.904361</v>
       </c>
       <c r="J28" t="n">
-        <v>581.181292</v>
-      </c>
-      <c r="K28" t="n">
-        <v>760.684691</v>
+        <v>442.591265</v>
       </c>
     </row>
     <row r="29">
@@ -1491,34 +1405,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5465680000000001</v>
+        <v>3.870842</v>
       </c>
       <c r="C29" t="n">
-        <v>1.25852</v>
+        <v>3.014909</v>
       </c>
       <c r="D29" t="n">
-        <v>3.43964375</v>
+        <v>2.798222</v>
       </c>
       <c r="E29" t="n">
-        <v>2.799962</v>
+        <v>1.916666</v>
       </c>
       <c r="F29" t="n">
-        <v>3.870842</v>
+        <v>1.346726</v>
       </c>
       <c r="G29" t="n">
-        <v>3.314639</v>
+        <v>2.065627</v>
       </c>
       <c r="H29" t="n">
-        <v>2.798222</v>
+        <v>3.594352</v>
       </c>
       <c r="I29" t="n">
-        <v>1.921964</v>
+        <v>1.656178</v>
       </c>
       <c r="J29" t="n">
-        <v>1.392017</v>
-      </c>
-      <c r="K29" t="n">
-        <v>2.065627</v>
+        <v>2.756974</v>
       </c>
     </row>
     <row r="30">
@@ -1528,34 +1439,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>7597.674652</v>
+        <v>22596.585642</v>
       </c>
       <c r="C30" t="n">
-        <v>2917.366962</v>
+        <v>16387.243</v>
       </c>
       <c r="D30" t="n">
-        <v>2308.976704</v>
+        <v>11929.565547</v>
       </c>
       <c r="E30" t="n">
-        <v>8542.126894999999</v>
+        <v>10260.117717</v>
       </c>
       <c r="F30" t="n">
-        <v>22596.585642</v>
+        <v>10867.276106</v>
       </c>
       <c r="G30" t="n">
-        <v>16387.243</v>
+        <v>13748.727764</v>
       </c>
       <c r="H30" t="n">
-        <v>11929.565547</v>
+        <v>14185.616342</v>
       </c>
       <c r="I30" t="n">
-        <v>10260.117717</v>
+        <v>6744.448743</v>
       </c>
       <c r="J30" t="n">
-        <v>10867.276106</v>
-      </c>
-      <c r="K30" t="n">
-        <v>13748.727764</v>
+        <v>14878.392181</v>
       </c>
     </row>
     <row r="31">
@@ -1565,34 +1473,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.320835</v>
+        <v>5.344747</v>
       </c>
       <c r="C31" t="n">
-        <v>4.32494</v>
+        <v>1.44076</v>
       </c>
       <c r="D31" t="n">
-        <v>1.249045</v>
+        <v>4.486392</v>
       </c>
       <c r="E31" t="n">
-        <v>0.5613050000000001</v>
+        <v>2.816332</v>
       </c>
       <c r="F31" t="n">
-        <v>5.344747</v>
+        <v>3.909387</v>
       </c>
       <c r="G31" t="n">
-        <v>1.14103</v>
+        <v>5.05311</v>
       </c>
       <c r="H31" t="n">
-        <v>4.486392</v>
+        <v>5.007019</v>
       </c>
       <c r="I31" t="n">
-        <v>2.811034</v>
+        <v>2.07001</v>
       </c>
       <c r="J31" t="n">
-        <v>3.864096</v>
-      </c>
-      <c r="K31" t="n">
-        <v>5.05311</v>
+        <v>3.3173</v>
       </c>
     </row>
     <row r="32">
@@ -1602,34 +1507,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>50101.503575</v>
+        <v>56568.545658</v>
       </c>
       <c r="C32" t="n">
-        <v>42180.98931</v>
+        <v>51459.656456</v>
       </c>
       <c r="D32" t="n">
-        <v>55899.029209</v>
+        <v>39037.126155</v>
       </c>
       <c r="E32" t="n">
-        <v>90999.25553900001</v>
+        <v>39486.980971</v>
       </c>
       <c r="F32" t="n">
-        <v>56568.545658</v>
+        <v>45724.884283</v>
       </c>
       <c r="G32" t="n">
-        <v>51459.656456</v>
+        <v>37322.962106</v>
       </c>
       <c r="H32" t="n">
-        <v>39037.126155</v>
+        <v>40553.402589</v>
       </c>
       <c r="I32" t="n">
-        <v>39486.980971</v>
+        <v>31571.572505</v>
       </c>
       <c r="J32" t="n">
-        <v>45724.884283</v>
-      </c>
-      <c r="K32" t="n">
-        <v>37322.962106</v>
+        <v>25206.100319</v>
       </c>
     </row>
     <row r="33">
@@ -1642,16 +1544,17 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="F33" t="n">
+        <v>0.002798</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.003253</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.000506</v>
+      </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="n">
-        <v>0.002798</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0.003253</v>
-      </c>
+      <c r="J33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -1660,34 +1563,31 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>15.404189</v>
+        <v>31.301015</v>
       </c>
       <c r="C34" t="n">
-        <v>16.601022</v>
+        <v>12.398804</v>
       </c>
       <c r="D34" t="n">
-        <v>23.758345</v>
+        <v>47.413407</v>
       </c>
       <c r="E34" t="n">
-        <v>33.668754</v>
+        <v>49.485111</v>
       </c>
       <c r="F34" t="n">
-        <v>31.301015</v>
+        <v>24.236528</v>
       </c>
       <c r="G34" t="n">
-        <v>12.398804</v>
+        <v>39.447818</v>
       </c>
       <c r="H34" t="n">
-        <v>47.413407</v>
+        <v>34.049065</v>
       </c>
       <c r="I34" t="n">
-        <v>49.485111</v>
+        <v>19.874418</v>
       </c>
       <c r="J34" t="n">
-        <v>24.236528</v>
-      </c>
-      <c r="K34" t="n">
-        <v>39.447818</v>
+        <v>20.940155</v>
       </c>
     </row>
     <row r="35">
@@ -1697,34 +1597,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.03893</v>
+        <v>0.023263</v>
       </c>
       <c r="C35" t="n">
-        <v>0.01564</v>
+        <v>0.018657</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0376</v>
+        <v>0.014902</v>
       </c>
       <c r="E35" t="n">
-        <v>0.015035</v>
+        <v>0.02465</v>
       </c>
       <c r="F35" t="n">
-        <v>0.023263</v>
+        <v>0.012504</v>
       </c>
       <c r="G35" t="n">
-        <v>0.018657</v>
+        <v>0.01397333333333333</v>
       </c>
       <c r="H35" t="n">
-        <v>0.014902</v>
+        <v>0.0117195</v>
       </c>
       <c r="I35" t="n">
-        <v>0.02465</v>
+        <v>0.0105355</v>
       </c>
       <c r="J35" t="n">
-        <v>0.012504</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0.01397333333333333</v>
+        <v>0.012004</v>
       </c>
     </row>
     <row r="36">
@@ -1734,34 +1631,31 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>41.081579</v>
+        <v>162.490625</v>
       </c>
       <c r="C36" t="n">
-        <v>35.111708</v>
+        <v>41.126397</v>
       </c>
       <c r="D36" t="n">
-        <v>6.776158</v>
+        <v>40.174258</v>
       </c>
       <c r="E36" t="n">
-        <v>108.41809</v>
+        <v>54.384911</v>
       </c>
       <c r="F36" t="n">
-        <v>162.490625</v>
+        <v>55.723207</v>
       </c>
       <c r="G36" t="n">
-        <v>41.126397</v>
+        <v>61.02265</v>
       </c>
       <c r="H36" t="n">
-        <v>40.174258</v>
+        <v>130.571166</v>
       </c>
       <c r="I36" t="n">
-        <v>54.384911</v>
+        <v>62.995293</v>
       </c>
       <c r="J36" t="n">
-        <v>55.723207</v>
-      </c>
-      <c r="K36" t="n">
-        <v>61.02265</v>
+        <v>65.762333</v>
       </c>
     </row>
     <row r="37">
@@ -1771,34 +1665,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.000452</v>
+        <v>0.000437</v>
       </c>
       <c r="C37" t="n">
-        <v>0.000501</v>
+        <v>0.000169</v>
       </c>
       <c r="D37" t="n">
-        <v>0.000252</v>
+        <v>0.003312</v>
       </c>
       <c r="E37" t="n">
-        <v>0.000121</v>
+        <v>0.00536</v>
       </c>
       <c r="F37" t="n">
-        <v>0.000437</v>
+        <v>0.000182</v>
       </c>
       <c r="G37" t="n">
-        <v>0.000169</v>
+        <v>0.002672</v>
       </c>
       <c r="H37" t="n">
-        <v>0.003312</v>
+        <v>0.002798</v>
       </c>
       <c r="I37" t="n">
-        <v>0.00536</v>
+        <v>0.00166</v>
       </c>
       <c r="J37" t="n">
-        <v>0.000182</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0.002672</v>
+        <v>0.001193</v>
       </c>
     </row>
     <row r="38">
@@ -1807,32 +1698,27 @@
           <t>居家生活右上上櫃</t>
         </is>
       </c>
-      <c r="B38" t="n">
-        <v>0.00124</v>
-      </c>
+      <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>0.005921</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0.000149</v>
-      </c>
+        <v>0.000374</v>
+      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="n">
-        <v>0.000654</v>
-      </c>
-      <c r="F38" t="inlineStr"/>
+        <v>0.000566</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.000794</v>
+      </c>
       <c r="G38" t="n">
-        <v>0.000374</v>
-      </c>
-      <c r="H38" t="inlineStr"/>
+        <v>0.000838</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.000265</v>
+      </c>
       <c r="I38" t="n">
-        <v>0.000566</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0.000794</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0.000838</v>
-      </c>
+        <v>2.2e-05</v>
+      </c>
+      <c r="J38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
@@ -1841,34 +1727,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>112.086444</v>
+        <v>370.89283</v>
       </c>
       <c r="C39" t="n">
-        <v>218.849283</v>
+        <v>334.364303</v>
       </c>
       <c r="D39" t="n">
-        <v>45.219145</v>
+        <v>478.504812</v>
       </c>
       <c r="E39" t="n">
-        <v>333.169382</v>
+        <v>327.742795</v>
       </c>
       <c r="F39" t="n">
-        <v>370.89283</v>
+        <v>283.350769</v>
       </c>
       <c r="G39" t="n">
-        <v>334.364303</v>
+        <v>357.214741</v>
       </c>
       <c r="H39" t="n">
-        <v>478.504812</v>
+        <v>346.12963</v>
       </c>
       <c r="I39" t="n">
-        <v>327.742795</v>
+        <v>41.265267</v>
       </c>
       <c r="J39" t="n">
-        <v>283.350769</v>
-      </c>
-      <c r="K39" t="n">
-        <v>357.214741</v>
+        <v>242.77061</v>
       </c>
     </row>
     <row r="40">
@@ -1878,34 +1761,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.17568</v>
+        <v>0.681119</v>
       </c>
       <c r="C40" t="n">
-        <v>0.6648365000000001</v>
+        <v>0.551221</v>
       </c>
       <c r="D40" t="n">
-        <v>0.2781855</v>
+        <v>0.374704</v>
       </c>
       <c r="E40" t="n">
-        <v>0.1941435</v>
+        <v>0.15335</v>
       </c>
       <c r="F40" t="n">
-        <v>0.681119</v>
+        <v>0.254119</v>
       </c>
       <c r="G40" t="n">
-        <v>0.551221</v>
+        <v>0.377294</v>
       </c>
       <c r="H40" t="n">
-        <v>0.374704</v>
+        <v>0.286058</v>
       </c>
       <c r="I40" t="n">
-        <v>0.15335</v>
+        <v>0.328424</v>
       </c>
       <c r="J40" t="n">
-        <v>0.254119</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0.377294</v>
+        <v>0.18511</v>
       </c>
     </row>
     <row r="41">
@@ -1915,27 +1795,20 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.099395</v>
+        <v>0.151178</v>
       </c>
       <c r="C41" t="n">
-        <v>0.052789</v>
-      </c>
-      <c r="D41" t="n">
-        <v>175.402923</v>
-      </c>
-      <c r="E41" t="n">
-        <v>0.162383</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0.151178</v>
-      </c>
-      <c r="G41" t="n">
         <v>5.927249</v>
       </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="n">
+        <v>133.809475</v>
+      </c>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
@@ -1944,34 +1817,31 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.000398</v>
+        <v>0.001168</v>
       </c>
       <c r="C42" t="n">
-        <v>0.001559</v>
+        <v>0.005161</v>
       </c>
       <c r="D42" t="n">
-        <v>0.003731</v>
+        <v>0.000919</v>
       </c>
       <c r="E42" t="n">
-        <v>0.001263</v>
+        <v>2e-06</v>
       </c>
       <c r="F42" t="n">
-        <v>0.001168</v>
+        <v>1.525e-05</v>
       </c>
       <c r="G42" t="n">
-        <v>0.005161</v>
+        <v>0.00086</v>
       </c>
       <c r="H42" t="n">
-        <v>0.000919</v>
+        <v>0.0006089999999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>2e-06</v>
+        <v>0.000505</v>
       </c>
       <c r="J42" t="n">
-        <v>1.525e-05</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0.00086</v>
+        <v>0.0029015</v>
       </c>
     </row>
     <row r="43">
@@ -1981,34 +1851,31 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>99.41713900000001</v>
+        <v>183.641381</v>
       </c>
       <c r="C43" t="n">
-        <v>228.340317</v>
+        <v>119.483677</v>
       </c>
       <c r="D43" t="n">
-        <v>258.123264</v>
+        <v>155.635763</v>
       </c>
       <c r="E43" t="n">
-        <v>173.414347</v>
+        <v>94.819248</v>
       </c>
       <c r="F43" t="n">
-        <v>183.641381</v>
+        <v>106.908919</v>
       </c>
       <c r="G43" t="n">
-        <v>119.483677</v>
+        <v>150.02383</v>
       </c>
       <c r="H43" t="n">
-        <v>155.635763</v>
+        <v>799.2471839999999</v>
       </c>
       <c r="I43" t="n">
-        <v>94.819248</v>
+        <v>337.228122</v>
       </c>
       <c r="J43" t="n">
-        <v>106.908919</v>
-      </c>
-      <c r="K43" t="n">
-        <v>150.02383</v>
+        <v>199.92394</v>
       </c>
     </row>
     <row r="44">
@@ -2018,34 +1885,31 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.017281</v>
+        <v>0.015947</v>
       </c>
       <c r="C44" t="n">
-        <v>0.009006999999999999</v>
+        <v>0.017943</v>
       </c>
       <c r="D44" t="n">
-        <v>0.010999</v>
+        <v>0.010616</v>
       </c>
       <c r="E44" t="n">
-        <v>0.014612</v>
+        <v>0.007229</v>
       </c>
       <c r="F44" t="n">
-        <v>0.015947</v>
+        <v>0.008765999999999999</v>
       </c>
       <c r="G44" t="n">
-        <v>0.017943</v>
+        <v>0.0073135</v>
       </c>
       <c r="H44" t="n">
-        <v>0.010616</v>
+        <v>0.007417</v>
       </c>
       <c r="I44" t="n">
-        <v>0.007229</v>
+        <v>0.004086</v>
       </c>
       <c r="J44" t="n">
-        <v>0.008765999999999999</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0.0073135</v>
+        <v>0.015422</v>
       </c>
     </row>
     <row r="45">
@@ -2055,34 +1919,31 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>822.034456</v>
+        <v>1157.936493</v>
       </c>
       <c r="C45" t="n">
-        <v>594.209527</v>
+        <v>748.572722</v>
       </c>
       <c r="D45" t="n">
-        <v>1065.118136</v>
+        <v>636.517282</v>
       </c>
       <c r="E45" t="n">
-        <v>726.277963</v>
+        <v>630.8495809999999</v>
       </c>
       <c r="F45" t="n">
-        <v>1157.936493</v>
+        <v>517.395887</v>
       </c>
       <c r="G45" t="n">
-        <v>748.572722</v>
+        <v>645.389143</v>
       </c>
       <c r="H45" t="n">
-        <v>636.517282</v>
+        <v>1048.792221</v>
       </c>
       <c r="I45" t="n">
-        <v>630.8495809999999</v>
+        <v>1171.402774</v>
       </c>
       <c r="J45" t="n">
-        <v>517.395887</v>
-      </c>
-      <c r="K45" t="n">
-        <v>645.389143</v>
+        <v>842.821444</v>
       </c>
     </row>
     <row r="46">
@@ -2092,34 +1953,31 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.05922616666666666</v>
+        <v>0.081526</v>
       </c>
       <c r="C46" t="n">
-        <v>0.06313766666666666</v>
+        <v>0.049072</v>
       </c>
       <c r="D46" t="n">
-        <v>0.052888</v>
+        <v>0.056935</v>
       </c>
       <c r="E46" t="n">
-        <v>0.03973</v>
+        <v>0.036186</v>
       </c>
       <c r="F46" t="n">
-        <v>0.081526</v>
+        <v>0.035261</v>
       </c>
       <c r="G46" t="n">
-        <v>0.049072</v>
+        <v>0.056238</v>
       </c>
       <c r="H46" t="n">
-        <v>0.056935</v>
+        <v>0.0412595</v>
       </c>
       <c r="I46" t="n">
-        <v>0.036186</v>
+        <v>0.0347025</v>
       </c>
       <c r="J46" t="n">
-        <v>0.035261</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0.056238</v>
+        <v>0.06837500000000001</v>
       </c>
     </row>
     <row r="47">
@@ -2129,34 +1987,31 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>125.602681</v>
+        <v>140.201432</v>
       </c>
       <c r="C47" t="n">
-        <v>752.955744</v>
+        <v>53.098055</v>
       </c>
       <c r="D47" t="n">
-        <v>32.368992</v>
+        <v>495.524957</v>
       </c>
       <c r="E47" t="n">
-        <v>48.812522</v>
+        <v>372.014927</v>
       </c>
       <c r="F47" t="n">
-        <v>140.201432</v>
+        <v>384.266306</v>
       </c>
       <c r="G47" t="n">
-        <v>53.098055</v>
+        <v>428.254098</v>
       </c>
       <c r="H47" t="n">
-        <v>495.524957</v>
+        <v>1930.844136</v>
       </c>
       <c r="I47" t="n">
-        <v>372.014927</v>
+        <v>141.401506</v>
       </c>
       <c r="J47" t="n">
-        <v>384.266306</v>
-      </c>
-      <c r="K47" t="n">
-        <v>428.254098</v>
+        <v>30.078884</v>
       </c>
     </row>
     <row r="48">
@@ -2166,34 +2021,31 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.009823</v>
+        <v>0.009468000000000001</v>
       </c>
       <c r="C48" t="n">
-        <v>0.009965999999999999</v>
+        <v>0.005543</v>
       </c>
       <c r="D48" t="n">
-        <v>0.006973</v>
+        <v>0.004668</v>
       </c>
       <c r="E48" t="n">
-        <v>0.002181</v>
+        <v>0.001414</v>
       </c>
       <c r="F48" t="n">
-        <v>0.009468000000000001</v>
+        <v>0.00808</v>
       </c>
       <c r="G48" t="n">
-        <v>0.005543</v>
+        <v>0.004919</v>
       </c>
       <c r="H48" t="n">
-        <v>0.004668</v>
+        <v>0.004477</v>
       </c>
       <c r="I48" t="n">
-        <v>0.001414</v>
+        <v>0.001299</v>
       </c>
       <c r="J48" t="n">
-        <v>0.00808</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0.004919</v>
+        <v>0.00281825</v>
       </c>
     </row>
     <row r="49">
@@ -2203,34 +2055,31 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>38.724278</v>
+        <v>26.152505</v>
       </c>
       <c r="C49" t="n">
-        <v>23.253894</v>
+        <v>38.033875</v>
       </c>
       <c r="D49" t="n">
-        <v>69.83696999999999</v>
+        <v>38.339969</v>
       </c>
       <c r="E49" t="n">
-        <v>27.846748</v>
+        <v>129.269941</v>
       </c>
       <c r="F49" t="n">
-        <v>26.152505</v>
+        <v>385.506143</v>
       </c>
       <c r="G49" t="n">
-        <v>38.033875</v>
+        <v>312.441913</v>
       </c>
       <c r="H49" t="n">
-        <v>38.339969</v>
+        <v>183.41128</v>
       </c>
       <c r="I49" t="n">
-        <v>129.269941</v>
+        <v>167.431964</v>
       </c>
       <c r="J49" t="n">
-        <v>385.506143</v>
-      </c>
-      <c r="K49" t="n">
-        <v>312.441913</v>
+        <v>48.874291</v>
       </c>
     </row>
     <row r="50">
@@ -2240,34 +2089,31 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.671671</v>
+        <v>0.216161</v>
       </c>
       <c r="C50" t="n">
-        <v>0.218515</v>
+        <v>0.323812</v>
       </c>
       <c r="D50" t="n">
-        <v>0.424912</v>
+        <v>0.260287</v>
       </c>
       <c r="E50" t="n">
-        <v>0.2734</v>
+        <v>0.232099</v>
       </c>
       <c r="F50" t="n">
-        <v>0.216161</v>
+        <v>0.304774</v>
       </c>
       <c r="G50" t="n">
-        <v>0.323812</v>
+        <v>0.383423</v>
       </c>
       <c r="H50" t="n">
-        <v>0.260287</v>
+        <v>0.6482055</v>
       </c>
       <c r="I50" t="n">
-        <v>0.232099</v>
+        <v>0.509309</v>
       </c>
       <c r="J50" t="n">
-        <v>0.304774</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0.383423</v>
+        <v>0.381127</v>
       </c>
     </row>
     <row r="51">
@@ -2277,34 +2123,31 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>48.424674</v>
+        <v>109.863082</v>
       </c>
       <c r="C51" t="n">
-        <v>69.61456099999999</v>
+        <v>118.655546</v>
       </c>
       <c r="D51" t="n">
-        <v>64.845489</v>
+        <v>74.35132900000001</v>
       </c>
       <c r="E51" t="n">
-        <v>46.309135</v>
+        <v>51.034447</v>
       </c>
       <c r="F51" t="n">
-        <v>111.115525</v>
+        <v>36.921702</v>
       </c>
       <c r="G51" t="n">
-        <v>119.635095</v>
+        <v>83.705129</v>
       </c>
       <c r="H51" t="n">
-        <v>74.35132900000001</v>
+        <v>53.990394</v>
       </c>
       <c r="I51" t="n">
-        <v>51.034447</v>
+        <v>82.77434100000001</v>
       </c>
       <c r="J51" t="n">
-        <v>36.921702</v>
-      </c>
-      <c r="K51" t="n">
-        <v>83.705129</v>
+        <v>74.98517200000001</v>
       </c>
     </row>
     <row r="52">
@@ -2314,34 +2157,31 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.288828</v>
+        <v>0.316047</v>
       </c>
       <c r="C52" t="n">
-        <v>0.469014</v>
+        <v>0.3032035</v>
       </c>
       <c r="D52" t="n">
-        <v>0.520174</v>
+        <v>0.184877</v>
       </c>
       <c r="E52" t="n">
-        <v>0.23410225</v>
+        <v>0.165061</v>
       </c>
       <c r="F52" t="n">
-        <v>0.316047</v>
+        <v>0.3296095</v>
       </c>
       <c r="G52" t="n">
-        <v>0.3032035</v>
+        <v>0.263438</v>
       </c>
       <c r="H52" t="n">
-        <v>0.184877</v>
+        <v>0.163885</v>
       </c>
       <c r="I52" t="n">
-        <v>0.165061</v>
+        <v>0.108714</v>
       </c>
       <c r="J52" t="n">
-        <v>0.3296095</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0.263438</v>
+        <v>0.168217</v>
       </c>
     </row>
     <row r="53">
@@ -2351,34 +2191,31 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>39.334486</v>
+        <v>168.917668</v>
       </c>
       <c r="C53" t="n">
-        <v>39.982419</v>
+        <v>251.898712</v>
       </c>
       <c r="D53" t="n">
-        <v>53.018351</v>
+        <v>325.752664</v>
       </c>
       <c r="E53" t="n">
-        <v>98.42041399999999</v>
+        <v>232.060711</v>
       </c>
       <c r="F53" t="n">
-        <v>167.665225</v>
+        <v>78.332365</v>
       </c>
       <c r="G53" t="n">
-        <v>250.919163</v>
+        <v>224.088917</v>
       </c>
       <c r="H53" t="n">
-        <v>325.752664</v>
+        <v>240.919601</v>
       </c>
       <c r="I53" t="n">
-        <v>232.060711</v>
+        <v>49.473022</v>
       </c>
       <c r="J53" t="n">
-        <v>78.332365</v>
-      </c>
-      <c r="K53" t="n">
-        <v>224.088917</v>
+        <v>169.538055</v>
       </c>
     </row>
     <row r="54">
@@ -2388,34 +2225,31 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.000869</v>
+        <v>0.170077</v>
       </c>
       <c r="C54" t="n">
-        <v>0.001298</v>
+        <v>0.182745</v>
       </c>
       <c r="D54" t="n">
-        <v>0.001023</v>
+        <v>0.479193</v>
       </c>
       <c r="E54" t="n">
-        <v>0.0008</v>
+        <v>0.237065</v>
       </c>
       <c r="F54" t="n">
-        <v>0.170077</v>
+        <v>0.001109</v>
       </c>
       <c r="G54" t="n">
-        <v>0.182745</v>
+        <v>0.891181</v>
       </c>
       <c r="H54" t="n">
-        <v>0.479193</v>
+        <v>0.041797</v>
       </c>
       <c r="I54" t="n">
-        <v>0.237065</v>
+        <v>0.04179</v>
       </c>
       <c r="J54" t="n">
-        <v>0.001109</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0.891181</v>
+        <v>0.001458</v>
       </c>
     </row>
     <row r="55">
@@ -2425,32 +2259,29 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.835421</v>
+        <v>2.493209</v>
       </c>
       <c r="C55" t="n">
-        <v>1.651831</v>
-      </c>
-      <c r="D55" t="n">
-        <v>1.495517</v>
-      </c>
+        <v>2.770772</v>
+      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="n">
-        <v>1.981826</v>
+        <v>0.001327</v>
       </c>
       <c r="F55" t="n">
-        <v>2.493209</v>
+        <v>0.000384</v>
       </c>
       <c r="G55" t="n">
-        <v>2.770772</v>
-      </c>
-      <c r="H55" t="inlineStr"/>
+        <v>1.014694</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.794714</v>
+      </c>
       <c r="I55" t="n">
-        <v>0.001327</v>
+        <v>1.099012</v>
       </c>
       <c r="J55" t="n">
-        <v>0.000384</v>
-      </c>
-      <c r="K55" t="n">
-        <v>1.014694</v>
+        <v>1.267572</v>
       </c>
     </row>
     <row r="56">
@@ -2460,34 +2291,31 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.06775100000000001</v>
+        <v>0.09723825</v>
       </c>
       <c r="C56" t="n">
-        <v>0.13099975</v>
+        <v>0.060699</v>
       </c>
       <c r="D56" t="n">
-        <v>0.1751533333333334</v>
+        <v>0.06481525</v>
       </c>
       <c r="E56" t="n">
-        <v>0.08835850000000001</v>
+        <v>0.05732625</v>
       </c>
       <c r="F56" t="n">
-        <v>0.09723825</v>
+        <v>0.066925</v>
       </c>
       <c r="G56" t="n">
-        <v>0.060699</v>
+        <v>0.07106899999999999</v>
       </c>
       <c r="H56" t="n">
-        <v>0.06481525</v>
+        <v>0.07862325000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>0.05732625</v>
+        <v>0.043873</v>
       </c>
       <c r="J56" t="n">
-        <v>0.066925</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0.07106899999999999</v>
+        <v>0.07008733333333333</v>
       </c>
     </row>
     <row r="57">
@@ -2497,34 +2325,31 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.090199</v>
+        <v>0.040001</v>
       </c>
       <c r="C57" t="n">
-        <v>0.000243</v>
+        <v>0.002196</v>
       </c>
       <c r="D57" t="n">
-        <v>0.000547</v>
+        <v>1.407788</v>
       </c>
       <c r="E57" t="n">
-        <v>0.001062</v>
+        <v>1.261628</v>
       </c>
       <c r="F57" t="n">
-        <v>0.040001</v>
+        <v>0.914431</v>
       </c>
       <c r="G57" t="n">
-        <v>0.002196</v>
+        <v>0.00028</v>
       </c>
       <c r="H57" t="n">
-        <v>1.407788</v>
+        <v>0.000842</v>
       </c>
       <c r="I57" t="n">
-        <v>1.261628</v>
+        <v>0.000733</v>
       </c>
       <c r="J57" t="n">
-        <v>0.914431</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0.00028</v>
+        <v>0.000552</v>
       </c>
     </row>
     <row r="58">
@@ -2534,34 +2359,31 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>340.685002</v>
+        <v>256.784831</v>
       </c>
       <c r="C58" t="n">
-        <v>409.85475</v>
+        <v>120.587872</v>
       </c>
       <c r="D58" t="n">
-        <v>190.591132</v>
+        <v>127.325474</v>
       </c>
       <c r="E58" t="n">
-        <v>326.506455</v>
+        <v>98.65007799999999</v>
       </c>
       <c r="F58" t="n">
-        <v>256.784831</v>
+        <v>121.043682</v>
       </c>
       <c r="G58" t="n">
-        <v>120.587872</v>
+        <v>114.620812</v>
       </c>
       <c r="H58" t="n">
-        <v>127.325474</v>
+        <v>118.910286</v>
       </c>
       <c r="I58" t="n">
-        <v>98.65007799999999</v>
+        <v>79.813745</v>
       </c>
       <c r="J58" t="n">
-        <v>121.043682</v>
-      </c>
-      <c r="K58" t="n">
-        <v>114.620812</v>
+        <v>85.495721</v>
       </c>
     </row>
     <row r="59">
@@ -2571,34 +2393,31 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>217.105003</v>
+        <v>577.052413</v>
       </c>
       <c r="C59" t="n">
-        <v>176.797709</v>
+        <v>95.38098100000001</v>
       </c>
       <c r="D59" t="n">
-        <v>217.899501</v>
+        <v>347.636927</v>
       </c>
       <c r="E59" t="n">
-        <v>365.805861</v>
+        <v>256.729258</v>
       </c>
       <c r="F59" t="n">
-        <v>577.052413</v>
+        <v>206.727109</v>
       </c>
       <c r="G59" t="n">
-        <v>95.38098100000001</v>
+        <v>193.267517</v>
       </c>
       <c r="H59" t="n">
-        <v>347.636927</v>
+        <v>743.324956</v>
       </c>
       <c r="I59" t="n">
-        <v>256.729258</v>
+        <v>301.451556</v>
       </c>
       <c r="J59" t="n">
-        <v>206.727109</v>
-      </c>
-      <c r="K59" t="n">
-        <v>193.267517</v>
+        <v>161.461116</v>
       </c>
     </row>
     <row r="60">
@@ -2608,29 +2427,26 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1.906604</v>
+        <v>1.16153</v>
       </c>
       <c r="C60" t="n">
-        <v>4.559692</v>
-      </c>
-      <c r="D60" t="n">
-        <v>3.426164</v>
-      </c>
+        <v>445.658223</v>
+      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="n">
-        <v>1.569808</v>
-      </c>
-      <c r="F60" t="n">
-        <v>1.16153</v>
-      </c>
-      <c r="G60" t="n">
-        <v>445.658223</v>
-      </c>
-      <c r="H60" t="inlineStr"/>
+        <v>1.439041</v>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="n">
+        <v>66.61608699999999</v>
+      </c>
       <c r="I60" t="n">
-        <v>1.439041</v>
-      </c>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
+        <v>19.359458</v>
+      </c>
+      <c r="J60" t="n">
+        <v>26.404941</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
@@ -2639,34 +2455,31 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>851.041282</v>
+        <v>1131.441578</v>
       </c>
       <c r="C61" t="n">
-        <v>3440.262713</v>
+        <v>1574.086796</v>
       </c>
       <c r="D61" t="n">
-        <v>1459.107193</v>
+        <v>804.543034</v>
       </c>
       <c r="E61" t="n">
-        <v>2191.943596</v>
+        <v>894.802743</v>
       </c>
       <c r="F61" t="n">
-        <v>1131.441578</v>
+        <v>799.8201350000001</v>
       </c>
       <c r="G61" t="n">
-        <v>1574.086796</v>
+        <v>3345.855402</v>
       </c>
       <c r="H61" t="n">
-        <v>804.543034</v>
+        <v>1734.701539</v>
       </c>
       <c r="I61" t="n">
-        <v>894.802743</v>
+        <v>1010.555188</v>
       </c>
       <c r="J61" t="n">
-        <v>799.8201350000001</v>
-      </c>
-      <c r="K61" t="n">
-        <v>3345.855402</v>
+        <v>896.876493</v>
       </c>
     </row>
     <row r="62">
@@ -2676,34 +2489,31 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>14.150035</v>
+        <v>29.200467</v>
       </c>
       <c r="C62" t="n">
-        <v>25.917989</v>
+        <v>21.43664</v>
       </c>
       <c r="D62" t="n">
-        <v>30.703446</v>
+        <v>26.94314</v>
       </c>
       <c r="E62" t="n">
-        <v>21.030979</v>
+        <v>17.410946</v>
       </c>
       <c r="F62" t="n">
-        <v>29.200467</v>
+        <v>17.89129</v>
       </c>
       <c r="G62" t="n">
-        <v>21.43664</v>
+        <v>16.365514</v>
       </c>
       <c r="H62" t="n">
-        <v>26.94314</v>
+        <v>26.037335</v>
       </c>
       <c r="I62" t="n">
-        <v>17.410946</v>
+        <v>12.677953</v>
       </c>
       <c r="J62" t="n">
-        <v>17.89129</v>
-      </c>
-      <c r="K62" t="n">
-        <v>16.365514</v>
+        <v>12.545816</v>
       </c>
     </row>
     <row r="63">
@@ -2713,34 +2523,31 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>390.153035</v>
+        <v>507.826902</v>
       </c>
       <c r="C63" t="n">
-        <v>212.902267</v>
+        <v>310.82796</v>
       </c>
       <c r="D63" t="n">
-        <v>292.80074</v>
+        <v>274.869932</v>
       </c>
       <c r="E63" t="n">
-        <v>263.684776</v>
+        <v>290.659288</v>
       </c>
       <c r="F63" t="n">
-        <v>507.826902</v>
+        <v>164.303141</v>
       </c>
       <c r="G63" t="n">
-        <v>310.82796</v>
+        <v>14.864183</v>
       </c>
       <c r="H63" t="n">
-        <v>274.869932</v>
+        <v>10.761111</v>
       </c>
       <c r="I63" t="n">
-        <v>290.659288</v>
+        <v>258.908291</v>
       </c>
       <c r="J63" t="n">
-        <v>164.303141</v>
-      </c>
-      <c r="K63" t="n">
-        <v>14.864183</v>
+        <v>214.244431</v>
       </c>
     </row>
     <row r="64">
@@ -2750,34 +2557,31 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2426.643378</v>
+        <v>1244.79658</v>
       </c>
       <c r="C64" t="n">
-        <v>1540.818611</v>
+        <v>1001.21699</v>
       </c>
       <c r="D64" t="n">
-        <v>1935.242207</v>
+        <v>859.27977</v>
       </c>
       <c r="E64" t="n">
-        <v>1557.773388</v>
+        <v>1130.074831</v>
       </c>
       <c r="F64" t="n">
-        <v>1244.79658</v>
+        <v>773.779114</v>
       </c>
       <c r="G64" t="n">
-        <v>1001.21699</v>
+        <v>771.234021</v>
       </c>
       <c r="H64" t="n">
-        <v>859.27977</v>
+        <v>686.1653240000001</v>
       </c>
       <c r="I64" t="n">
-        <v>1130.074831</v>
+        <v>479.471548</v>
       </c>
       <c r="J64" t="n">
-        <v>773.779114</v>
-      </c>
-      <c r="K64" t="n">
-        <v>771.234021</v>
+        <v>513.407341</v>
       </c>
     </row>
     <row r="65">
@@ -2787,34 +2591,31 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>570.641566</v>
+        <v>787.909998</v>
       </c>
       <c r="C65" t="n">
-        <v>542.7140900000001</v>
+        <v>631.922905</v>
       </c>
       <c r="D65" t="n">
-        <v>1446.864378</v>
+        <v>519.952883</v>
       </c>
       <c r="E65" t="n">
-        <v>455.494981</v>
+        <v>373.690509</v>
       </c>
       <c r="F65" t="n">
-        <v>787.909998</v>
+        <v>520.635439</v>
       </c>
       <c r="G65" t="n">
-        <v>631.922905</v>
+        <v>560.9419685</v>
       </c>
       <c r="H65" t="n">
-        <v>519.952883</v>
+        <v>913.473915</v>
       </c>
       <c r="I65" t="n">
-        <v>373.690509</v>
+        <v>567.521568</v>
       </c>
       <c r="J65" t="n">
-        <v>520.635439</v>
-      </c>
-      <c r="K65" t="n">
-        <v>560.9419685</v>
+        <v>377.466312</v>
       </c>
     </row>
     <row r="66">
@@ -2824,34 +2625,31 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>30.822172</v>
+        <v>229.226956</v>
       </c>
       <c r="C66" t="n">
-        <v>120.44585</v>
+        <v>213.05279</v>
       </c>
       <c r="D66" t="n">
-        <v>206.870462</v>
+        <v>66.733133</v>
       </c>
       <c r="E66" t="n">
-        <v>231.283392</v>
+        <v>136.075142</v>
       </c>
       <c r="F66" t="n">
-        <v>229.226956</v>
+        <v>110.807762</v>
       </c>
       <c r="G66" t="n">
-        <v>213.05279</v>
+        <v>105.866611</v>
       </c>
       <c r="H66" t="n">
-        <v>66.733133</v>
+        <v>427.347026</v>
       </c>
       <c r="I66" t="n">
-        <v>136.075142</v>
+        <v>156.326729</v>
       </c>
       <c r="J66" t="n">
-        <v>110.807762</v>
-      </c>
-      <c r="K66" t="n">
-        <v>105.866611</v>
+        <v>109.416659</v>
       </c>
     </row>
     <row r="67">
@@ -2861,34 +2659,31 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>4743.682442</v>
+        <v>6750.49278</v>
       </c>
       <c r="C67" t="n">
-        <v>4671.907708</v>
+        <v>6032.672945</v>
       </c>
       <c r="D67" t="n">
-        <v>8215.694162</v>
+        <v>9123.656804</v>
       </c>
       <c r="E67" t="n">
-        <v>17337.946637</v>
+        <v>5948.821357</v>
       </c>
       <c r="F67" t="n">
-        <v>6750.49278</v>
+        <v>4361.375109</v>
       </c>
       <c r="G67" t="n">
-        <v>6032.672945</v>
+        <v>3988.662239</v>
       </c>
       <c r="H67" t="n">
-        <v>9123.656804</v>
+        <v>2239.750451</v>
       </c>
       <c r="I67" t="n">
-        <v>5948.821357</v>
+        <v>2718.358779</v>
       </c>
       <c r="J67" t="n">
-        <v>4361.375109</v>
-      </c>
-      <c r="K67" t="n">
-        <v>3988.662239</v>
+        <v>2282.874727</v>
       </c>
     </row>
     <row r="68">
@@ -2898,34 +2693,31 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>5.855854</v>
+        <v>9.086698</v>
       </c>
       <c r="C68" t="n">
-        <v>6.94692</v>
+        <v>6.074252</v>
       </c>
       <c r="D68" t="n">
-        <v>7.921055</v>
+        <v>7.701942</v>
       </c>
       <c r="E68" t="n">
-        <v>5.661461</v>
+        <v>9.683154</v>
       </c>
       <c r="F68" t="n">
-        <v>9.086698</v>
+        <v>7.176474</v>
       </c>
       <c r="G68" t="n">
-        <v>6.074252</v>
+        <v>8.333875000000001</v>
       </c>
       <c r="H68" t="n">
-        <v>7.701942</v>
+        <v>14.849422</v>
       </c>
       <c r="I68" t="n">
-        <v>9.683154</v>
+        <v>9.623455</v>
       </c>
       <c r="J68" t="n">
-        <v>7.176474</v>
-      </c>
-      <c r="K68" t="n">
-        <v>8.333875000000001</v>
+        <v>8.748628</v>
       </c>
     </row>
     <row r="69">
@@ -2935,34 +2727,31 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.004674</v>
+        <v>0.005453</v>
       </c>
       <c r="C69" t="n">
-        <v>0.00381</v>
+        <v>0.0043975</v>
       </c>
       <c r="D69" t="n">
-        <v>0.005626</v>
+        <v>0.008373</v>
       </c>
       <c r="E69" t="n">
-        <v>0.008741000000000001</v>
+        <v>0.008206</v>
       </c>
       <c r="F69" t="n">
-        <v>0.005453</v>
+        <v>0.004415</v>
       </c>
       <c r="G69" t="n">
-        <v>0.0043975</v>
+        <v>0.004137</v>
       </c>
       <c r="H69" t="n">
-        <v>0.008373</v>
+        <v>0.005494</v>
       </c>
       <c r="I69" t="n">
-        <v>0.008206</v>
+        <v>0.003423</v>
       </c>
       <c r="J69" t="n">
-        <v>0.004415</v>
-      </c>
-      <c r="K69" t="n">
-        <v>0.004137</v>
+        <v>0.003731</v>
       </c>
     </row>
     <row r="70">
@@ -2972,34 +2761,31 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.64676</v>
+        <v>1.652656</v>
       </c>
       <c r="C70" t="n">
-        <v>0.9210660000000001</v>
+        <v>0.548177</v>
       </c>
       <c r="D70" t="n">
-        <v>0.345815</v>
+        <v>0.693272</v>
       </c>
       <c r="E70" t="n">
-        <v>0.257067</v>
+        <v>1.371864</v>
       </c>
       <c r="F70" t="n">
-        <v>1.652656</v>
+        <v>0.911798</v>
       </c>
       <c r="G70" t="n">
-        <v>0.548177</v>
+        <v>1.43441</v>
       </c>
       <c r="H70" t="n">
-        <v>0.693272</v>
+        <v>1.695991</v>
       </c>
       <c r="I70" t="n">
-        <v>1.371864</v>
+        <v>1.208114</v>
       </c>
       <c r="J70" t="n">
-        <v>0.911798</v>
-      </c>
-      <c r="K70" t="n">
-        <v>1.43441</v>
+        <v>0.024509</v>
       </c>
     </row>
     <row r="71">
@@ -3009,34 +2795,31 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>10429.506015</v>
+        <v>5292.823429</v>
       </c>
       <c r="C71" t="n">
-        <v>6504.096007</v>
+        <v>9590.965711000001</v>
       </c>
       <c r="D71" t="n">
-        <v>2926.049538</v>
+        <v>14522.891958</v>
       </c>
       <c r="E71" t="n">
-        <v>12613.655741</v>
+        <v>14761.244176</v>
       </c>
       <c r="F71" t="n">
-        <v>5292.823429</v>
+        <v>10579.17522</v>
       </c>
       <c r="G71" t="n">
-        <v>9590.965711000001</v>
+        <v>19617.035707</v>
       </c>
       <c r="H71" t="n">
-        <v>14522.891958</v>
+        <v>8320.91656</v>
       </c>
       <c r="I71" t="n">
-        <v>14761.244176</v>
+        <v>8573.630485</v>
       </c>
       <c r="J71" t="n">
-        <v>10579.17522</v>
-      </c>
-      <c r="K71" t="n">
-        <v>19617.035707</v>
+        <v>4655.755978</v>
       </c>
     </row>
     <row r="72">
@@ -3046,34 +2829,31 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1.373989</v>
+        <v>1.613938</v>
       </c>
       <c r="C72" t="n">
-        <v>0.730162</v>
+        <v>1.940996</v>
       </c>
       <c r="D72" t="n">
-        <v>0.593838</v>
+        <v>1.564369</v>
       </c>
       <c r="E72" t="n">
-        <v>1.36128</v>
+        <v>2.889618</v>
       </c>
       <c r="F72" t="n">
-        <v>1.613938</v>
+        <v>1.366585</v>
       </c>
       <c r="G72" t="n">
-        <v>1.940996</v>
+        <v>0.917232</v>
       </c>
       <c r="H72" t="n">
-        <v>1.564369</v>
+        <v>0.792461</v>
       </c>
       <c r="I72" t="n">
-        <v>2.889618</v>
+        <v>0.574948</v>
       </c>
       <c r="J72" t="n">
-        <v>1.366585</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0.917232</v>
+        <v>0.759304</v>
       </c>
     </row>
     <row r="73">
@@ -3083,34 +2863,31 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.960659</v>
+        <v>1.290888</v>
       </c>
       <c r="C73" t="n">
-        <v>1.418611</v>
+        <v>0.199999</v>
       </c>
       <c r="D73" t="n">
-        <v>1.087056</v>
+        <v>0.625051</v>
       </c>
       <c r="E73" t="n">
-        <v>0.997908</v>
+        <v>0.754844</v>
       </c>
       <c r="F73" t="n">
-        <v>1.290888</v>
+        <v>1.74787</v>
       </c>
       <c r="G73" t="n">
-        <v>0.199999</v>
+        <v>0.605754</v>
       </c>
       <c r="H73" t="n">
-        <v>0.625051</v>
+        <v>1.403511</v>
       </c>
       <c r="I73" t="n">
-        <v>0.754844</v>
+        <v>0.575786</v>
       </c>
       <c r="J73" t="n">
-        <v>1.74787</v>
-      </c>
-      <c r="K73" t="n">
-        <v>0.605754</v>
+        <v>0.420326</v>
       </c>
     </row>
     <row r="74">
@@ -3120,34 +2897,31 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>3190.48216</v>
+        <v>5166.152157</v>
       </c>
       <c r="C74" t="n">
-        <v>2261.789606</v>
+        <v>5234.524655</v>
       </c>
       <c r="D74" t="n">
-        <v>2069.752334</v>
+        <v>3678.540566</v>
       </c>
       <c r="E74" t="n">
-        <v>1920.469622</v>
+        <v>2161.937275</v>
       </c>
       <c r="F74" t="n">
-        <v>5166.152157</v>
+        <v>2934.638464</v>
       </c>
       <c r="G74" t="n">
-        <v>5234.524655</v>
+        <v>2019.571871</v>
       </c>
       <c r="H74" t="n">
-        <v>3678.540566</v>
+        <v>2995.752028</v>
       </c>
       <c r="I74" t="n">
-        <v>2748.894623</v>
+        <v>1834.755329</v>
       </c>
       <c r="J74" t="n">
-        <v>2934.638464</v>
-      </c>
-      <c r="K74" t="n">
-        <v>2238.815385</v>
+        <v>2968.33159</v>
       </c>
     </row>
     <row r="75">
@@ -3157,34 +2931,31 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1.094319</v>
+        <v>1.461627</v>
       </c>
       <c r="C75" t="n">
-        <v>1.20142</v>
+        <v>1.342721</v>
       </c>
       <c r="D75" t="n">
-        <v>0.925351</v>
+        <v>1.05523375</v>
       </c>
       <c r="E75" t="n">
-        <v>0.903649</v>
+        <v>0.7004629999999999</v>
       </c>
       <c r="F75" t="n">
-        <v>1.461627</v>
+        <v>0.4989105</v>
       </c>
       <c r="G75" t="n">
-        <v>1.342721</v>
+        <v>0.84087425</v>
       </c>
       <c r="H75" t="n">
-        <v>1.05523375</v>
+        <v>0.8081739999999999</v>
       </c>
       <c r="I75" t="n">
-        <v>0.7004629999999999</v>
+        <v>0.4811093333333333</v>
       </c>
       <c r="J75" t="n">
-        <v>0.4989105</v>
-      </c>
-      <c r="K75" t="n">
-        <v>0.84087425</v>
+        <v>0.406997</v>
       </c>
     </row>
     <row r="76">
@@ -3194,34 +2965,31 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>912.773399</v>
+        <v>1353.186506</v>
       </c>
       <c r="C76" t="n">
-        <v>989.217021</v>
+        <v>915.494014</v>
       </c>
       <c r="D76" t="n">
-        <v>1409.015519</v>
+        <v>1082.266233</v>
       </c>
       <c r="E76" t="n">
-        <v>1305.899836</v>
+        <v>804.787636</v>
       </c>
       <c r="F76" t="n">
-        <v>1353.186506</v>
+        <v>1081.849325</v>
       </c>
       <c r="G76" t="n">
-        <v>915.494014</v>
+        <v>825.077547</v>
       </c>
       <c r="H76" t="n">
-        <v>1086.809912</v>
+        <v>1466.381774</v>
       </c>
       <c r="I76" t="n">
-        <v>804.787636</v>
+        <v>1156.664586</v>
       </c>
       <c r="J76" t="n">
-        <v>1135.632125</v>
-      </c>
-      <c r="K76" t="n">
-        <v>825.077547</v>
+        <v>1341.859916</v>
       </c>
     </row>
     <row r="77">
@@ -3231,34 +2999,31 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5777460833333333</v>
+        <v>0.632834</v>
       </c>
       <c r="C77" t="n">
-        <v>0.60334775</v>
+        <v>0.61683075</v>
       </c>
       <c r="D77" t="n">
-        <v>0.612161</v>
+        <v>0.4672313333333333</v>
       </c>
       <c r="E77" t="n">
-        <v>0.35998</v>
+        <v>0.29997375</v>
       </c>
       <c r="F77" t="n">
-        <v>0.632834</v>
+        <v>0.312439</v>
       </c>
       <c r="G77" t="n">
-        <v>0.61683075</v>
+        <v>0.400125</v>
       </c>
       <c r="H77" t="n">
-        <v>0.4672313333333333</v>
+        <v>0.3790386666666667</v>
       </c>
       <c r="I77" t="n">
-        <v>0.30532175</v>
+        <v>0.311228</v>
       </c>
       <c r="J77" t="n">
-        <v>0.312439</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0.400125</v>
+        <v>0.28865475</v>
       </c>
     </row>
     <row r="78">
@@ -3268,34 +3033,31 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>46.516881</v>
+        <v>468.304146</v>
       </c>
       <c r="C78" t="n">
-        <v>472.4874</v>
+        <v>243.10656</v>
       </c>
       <c r="D78" t="n">
-        <v>710.873299</v>
+        <v>259.176472</v>
       </c>
       <c r="E78" t="n">
-        <v>230.843733</v>
+        <v>769.364043</v>
       </c>
       <c r="F78" t="n">
-        <v>468.304146</v>
+        <v>204.457131</v>
       </c>
       <c r="G78" t="n">
-        <v>243.10656</v>
+        <v>374.574502</v>
       </c>
       <c r="H78" t="n">
-        <v>254.632793</v>
+        <v>450.70307</v>
       </c>
       <c r="I78" t="n">
-        <v>182.406695</v>
+        <v>120.197101</v>
       </c>
       <c r="J78" t="n">
-        <v>150.674331</v>
-      </c>
-      <c r="K78" t="n">
-        <v>155.330988</v>
+        <v>273.934396</v>
       </c>
     </row>
     <row r="79">
@@ -3305,34 +3067,31 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.111324</v>
+        <v>0.08527</v>
       </c>
       <c r="C79" t="n">
-        <v>0.04212</v>
+        <v>0.060649</v>
       </c>
       <c r="D79" t="n">
-        <v>0.112595</v>
+        <v>0.098855</v>
       </c>
       <c r="E79" t="n">
-        <v>0.050569</v>
+        <v>0.068686</v>
       </c>
       <c r="F79" t="n">
-        <v>0.08527</v>
+        <v>0.08888699999999999</v>
       </c>
       <c r="G79" t="n">
-        <v>0.060649</v>
+        <v>0.035027</v>
       </c>
       <c r="H79" t="n">
-        <v>0.098855</v>
+        <v>0.008642</v>
       </c>
       <c r="I79" t="n">
-        <v>0.06333800000000001</v>
+        <v>0.023914</v>
       </c>
       <c r="J79" t="n">
-        <v>0.08888699999999999</v>
-      </c>
-      <c r="K79" t="n">
-        <v>0.035027</v>
+        <v>0.041112</v>
       </c>
     </row>
     <row r="80">
@@ -3342,34 +3101,31 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>931.901439</v>
+        <v>1345.254825</v>
       </c>
       <c r="C80" t="n">
-        <v>597.561423</v>
+        <v>608.9787894999999</v>
       </c>
       <c r="D80" t="n">
-        <v>527.572399</v>
+        <v>295.797683</v>
       </c>
       <c r="E80" t="n">
-        <v>2294.561808</v>
+        <v>248.637091</v>
       </c>
       <c r="F80" t="n">
-        <v>1345.254825</v>
+        <v>191.868858</v>
       </c>
       <c r="G80" t="n">
-        <v>608.9787894999999</v>
+        <v>212.699101</v>
       </c>
       <c r="H80" t="n">
-        <v>295.797683</v>
+        <v>350.86005</v>
       </c>
       <c r="I80" t="n">
-        <v>248.637091</v>
+        <v>170.641276</v>
       </c>
       <c r="J80" t="n">
-        <v>191.868858</v>
-      </c>
-      <c r="K80" t="n">
-        <v>212.699101</v>
+        <v>136.894967</v>
       </c>
     </row>
     <row r="81">
@@ -3379,34 +3135,31 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.002726</v>
+        <v>0.002773</v>
       </c>
       <c r="C81" t="n">
-        <v>0.002507</v>
+        <v>0.003866</v>
       </c>
       <c r="D81" t="n">
-        <v>0.001812</v>
+        <v>0.002113</v>
       </c>
       <c r="E81" t="n">
-        <v>0.002089</v>
+        <v>0.002928</v>
       </c>
       <c r="F81" t="n">
-        <v>0.002773</v>
+        <v>0.002257</v>
       </c>
       <c r="G81" t="n">
-        <v>0.003866</v>
+        <v>0.004953</v>
       </c>
       <c r="H81" t="n">
-        <v>0.002113</v>
+        <v>0.0019</v>
       </c>
       <c r="I81" t="n">
-        <v>0.002928</v>
+        <v>0.004195</v>
       </c>
       <c r="J81" t="n">
-        <v>0.002257</v>
-      </c>
-      <c r="K81" t="n">
-        <v>0.004953</v>
+        <v>0.00232</v>
       </c>
     </row>
     <row r="82">
@@ -3416,34 +3169,31 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1645.574401</v>
+        <v>1546.280262</v>
       </c>
       <c r="C82" t="n">
-        <v>1060.785575</v>
+        <v>1017.26617</v>
       </c>
       <c r="D82" t="n">
-        <v>788.708321</v>
+        <v>567.45573</v>
       </c>
       <c r="E82" t="n">
-        <v>729.383301</v>
+        <v>703.43878</v>
       </c>
       <c r="F82" t="n">
-        <v>1546.280262</v>
+        <v>544.980269</v>
       </c>
       <c r="G82" t="n">
-        <v>1017.26617</v>
+        <v>524.011943</v>
       </c>
       <c r="H82" t="n">
-        <v>567.45573</v>
+        <v>955.361952</v>
       </c>
       <c r="I82" t="n">
-        <v>703.43878</v>
+        <v>356.346937</v>
       </c>
       <c r="J82" t="n">
-        <v>544.980269</v>
-      </c>
-      <c r="K82" t="n">
-        <v>524.011943</v>
+        <v>491.181622</v>
       </c>
     </row>
     <row r="83">
@@ -3453,34 +3203,31 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.003897</v>
+        <v>0.005595</v>
       </c>
       <c r="C83" t="n">
-        <v>0.005206</v>
+        <v>0.004067</v>
       </c>
       <c r="D83" t="n">
-        <v>0.004338</v>
+        <v>0.00165</v>
       </c>
       <c r="E83" t="n">
-        <v>0.004179</v>
+        <v>0.004333</v>
       </c>
       <c r="F83" t="n">
-        <v>0.005595</v>
+        <v>0.003745</v>
       </c>
       <c r="G83" t="n">
-        <v>0.004067</v>
+        <v>0.004421</v>
       </c>
       <c r="H83" t="n">
-        <v>0.00165</v>
+        <v>0.00321</v>
       </c>
       <c r="I83" t="n">
-        <v>0.004333</v>
+        <v>0.002017</v>
       </c>
       <c r="J83" t="n">
-        <v>0.003745</v>
-      </c>
-      <c r="K83" t="n">
-        <v>0.004421</v>
+        <v>0.001719</v>
       </c>
     </row>
     <row r="84">
@@ -3490,34 +3237,31 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>130.480298</v>
+        <v>27.262329</v>
       </c>
       <c r="C84" t="n">
-        <v>286.14389</v>
+        <v>13.30453</v>
       </c>
       <c r="D84" t="n">
-        <v>142.265332</v>
+        <v>208.289501</v>
       </c>
       <c r="E84" t="n">
-        <v>2.956679</v>
+        <v>195.224665</v>
       </c>
       <c r="F84" t="n">
-        <v>27.262329</v>
+        <v>138.419356</v>
       </c>
       <c r="G84" t="n">
-        <v>13.30453</v>
+        <v>222.888126</v>
       </c>
       <c r="H84" t="n">
-        <v>208.289501</v>
+        <v>372.137061</v>
       </c>
       <c r="I84" t="n">
-        <v>195.224665</v>
+        <v>280.91454</v>
       </c>
       <c r="J84" t="n">
-        <v>138.419356</v>
-      </c>
-      <c r="K84" t="n">
-        <v>222.888126</v>
+        <v>92.450514</v>
       </c>
     </row>
     <row r="85">
@@ -3527,34 +3271,31 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.001738</v>
+        <v>0.001754</v>
       </c>
       <c r="C85" t="n">
-        <v>0.01827</v>
+        <v>0.002481</v>
       </c>
       <c r="D85" t="n">
-        <v>0.025966</v>
+        <v>0.00147</v>
       </c>
       <c r="E85" t="n">
-        <v>0.002587</v>
+        <v>0.000663</v>
       </c>
       <c r="F85" t="n">
-        <v>0.001754</v>
+        <v>0.001107</v>
       </c>
       <c r="G85" t="n">
-        <v>0.002481</v>
+        <v>0.003034</v>
       </c>
       <c r="H85" t="n">
-        <v>0.00147</v>
+        <v>0.000435</v>
       </c>
       <c r="I85" t="n">
-        <v>0.000663</v>
+        <v>0.0019</v>
       </c>
       <c r="J85" t="n">
-        <v>0.001107</v>
-      </c>
-      <c r="K85" t="n">
-        <v>0.003034</v>
+        <v>0.001241</v>
       </c>
     </row>
     <row r="86">
@@ -3564,34 +3305,31 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>2522.789547</v>
+        <v>2046.733668</v>
       </c>
       <c r="C86" t="n">
-        <v>1771.625518</v>
+        <v>1276.134651</v>
       </c>
       <c r="D86" t="n">
-        <v>1942.64528</v>
+        <v>1051.752425</v>
       </c>
       <c r="E86" t="n">
-        <v>989.842979</v>
+        <v>618.413716</v>
       </c>
       <c r="F86" t="n">
-        <v>2046.733668</v>
+        <v>634.992787</v>
       </c>
       <c r="G86" t="n">
-        <v>1276.134651</v>
+        <v>720.727899</v>
       </c>
       <c r="H86" t="n">
-        <v>1051.752425</v>
+        <v>803.373006</v>
       </c>
       <c r="I86" t="n">
-        <v>618.413716</v>
+        <v>621.345197</v>
       </c>
       <c r="J86" t="n">
-        <v>634.992787</v>
-      </c>
-      <c r="K86" t="n">
-        <v>720.727899</v>
+        <v>540.278565</v>
       </c>
     </row>
     <row r="87">
@@ -3601,34 +3339,31 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.240485</v>
+        <v>0.265565</v>
       </c>
       <c r="C87" t="n">
-        <v>0.404338</v>
+        <v>0.162309</v>
       </c>
       <c r="D87" t="n">
-        <v>0.241715</v>
+        <v>0.097995</v>
       </c>
       <c r="E87" t="n">
-        <v>0.427297</v>
+        <v>0.210654</v>
       </c>
       <c r="F87" t="n">
-        <v>0.265565</v>
+        <v>0.340931</v>
       </c>
       <c r="G87" t="n">
-        <v>0.162309</v>
+        <v>0.169087</v>
       </c>
       <c r="H87" t="n">
-        <v>0.097995</v>
+        <v>0.120671</v>
       </c>
       <c r="I87" t="n">
-        <v>0.210654</v>
+        <v>0.09860099999999999</v>
       </c>
       <c r="J87" t="n">
-        <v>0.340931</v>
-      </c>
-      <c r="K87" t="n">
-        <v>0.169087</v>
+        <v>0.104036</v>
       </c>
     </row>
     <row r="88">
@@ -3638,34 +3373,31 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>280.293823</v>
+        <v>409.612579</v>
       </c>
       <c r="C88" t="n">
-        <v>419.955127</v>
+        <v>259.245057</v>
       </c>
       <c r="D88" t="n">
-        <v>346.311045</v>
+        <v>670.640525</v>
       </c>
       <c r="E88" t="n">
-        <v>243.104347</v>
+        <v>435.219971</v>
       </c>
       <c r="F88" t="n">
-        <v>409.612579</v>
+        <v>345.353824</v>
       </c>
       <c r="G88" t="n">
-        <v>259.245057</v>
+        <v>482.492748</v>
       </c>
       <c r="H88" t="n">
-        <v>670.640525</v>
+        <v>686.445857</v>
       </c>
       <c r="I88" t="n">
-        <v>435.219971</v>
+        <v>329.638935</v>
       </c>
       <c r="J88" t="n">
-        <v>345.353824</v>
-      </c>
-      <c r="K88" t="n">
-        <v>482.492748</v>
+        <v>447.124205</v>
       </c>
     </row>
     <row r="89">
@@ -3675,34 +3407,31 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.03328925</v>
+        <v>0.059544</v>
       </c>
       <c r="C89" t="n">
-        <v>0.044408</v>
+        <v>0.02936425</v>
       </c>
       <c r="D89" t="n">
-        <v>0.041502</v>
+        <v>0.030471</v>
       </c>
       <c r="E89" t="n">
-        <v>0.025163</v>
+        <v>0.022361</v>
       </c>
       <c r="F89" t="n">
-        <v>0.059544</v>
+        <v>0.02103</v>
       </c>
       <c r="G89" t="n">
-        <v>0.02936425</v>
+        <v>0.025786</v>
       </c>
       <c r="H89" t="n">
-        <v>0.030471</v>
+        <v>0.026421</v>
       </c>
       <c r="I89" t="n">
-        <v>0.022361</v>
+        <v>0.022317</v>
       </c>
       <c r="J89" t="n">
-        <v>0.02103</v>
-      </c>
-      <c r="K89" t="n">
-        <v>0.025786</v>
+        <v>0.034153</v>
       </c>
     </row>
     <row r="90">
@@ -3712,34 +3441,31 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>11.01956</v>
+        <v>19.279893</v>
       </c>
       <c r="C90" t="n">
-        <v>16.720189</v>
+        <v>10.540074</v>
       </c>
       <c r="D90" t="n">
-        <v>27.391598</v>
+        <v>23.53453</v>
       </c>
       <c r="E90" t="n">
-        <v>13.047469</v>
+        <v>190.558933</v>
       </c>
       <c r="F90" t="n">
-        <v>19.279893</v>
+        <v>20.400783</v>
       </c>
       <c r="G90" t="n">
-        <v>10.540074</v>
+        <v>205.505945</v>
       </c>
       <c r="H90" t="n">
-        <v>23.53453</v>
+        <v>238.609366</v>
       </c>
       <c r="I90" t="n">
-        <v>190.558933</v>
+        <v>211.811151</v>
       </c>
       <c r="J90" t="n">
-        <v>20.400783</v>
-      </c>
-      <c r="K90" t="n">
-        <v>205.505945</v>
+        <v>132.143642</v>
       </c>
     </row>
     <row r="91">
@@ -3749,34 +3475,31 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.030791</v>
+        <v>0.031456</v>
       </c>
       <c r="C91" t="n">
-        <v>0.001162</v>
+        <v>0.077955</v>
       </c>
       <c r="D91" t="n">
-        <v>0.028388</v>
+        <v>0.09163300000000001</v>
       </c>
       <c r="E91" t="n">
-        <v>0.011932</v>
+        <v>0.061321</v>
       </c>
       <c r="F91" t="n">
-        <v>0.031456</v>
+        <v>0.048884</v>
       </c>
       <c r="G91" t="n">
-        <v>0.077955</v>
+        <v>0.08021399999999999</v>
       </c>
       <c r="H91" t="n">
-        <v>0.09163300000000001</v>
+        <v>0.13598</v>
       </c>
       <c r="I91" t="n">
-        <v>0.061321</v>
+        <v>0.112242</v>
       </c>
       <c r="J91" t="n">
-        <v>0.048884</v>
-      </c>
-      <c r="K91" t="n">
-        <v>0.08021399999999999</v>
+        <v>0.07532899999999999</v>
       </c>
     </row>
     <row r="92">
@@ -3786,34 +3509,31 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>3846.12291</v>
+        <v>10543.385209</v>
       </c>
       <c r="C92" t="n">
-        <v>26414.590776</v>
+        <v>11486.848972</v>
       </c>
       <c r="D92" t="n">
-        <v>27550.622289</v>
+        <v>7024.241639</v>
       </c>
       <c r="E92" t="n">
-        <v>15617.149245</v>
+        <v>5990.20021</v>
       </c>
       <c r="F92" t="n">
-        <v>10543.385209</v>
+        <v>6626.258885</v>
       </c>
       <c r="G92" t="n">
-        <v>11486.848972</v>
+        <v>5855.753238</v>
       </c>
       <c r="H92" t="n">
-        <v>7024.241639</v>
+        <v>7880.08759</v>
       </c>
       <c r="I92" t="n">
-        <v>5990.20021</v>
+        <v>4218.222346</v>
       </c>
       <c r="J92" t="n">
-        <v>6626.258885</v>
-      </c>
-      <c r="K92" t="n">
-        <v>5855.753238</v>
+        <v>4008.699382</v>
       </c>
     </row>
     <row r="93">
@@ -3823,34 +3543,31 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>231.373712</v>
+        <v>428.272493</v>
       </c>
       <c r="C93" t="n">
-        <v>305.095399</v>
+        <v>381.294679</v>
       </c>
       <c r="D93" t="n">
-        <v>322.839717</v>
+        <v>333.717318</v>
       </c>
       <c r="E93" t="n">
-        <v>251.972746</v>
+        <v>285.267483</v>
       </c>
       <c r="F93" t="n">
-        <v>428.272493</v>
+        <v>272.056872</v>
       </c>
       <c r="G93" t="n">
-        <v>381.294679</v>
+        <v>324.828823</v>
       </c>
       <c r="H93" t="n">
-        <v>333.717318</v>
+        <v>455.231814</v>
       </c>
       <c r="I93" t="n">
-        <v>285.267483</v>
+        <v>398.242969</v>
       </c>
       <c r="J93" t="n">
-        <v>272.056872</v>
-      </c>
-      <c r="K93" t="n">
-        <v>324.828823</v>
+        <v>258.784612</v>
       </c>
     </row>
     <row r="94">
@@ -3860,34 +3577,31 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.013256</v>
+        <v>0.026711</v>
       </c>
       <c r="C94" t="n">
-        <v>0.0430005</v>
+        <v>0.013497</v>
       </c>
       <c r="D94" t="n">
-        <v>0.027128</v>
+        <v>0.02439075</v>
       </c>
       <c r="E94" t="n">
-        <v>0.018892</v>
+        <v>0.017441</v>
       </c>
       <c r="F94" t="n">
-        <v>0.026711</v>
+        <v>0.0139595</v>
       </c>
       <c r="G94" t="n">
-        <v>0.013497</v>
+        <v>0.013798</v>
       </c>
       <c r="H94" t="n">
-        <v>0.02439075</v>
+        <v>0.01124266666666667</v>
       </c>
       <c r="I94" t="n">
-        <v>0.017441</v>
+        <v>0.014224</v>
       </c>
       <c r="J94" t="n">
-        <v>0.0139595</v>
-      </c>
-      <c r="K94" t="n">
-        <v>0.013798</v>
+        <v>0.0165205</v>
       </c>
     </row>
     <row r="95">
@@ -3897,34 +3611,31 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>1316.93016</v>
+        <v>504.812143</v>
       </c>
       <c r="C95" t="n">
-        <v>607.436062</v>
+        <v>1053.949158</v>
       </c>
       <c r="D95" t="n">
-        <v>456.993702</v>
+        <v>429.448187</v>
       </c>
       <c r="E95" t="n">
-        <v>414.442603</v>
+        <v>405.79081</v>
       </c>
       <c r="F95" t="n">
-        <v>504.812143</v>
+        <v>336.288928</v>
       </c>
       <c r="G95" t="n">
-        <v>1053.949158</v>
+        <v>316.722726</v>
       </c>
       <c r="H95" t="n">
-        <v>429.448187</v>
+        <v>387.168212</v>
       </c>
       <c r="I95" t="n">
-        <v>405.79081</v>
+        <v>318.778998</v>
       </c>
       <c r="J95" t="n">
-        <v>336.288928</v>
-      </c>
-      <c r="K95" t="n">
-        <v>316.722726</v>
+        <v>347.368203</v>
       </c>
     </row>
     <row r="96">
@@ -3934,34 +3645,31 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.013006</v>
+        <v>0.013613</v>
       </c>
       <c r="C96" t="n">
-        <v>0.020498</v>
+        <v>0.011385</v>
       </c>
       <c r="D96" t="n">
-        <v>0.010843</v>
+        <v>0.008755000000000001</v>
       </c>
       <c r="E96" t="n">
-        <v>0.014403</v>
+        <v>0.005496</v>
       </c>
       <c r="F96" t="n">
-        <v>0.013613</v>
+        <v>0.009808000000000001</v>
       </c>
       <c r="G96" t="n">
-        <v>0.011385</v>
+        <v>0.009979999999999999</v>
       </c>
       <c r="H96" t="n">
-        <v>0.008755000000000001</v>
+        <v>0.018619</v>
       </c>
       <c r="I96" t="n">
-        <v>0.005496</v>
+        <v>0.009264</v>
       </c>
       <c r="J96" t="n">
-        <v>0.009808000000000001</v>
-      </c>
-      <c r="K96" t="n">
-        <v>0.009979999999999999</v>
+        <v>0.007109</v>
       </c>
     </row>
     <row r="97">
@@ -3971,34 +3679,31 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>124.568896</v>
+        <v>319.876891</v>
       </c>
       <c r="C97" t="n">
-        <v>192.598552</v>
+        <v>147.465323</v>
       </c>
       <c r="D97" t="n">
-        <v>161.266218</v>
+        <v>105.537485</v>
       </c>
       <c r="E97" t="n">
-        <v>67.864903</v>
+        <v>94.891927</v>
       </c>
       <c r="F97" t="n">
-        <v>319.876891</v>
+        <v>95.083974</v>
       </c>
       <c r="G97" t="n">
-        <v>147.465323</v>
+        <v>100.186322</v>
       </c>
       <c r="H97" t="n">
-        <v>105.537485</v>
+        <v>93.857151</v>
       </c>
       <c r="I97" t="n">
-        <v>94.891927</v>
+        <v>62.84585</v>
       </c>
       <c r="J97" t="n">
-        <v>95.083974</v>
-      </c>
-      <c r="K97" t="n">
-        <v>100.186322</v>
+        <v>63.914319</v>
       </c>
     </row>
     <row r="98">
@@ -4008,34 +3713,31 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.003916</v>
+        <v>0.015079</v>
       </c>
       <c r="C98" t="n">
-        <v>0.0095345</v>
+        <v>0.003464666666666667</v>
       </c>
       <c r="D98" t="n">
-        <v>0.004104</v>
+        <v>0.002068666666666667</v>
       </c>
       <c r="E98" t="n">
-        <v>0.00209</v>
+        <v>0.004654</v>
       </c>
       <c r="F98" t="n">
-        <v>0.015079</v>
+        <v>0.003868</v>
       </c>
       <c r="G98" t="n">
-        <v>0.003464666666666667</v>
+        <v>0.006015</v>
       </c>
       <c r="H98" t="n">
-        <v>0.002068666666666667</v>
+        <v>0.003297</v>
       </c>
       <c r="I98" t="n">
-        <v>0.004654</v>
+        <v>0.012757</v>
       </c>
       <c r="J98" t="n">
-        <v>0.003868</v>
-      </c>
-      <c r="K98" t="n">
-        <v>0.006015</v>
+        <v>0.00767</v>
       </c>
     </row>
     <row r="99">
@@ -4045,34 +3747,31 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>70.1717</v>
+        <v>156.495259</v>
       </c>
       <c r="C99" t="n">
-        <v>69.915561</v>
+        <v>102.21092</v>
       </c>
       <c r="D99" t="n">
-        <v>107.661405</v>
+        <v>64.102439</v>
       </c>
       <c r="E99" t="n">
-        <v>95.802745</v>
+        <v>93.322474</v>
       </c>
       <c r="F99" t="n">
-        <v>156.495259</v>
+        <v>55.077038</v>
       </c>
       <c r="G99" t="n">
-        <v>102.21092</v>
+        <v>95.97843399999999</v>
       </c>
       <c r="H99" t="n">
-        <v>64.102439</v>
+        <v>165.196967</v>
       </c>
       <c r="I99" t="n">
-        <v>93.322474</v>
+        <v>129.628898</v>
       </c>
       <c r="J99" t="n">
-        <v>55.077038</v>
-      </c>
-      <c r="K99" t="n">
-        <v>95.97843399999999</v>
+        <v>68.697436</v>
       </c>
     </row>
     <row r="100">
@@ -4082,34 +3781,31 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.048153</v>
+        <v>0.046628</v>
       </c>
       <c r="C100" t="n">
-        <v>0.04267725</v>
+        <v>0.035645</v>
       </c>
       <c r="D100" t="n">
-        <v>0.03791033333333334</v>
+        <v>0.024784</v>
       </c>
       <c r="E100" t="n">
-        <v>0.041525</v>
+        <v>0.02873575</v>
       </c>
       <c r="F100" t="n">
-        <v>0.046628</v>
+        <v>0.02663225</v>
       </c>
       <c r="G100" t="n">
-        <v>0.035645</v>
+        <v>0.02465833333333333</v>
       </c>
       <c r="H100" t="n">
-        <v>0.024784</v>
+        <v>0.028249</v>
       </c>
       <c r="I100" t="n">
-        <v>0.02873575</v>
+        <v>0.02861575</v>
       </c>
       <c r="J100" t="n">
-        <v>0.02663225</v>
-      </c>
-      <c r="K100" t="n">
-        <v>0.02465833333333333</v>
+        <v>0.0370275</v>
       </c>
     </row>
     <row r="101">
@@ -4119,34 +3815,31 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>30.020113</v>
+        <v>34.262758</v>
       </c>
       <c r="C101" t="n">
-        <v>28.001421</v>
+        <v>22.889902</v>
       </c>
       <c r="D101" t="n">
-        <v>19.469583</v>
+        <v>22.613706</v>
       </c>
       <c r="E101" t="n">
-        <v>14.502247</v>
+        <v>19.89963</v>
       </c>
       <c r="F101" t="n">
-        <v>34.262758</v>
+        <v>30.053022</v>
       </c>
       <c r="G101" t="n">
-        <v>22.889902</v>
+        <v>1.783048</v>
       </c>
       <c r="H101" t="n">
-        <v>22.613706</v>
+        <v>95.505253</v>
       </c>
       <c r="I101" t="n">
-        <v>19.89963</v>
+        <v>2.496406</v>
       </c>
       <c r="J101" t="n">
-        <v>30.053022</v>
-      </c>
-      <c r="K101" t="n">
-        <v>1.783048</v>
+        <v>3.33623</v>
       </c>
     </row>
     <row r="102">
@@ -4156,29 +3849,26 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>4.7e-05</v>
+        <v>4.9e-05</v>
       </c>
       <c r="C102" t="n">
-        <v>0.000183</v>
+        <v>0.000116</v>
       </c>
       <c r="D102" t="n">
-        <v>0.000411</v>
-      </c>
-      <c r="E102" t="n">
-        <v>0.000332</v>
-      </c>
-      <c r="F102" t="n">
-        <v>4.9e-05</v>
-      </c>
-      <c r="G102" t="n">
-        <v>0.000116</v>
-      </c>
+        <v>6.7e-05</v>
+      </c>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
-        <v>6.7e-05</v>
-      </c>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
+        <v>9.7e-05</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0.000504</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0.000464</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
@@ -4187,34 +3877,31 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>112.510673</v>
+        <v>137.588249</v>
       </c>
       <c r="C103" t="n">
-        <v>126.678757</v>
+        <v>128.75096475</v>
       </c>
       <c r="D103" t="n">
-        <v>131.743272</v>
+        <v>140.190352</v>
       </c>
       <c r="E103" t="n">
-        <v>89.381399</v>
+        <v>116.670222</v>
       </c>
       <c r="F103" t="n">
-        <v>137.588249</v>
+        <v>131.438059</v>
       </c>
       <c r="G103" t="n">
-        <v>128.75096475</v>
+        <v>116.348776</v>
       </c>
       <c r="H103" t="n">
-        <v>140.190352</v>
+        <v>65.234769</v>
       </c>
       <c r="I103" t="n">
-        <v>116.670222</v>
+        <v>155.847863</v>
       </c>
       <c r="J103" t="n">
-        <v>131.438059</v>
-      </c>
-      <c r="K103" t="n">
-        <v>116.348776</v>
+        <v>112.212126</v>
       </c>
     </row>
     <row r="104">
@@ -4224,34 +3911,31 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>414.486803</v>
+        <v>1500.974829</v>
       </c>
       <c r="C104" t="n">
-        <v>463.344724</v>
+        <v>1270.345084</v>
       </c>
       <c r="D104" t="n">
-        <v>423.679191</v>
+        <v>1276.408497</v>
       </c>
       <c r="E104" t="n">
-        <v>784.190293</v>
+        <v>434.218828</v>
       </c>
       <c r="F104" t="n">
-        <v>1500.974829</v>
+        <v>390.718436</v>
       </c>
       <c r="G104" t="n">
-        <v>1270.345084</v>
+        <v>467.491935</v>
       </c>
       <c r="H104" t="n">
-        <v>1276.408497</v>
+        <v>612.164225</v>
       </c>
       <c r="I104" t="n">
-        <v>434.218828</v>
+        <v>693.404366</v>
       </c>
       <c r="J104" t="n">
-        <v>390.718436</v>
-      </c>
-      <c r="K104" t="n">
-        <v>467.491935</v>
+        <v>440.79424</v>
       </c>
     </row>
     <row r="105">
@@ -4261,34 +3945,31 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>37.596639</v>
+        <v>64.42345400000001</v>
       </c>
       <c r="C105" t="n">
-        <v>55.336026</v>
+        <v>41.367954</v>
       </c>
       <c r="D105" t="n">
-        <v>29.73499</v>
+        <v>31.043476</v>
       </c>
       <c r="E105" t="n">
-        <v>34.343915</v>
+        <v>3.13383</v>
       </c>
       <c r="F105" t="n">
-        <v>64.42345400000001</v>
+        <v>2.8508</v>
       </c>
       <c r="G105" t="n">
-        <v>41.367954</v>
+        <v>3.327093</v>
       </c>
       <c r="H105" t="n">
-        <v>31.043476</v>
+        <v>2.304672</v>
       </c>
       <c r="I105" t="n">
-        <v>3.13383</v>
+        <v>2.066771</v>
       </c>
       <c r="J105" t="n">
-        <v>2.8508</v>
-      </c>
-      <c r="K105" t="n">
-        <v>3.327093</v>
+        <v>2.46186</v>
       </c>
     </row>
     <row r="106">
@@ -4298,34 +3979,31 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>249.414713</v>
+        <v>647.83709</v>
       </c>
       <c r="C106" t="n">
-        <v>765.439792</v>
+        <v>1724.96783</v>
       </c>
       <c r="D106" t="n">
-        <v>924.991957</v>
+        <v>432.610359</v>
       </c>
       <c r="E106" t="n">
-        <v>680.574489</v>
+        <v>180.215207</v>
       </c>
       <c r="F106" t="n">
-        <v>647.83709</v>
+        <v>651.772335</v>
       </c>
       <c r="G106" t="n">
-        <v>1724.96783</v>
+        <v>1960.644805</v>
       </c>
       <c r="H106" t="n">
-        <v>432.610359</v>
+        <v>3453.042004</v>
       </c>
       <c r="I106" t="n">
-        <v>180.215207</v>
+        <v>1933.400534</v>
       </c>
       <c r="J106" t="n">
-        <v>651.772335</v>
-      </c>
-      <c r="K106" t="n">
-        <v>1960.644805</v>
+        <v>878.010869</v>
       </c>
     </row>
     <row r="107">
@@ -4335,34 +4013,31 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.823707</v>
+        <v>0.336738</v>
       </c>
       <c r="C107" t="n">
-        <v>0.575966</v>
+        <v>0.46604</v>
       </c>
       <c r="D107" t="n">
-        <v>0.593033</v>
+        <v>0.571151</v>
       </c>
       <c r="E107" t="n">
-        <v>0.628089</v>
+        <v>0.259937</v>
       </c>
       <c r="F107" t="n">
-        <v>0.336738</v>
+        <v>0.631062</v>
       </c>
       <c r="G107" t="n">
-        <v>0.46604</v>
+        <v>0.656298</v>
       </c>
       <c r="H107" t="n">
-        <v>0.571151</v>
+        <v>0.670773</v>
       </c>
       <c r="I107" t="n">
-        <v>0.259937</v>
+        <v>0.864629</v>
       </c>
       <c r="J107" t="n">
-        <v>0.631062</v>
-      </c>
-      <c r="K107" t="n">
-        <v>0.656298</v>
+        <v>1.367999</v>
       </c>
     </row>
     <row r="108">
@@ -4372,34 +4047,31 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>111.060154</v>
+        <v>91.55938</v>
       </c>
       <c r="C108" t="n">
-        <v>81.041877</v>
+        <v>50.13991</v>
       </c>
       <c r="D108" t="n">
-        <v>72.387227</v>
+        <v>48.622336</v>
       </c>
       <c r="E108" t="n">
-        <v>49.934651</v>
+        <v>28.670208</v>
       </c>
       <c r="F108" t="n">
-        <v>91.55938</v>
+        <v>33.945377</v>
       </c>
       <c r="G108" t="n">
-        <v>50.13991</v>
+        <v>69.141695</v>
       </c>
       <c r="H108" t="n">
-        <v>48.622336</v>
+        <v>86.43472199999999</v>
       </c>
       <c r="I108" t="n">
-        <v>28.670208</v>
+        <v>30.692105</v>
       </c>
       <c r="J108" t="n">
-        <v>33.945377</v>
-      </c>
-      <c r="K108" t="n">
-        <v>69.141695</v>
+        <v>63.709984</v>
       </c>
     </row>
     <row r="109">
@@ -4409,34 +4081,31 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.043318</v>
+        <v>0.091789</v>
       </c>
       <c r="C109" t="n">
-        <v>0.064952</v>
+        <v>0.06341425000000001</v>
       </c>
       <c r="D109" t="n">
-        <v>0.08289199999999999</v>
+        <v>0.043578</v>
       </c>
       <c r="E109" t="n">
-        <v>0.061841</v>
+        <v>0.04419866666666666</v>
       </c>
       <c r="F109" t="n">
-        <v>0.091789</v>
+        <v>0.028136</v>
       </c>
       <c r="G109" t="n">
-        <v>0.06341425000000001</v>
+        <v>0.047992</v>
       </c>
       <c r="H109" t="n">
-        <v>0.043578</v>
+        <v>0.136048</v>
       </c>
       <c r="I109" t="n">
-        <v>0.04419866666666666</v>
+        <v>0.058137</v>
       </c>
       <c r="J109" t="n">
-        <v>0.028136</v>
-      </c>
-      <c r="K109" t="n">
-        <v>0.047992</v>
+        <v>0.086058</v>
       </c>
     </row>
     <row r="110">
@@ -4446,34 +4115,27 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>89.83358699999999</v>
+        <v>639.366413</v>
       </c>
       <c r="C110" t="n">
-        <v>272.924504</v>
+        <v>437.475353</v>
       </c>
       <c r="D110" t="n">
-        <v>846.38107</v>
+        <v>1358.351665</v>
       </c>
       <c r="E110" t="n">
-        <v>204.916912</v>
+        <v>455.205895</v>
       </c>
       <c r="F110" t="n">
-        <v>639.366413</v>
+        <v>42.162402</v>
       </c>
       <c r="G110" t="n">
-        <v>437.475353</v>
-      </c>
-      <c r="H110" t="n">
-        <v>1358.351665</v>
-      </c>
-      <c r="I110" t="n">
-        <v>455.205895</v>
-      </c>
+        <v>190.401814</v>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
       <c r="J110" t="n">
-        <v>42.162402</v>
-      </c>
-      <c r="K110" t="n">
-        <v>190.401814</v>
+        <v>55.006575</v>
       </c>
     </row>
     <row r="111">
@@ -4483,34 +4145,31 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.174742</v>
+        <v>0.789226</v>
       </c>
       <c r="C111" t="n">
-        <v>0.564962</v>
+        <v>0.958326</v>
       </c>
       <c r="D111" t="n">
-        <v>0.917744</v>
+        <v>0.909138</v>
       </c>
       <c r="E111" t="n">
-        <v>0.639838</v>
+        <v>0.363006</v>
       </c>
       <c r="F111" t="n">
-        <v>0.789226</v>
+        <v>0.378988</v>
       </c>
       <c r="G111" t="n">
-        <v>0.958326</v>
+        <v>1.140258</v>
       </c>
       <c r="H111" t="n">
-        <v>0.909138</v>
+        <v>1.428417</v>
       </c>
       <c r="I111" t="n">
-        <v>0.363006</v>
+        <v>0.901454</v>
       </c>
       <c r="J111" t="n">
-        <v>0.378988</v>
-      </c>
-      <c r="K111" t="n">
-        <v>1.140258</v>
+        <v>0.569587</v>
       </c>
     </row>
     <row r="112">
@@ -4520,30 +4179,27 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.000958</v>
+        <v>0.000425</v>
       </c>
       <c r="C112" t="n">
-        <v>0.001266</v>
+        <v>0.000557</v>
       </c>
       <c r="D112" t="n">
-        <v>0.00065</v>
-      </c>
-      <c r="E112" t="n">
-        <v>0.000269</v>
-      </c>
-      <c r="F112" t="n">
-        <v>0.000425</v>
-      </c>
+        <v>0.000392</v>
+      </c>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
       <c r="G112" t="n">
-        <v>0.000557</v>
+        <v>0.003449</v>
       </c>
       <c r="H112" t="n">
-        <v>0.000392</v>
-      </c>
-      <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="n">
-        <v>0.003449</v>
+        <v>0.000749</v>
+      </c>
+      <c r="I112" t="n">
+        <v>0.000753</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0.000348</v>
       </c>
     </row>
     <row r="113">
@@ -4553,34 +4209,31 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.001365</v>
+        <v>0.006127</v>
       </c>
       <c r="C113" t="n">
-        <v>0.002449</v>
+        <v>0.002604</v>
       </c>
       <c r="D113" t="n">
-        <v>0.009594</v>
+        <v>0.002352</v>
       </c>
       <c r="E113" t="n">
-        <v>0.007594</v>
+        <v>0.002214</v>
       </c>
       <c r="F113" t="n">
-        <v>0.006127</v>
+        <v>0.001819</v>
       </c>
       <c r="G113" t="n">
-        <v>0.002604</v>
+        <v>0.003116</v>
       </c>
       <c r="H113" t="n">
-        <v>0.002352</v>
+        <v>0.00277</v>
       </c>
       <c r="I113" t="n">
-        <v>0.002214</v>
+        <v>0.001897</v>
       </c>
       <c r="J113" t="n">
-        <v>0.001819</v>
-      </c>
-      <c r="K113" t="n">
-        <v>0.003116</v>
+        <v>0.00232</v>
       </c>
     </row>
     <row r="114">
@@ -4589,24 +4242,19 @@
           <t>農業科技業平上櫃</t>
         </is>
       </c>
-      <c r="B114" t="n">
-        <v>0.050946</v>
-      </c>
-      <c r="C114" t="n">
-        <v>0.029436</v>
-      </c>
+      <c r="B114" t="inlineStr"/>
+      <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr"/>
-      <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr"/>
+      <c r="E114" t="n">
+        <v>0.000429</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0.000733</v>
+      </c>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr"/>
-      <c r="I114" t="n">
-        <v>0.000429</v>
-      </c>
-      <c r="J114" t="n">
-        <v>0.000733</v>
-      </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
@@ -4615,34 +4263,31 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>25255.472782</v>
+        <v>29221.238724</v>
       </c>
       <c r="C115" t="n">
-        <v>25583.707465</v>
+        <v>23689.328803</v>
       </c>
       <c r="D115" t="n">
-        <v>32739.140457</v>
+        <v>23865.695498</v>
       </c>
       <c r="E115" t="n">
-        <v>24301.194138</v>
+        <v>18716.52571</v>
       </c>
       <c r="F115" t="n">
-        <v>29221.238724</v>
+        <v>29109.164676</v>
       </c>
       <c r="G115" t="n">
-        <v>23689.328803</v>
+        <v>17026.871017</v>
       </c>
       <c r="H115" t="n">
-        <v>23865.695498</v>
+        <v>17907.065865</v>
       </c>
       <c r="I115" t="n">
-        <v>18716.52571</v>
+        <v>17209.941215</v>
       </c>
       <c r="J115" t="n">
-        <v>29109.164676</v>
-      </c>
-      <c r="K115" t="n">
-        <v>17026.871017</v>
+        <v>22415.774526</v>
       </c>
     </row>
     <row r="116">
@@ -4652,34 +4297,31 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>20.250653</v>
+        <v>17.786353</v>
       </c>
       <c r="C116" t="n">
-        <v>18.582973</v>
+        <v>21.297676</v>
       </c>
       <c r="D116" t="n">
-        <v>24.835122</v>
+        <v>13.45781</v>
       </c>
       <c r="E116" t="n">
-        <v>22.129946</v>
+        <v>10.86563</v>
       </c>
       <c r="F116" t="n">
-        <v>17.786353</v>
+        <v>10.11165</v>
       </c>
       <c r="G116" t="n">
-        <v>21.297676</v>
+        <v>13.436873</v>
       </c>
       <c r="H116" t="n">
-        <v>13.45781</v>
+        <v>12.266752</v>
       </c>
       <c r="I116" t="n">
-        <v>10.86563</v>
+        <v>12.098587</v>
       </c>
       <c r="J116" t="n">
-        <v>10.11165</v>
-      </c>
-      <c r="K116" t="n">
-        <v>13.436873</v>
+        <v>19.597589</v>
       </c>
     </row>
     <row r="117">
@@ -4689,34 +4331,31 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>893.075661</v>
+        <v>970.944972</v>
       </c>
       <c r="C117" t="n">
-        <v>805.4858359999999</v>
+        <v>1232.292849</v>
       </c>
       <c r="D117" t="n">
-        <v>826.805561</v>
+        <v>813.427695</v>
       </c>
       <c r="E117" t="n">
-        <v>928.809391</v>
+        <v>616.561423</v>
       </c>
       <c r="F117" t="n">
-        <v>970.944972</v>
+        <v>753.0441510000001</v>
       </c>
       <c r="G117" t="n">
-        <v>1232.292849</v>
+        <v>795.101355</v>
       </c>
       <c r="H117" t="n">
-        <v>813.427695</v>
+        <v>1054.902316</v>
       </c>
       <c r="I117" t="n">
-        <v>616.561423</v>
+        <v>621.182799</v>
       </c>
       <c r="J117" t="n">
-        <v>765.001264</v>
-      </c>
-      <c r="K117" t="n">
-        <v>795.101355</v>
+        <v>611.530382</v>
       </c>
     </row>
     <row r="118">
@@ -4726,34 +4365,31 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.118458</v>
+        <v>0.150084</v>
       </c>
       <c r="C118" t="n">
-        <v>0.123824</v>
+        <v>0.119453</v>
       </c>
       <c r="D118" t="n">
-        <v>0.13111</v>
+        <v>0.1368</v>
       </c>
       <c r="E118" t="n">
-        <v>0.072089</v>
+        <v>0.242976</v>
       </c>
       <c r="F118" t="n">
-        <v>0.150084</v>
+        <v>0.15816</v>
       </c>
       <c r="G118" t="n">
-        <v>0.119453</v>
+        <v>0.229197</v>
       </c>
       <c r="H118" t="n">
-        <v>0.1368</v>
+        <v>0.311284</v>
       </c>
       <c r="I118" t="n">
-        <v>0.242976</v>
+        <v>0.2129</v>
       </c>
       <c r="J118" t="n">
-        <v>0.15816</v>
-      </c>
-      <c r="K118" t="n">
-        <v>0.229197</v>
+        <v>0.395204</v>
       </c>
     </row>
     <row r="119">
@@ -4763,34 +4399,31 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>584.965255</v>
+        <v>237.604652</v>
       </c>
       <c r="C119" t="n">
-        <v>392.91339</v>
+        <v>297.191071</v>
       </c>
       <c r="D119" t="n">
-        <v>405.627643</v>
+        <v>188.306349</v>
       </c>
       <c r="E119" t="n">
-        <v>199.655727</v>
+        <v>2009.813657</v>
       </c>
       <c r="F119" t="n">
-        <v>237.604652</v>
+        <v>346.941465</v>
       </c>
       <c r="G119" t="n">
-        <v>297.191071</v>
+        <v>2028.738573</v>
       </c>
       <c r="H119" t="n">
-        <v>188.306349</v>
+        <v>2170.851283</v>
       </c>
       <c r="I119" t="n">
-        <v>2009.813657</v>
+        <v>1410.051718</v>
       </c>
       <c r="J119" t="n">
-        <v>334.984352</v>
-      </c>
-      <c r="K119" t="n">
-        <v>2028.738573</v>
+        <v>2921.042101</v>
       </c>
     </row>
     <row r="120">
@@ -4800,34 +4433,31 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.426948</v>
+        <v>2.779475</v>
       </c>
       <c r="C120" t="n">
-        <v>0.312588</v>
+        <v>2.073253</v>
       </c>
       <c r="D120" t="n">
-        <v>3.423157</v>
+        <v>2.173097</v>
       </c>
       <c r="E120" t="n">
-        <v>1.656723</v>
+        <v>1.498725</v>
       </c>
       <c r="F120" t="n">
-        <v>2.779475</v>
+        <v>1.880031</v>
       </c>
       <c r="G120" t="n">
-        <v>2.073253</v>
+        <v>2.860901</v>
       </c>
       <c r="H120" t="n">
-        <v>2.173097</v>
+        <v>1.897831</v>
       </c>
       <c r="I120" t="n">
-        <v>1.498725</v>
+        <v>1.719239</v>
       </c>
       <c r="J120" t="n">
-        <v>1.880031</v>
-      </c>
-      <c r="K120" t="n">
-        <v>2.860901</v>
+        <v>2.523746</v>
       </c>
     </row>
     <row r="121">
@@ -4837,34 +4467,31 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>56.860276</v>
+        <v>160.911874</v>
       </c>
       <c r="C121" t="n">
-        <v>73.22282199999999</v>
+        <v>79.776139</v>
       </c>
       <c r="D121" t="n">
-        <v>95.43985600000001</v>
+        <v>58.508732</v>
       </c>
       <c r="E121" t="n">
-        <v>620.293591</v>
+        <v>86.105074</v>
       </c>
       <c r="F121" t="n">
-        <v>160.911874</v>
+        <v>51.561188</v>
       </c>
       <c r="G121" t="n">
-        <v>79.776139</v>
+        <v>29.226817</v>
       </c>
       <c r="H121" t="n">
-        <v>58.508732</v>
+        <v>74.29553300000001</v>
       </c>
       <c r="I121" t="n">
-        <v>86.105074</v>
+        <v>52.944199</v>
       </c>
       <c r="J121" t="n">
-        <v>51.561188</v>
-      </c>
-      <c r="K121" t="n">
-        <v>29.226817</v>
+        <v>49.507243</v>
       </c>
     </row>
     <row r="122">
@@ -4874,34 +4501,31 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>8.628501999999999</v>
+        <v>7.803697</v>
       </c>
       <c r="C122" t="n">
-        <v>7.654183</v>
+        <v>6.192561</v>
       </c>
       <c r="D122" t="n">
-        <v>9.449596</v>
+        <v>8.273391</v>
       </c>
       <c r="E122" t="n">
-        <v>6.313389</v>
+        <v>4.759663</v>
       </c>
       <c r="F122" t="n">
-        <v>7.803697</v>
+        <v>7.401011</v>
       </c>
       <c r="G122" t="n">
-        <v>6.192561</v>
+        <v>5.426103</v>
       </c>
       <c r="H122" t="n">
-        <v>8.273391</v>
+        <v>6.686925</v>
       </c>
       <c r="I122" t="n">
-        <v>4.759663</v>
+        <v>7.952223</v>
       </c>
       <c r="J122" t="n">
-        <v>7.401011</v>
-      </c>
-      <c r="K122" t="n">
-        <v>5.426103</v>
+        <v>5.702471</v>
       </c>
     </row>
     <row r="123">
@@ -4911,34 +4535,31 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>13.522615</v>
+        <v>46.057863</v>
       </c>
       <c r="C123" t="n">
-        <v>17.063821</v>
+        <v>29.321354</v>
       </c>
       <c r="D123" t="n">
-        <v>20.429546</v>
+        <v>25.745741</v>
       </c>
       <c r="E123" t="n">
-        <v>29.518382</v>
+        <v>31.758045</v>
       </c>
       <c r="F123" t="n">
-        <v>46.057863</v>
+        <v>43.067624</v>
       </c>
       <c r="G123" t="n">
-        <v>29.321354</v>
+        <v>28.785075</v>
       </c>
       <c r="H123" t="n">
-        <v>25.745741</v>
+        <v>33.512378</v>
       </c>
       <c r="I123" t="n">
-        <v>31.758045</v>
+        <v>23.447801</v>
       </c>
       <c r="J123" t="n">
-        <v>43.067624</v>
-      </c>
-      <c r="K123" t="n">
-        <v>28.785075</v>
+        <v>35.0707</v>
       </c>
     </row>
     <row r="124">
@@ -4948,30 +4569,31 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>19.219588</v>
+        <v>13.454182</v>
       </c>
       <c r="C124" t="n">
-        <v>13.233913</v>
-      </c>
-      <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr"/>
+        <v>9.400376</v>
+      </c>
+      <c r="D124" t="n">
+        <v>20.184931</v>
+      </c>
+      <c r="E124" t="n">
+        <v>40.641022</v>
+      </c>
       <c r="F124" t="n">
-        <v>13.454182</v>
+        <v>104.901909</v>
       </c>
       <c r="G124" t="n">
-        <v>9.400376</v>
+        <v>35.760378</v>
       </c>
       <c r="H124" t="n">
-        <v>20.184931</v>
+        <v>101.905354</v>
       </c>
       <c r="I124" t="n">
-        <v>40.641022</v>
+        <v>41.723378</v>
       </c>
       <c r="J124" t="n">
-        <v>104.901909</v>
-      </c>
-      <c r="K124" t="n">
-        <v>35.760378</v>
+        <v>8.526634</v>
       </c>
     </row>
     <row r="125">
@@ -4981,34 +4603,31 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.000762</v>
+        <v>0.001496</v>
       </c>
       <c r="C125" t="n">
-        <v>0.002955</v>
+        <v>0.005709</v>
       </c>
       <c r="D125" t="n">
-        <v>0.001541</v>
+        <v>0.002274</v>
       </c>
       <c r="E125" t="n">
-        <v>0.002365</v>
+        <v>0.001796</v>
       </c>
       <c r="F125" t="n">
-        <v>0.001496</v>
+        <v>0.001943</v>
       </c>
       <c r="G125" t="n">
-        <v>0.005709</v>
+        <v>0.001247</v>
       </c>
       <c r="H125" t="n">
-        <v>0.002274</v>
+        <v>0.00146</v>
       </c>
       <c r="I125" t="n">
-        <v>0.001796</v>
+        <v>0.000743</v>
       </c>
       <c r="J125" t="n">
-        <v>0.001943</v>
-      </c>
-      <c r="K125" t="n">
-        <v>0.001247</v>
+        <v>0.001786</v>
       </c>
     </row>
     <row r="126">
@@ -5018,34 +4637,31 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>653.593252</v>
+        <v>1158.378359</v>
       </c>
       <c r="C126" t="n">
-        <v>887.262399</v>
+        <v>980.0030400000001</v>
       </c>
       <c r="D126" t="n">
-        <v>950.6537</v>
+        <v>793.010167</v>
       </c>
       <c r="E126" t="n">
-        <v>725.094562</v>
+        <v>718.786573</v>
       </c>
       <c r="F126" t="n">
-        <v>1158.378359</v>
+        <v>927.2286810000001</v>
       </c>
       <c r="G126" t="n">
-        <v>980.0030400000001</v>
+        <v>1101.476089</v>
       </c>
       <c r="H126" t="n">
-        <v>793.010167</v>
+        <v>1527.017845</v>
       </c>
       <c r="I126" t="n">
-        <v>718.786573</v>
+        <v>1302.824046</v>
       </c>
       <c r="J126" t="n">
-        <v>927.2286810000001</v>
-      </c>
-      <c r="K126" t="n">
-        <v>1101.476089</v>
+        <v>841.355541</v>
       </c>
     </row>
     <row r="127">
@@ -5055,34 +4671,31 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.008103000000000001</v>
+        <v>0.010944</v>
       </c>
       <c r="C127" t="n">
-        <v>0.013165</v>
+        <v>0.051479</v>
       </c>
       <c r="D127" t="n">
-        <v>0.01960175</v>
+        <v>0.019638</v>
       </c>
       <c r="E127" t="n">
-        <v>0.008484</v>
+        <v>0.013057</v>
       </c>
       <c r="F127" t="n">
-        <v>0.010944</v>
+        <v>0.011711</v>
       </c>
       <c r="G127" t="n">
-        <v>0.051479</v>
+        <v>0.01282675</v>
       </c>
       <c r="H127" t="n">
-        <v>0.019638</v>
+        <v>0.010744</v>
       </c>
       <c r="I127" t="n">
-        <v>0.013057</v>
+        <v>0.009403</v>
       </c>
       <c r="J127" t="n">
-        <v>0.011711</v>
-      </c>
-      <c r="K127" t="n">
-        <v>0.01282675</v>
+        <v>0.005297</v>
       </c>
     </row>
     <row r="128">
@@ -5092,34 +4705,31 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>185.434387</v>
+        <v>362.16461</v>
       </c>
       <c r="C128" t="n">
-        <v>181.027348</v>
+        <v>135.759536</v>
       </c>
       <c r="D128" t="n">
-        <v>169.869811</v>
+        <v>184.75593</v>
       </c>
       <c r="E128" t="n">
-        <v>123.151594</v>
+        <v>143.780451</v>
       </c>
       <c r="F128" t="n">
-        <v>362.16461</v>
+        <v>142.344478</v>
       </c>
       <c r="G128" t="n">
-        <v>135.759536</v>
+        <v>41.631818</v>
       </c>
       <c r="H128" t="n">
-        <v>184.75593</v>
+        <v>218.704712</v>
       </c>
       <c r="I128" t="n">
-        <v>143.780451</v>
+        <v>12.374039</v>
       </c>
       <c r="J128" t="n">
-        <v>142.344478</v>
-      </c>
-      <c r="K128" t="n">
-        <v>41.631818</v>
+        <v>3.083981</v>
       </c>
     </row>
     <row r="129">
@@ -5129,31 +4739,28 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.000602</v>
+        <v>7.7e-05</v>
       </c>
       <c r="C129" t="n">
-        <v>2.1e-05</v>
+        <v>0.000127</v>
       </c>
       <c r="D129" t="n">
-        <v>0.000411</v>
+        <v>1.7e-05</v>
       </c>
       <c r="E129" t="n">
-        <v>0.001084</v>
-      </c>
-      <c r="F129" t="n">
-        <v>7.7e-05</v>
-      </c>
-      <c r="G129" t="n">
-        <v>0.000127</v>
-      </c>
+        <v>0.000413</v>
+      </c>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
-        <v>1.7e-05</v>
+        <v>0.000429</v>
       </c>
       <c r="I129" t="n">
-        <v>0.000413</v>
-      </c>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
+        <v>0.000532</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.000311</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
@@ -5162,34 +4769,31 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>17156.764051</v>
+        <v>35449.998064</v>
       </c>
       <c r="C130" t="n">
-        <v>20598.012892</v>
+        <v>28927.249252</v>
       </c>
       <c r="D130" t="n">
-        <v>25109.015918</v>
+        <v>20148.564437</v>
       </c>
       <c r="E130" t="n">
-        <v>23963.659659</v>
+        <v>19128.336859</v>
       </c>
       <c r="F130" t="n">
-        <v>35449.998064</v>
+        <v>21837.620673</v>
       </c>
       <c r="G130" t="n">
-        <v>28927.249252</v>
+        <v>19211.706761</v>
       </c>
       <c r="H130" t="n">
-        <v>20148.564437</v>
+        <v>31667.832324</v>
       </c>
       <c r="I130" t="n">
-        <v>19128.336859</v>
+        <v>16449.342725</v>
       </c>
       <c r="J130" t="n">
-        <v>21837.620673</v>
-      </c>
-      <c r="K130" t="n">
-        <v>19211.706761</v>
+        <v>16278.565632</v>
       </c>
     </row>
     <row r="131">
@@ -5199,34 +4803,31 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>74.259749</v>
+        <v>313.057836</v>
       </c>
       <c r="C131" t="n">
-        <v>448.914137</v>
+        <v>258.249554</v>
       </c>
       <c r="D131" t="n">
-        <v>294.731167</v>
+        <v>190.677356</v>
       </c>
       <c r="E131" t="n">
-        <v>133.126017</v>
+        <v>193.630935</v>
       </c>
       <c r="F131" t="n">
-        <v>313.057836</v>
+        <v>137.66002</v>
       </c>
       <c r="G131" t="n">
-        <v>258.249554</v>
+        <v>158.800948</v>
       </c>
       <c r="H131" t="n">
-        <v>190.677356</v>
+        <v>142.063186</v>
       </c>
       <c r="I131" t="n">
-        <v>193.630935</v>
+        <v>108.445934</v>
       </c>
       <c r="J131" t="n">
-        <v>137.66002</v>
-      </c>
-      <c r="K131" t="n">
-        <v>158.800948</v>
+        <v>135.397884</v>
       </c>
     </row>
     <row r="132">
@@ -5236,34 +4837,31 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>50.226125</v>
+        <v>11.910874</v>
       </c>
       <c r="C132" t="n">
-        <v>77.64404500000001</v>
+        <v>26.483238</v>
       </c>
       <c r="D132" t="n">
-        <v>43.13955</v>
+        <v>130.568197</v>
       </c>
       <c r="E132" t="n">
-        <v>54.037073</v>
+        <v>55.324957</v>
       </c>
       <c r="F132" t="n">
-        <v>11.910874</v>
+        <v>57.040545</v>
       </c>
       <c r="G132" t="n">
-        <v>26.483238</v>
+        <v>41.800411</v>
       </c>
       <c r="H132" t="n">
-        <v>130.568197</v>
+        <v>15.258326</v>
       </c>
       <c r="I132" t="n">
-        <v>55.324957</v>
+        <v>37.980158</v>
       </c>
       <c r="J132" t="n">
-        <v>57.040545</v>
-      </c>
-      <c r="K132" t="n">
-        <v>41.800411</v>
+        <v>10.626671</v>
       </c>
     </row>
     <row r="133">
@@ -5273,34 +4871,31 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.321457</v>
+        <v>0.463364</v>
       </c>
       <c r="C133" t="n">
-        <v>0.260748</v>
+        <v>0.293248</v>
       </c>
       <c r="D133" t="n">
-        <v>0.472466</v>
+        <v>0.280048</v>
       </c>
       <c r="E133" t="n">
-        <v>0.6153920000000001</v>
+        <v>0.205582</v>
       </c>
       <c r="F133" t="n">
-        <v>0.463364</v>
+        <v>0.14767</v>
       </c>
       <c r="G133" t="n">
-        <v>0.293248</v>
+        <v>0.162321</v>
       </c>
       <c r="H133" t="n">
-        <v>0.280048</v>
+        <v>0.151156</v>
       </c>
       <c r="I133" t="n">
-        <v>0.205582</v>
+        <v>0.168285</v>
       </c>
       <c r="J133" t="n">
-        <v>0.14767</v>
-      </c>
-      <c r="K133" t="n">
-        <v>0.162321</v>
+        <v>0.143367</v>
       </c>
     </row>
     <row r="134">
@@ -5310,34 +4905,31 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.018194</v>
+        <v>0.064164</v>
       </c>
       <c r="C134" t="n">
-        <v>0.02048</v>
+        <v>0.046877</v>
       </c>
       <c r="D134" t="n">
-        <v>0.056008</v>
+        <v>0.052364</v>
       </c>
       <c r="E134" t="n">
-        <v>0.026671</v>
+        <v>0.043636</v>
       </c>
       <c r="F134" t="n">
-        <v>0.064164</v>
+        <v>0.03427</v>
       </c>
       <c r="G134" t="n">
-        <v>0.046877</v>
+        <v>0.021858</v>
       </c>
       <c r="H134" t="n">
-        <v>0.052364</v>
+        <v>0.022643</v>
       </c>
       <c r="I134" t="n">
-        <v>0.043636</v>
+        <v>0.018471</v>
       </c>
       <c r="J134" t="n">
-        <v>0.03427</v>
-      </c>
-      <c r="K134" t="n">
-        <v>0.021858</v>
+        <v>0.012521</v>
       </c>
     </row>
     <row r="135">
@@ -5347,34 +4939,31 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>962.375631</v>
+        <v>1356.040678</v>
       </c>
       <c r="C135" t="n">
-        <v>789.719156</v>
+        <v>2963.163965</v>
       </c>
       <c r="D135" t="n">
-        <v>1550.176211</v>
+        <v>1492.10477</v>
       </c>
       <c r="E135" t="n">
-        <v>1643.28704</v>
+        <v>2663.206052</v>
       </c>
       <c r="F135" t="n">
-        <v>1356.040678</v>
+        <v>2208.951272</v>
       </c>
       <c r="G135" t="n">
-        <v>2963.163965</v>
+        <v>2963.440125</v>
       </c>
       <c r="H135" t="n">
-        <v>1492.10477</v>
+        <v>2607.460876</v>
       </c>
       <c r="I135" t="n">
-        <v>2663.206052</v>
+        <v>1699.557954</v>
       </c>
       <c r="J135" t="n">
-        <v>2208.951272</v>
-      </c>
-      <c r="K135" t="n">
-        <v>2963.440125</v>
+        <v>793.506208</v>
       </c>
     </row>
     <row r="136">
@@ -5384,34 +4973,31 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.073502</v>
+        <v>0.058361</v>
       </c>
       <c r="C136" t="n">
-        <v>0.06665699999999999</v>
+        <v>0.064585</v>
       </c>
       <c r="D136" t="n">
-        <v>0.06342</v>
+        <v>0.135021</v>
       </c>
       <c r="E136" t="n">
-        <v>0.059589</v>
+        <v>0.103216</v>
       </c>
       <c r="F136" t="n">
-        <v>0.058361</v>
+        <v>0.056944</v>
       </c>
       <c r="G136" t="n">
-        <v>0.064585</v>
+        <v>0.20184</v>
       </c>
       <c r="H136" t="n">
-        <v>0.135021</v>
+        <v>0.062697</v>
       </c>
       <c r="I136" t="n">
-        <v>0.103216</v>
+        <v>0.049454</v>
       </c>
       <c r="J136" t="n">
-        <v>0.056944</v>
-      </c>
-      <c r="K136" t="n">
-        <v>0.20184</v>
+        <v>0.16093</v>
       </c>
     </row>
     <row r="137">
@@ -5421,34 +5007,31 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>604.521476</v>
+        <v>257.71903</v>
       </c>
       <c r="C137" t="n">
-        <v>164.932517</v>
+        <v>244.828967</v>
       </c>
       <c r="D137" t="n">
-        <v>134.193253</v>
+        <v>278.44663</v>
       </c>
       <c r="E137" t="n">
-        <v>116.553101</v>
+        <v>143.434833</v>
       </c>
       <c r="F137" t="n">
-        <v>257.71903</v>
+        <v>161.302958</v>
       </c>
       <c r="G137" t="n">
-        <v>244.828967</v>
+        <v>170.540974</v>
       </c>
       <c r="H137" t="n">
-        <v>278.44663</v>
+        <v>396.047682</v>
       </c>
       <c r="I137" t="n">
-        <v>143.434833</v>
+        <v>130.53509</v>
       </c>
       <c r="J137" t="n">
-        <v>161.302958</v>
-      </c>
-      <c r="K137" t="n">
-        <v>170.540974</v>
+        <v>142.222812</v>
       </c>
     </row>
     <row r="138">
@@ -5458,34 +5041,31 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.145907</v>
+        <v>0.07928300000000001</v>
       </c>
       <c r="C138" t="n">
-        <v>0.00883225</v>
+        <v>0.014179</v>
       </c>
       <c r="D138" t="n">
-        <v>0.062358</v>
+        <v>0.009131</v>
       </c>
       <c r="E138" t="n">
-        <v>0.01344233333333333</v>
+        <v>0.033395</v>
       </c>
       <c r="F138" t="n">
-        <v>0.07928300000000001</v>
+        <v>0.07098699999999999</v>
       </c>
       <c r="G138" t="n">
-        <v>0.014179</v>
+        <v>0.006889</v>
       </c>
       <c r="H138" t="n">
-        <v>0.009131</v>
+        <v>0.07658175</v>
       </c>
       <c r="I138" t="n">
-        <v>0.033395</v>
+        <v>0.031658</v>
       </c>
       <c r="J138" t="n">
-        <v>0.07098699999999999</v>
-      </c>
-      <c r="K138" t="n">
-        <v>0.006889</v>
+        <v>0.0393</v>
       </c>
     </row>
     <row r="139">
@@ -5495,34 +5075,31 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>84.713707</v>
+        <v>1097.760524</v>
       </c>
       <c r="C139" t="n">
-        <v>1268.175432</v>
+        <v>53.245693</v>
       </c>
       <c r="D139" t="n">
-        <v>704.0940450000001</v>
+        <v>896.350784</v>
       </c>
       <c r="E139" t="n">
-        <v>2190.043855</v>
+        <v>104.276388</v>
       </c>
       <c r="F139" t="n">
-        <v>1097.760524</v>
+        <v>135.167745</v>
       </c>
       <c r="G139" t="n">
-        <v>53.245693</v>
+        <v>105.526739</v>
       </c>
       <c r="H139" t="n">
-        <v>896.350784</v>
+        <v>65.224189</v>
       </c>
       <c r="I139" t="n">
-        <v>104.276388</v>
+        <v>119.64436</v>
       </c>
       <c r="J139" t="n">
-        <v>135.167745</v>
-      </c>
-      <c r="K139" t="n">
-        <v>105.526739</v>
+        <v>600.754455</v>
       </c>
     </row>
     <row r="140">
@@ -5532,35 +5109,30 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.000221</v>
+        <v>0.001748</v>
       </c>
       <c r="C140" t="n">
-        <v>0.092358</v>
+        <v>0.07703699999999999</v>
       </c>
       <c r="D140" t="n">
-        <v>0.001838</v>
+        <v>0.042344</v>
       </c>
       <c r="E140" t="n">
-        <v>0.060227</v>
+        <v>0.000472</v>
       </c>
       <c r="F140" t="n">
-        <v>0.001748</v>
+        <v>0.000633</v>
       </c>
       <c r="G140" t="n">
-        <v>0.07703699999999999</v>
+        <v>0.09809725</v>
       </c>
       <c r="H140" t="n">
-        <v>0.042344</v>
+        <v>0.000282</v>
       </c>
       <c r="I140" t="n">
-        <v>0.000472</v>
-      </c>
-      <c r="J140" t="n">
-        <v>0.000633</v>
-      </c>
-      <c r="K140" t="n">
-        <v>0.09809725</v>
-      </c>
+        <v>3e-06</v>
+      </c>
+      <c r="J140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
@@ -5569,34 +5141,31 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>1041.428629</v>
+        <v>3020.377115</v>
       </c>
       <c r="C141" t="n">
-        <v>2380.416448</v>
+        <v>1437.331486</v>
       </c>
       <c r="D141" t="n">
-        <v>1652.845578</v>
+        <v>1121.222264</v>
       </c>
       <c r="E141" t="n">
-        <v>3526.040941</v>
+        <v>640.157403</v>
       </c>
       <c r="F141" t="n">
-        <v>3020.377115</v>
+        <v>468.663467</v>
       </c>
       <c r="G141" t="n">
-        <v>1437.331486</v>
+        <v>549.045074</v>
       </c>
       <c r="H141" t="n">
-        <v>1121.222264</v>
+        <v>698.619945</v>
       </c>
       <c r="I141" t="n">
-        <v>597.051374</v>
+        <v>479.877796</v>
       </c>
       <c r="J141" t="n">
-        <v>468.663467</v>
-      </c>
-      <c r="K141" t="n">
-        <v>549.045074</v>
+        <v>399.799791</v>
       </c>
     </row>
     <row r="142">
@@ -5606,34 +5175,31 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.150452</v>
+        <v>0.14244</v>
       </c>
       <c r="C142" t="n">
-        <v>0.192913</v>
+        <v>0.089825</v>
       </c>
       <c r="D142" t="n">
-        <v>0.15041</v>
+        <v>0.08122</v>
       </c>
       <c r="E142" t="n">
-        <v>0.148937</v>
+        <v>0.06408899999999999</v>
       </c>
       <c r="F142" t="n">
-        <v>0.14244</v>
+        <v>0.077725</v>
       </c>
       <c r="G142" t="n">
-        <v>0.089825</v>
+        <v>0.063419</v>
       </c>
       <c r="H142" t="n">
-        <v>0.08122</v>
+        <v>0.06467100000000001</v>
       </c>
       <c r="I142" t="n">
-        <v>0.06408899999999999</v>
+        <v>0.14235</v>
       </c>
       <c r="J142" t="n">
-        <v>0.077725</v>
-      </c>
-      <c r="K142" t="n">
-        <v>0.063419</v>
+        <v>0.20836</v>
       </c>
     </row>
     <row r="143">
@@ -5643,34 +5209,31 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>187.344101</v>
+        <v>95.418598</v>
       </c>
       <c r="C143" t="n">
-        <v>76.255154</v>
+        <v>52.871653</v>
       </c>
       <c r="D143" t="n">
-        <v>110.812447</v>
+        <v>81.429742</v>
       </c>
       <c r="E143" t="n">
-        <v>60.484787</v>
+        <v>56.265111</v>
       </c>
       <c r="F143" t="n">
-        <v>95.418598</v>
+        <v>50.845094</v>
       </c>
       <c r="G143" t="n">
-        <v>52.871653</v>
+        <v>64.46852199999999</v>
       </c>
       <c r="H143" t="n">
-        <v>81.429742</v>
+        <v>144.640413</v>
       </c>
       <c r="I143" t="n">
-        <v>56.265111</v>
+        <v>52.136607</v>
       </c>
       <c r="J143" t="n">
-        <v>50.845094</v>
-      </c>
-      <c r="K143" t="n">
-        <v>64.46852199999999</v>
+        <v>104.102574</v>
       </c>
     </row>
     <row r="144">
@@ -5679,29 +5242,30 @@
           <t>電器電纜平上市</t>
         </is>
       </c>
-      <c r="B144" t="n">
-        <v>115.350516</v>
-      </c>
-      <c r="C144" t="inlineStr"/>
+      <c r="B144" t="inlineStr"/>
+      <c r="C144" t="n">
+        <v>140.144075</v>
+      </c>
       <c r="D144" t="n">
-        <v>161.179866</v>
-      </c>
-      <c r="E144" t="inlineStr"/>
-      <c r="F144" t="inlineStr"/>
+        <v>138.823516</v>
+      </c>
+      <c r="E144" t="n">
+        <v>84.123322</v>
+      </c>
+      <c r="F144" t="n">
+        <v>88.273901</v>
+      </c>
       <c r="G144" t="n">
-        <v>140.144075</v>
+        <v>106.428955</v>
       </c>
       <c r="H144" t="n">
-        <v>138.823516</v>
+        <v>88.783907</v>
       </c>
       <c r="I144" t="n">
-        <v>127.229351</v>
+        <v>65.779991</v>
       </c>
       <c r="J144" t="n">
-        <v>88.273901</v>
-      </c>
-      <c r="K144" t="n">
-        <v>106.428955</v>
+        <v>11.536856</v>
       </c>
     </row>
     <row r="145">
@@ -5711,34 +5275,31 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>4913.476519</v>
+        <v>5943.805008</v>
       </c>
       <c r="C145" t="n">
-        <v>5794.291198</v>
+        <v>5352.027379</v>
       </c>
       <c r="D145" t="n">
-        <v>6928.273658</v>
+        <v>4216.801423</v>
       </c>
       <c r="E145" t="n">
-        <v>5341.944198</v>
+        <v>3310.887283</v>
       </c>
       <c r="F145" t="n">
-        <v>5943.805008</v>
+        <v>3481.54415</v>
       </c>
       <c r="G145" t="n">
-        <v>5352.027379</v>
+        <v>4224.814142</v>
       </c>
       <c r="H145" t="n">
-        <v>4216.801423</v>
+        <v>5680.179409</v>
       </c>
       <c r="I145" t="n">
-        <v>3310.887283</v>
+        <v>3647.395464</v>
       </c>
       <c r="J145" t="n">
-        <v>3481.54415</v>
-      </c>
-      <c r="K145" t="n">
-        <v>4224.814142</v>
+        <v>4527.099155</v>
       </c>
     </row>
     <row r="146">
@@ -5748,34 +5309,31 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.295139</v>
+        <v>0.14276</v>
       </c>
       <c r="C146" t="n">
-        <v>0.701611</v>
+        <v>0.08462</v>
       </c>
       <c r="D146" t="n">
-        <v>0.242673</v>
+        <v>0.096876</v>
       </c>
       <c r="E146" t="n">
-        <v>0.222482</v>
+        <v>0.06115</v>
       </c>
       <c r="F146" t="n">
-        <v>0.14276</v>
+        <v>0.065174</v>
       </c>
       <c r="G146" t="n">
-        <v>0.08462</v>
+        <v>0.08644300000000001</v>
       </c>
       <c r="H146" t="n">
-        <v>0.096876</v>
+        <v>0.05964</v>
       </c>
       <c r="I146" t="n">
-        <v>0.06115</v>
+        <v>0.063456</v>
       </c>
       <c r="J146" t="n">
-        <v>0.065174</v>
-      </c>
-      <c r="K146" t="n">
-        <v>0.08644300000000001</v>
+        <v>0.101268</v>
       </c>
     </row>
     <row r="147">
@@ -5785,34 +5343,31 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>9.756826999999999</v>
+        <v>10.41061</v>
       </c>
       <c r="C147" t="n">
-        <v>10.861653</v>
+        <v>9.936412000000001</v>
       </c>
       <c r="D147" t="n">
-        <v>9.789550999999999</v>
+        <v>28.982313</v>
       </c>
       <c r="E147" t="n">
-        <v>9.075695</v>
+        <v>21.588764</v>
       </c>
       <c r="F147" t="n">
-        <v>10.41061</v>
+        <v>18.532432</v>
       </c>
       <c r="G147" t="n">
-        <v>9.936412000000001</v>
+        <v>24.553908</v>
       </c>
       <c r="H147" t="n">
-        <v>28.982313</v>
+        <v>23.830889</v>
       </c>
       <c r="I147" t="n">
-        <v>21.588764</v>
+        <v>14.305895</v>
       </c>
       <c r="J147" t="n">
-        <v>18.532432</v>
-      </c>
-      <c r="K147" t="n">
-        <v>24.553908</v>
+        <v>13.714789</v>
       </c>
     </row>
     <row r="148">
@@ -5822,34 +5377,31 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.057118</v>
+        <v>0.018248</v>
       </c>
       <c r="C148" t="n">
-        <v>0.070995</v>
+        <v>0.014132</v>
       </c>
       <c r="D148" t="n">
-        <v>0.046428</v>
+        <v>0.01328775</v>
       </c>
       <c r="E148" t="n">
-        <v>0.029028</v>
+        <v>0.023617</v>
       </c>
       <c r="F148" t="n">
-        <v>0.018248</v>
+        <v>0.024176</v>
       </c>
       <c r="G148" t="n">
-        <v>0.014132</v>
+        <v>0.012349</v>
       </c>
       <c r="H148" t="n">
-        <v>0.01328775</v>
+        <v>0.01372</v>
       </c>
       <c r="I148" t="n">
-        <v>0.023617</v>
+        <v>0.014394</v>
       </c>
       <c r="J148" t="n">
-        <v>0.024176</v>
-      </c>
-      <c r="K148" t="n">
-        <v>0.012349</v>
+        <v>0.013219</v>
       </c>
     </row>
     <row r="149">
@@ -5859,34 +5411,31 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>56.281587</v>
+        <v>65.88053499999999</v>
       </c>
       <c r="C149" t="n">
-        <v>48.466276</v>
+        <v>105.135225</v>
       </c>
       <c r="D149" t="n">
-        <v>146.853345</v>
+        <v>99.78953</v>
       </c>
       <c r="E149" t="n">
-        <v>20.282854</v>
+        <v>72.068825</v>
       </c>
       <c r="F149" t="n">
-        <v>65.88053499999999</v>
+        <v>46.423877</v>
       </c>
       <c r="G149" t="n">
-        <v>105.135225</v>
+        <v>51.386202</v>
       </c>
       <c r="H149" t="n">
-        <v>99.78953</v>
+        <v>116.507832</v>
       </c>
       <c r="I149" t="n">
-        <v>72.068825</v>
+        <v>61.506774</v>
       </c>
       <c r="J149" t="n">
-        <v>46.423877</v>
-      </c>
-      <c r="K149" t="n">
-        <v>51.386202</v>
+        <v>48.141145</v>
       </c>
     </row>
     <row r="150">
@@ -5896,34 +5445,31 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.012561</v>
+        <v>0.2213</v>
       </c>
       <c r="C150" t="n">
-        <v>0.048949</v>
+        <v>0.121082</v>
       </c>
       <c r="D150" t="n">
-        <v>0.281443</v>
+        <v>0.199947</v>
       </c>
       <c r="E150" t="n">
-        <v>0.005076</v>
+        <v>0.140783</v>
       </c>
       <c r="F150" t="n">
-        <v>0.2213</v>
+        <v>0.132337</v>
       </c>
       <c r="G150" t="n">
-        <v>0.121082</v>
+        <v>0.169785</v>
       </c>
       <c r="H150" t="n">
-        <v>0.199947</v>
+        <v>0.17559</v>
       </c>
       <c r="I150" t="n">
-        <v>0.140783</v>
+        <v>0.169128</v>
       </c>
       <c r="J150" t="n">
-        <v>0.132337</v>
-      </c>
-      <c r="K150" t="n">
-        <v>0.169785</v>
+        <v>0.190272</v>
       </c>
     </row>
     <row r="151">
@@ -5933,34 +5479,31 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>246129.878716</v>
+        <v>304889.285723</v>
       </c>
       <c r="C151" t="n">
-        <v>187567.231862</v>
+        <v>199573.807519</v>
       </c>
       <c r="D151" t="n">
-        <v>246211.641797</v>
+        <v>205300.203721</v>
       </c>
       <c r="E151" t="n">
-        <v>214113.50732</v>
+        <v>209163.855494</v>
       </c>
       <c r="F151" t="n">
-        <v>304889.285723</v>
+        <v>223851.764794</v>
       </c>
       <c r="G151" t="n">
-        <v>199573.807519</v>
+        <v>255646.88146</v>
       </c>
       <c r="H151" t="n">
-        <v>205300.203721</v>
+        <v>269694.18557</v>
       </c>
       <c r="I151" t="n">
-        <v>209163.855494</v>
+        <v>183651.583309</v>
       </c>
       <c r="J151" t="n">
-        <v>223851.764794</v>
-      </c>
-      <c r="K151" t="n">
-        <v>255646.88146</v>
+        <v>178535.50686</v>
       </c>
     </row>
     <row r="152">
@@ -5970,34 +5513,31 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>57.358641</v>
+        <v>66.413197</v>
       </c>
       <c r="C152" t="n">
-        <v>46.172949</v>
+        <v>68.66043633333332</v>
       </c>
       <c r="D152" t="n">
-        <v>52.237136</v>
+        <v>79.239329</v>
       </c>
       <c r="E152" t="n">
-        <v>68.77581466666668</v>
+        <v>85.90924200000001</v>
       </c>
       <c r="F152" t="n">
-        <v>66.413197</v>
+        <v>85.52268866666667</v>
       </c>
       <c r="G152" t="n">
-        <v>68.66043633333332</v>
+        <v>87.55076699999999</v>
       </c>
       <c r="H152" t="n">
-        <v>79.239329</v>
+        <v>46.793764</v>
       </c>
       <c r="I152" t="n">
-        <v>85.90924200000001</v>
+        <v>32.517482</v>
       </c>
       <c r="J152" t="n">
-        <v>85.52268866666667</v>
-      </c>
-      <c r="K152" t="n">
-        <v>87.55076699999999</v>
+        <v>44.820265</v>
       </c>
     </row>
     <row r="153">
@@ -6007,34 +5547,31 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>1126.014763</v>
+        <v>1778.770117</v>
       </c>
       <c r="C153" t="n">
-        <v>2008.675927</v>
+        <v>1610.391026</v>
       </c>
       <c r="D153" t="n">
-        <v>930.064726</v>
+        <v>1986.703971</v>
       </c>
       <c r="E153" t="n">
-        <v>1510.887253</v>
+        <v>1729.714195</v>
       </c>
       <c r="F153" t="n">
-        <v>1778.770117</v>
+        <v>1585.133452</v>
       </c>
       <c r="G153" t="n">
-        <v>1610.391026</v>
+        <v>1437.164907</v>
       </c>
       <c r="H153" t="n">
-        <v>1986.703971</v>
+        <v>3305.876797</v>
       </c>
       <c r="I153" t="n">
-        <v>1729.714195</v>
+        <v>925.1294779999999</v>
       </c>
       <c r="J153" t="n">
-        <v>1608.125564</v>
-      </c>
-      <c r="K153" t="n">
-        <v>1437.164907</v>
+        <v>2508.546971</v>
       </c>
     </row>
     <row r="154">
@@ -6044,34 +5581,31 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.711408</v>
+        <v>0.541832</v>
       </c>
       <c r="C154" t="n">
-        <v>0.696469</v>
+        <v>0.465636</v>
       </c>
       <c r="D154" t="n">
-        <v>0.950691</v>
+        <v>0.559515</v>
       </c>
       <c r="E154" t="n">
-        <v>0.527877</v>
+        <v>0.472442</v>
       </c>
       <c r="F154" t="n">
-        <v>0.541832</v>
+        <v>0.343509</v>
       </c>
       <c r="G154" t="n">
-        <v>0.466484</v>
+        <v>0.582906</v>
       </c>
       <c r="H154" t="n">
-        <v>0.559515</v>
+        <v>0.54318475</v>
       </c>
       <c r="I154" t="n">
-        <v>0.472442</v>
+        <v>0.57746</v>
       </c>
       <c r="J154" t="n">
-        <v>0.395845</v>
-      </c>
-      <c r="K154" t="n">
-        <v>0.582906</v>
+        <v>0.55032525</v>
       </c>
     </row>
     <row r="155">
@@ -6081,34 +5615,31 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>972.3518</v>
+        <v>6820.63797</v>
       </c>
       <c r="C155" t="n">
-        <v>2047.820503</v>
+        <v>5748.740213</v>
       </c>
       <c r="D155" t="n">
-        <v>4539.84803</v>
+        <v>3979.847094</v>
       </c>
       <c r="E155" t="n">
-        <v>2366.111101</v>
+        <v>4143.613972</v>
       </c>
       <c r="F155" t="n">
-        <v>6820.63797</v>
+        <v>3268.133056</v>
       </c>
       <c r="G155" t="n">
-        <v>5748.740213</v>
+        <v>29016.078938</v>
       </c>
       <c r="H155" t="n">
-        <v>3979.847094</v>
+        <v>2304.113488</v>
       </c>
       <c r="I155" t="n">
-        <v>4143.613972</v>
+        <v>1520.305843</v>
       </c>
       <c r="J155" t="n">
-        <v>3245.140944</v>
-      </c>
-      <c r="K155" t="n">
-        <v>29016.078938</v>
+        <v>27911.52985</v>
       </c>
     </row>
     <row r="156">
@@ -6118,34 +5649,31 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.208691</v>
+        <v>0.469598</v>
       </c>
       <c r="C156" t="n">
-        <v>0.178582</v>
+        <v>0.437764</v>
       </c>
       <c r="D156" t="n">
-        <v>0.244586</v>
+        <v>0.340724</v>
       </c>
       <c r="E156" t="n">
-        <v>0.203788</v>
+        <v>0.254331</v>
       </c>
       <c r="F156" t="n">
-        <v>0.469598</v>
+        <v>0.330163</v>
       </c>
       <c r="G156" t="n">
-        <v>0.436916</v>
+        <v>0.526743</v>
       </c>
       <c r="H156" t="n">
-        <v>0.340724</v>
+        <v>0.56113</v>
       </c>
       <c r="I156" t="n">
-        <v>0.254331</v>
+        <v>0.203102</v>
       </c>
       <c r="J156" t="n">
-        <v>0.277827</v>
-      </c>
-      <c r="K156" t="n">
-        <v>0.526743</v>
+        <v>0.50391825</v>
       </c>
     </row>
     <row r="157">
@@ -6155,34 +5683,31 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>7792.665068</v>
+        <v>21922.178132</v>
       </c>
       <c r="C157" t="n">
-        <v>7658.480151</v>
+        <v>21596.455042</v>
       </c>
       <c r="D157" t="n">
-        <v>21347.714773</v>
+        <v>17643.132366</v>
       </c>
       <c r="E157" t="n">
-        <v>17129.145845</v>
+        <v>10308.66158</v>
       </c>
       <c r="F157" t="n">
-        <v>21922.178132</v>
+        <v>15560.961724</v>
       </c>
       <c r="G157" t="n">
-        <v>21596.455042</v>
+        <v>16569.032242</v>
       </c>
       <c r="H157" t="n">
-        <v>17643.132366</v>
+        <v>17342.985461</v>
       </c>
       <c r="I157" t="n">
-        <v>10550.395861</v>
+        <v>18400.061234</v>
       </c>
       <c r="J157" t="n">
-        <v>15560.961724</v>
-      </c>
-      <c r="K157" t="n">
-        <v>16569.032242</v>
+        <v>17863.67929</v>
       </c>
     </row>
     <row r="158">
@@ -6192,34 +5717,31 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0.913235</v>
+        <v>0.898227</v>
       </c>
       <c r="C158" t="n">
-        <v>1.162125</v>
+        <v>0.6324689999999999</v>
       </c>
       <c r="D158" t="n">
-        <v>1.090835</v>
+        <v>0.569712</v>
       </c>
       <c r="E158" t="n">
-        <v>0.784849</v>
+        <v>0.685992</v>
       </c>
       <c r="F158" t="n">
-        <v>0.898227</v>
+        <v>0.847919</v>
       </c>
       <c r="G158" t="n">
-        <v>0.6324689999999999</v>
+        <v>0.877193</v>
       </c>
       <c r="H158" t="n">
-        <v>0.569712</v>
+        <v>0.600058</v>
       </c>
       <c r="I158" t="n">
-        <v>0.685992</v>
+        <v>0.9077769999999999</v>
       </c>
       <c r="J158" t="n">
-        <v>0.847919</v>
-      </c>
-      <c r="K158" t="n">
-        <v>0.908417</v>
+        <v>0.632109</v>
       </c>
     </row>
     <row r="159">
@@ -6229,34 +5751,31 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>429.733028</v>
+        <v>2616.797834</v>
       </c>
       <c r="C159" t="n">
-        <v>456.012036</v>
+        <v>1023.422566</v>
       </c>
       <c r="D159" t="n">
-        <v>3814.329931</v>
+        <v>1469.13372</v>
       </c>
       <c r="E159" t="n">
-        <v>602.167522</v>
+        <v>1210.84740475</v>
       </c>
       <c r="F159" t="n">
-        <v>2616.797834</v>
+        <v>1200.857364</v>
       </c>
       <c r="G159" t="n">
-        <v>1023.422566</v>
+        <v>990.296252</v>
       </c>
       <c r="H159" t="n">
-        <v>1469.13372</v>
+        <v>2627.372428</v>
       </c>
       <c r="I159" t="n">
-        <v>1210.84740475</v>
+        <v>1174.272544</v>
       </c>
       <c r="J159" t="n">
-        <v>1218.192664</v>
-      </c>
-      <c r="K159" t="n">
-        <v>990.296252</v>
+        <v>1421.980219</v>
       </c>
     </row>
     <row r="160">
@@ -6266,34 +5785,31 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>0.122212</v>
+        <v>0.144987</v>
       </c>
       <c r="C160" t="n">
-        <v>0.100377</v>
+        <v>0.0796785</v>
       </c>
       <c r="D160" t="n">
-        <v>0.104297</v>
+        <v>0.091709</v>
       </c>
       <c r="E160" t="n">
-        <v>0.094176</v>
+        <v>0.07321133333333332</v>
       </c>
       <c r="F160" t="n">
-        <v>0.144987</v>
+        <v>0.12867</v>
       </c>
       <c r="G160" t="n">
-        <v>0.0796785</v>
+        <v>0.134474</v>
       </c>
       <c r="H160" t="n">
-        <v>0.091709</v>
+        <v>0.111127</v>
       </c>
       <c r="I160" t="n">
-        <v>0.07321133333333332</v>
+        <v>0.099802</v>
       </c>
       <c r="J160" t="n">
-        <v>0.12867</v>
-      </c>
-      <c r="K160" t="n">
-        <v>0.134474</v>
+        <v>0.188266</v>
       </c>
     </row>
     <row r="161">
@@ -6303,34 +5819,31 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>1679.984799</v>
+        <v>2132.066124</v>
       </c>
       <c r="C161" t="n">
-        <v>4843.889516</v>
+        <v>1486.959468</v>
       </c>
       <c r="D161" t="n">
-        <v>1304.229169</v>
+        <v>1947.052022</v>
       </c>
       <c r="E161" t="n">
-        <v>2373.007466</v>
+        <v>2898.624755</v>
       </c>
       <c r="F161" t="n">
-        <v>2132.066124</v>
+        <v>2124.416782</v>
       </c>
       <c r="G161" t="n">
-        <v>1486.959468</v>
+        <v>1727.728272</v>
       </c>
       <c r="H161" t="n">
-        <v>1947.052022</v>
+        <v>3330.957109</v>
       </c>
       <c r="I161" t="n">
-        <v>2656.890474</v>
+        <v>1247.567523</v>
       </c>
       <c r="J161" t="n">
-        <v>2107.081482</v>
-      </c>
-      <c r="K161" t="n">
-        <v>1727.728272</v>
+        <v>1450.331249</v>
       </c>
     </row>
     <row r="162">
@@ -6340,34 +5853,31 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>0.046861</v>
+        <v>0.11245</v>
       </c>
       <c r="C162" t="n">
-        <v>0.079084</v>
+        <v>0.085339</v>
       </c>
       <c r="D162" t="n">
-        <v>0.141759</v>
+        <v>0.112254</v>
       </c>
       <c r="E162" t="n">
-        <v>0.08741500000000001</v>
+        <v>0.196656</v>
       </c>
       <c r="F162" t="n">
-        <v>0.11245</v>
+        <v>0.059169</v>
       </c>
       <c r="G162" t="n">
-        <v>0.085339</v>
+        <v>0.216698</v>
       </c>
       <c r="H162" t="n">
-        <v>0.112254</v>
+        <v>0.145061</v>
       </c>
       <c r="I162" t="n">
-        <v>0.196656</v>
+        <v>0.244256</v>
       </c>
       <c r="J162" t="n">
-        <v>0.059169</v>
-      </c>
-      <c r="K162" t="n">
-        <v>0.185474</v>
+        <v>0.09064800000000001</v>
       </c>
     </row>
     <row r="163">
@@ -6377,34 +5887,31 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>39388.800034</v>
+        <v>55753.091306</v>
       </c>
       <c r="C163" t="n">
-        <v>45205.936905</v>
+        <v>42056.973253</v>
       </c>
       <c r="D163" t="n">
-        <v>50654.030068</v>
+        <v>37134.374792</v>
       </c>
       <c r="E163" t="n">
-        <v>35359.84671</v>
+        <v>45284.793045</v>
       </c>
       <c r="F163" t="n">
-        <v>55753.091306</v>
+        <v>52953.900936</v>
       </c>
       <c r="G163" t="n">
-        <v>42056.973253</v>
+        <v>35158.19108</v>
       </c>
       <c r="H163" t="n">
-        <v>37134.374792</v>
+        <v>45253.003247</v>
       </c>
       <c r="I163" t="n">
-        <v>45284.793045</v>
+        <v>34886.42037</v>
       </c>
       <c r="J163" t="n">
-        <v>52953.900936</v>
-      </c>
-      <c r="K163" t="n">
-        <v>35158.19108</v>
+        <v>37504.351616</v>
       </c>
     </row>
     <row r="164">
@@ -6414,34 +5921,31 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>10.27295</v>
+        <v>6.122937</v>
       </c>
       <c r="C164" t="n">
-        <v>5.087297</v>
+        <v>4.828848</v>
       </c>
       <c r="D164" t="n">
-        <v>8.945174</v>
+        <v>4.39085</v>
       </c>
       <c r="E164" t="n">
-        <v>8.168549000000001</v>
+        <v>3.992018</v>
       </c>
       <c r="F164" t="n">
-        <v>6.122937</v>
+        <v>4.706055</v>
       </c>
       <c r="G164" t="n">
-        <v>4.828848</v>
+        <v>6.825057</v>
       </c>
       <c r="H164" t="n">
-        <v>4.39085</v>
+        <v>5.063657</v>
       </c>
       <c r="I164" t="n">
-        <v>3.992018</v>
+        <v>7.290765</v>
       </c>
       <c r="J164" t="n">
-        <v>4.706055</v>
-      </c>
-      <c r="K164" t="n">
-        <v>6.825057</v>
+        <v>5.758477</v>
       </c>
     </row>
     <row r="165">
@@ -6451,34 +5955,31 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>6376.132278</v>
+        <v>20500.120576</v>
       </c>
       <c r="C165" t="n">
-        <v>7454.907283</v>
+        <v>26410.760531</v>
       </c>
       <c r="D165" t="n">
-        <v>7250.317126</v>
+        <v>13215.001859</v>
       </c>
       <c r="E165" t="n">
-        <v>17358.622509</v>
+        <v>10256.003434</v>
       </c>
       <c r="F165" t="n">
-        <v>20500.120576</v>
+        <v>12710.957755</v>
       </c>
       <c r="G165" t="n">
-        <v>26410.760531</v>
+        <v>9663.959551</v>
       </c>
       <c r="H165" t="n">
-        <v>13215.001859</v>
+        <v>10831.789233</v>
       </c>
       <c r="I165" t="n">
-        <v>10256.003434</v>
+        <v>7673.8907</v>
       </c>
       <c r="J165" t="n">
-        <v>12710.957755</v>
-      </c>
-      <c r="K165" t="n">
-        <v>9663.959551</v>
+        <v>7164.955578</v>
       </c>
     </row>
     <row r="166">
@@ -6488,34 +5989,31 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>0.347794</v>
+        <v>0.265974</v>
       </c>
       <c r="C166" t="n">
-        <v>0.356732</v>
+        <v>0.253577</v>
       </c>
       <c r="D166" t="n">
-        <v>0.662868</v>
+        <v>0.238332</v>
       </c>
       <c r="E166" t="n">
-        <v>0.51947</v>
+        <v>0.12927775</v>
       </c>
       <c r="F166" t="n">
-        <v>0.265974</v>
+        <v>0.120142</v>
       </c>
       <c r="G166" t="n">
-        <v>0.253577</v>
+        <v>0.337804</v>
       </c>
       <c r="H166" t="n">
-        <v>0.238332</v>
+        <v>0.286702</v>
       </c>
       <c r="I166" t="n">
-        <v>0.12927775</v>
+        <v>0.188646</v>
       </c>
       <c r="J166" t="n">
-        <v>0.120142</v>
-      </c>
-      <c r="K166" t="n">
-        <v>0.337804</v>
+        <v>0.142492</v>
       </c>
     </row>
     <row r="167">
@@ -6525,34 +6023,31 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>3203.289644</v>
+        <v>3850.866249</v>
       </c>
       <c r="C167" t="n">
-        <v>3363.930259</v>
+        <v>2010.607199</v>
       </c>
       <c r="D167" t="n">
-        <v>3590.364343</v>
+        <v>1849.664547</v>
       </c>
       <c r="E167" t="n">
-        <v>2810.956448</v>
+        <v>1437.304534</v>
       </c>
       <c r="F167" t="n">
-        <v>3850.866249</v>
+        <v>2068.85697</v>
       </c>
       <c r="G167" t="n">
-        <v>2010.607199</v>
+        <v>2373.833127</v>
       </c>
       <c r="H167" t="n">
-        <v>1849.664547</v>
+        <v>1690.235424</v>
       </c>
       <c r="I167" t="n">
-        <v>1437.304534</v>
+        <v>1309.380951</v>
       </c>
       <c r="J167" t="n">
-        <v>2068.85697</v>
-      </c>
-      <c r="K167" t="n">
-        <v>2373.833127</v>
+        <v>1863.972776</v>
       </c>
     </row>
     <row r="168">
@@ -6562,34 +6057,31 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>0.06085</v>
+        <v>1.867231</v>
       </c>
       <c r="C168" t="n">
-        <v>0.311449</v>
+        <v>0.8304</v>
       </c>
       <c r="D168" t="n">
-        <v>0.028226</v>
+        <v>1.067919</v>
       </c>
       <c r="E168" t="n">
-        <v>0.307002</v>
+        <v>1.006393</v>
       </c>
       <c r="F168" t="n">
-        <v>1.867231</v>
+        <v>1.488073</v>
       </c>
       <c r="G168" t="n">
-        <v>0.8304</v>
+        <v>1.226363</v>
       </c>
       <c r="H168" t="n">
-        <v>1.067919</v>
+        <v>0.804508</v>
       </c>
       <c r="I168" t="n">
-        <v>1.006393</v>
+        <v>0.939728</v>
       </c>
       <c r="J168" t="n">
-        <v>1.488073</v>
-      </c>
-      <c r="K168" t="n">
-        <v>1.226363</v>
+        <v>0.712465</v>
       </c>
     </row>
     <row r="169">
@@ -6599,34 +6091,31 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>10.297645</v>
+        <v>3139.295951</v>
       </c>
       <c r="C169" t="n">
-        <v>15.193654</v>
+        <v>1291.778888</v>
       </c>
       <c r="D169" t="n">
-        <v>26.352452</v>
+        <v>1359.323921</v>
       </c>
       <c r="E169" t="n">
-        <v>1239.642301</v>
+        <v>839.6985069999999</v>
       </c>
       <c r="F169" t="n">
-        <v>3139.295951</v>
+        <v>894.768297</v>
       </c>
       <c r="G169" t="n">
-        <v>1291.778888</v>
+        <v>815.884941</v>
       </c>
       <c r="H169" t="n">
-        <v>1359.323921</v>
+        <v>1400.862561</v>
       </c>
       <c r="I169" t="n">
-        <v>839.6985069999999</v>
+        <v>527.488537</v>
       </c>
       <c r="J169" t="n">
-        <v>894.768297</v>
-      </c>
-      <c r="K169" t="n">
-        <v>815.884941</v>
+        <v>555.074196</v>
       </c>
     </row>
     <row r="170">
@@ -6636,35 +6125,30 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>0.007553</v>
+        <v>0.022387</v>
       </c>
       <c r="C170" t="n">
-        <v>0.003842</v>
+        <v>0.011223</v>
       </c>
       <c r="D170" t="n">
-        <v>0.000674</v>
+        <v>0.002333</v>
       </c>
       <c r="E170" t="n">
-        <v>0.008137999999999999</v>
+        <v>0.005333</v>
       </c>
       <c r="F170" t="n">
-        <v>0.022387</v>
+        <v>0.004641</v>
       </c>
       <c r="G170" t="n">
-        <v>0.001583</v>
+        <v>0.001331</v>
       </c>
       <c r="H170" t="n">
-        <v>0.002333</v>
+        <v>0.0007470000000000001</v>
       </c>
       <c r="I170" t="n">
-        <v>0.001329</v>
-      </c>
-      <c r="J170" t="n">
-        <v>0.001477</v>
-      </c>
-      <c r="K170" t="n">
-        <v>0.001331</v>
-      </c>
+        <v>0.003183</v>
+      </c>
+      <c r="J170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
@@ -6673,34 +6157,31 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>269.747139</v>
+        <v>551.697779</v>
       </c>
       <c r="C171" t="n">
-        <v>297.366972</v>
+        <v>297.861558</v>
       </c>
       <c r="D171" t="n">
-        <v>405.043226</v>
+        <v>319.044069</v>
       </c>
       <c r="E171" t="n">
-        <v>385.907919</v>
+        <v>351.382043</v>
       </c>
       <c r="F171" t="n">
-        <v>551.697779</v>
+        <v>245.046335</v>
       </c>
       <c r="G171" t="n">
-        <v>297.861558</v>
+        <v>200.925126</v>
       </c>
       <c r="H171" t="n">
-        <v>319.044069</v>
+        <v>891.332178</v>
       </c>
       <c r="I171" t="n">
-        <v>351.382043</v>
+        <v>380.624011</v>
       </c>
       <c r="J171" t="n">
-        <v>245.046335</v>
-      </c>
-      <c r="K171" t="n">
-        <v>200.925126</v>
+        <v>252.00198375</v>
       </c>
     </row>
     <row r="172">
@@ -6710,34 +6191,31 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>0.014538</v>
+        <v>0.013137</v>
       </c>
       <c r="C172" t="n">
-        <v>0.010585</v>
+        <v>0.006357</v>
       </c>
       <c r="D172" t="n">
-        <v>0.012698</v>
+        <v>0.013048</v>
       </c>
       <c r="E172" t="n">
-        <v>0.008316</v>
+        <v>0.006316</v>
       </c>
       <c r="F172" t="n">
-        <v>0.013137</v>
+        <v>0.007833</v>
       </c>
       <c r="G172" t="n">
-        <v>0.006357</v>
+        <v>0.007666</v>
       </c>
       <c r="H172" t="n">
-        <v>0.021946</v>
+        <v>0.008423999999999999</v>
       </c>
       <c r="I172" t="n">
-        <v>0.01032</v>
+        <v>0.008969</v>
       </c>
       <c r="J172" t="n">
-        <v>0.007833</v>
-      </c>
-      <c r="K172" t="n">
-        <v>0.012781</v>
+        <v>0.008723</v>
       </c>
     </row>
     <row r="173">
@@ -6746,24 +6224,17 @@
           <t>食品工業平上市</t>
         </is>
       </c>
-      <c r="B173" t="n">
-        <v>773.6783349999999</v>
-      </c>
-      <c r="C173" t="n">
-        <v>753.666049</v>
-      </c>
-      <c r="D173" t="n">
-        <v>1312.629839</v>
-      </c>
+      <c r="B173" t="inlineStr"/>
+      <c r="C173" t="inlineStr"/>
+      <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr"/>
-      <c r="F173" t="inlineStr"/>
+      <c r="F173" t="n">
+        <v>0.735418</v>
+      </c>
       <c r="G173" t="inlineStr"/>
       <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr"/>
-      <c r="J173" t="n">
-        <v>0.735418</v>
-      </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
@@ -6772,34 +6243,31 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>0.001103</v>
+        <v>0.003119</v>
       </c>
       <c r="C174" t="n">
-        <v>0.000891</v>
+        <v>0.001706</v>
       </c>
       <c r="D174" t="n">
-        <v>0.001254</v>
+        <v>0.01092</v>
       </c>
       <c r="E174" t="n">
-        <v>0.003657</v>
+        <v>0.001098</v>
       </c>
       <c r="F174" t="n">
-        <v>0.003119</v>
+        <v>0.000977</v>
       </c>
       <c r="G174" t="n">
-        <v>0.011346</v>
+        <v>0.005867</v>
       </c>
       <c r="H174" t="n">
-        <v>0.002022</v>
+        <v>0.001971</v>
       </c>
       <c r="I174" t="n">
-        <v>0.001098</v>
+        <v>0.000494</v>
       </c>
       <c r="J174" t="n">
-        <v>0.004141</v>
-      </c>
-      <c r="K174" t="n">
-        <v>0.000752</v>
+        <v>0.001825</v>
       </c>
     </row>
   </sheetData>

--- a/Result/analyze_2.xlsx
+++ b/Result/analyze_2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J174"/>
+  <dimension ref="A1:J175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,47 +436,47 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -487,31 +487,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>88885.523634</v>
+        <v>92586.35597600001</v>
       </c>
       <c r="C2" t="n">
-        <v>92586.35597600001</v>
+        <v>54637.518222</v>
       </c>
       <c r="D2" t="n">
-        <v>54637.518222</v>
+        <v>65405.359272</v>
       </c>
       <c r="E2" t="n">
-        <v>65405.359272</v>
+        <v>64353.140658</v>
       </c>
       <c r="F2" t="n">
-        <v>64353.140658</v>
+        <v>70386.353499</v>
       </c>
       <c r="G2" t="n">
-        <v>70386.353499</v>
+        <v>63331.893018</v>
       </c>
       <c r="H2" t="n">
-        <v>63260.686172</v>
+        <v>50896.278191</v>
       </c>
       <c r="I2" t="n">
-        <v>50896.278191</v>
+        <v>65242.250565</v>
       </c>
       <c r="J2" t="n">
-        <v>65242.250565</v>
+        <v>51876.611083</v>
       </c>
     </row>
     <row r="3">
@@ -521,31 +521,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.670187</v>
+        <v>4.065067</v>
       </c>
       <c r="C3" t="n">
-        <v>4.065067</v>
+        <v>3.332657</v>
       </c>
       <c r="D3" t="n">
-        <v>3.332657</v>
+        <v>5.134843</v>
       </c>
       <c r="E3" t="n">
-        <v>5.134843</v>
+        <v>12.88341</v>
       </c>
       <c r="F3" t="n">
-        <v>12.88341</v>
+        <v>6.306559</v>
       </c>
       <c r="G3" t="n">
-        <v>6.306559</v>
+        <v>4.813261</v>
       </c>
       <c r="H3" t="n">
-        <v>4.813261</v>
+        <v>6.66071</v>
       </c>
       <c r="I3" t="n">
-        <v>6.66071</v>
+        <v>2.920854</v>
       </c>
       <c r="J3" t="n">
-        <v>2.920854</v>
+        <v>4.350234</v>
       </c>
     </row>
     <row r="4">
@@ -555,31 +555,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1117.670322</v>
+        <v>855.579436</v>
       </c>
       <c r="C4" t="n">
-        <v>855.579436</v>
+        <v>767.424752</v>
       </c>
       <c r="D4" t="n">
-        <v>767.424752</v>
+        <v>741.0858030000001</v>
       </c>
       <c r="E4" t="n">
-        <v>741.0858030000001</v>
+        <v>968.803388</v>
       </c>
       <c r="F4" t="n">
-        <v>968.803388</v>
+        <v>780.990329</v>
       </c>
       <c r="G4" t="n">
-        <v>780.990329</v>
+        <v>844.191047</v>
       </c>
       <c r="H4" t="n">
-        <v>844.191047</v>
+        <v>692.246384</v>
       </c>
       <c r="I4" t="n">
-        <v>692.246384</v>
+        <v>802.887867</v>
       </c>
       <c r="J4" t="n">
-        <v>802.887867</v>
+        <v>1617.356041</v>
       </c>
     </row>
     <row r="5">
@@ -589,31 +589,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.450457</v>
+        <v>2.381268</v>
       </c>
       <c r="C5" t="n">
-        <v>2.381268</v>
+        <v>1.721428</v>
       </c>
       <c r="D5" t="n">
-        <v>1.721428</v>
+        <v>1.167368</v>
       </c>
       <c r="E5" t="n">
-        <v>1.167368</v>
+        <v>1.082715</v>
       </c>
       <c r="F5" t="n">
-        <v>1.082715</v>
+        <v>1.167036</v>
       </c>
       <c r="G5" t="n">
-        <v>1.167036</v>
+        <v>2.00258975</v>
       </c>
       <c r="H5" t="n">
-        <v>2.00258975</v>
+        <v>1.026739</v>
       </c>
       <c r="I5" t="n">
-        <v>1.026739</v>
+        <v>0.9920183333333333</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9920183333333333</v>
+        <v>1.296941</v>
       </c>
     </row>
     <row r="6">
@@ -623,31 +623,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>488.255341</v>
+        <v>348.954905</v>
       </c>
       <c r="C6" t="n">
-        <v>348.954905</v>
+        <v>1521.70643</v>
       </c>
       <c r="D6" t="n">
-        <v>1521.70643</v>
+        <v>756.272438</v>
       </c>
       <c r="E6" t="n">
-        <v>756.272438</v>
+        <v>1073.492406</v>
       </c>
       <c r="F6" t="n">
-        <v>1073.492406</v>
+        <v>1162.39281</v>
       </c>
       <c r="G6" t="n">
-        <v>1162.39281</v>
+        <v>640.678449</v>
       </c>
       <c r="H6" t="n">
-        <v>711.885295</v>
+        <v>209.789512</v>
       </c>
       <c r="I6" t="n">
-        <v>209.789512</v>
+        <v>145.869244</v>
       </c>
       <c r="J6" t="n">
-        <v>145.869244</v>
+        <v>759.996632</v>
       </c>
     </row>
     <row r="7">
@@ -657,31 +657,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.146814</v>
+        <v>0.597955</v>
       </c>
       <c r="C7" t="n">
-        <v>0.597955</v>
+        <v>0.075878</v>
       </c>
       <c r="D7" t="n">
-        <v>0.075878</v>
+        <v>0.228206</v>
       </c>
       <c r="E7" t="n">
-        <v>0.228206</v>
+        <v>0.270917</v>
       </c>
       <c r="F7" t="n">
-        <v>0.270917</v>
+        <v>0.253571</v>
       </c>
       <c r="G7" t="n">
-        <v>0.253571</v>
+        <v>0.134186</v>
       </c>
       <c r="H7" t="n">
-        <v>0.134186</v>
+        <v>0.041858</v>
       </c>
       <c r="I7" t="n">
-        <v>0.041858</v>
+        <v>0.097231</v>
       </c>
       <c r="J7" t="n">
-        <v>0.097231</v>
+        <v>0.146173</v>
       </c>
     </row>
     <row r="8">
@@ -691,31 +691,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>980.069929</v>
+        <v>926.218018</v>
       </c>
       <c r="C8" t="n">
-        <v>926.218018</v>
+        <v>1063.032343</v>
       </c>
       <c r="D8" t="n">
-        <v>1063.032343</v>
+        <v>1369.200591</v>
       </c>
       <c r="E8" t="n">
-        <v>1369.200591</v>
+        <v>942.0624299999999</v>
       </c>
       <c r="F8" t="n">
-        <v>942.0624299999999</v>
+        <v>895.523136</v>
       </c>
       <c r="G8" t="n">
-        <v>895.523136</v>
+        <v>921.6118750000001</v>
       </c>
       <c r="H8" t="n">
-        <v>921.6118750000001</v>
+        <v>753.892984</v>
       </c>
       <c r="I8" t="n">
-        <v>753.892984</v>
+        <v>964.354775</v>
       </c>
       <c r="J8" t="n">
-        <v>964.354775</v>
+        <v>948.102269</v>
       </c>
     </row>
     <row r="9">
@@ -725,31 +725,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.772869</v>
+        <v>2.490978</v>
       </c>
       <c r="C9" t="n">
-        <v>2.490978</v>
+        <v>1.17748075</v>
       </c>
       <c r="D9" t="n">
-        <v>1.17748075</v>
+        <v>1.39837225</v>
       </c>
       <c r="E9" t="n">
-        <v>1.39837225</v>
+        <v>1.435431</v>
       </c>
       <c r="F9" t="n">
-        <v>1.435431</v>
+        <v>2.181994</v>
       </c>
       <c r="G9" t="n">
-        <v>2.181994</v>
+        <v>1.714407</v>
       </c>
       <c r="H9" t="n">
-        <v>1.714407</v>
+        <v>1.99273</v>
       </c>
       <c r="I9" t="n">
-        <v>1.99273</v>
+        <v>2.127602</v>
       </c>
       <c r="J9" t="n">
-        <v>2.127602</v>
+        <v>5.50143</v>
       </c>
     </row>
     <row r="10">
@@ -759,31 +759,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2232.320575</v>
+        <v>1119.634381</v>
       </c>
       <c r="C10" t="n">
-        <v>1119.634381</v>
+        <v>850.886402</v>
       </c>
       <c r="D10" t="n">
-        <v>850.886402</v>
+        <v>720.495889</v>
       </c>
       <c r="E10" t="n">
-        <v>720.495889</v>
+        <v>767.397998</v>
       </c>
       <c r="F10" t="n">
-        <v>767.397998</v>
+        <v>882.20808</v>
       </c>
       <c r="G10" t="n">
-        <v>882.20808</v>
+        <v>1480.214998</v>
       </c>
       <c r="H10" t="n">
-        <v>1480.214998</v>
+        <v>1079.407824</v>
       </c>
       <c r="I10" t="n">
-        <v>1079.407824</v>
+        <v>1085.078222</v>
       </c>
       <c r="J10" t="n">
-        <v>1085.078222</v>
+        <v>1592.350211</v>
       </c>
     </row>
     <row r="11">
@@ -793,31 +793,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7544403333333334</v>
+        <v>0.600169</v>
       </c>
       <c r="C11" t="n">
-        <v>0.600169</v>
+        <v>1.807453</v>
       </c>
       <c r="D11" t="n">
-        <v>1.807453</v>
+        <v>0.788442</v>
       </c>
       <c r="E11" t="n">
-        <v>0.788442</v>
+        <v>0.49820625</v>
       </c>
       <c r="F11" t="n">
-        <v>0.49820625</v>
+        <v>0.7551346666666666</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7551346666666666</v>
+        <v>0.548862</v>
       </c>
       <c r="H11" t="n">
-        <v>0.548862</v>
+        <v>0.384309</v>
       </c>
       <c r="I11" t="n">
-        <v>0.384309</v>
+        <v>0.353765</v>
       </c>
       <c r="J11" t="n">
-        <v>0.353765</v>
+        <v>0.423124</v>
       </c>
     </row>
     <row r="12">
@@ -827,31 +827,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>303.313328</v>
+        <v>113.302968</v>
       </c>
       <c r="C12" t="n">
-        <v>113.302968</v>
+        <v>122.996559</v>
       </c>
       <c r="D12" t="n">
-        <v>122.996559</v>
+        <v>87.73246399999999</v>
       </c>
       <c r="E12" t="n">
-        <v>87.73246399999999</v>
+        <v>301.656644</v>
       </c>
       <c r="F12" t="n">
-        <v>301.656644</v>
+        <v>222.464648</v>
       </c>
       <c r="G12" t="n">
-        <v>222.464648</v>
+        <v>745.438097</v>
       </c>
       <c r="H12" t="n">
-        <v>745.438097</v>
+        <v>388.15968</v>
       </c>
       <c r="I12" t="n">
-        <v>388.15968</v>
+        <v>299.604215</v>
       </c>
       <c r="J12" t="n">
-        <v>299.604215</v>
+        <v>332.166739</v>
       </c>
     </row>
     <row r="13">
@@ -861,31 +861,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.062015</v>
+        <v>0.059453</v>
       </c>
       <c r="C13" t="n">
-        <v>0.059453</v>
+        <v>0.046284</v>
       </c>
       <c r="D13" t="n">
-        <v>0.046284</v>
+        <v>0.035646</v>
       </c>
       <c r="E13" t="n">
-        <v>0.035646</v>
+        <v>0.044337</v>
       </c>
       <c r="F13" t="n">
-        <v>0.044337</v>
+        <v>0.065011</v>
       </c>
       <c r="G13" t="n">
-        <v>0.065011</v>
+        <v>0.04549533333333334</v>
       </c>
       <c r="H13" t="n">
-        <v>0.04549533333333334</v>
+        <v>0.030511</v>
       </c>
       <c r="I13" t="n">
-        <v>0.030511</v>
+        <v>0.02172666666666667</v>
       </c>
       <c r="J13" t="n">
-        <v>0.02172666666666667</v>
+        <v>0.0317825</v>
       </c>
     </row>
     <row r="14">
@@ -895,31 +895,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>38606.288991</v>
+        <v>33005.329183</v>
       </c>
       <c r="C14" t="n">
-        <v>33005.329183</v>
+        <v>31624.413326</v>
       </c>
       <c r="D14" t="n">
-        <v>31624.413326</v>
+        <v>25649.875489</v>
       </c>
       <c r="E14" t="n">
-        <v>25649.875489</v>
+        <v>36829.671726</v>
       </c>
       <c r="F14" t="n">
-        <v>36829.671726</v>
+        <v>24951.208776</v>
       </c>
       <c r="G14" t="n">
-        <v>24951.208776</v>
+        <v>31455.451221</v>
       </c>
       <c r="H14" t="n">
-        <v>31455.451221</v>
+        <v>33234.465186</v>
       </c>
       <c r="I14" t="n">
-        <v>33234.465186</v>
+        <v>17038.278289</v>
       </c>
       <c r="J14" t="n">
-        <v>16962.193849</v>
+        <v>17766.254761</v>
       </c>
     </row>
     <row r="15">
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9.192671000000001</v>
+        <v>8.302375</v>
       </c>
       <c r="C15" t="n">
-        <v>8.302375</v>
+        <v>7.101097</v>
       </c>
       <c r="D15" t="n">
-        <v>7.101097</v>
+        <v>7.906817</v>
       </c>
       <c r="E15" t="n">
-        <v>7.906817</v>
+        <v>11.450579</v>
       </c>
       <c r="F15" t="n">
-        <v>11.450579</v>
+        <v>9.621321999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>9.621321999999999</v>
+        <v>6.884802</v>
       </c>
       <c r="H15" t="n">
-        <v>6.884802</v>
+        <v>7.866023</v>
       </c>
       <c r="I15" t="n">
-        <v>7.866023</v>
+        <v>10.947901</v>
       </c>
       <c r="J15" t="n">
-        <v>10.947901</v>
+        <v>7.101847</v>
       </c>
     </row>
     <row r="16">
@@ -963,31 +963,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1229.037194</v>
+        <v>592.8472839999999</v>
       </c>
       <c r="C16" t="n">
-        <v>592.8472839999999</v>
+        <v>1068.677673</v>
       </c>
       <c r="D16" t="n">
-        <v>1068.677673</v>
+        <v>593.969129</v>
       </c>
       <c r="E16" t="n">
-        <v>593.969129</v>
+        <v>760.486909</v>
       </c>
       <c r="F16" t="n">
-        <v>760.486909</v>
+        <v>666.830693</v>
       </c>
       <c r="G16" t="n">
-        <v>666.830693</v>
+        <v>491.303779</v>
       </c>
       <c r="H16" t="n">
-        <v>491.303779</v>
+        <v>1091.990231</v>
       </c>
       <c r="I16" t="n">
-        <v>1091.990231</v>
+        <v>852.850742</v>
       </c>
       <c r="J16" t="n">
-        <v>697.4192420000001</v>
+        <v>1271.26367</v>
       </c>
     </row>
     <row r="17">
@@ -997,31 +997,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.09390900000000001</v>
+        <v>0.070607</v>
       </c>
       <c r="C17" t="n">
-        <v>0.070607</v>
+        <v>0.058583</v>
       </c>
       <c r="D17" t="n">
-        <v>0.058583</v>
+        <v>0.047846</v>
       </c>
       <c r="E17" t="n">
-        <v>0.047846</v>
+        <v>0.036332</v>
       </c>
       <c r="F17" t="n">
-        <v>0.036332</v>
+        <v>0.056001</v>
       </c>
       <c r="G17" t="n">
-        <v>0.056001</v>
+        <v>0.07004000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>0.07004000000000001</v>
+        <v>0.053983</v>
       </c>
       <c r="I17" t="n">
-        <v>0.053983</v>
+        <v>0.061414</v>
       </c>
       <c r="J17" t="n">
-        <v>0.061414</v>
+        <v>0.115474</v>
       </c>
     </row>
     <row r="18">
@@ -1031,31 +1031,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>433.142001</v>
+        <v>460.333694</v>
       </c>
       <c r="C18" t="n">
-        <v>460.333694</v>
+        <v>263.870993</v>
       </c>
       <c r="D18" t="n">
-        <v>263.870993</v>
+        <v>257.258089</v>
       </c>
       <c r="E18" t="n">
-        <v>257.258089</v>
+        <v>700.153453</v>
       </c>
       <c r="F18" t="n">
-        <v>700.153453</v>
+        <v>784.406296</v>
       </c>
       <c r="G18" t="n">
-        <v>784.406296</v>
+        <v>12293.964655</v>
       </c>
       <c r="H18" t="n">
-        <v>12293.964655</v>
+        <v>620.030246</v>
       </c>
       <c r="I18" t="n">
-        <v>620.030246</v>
+        <v>5728.311345</v>
       </c>
       <c r="J18" t="n">
-        <v>5728.311345</v>
+        <v>6133.635645</v>
       </c>
     </row>
     <row r="19">
@@ -1065,31 +1065,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.421391</v>
+        <v>0.666552</v>
       </c>
       <c r="C19" t="n">
-        <v>0.666552</v>
+        <v>2.212432</v>
       </c>
       <c r="D19" t="n">
-        <v>2.212432</v>
+        <v>1.201581</v>
       </c>
       <c r="E19" t="n">
-        <v>1.201581</v>
+        <v>1.264365</v>
       </c>
       <c r="F19" t="n">
-        <v>1.264365</v>
+        <v>1.633723</v>
       </c>
       <c r="G19" t="n">
-        <v>1.633723</v>
+        <v>2.234588</v>
       </c>
       <c r="H19" t="n">
-        <v>2.234588</v>
+        <v>1.350974</v>
       </c>
       <c r="I19" t="n">
-        <v>1.350974</v>
+        <v>1.513105</v>
       </c>
       <c r="J19" t="n">
-        <v>1.513105</v>
+        <v>1.817287</v>
       </c>
     </row>
     <row r="20">
@@ -1099,31 +1099,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5661.701177</v>
+        <v>5259.441078</v>
       </c>
       <c r="C20" t="n">
-        <v>5259.441078</v>
+        <v>3353.306981</v>
       </c>
       <c r="D20" t="n">
-        <v>3353.306981</v>
+        <v>4705.864866</v>
       </c>
       <c r="E20" t="n">
-        <v>4705.864866</v>
+        <v>7314.547126</v>
       </c>
       <c r="F20" t="n">
-        <v>7314.547126</v>
+        <v>5379.148063</v>
       </c>
       <c r="G20" t="n">
-        <v>5379.148063</v>
+        <v>3940.727708</v>
       </c>
       <c r="H20" t="n">
-        <v>3940.727708</v>
+        <v>3494.887648</v>
       </c>
       <c r="I20" t="n">
-        <v>3494.887648</v>
+        <v>2587.82531</v>
       </c>
       <c r="J20" t="n">
-        <v>2587.82531</v>
+        <v>2754.379489</v>
       </c>
     </row>
     <row r="21">
@@ -1133,31 +1133,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.407707</v>
+        <v>0.297397</v>
       </c>
       <c r="C21" t="n">
-        <v>0.297397</v>
+        <v>0.289202</v>
       </c>
       <c r="D21" t="n">
-        <v>0.337121</v>
+        <v>0.381888</v>
       </c>
       <c r="E21" t="n">
-        <v>0.381888</v>
+        <v>0.236467</v>
       </c>
       <c r="F21" t="n">
-        <v>0.236467</v>
+        <v>0.231797</v>
       </c>
       <c r="G21" t="n">
-        <v>0.231797</v>
+        <v>0.315485</v>
       </c>
       <c r="H21" t="n">
-        <v>0.315485</v>
+        <v>0.263044</v>
       </c>
       <c r="I21" t="n">
-        <v>0.263044</v>
+        <v>0.348404</v>
       </c>
       <c r="J21" t="n">
-        <v>0.348404</v>
+        <v>0.236122</v>
       </c>
     </row>
     <row r="22">
@@ -1167,31 +1167,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>173.457935</v>
+        <v>96.576919</v>
       </c>
       <c r="C22" t="n">
-        <v>96.576919</v>
+        <v>134.912417</v>
       </c>
       <c r="D22" t="n">
-        <v>134.912417</v>
+        <v>136.023827</v>
       </c>
       <c r="E22" t="n">
-        <v>136.023827</v>
+        <v>109.538916</v>
       </c>
       <c r="F22" t="n">
-        <v>109.538916</v>
+        <v>91.082618</v>
       </c>
       <c r="G22" t="n">
-        <v>91.082618</v>
+        <v>312.011029</v>
       </c>
       <c r="H22" t="n">
-        <v>312.011029</v>
+        <v>112.827469</v>
       </c>
       <c r="I22" t="n">
-        <v>112.827469</v>
+        <v>102.299707</v>
       </c>
       <c r="J22" t="n">
-        <v>102.299707</v>
+        <v>98.574454</v>
       </c>
     </row>
     <row r="23">
@@ -1201,31 +1201,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.181323</v>
+        <v>0.020694</v>
       </c>
       <c r="C23" t="n">
-        <v>0.020694</v>
+        <v>0.231682</v>
       </c>
       <c r="D23" t="n">
-        <v>0.231682</v>
+        <v>0.198653</v>
       </c>
       <c r="E23" t="n">
-        <v>0.198653</v>
+        <v>0.012894</v>
       </c>
       <c r="F23" t="n">
-        <v>0.012894</v>
+        <v>0.179984</v>
       </c>
       <c r="G23" t="n">
-        <v>0.179984</v>
+        <v>0.194294</v>
       </c>
       <c r="H23" t="n">
-        <v>0.194294</v>
+        <v>0.155027</v>
       </c>
       <c r="I23" t="n">
-        <v>0.155027</v>
+        <v>0.322795</v>
       </c>
       <c r="J23" t="n">
-        <v>0.322795</v>
+        <v>0.295656</v>
       </c>
     </row>
     <row r="24">
@@ -1235,31 +1235,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>272.575433</v>
+        <v>413.901252</v>
       </c>
       <c r="C24" t="n">
-        <v>413.901252</v>
+        <v>559.953737</v>
       </c>
       <c r="D24" t="n">
-        <v>559.953737</v>
+        <v>609.50382</v>
       </c>
       <c r="E24" t="n">
-        <v>609.50382</v>
+        <v>376.309095</v>
       </c>
       <c r="F24" t="n">
-        <v>376.309095</v>
+        <v>566.956783</v>
       </c>
       <c r="G24" t="n">
-        <v>566.956783</v>
+        <v>736.50087</v>
       </c>
       <c r="H24" t="n">
-        <v>736.50087</v>
+        <v>296.144729</v>
       </c>
       <c r="I24" t="n">
-        <v>296.144729</v>
+        <v>337.969955</v>
       </c>
       <c r="J24" t="n">
-        <v>337.969955</v>
+        <v>862.572782</v>
       </c>
     </row>
     <row r="25">
@@ -1269,31 +1269,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.069926</v>
+        <v>0.167024</v>
       </c>
       <c r="C25" t="n">
-        <v>0.167024</v>
+        <v>0.085093</v>
       </c>
       <c r="D25" t="n">
-        <v>0.037174</v>
+        <v>0.02765</v>
       </c>
       <c r="E25" t="n">
-        <v>0.02765</v>
+        <v>0.287736</v>
       </c>
       <c r="F25" t="n">
-        <v>0.287736</v>
+        <v>0.19613</v>
       </c>
       <c r="G25" t="n">
-        <v>0.19613</v>
+        <v>0.112262</v>
       </c>
       <c r="H25" t="n">
-        <v>0.112262</v>
+        <v>0.129903</v>
       </c>
       <c r="I25" t="n">
-        <v>0.129903</v>
+        <v>0.117631</v>
       </c>
       <c r="J25" t="n">
-        <v>0.117631</v>
+        <v>0.150167</v>
       </c>
     </row>
     <row r="26">
@@ -1303,31 +1303,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>444793.551669</v>
+        <v>288293.793547</v>
       </c>
       <c r="C26" t="n">
-        <v>288293.793547</v>
+        <v>230232.353759</v>
       </c>
       <c r="D26" t="n">
-        <v>230232.353759</v>
+        <v>191182.562802</v>
       </c>
       <c r="E26" t="n">
-        <v>191182.562802</v>
+        <v>229960.560629</v>
       </c>
       <c r="F26" t="n">
-        <v>229960.560629</v>
+        <v>233466.654463</v>
       </c>
       <c r="G26" t="n">
-        <v>233466.654463</v>
+        <v>308962.846639</v>
       </c>
       <c r="H26" t="n">
-        <v>308962.846639</v>
+        <v>244308.296052</v>
       </c>
       <c r="I26" t="n">
-        <v>244308.296052</v>
+        <v>268679.700777</v>
       </c>
       <c r="J26" t="n">
-        <v>268263.36376</v>
+        <v>294302.608858</v>
       </c>
     </row>
     <row r="27">
@@ -1337,31 +1337,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>110.047906</v>
+        <v>88.645197</v>
       </c>
       <c r="C27" t="n">
-        <v>88.645197</v>
+        <v>76.91721200000001</v>
       </c>
       <c r="D27" t="n">
-        <v>76.91721200000001</v>
+        <v>72.951875</v>
       </c>
       <c r="E27" t="n">
-        <v>72.951875</v>
+        <v>68.364958</v>
       </c>
       <c r="F27" t="n">
-        <v>68.364958</v>
+        <v>73.215756</v>
       </c>
       <c r="G27" t="n">
-        <v>73.215756</v>
+        <v>71.80604700000001</v>
       </c>
       <c r="H27" t="n">
-        <v>71.80018</v>
+        <v>76.080887</v>
       </c>
       <c r="I27" t="n">
-        <v>76.080887</v>
+        <v>100.164704</v>
       </c>
       <c r="J27" t="n">
-        <v>100.164704</v>
+        <v>98.365404</v>
       </c>
     </row>
     <row r="28">
@@ -1371,31 +1371,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1207.303954</v>
+        <v>797.577685</v>
       </c>
       <c r="C28" t="n">
-        <v>797.577685</v>
+        <v>797.388914</v>
       </c>
       <c r="D28" t="n">
-        <v>797.388914</v>
+        <v>592.914996</v>
       </c>
       <c r="E28" t="n">
-        <v>592.914996</v>
+        <v>436.940119</v>
       </c>
       <c r="F28" t="n">
-        <v>581.181292</v>
+        <v>760.684691</v>
       </c>
       <c r="G28" t="n">
-        <v>760.684691</v>
+        <v>981.010322</v>
       </c>
       <c r="H28" t="n">
-        <v>981.010322</v>
+        <v>717.904361</v>
       </c>
       <c r="I28" t="n">
-        <v>717.904361</v>
+        <v>442.591265</v>
       </c>
       <c r="J28" t="n">
-        <v>442.591265</v>
+        <v>1478.888306</v>
       </c>
     </row>
     <row r="29">
@@ -1405,31 +1405,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3.870842</v>
+        <v>3.014909</v>
       </c>
       <c r="C29" t="n">
-        <v>3.014909</v>
+        <v>2.798222</v>
       </c>
       <c r="D29" t="n">
-        <v>2.798222</v>
+        <v>1.916666</v>
       </c>
       <c r="E29" t="n">
-        <v>1.916666</v>
+        <v>1.346726</v>
       </c>
       <c r="F29" t="n">
-        <v>1.346726</v>
+        <v>2.065627</v>
       </c>
       <c r="G29" t="n">
-        <v>2.065627</v>
+        <v>3.594352</v>
       </c>
       <c r="H29" t="n">
-        <v>3.594352</v>
+        <v>1.656178</v>
       </c>
       <c r="I29" t="n">
-        <v>1.656178</v>
+        <v>2.756974</v>
       </c>
       <c r="J29" t="n">
-        <v>2.756974</v>
+        <v>3.469065</v>
       </c>
     </row>
     <row r="30">
@@ -1439,31 +1439,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>22596.585642</v>
+        <v>16387.243</v>
       </c>
       <c r="C30" t="n">
-        <v>16387.243</v>
+        <v>11929.565547</v>
       </c>
       <c r="D30" t="n">
-        <v>11929.565547</v>
+        <v>10260.117717</v>
       </c>
       <c r="E30" t="n">
-        <v>10260.117717</v>
+        <v>11011.517279</v>
       </c>
       <c r="F30" t="n">
-        <v>10867.276106</v>
+        <v>13748.727764</v>
       </c>
       <c r="G30" t="n">
-        <v>13748.727764</v>
+        <v>14185.616342</v>
       </c>
       <c r="H30" t="n">
-        <v>14185.616342</v>
+        <v>6744.448743</v>
       </c>
       <c r="I30" t="n">
-        <v>6744.448743</v>
+        <v>14878.392181</v>
       </c>
       <c r="J30" t="n">
-        <v>14878.392181</v>
+        <v>24858.261563</v>
       </c>
     </row>
     <row r="31">
@@ -1473,31 +1473,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>5.344747</v>
+        <v>1.44076</v>
       </c>
       <c r="C31" t="n">
-        <v>1.44076</v>
+        <v>4.486392</v>
       </c>
       <c r="D31" t="n">
-        <v>4.486392</v>
+        <v>2.816332</v>
       </c>
       <c r="E31" t="n">
-        <v>2.816332</v>
+        <v>3.909387</v>
       </c>
       <c r="F31" t="n">
-        <v>3.909387</v>
+        <v>5.05311</v>
       </c>
       <c r="G31" t="n">
-        <v>5.05311</v>
+        <v>5.001152</v>
       </c>
       <c r="H31" t="n">
-        <v>5.007019</v>
+        <v>2.07001</v>
       </c>
       <c r="I31" t="n">
-        <v>2.07001</v>
+        <v>3.3173</v>
       </c>
       <c r="J31" t="n">
-        <v>3.3173</v>
+        <v>6.174084</v>
       </c>
     </row>
     <row r="32">
@@ -1507,31 +1507,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>56568.545658</v>
+        <v>51459.656456</v>
       </c>
       <c r="C32" t="n">
-        <v>51459.656456</v>
+        <v>39037.126155</v>
       </c>
       <c r="D32" t="n">
-        <v>39037.126155</v>
+        <v>39486.980971</v>
       </c>
       <c r="E32" t="n">
-        <v>39486.980971</v>
+        <v>45724.884283</v>
       </c>
       <c r="F32" t="n">
-        <v>45724.884283</v>
+        <v>37322.962106</v>
       </c>
       <c r="G32" t="n">
-        <v>37322.962106</v>
+        <v>40553.402589</v>
       </c>
       <c r="H32" t="n">
-        <v>40553.402589</v>
+        <v>31571.572505</v>
       </c>
       <c r="I32" t="n">
-        <v>31571.572505</v>
+        <v>25206.100319</v>
       </c>
       <c r="J32" t="n">
-        <v>25206.100319</v>
+        <v>25941.453102</v>
       </c>
     </row>
     <row r="33">
@@ -1543,18 +1543,20 @@
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
+      <c r="E33" t="n">
+        <v>0.002798</v>
+      </c>
       <c r="F33" t="n">
-        <v>0.002798</v>
+        <v>0.003253</v>
       </c>
       <c r="G33" t="n">
-        <v>0.003253</v>
-      </c>
-      <c r="H33" t="n">
         <v>0.000506</v>
       </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+      <c r="J33" t="n">
+        <v>0.009419</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -1563,31 +1565,31 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>31.301015</v>
+        <v>12.398804</v>
       </c>
       <c r="C34" t="n">
-        <v>12.398804</v>
+        <v>47.413407</v>
       </c>
       <c r="D34" t="n">
-        <v>47.413407</v>
+        <v>49.485111</v>
       </c>
       <c r="E34" t="n">
-        <v>49.485111</v>
+        <v>24.236528</v>
       </c>
       <c r="F34" t="n">
-        <v>24.236528</v>
+        <v>39.447818</v>
       </c>
       <c r="G34" t="n">
-        <v>39.447818</v>
+        <v>34.049065</v>
       </c>
       <c r="H34" t="n">
-        <v>34.049065</v>
+        <v>19.874418</v>
       </c>
       <c r="I34" t="n">
-        <v>19.874418</v>
+        <v>20.940155</v>
       </c>
       <c r="J34" t="n">
-        <v>20.940155</v>
+        <v>48.628192</v>
       </c>
     </row>
     <row r="35">
@@ -1597,31 +1599,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.023263</v>
+        <v>0.018657</v>
       </c>
       <c r="C35" t="n">
-        <v>0.018657</v>
+        <v>0.014902</v>
       </c>
       <c r="D35" t="n">
-        <v>0.014902</v>
+        <v>0.02465</v>
       </c>
       <c r="E35" t="n">
-        <v>0.02465</v>
+        <v>0.012504</v>
       </c>
       <c r="F35" t="n">
-        <v>0.012504</v>
+        <v>0.01397333333333333</v>
       </c>
       <c r="G35" t="n">
-        <v>0.01397333333333333</v>
+        <v>0.0117195</v>
       </c>
       <c r="H35" t="n">
-        <v>0.0117195</v>
+        <v>0.0105355</v>
       </c>
       <c r="I35" t="n">
-        <v>0.0105355</v>
+        <v>0.012004</v>
       </c>
       <c r="J35" t="n">
-        <v>0.012004</v>
+        <v>0.015172</v>
       </c>
     </row>
     <row r="36">
@@ -1631,31 +1633,31 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>162.490625</v>
+        <v>41.126397</v>
       </c>
       <c r="C36" t="n">
-        <v>41.126397</v>
+        <v>40.174258</v>
       </c>
       <c r="D36" t="n">
-        <v>40.174258</v>
+        <v>54.384911</v>
       </c>
       <c r="E36" t="n">
-        <v>54.384911</v>
+        <v>55.723207</v>
       </c>
       <c r="F36" t="n">
-        <v>55.723207</v>
+        <v>61.02265</v>
       </c>
       <c r="G36" t="n">
-        <v>61.02265</v>
+        <v>130.571166</v>
       </c>
       <c r="H36" t="n">
-        <v>130.571166</v>
+        <v>62.995293</v>
       </c>
       <c r="I36" t="n">
-        <v>62.995293</v>
+        <v>65.762333</v>
       </c>
       <c r="J36" t="n">
-        <v>65.762333</v>
+        <v>133.828248</v>
       </c>
     </row>
     <row r="37">
@@ -1665,31 +1667,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.000437</v>
+        <v>0.000169</v>
       </c>
       <c r="C37" t="n">
-        <v>0.000169</v>
+        <v>0.003312</v>
       </c>
       <c r="D37" t="n">
-        <v>0.003312</v>
+        <v>0.00536</v>
       </c>
       <c r="E37" t="n">
-        <v>0.00536</v>
+        <v>0.000182</v>
       </c>
       <c r="F37" t="n">
-        <v>0.000182</v>
+        <v>0.002672</v>
       </c>
       <c r="G37" t="n">
-        <v>0.002672</v>
+        <v>0.002798</v>
       </c>
       <c r="H37" t="n">
-        <v>0.002798</v>
+        <v>0.00166</v>
       </c>
       <c r="I37" t="n">
-        <v>0.00166</v>
+        <v>0.001193</v>
       </c>
       <c r="J37" t="n">
-        <v>0.001193</v>
+        <v>0.000144</v>
       </c>
     </row>
     <row r="38">
@@ -1698,26 +1700,26 @@
           <t>居家生活右上上櫃</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="n">
+      <c r="B38" t="n">
         <v>0.000374</v>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="n">
+        <v>0.000566</v>
+      </c>
       <c r="E38" t="n">
-        <v>0.000566</v>
+        <v>0.000794</v>
       </c>
       <c r="F38" t="n">
-        <v>0.000794</v>
+        <v>0.000838</v>
       </c>
       <c r="G38" t="n">
-        <v>0.000838</v>
+        <v>0.000265</v>
       </c>
       <c r="H38" t="n">
-        <v>0.000265</v>
-      </c>
-      <c r="I38" t="n">
         <v>2.2e-05</v>
       </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
     </row>
     <row r="39">
@@ -1727,31 +1729,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>370.89283</v>
+        <v>334.364303</v>
       </c>
       <c r="C39" t="n">
-        <v>334.364303</v>
+        <v>478.504812</v>
       </c>
       <c r="D39" t="n">
-        <v>478.504812</v>
+        <v>327.742795</v>
       </c>
       <c r="E39" t="n">
-        <v>327.742795</v>
+        <v>283.350769</v>
       </c>
       <c r="F39" t="n">
-        <v>283.350769</v>
+        <v>357.214741</v>
       </c>
       <c r="G39" t="n">
-        <v>357.214741</v>
+        <v>42.867176</v>
       </c>
       <c r="H39" t="n">
-        <v>346.12963</v>
+        <v>41.265267</v>
       </c>
       <c r="I39" t="n">
-        <v>41.265267</v>
+        <v>242.77061</v>
       </c>
       <c r="J39" t="n">
-        <v>242.77061</v>
+        <v>125.322738</v>
       </c>
     </row>
     <row r="40">
@@ -1761,31 +1763,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.681119</v>
+        <v>0.551221</v>
       </c>
       <c r="C40" t="n">
-        <v>0.551221</v>
+        <v>0.374704</v>
       </c>
       <c r="D40" t="n">
-        <v>0.374704</v>
+        <v>0.15335</v>
       </c>
       <c r="E40" t="n">
-        <v>0.15335</v>
+        <v>0.254119</v>
       </c>
       <c r="F40" t="n">
-        <v>0.254119</v>
+        <v>0.377294</v>
       </c>
       <c r="G40" t="n">
-        <v>0.377294</v>
+        <v>0.286058</v>
       </c>
       <c r="H40" t="n">
-        <v>0.286058</v>
+        <v>0.328424</v>
       </c>
       <c r="I40" t="n">
-        <v>0.328424</v>
+        <v>0.18511</v>
       </c>
       <c r="J40" t="n">
-        <v>0.18511</v>
+        <v>0.52964225</v>
       </c>
     </row>
     <row r="41">
@@ -1795,19 +1797,19 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.151178</v>
-      </c>
-      <c r="C41" t="n">
         <v>5.927249</v>
       </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="n">
+      <c r="G41" t="n">
+        <v>303.262454</v>
+      </c>
+      <c r="H41" t="n">
         <v>133.809475</v>
       </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
     </row>
     <row r="42">
@@ -1817,31 +1819,31 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.001168</v>
+        <v>0.005161</v>
       </c>
       <c r="C42" t="n">
-        <v>0.005161</v>
+        <v>0.000919</v>
       </c>
       <c r="D42" t="n">
-        <v>0.000919</v>
+        <v>2e-06</v>
       </c>
       <c r="E42" t="n">
-        <v>2e-06</v>
+        <v>1.525e-05</v>
       </c>
       <c r="F42" t="n">
-        <v>1.525e-05</v>
+        <v>0.00086</v>
       </c>
       <c r="G42" t="n">
-        <v>0.00086</v>
+        <v>0.0006089999999999999</v>
       </c>
       <c r="H42" t="n">
-        <v>0.0006089999999999999</v>
+        <v>0.000505</v>
       </c>
       <c r="I42" t="n">
-        <v>0.000505</v>
+        <v>0.0029015</v>
       </c>
       <c r="J42" t="n">
-        <v>0.0029015</v>
+        <v>0.001078</v>
       </c>
     </row>
     <row r="43">
@@ -1851,31 +1853,31 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>183.641381</v>
+        <v>119.483677</v>
       </c>
       <c r="C43" t="n">
-        <v>119.483677</v>
+        <v>155.635763</v>
       </c>
       <c r="D43" t="n">
-        <v>155.635763</v>
+        <v>94.819248</v>
       </c>
       <c r="E43" t="n">
-        <v>94.819248</v>
+        <v>106.908919</v>
       </c>
       <c r="F43" t="n">
-        <v>106.908919</v>
+        <v>150.02383</v>
       </c>
       <c r="G43" t="n">
-        <v>150.02383</v>
+        <v>799.2471839999999</v>
       </c>
       <c r="H43" t="n">
-        <v>799.2471839999999</v>
+        <v>337.228122</v>
       </c>
       <c r="I43" t="n">
-        <v>337.228122</v>
+        <v>199.92394</v>
       </c>
       <c r="J43" t="n">
-        <v>199.92394</v>
+        <v>192.325936</v>
       </c>
     </row>
     <row r="44">
@@ -1885,31 +1887,31 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.015947</v>
+        <v>0.017943</v>
       </c>
       <c r="C44" t="n">
-        <v>0.017943</v>
+        <v>0.010616</v>
       </c>
       <c r="D44" t="n">
-        <v>0.010616</v>
+        <v>0.007229</v>
       </c>
       <c r="E44" t="n">
-        <v>0.007229</v>
+        <v>0.008765999999999999</v>
       </c>
       <c r="F44" t="n">
-        <v>0.008765999999999999</v>
+        <v>0.0073135</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0073135</v>
+        <v>0.007417</v>
       </c>
       <c r="H44" t="n">
-        <v>0.007417</v>
+        <v>0.004086</v>
       </c>
       <c r="I44" t="n">
-        <v>0.004086</v>
+        <v>0.015422</v>
       </c>
       <c r="J44" t="n">
-        <v>0.015422</v>
+        <v>0.009783999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -1919,31 +1921,31 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1157.936493</v>
+        <v>748.572722</v>
       </c>
       <c r="C45" t="n">
-        <v>748.572722</v>
+        <v>636.517282</v>
       </c>
       <c r="D45" t="n">
-        <v>636.517282</v>
+        <v>630.8495809999999</v>
       </c>
       <c r="E45" t="n">
-        <v>630.8495809999999</v>
+        <v>517.395887</v>
       </c>
       <c r="F45" t="n">
-        <v>517.395887</v>
+        <v>645.389143</v>
       </c>
       <c r="G45" t="n">
-        <v>645.389143</v>
+        <v>1048.792221</v>
       </c>
       <c r="H45" t="n">
-        <v>1048.792221</v>
+        <v>1171.402774</v>
       </c>
       <c r="I45" t="n">
-        <v>1171.402774</v>
+        <v>842.821444</v>
       </c>
       <c r="J45" t="n">
-        <v>842.821444</v>
+        <v>1106.331154</v>
       </c>
     </row>
     <row r="46">
@@ -1953,31 +1955,31 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.081526</v>
+        <v>0.049072</v>
       </c>
       <c r="C46" t="n">
-        <v>0.049072</v>
+        <v>0.056935</v>
       </c>
       <c r="D46" t="n">
-        <v>0.056935</v>
+        <v>0.036186</v>
       </c>
       <c r="E46" t="n">
-        <v>0.036186</v>
+        <v>0.035261</v>
       </c>
       <c r="F46" t="n">
-        <v>0.035261</v>
+        <v>0.056238</v>
       </c>
       <c r="G46" t="n">
-        <v>0.056238</v>
+        <v>0.0412595</v>
       </c>
       <c r="H46" t="n">
-        <v>0.0412595</v>
+        <v>0.0347025</v>
       </c>
       <c r="I46" t="n">
-        <v>0.0347025</v>
+        <v>0.06837500000000001</v>
       </c>
       <c r="J46" t="n">
-        <v>0.06837500000000001</v>
+        <v>0.0922</v>
       </c>
     </row>
     <row r="47">
@@ -1987,31 +1989,31 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>140.201432</v>
+        <v>53.098055</v>
       </c>
       <c r="C47" t="n">
-        <v>53.098055</v>
+        <v>495.524957</v>
       </c>
       <c r="D47" t="n">
-        <v>495.524957</v>
+        <v>372.014927</v>
       </c>
       <c r="E47" t="n">
-        <v>372.014927</v>
+        <v>384.266306</v>
       </c>
       <c r="F47" t="n">
-        <v>384.266306</v>
+        <v>428.254098</v>
       </c>
       <c r="G47" t="n">
-        <v>428.254098</v>
+        <v>1930.844136</v>
       </c>
       <c r="H47" t="n">
-        <v>1930.844136</v>
+        <v>141.401506</v>
       </c>
       <c r="I47" t="n">
-        <v>141.401506</v>
+        <v>30.078884</v>
       </c>
       <c r="J47" t="n">
-        <v>30.078884</v>
+        <v>66.399404</v>
       </c>
     </row>
     <row r="48">
@@ -2021,31 +2023,31 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.009468000000000001</v>
+        <v>0.005543</v>
       </c>
       <c r="C48" t="n">
-        <v>0.005543</v>
+        <v>0.004668</v>
       </c>
       <c r="D48" t="n">
-        <v>0.004668</v>
+        <v>0.001414</v>
       </c>
       <c r="E48" t="n">
-        <v>0.001414</v>
+        <v>0.00808</v>
       </c>
       <c r="F48" t="n">
-        <v>0.00808</v>
+        <v>0.004919</v>
       </c>
       <c r="G48" t="n">
-        <v>0.004919</v>
+        <v>0.004477</v>
       </c>
       <c r="H48" t="n">
-        <v>0.004477</v>
+        <v>0.001299</v>
       </c>
       <c r="I48" t="n">
-        <v>0.001299</v>
+        <v>0.00281825</v>
       </c>
       <c r="J48" t="n">
-        <v>0.00281825</v>
+        <v>0.008833000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -2055,31 +2057,31 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>26.152505</v>
+        <v>38.033875</v>
       </c>
       <c r="C49" t="n">
-        <v>38.033875</v>
+        <v>38.339969</v>
       </c>
       <c r="D49" t="n">
-        <v>38.339969</v>
+        <v>129.269941</v>
       </c>
       <c r="E49" t="n">
-        <v>129.269941</v>
+        <v>385.506143</v>
       </c>
       <c r="F49" t="n">
-        <v>385.506143</v>
+        <v>312.441913</v>
       </c>
       <c r="G49" t="n">
-        <v>312.441913</v>
+        <v>183.41128</v>
       </c>
       <c r="H49" t="n">
-        <v>183.41128</v>
+        <v>167.431964</v>
       </c>
       <c r="I49" t="n">
-        <v>167.431964</v>
+        <v>48.874291</v>
       </c>
       <c r="J49" t="n">
-        <v>48.874291</v>
+        <v>49.367457</v>
       </c>
     </row>
     <row r="50">
@@ -2089,31 +2091,31 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.216161</v>
+        <v>0.323812</v>
       </c>
       <c r="C50" t="n">
-        <v>0.323812</v>
+        <v>0.260287</v>
       </c>
       <c r="D50" t="n">
-        <v>0.260287</v>
+        <v>0.232099</v>
       </c>
       <c r="E50" t="n">
-        <v>0.232099</v>
+        <v>0.304774</v>
       </c>
       <c r="F50" t="n">
-        <v>0.304774</v>
+        <v>0.383423</v>
       </c>
       <c r="G50" t="n">
-        <v>0.383423</v>
+        <v>0.6482055</v>
       </c>
       <c r="H50" t="n">
-        <v>0.6482055</v>
+        <v>0.509309</v>
       </c>
       <c r="I50" t="n">
-        <v>0.509309</v>
+        <v>0.381127</v>
       </c>
       <c r="J50" t="n">
-        <v>0.381127</v>
+        <v>0.397733</v>
       </c>
     </row>
     <row r="51">
@@ -2123,31 +2125,31 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>109.863082</v>
+        <v>118.655546</v>
       </c>
       <c r="C51" t="n">
-        <v>118.655546</v>
+        <v>74.35132900000001</v>
       </c>
       <c r="D51" t="n">
-        <v>74.35132900000001</v>
+        <v>51.034447</v>
       </c>
       <c r="E51" t="n">
-        <v>51.034447</v>
+        <v>36.921702</v>
       </c>
       <c r="F51" t="n">
-        <v>36.921702</v>
+        <v>83.705129</v>
       </c>
       <c r="G51" t="n">
-        <v>83.705129</v>
+        <v>53.990394</v>
       </c>
       <c r="H51" t="n">
-        <v>53.990394</v>
+        <v>82.77434100000001</v>
       </c>
       <c r="I51" t="n">
-        <v>82.77434100000001</v>
+        <v>74.98517200000001</v>
       </c>
       <c r="J51" t="n">
-        <v>74.98517200000001</v>
+        <v>207.978681</v>
       </c>
     </row>
     <row r="52">
@@ -2157,31 +2159,31 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.316047</v>
+        <v>0.3032035</v>
       </c>
       <c r="C52" t="n">
-        <v>0.3032035</v>
+        <v>0.184877</v>
       </c>
       <c r="D52" t="n">
-        <v>0.184877</v>
+        <v>0.165061</v>
       </c>
       <c r="E52" t="n">
-        <v>0.165061</v>
+        <v>0.3296095</v>
       </c>
       <c r="F52" t="n">
-        <v>0.3296095</v>
+        <v>0.263438</v>
       </c>
       <c r="G52" t="n">
-        <v>0.263438</v>
+        <v>0.163885</v>
       </c>
       <c r="H52" t="n">
-        <v>0.163885</v>
+        <v>0.108714</v>
       </c>
       <c r="I52" t="n">
-        <v>0.108714</v>
+        <v>0.168217</v>
       </c>
       <c r="J52" t="n">
-        <v>0.168217</v>
+        <v>0.21473</v>
       </c>
     </row>
     <row r="53">
@@ -2191,31 +2193,31 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>168.917668</v>
+        <v>251.898712</v>
       </c>
       <c r="C53" t="n">
-        <v>251.898712</v>
+        <v>325.752664</v>
       </c>
       <c r="D53" t="n">
-        <v>325.752664</v>
+        <v>232.060711</v>
       </c>
       <c r="E53" t="n">
-        <v>232.060711</v>
+        <v>78.332365</v>
       </c>
       <c r="F53" t="n">
-        <v>78.332365</v>
+        <v>224.088917</v>
       </c>
       <c r="G53" t="n">
-        <v>224.088917</v>
+        <v>240.919601</v>
       </c>
       <c r="H53" t="n">
-        <v>240.919601</v>
+        <v>49.473022</v>
       </c>
       <c r="I53" t="n">
-        <v>49.473022</v>
+        <v>169.538055</v>
       </c>
       <c r="J53" t="n">
-        <v>169.538055</v>
+        <v>147.95016</v>
       </c>
     </row>
     <row r="54">
@@ -2225,31 +2227,31 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.170077</v>
+        <v>0.182745</v>
       </c>
       <c r="C54" t="n">
-        <v>0.182745</v>
+        <v>0.479193</v>
       </c>
       <c r="D54" t="n">
-        <v>0.479193</v>
+        <v>0.237065</v>
       </c>
       <c r="E54" t="n">
-        <v>0.237065</v>
+        <v>0.001109</v>
       </c>
       <c r="F54" t="n">
-        <v>0.001109</v>
+        <v>0.891181</v>
       </c>
       <c r="G54" t="n">
-        <v>0.891181</v>
+        <v>0.041797</v>
       </c>
       <c r="H54" t="n">
-        <v>0.041797</v>
+        <v>0.04179</v>
       </c>
       <c r="I54" t="n">
-        <v>0.04179</v>
+        <v>0.001458</v>
       </c>
       <c r="J54" t="n">
-        <v>0.001458</v>
+        <v>0.000147</v>
       </c>
     </row>
     <row r="55">
@@ -2259,29 +2261,29 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2.493209</v>
-      </c>
-      <c r="C55" t="n">
         <v>2.770772</v>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="n">
+        <v>0.001327</v>
+      </c>
       <c r="E55" t="n">
-        <v>0.001327</v>
+        <v>0.000384</v>
       </c>
       <c r="F55" t="n">
-        <v>0.000384</v>
+        <v>1.014694</v>
       </c>
       <c r="G55" t="n">
-        <v>1.014694</v>
+        <v>0.794714</v>
       </c>
       <c r="H55" t="n">
-        <v>0.794714</v>
+        <v>1.099012</v>
       </c>
       <c r="I55" t="n">
-        <v>1.099012</v>
+        <v>1.267572</v>
       </c>
       <c r="J55" t="n">
-        <v>1.267572</v>
+        <v>1.611405</v>
       </c>
     </row>
     <row r="56">
@@ -2291,31 +2293,31 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.09723825</v>
+        <v>0.060699</v>
       </c>
       <c r="C56" t="n">
-        <v>0.060699</v>
+        <v>0.06481525</v>
       </c>
       <c r="D56" t="n">
-        <v>0.06481525</v>
+        <v>0.05732625</v>
       </c>
       <c r="E56" t="n">
-        <v>0.05732625</v>
+        <v>0.066925</v>
       </c>
       <c r="F56" t="n">
-        <v>0.066925</v>
+        <v>0.07106899999999999</v>
       </c>
       <c r="G56" t="n">
-        <v>0.07106899999999999</v>
+        <v>0.07862325000000001</v>
       </c>
       <c r="H56" t="n">
-        <v>0.07862325000000001</v>
+        <v>0.043873</v>
       </c>
       <c r="I56" t="n">
-        <v>0.043873</v>
+        <v>0.07008733333333333</v>
       </c>
       <c r="J56" t="n">
-        <v>0.07008733333333333</v>
+        <v>0.124271</v>
       </c>
     </row>
     <row r="57">
@@ -2325,31 +2327,31 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.040001</v>
+        <v>0.002196</v>
       </c>
       <c r="C57" t="n">
-        <v>0.002196</v>
+        <v>1.407788</v>
       </c>
       <c r="D57" t="n">
-        <v>1.407788</v>
+        <v>1.261628</v>
       </c>
       <c r="E57" t="n">
-        <v>1.261628</v>
+        <v>0.914431</v>
       </c>
       <c r="F57" t="n">
-        <v>0.914431</v>
+        <v>0.00028</v>
       </c>
       <c r="G57" t="n">
-        <v>0.00028</v>
+        <v>0.000842</v>
       </c>
       <c r="H57" t="n">
-        <v>0.000842</v>
+        <v>0.000733</v>
       </c>
       <c r="I57" t="n">
-        <v>0.000733</v>
+        <v>0.000552</v>
       </c>
       <c r="J57" t="n">
-        <v>0.000552</v>
+        <v>0.000967</v>
       </c>
     </row>
     <row r="58">
@@ -2359,31 +2361,31 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>256.784831</v>
+        <v>120.587872</v>
       </c>
       <c r="C58" t="n">
-        <v>120.587872</v>
+        <v>127.325474</v>
       </c>
       <c r="D58" t="n">
-        <v>127.325474</v>
+        <v>98.65007799999999</v>
       </c>
       <c r="E58" t="n">
-        <v>98.65007799999999</v>
+        <v>121.043682</v>
       </c>
       <c r="F58" t="n">
-        <v>121.043682</v>
+        <v>114.620812</v>
       </c>
       <c r="G58" t="n">
-        <v>114.620812</v>
+        <v>118.910286</v>
       </c>
       <c r="H58" t="n">
-        <v>118.910286</v>
+        <v>79.813745</v>
       </c>
       <c r="I58" t="n">
-        <v>79.813745</v>
+        <v>85.495721</v>
       </c>
       <c r="J58" t="n">
-        <v>85.495721</v>
+        <v>128.188339</v>
       </c>
     </row>
     <row r="59">
@@ -2393,31 +2395,31 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>577.052413</v>
+        <v>95.38098100000001</v>
       </c>
       <c r="C59" t="n">
-        <v>95.38098100000001</v>
+        <v>347.636927</v>
       </c>
       <c r="D59" t="n">
-        <v>347.636927</v>
+        <v>256.729258</v>
       </c>
       <c r="E59" t="n">
-        <v>256.729258</v>
+        <v>206.727109</v>
       </c>
       <c r="F59" t="n">
-        <v>206.727109</v>
+        <v>193.267517</v>
       </c>
       <c r="G59" t="n">
-        <v>193.267517</v>
+        <v>743.324956</v>
       </c>
       <c r="H59" t="n">
-        <v>743.324956</v>
+        <v>301.451556</v>
       </c>
       <c r="I59" t="n">
-        <v>301.451556</v>
+        <v>161.461116</v>
       </c>
       <c r="J59" t="n">
-        <v>161.461116</v>
+        <v>274.523506</v>
       </c>
     </row>
     <row r="60">
@@ -2427,25 +2429,25 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1.16153</v>
-      </c>
-      <c r="C60" t="n">
         <v>445.658223</v>
       </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="n">
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="n">
         <v>1.439041</v>
       </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
+      <c r="G60" t="n">
+        <v>66.61608699999999</v>
+      </c>
       <c r="H60" t="n">
-        <v>66.61608699999999</v>
+        <v>19.359458</v>
       </c>
       <c r="I60" t="n">
-        <v>19.359458</v>
+        <v>26.404941</v>
       </c>
       <c r="J60" t="n">
-        <v>26.404941</v>
+        <v>36.433736</v>
       </c>
     </row>
     <row r="61">
@@ -2455,31 +2457,31 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1131.441578</v>
+        <v>1574.086796</v>
       </c>
       <c r="C61" t="n">
-        <v>1574.086796</v>
+        <v>804.543034</v>
       </c>
       <c r="D61" t="n">
-        <v>804.543034</v>
+        <v>894.802743</v>
       </c>
       <c r="E61" t="n">
-        <v>894.802743</v>
+        <v>799.8201350000001</v>
       </c>
       <c r="F61" t="n">
-        <v>799.8201350000001</v>
+        <v>3345.855402</v>
       </c>
       <c r="G61" t="n">
-        <v>3345.855402</v>
+        <v>1734.701539</v>
       </c>
       <c r="H61" t="n">
-        <v>1734.701539</v>
+        <v>1010.555188</v>
       </c>
       <c r="I61" t="n">
-        <v>1010.555188</v>
+        <v>896.876493</v>
       </c>
       <c r="J61" t="n">
-        <v>896.876493</v>
+        <v>1180.622016</v>
       </c>
     </row>
     <row r="62">
@@ -2489,31 +2491,31 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>29.200467</v>
+        <v>21.43664</v>
       </c>
       <c r="C62" t="n">
-        <v>21.43664</v>
+        <v>26.94314</v>
       </c>
       <c r="D62" t="n">
-        <v>26.94314</v>
+        <v>17.410946</v>
       </c>
       <c r="E62" t="n">
-        <v>17.410946</v>
+        <v>17.89129</v>
       </c>
       <c r="F62" t="n">
-        <v>17.89129</v>
+        <v>16.365514</v>
       </c>
       <c r="G62" t="n">
-        <v>16.365514</v>
+        <v>26.037335</v>
       </c>
       <c r="H62" t="n">
-        <v>26.037335</v>
+        <v>12.677953</v>
       </c>
       <c r="I62" t="n">
-        <v>12.677953</v>
+        <v>12.545816</v>
       </c>
       <c r="J62" t="n">
-        <v>12.545816</v>
+        <v>17.331738</v>
       </c>
     </row>
     <row r="63">
@@ -2523,31 +2525,31 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>507.826902</v>
+        <v>310.82796</v>
       </c>
       <c r="C63" t="n">
-        <v>310.82796</v>
+        <v>274.869932</v>
       </c>
       <c r="D63" t="n">
-        <v>274.869932</v>
+        <v>290.659288</v>
       </c>
       <c r="E63" t="n">
-        <v>290.659288</v>
+        <v>164.303141</v>
       </c>
       <c r="F63" t="n">
-        <v>164.303141</v>
+        <v>14.864183</v>
       </c>
       <c r="G63" t="n">
-        <v>14.864183</v>
+        <v>10.761111</v>
       </c>
       <c r="H63" t="n">
-        <v>10.761111</v>
+        <v>258.908291</v>
       </c>
       <c r="I63" t="n">
-        <v>258.908291</v>
+        <v>214.244431</v>
       </c>
       <c r="J63" t="n">
-        <v>214.244431</v>
+        <v>192.875758</v>
       </c>
     </row>
     <row r="64">
@@ -2557,31 +2559,31 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1244.79658</v>
+        <v>1001.21699</v>
       </c>
       <c r="C64" t="n">
-        <v>1001.21699</v>
+        <v>859.27977</v>
       </c>
       <c r="D64" t="n">
-        <v>859.27977</v>
+        <v>1130.074831</v>
       </c>
       <c r="E64" t="n">
-        <v>1130.074831</v>
+        <v>773.779114</v>
       </c>
       <c r="F64" t="n">
-        <v>773.779114</v>
+        <v>771.234021</v>
       </c>
       <c r="G64" t="n">
-        <v>771.234021</v>
+        <v>686.1653240000001</v>
       </c>
       <c r="H64" t="n">
-        <v>686.1653240000001</v>
+        <v>479.471548</v>
       </c>
       <c r="I64" t="n">
-        <v>479.471548</v>
+        <v>513.407341</v>
       </c>
       <c r="J64" t="n">
-        <v>513.407341</v>
+        <v>577.563361</v>
       </c>
     </row>
     <row r="65">
@@ -2591,31 +2593,31 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>787.909998</v>
+        <v>631.922905</v>
       </c>
       <c r="C65" t="n">
-        <v>631.922905</v>
+        <v>519.952883</v>
       </c>
       <c r="D65" t="n">
-        <v>519.952883</v>
+        <v>373.690509</v>
       </c>
       <c r="E65" t="n">
-        <v>373.690509</v>
+        <v>520.635439</v>
       </c>
       <c r="F65" t="n">
-        <v>520.635439</v>
+        <v>560.9419685</v>
       </c>
       <c r="G65" t="n">
-        <v>560.9419685</v>
+        <v>913.473915</v>
       </c>
       <c r="H65" t="n">
-        <v>913.473915</v>
+        <v>567.521568</v>
       </c>
       <c r="I65" t="n">
-        <v>567.521568</v>
+        <v>377.466312</v>
       </c>
       <c r="J65" t="n">
-        <v>377.466312</v>
+        <v>509.809388</v>
       </c>
     </row>
     <row r="66">
@@ -2625,31 +2627,31 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>229.226956</v>
+        <v>213.05279</v>
       </c>
       <c r="C66" t="n">
-        <v>213.05279</v>
+        <v>66.733133</v>
       </c>
       <c r="D66" t="n">
-        <v>66.733133</v>
+        <v>136.075142</v>
       </c>
       <c r="E66" t="n">
-        <v>136.075142</v>
+        <v>110.807762</v>
       </c>
       <c r="F66" t="n">
-        <v>110.807762</v>
+        <v>105.866611</v>
       </c>
       <c r="G66" t="n">
-        <v>105.866611</v>
+        <v>427.347026</v>
       </c>
       <c r="H66" t="n">
-        <v>427.347026</v>
+        <v>156.326729</v>
       </c>
       <c r="I66" t="n">
-        <v>156.326729</v>
+        <v>109.416659</v>
       </c>
       <c r="J66" t="n">
-        <v>109.416659</v>
+        <v>306.970682</v>
       </c>
     </row>
     <row r="67">
@@ -2659,31 +2661,31 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>6750.49278</v>
+        <v>6032.672945</v>
       </c>
       <c r="C67" t="n">
-        <v>6032.672945</v>
+        <v>9123.656804</v>
       </c>
       <c r="D67" t="n">
-        <v>9123.656804</v>
+        <v>5948.821357</v>
       </c>
       <c r="E67" t="n">
-        <v>5948.821357</v>
+        <v>4361.375109</v>
       </c>
       <c r="F67" t="n">
-        <v>4361.375109</v>
+        <v>3988.662239</v>
       </c>
       <c r="G67" t="n">
-        <v>3988.662239</v>
+        <v>2239.750451</v>
       </c>
       <c r="H67" t="n">
-        <v>2239.750451</v>
+        <v>2718.358779</v>
       </c>
       <c r="I67" t="n">
-        <v>2718.358779</v>
+        <v>2282.874727</v>
       </c>
       <c r="J67" t="n">
-        <v>2282.874727</v>
+        <v>3522.413913</v>
       </c>
     </row>
     <row r="68">
@@ -2693,31 +2695,31 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>9.086698</v>
+        <v>6.074252</v>
       </c>
       <c r="C68" t="n">
-        <v>6.074252</v>
+        <v>7.701942</v>
       </c>
       <c r="D68" t="n">
-        <v>7.701942</v>
+        <v>9.683154</v>
       </c>
       <c r="E68" t="n">
-        <v>9.683154</v>
+        <v>7.176474</v>
       </c>
       <c r="F68" t="n">
-        <v>7.176474</v>
+        <v>8.333875000000001</v>
       </c>
       <c r="G68" t="n">
-        <v>8.333875000000001</v>
+        <v>14.849422</v>
       </c>
       <c r="H68" t="n">
-        <v>14.849422</v>
+        <v>9.623455</v>
       </c>
       <c r="I68" t="n">
-        <v>9.623455</v>
+        <v>8.748628</v>
       </c>
       <c r="J68" t="n">
-        <v>8.748628</v>
+        <v>11.247665</v>
       </c>
     </row>
     <row r="69">
@@ -2727,31 +2729,31 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.005453</v>
+        <v>0.0043975</v>
       </c>
       <c r="C69" t="n">
-        <v>0.0043975</v>
+        <v>0.008373</v>
       </c>
       <c r="D69" t="n">
-        <v>0.008373</v>
+        <v>0.008206</v>
       </c>
       <c r="E69" t="n">
-        <v>0.008206</v>
+        <v>0.004415</v>
       </c>
       <c r="F69" t="n">
-        <v>0.004415</v>
+        <v>0.004137</v>
       </c>
       <c r="G69" t="n">
-        <v>0.004137</v>
+        <v>0.005494</v>
       </c>
       <c r="H69" t="n">
-        <v>0.005494</v>
+        <v>0.003423</v>
       </c>
       <c r="I69" t="n">
-        <v>0.003423</v>
+        <v>0.003731</v>
       </c>
       <c r="J69" t="n">
-        <v>0.003731</v>
+        <v>0.013659</v>
       </c>
     </row>
     <row r="70">
@@ -2761,31 +2763,31 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1.652656</v>
+        <v>0.548177</v>
       </c>
       <c r="C70" t="n">
-        <v>0.548177</v>
+        <v>0.693272</v>
       </c>
       <c r="D70" t="n">
-        <v>0.693272</v>
+        <v>1.371864</v>
       </c>
       <c r="E70" t="n">
-        <v>1.371864</v>
+        <v>0.911798</v>
       </c>
       <c r="F70" t="n">
-        <v>0.911798</v>
+        <v>1.43441</v>
       </c>
       <c r="G70" t="n">
-        <v>1.43441</v>
+        <v>1.695991</v>
       </c>
       <c r="H70" t="n">
-        <v>1.695991</v>
+        <v>1.208114</v>
       </c>
       <c r="I70" t="n">
-        <v>1.208114</v>
+        <v>0.024509</v>
       </c>
       <c r="J70" t="n">
-        <v>0.024509</v>
+        <v>2.548669</v>
       </c>
     </row>
     <row r="71">
@@ -2795,31 +2797,31 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>5292.823429</v>
+        <v>9590.965711000001</v>
       </c>
       <c r="C71" t="n">
-        <v>9590.965711000001</v>
+        <v>14522.891958</v>
       </c>
       <c r="D71" t="n">
-        <v>14522.891958</v>
+        <v>14761.244176</v>
       </c>
       <c r="E71" t="n">
-        <v>14761.244176</v>
+        <v>10579.17522</v>
       </c>
       <c r="F71" t="n">
-        <v>10579.17522</v>
+        <v>19617.035707</v>
       </c>
       <c r="G71" t="n">
-        <v>19617.035707</v>
+        <v>8320.91656</v>
       </c>
       <c r="H71" t="n">
-        <v>8320.91656</v>
+        <v>8573.630485</v>
       </c>
       <c r="I71" t="n">
-        <v>8573.630485</v>
+        <v>4655.755978</v>
       </c>
       <c r="J71" t="n">
-        <v>4655.755978</v>
+        <v>5519.836799</v>
       </c>
     </row>
     <row r="72">
@@ -2829,31 +2831,31 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1.613938</v>
+        <v>1.940996</v>
       </c>
       <c r="C72" t="n">
-        <v>1.940996</v>
+        <v>1.564369</v>
       </c>
       <c r="D72" t="n">
-        <v>1.564369</v>
+        <v>2.889618</v>
       </c>
       <c r="E72" t="n">
-        <v>2.889618</v>
+        <v>1.366585</v>
       </c>
       <c r="F72" t="n">
-        <v>1.366585</v>
+        <v>0.917232</v>
       </c>
       <c r="G72" t="n">
-        <v>0.917232</v>
+        <v>0.792461</v>
       </c>
       <c r="H72" t="n">
-        <v>0.792461</v>
+        <v>0.574948</v>
       </c>
       <c r="I72" t="n">
-        <v>0.574948</v>
+        <v>0.759304</v>
       </c>
       <c r="J72" t="n">
-        <v>0.759304</v>
+        <v>0.890266</v>
       </c>
     </row>
     <row r="73">
@@ -2863,32 +2865,30 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1.290888</v>
+        <v>0.199999</v>
       </c>
       <c r="C73" t="n">
-        <v>0.199999</v>
+        <v>0.625051</v>
       </c>
       <c r="D73" t="n">
-        <v>0.625051</v>
+        <v>0.754844</v>
       </c>
       <c r="E73" t="n">
-        <v>0.754844</v>
+        <v>1.74787</v>
       </c>
       <c r="F73" t="n">
-        <v>1.74787</v>
+        <v>0.605754</v>
       </c>
       <c r="G73" t="n">
-        <v>0.605754</v>
+        <v>1.403511</v>
       </c>
       <c r="H73" t="n">
-        <v>1.403511</v>
+        <v>0.575786</v>
       </c>
       <c r="I73" t="n">
-        <v>0.575786</v>
-      </c>
-      <c r="J73" t="n">
         <v>0.420326</v>
       </c>
+      <c r="J73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
@@ -2897,31 +2897,31 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>5166.152157</v>
+        <v>5234.524655</v>
       </c>
       <c r="C74" t="n">
-        <v>5234.524655</v>
+        <v>3678.540566</v>
       </c>
       <c r="D74" t="n">
-        <v>3678.540566</v>
+        <v>2161.937275</v>
       </c>
       <c r="E74" t="n">
-        <v>2161.937275</v>
+        <v>2934.638464</v>
       </c>
       <c r="F74" t="n">
-        <v>2934.638464</v>
+        <v>2019.571871</v>
       </c>
       <c r="G74" t="n">
-        <v>2019.571871</v>
+        <v>2995.752028</v>
       </c>
       <c r="H74" t="n">
-        <v>2995.752028</v>
+        <v>1834.755329</v>
       </c>
       <c r="I74" t="n">
-        <v>1834.755329</v>
+        <v>2968.33159</v>
       </c>
       <c r="J74" t="n">
-        <v>2968.33159</v>
+        <v>4476.683825</v>
       </c>
     </row>
     <row r="75">
@@ -2931,31 +2931,31 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1.461627</v>
+        <v>1.342721</v>
       </c>
       <c r="C75" t="n">
-        <v>1.342721</v>
+        <v>1.05523375</v>
       </c>
       <c r="D75" t="n">
-        <v>1.05523375</v>
+        <v>0.7004629999999999</v>
       </c>
       <c r="E75" t="n">
-        <v>0.7004629999999999</v>
+        <v>0.4989105</v>
       </c>
       <c r="F75" t="n">
-        <v>0.4989105</v>
+        <v>0.84087425</v>
       </c>
       <c r="G75" t="n">
-        <v>0.84087425</v>
+        <v>0.8081739999999999</v>
       </c>
       <c r="H75" t="n">
-        <v>0.8081739999999999</v>
+        <v>0.4811093333333333</v>
       </c>
       <c r="I75" t="n">
-        <v>0.4811093333333333</v>
+        <v>0.406997</v>
       </c>
       <c r="J75" t="n">
-        <v>0.406997</v>
+        <v>0.5797369999999999</v>
       </c>
     </row>
     <row r="76">
@@ -2965,31 +2965,31 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1353.186506</v>
+        <v>912.4518890000001</v>
       </c>
       <c r="C76" t="n">
-        <v>915.494014</v>
+        <v>1082.266233</v>
       </c>
       <c r="D76" t="n">
-        <v>1082.266233</v>
+        <v>804.787636</v>
       </c>
       <c r="E76" t="n">
-        <v>804.787636</v>
+        <v>1081.849325</v>
       </c>
       <c r="F76" t="n">
-        <v>1081.849325</v>
+        <v>825.077547</v>
       </c>
       <c r="G76" t="n">
-        <v>825.077547</v>
+        <v>1466.381774</v>
       </c>
       <c r="H76" t="n">
-        <v>1466.381774</v>
+        <v>1156.664586</v>
       </c>
       <c r="I76" t="n">
-        <v>1156.664586</v>
+        <v>1341.859916</v>
       </c>
       <c r="J76" t="n">
-        <v>1341.859916</v>
+        <v>1295.425709</v>
       </c>
     </row>
     <row r="77">
@@ -2999,31 +2999,31 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.632834</v>
+        <v>0.61683075</v>
       </c>
       <c r="C77" t="n">
-        <v>0.61683075</v>
+        <v>0.4672313333333333</v>
       </c>
       <c r="D77" t="n">
-        <v>0.4672313333333333</v>
+        <v>0.29997375</v>
       </c>
       <c r="E77" t="n">
-        <v>0.29997375</v>
+        <v>0.312439</v>
       </c>
       <c r="F77" t="n">
-        <v>0.312439</v>
+        <v>0.400125</v>
       </c>
       <c r="G77" t="n">
-        <v>0.400125</v>
+        <v>0.3790386666666667</v>
       </c>
       <c r="H77" t="n">
-        <v>0.3790386666666667</v>
+        <v>0.311228</v>
       </c>
       <c r="I77" t="n">
-        <v>0.311228</v>
+        <v>0.28865475</v>
       </c>
       <c r="J77" t="n">
-        <v>0.28865475</v>
+        <v>0.59304925</v>
       </c>
     </row>
     <row r="78">
@@ -3033,31 +3033,31 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>468.304146</v>
+        <v>246.148685</v>
       </c>
       <c r="C78" t="n">
-        <v>243.10656</v>
+        <v>259.176472</v>
       </c>
       <c r="D78" t="n">
-        <v>259.176472</v>
+        <v>769.364043</v>
       </c>
       <c r="E78" t="n">
-        <v>769.364043</v>
+        <v>204.457131</v>
       </c>
       <c r="F78" t="n">
-        <v>204.457131</v>
+        <v>374.574502</v>
       </c>
       <c r="G78" t="n">
-        <v>374.574502</v>
+        <v>450.70307</v>
       </c>
       <c r="H78" t="n">
-        <v>450.70307</v>
+        <v>120.197101</v>
       </c>
       <c r="I78" t="n">
-        <v>120.197101</v>
+        <v>273.934396</v>
       </c>
       <c r="J78" t="n">
-        <v>273.934396</v>
+        <v>290.451848</v>
       </c>
     </row>
     <row r="79">
@@ -3067,31 +3067,31 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.08527</v>
+        <v>0.060649</v>
       </c>
       <c r="C79" t="n">
-        <v>0.060649</v>
+        <v>0.098855</v>
       </c>
       <c r="D79" t="n">
-        <v>0.098855</v>
+        <v>0.068686</v>
       </c>
       <c r="E79" t="n">
-        <v>0.068686</v>
+        <v>0.08888699999999999</v>
       </c>
       <c r="F79" t="n">
-        <v>0.08888699999999999</v>
+        <v>0.035027</v>
       </c>
       <c r="G79" t="n">
-        <v>0.035027</v>
+        <v>0.008642</v>
       </c>
       <c r="H79" t="n">
-        <v>0.008642</v>
+        <v>0.023914</v>
       </c>
       <c r="I79" t="n">
-        <v>0.023914</v>
+        <v>0.041112</v>
       </c>
       <c r="J79" t="n">
-        <v>0.041112</v>
+        <v>0.008437999999999999</v>
       </c>
     </row>
     <row r="80">
@@ -3101,31 +3101,31 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1345.254825</v>
+        <v>608.9787894999999</v>
       </c>
       <c r="C80" t="n">
-        <v>608.9787894999999</v>
+        <v>295.797683</v>
       </c>
       <c r="D80" t="n">
-        <v>295.797683</v>
+        <v>248.637091</v>
       </c>
       <c r="E80" t="n">
-        <v>248.637091</v>
+        <v>191.868858</v>
       </c>
       <c r="F80" t="n">
-        <v>191.868858</v>
+        <v>212.699101</v>
       </c>
       <c r="G80" t="n">
-        <v>212.699101</v>
+        <v>350.86005</v>
       </c>
       <c r="H80" t="n">
-        <v>350.86005</v>
+        <v>170.641276</v>
       </c>
       <c r="I80" t="n">
-        <v>170.641276</v>
+        <v>136.894967</v>
       </c>
       <c r="J80" t="n">
-        <v>136.894967</v>
+        <v>332.14207125</v>
       </c>
     </row>
     <row r="81">
@@ -3135,31 +3135,31 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.002773</v>
+        <v>0.003866</v>
       </c>
       <c r="C81" t="n">
-        <v>0.003866</v>
+        <v>0.002113</v>
       </c>
       <c r="D81" t="n">
-        <v>0.002113</v>
+        <v>0.002928</v>
       </c>
       <c r="E81" t="n">
-        <v>0.002928</v>
+        <v>0.002257</v>
       </c>
       <c r="F81" t="n">
-        <v>0.002257</v>
+        <v>0.004953</v>
       </c>
       <c r="G81" t="n">
-        <v>0.004953</v>
+        <v>0.0019</v>
       </c>
       <c r="H81" t="n">
-        <v>0.0019</v>
+        <v>0.004195</v>
       </c>
       <c r="I81" t="n">
-        <v>0.004195</v>
+        <v>0.00232</v>
       </c>
       <c r="J81" t="n">
-        <v>0.00232</v>
+        <v>0.001136</v>
       </c>
     </row>
     <row r="82">
@@ -3169,31 +3169,31 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1546.280262</v>
+        <v>1017.26617</v>
       </c>
       <c r="C82" t="n">
-        <v>1017.26617</v>
+        <v>567.45573</v>
       </c>
       <c r="D82" t="n">
-        <v>567.45573</v>
+        <v>703.43878</v>
       </c>
       <c r="E82" t="n">
-        <v>703.43878</v>
+        <v>544.980269</v>
       </c>
       <c r="F82" t="n">
-        <v>544.980269</v>
+        <v>524.011943</v>
       </c>
       <c r="G82" t="n">
-        <v>524.011943</v>
+        <v>955.361952</v>
       </c>
       <c r="H82" t="n">
-        <v>955.361952</v>
+        <v>356.346937</v>
       </c>
       <c r="I82" t="n">
-        <v>356.346937</v>
+        <v>491.181622</v>
       </c>
       <c r="J82" t="n">
-        <v>491.181622</v>
+        <v>430.856724</v>
       </c>
     </row>
     <row r="83">
@@ -3203,31 +3203,31 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.005595</v>
+        <v>0.004067</v>
       </c>
       <c r="C83" t="n">
-        <v>0.004067</v>
+        <v>0.00165</v>
       </c>
       <c r="D83" t="n">
-        <v>0.00165</v>
+        <v>0.004333</v>
       </c>
       <c r="E83" t="n">
-        <v>0.004333</v>
+        <v>0.003745</v>
       </c>
       <c r="F83" t="n">
-        <v>0.003745</v>
+        <v>0.004421</v>
       </c>
       <c r="G83" t="n">
-        <v>0.004421</v>
+        <v>0.00321</v>
       </c>
       <c r="H83" t="n">
-        <v>0.00321</v>
+        <v>0.002017</v>
       </c>
       <c r="I83" t="n">
-        <v>0.002017</v>
+        <v>0.001719</v>
       </c>
       <c r="J83" t="n">
-        <v>0.001719</v>
+        <v>0.002514</v>
       </c>
     </row>
     <row r="84">
@@ -3237,31 +3237,31 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>27.262329</v>
+        <v>13.30453</v>
       </c>
       <c r="C84" t="n">
-        <v>13.30453</v>
+        <v>208.289501</v>
       </c>
       <c r="D84" t="n">
-        <v>208.289501</v>
+        <v>195.224665</v>
       </c>
       <c r="E84" t="n">
-        <v>195.224665</v>
+        <v>138.419356</v>
       </c>
       <c r="F84" t="n">
-        <v>138.419356</v>
+        <v>222.888126</v>
       </c>
       <c r="G84" t="n">
-        <v>222.888126</v>
+        <v>372.137061</v>
       </c>
       <c r="H84" t="n">
-        <v>372.137061</v>
+        <v>280.91454</v>
       </c>
       <c r="I84" t="n">
-        <v>280.91454</v>
+        <v>92.450514</v>
       </c>
       <c r="J84" t="n">
-        <v>92.450514</v>
+        <v>241.589197</v>
       </c>
     </row>
     <row r="85">
@@ -3271,31 +3271,31 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.001754</v>
+        <v>0.002481</v>
       </c>
       <c r="C85" t="n">
-        <v>0.002481</v>
+        <v>0.00147</v>
       </c>
       <c r="D85" t="n">
-        <v>0.00147</v>
+        <v>0.000663</v>
       </c>
       <c r="E85" t="n">
-        <v>0.000663</v>
+        <v>0.001107</v>
       </c>
       <c r="F85" t="n">
-        <v>0.001107</v>
+        <v>0.003034</v>
       </c>
       <c r="G85" t="n">
-        <v>0.003034</v>
+        <v>0.000435</v>
       </c>
       <c r="H85" t="n">
-        <v>0.000435</v>
+        <v>0.0019</v>
       </c>
       <c r="I85" t="n">
-        <v>0.0019</v>
+        <v>0.001241</v>
       </c>
       <c r="J85" t="n">
-        <v>0.001241</v>
+        <v>0.002112</v>
       </c>
     </row>
     <row r="86">
@@ -3305,31 +3305,31 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>2046.733668</v>
+        <v>1276.134651</v>
       </c>
       <c r="C86" t="n">
-        <v>1276.134651</v>
+        <v>1051.752425</v>
       </c>
       <c r="D86" t="n">
-        <v>1051.752425</v>
+        <v>618.413716</v>
       </c>
       <c r="E86" t="n">
-        <v>618.413716</v>
+        <v>634.992787</v>
       </c>
       <c r="F86" t="n">
-        <v>634.992787</v>
+        <v>720.727899</v>
       </c>
       <c r="G86" t="n">
-        <v>720.727899</v>
+        <v>803.373006</v>
       </c>
       <c r="H86" t="n">
-        <v>803.373006</v>
+        <v>621.345197</v>
       </c>
       <c r="I86" t="n">
-        <v>621.345197</v>
+        <v>540.278565</v>
       </c>
       <c r="J86" t="n">
-        <v>540.278565</v>
+        <v>537.619158</v>
       </c>
     </row>
     <row r="87">
@@ -3339,31 +3339,31 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.265565</v>
+        <v>0.162309</v>
       </c>
       <c r="C87" t="n">
-        <v>0.162309</v>
+        <v>0.097995</v>
       </c>
       <c r="D87" t="n">
-        <v>0.097995</v>
+        <v>0.210654</v>
       </c>
       <c r="E87" t="n">
-        <v>0.210654</v>
+        <v>0.340931</v>
       </c>
       <c r="F87" t="n">
-        <v>0.340931</v>
+        <v>0.169087</v>
       </c>
       <c r="G87" t="n">
-        <v>0.169087</v>
+        <v>0.120671</v>
       </c>
       <c r="H87" t="n">
-        <v>0.120671</v>
+        <v>0.09860099999999999</v>
       </c>
       <c r="I87" t="n">
-        <v>0.09860099999999999</v>
+        <v>0.104036</v>
       </c>
       <c r="J87" t="n">
-        <v>0.104036</v>
+        <v>0.090548</v>
       </c>
     </row>
     <row r="88">
@@ -3373,31 +3373,31 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>409.612579</v>
+        <v>259.245057</v>
       </c>
       <c r="C88" t="n">
-        <v>259.245057</v>
+        <v>670.640525</v>
       </c>
       <c r="D88" t="n">
-        <v>670.640525</v>
+        <v>435.219971</v>
       </c>
       <c r="E88" t="n">
-        <v>435.219971</v>
+        <v>345.353824</v>
       </c>
       <c r="F88" t="n">
-        <v>345.353824</v>
+        <v>482.492748</v>
       </c>
       <c r="G88" t="n">
-        <v>482.492748</v>
+        <v>686.445857</v>
       </c>
       <c r="H88" t="n">
-        <v>686.445857</v>
+        <v>329.638935</v>
       </c>
       <c r="I88" t="n">
-        <v>329.638935</v>
+        <v>447.124205</v>
       </c>
       <c r="J88" t="n">
-        <v>447.124205</v>
+        <v>558.5523930000001</v>
       </c>
     </row>
     <row r="89">
@@ -3407,31 +3407,31 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.059544</v>
+        <v>0.02936425</v>
       </c>
       <c r="C89" t="n">
-        <v>0.02936425</v>
+        <v>0.030471</v>
       </c>
       <c r="D89" t="n">
-        <v>0.030471</v>
+        <v>0.022361</v>
       </c>
       <c r="E89" t="n">
-        <v>0.022361</v>
+        <v>0.02103</v>
       </c>
       <c r="F89" t="n">
-        <v>0.02103</v>
+        <v>0.025786</v>
       </c>
       <c r="G89" t="n">
-        <v>0.025786</v>
+        <v>0.026421</v>
       </c>
       <c r="H89" t="n">
-        <v>0.026421</v>
+        <v>0.022317</v>
       </c>
       <c r="I89" t="n">
-        <v>0.022317</v>
+        <v>0.034153</v>
       </c>
       <c r="J89" t="n">
-        <v>0.034153</v>
+        <v>0.036059</v>
       </c>
     </row>
     <row r="90">
@@ -3441,31 +3441,31 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>19.279893</v>
+        <v>10.540074</v>
       </c>
       <c r="C90" t="n">
-        <v>10.540074</v>
+        <v>23.53453</v>
       </c>
       <c r="D90" t="n">
-        <v>23.53453</v>
+        <v>190.558933</v>
       </c>
       <c r="E90" t="n">
-        <v>190.558933</v>
+        <v>20.400783</v>
       </c>
       <c r="F90" t="n">
-        <v>20.400783</v>
+        <v>205.505945</v>
       </c>
       <c r="G90" t="n">
-        <v>205.505945</v>
+        <v>238.609366</v>
       </c>
       <c r="H90" t="n">
-        <v>238.609366</v>
+        <v>211.811151</v>
       </c>
       <c r="I90" t="n">
-        <v>211.811151</v>
+        <v>132.143642</v>
       </c>
       <c r="J90" t="n">
-        <v>132.143642</v>
+        <v>300.372314</v>
       </c>
     </row>
     <row r="91">
@@ -3475,31 +3475,31 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.031456</v>
+        <v>0.077955</v>
       </c>
       <c r="C91" t="n">
-        <v>0.077955</v>
+        <v>0.09163300000000001</v>
       </c>
       <c r="D91" t="n">
-        <v>0.09163300000000001</v>
+        <v>0.061321</v>
       </c>
       <c r="E91" t="n">
-        <v>0.061321</v>
+        <v>0.048884</v>
       </c>
       <c r="F91" t="n">
-        <v>0.048884</v>
+        <v>0.08021399999999999</v>
       </c>
       <c r="G91" t="n">
-        <v>0.08021399999999999</v>
+        <v>0.13598</v>
       </c>
       <c r="H91" t="n">
-        <v>0.13598</v>
+        <v>0.112242</v>
       </c>
       <c r="I91" t="n">
-        <v>0.112242</v>
+        <v>0.07532899999999999</v>
       </c>
       <c r="J91" t="n">
-        <v>0.07532899999999999</v>
+        <v>0.165737</v>
       </c>
     </row>
     <row r="92">
@@ -3509,31 +3509,31 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>10543.385209</v>
+        <v>11486.848972</v>
       </c>
       <c r="C92" t="n">
-        <v>11486.848972</v>
+        <v>7024.241639</v>
       </c>
       <c r="D92" t="n">
-        <v>7024.241639</v>
+        <v>5990.20021</v>
       </c>
       <c r="E92" t="n">
-        <v>5990.20021</v>
+        <v>6626.258885</v>
       </c>
       <c r="F92" t="n">
-        <v>6626.258885</v>
+        <v>5855.753238</v>
       </c>
       <c r="G92" t="n">
-        <v>5855.753238</v>
+        <v>7880.08759</v>
       </c>
       <c r="H92" t="n">
-        <v>7880.08759</v>
+        <v>4218.222346</v>
       </c>
       <c r="I92" t="n">
-        <v>4218.222346</v>
+        <v>4008.699382</v>
       </c>
       <c r="J92" t="n">
-        <v>4008.699382</v>
+        <v>11541.491771</v>
       </c>
     </row>
     <row r="93">
@@ -3543,31 +3543,31 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>428.272493</v>
+        <v>381.294679</v>
       </c>
       <c r="C93" t="n">
-        <v>381.294679</v>
+        <v>333.717318</v>
       </c>
       <c r="D93" t="n">
-        <v>333.717318</v>
+        <v>285.267483</v>
       </c>
       <c r="E93" t="n">
-        <v>285.267483</v>
+        <v>272.056872</v>
       </c>
       <c r="F93" t="n">
-        <v>272.056872</v>
+        <v>324.828823</v>
       </c>
       <c r="G93" t="n">
-        <v>324.828823</v>
+        <v>455.231814</v>
       </c>
       <c r="H93" t="n">
-        <v>455.231814</v>
+        <v>398.242969</v>
       </c>
       <c r="I93" t="n">
-        <v>398.242969</v>
+        <v>258.784612</v>
       </c>
       <c r="J93" t="n">
-        <v>258.784612</v>
+        <v>445.704742</v>
       </c>
     </row>
     <row r="94">
@@ -3577,31 +3577,31 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.026711</v>
+        <v>0.013497</v>
       </c>
       <c r="C94" t="n">
-        <v>0.013497</v>
+        <v>0.02439075</v>
       </c>
       <c r="D94" t="n">
-        <v>0.02439075</v>
+        <v>0.017441</v>
       </c>
       <c r="E94" t="n">
-        <v>0.017441</v>
+        <v>0.0139595</v>
       </c>
       <c r="F94" t="n">
-        <v>0.0139595</v>
+        <v>0.013798</v>
       </c>
       <c r="G94" t="n">
-        <v>0.013798</v>
+        <v>0.01124266666666667</v>
       </c>
       <c r="H94" t="n">
-        <v>0.01124266666666667</v>
+        <v>0.014224</v>
       </c>
       <c r="I94" t="n">
-        <v>0.014224</v>
+        <v>0.0165205</v>
       </c>
       <c r="J94" t="n">
-        <v>0.0165205</v>
+        <v>0.0227925</v>
       </c>
     </row>
     <row r="95">
@@ -3611,31 +3611,31 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>504.812143</v>
+        <v>1053.949158</v>
       </c>
       <c r="C95" t="n">
-        <v>1053.949158</v>
+        <v>429.448187</v>
       </c>
       <c r="D95" t="n">
-        <v>429.448187</v>
+        <v>405.79081</v>
       </c>
       <c r="E95" t="n">
-        <v>405.79081</v>
+        <v>336.288928</v>
       </c>
       <c r="F95" t="n">
-        <v>336.288928</v>
+        <v>316.722726</v>
       </c>
       <c r="G95" t="n">
-        <v>316.722726</v>
+        <v>387.168212</v>
       </c>
       <c r="H95" t="n">
-        <v>387.168212</v>
+        <v>318.778998</v>
       </c>
       <c r="I95" t="n">
-        <v>318.778998</v>
+        <v>347.368203</v>
       </c>
       <c r="J95" t="n">
-        <v>347.368203</v>
+        <v>671.624054</v>
       </c>
     </row>
     <row r="96">
@@ -3645,31 +3645,31 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.013613</v>
+        <v>0.011385</v>
       </c>
       <c r="C96" t="n">
-        <v>0.011385</v>
+        <v>0.008755000000000001</v>
       </c>
       <c r="D96" t="n">
-        <v>0.008755000000000001</v>
+        <v>0.005496</v>
       </c>
       <c r="E96" t="n">
-        <v>0.005496</v>
+        <v>0.009808000000000001</v>
       </c>
       <c r="F96" t="n">
-        <v>0.009808000000000001</v>
+        <v>0.009979999999999999</v>
       </c>
       <c r="G96" t="n">
-        <v>0.009979999999999999</v>
+        <v>0.018619</v>
       </c>
       <c r="H96" t="n">
-        <v>0.018619</v>
+        <v>0.009264</v>
       </c>
       <c r="I96" t="n">
-        <v>0.009264</v>
+        <v>0.007109</v>
       </c>
       <c r="J96" t="n">
-        <v>0.007109</v>
+        <v>0.010601</v>
       </c>
     </row>
     <row r="97">
@@ -3679,31 +3679,31 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>319.876891</v>
+        <v>147.465323</v>
       </c>
       <c r="C97" t="n">
-        <v>147.465323</v>
+        <v>105.537485</v>
       </c>
       <c r="D97" t="n">
-        <v>105.537485</v>
+        <v>94.891927</v>
       </c>
       <c r="E97" t="n">
-        <v>94.891927</v>
+        <v>95.083974</v>
       </c>
       <c r="F97" t="n">
-        <v>95.083974</v>
+        <v>100.186322</v>
       </c>
       <c r="G97" t="n">
-        <v>100.186322</v>
+        <v>93.857151</v>
       </c>
       <c r="H97" t="n">
-        <v>93.857151</v>
+        <v>62.84585</v>
       </c>
       <c r="I97" t="n">
-        <v>62.84585</v>
+        <v>63.914319</v>
       </c>
       <c r="J97" t="n">
-        <v>63.914319</v>
+        <v>91.15087200000001</v>
       </c>
     </row>
     <row r="98">
@@ -3713,31 +3713,31 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.015079</v>
+        <v>0.003464666666666667</v>
       </c>
       <c r="C98" t="n">
-        <v>0.003464666666666667</v>
+        <v>0.002068666666666667</v>
       </c>
       <c r="D98" t="n">
-        <v>0.002068666666666667</v>
+        <v>0.004654</v>
       </c>
       <c r="E98" t="n">
-        <v>0.004654</v>
+        <v>0.003868</v>
       </c>
       <c r="F98" t="n">
-        <v>0.003868</v>
+        <v>0.006015</v>
       </c>
       <c r="G98" t="n">
-        <v>0.006015</v>
+        <v>0.003297</v>
       </c>
       <c r="H98" t="n">
-        <v>0.003297</v>
+        <v>0.012757</v>
       </c>
       <c r="I98" t="n">
-        <v>0.012757</v>
+        <v>0.00767</v>
       </c>
       <c r="J98" t="n">
-        <v>0.00767</v>
+        <v>0.011396</v>
       </c>
     </row>
     <row r="99">
@@ -3747,31 +3747,31 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>156.495259</v>
+        <v>102.21092</v>
       </c>
       <c r="C99" t="n">
-        <v>102.21092</v>
+        <v>64.102439</v>
       </c>
       <c r="D99" t="n">
-        <v>64.102439</v>
+        <v>93.322474</v>
       </c>
       <c r="E99" t="n">
-        <v>93.322474</v>
+        <v>55.077038</v>
       </c>
       <c r="F99" t="n">
-        <v>55.077038</v>
+        <v>95.97843399999999</v>
       </c>
       <c r="G99" t="n">
-        <v>95.97843399999999</v>
+        <v>165.196967</v>
       </c>
       <c r="H99" t="n">
-        <v>165.196967</v>
+        <v>129.628898</v>
       </c>
       <c r="I99" t="n">
-        <v>129.628898</v>
+        <v>68.697436</v>
       </c>
       <c r="J99" t="n">
-        <v>68.697436</v>
+        <v>106.953609</v>
       </c>
     </row>
     <row r="100">
@@ -3781,31 +3781,31 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.046628</v>
+        <v>0.035645</v>
       </c>
       <c r="C100" t="n">
-        <v>0.035645</v>
+        <v>0.024784</v>
       </c>
       <c r="D100" t="n">
-        <v>0.024784</v>
+        <v>0.02873575</v>
       </c>
       <c r="E100" t="n">
-        <v>0.02873575</v>
+        <v>0.02663225</v>
       </c>
       <c r="F100" t="n">
-        <v>0.02663225</v>
+        <v>0.02465833333333333</v>
       </c>
       <c r="G100" t="n">
-        <v>0.02465833333333333</v>
+        <v>0.028249</v>
       </c>
       <c r="H100" t="n">
-        <v>0.028249</v>
+        <v>0.02861575</v>
       </c>
       <c r="I100" t="n">
-        <v>0.02861575</v>
+        <v>0.0370275</v>
       </c>
       <c r="J100" t="n">
-        <v>0.0370275</v>
+        <v>0.05126</v>
       </c>
     </row>
     <row r="101">
@@ -3815,31 +3815,31 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>34.262758</v>
+        <v>22.889902</v>
       </c>
       <c r="C101" t="n">
-        <v>22.889902</v>
+        <v>22.613706</v>
       </c>
       <c r="D101" t="n">
-        <v>22.613706</v>
+        <v>19.89963</v>
       </c>
       <c r="E101" t="n">
-        <v>19.89963</v>
+        <v>30.053022</v>
       </c>
       <c r="F101" t="n">
-        <v>30.053022</v>
+        <v>1.783048</v>
       </c>
       <c r="G101" t="n">
-        <v>1.783048</v>
+        <v>95.505253</v>
       </c>
       <c r="H101" t="n">
-        <v>95.505253</v>
+        <v>2.496406</v>
       </c>
       <c r="I101" t="n">
-        <v>2.496406</v>
+        <v>3.33623</v>
       </c>
       <c r="J101" t="n">
-        <v>3.33623</v>
+        <v>4.620654</v>
       </c>
     </row>
     <row r="102">
@@ -3849,25 +3849,25 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>4.9e-05</v>
+        <v>0.000116</v>
       </c>
       <c r="C102" t="n">
-        <v>0.000116</v>
-      </c>
-      <c r="D102" t="n">
         <v>6.7e-05</v>
       </c>
+      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
+      <c r="G102" t="n">
+        <v>9.7e-05</v>
+      </c>
       <c r="H102" t="n">
-        <v>9.7e-05</v>
+        <v>0.000504</v>
       </c>
       <c r="I102" t="n">
-        <v>0.000504</v>
+        <v>0.000464</v>
       </c>
       <c r="J102" t="n">
-        <v>0.000464</v>
+        <v>0.000145</v>
       </c>
     </row>
     <row r="103">
@@ -3877,31 +3877,31 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>137.588249</v>
+        <v>128.75096475</v>
       </c>
       <c r="C103" t="n">
-        <v>128.75096475</v>
+        <v>140.190352</v>
       </c>
       <c r="D103" t="n">
-        <v>140.190352</v>
+        <v>116.670222</v>
       </c>
       <c r="E103" t="n">
-        <v>116.670222</v>
+        <v>131.438059</v>
       </c>
       <c r="F103" t="n">
-        <v>131.438059</v>
+        <v>116.348776</v>
       </c>
       <c r="G103" t="n">
-        <v>116.348776</v>
+        <v>65.234769</v>
       </c>
       <c r="H103" t="n">
-        <v>65.234769</v>
+        <v>155.847863</v>
       </c>
       <c r="I103" t="n">
-        <v>155.847863</v>
+        <v>112.212126</v>
       </c>
       <c r="J103" t="n">
-        <v>112.212126</v>
+        <v>139.522438</v>
       </c>
     </row>
     <row r="104">
@@ -3911,31 +3911,31 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>1500.974829</v>
+        <v>1270.345084</v>
       </c>
       <c r="C104" t="n">
-        <v>1270.345084</v>
+        <v>1276.408497</v>
       </c>
       <c r="D104" t="n">
-        <v>1276.408497</v>
+        <v>434.218828</v>
       </c>
       <c r="E104" t="n">
-        <v>434.218828</v>
+        <v>390.718436</v>
       </c>
       <c r="F104" t="n">
-        <v>390.718436</v>
+        <v>467.491935</v>
       </c>
       <c r="G104" t="n">
-        <v>467.491935</v>
+        <v>612.164225</v>
       </c>
       <c r="H104" t="n">
-        <v>612.164225</v>
+        <v>693.404366</v>
       </c>
       <c r="I104" t="n">
-        <v>693.404366</v>
+        <v>459.53632</v>
       </c>
       <c r="J104" t="n">
-        <v>440.79424</v>
+        <v>787.559262</v>
       </c>
     </row>
     <row r="105">
@@ -3945,31 +3945,31 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>64.42345400000001</v>
+        <v>41.367954</v>
       </c>
       <c r="C105" t="n">
-        <v>41.367954</v>
+        <v>31.043476</v>
       </c>
       <c r="D105" t="n">
-        <v>31.043476</v>
+        <v>3.13383</v>
       </c>
       <c r="E105" t="n">
-        <v>3.13383</v>
+        <v>2.8508</v>
       </c>
       <c r="F105" t="n">
-        <v>2.8508</v>
+        <v>3.327093</v>
       </c>
       <c r="G105" t="n">
-        <v>3.327093</v>
+        <v>2.304672</v>
       </c>
       <c r="H105" t="n">
-        <v>2.304672</v>
+        <v>2.066771</v>
       </c>
       <c r="I105" t="n">
-        <v>2.066771</v>
+        <v>2.46186</v>
       </c>
       <c r="J105" t="n">
-        <v>2.46186</v>
+        <v>3.319155</v>
       </c>
     </row>
     <row r="106">
@@ -3979,31 +3979,31 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>647.83709</v>
+        <v>1724.96783</v>
       </c>
       <c r="C106" t="n">
-        <v>1724.96783</v>
+        <v>432.610359</v>
       </c>
       <c r="D106" t="n">
-        <v>432.610359</v>
+        <v>180.215207</v>
       </c>
       <c r="E106" t="n">
-        <v>180.215207</v>
+        <v>651.772335</v>
       </c>
       <c r="F106" t="n">
-        <v>651.772335</v>
+        <v>1960.644805</v>
       </c>
       <c r="G106" t="n">
-        <v>1960.644805</v>
+        <v>3453.042004</v>
       </c>
       <c r="H106" t="n">
-        <v>3453.042004</v>
+        <v>1933.400534</v>
       </c>
       <c r="I106" t="n">
-        <v>1933.400534</v>
+        <v>878.010869</v>
       </c>
       <c r="J106" t="n">
-        <v>878.010869</v>
+        <v>2252.603586</v>
       </c>
     </row>
     <row r="107">
@@ -4013,31 +4013,31 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.336738</v>
+        <v>0.46604</v>
       </c>
       <c r="C107" t="n">
-        <v>0.46604</v>
+        <v>0.571151</v>
       </c>
       <c r="D107" t="n">
-        <v>0.571151</v>
+        <v>0.259937</v>
       </c>
       <c r="E107" t="n">
-        <v>0.259937</v>
+        <v>0.631062</v>
       </c>
       <c r="F107" t="n">
-        <v>0.631062</v>
+        <v>0.656298</v>
       </c>
       <c r="G107" t="n">
-        <v>0.656298</v>
+        <v>0.670773</v>
       </c>
       <c r="H107" t="n">
-        <v>0.670773</v>
+        <v>0.864629</v>
       </c>
       <c r="I107" t="n">
-        <v>0.864629</v>
+        <v>1.367999</v>
       </c>
       <c r="J107" t="n">
-        <v>1.367999</v>
+        <v>1.736339</v>
       </c>
     </row>
     <row r="108">
@@ -4047,31 +4047,31 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>91.55938</v>
+        <v>50.13991</v>
       </c>
       <c r="C108" t="n">
-        <v>50.13991</v>
+        <v>48.622336</v>
       </c>
       <c r="D108" t="n">
-        <v>48.622336</v>
+        <v>28.670208</v>
       </c>
       <c r="E108" t="n">
-        <v>28.670208</v>
+        <v>33.945377</v>
       </c>
       <c r="F108" t="n">
-        <v>33.945377</v>
+        <v>69.141695</v>
       </c>
       <c r="G108" t="n">
-        <v>69.141695</v>
+        <v>86.43472199999999</v>
       </c>
       <c r="H108" t="n">
-        <v>86.43472199999999</v>
+        <v>30.692105</v>
       </c>
       <c r="I108" t="n">
-        <v>30.692105</v>
+        <v>63.709984</v>
       </c>
       <c r="J108" t="n">
-        <v>63.709984</v>
+        <v>47.735336</v>
       </c>
     </row>
     <row r="109">
@@ -4081,31 +4081,31 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.091789</v>
+        <v>0.06341425000000001</v>
       </c>
       <c r="C109" t="n">
-        <v>0.06341425000000001</v>
+        <v>0.043578</v>
       </c>
       <c r="D109" t="n">
-        <v>0.043578</v>
+        <v>0.04419866666666666</v>
       </c>
       <c r="E109" t="n">
-        <v>0.04419866666666666</v>
+        <v>0.028136</v>
       </c>
       <c r="F109" t="n">
-        <v>0.028136</v>
+        <v>0.047992</v>
       </c>
       <c r="G109" t="n">
-        <v>0.047992</v>
+        <v>0.093903</v>
       </c>
       <c r="H109" t="n">
-        <v>0.136048</v>
+        <v>0.058137</v>
       </c>
       <c r="I109" t="n">
-        <v>0.058137</v>
+        <v>0.086058</v>
       </c>
       <c r="J109" t="n">
-        <v>0.086058</v>
+        <v>0.211332</v>
       </c>
     </row>
     <row r="110">
@@ -4115,27 +4115,27 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>639.366413</v>
+        <v>437.475353</v>
       </c>
       <c r="C110" t="n">
-        <v>437.475353</v>
+        <v>1358.351665</v>
       </c>
       <c r="D110" t="n">
-        <v>1358.351665</v>
+        <v>455.205895</v>
       </c>
       <c r="E110" t="n">
-        <v>455.205895</v>
+        <v>42.162402</v>
       </c>
       <c r="F110" t="n">
-        <v>42.162402</v>
-      </c>
-      <c r="G110" t="n">
         <v>190.401814</v>
       </c>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
+      <c r="I110" t="n">
+        <v>55.006575</v>
+      </c>
       <c r="J110" t="n">
-        <v>55.006575</v>
+        <v>60.556877</v>
       </c>
     </row>
     <row r="111">
@@ -4145,31 +4145,31 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.789226</v>
+        <v>0.958326</v>
       </c>
       <c r="C111" t="n">
-        <v>0.958326</v>
+        <v>0.909138</v>
       </c>
       <c r="D111" t="n">
-        <v>0.909138</v>
+        <v>0.363006</v>
       </c>
       <c r="E111" t="n">
-        <v>0.363006</v>
+        <v>0.378988</v>
       </c>
       <c r="F111" t="n">
-        <v>0.378988</v>
+        <v>1.140258</v>
       </c>
       <c r="G111" t="n">
-        <v>1.140258</v>
+        <v>1.470562</v>
       </c>
       <c r="H111" t="n">
-        <v>1.428417</v>
+        <v>0.901454</v>
       </c>
       <c r="I111" t="n">
-        <v>0.901454</v>
+        <v>0.569587</v>
       </c>
       <c r="J111" t="n">
-        <v>0.569587</v>
+        <v>1.047955</v>
       </c>
     </row>
     <row r="112">
@@ -4179,27 +4179,27 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.000425</v>
+        <v>0.000557</v>
       </c>
       <c r="C112" t="n">
-        <v>0.000557</v>
-      </c>
-      <c r="D112" t="n">
         <v>0.000392</v>
       </c>
+      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
+      <c r="F112" t="n">
+        <v>0.003449</v>
+      </c>
       <c r="G112" t="n">
-        <v>0.003449</v>
+        <v>0.000749</v>
       </c>
       <c r="H112" t="n">
-        <v>0.000749</v>
+        <v>0.000753</v>
       </c>
       <c r="I112" t="n">
-        <v>0.000753</v>
+        <v>0.000348</v>
       </c>
       <c r="J112" t="n">
-        <v>0.000348</v>
+        <v>0.0009840000000000001</v>
       </c>
     </row>
     <row r="113">
@@ -4209,31 +4209,31 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.006127</v>
+        <v>0.002604</v>
       </c>
       <c r="C113" t="n">
-        <v>0.002604</v>
+        <v>0.002352</v>
       </c>
       <c r="D113" t="n">
-        <v>0.002352</v>
+        <v>0.002214</v>
       </c>
       <c r="E113" t="n">
-        <v>0.002214</v>
+        <v>0.001819</v>
       </c>
       <c r="F113" t="n">
-        <v>0.001819</v>
+        <v>0.003116</v>
       </c>
       <c r="G113" t="n">
-        <v>0.003116</v>
+        <v>0.00277</v>
       </c>
       <c r="H113" t="n">
-        <v>0.00277</v>
+        <v>0.001897</v>
       </c>
       <c r="I113" t="n">
-        <v>0.001897</v>
+        <v>0.00232</v>
       </c>
       <c r="J113" t="n">
-        <v>0.00232</v>
+        <v>0.002834</v>
       </c>
     </row>
     <row r="114">
@@ -4244,13 +4244,13 @@
       </c>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr"/>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="n">
+        <v>0.000429</v>
+      </c>
       <c r="E114" t="n">
-        <v>0.000429</v>
-      </c>
-      <c r="F114" t="n">
         <v>0.000733</v>
       </c>
+      <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr"/>
@@ -4263,31 +4263,31 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>29221.238724</v>
+        <v>23689.328803</v>
       </c>
       <c r="C115" t="n">
-        <v>23689.328803</v>
+        <v>23865.695498</v>
       </c>
       <c r="D115" t="n">
-        <v>23865.695498</v>
+        <v>18716.52571</v>
       </c>
       <c r="E115" t="n">
-        <v>18716.52571</v>
+        <v>29109.164676</v>
       </c>
       <c r="F115" t="n">
-        <v>29109.164676</v>
+        <v>17026.871017</v>
       </c>
       <c r="G115" t="n">
-        <v>17026.871017</v>
+        <v>17907.065865</v>
       </c>
       <c r="H115" t="n">
-        <v>17907.065865</v>
+        <v>17209.941215</v>
       </c>
       <c r="I115" t="n">
-        <v>17209.941215</v>
+        <v>22415.774526</v>
       </c>
       <c r="J115" t="n">
-        <v>22415.774526</v>
+        <v>10631.187408</v>
       </c>
     </row>
     <row r="116">
@@ -4297,31 +4297,31 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>17.786353</v>
+        <v>21.297676</v>
       </c>
       <c r="C116" t="n">
-        <v>21.297676</v>
+        <v>13.45781</v>
       </c>
       <c r="D116" t="n">
-        <v>13.45781</v>
+        <v>10.86563</v>
       </c>
       <c r="E116" t="n">
-        <v>10.86563</v>
+        <v>10.11165</v>
       </c>
       <c r="F116" t="n">
-        <v>10.11165</v>
+        <v>13.436873</v>
       </c>
       <c r="G116" t="n">
-        <v>13.436873</v>
+        <v>12.266752</v>
       </c>
       <c r="H116" t="n">
-        <v>12.266752</v>
+        <v>12.098587</v>
       </c>
       <c r="I116" t="n">
-        <v>12.098587</v>
+        <v>19.597589</v>
       </c>
       <c r="J116" t="n">
-        <v>19.597589</v>
+        <v>14.719299</v>
       </c>
     </row>
     <row r="117">
@@ -4331,31 +4331,31 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>970.944972</v>
+        <v>1232.292849</v>
       </c>
       <c r="C117" t="n">
-        <v>1232.292849</v>
+        <v>813.427695</v>
       </c>
       <c r="D117" t="n">
-        <v>813.427695</v>
+        <v>616.561423</v>
       </c>
       <c r="E117" t="n">
-        <v>616.561423</v>
+        <v>753.0441510000001</v>
       </c>
       <c r="F117" t="n">
-        <v>753.0441510000001</v>
+        <v>795.101355</v>
       </c>
       <c r="G117" t="n">
-        <v>795.101355</v>
+        <v>1054.902316</v>
       </c>
       <c r="H117" t="n">
-        <v>1054.902316</v>
+        <v>621.182799</v>
       </c>
       <c r="I117" t="n">
-        <v>621.182799</v>
+        <v>611.530382</v>
       </c>
       <c r="J117" t="n">
-        <v>611.530382</v>
+        <v>990.258572</v>
       </c>
     </row>
     <row r="118">
@@ -4365,31 +4365,31 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.150084</v>
+        <v>0.119453</v>
       </c>
       <c r="C118" t="n">
-        <v>0.119453</v>
+        <v>0.1368</v>
       </c>
       <c r="D118" t="n">
-        <v>0.1368</v>
+        <v>0.242976</v>
       </c>
       <c r="E118" t="n">
-        <v>0.242976</v>
+        <v>0.15816</v>
       </c>
       <c r="F118" t="n">
-        <v>0.15816</v>
+        <v>0.229197</v>
       </c>
       <c r="G118" t="n">
-        <v>0.229197</v>
+        <v>0.311284</v>
       </c>
       <c r="H118" t="n">
-        <v>0.311284</v>
+        <v>0.2129</v>
       </c>
       <c r="I118" t="n">
-        <v>0.2129</v>
+        <v>0.395204</v>
       </c>
       <c r="J118" t="n">
-        <v>0.395204</v>
+        <v>0.329626</v>
       </c>
     </row>
     <row r="119">
@@ -4399,31 +4399,31 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>237.604652</v>
+        <v>297.191071</v>
       </c>
       <c r="C119" t="n">
-        <v>297.191071</v>
+        <v>188.306349</v>
       </c>
       <c r="D119" t="n">
-        <v>188.306349</v>
+        <v>2009.813657</v>
       </c>
       <c r="E119" t="n">
-        <v>2009.813657</v>
+        <v>346.941465</v>
       </c>
       <c r="F119" t="n">
-        <v>346.941465</v>
+        <v>2028.738573</v>
       </c>
       <c r="G119" t="n">
-        <v>2028.738573</v>
+        <v>2170.851283</v>
       </c>
       <c r="H119" t="n">
-        <v>2170.851283</v>
+        <v>1410.051718</v>
       </c>
       <c r="I119" t="n">
-        <v>1410.051718</v>
+        <v>2921.042101</v>
       </c>
       <c r="J119" t="n">
-        <v>2921.042101</v>
+        <v>10804.075222</v>
       </c>
     </row>
     <row r="120">
@@ -4433,31 +4433,31 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>2.779475</v>
+        <v>2.073253</v>
       </c>
       <c r="C120" t="n">
-        <v>2.073253</v>
+        <v>2.173097</v>
       </c>
       <c r="D120" t="n">
-        <v>2.173097</v>
+        <v>1.498725</v>
       </c>
       <c r="E120" t="n">
-        <v>1.498725</v>
+        <v>1.880031</v>
       </c>
       <c r="F120" t="n">
-        <v>1.880031</v>
+        <v>2.860901</v>
       </c>
       <c r="G120" t="n">
-        <v>2.860901</v>
+        <v>1.897831</v>
       </c>
       <c r="H120" t="n">
-        <v>1.897831</v>
+        <v>1.719239</v>
       </c>
       <c r="I120" t="n">
-        <v>1.719239</v>
+        <v>2.523746</v>
       </c>
       <c r="J120" t="n">
-        <v>2.523746</v>
+        <v>2.539256</v>
       </c>
     </row>
     <row r="121">
@@ -4467,31 +4467,31 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>160.911874</v>
+        <v>79.776139</v>
       </c>
       <c r="C121" t="n">
-        <v>79.776139</v>
+        <v>58.508732</v>
       </c>
       <c r="D121" t="n">
-        <v>58.508732</v>
+        <v>86.105074</v>
       </c>
       <c r="E121" t="n">
-        <v>86.105074</v>
+        <v>51.561188</v>
       </c>
       <c r="F121" t="n">
-        <v>51.561188</v>
+        <v>29.226817</v>
       </c>
       <c r="G121" t="n">
-        <v>29.226817</v>
+        <v>74.29553300000001</v>
       </c>
       <c r="H121" t="n">
-        <v>74.29553300000001</v>
+        <v>52.944199</v>
       </c>
       <c r="I121" t="n">
-        <v>52.944199</v>
+        <v>49.507243</v>
       </c>
       <c r="J121" t="n">
-        <v>49.507243</v>
+        <v>96.176267</v>
       </c>
     </row>
     <row r="122">
@@ -4501,31 +4501,31 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>7.803697</v>
+        <v>6.192561</v>
       </c>
       <c r="C122" t="n">
-        <v>6.192561</v>
+        <v>8.273391</v>
       </c>
       <c r="D122" t="n">
-        <v>8.273391</v>
+        <v>4.759663</v>
       </c>
       <c r="E122" t="n">
-        <v>4.759663</v>
+        <v>7.401011</v>
       </c>
       <c r="F122" t="n">
-        <v>7.401011</v>
+        <v>5.426103</v>
       </c>
       <c r="G122" t="n">
-        <v>5.426103</v>
+        <v>6.686925</v>
       </c>
       <c r="H122" t="n">
-        <v>6.686925</v>
+        <v>7.952223</v>
       </c>
       <c r="I122" t="n">
-        <v>7.952223</v>
+        <v>5.702471</v>
       </c>
       <c r="J122" t="n">
-        <v>5.702471</v>
+        <v>34.281994</v>
       </c>
     </row>
     <row r="123">
@@ -4535,31 +4535,31 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>46.057863</v>
+        <v>29.321354</v>
       </c>
       <c r="C123" t="n">
-        <v>29.321354</v>
+        <v>25.745741</v>
       </c>
       <c r="D123" t="n">
-        <v>25.745741</v>
+        <v>31.758045</v>
       </c>
       <c r="E123" t="n">
-        <v>31.758045</v>
+        <v>43.067624</v>
       </c>
       <c r="F123" t="n">
-        <v>43.067624</v>
+        <v>28.785075</v>
       </c>
       <c r="G123" t="n">
-        <v>28.785075</v>
+        <v>33.512378</v>
       </c>
       <c r="H123" t="n">
-        <v>33.512378</v>
+        <v>23.447801</v>
       </c>
       <c r="I123" t="n">
-        <v>23.447801</v>
+        <v>35.0707</v>
       </c>
       <c r="J123" t="n">
-        <v>35.0707</v>
+        <v>27.312669</v>
       </c>
     </row>
     <row r="124">
@@ -4569,31 +4569,31 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>13.454182</v>
+        <v>9.400376</v>
       </c>
       <c r="C124" t="n">
-        <v>9.400376</v>
+        <v>20.184931</v>
       </c>
       <c r="D124" t="n">
-        <v>20.184931</v>
+        <v>40.641022</v>
       </c>
       <c r="E124" t="n">
-        <v>40.641022</v>
+        <v>104.901909</v>
       </c>
       <c r="F124" t="n">
-        <v>104.901909</v>
+        <v>35.760378</v>
       </c>
       <c r="G124" t="n">
-        <v>35.760378</v>
+        <v>101.905354</v>
       </c>
       <c r="H124" t="n">
-        <v>101.905354</v>
+        <v>41.723378</v>
       </c>
       <c r="I124" t="n">
-        <v>41.723378</v>
+        <v>8.526634</v>
       </c>
       <c r="J124" t="n">
-        <v>8.526634</v>
+        <v>22.270006</v>
       </c>
     </row>
     <row r="125">
@@ -4603,31 +4603,31 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.001496</v>
+        <v>0.005709</v>
       </c>
       <c r="C125" t="n">
-        <v>0.005709</v>
+        <v>0.002274</v>
       </c>
       <c r="D125" t="n">
-        <v>0.002274</v>
+        <v>0.001796</v>
       </c>
       <c r="E125" t="n">
-        <v>0.001796</v>
+        <v>0.001943</v>
       </c>
       <c r="F125" t="n">
-        <v>0.001943</v>
+        <v>0.001247</v>
       </c>
       <c r="G125" t="n">
-        <v>0.001247</v>
+        <v>0.00146</v>
       </c>
       <c r="H125" t="n">
-        <v>0.00146</v>
+        <v>0.000743</v>
       </c>
       <c r="I125" t="n">
-        <v>0.000743</v>
+        <v>0.001786</v>
       </c>
       <c r="J125" t="n">
-        <v>0.001786</v>
+        <v>0.00121</v>
       </c>
     </row>
     <row r="126">
@@ -4637,31 +4637,31 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>1158.378359</v>
+        <v>980.0030400000001</v>
       </c>
       <c r="C126" t="n">
-        <v>980.0030400000001</v>
+        <v>793.010167</v>
       </c>
       <c r="D126" t="n">
-        <v>793.010167</v>
+        <v>718.786573</v>
       </c>
       <c r="E126" t="n">
-        <v>718.786573</v>
+        <v>927.2286810000001</v>
       </c>
       <c r="F126" t="n">
-        <v>927.2286810000001</v>
+        <v>1101.476089</v>
       </c>
       <c r="G126" t="n">
-        <v>1101.476089</v>
+        <v>1527.017845</v>
       </c>
       <c r="H126" t="n">
-        <v>1527.017845</v>
+        <v>1302.824046</v>
       </c>
       <c r="I126" t="n">
-        <v>1302.824046</v>
+        <v>841.355541</v>
       </c>
       <c r="J126" t="n">
-        <v>841.355541</v>
+        <v>1218.543572</v>
       </c>
     </row>
     <row r="127">
@@ -4671,31 +4671,31 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.010944</v>
+        <v>0.051479</v>
       </c>
       <c r="C127" t="n">
-        <v>0.051479</v>
+        <v>0.019638</v>
       </c>
       <c r="D127" t="n">
-        <v>0.019638</v>
+        <v>0.013057</v>
       </c>
       <c r="E127" t="n">
-        <v>0.013057</v>
+        <v>0.011711</v>
       </c>
       <c r="F127" t="n">
-        <v>0.011711</v>
+        <v>0.01282675</v>
       </c>
       <c r="G127" t="n">
-        <v>0.01282675</v>
+        <v>0.010744</v>
       </c>
       <c r="H127" t="n">
-        <v>0.010744</v>
+        <v>0.009403</v>
       </c>
       <c r="I127" t="n">
-        <v>0.009403</v>
+        <v>0.005297</v>
       </c>
       <c r="J127" t="n">
-        <v>0.005297</v>
+        <v>0.009745</v>
       </c>
     </row>
     <row r="128">
@@ -4705,31 +4705,31 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>362.16461</v>
+        <v>135.759536</v>
       </c>
       <c r="C128" t="n">
-        <v>135.759536</v>
+        <v>184.75593</v>
       </c>
       <c r="D128" t="n">
-        <v>184.75593</v>
+        <v>143.780451</v>
       </c>
       <c r="E128" t="n">
-        <v>143.780451</v>
+        <v>142.344478</v>
       </c>
       <c r="F128" t="n">
-        <v>142.344478</v>
+        <v>41.631818</v>
       </c>
       <c r="G128" t="n">
-        <v>41.631818</v>
+        <v>218.704712</v>
       </c>
       <c r="H128" t="n">
-        <v>218.704712</v>
+        <v>12.374039</v>
       </c>
       <c r="I128" t="n">
-        <v>12.374039</v>
+        <v>3.083981</v>
       </c>
       <c r="J128" t="n">
-        <v>3.083981</v>
+        <v>3.902189</v>
       </c>
     </row>
     <row r="129">
@@ -4739,27 +4739,27 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>7.7e-05</v>
+        <v>0.000127</v>
       </c>
       <c r="C129" t="n">
-        <v>0.000127</v>
+        <v>1.7e-05</v>
       </c>
       <c r="D129" t="n">
-        <v>1.7e-05</v>
-      </c>
-      <c r="E129" t="n">
         <v>0.000413</v>
       </c>
+      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr"/>
+      <c r="G129" t="n">
+        <v>0.000429</v>
+      </c>
       <c r="H129" t="n">
-        <v>0.000429</v>
+        <v>0.000532</v>
       </c>
       <c r="I129" t="n">
-        <v>0.000532</v>
+        <v>0.000311</v>
       </c>
       <c r="J129" t="n">
-        <v>0.000311</v>
+        <v>0.001149</v>
       </c>
     </row>
     <row r="130">
@@ -4769,31 +4769,31 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>35449.998064</v>
+        <v>28927.249252</v>
       </c>
       <c r="C130" t="n">
-        <v>28927.249252</v>
+        <v>20148.564437</v>
       </c>
       <c r="D130" t="n">
-        <v>20148.564437</v>
+        <v>19128.336859</v>
       </c>
       <c r="E130" t="n">
-        <v>19128.336859</v>
+        <v>21837.620673</v>
       </c>
       <c r="F130" t="n">
-        <v>21837.620673</v>
+        <v>19211.706761</v>
       </c>
       <c r="G130" t="n">
-        <v>19211.706761</v>
+        <v>31667.832324</v>
       </c>
       <c r="H130" t="n">
-        <v>31667.832324</v>
+        <v>16449.342725</v>
       </c>
       <c r="I130" t="n">
-        <v>16449.342725</v>
+        <v>16351.435632</v>
       </c>
       <c r="J130" t="n">
-        <v>16278.565632</v>
+        <v>22272.168735</v>
       </c>
     </row>
     <row r="131">
@@ -4803,31 +4803,31 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>313.057836</v>
+        <v>258.249554</v>
       </c>
       <c r="C131" t="n">
-        <v>258.249554</v>
+        <v>190.677356</v>
       </c>
       <c r="D131" t="n">
-        <v>190.677356</v>
+        <v>193.630935</v>
       </c>
       <c r="E131" t="n">
-        <v>193.630935</v>
+        <v>137.66002</v>
       </c>
       <c r="F131" t="n">
-        <v>137.66002</v>
+        <v>158.800948</v>
       </c>
       <c r="G131" t="n">
-        <v>158.800948</v>
+        <v>142.063186</v>
       </c>
       <c r="H131" t="n">
-        <v>142.063186</v>
+        <v>108.445934</v>
       </c>
       <c r="I131" t="n">
-        <v>108.445934</v>
+        <v>135.397884</v>
       </c>
       <c r="J131" t="n">
-        <v>135.397884</v>
+        <v>246.000319</v>
       </c>
     </row>
     <row r="132">
@@ -4837,31 +4837,31 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>11.910874</v>
+        <v>26.483238</v>
       </c>
       <c r="C132" t="n">
-        <v>26.483238</v>
+        <v>130.568197</v>
       </c>
       <c r="D132" t="n">
-        <v>130.568197</v>
+        <v>55.324957</v>
       </c>
       <c r="E132" t="n">
-        <v>55.324957</v>
+        <v>57.040545</v>
       </c>
       <c r="F132" t="n">
-        <v>57.040545</v>
+        <v>41.800411</v>
       </c>
       <c r="G132" t="n">
-        <v>41.800411</v>
+        <v>15.258326</v>
       </c>
       <c r="H132" t="n">
-        <v>15.258326</v>
+        <v>37.980158</v>
       </c>
       <c r="I132" t="n">
-        <v>37.980158</v>
+        <v>10.626671</v>
       </c>
       <c r="J132" t="n">
-        <v>10.626671</v>
+        <v>8.705826999999999</v>
       </c>
     </row>
     <row r="133">
@@ -4871,31 +4871,31 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.463364</v>
+        <v>0.293248</v>
       </c>
       <c r="C133" t="n">
-        <v>0.293248</v>
+        <v>0.280048</v>
       </c>
       <c r="D133" t="n">
-        <v>0.280048</v>
+        <v>0.205582</v>
       </c>
       <c r="E133" t="n">
-        <v>0.205582</v>
+        <v>0.14767</v>
       </c>
       <c r="F133" t="n">
-        <v>0.14767</v>
+        <v>0.162321</v>
       </c>
       <c r="G133" t="n">
-        <v>0.162321</v>
+        <v>0.151156</v>
       </c>
       <c r="H133" t="n">
-        <v>0.151156</v>
+        <v>0.168285</v>
       </c>
       <c r="I133" t="n">
-        <v>0.168285</v>
+        <v>0.143367</v>
       </c>
       <c r="J133" t="n">
-        <v>0.143367</v>
+        <v>0.236878</v>
       </c>
     </row>
     <row r="134">
@@ -4905,1369 +4905,1389 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.064164</v>
+        <v>0.046877</v>
       </c>
       <c r="C134" t="n">
-        <v>0.046877</v>
+        <v>0.052364</v>
       </c>
       <c r="D134" t="n">
-        <v>0.052364</v>
+        <v>0.043636</v>
       </c>
       <c r="E134" t="n">
-        <v>0.043636</v>
+        <v>0.03427</v>
       </c>
       <c r="F134" t="n">
-        <v>0.03427</v>
+        <v>0.021858</v>
       </c>
       <c r="G134" t="n">
-        <v>0.021858</v>
+        <v>0.022643</v>
       </c>
       <c r="H134" t="n">
-        <v>0.022643</v>
+        <v>0.018471</v>
       </c>
       <c r="I134" t="n">
-        <v>0.018471</v>
+        <v>0.012521</v>
       </c>
       <c r="J134" t="n">
-        <v>0.012521</v>
+        <v>0.038907</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上上市</t>
-        </is>
-      </c>
-      <c r="B135" t="n">
-        <v>1356.040678</v>
-      </c>
-      <c r="C135" t="n">
-        <v>2963.163965</v>
-      </c>
-      <c r="D135" t="n">
-        <v>1492.10477</v>
-      </c>
-      <c r="E135" t="n">
-        <v>2663.206052</v>
-      </c>
-      <c r="F135" t="n">
-        <v>2208.951272</v>
-      </c>
-      <c r="G135" t="n">
-        <v>2963.440125</v>
-      </c>
-      <c r="H135" t="n">
-        <v>2607.460876</v>
-      </c>
-      <c r="I135" t="n">
-        <v>1699.557954</v>
-      </c>
+          <t>金融業平上櫃</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr"/>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
       <c r="J135" t="n">
-        <v>793.506208</v>
+        <v>0.00029</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右上上櫃</t>
+          <t>鋼鐵工業右上上市</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.058361</v>
+        <v>2963.163965</v>
       </c>
       <c r="C136" t="n">
-        <v>0.064585</v>
+        <v>1492.10477</v>
       </c>
       <c r="D136" t="n">
-        <v>0.135021</v>
+        <v>2663.206052</v>
       </c>
       <c r="E136" t="n">
-        <v>0.103216</v>
+        <v>2208.951272</v>
       </c>
       <c r="F136" t="n">
-        <v>0.056944</v>
+        <v>2963.440125</v>
       </c>
       <c r="G136" t="n">
-        <v>0.20184</v>
+        <v>2607.460876</v>
       </c>
       <c r="H136" t="n">
-        <v>0.062697</v>
+        <v>1699.557954</v>
       </c>
       <c r="I136" t="n">
-        <v>0.049454</v>
+        <v>793.506208</v>
       </c>
       <c r="J136" t="n">
-        <v>0.16093</v>
+        <v>1193.424258</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右下上市</t>
+          <t>鋼鐵工業右上上櫃</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>257.71903</v>
+        <v>0.064585</v>
       </c>
       <c r="C137" t="n">
-        <v>244.828967</v>
+        <v>0.135021</v>
       </c>
       <c r="D137" t="n">
-        <v>278.44663</v>
+        <v>0.103216</v>
       </c>
       <c r="E137" t="n">
-        <v>143.434833</v>
+        <v>0.056944</v>
       </c>
       <c r="F137" t="n">
-        <v>161.302958</v>
+        <v>0.20184</v>
       </c>
       <c r="G137" t="n">
-        <v>170.540974</v>
+        <v>0.062697</v>
       </c>
       <c r="H137" t="n">
-        <v>396.047682</v>
+        <v>0.049454</v>
       </c>
       <c r="I137" t="n">
-        <v>130.53509</v>
+        <v>0.16093</v>
       </c>
       <c r="J137" t="n">
-        <v>142.222812</v>
+        <v>0.187531</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業右下上櫃</t>
+          <t>鋼鐵工業右下上市</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.07928300000000001</v>
+        <v>244.828967</v>
       </c>
       <c r="C138" t="n">
-        <v>0.014179</v>
+        <v>278.44663</v>
       </c>
       <c r="D138" t="n">
-        <v>0.009131</v>
+        <v>143.434833</v>
       </c>
       <c r="E138" t="n">
-        <v>0.033395</v>
+        <v>161.302958</v>
       </c>
       <c r="F138" t="n">
-        <v>0.07098699999999999</v>
+        <v>170.540974</v>
       </c>
       <c r="G138" t="n">
-        <v>0.006889</v>
+        <v>396.047682</v>
       </c>
       <c r="H138" t="n">
-        <v>0.07658175</v>
+        <v>130.53509</v>
       </c>
       <c r="I138" t="n">
-        <v>0.031658</v>
+        <v>142.222812</v>
       </c>
       <c r="J138" t="n">
-        <v>0.0393</v>
+        <v>382.148457</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業平上市</t>
+          <t>鋼鐵工業右下上櫃</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>1097.760524</v>
+        <v>0.014179</v>
       </c>
       <c r="C139" t="n">
-        <v>53.245693</v>
+        <v>0.009131</v>
       </c>
       <c r="D139" t="n">
-        <v>896.350784</v>
+        <v>0.033395</v>
       </c>
       <c r="E139" t="n">
-        <v>104.276388</v>
+        <v>0.07098699999999999</v>
       </c>
       <c r="F139" t="n">
-        <v>135.167745</v>
+        <v>0.006889</v>
       </c>
       <c r="G139" t="n">
-        <v>105.526739</v>
+        <v>0.07658175</v>
       </c>
       <c r="H139" t="n">
-        <v>65.224189</v>
+        <v>0.031658</v>
       </c>
       <c r="I139" t="n">
-        <v>119.64436</v>
+        <v>0.0393</v>
       </c>
       <c r="J139" t="n">
-        <v>600.754455</v>
+        <v>0.09736599999999999</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>鋼鐵工業平上櫃</t>
+          <t>鋼鐵工業平上市</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.001748</v>
+        <v>53.245693</v>
       </c>
       <c r="C140" t="n">
-        <v>0.07703699999999999</v>
+        <v>896.350784</v>
       </c>
       <c r="D140" t="n">
-        <v>0.042344</v>
+        <v>104.276388</v>
       </c>
       <c r="E140" t="n">
-        <v>0.000472</v>
+        <v>135.167745</v>
       </c>
       <c r="F140" t="n">
-        <v>0.000633</v>
+        <v>105.526739</v>
       </c>
       <c r="G140" t="n">
-        <v>0.09809725</v>
+        <v>65.224189</v>
       </c>
       <c r="H140" t="n">
-        <v>0.000282</v>
+        <v>119.64436</v>
       </c>
       <c r="I140" t="n">
-        <v>3e-06</v>
-      </c>
-      <c r="J140" t="inlineStr"/>
+        <v>600.754455</v>
+      </c>
+      <c r="J140" t="n">
+        <v>727.432351</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右上上市</t>
+          <t>鋼鐵工業平上櫃</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>3020.377115</v>
+        <v>0.07703699999999999</v>
       </c>
       <c r="C141" t="n">
-        <v>1437.331486</v>
+        <v>0.042344</v>
       </c>
       <c r="D141" t="n">
-        <v>1121.222264</v>
+        <v>0.000472</v>
       </c>
       <c r="E141" t="n">
-        <v>640.157403</v>
+        <v>0.000633</v>
       </c>
       <c r="F141" t="n">
-        <v>468.663467</v>
+        <v>0.09809725</v>
       </c>
       <c r="G141" t="n">
-        <v>549.045074</v>
+        <v>0.000282</v>
       </c>
       <c r="H141" t="n">
-        <v>698.619945</v>
-      </c>
-      <c r="I141" t="n">
-        <v>479.877796</v>
-      </c>
+        <v>3e-06</v>
+      </c>
+      <c r="I141" t="inlineStr"/>
       <c r="J141" t="n">
-        <v>399.799791</v>
+        <v>0.000288</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右上上櫃</t>
+          <t>電器電纜右上上市</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.14244</v>
+        <v>1437.331486</v>
       </c>
       <c r="C142" t="n">
-        <v>0.089825</v>
+        <v>1121.222264</v>
       </c>
       <c r="D142" t="n">
-        <v>0.08122</v>
+        <v>640.157403</v>
       </c>
       <c r="E142" t="n">
-        <v>0.06408899999999999</v>
+        <v>468.663467</v>
       </c>
       <c r="F142" t="n">
-        <v>0.077725</v>
+        <v>549.045074</v>
       </c>
       <c r="G142" t="n">
-        <v>0.063419</v>
+        <v>698.619945</v>
       </c>
       <c r="H142" t="n">
-        <v>0.06467100000000001</v>
+        <v>479.877796</v>
       </c>
       <c r="I142" t="n">
-        <v>0.14235</v>
+        <v>399.799791</v>
       </c>
       <c r="J142" t="n">
-        <v>0.20836</v>
+        <v>784.829217</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>電器電纜右下上市</t>
+          <t>電器電纜右上上櫃</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>95.418598</v>
+        <v>0.089825</v>
       </c>
       <c r="C143" t="n">
-        <v>52.871653</v>
+        <v>0.08122</v>
       </c>
       <c r="D143" t="n">
-        <v>81.429742</v>
+        <v>0.06408899999999999</v>
       </c>
       <c r="E143" t="n">
-        <v>56.265111</v>
+        <v>0.077725</v>
       </c>
       <c r="F143" t="n">
-        <v>50.845094</v>
+        <v>0.063419</v>
       </c>
       <c r="G143" t="n">
-        <v>64.46852199999999</v>
+        <v>0.06467100000000001</v>
       </c>
       <c r="H143" t="n">
-        <v>144.640413</v>
+        <v>0.14235</v>
       </c>
       <c r="I143" t="n">
-        <v>52.136607</v>
+        <v>0.20836</v>
       </c>
       <c r="J143" t="n">
-        <v>104.102574</v>
+        <v>0.106769</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>電器電纜平上市</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr"/>
+          <t>電器電纜右下上市</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>52.871653</v>
+      </c>
       <c r="C144" t="n">
-        <v>140.144075</v>
+        <v>81.429742</v>
       </c>
       <c r="D144" t="n">
-        <v>138.823516</v>
+        <v>56.265111</v>
       </c>
       <c r="E144" t="n">
-        <v>84.123322</v>
+        <v>50.845094</v>
       </c>
       <c r="F144" t="n">
-        <v>88.273901</v>
+        <v>64.46852199999999</v>
       </c>
       <c r="G144" t="n">
-        <v>106.428955</v>
+        <v>144.640413</v>
       </c>
       <c r="H144" t="n">
-        <v>88.783907</v>
+        <v>52.136607</v>
       </c>
       <c r="I144" t="n">
-        <v>65.779991</v>
+        <v>104.102574</v>
       </c>
       <c r="J144" t="n">
-        <v>11.536856</v>
+        <v>375.35883</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右上上市</t>
+          <t>電器電纜平上市</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>5943.805008</v>
+        <v>140.144075</v>
       </c>
       <c r="C145" t="n">
-        <v>5352.027379</v>
+        <v>138.823516</v>
       </c>
       <c r="D145" t="n">
-        <v>4216.801423</v>
+        <v>84.123322</v>
       </c>
       <c r="E145" t="n">
-        <v>3310.887283</v>
+        <v>88.273901</v>
       </c>
       <c r="F145" t="n">
-        <v>3481.54415</v>
+        <v>106.428955</v>
       </c>
       <c r="G145" t="n">
-        <v>4224.814142</v>
+        <v>88.783907</v>
       </c>
       <c r="H145" t="n">
-        <v>5680.179409</v>
+        <v>65.779991</v>
       </c>
       <c r="I145" t="n">
-        <v>3647.395464</v>
+        <v>11.536856</v>
       </c>
       <c r="J145" t="n">
-        <v>4527.099155</v>
+        <v>54.088797</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右上上櫃</t>
+          <t>電子通路業右上上市</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.14276</v>
+        <v>5352.027379</v>
       </c>
       <c r="C146" t="n">
-        <v>0.08462</v>
+        <v>4216.801423</v>
       </c>
       <c r="D146" t="n">
-        <v>0.096876</v>
+        <v>3310.887283</v>
       </c>
       <c r="E146" t="n">
-        <v>0.06115</v>
+        <v>3481.54415</v>
       </c>
       <c r="F146" t="n">
-        <v>0.065174</v>
+        <v>4224.814142</v>
       </c>
       <c r="G146" t="n">
-        <v>0.08644300000000001</v>
+        <v>5680.179409</v>
       </c>
       <c r="H146" t="n">
-        <v>0.05964</v>
+        <v>3647.395464</v>
       </c>
       <c r="I146" t="n">
-        <v>0.063456</v>
+        <v>4585.960621</v>
       </c>
       <c r="J146" t="n">
-        <v>0.101268</v>
+        <v>4559.281146</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右下上市</t>
+          <t>電子通路業右上上櫃</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>10.41061</v>
+        <v>0.08462</v>
       </c>
       <c r="C147" t="n">
-        <v>9.936412000000001</v>
+        <v>0.096876</v>
       </c>
       <c r="D147" t="n">
-        <v>28.982313</v>
+        <v>0.06115</v>
       </c>
       <c r="E147" t="n">
-        <v>21.588764</v>
+        <v>0.065174</v>
       </c>
       <c r="F147" t="n">
-        <v>18.532432</v>
+        <v>0.08644300000000001</v>
       </c>
       <c r="G147" t="n">
-        <v>24.553908</v>
+        <v>0.05964</v>
       </c>
       <c r="H147" t="n">
-        <v>23.830889</v>
+        <v>0.063456</v>
       </c>
       <c r="I147" t="n">
-        <v>14.305895</v>
+        <v>0.101268</v>
       </c>
       <c r="J147" t="n">
-        <v>13.714789</v>
+        <v>0.098093</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>電子通路業右下上櫃</t>
+          <t>電子通路業右下上市</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.018248</v>
+        <v>9.936412000000001</v>
       </c>
       <c r="C148" t="n">
-        <v>0.014132</v>
+        <v>28.982313</v>
       </c>
       <c r="D148" t="n">
-        <v>0.01328775</v>
+        <v>21.588764</v>
       </c>
       <c r="E148" t="n">
-        <v>0.023617</v>
+        <v>18.532432</v>
       </c>
       <c r="F148" t="n">
-        <v>0.024176</v>
+        <v>24.553908</v>
       </c>
       <c r="G148" t="n">
-        <v>0.012349</v>
+        <v>23.830889</v>
       </c>
       <c r="H148" t="n">
-        <v>0.01372</v>
+        <v>14.305895</v>
       </c>
       <c r="I148" t="n">
-        <v>0.014394</v>
+        <v>13.714789</v>
       </c>
       <c r="J148" t="n">
-        <v>0.013219</v>
+        <v>32.735762</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>電子通路業平上市</t>
+          <t>電子通路業右下上櫃</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>65.88053499999999</v>
+        <v>0.014132</v>
       </c>
       <c r="C149" t="n">
-        <v>105.135225</v>
+        <v>0.01328775</v>
       </c>
       <c r="D149" t="n">
-        <v>99.78953</v>
+        <v>0.023617</v>
       </c>
       <c r="E149" t="n">
-        <v>72.068825</v>
+        <v>0.024176</v>
       </c>
       <c r="F149" t="n">
-        <v>46.423877</v>
+        <v>0.012349</v>
       </c>
       <c r="G149" t="n">
-        <v>51.386202</v>
+        <v>0.01372</v>
       </c>
       <c r="H149" t="n">
-        <v>116.507832</v>
+        <v>0.014394</v>
       </c>
       <c r="I149" t="n">
-        <v>61.506774</v>
+        <v>0.013219</v>
       </c>
       <c r="J149" t="n">
-        <v>48.141145</v>
+        <v>0.015071</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>電子通路業平上櫃</t>
+          <t>電子通路業平上市</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.2213</v>
+        <v>105.135225</v>
       </c>
       <c r="C150" t="n">
-        <v>0.121082</v>
+        <v>99.78953</v>
       </c>
       <c r="D150" t="n">
-        <v>0.199947</v>
+        <v>72.068825</v>
       </c>
       <c r="E150" t="n">
-        <v>0.140783</v>
+        <v>46.423877</v>
       </c>
       <c r="F150" t="n">
-        <v>0.132337</v>
+        <v>51.386202</v>
       </c>
       <c r="G150" t="n">
-        <v>0.169785</v>
+        <v>116.507832</v>
       </c>
       <c r="H150" t="n">
-        <v>0.17559</v>
+        <v>61.506774</v>
       </c>
       <c r="I150" t="n">
-        <v>0.169128</v>
+        <v>48.141145</v>
       </c>
       <c r="J150" t="n">
-        <v>0.190272</v>
+        <v>114.882025</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右上上市</t>
+          <t>電子通路業平上櫃</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>304889.285723</v>
+        <v>0.121082</v>
       </c>
       <c r="C151" t="n">
-        <v>199573.807519</v>
+        <v>0.199947</v>
       </c>
       <c r="D151" t="n">
-        <v>205300.203721</v>
+        <v>0.140783</v>
       </c>
       <c r="E151" t="n">
-        <v>209163.855494</v>
+        <v>0.132337</v>
       </c>
       <c r="F151" t="n">
-        <v>223851.764794</v>
+        <v>0.169785</v>
       </c>
       <c r="G151" t="n">
-        <v>255646.88146</v>
+        <v>0.17559</v>
       </c>
       <c r="H151" t="n">
-        <v>269694.18557</v>
+        <v>0.169128</v>
       </c>
       <c r="I151" t="n">
-        <v>183651.583309</v>
+        <v>0.190272</v>
       </c>
       <c r="J151" t="n">
-        <v>178535.50686</v>
+        <v>0.176671</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右上上櫃</t>
+          <t>電子零組件業右上上市</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>66.413197</v>
+        <v>199573.807519</v>
       </c>
       <c r="C152" t="n">
-        <v>68.66043633333332</v>
+        <v>205300.203721</v>
       </c>
       <c r="D152" t="n">
-        <v>79.239329</v>
+        <v>209163.855494</v>
       </c>
       <c r="E152" t="n">
-        <v>85.90924200000001</v>
+        <v>223851.764794</v>
       </c>
       <c r="F152" t="n">
-        <v>85.52268866666667</v>
+        <v>255646.88146</v>
       </c>
       <c r="G152" t="n">
-        <v>87.55076699999999</v>
+        <v>269694.18557</v>
       </c>
       <c r="H152" t="n">
-        <v>46.793764</v>
+        <v>183651.583309</v>
       </c>
       <c r="I152" t="n">
-        <v>32.517482</v>
+        <v>179731.39186</v>
       </c>
       <c r="J152" t="n">
-        <v>44.820265</v>
+        <v>145011.883366</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右下上市</t>
+          <t>電子零組件業右上上櫃</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>1778.770117</v>
+        <v>68.66043633333332</v>
       </c>
       <c r="C153" t="n">
-        <v>1610.391026</v>
+        <v>79.239329</v>
       </c>
       <c r="D153" t="n">
-        <v>1986.703971</v>
+        <v>85.90924200000001</v>
       </c>
       <c r="E153" t="n">
-        <v>1729.714195</v>
+        <v>85.52268866666667</v>
       </c>
       <c r="F153" t="n">
-        <v>1585.133452</v>
+        <v>87.55076699999999</v>
       </c>
       <c r="G153" t="n">
-        <v>1437.164907</v>
+        <v>46.793764</v>
       </c>
       <c r="H153" t="n">
-        <v>3305.876797</v>
+        <v>32.517482</v>
       </c>
       <c r="I153" t="n">
-        <v>925.1294779999999</v>
+        <v>44.820265</v>
       </c>
       <c r="J153" t="n">
-        <v>2508.546971</v>
+        <v>31.981373</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業右下上櫃</t>
+          <t>電子零組件業右下上市</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.541832</v>
+        <v>1610.391026</v>
       </c>
       <c r="C154" t="n">
-        <v>0.465636</v>
+        <v>1986.703971</v>
       </c>
       <c r="D154" t="n">
-        <v>0.559515</v>
+        <v>1729.714195</v>
       </c>
       <c r="E154" t="n">
-        <v>0.472442</v>
+        <v>1585.133452</v>
       </c>
       <c r="F154" t="n">
-        <v>0.343509</v>
+        <v>1437.164907</v>
       </c>
       <c r="G154" t="n">
-        <v>0.582906</v>
+        <v>3305.876797</v>
       </c>
       <c r="H154" t="n">
-        <v>0.54318475</v>
+        <v>925.1294779999999</v>
       </c>
       <c r="I154" t="n">
-        <v>0.57746</v>
+        <v>2508.546971</v>
       </c>
       <c r="J154" t="n">
-        <v>0.55032525</v>
+        <v>2881.891331</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業平上市</t>
+          <t>電子零組件業右下上櫃</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>6820.63797</v>
+        <v>0.465636</v>
       </c>
       <c r="C155" t="n">
-        <v>5748.740213</v>
+        <v>0.559515</v>
       </c>
       <c r="D155" t="n">
-        <v>3979.847094</v>
+        <v>0.472442</v>
       </c>
       <c r="E155" t="n">
-        <v>4143.613972</v>
+        <v>0.343509</v>
       </c>
       <c r="F155" t="n">
-        <v>3268.133056</v>
+        <v>0.582906</v>
       </c>
       <c r="G155" t="n">
-        <v>29016.078938</v>
+        <v>0.54318475</v>
       </c>
       <c r="H155" t="n">
-        <v>2304.113488</v>
+        <v>0.57746</v>
       </c>
       <c r="I155" t="n">
-        <v>1520.305843</v>
+        <v>0.55032525</v>
       </c>
       <c r="J155" t="n">
-        <v>27911.52985</v>
+        <v>0.789147</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>電子零組件業平上櫃</t>
+          <t>電子零組件業平上市</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.469598</v>
+        <v>5748.740213</v>
       </c>
       <c r="C156" t="n">
-        <v>0.437764</v>
+        <v>3979.847094</v>
       </c>
       <c r="D156" t="n">
-        <v>0.340724</v>
+        <v>4143.613972</v>
       </c>
       <c r="E156" t="n">
-        <v>0.254331</v>
+        <v>3268.133056</v>
       </c>
       <c r="F156" t="n">
-        <v>0.330163</v>
+        <v>29016.078938</v>
       </c>
       <c r="G156" t="n">
-        <v>0.526743</v>
+        <v>2304.113488</v>
       </c>
       <c r="H156" t="n">
-        <v>0.56113</v>
+        <v>1520.305843</v>
       </c>
       <c r="I156" t="n">
-        <v>0.203102</v>
+        <v>28070.809591</v>
       </c>
       <c r="J156" t="n">
-        <v>0.50391825</v>
+        <v>58692.393457</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>電機機械右上上市</t>
+          <t>電子零組件業平上櫃</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>21922.178132</v>
+        <v>0.437764</v>
       </c>
       <c r="C157" t="n">
-        <v>21596.455042</v>
+        <v>0.340724</v>
       </c>
       <c r="D157" t="n">
-        <v>17643.132366</v>
+        <v>0.254331</v>
       </c>
       <c r="E157" t="n">
-        <v>10308.66158</v>
+        <v>0.330163</v>
       </c>
       <c r="F157" t="n">
-        <v>15560.961724</v>
+        <v>0.526743</v>
       </c>
       <c r="G157" t="n">
-        <v>16569.032242</v>
+        <v>0.56113</v>
       </c>
       <c r="H157" t="n">
-        <v>17342.985461</v>
+        <v>0.203102</v>
       </c>
       <c r="I157" t="n">
-        <v>18400.061234</v>
+        <v>0.50391825</v>
       </c>
       <c r="J157" t="n">
-        <v>17863.67929</v>
+        <v>0.8342889999999999</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>電機機械右上上櫃</t>
+          <t>電機機械右上上市</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0.898227</v>
+        <v>21596.455042</v>
       </c>
       <c r="C158" t="n">
-        <v>0.6324689999999999</v>
+        <v>17643.132366</v>
       </c>
       <c r="D158" t="n">
-        <v>0.569712</v>
+        <v>10308.66158</v>
       </c>
       <c r="E158" t="n">
-        <v>0.685992</v>
+        <v>15560.961724</v>
       </c>
       <c r="F158" t="n">
-        <v>0.847919</v>
+        <v>16569.032242</v>
       </c>
       <c r="G158" t="n">
-        <v>0.877193</v>
+        <v>17342.985461</v>
       </c>
       <c r="H158" t="n">
-        <v>0.600058</v>
+        <v>18400.061234</v>
       </c>
       <c r="I158" t="n">
-        <v>0.9077769999999999</v>
+        <v>17863.67929</v>
       </c>
       <c r="J158" t="n">
-        <v>0.632109</v>
+        <v>14376.520782</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>電機機械右下上市</t>
+          <t>電機機械右上上櫃</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>2616.797834</v>
+        <v>0.6324689999999999</v>
       </c>
       <c r="C159" t="n">
-        <v>1023.422566</v>
+        <v>0.569712</v>
       </c>
       <c r="D159" t="n">
-        <v>1469.13372</v>
+        <v>0.685992</v>
       </c>
       <c r="E159" t="n">
-        <v>1210.84740475</v>
+        <v>0.847919</v>
       </c>
       <c r="F159" t="n">
-        <v>1200.857364</v>
+        <v>0.877193</v>
       </c>
       <c r="G159" t="n">
-        <v>990.296252</v>
+        <v>0.600058</v>
       </c>
       <c r="H159" t="n">
-        <v>2627.372428</v>
+        <v>0.9077769999999999</v>
       </c>
       <c r="I159" t="n">
-        <v>1174.272544</v>
+        <v>0.632109</v>
       </c>
       <c r="J159" t="n">
-        <v>1421.980219</v>
+        <v>0.656118</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>電機機械右下上櫃</t>
+          <t>電機機械右下上市</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>0.144987</v>
+        <v>1023.422566</v>
       </c>
       <c r="C160" t="n">
-        <v>0.0796785</v>
+        <v>1469.13372</v>
       </c>
       <c r="D160" t="n">
-        <v>0.091709</v>
+        <v>1210.84740475</v>
       </c>
       <c r="E160" t="n">
-        <v>0.07321133333333332</v>
+        <v>1200.857364</v>
       </c>
       <c r="F160" t="n">
-        <v>0.12867</v>
+        <v>990.296252</v>
       </c>
       <c r="G160" t="n">
-        <v>0.134474</v>
+        <v>2627.372428</v>
       </c>
       <c r="H160" t="n">
-        <v>0.111127</v>
+        <v>1174.272544</v>
       </c>
       <c r="I160" t="n">
-        <v>0.099802</v>
+        <v>1421.980219</v>
       </c>
       <c r="J160" t="n">
-        <v>0.188266</v>
+        <v>2169.569959</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>電機機械平上市</t>
+          <t>電機機械右下上櫃</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>2132.066124</v>
+        <v>0.0796785</v>
       </c>
       <c r="C161" t="n">
-        <v>1486.959468</v>
+        <v>0.091709</v>
       </c>
       <c r="D161" t="n">
-        <v>1947.052022</v>
+        <v>0.07321133333333332</v>
       </c>
       <c r="E161" t="n">
-        <v>2898.624755</v>
+        <v>0.12867</v>
       </c>
       <c r="F161" t="n">
-        <v>2124.416782</v>
+        <v>0.134474</v>
       </c>
       <c r="G161" t="n">
-        <v>1727.728272</v>
+        <v>0.111127</v>
       </c>
       <c r="H161" t="n">
-        <v>3330.957109</v>
+        <v>0.099802</v>
       </c>
       <c r="I161" t="n">
-        <v>1247.567523</v>
+        <v>0.188266</v>
       </c>
       <c r="J161" t="n">
-        <v>1450.331249</v>
+        <v>0.167666</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>電機機械平上櫃</t>
+          <t>電機機械平上市</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>0.11245</v>
+        <v>1486.959468</v>
       </c>
       <c r="C162" t="n">
-        <v>0.085339</v>
+        <v>1947.052022</v>
       </c>
       <c r="D162" t="n">
-        <v>0.112254</v>
+        <v>2898.624755</v>
       </c>
       <c r="E162" t="n">
-        <v>0.196656</v>
+        <v>2124.416782</v>
       </c>
       <c r="F162" t="n">
-        <v>0.059169</v>
+        <v>1727.728272</v>
       </c>
       <c r="G162" t="n">
-        <v>0.216698</v>
+        <v>3330.957109</v>
       </c>
       <c r="H162" t="n">
-        <v>0.145061</v>
+        <v>1247.567523</v>
       </c>
       <c r="I162" t="n">
-        <v>0.244256</v>
+        <v>1450.331249</v>
       </c>
       <c r="J162" t="n">
-        <v>0.09064800000000001</v>
+        <v>1929.571973</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上上市</t>
+          <t>電機機械平上櫃</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>55753.091306</v>
+        <v>0.085339</v>
       </c>
       <c r="C163" t="n">
-        <v>42056.973253</v>
+        <v>0.112254</v>
       </c>
       <c r="D163" t="n">
-        <v>37134.374792</v>
+        <v>0.196656</v>
       </c>
       <c r="E163" t="n">
-        <v>45284.793045</v>
+        <v>0.059169</v>
       </c>
       <c r="F163" t="n">
-        <v>52953.900936</v>
+        <v>0.216698</v>
       </c>
       <c r="G163" t="n">
-        <v>35158.19108</v>
+        <v>0.145061</v>
       </c>
       <c r="H163" t="n">
-        <v>45253.003247</v>
+        <v>0.244256</v>
       </c>
       <c r="I163" t="n">
-        <v>34886.42037</v>
+        <v>0.09064800000000001</v>
       </c>
       <c r="J163" t="n">
-        <v>37504.351616</v>
+        <v>0.142591</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上上櫃</t>
+          <t>電腦及週邊設備業右上上市</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>6.122937</v>
+        <v>42056.973253</v>
       </c>
       <c r="C164" t="n">
-        <v>4.828848</v>
+        <v>37029.810994</v>
       </c>
       <c r="D164" t="n">
-        <v>4.39085</v>
+        <v>45284.793045</v>
       </c>
       <c r="E164" t="n">
-        <v>3.992018</v>
+        <v>52953.900936</v>
       </c>
       <c r="F164" t="n">
-        <v>4.706055</v>
+        <v>35158.19108</v>
       </c>
       <c r="G164" t="n">
-        <v>6.825057</v>
+        <v>45253.003247</v>
       </c>
       <c r="H164" t="n">
-        <v>5.063657</v>
+        <v>34886.42037</v>
       </c>
       <c r="I164" t="n">
-        <v>7.290765</v>
+        <v>37730.002713</v>
       </c>
       <c r="J164" t="n">
-        <v>5.758477</v>
+        <v>43206.995955</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上市</t>
+          <t>電腦及週邊設備業右上上櫃</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>20500.120576</v>
+        <v>4.828848</v>
       </c>
       <c r="C165" t="n">
-        <v>26410.760531</v>
+        <v>4.39085</v>
       </c>
       <c r="D165" t="n">
-        <v>13215.001859</v>
+        <v>3.992018</v>
       </c>
       <c r="E165" t="n">
-        <v>10256.003434</v>
+        <v>4.706055</v>
       </c>
       <c r="F165" t="n">
-        <v>12710.957755</v>
+        <v>6.825057</v>
       </c>
       <c r="G165" t="n">
-        <v>9663.959551</v>
+        <v>5.063657</v>
       </c>
       <c r="H165" t="n">
-        <v>10831.789233</v>
+        <v>7.290765</v>
       </c>
       <c r="I165" t="n">
-        <v>7673.8907</v>
+        <v>5.758477</v>
       </c>
       <c r="J165" t="n">
-        <v>7164.955578</v>
+        <v>5.849827</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上櫃</t>
+          <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>0.265974</v>
+        <v>26410.760531</v>
       </c>
       <c r="C166" t="n">
-        <v>0.253577</v>
+        <v>13215.001859</v>
       </c>
       <c r="D166" t="n">
-        <v>0.238332</v>
+        <v>10256.003434</v>
       </c>
       <c r="E166" t="n">
-        <v>0.12927775</v>
+        <v>12710.957755</v>
       </c>
       <c r="F166" t="n">
-        <v>0.120142</v>
+        <v>9663.959551</v>
       </c>
       <c r="G166" t="n">
-        <v>0.337804</v>
+        <v>10831.789233</v>
       </c>
       <c r="H166" t="n">
-        <v>0.286702</v>
+        <v>7673.8907</v>
       </c>
       <c r="I166" t="n">
-        <v>0.188646</v>
+        <v>7164.955578</v>
       </c>
       <c r="J166" t="n">
-        <v>0.142492</v>
+        <v>10660.822788</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上市</t>
+          <t>電腦及週邊設備業右下上櫃</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>3850.866249</v>
+        <v>0.253577</v>
       </c>
       <c r="C167" t="n">
-        <v>2010.607199</v>
+        <v>0.238332</v>
       </c>
       <c r="D167" t="n">
-        <v>1849.664547</v>
+        <v>0.12927775</v>
       </c>
       <c r="E167" t="n">
-        <v>1437.304534</v>
+        <v>0.120142</v>
       </c>
       <c r="F167" t="n">
-        <v>2068.85697</v>
+        <v>0.337804</v>
       </c>
       <c r="G167" t="n">
-        <v>2373.833127</v>
+        <v>0.286702</v>
       </c>
       <c r="H167" t="n">
-        <v>1690.235424</v>
+        <v>0.188646</v>
       </c>
       <c r="I167" t="n">
-        <v>1309.380951</v>
+        <v>0.142492</v>
       </c>
       <c r="J167" t="n">
-        <v>1863.972776</v>
+        <v>0.268683</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上櫃</t>
+          <t>電腦及週邊設備業平上市</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>1.867231</v>
+        <v>2010.607199</v>
       </c>
       <c r="C168" t="n">
-        <v>0.8304</v>
+        <v>1954.228345</v>
       </c>
       <c r="D168" t="n">
-        <v>1.067919</v>
+        <v>1437.304534</v>
       </c>
       <c r="E168" t="n">
-        <v>1.006393</v>
+        <v>2068.85697</v>
       </c>
       <c r="F168" t="n">
-        <v>1.488073</v>
+        <v>2373.833127</v>
       </c>
       <c r="G168" t="n">
-        <v>1.226363</v>
+        <v>1690.235424</v>
       </c>
       <c r="H168" t="n">
-        <v>0.804508</v>
+        <v>1309.380951</v>
       </c>
       <c r="I168" t="n">
-        <v>0.939728</v>
+        <v>1784.896099</v>
       </c>
       <c r="J168" t="n">
-        <v>0.712465</v>
+        <v>1458.15114</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>食品工業右上上市</t>
+          <t>電腦及週邊設備業平上櫃</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>3139.295951</v>
+        <v>0.8304</v>
       </c>
       <c r="C169" t="n">
-        <v>1291.778888</v>
+        <v>1.067919</v>
       </c>
       <c r="D169" t="n">
-        <v>1359.323921</v>
+        <v>1.006393</v>
       </c>
       <c r="E169" t="n">
-        <v>839.6985069999999</v>
+        <v>1.488073</v>
       </c>
       <c r="F169" t="n">
-        <v>894.768297</v>
+        <v>1.226363</v>
       </c>
       <c r="G169" t="n">
-        <v>815.884941</v>
+        <v>0.804508</v>
       </c>
       <c r="H169" t="n">
-        <v>1400.862561</v>
+        <v>0.939728</v>
       </c>
       <c r="I169" t="n">
-        <v>527.488537</v>
+        <v>0.712465</v>
       </c>
       <c r="J169" t="n">
-        <v>555.074196</v>
+        <v>1.772974</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>食品工業右上上櫃</t>
+          <t>食品工業右上上市</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>0.022387</v>
+        <v>1291.778888</v>
       </c>
       <c r="C170" t="n">
-        <v>0.011223</v>
+        <v>1359.323921</v>
       </c>
       <c r="D170" t="n">
-        <v>0.002333</v>
+        <v>839.6985069999999</v>
       </c>
       <c r="E170" t="n">
-        <v>0.005333</v>
+        <v>894.768297</v>
       </c>
       <c r="F170" t="n">
-        <v>0.004641</v>
+        <v>815.884941</v>
       </c>
       <c r="G170" t="n">
-        <v>0.001331</v>
+        <v>1400.862561</v>
       </c>
       <c r="H170" t="n">
-        <v>0.0007470000000000001</v>
+        <v>527.488537</v>
       </c>
       <c r="I170" t="n">
-        <v>0.003183</v>
-      </c>
-      <c r="J170" t="inlineStr"/>
+        <v>555.074196</v>
+      </c>
+      <c r="J170" t="n">
+        <v>1249.208206</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t>食品工業右下上市</t>
+          <t>食品工業右上上櫃</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>551.697779</v>
+        <v>0.011223</v>
       </c>
       <c r="C171" t="n">
-        <v>297.861558</v>
+        <v>0.011231</v>
       </c>
       <c r="D171" t="n">
-        <v>319.044069</v>
+        <v>0.005333</v>
       </c>
       <c r="E171" t="n">
-        <v>351.382043</v>
+        <v>0.004641</v>
       </c>
       <c r="F171" t="n">
-        <v>245.046335</v>
+        <v>0.001331</v>
       </c>
       <c r="G171" t="n">
-        <v>200.925126</v>
+        <v>0.0007470000000000001</v>
       </c>
       <c r="H171" t="n">
-        <v>891.332178</v>
-      </c>
-      <c r="I171" t="n">
-        <v>380.624011</v>
-      </c>
-      <c r="J171" t="n">
-        <v>252.00198375</v>
-      </c>
+        <v>0.003183</v>
+      </c>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t>食品工業右下上櫃</t>
+          <t>食品工業右下上市</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>0.013137</v>
+        <v>297.861558</v>
       </c>
       <c r="C172" t="n">
-        <v>0.006357</v>
+        <v>319.044069</v>
       </c>
       <c r="D172" t="n">
-        <v>0.013048</v>
+        <v>351.382043</v>
       </c>
       <c r="E172" t="n">
-        <v>0.006316</v>
+        <v>245.046335</v>
       </c>
       <c r="F172" t="n">
-        <v>0.007833</v>
+        <v>200.925126</v>
       </c>
       <c r="G172" t="n">
-        <v>0.007666</v>
+        <v>891.332178</v>
       </c>
       <c r="H172" t="n">
-        <v>0.008423999999999999</v>
+        <v>380.624011</v>
       </c>
       <c r="I172" t="n">
-        <v>0.008969</v>
+        <v>252.00198375</v>
       </c>
       <c r="J172" t="n">
-        <v>0.008723</v>
+        <v>362.72842</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
         <is>
-          <t>食品工業平上市</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr"/>
-      <c r="C173" t="inlineStr"/>
-      <c r="D173" t="inlineStr"/>
-      <c r="E173" t="inlineStr"/>
+          <t>食品工業右下上櫃</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>0.006357</v>
+      </c>
+      <c r="C173" t="n">
+        <v>0.013048</v>
+      </c>
+      <c r="D173" t="n">
+        <v>0.006316</v>
+      </c>
+      <c r="E173" t="n">
+        <v>0.007833</v>
+      </c>
       <c r="F173" t="n">
-        <v>0.735418</v>
-      </c>
-      <c r="G173" t="inlineStr"/>
-      <c r="H173" t="inlineStr"/>
-      <c r="I173" t="inlineStr"/>
-      <c r="J173" t="inlineStr"/>
+        <v>0.007666</v>
+      </c>
+      <c r="G173" t="n">
+        <v>0.008423999999999999</v>
+      </c>
+      <c r="H173" t="n">
+        <v>0.008969</v>
+      </c>
+      <c r="I173" t="n">
+        <v>0.008723</v>
+      </c>
+      <c r="J173" t="n">
+        <v>0.01514</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
         <is>
+          <t>食品工業平上市</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr"/>
+      <c r="C174" t="inlineStr"/>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="n">
+        <v>0.735418</v>
+      </c>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="n">
+        <v>78.273599</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="inlineStr">
+        <is>
           <t>食品工業平上櫃</t>
         </is>
       </c>
-      <c r="B174" t="n">
-        <v>0.003119</v>
-      </c>
-      <c r="C174" t="n">
+      <c r="B175" t="n">
         <v>0.001706</v>
       </c>
-      <c r="D174" t="n">
-        <v>0.01092</v>
-      </c>
-      <c r="E174" t="n">
+      <c r="C175" t="n">
+        <v>0.002022</v>
+      </c>
+      <c r="D175" t="n">
         <v>0.001098</v>
       </c>
-      <c r="F174" t="n">
+      <c r="E175" t="n">
         <v>0.000977</v>
       </c>
-      <c r="G174" t="n">
+      <c r="F175" t="n">
         <v>0.005867</v>
       </c>
-      <c r="H174" t="n">
+      <c r="G175" t="n">
         <v>0.001971</v>
       </c>
-      <c r="I174" t="n">
+      <c r="H175" t="n">
         <v>0.000494</v>
       </c>
-      <c r="J174" t="n">
+      <c r="I175" t="n">
         <v>0.001825</v>
+      </c>
+      <c r="J175" t="n">
+        <v>0.00037</v>
       </c>
     </row>
   </sheetData>
